--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -9,6 +9,7 @@
     <sheet name="②製作図リスト" sheetId="2" r:id="rId6"/>
     <sheet name="③計画書要領書リスト" sheetId="3" r:id="rId7"/>
   </sheets>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -9588,7 +9589,9 @@
       <c r="K12" s="158">
         <v>7</v>
       </c>
-      <c r="L12" s="161"/>
+      <c r="L12" s="161">
+        <v>46302</v>
+      </c>
       <c r="M12" s="161"/>
       <c r="N12" s="161"/>
       <c r="O12" s="161"/>
@@ -22791,7 +22794,9 @@
       <c r="K13" s="158">
         <v>7</v>
       </c>
-      <c r="L13" s="161"/>
+      <c r="L13" s="161">
+        <v>46302</v>
+      </c>
       <c r="M13" s="161"/>
       <c r="N13" s="161"/>
       <c r="O13" s="161"/>
@@ -22991,7 +22996,9 @@
       <c r="K15" s="158">
         <v>7</v>
       </c>
-      <c r="L15" s="161"/>
+      <c r="L15" s="161">
+        <v>46302</v>
+      </c>
       <c r="M15" s="161"/>
       <c r="N15" s="161"/>
       <c r="O15" s="161"/>
@@ -23357,7 +23364,9 @@
       <c r="K19" s="158">
         <v>7</v>
       </c>
-      <c r="L19" s="161"/>
+      <c r="L19" s="161">
+        <v>46302</v>
+      </c>
       <c r="M19" s="161"/>
       <c r="N19" s="161"/>
       <c r="O19" s="161"/>
@@ -23549,8 +23558,12 @@
         <v>46293</v>
       </c>
       <c r="M21" s="161"/>
-      <c r="N21" s="161"/>
-      <c r="O21" s="161"/>
+      <c r="N21" s="161">
+        <v>46297</v>
+      </c>
+      <c r="O21" s="161">
+        <v>46304</v>
+      </c>
       <c r="P21" s="161" cm="1">
         <f t="array" ref="P21">IF(AG21="","",AC21-R21-Q21)</f>
         <v>46289</v>
@@ -23818,8 +23831,12 @@
         <v>46293</v>
       </c>
       <c r="M24" s="161"/>
-      <c r="N24" s="161"/>
-      <c r="O24" s="161"/>
+      <c r="N24" s="161">
+        <v>46297</v>
+      </c>
+      <c r="O24" s="161">
+        <v>46304</v>
+      </c>
       <c r="P24" s="161" cm="1">
         <f t="array" ref="P24">IF(AG24="","",AC24-R24-Q24)</f>
         <v>46283</v>
@@ -24000,7 +24017,9 @@
       <c r="K26" s="158">
         <v>7</v>
       </c>
-      <c r="L26" s="161"/>
+      <c r="L26" s="161">
+        <v>46301</v>
+      </c>
       <c r="M26" s="161"/>
       <c r="N26" s="161"/>
       <c r="O26" s="161"/>
@@ -24490,7 +24509,9 @@
       <c r="L31" s="161">
         <v>46293</v>
       </c>
-      <c r="M31" s="161"/>
+      <c r="M31" s="161">
+        <v>46303</v>
+      </c>
       <c r="N31" s="161"/>
       <c r="O31" s="161"/>
       <c r="P31" s="161" cm="1">
@@ -24673,7 +24694,9 @@
       <c r="K33" s="158">
         <v>7</v>
       </c>
-      <c r="L33" s="161"/>
+      <c r="L33" s="161">
+        <v>46296</v>
+      </c>
       <c r="M33" s="161"/>
       <c r="N33" s="161"/>
       <c r="O33" s="161"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -9966,7 +9966,9 @@
       <c r="R16" s="162">
         <v>14</v>
       </c>
-      <c r="S16" s="161"/>
+      <c r="S16" s="161">
+        <v>46303</v>
+      </c>
       <c r="T16" s="161"/>
       <c r="U16" s="161"/>
       <c r="V16" s="161"/>
@@ -23561,9 +23563,7 @@
       <c r="N21" s="161">
         <v>46297</v>
       </c>
-      <c r="O21" s="161">
-        <v>46304</v>
-      </c>
+      <c r="O21" s="161"/>
       <c r="P21" s="161" cm="1">
         <f t="array" ref="P21">IF(AG21="","",AC21-R21-Q21)</f>
         <v>46289</v>
@@ -23834,9 +23834,7 @@
       <c r="N24" s="161">
         <v>46297</v>
       </c>
-      <c r="O24" s="161">
-        <v>46304</v>
-      </c>
+      <c r="O24" s="161"/>
       <c r="P24" s="161" cm="1">
         <f t="array" ref="P24">IF(AG24="","",AC24-R24-Q24)</f>
         <v>46283</v>
@@ -24509,9 +24507,7 @@
       <c r="L31" s="161">
         <v>46293</v>
       </c>
-      <c r="M31" s="161">
-        <v>46303</v>
-      </c>
+      <c r="M31" s="161"/>
       <c r="N31" s="161"/>
       <c r="O31" s="161"/>
       <c r="P31" s="161" cm="1">

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -9966,9 +9966,7 @@
       <c r="R16" s="162">
         <v>14</v>
       </c>
-      <c r="S16" s="161">
-        <v>46303</v>
-      </c>
+      <c r="S16" s="161"/>
       <c r="T16" s="161"/>
       <c r="U16" s="161"/>
       <c r="V16" s="161"/>
@@ -23561,7 +23559,7 @@
       </c>
       <c r="M21" s="161"/>
       <c r="N21" s="161">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="O21" s="161"/>
       <c r="P21" s="161" cm="1">
@@ -23832,7 +23830,7 @@
       </c>
       <c r="M24" s="161"/>
       <c r="N24" s="161">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="O24" s="161"/>
       <c r="P24" s="161" cm="1">
@@ -24016,7 +24014,7 @@
         <v>7</v>
       </c>
       <c r="L26" s="161">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M26" s="161"/>
       <c r="N26" s="161"/>
@@ -24691,7 +24689,7 @@
         <v>7</v>
       </c>
       <c r="L33" s="161">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="M33" s="161"/>
       <c r="N33" s="161"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -24502,9 +24502,7 @@
       <c r="K31" s="158">
         <v>7</v>
       </c>
-      <c r="L31" s="161">
-        <v>46293</v>
-      </c>
+      <c r="L31" s="161"/>
       <c r="M31" s="161"/>
       <c r="N31" s="161"/>
       <c r="O31" s="161"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22665,41 +22665,43 @@
       <c r="BL11" s="12"/>
     </row>
     <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="155" cm="1">
-        <f t="array" ref="A12">A11+1</f>
-        <v>1</v>
-      </c>
-      <c r="B12" t="s" s="167">
-        <v>100</v>
-      </c>
-      <c r="C12" t="s" s="156">
-        <v>101</v>
+      <c r="A12" s="155">
+        <f>A11+1</f>
+      </c>
+      <c r="B12" s="167" t="inlineStr">
+        <is>
+          <t>三友-304</t>
+        </is>
+      </c>
+      <c r="C12" s="156" t="inlineStr">
+        <is>
+          <t>西側　1階食堂床見切り</t>
+        </is>
       </c>
       <c r="D12" s="165"/>
       <c r="E12" s="164"/>
-      <c r="F12" s="163" cm="1">
-        <f t="array" ref="F12">IF(AG12="","",I12-H12)</f>
-        <v>46308</v>
+      <c r="F12" s="163">
+        <f>IF(AG12="","",I12-H12)</f>
       </c>
       <c r="G12" s="160"/>
       <c r="H12" s="158">
         <v>7</v>
       </c>
-      <c r="I12" s="161" cm="1">
-        <f t="array" ref="I12">IF(AG12="","",P12-K12)</f>
-        <v>46315</v>
+      <c r="I12" s="161">
+        <f>IF(AG12="","",P12-K12)</f>
       </c>
       <c r="J12" s="160"/>
       <c r="K12" s="158">
         <v>7</v>
       </c>
-      <c r="L12" s="161"/>
+      <c r="L12" s="161">
+        <v>46302</v>
+      </c>
       <c r="M12" s="161"/>
       <c r="N12" s="161"/>
       <c r="O12" s="161"/>
-      <c r="P12" s="161" cm="1">
-        <f t="array" ref="P12">IF(AG12="","",AC12-R12-Q12)</f>
-        <v>46322</v>
+      <c r="P12" s="161">
+        <f>IF(AG12="","",AC12-R12-Q12)</f>
       </c>
       <c r="Q12" s="162">
         <v>7</v>
@@ -22718,18 +22720,17 @@
       <c r="AA12" s="161"/>
       <c r="AB12" s="160"/>
       <c r="AC12" s="163">
-        <v>46343</v>
-      </c>
-      <c r="AD12" s="161" cm="1">
-        <f t="array" ref="AD12">IF(AG12="","",$AG12-$AF12)</f>
-        <v>46343</v>
+        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD12" s="161">
+        <f>IF(AG12="","",$AG12-$AF12)</f>
       </c>
       <c r="AE12" s="160"/>
       <c r="AF12" s="196">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AG12" s="165">
-        <v>46357</v>
+        <v>46374</v>
       </c>
       <c r="AH12" s="164"/>
       <c r="AI12" s="163"/>
@@ -22737,9 +22738,7 @@
       <c r="AK12" s="161"/>
       <c r="AL12" s="160"/>
       <c r="AM12" s="165"/>
-      <c r="AN12" t="s" s="169">
-        <v>102</v>
-      </c>
+      <c r="AN12" s="169"/>
       <c r="AO12" s="10"/>
       <c r="AP12" s="12"/>
       <c r="AQ12" s="12"/>
@@ -22766,49 +22765,47 @@
       <c r="BL12" s="12"/>
     </row>
     <row r="13" ht="25.5" customHeight="1">
-      <c r="A13" s="155" cm="1">
-        <f t="array" ref="A13">A12+1</f>
-        <v>2</v>
-      </c>
-      <c r="B13" t="s" s="167">
-        <v>103</v>
-      </c>
-      <c r="C13" t="s" s="197">
-        <v>104</v>
+      <c r="A13" s="155">
+        <f>A12+1</f>
+      </c>
+      <c r="B13" s="167" t="inlineStr">
+        <is>
+          <t>三友-307</t>
+        </is>
+      </c>
+      <c r="C13" s="156" t="inlineStr">
+        <is>
+          <t>西側　ボックス席腰壁下地鉄骨</t>
+        </is>
       </c>
       <c r="D13" s="165"/>
       <c r="E13" s="164"/>
-      <c r="F13" s="163" cm="1">
-        <f t="array" ref="F13">IF(AG13="","",I13-H13)</f>
-        <v>46289</v>
+      <c r="F13" s="163">
+        <f>IF(AG13="","",I13-H13)</f>
       </c>
       <c r="G13" s="160"/>
       <c r="H13" s="158">
         <v>7</v>
       </c>
-      <c r="I13" s="161" cm="1">
-        <f t="array" ref="I13">IF(AG13="","",P13-K13)</f>
-        <v>46296</v>
+      <c r="I13" s="161">
+        <f>IF(AG13="","",P13-K13)</f>
       </c>
       <c r="J13" s="160"/>
       <c r="K13" s="158">
         <v>7</v>
       </c>
-      <c r="L13" s="161">
-        <v>46302</v>
-      </c>
+      <c r="L13" s="161"/>
       <c r="M13" s="161"/>
       <c r="N13" s="161"/>
       <c r="O13" s="161"/>
-      <c r="P13" s="161" cm="1">
-        <f t="array" ref="P13">IF(AG13="","",AC13-R13-Q13)</f>
-        <v>46303</v>
+      <c r="P13" s="161">
+        <f>IF(AG13="","",AC13-R13-Q13)</f>
       </c>
       <c r="Q13" s="162">
         <v>7</v>
       </c>
       <c r="R13" s="162">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S13" s="161"/>
       <c r="T13" s="161"/>
@@ -22821,18 +22818,17 @@
       <c r="AA13" s="161"/>
       <c r="AB13" s="160"/>
       <c r="AC13" s="163">
-        <v>46317</v>
-      </c>
-      <c r="AD13" s="161" cm="1">
-        <f t="array" ref="AD13">IF(AG13="","",$AG13-$AF13)</f>
-        <v>46317</v>
+        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD13" s="161">
+        <f>IF(AG13="","",$AG13-$AF13)</f>
       </c>
       <c r="AE13" s="160"/>
       <c r="AF13" s="196">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AG13" s="165">
-        <v>46377</v>
+        <v>46357</v>
       </c>
       <c r="AH13" s="164"/>
       <c r="AI13" s="163"/>
@@ -22840,8 +22836,10 @@
       <c r="AK13" s="161"/>
       <c r="AL13" s="160"/>
       <c r="AM13" s="165"/>
-      <c r="AN13" t="s" s="198">
-        <v>105</v>
+      <c r="AN13" s="169" t="inlineStr">
+        <is>
+          <t>製作２週間</t>
+        </is>
       </c>
       <c r="AO13" s="10"/>
       <c r="AP13" s="12"/>
@@ -22869,29 +22867,30 @@
       <c r="BL13" s="12"/>
     </row>
     <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="155" cm="1">
-        <f t="array" ref="A14">A13+1</f>
-        <v>3</v>
-      </c>
-      <c r="B14" t="s" s="167">
-        <v>106</v>
-      </c>
-      <c r="C14" t="s" s="156">
-        <v>107</v>
+      <c r="A14" s="155">
+        <f>A13+1</f>
+      </c>
+      <c r="B14" s="167" t="inlineStr">
+        <is>
+          <t>三友-308</t>
+        </is>
+      </c>
+      <c r="C14" s="156" t="inlineStr">
+        <is>
+          <t>東側　吹抜け部天井下地鉄骨</t>
+        </is>
       </c>
       <c r="D14" s="165"/>
       <c r="E14" s="164"/>
-      <c r="F14" s="163" cm="1">
-        <f t="array" ref="F14">IF(AG14="","",I14-H14)</f>
-        <v>46343</v>
+      <c r="F14" s="163">
+        <f>IF(AG14="","",I14-H14)</f>
       </c>
       <c r="G14" s="160"/>
       <c r="H14" s="158">
         <v>7</v>
       </c>
-      <c r="I14" s="161" cm="1">
-        <f t="array" ref="I14">IF(AG14="","",P14-K14)</f>
-        <v>46350</v>
+      <c r="I14" s="161">
+        <f>IF(AG14="","",P14-K14)</f>
       </c>
       <c r="J14" s="160"/>
       <c r="K14" s="158">
@@ -22901,9 +22900,8 @@
       <c r="M14" s="161"/>
       <c r="N14" s="161"/>
       <c r="O14" s="161"/>
-      <c r="P14" s="161" cm="1">
-        <f t="array" ref="P14">IF(AG14="","",AC14-R14-Q14)</f>
-        <v>46357</v>
+      <c r="P14" s="161">
+        <f>IF(AG14="","",AC14-R14-Q14)</f>
       </c>
       <c r="Q14" s="162">
         <v>7</v>
@@ -22922,11 +22920,10 @@
       <c r="AA14" s="161"/>
       <c r="AB14" s="160"/>
       <c r="AC14" s="163">
-        <v>46378</v>
-      </c>
-      <c r="AD14" s="161" cm="1">
-        <f t="array" ref="AD14">IF(AG14="","",$AG14-$AF14)</f>
-        <v>46378</v>
+        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD14" s="161">
+        <f>IF(AG14="","",$AG14-$AF14)</f>
       </c>
       <c r="AE14" s="160"/>
       <c r="AF14" s="196">
@@ -22941,7 +22938,7 @@
       <c r="AK14" s="161"/>
       <c r="AL14" s="160"/>
       <c r="AM14" s="165"/>
-      <c r="AN14" s="166"/>
+      <c r="AN14" s="169"/>
       <c r="AO14" s="10"/>
       <c r="AP14" s="12"/>
       <c r="AQ14" s="12"/>
@@ -22968,29 +22965,30 @@
       <c r="BL14" s="12"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
-      <c r="A15" s="155" cm="1">
-        <f t="array" ref="A15">A14+1</f>
-        <v>4</v>
-      </c>
-      <c r="B15" t="s" s="167">
-        <v>108</v>
-      </c>
-      <c r="C15" t="s" s="156">
-        <v>109</v>
+      <c r="A15" s="155">
+        <f>A14+1</f>
+      </c>
+      <c r="B15" s="167" t="inlineStr">
+        <is>
+          <t>三友-309</t>
+        </is>
+      </c>
+      <c r="C15" s="156" t="inlineStr">
+        <is>
+          <t>東側　吸音ルーバー壁下地鉄骨</t>
+        </is>
       </c>
       <c r="D15" s="165"/>
       <c r="E15" s="164"/>
-      <c r="F15" s="163" cm="1">
-        <f t="array" ref="F15">IF(AG15="","",I15-H15)</f>
-        <v>46346</v>
+      <c r="F15" s="163">
+        <f>IF(AG15="","",I15-H15)</f>
       </c>
       <c r="G15" s="160"/>
       <c r="H15" s="158">
         <v>7</v>
       </c>
-      <c r="I15" s="161" cm="1">
-        <f t="array" ref="I15">IF(AG15="","",P15-K15)</f>
-        <v>46353</v>
+      <c r="I15" s="161">
+        <f>IF(AG15="","",P15-K15)</f>
       </c>
       <c r="J15" s="160"/>
       <c r="K15" s="158">
@@ -23002,9 +23000,8 @@
       <c r="M15" s="161"/>
       <c r="N15" s="161"/>
       <c r="O15" s="161"/>
-      <c r="P15" s="161" cm="1">
-        <f t="array" ref="P15">IF(AG15="","",AC15-R15-Q15)</f>
-        <v>46360</v>
+      <c r="P15" s="161">
+        <f>IF(AG15="","",AC15-R15-Q15)</f>
       </c>
       <c r="Q15" s="162">
         <v>7</v>
@@ -23023,11 +23020,10 @@
       <c r="AA15" s="161"/>
       <c r="AB15" s="160"/>
       <c r="AC15" s="163">
-        <v>46381</v>
-      </c>
-      <c r="AD15" s="161" cm="1">
-        <f t="array" ref="AD15">IF(AG15="","",$AG15-$AF15)</f>
-        <v>46385</v>
+        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD15" s="161">
+        <f>IF(AG15="","",$AG15-$AF15)</f>
       </c>
       <c r="AE15" s="160"/>
       <c r="AF15" s="196">
@@ -23042,8 +23038,10 @@
       <c r="AK15" s="161"/>
       <c r="AL15" s="160"/>
       <c r="AM15" s="165"/>
-      <c r="AN15" t="s" s="169">
-        <v>102</v>
+      <c r="AN15" s="169" t="inlineStr">
+        <is>
+          <t>製作２週間</t>
+        </is>
       </c>
       <c r="AO15" s="10"/>
       <c r="AP15" s="12"/>
@@ -23071,29 +23069,30 @@
       <c r="BL15" s="12"/>
     </row>
     <row r="16" ht="25.5" customHeight="1">
-      <c r="A16" s="155" cm="1">
-        <f t="array" ref="A16">A15+1</f>
-        <v>5</v>
-      </c>
-      <c r="B16" t="s" s="167">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s" s="156">
-        <v>111</v>
+      <c r="A16" s="155">
+        <f>A15+1</f>
+      </c>
+      <c r="B16" s="167" t="inlineStr">
+        <is>
+          <t>三友-310</t>
+        </is>
+      </c>
+      <c r="C16" s="156" t="inlineStr">
+        <is>
+          <t>東側　吸音ルーバー壁⑤通り部天端塞ぎ</t>
+        </is>
       </c>
       <c r="D16" s="165"/>
       <c r="E16" s="164"/>
-      <c r="F16" s="163" cm="1">
-        <f t="array" ref="F16">IF(AG16="","",I16-H16)</f>
-        <v>46367</v>
+      <c r="F16" s="163">
+        <f>IF(AG16="","",I16-H16)</f>
       </c>
       <c r="G16" s="160"/>
       <c r="H16" s="158">
         <v>7</v>
       </c>
-      <c r="I16" s="161" cm="1">
-        <f t="array" ref="I16">IF(AG16="","",P16-K16)</f>
-        <v>46374</v>
+      <c r="I16" s="161">
+        <f>IF(AG16="","",P16-K16)</f>
       </c>
       <c r="J16" s="160"/>
       <c r="K16" s="158">
@@ -23103,9 +23102,8 @@
       <c r="M16" s="161"/>
       <c r="N16" s="161"/>
       <c r="O16" s="161"/>
-      <c r="P16" s="161" cm="1">
-        <f t="array" ref="P16">IF(AG16="","",AC16-R16-Q16)</f>
-        <v>46381</v>
+      <c r="P16" s="161">
+        <f>IF(AG16="","",AC16-R16-Q16)</f>
       </c>
       <c r="Q16" s="162">
         <v>7</v>
@@ -23124,18 +23122,17 @@
       <c r="AA16" s="161"/>
       <c r="AB16" s="160"/>
       <c r="AC16" s="163">
-        <v>46402</v>
-      </c>
-      <c r="AD16" s="161" cm="1">
-        <f t="array" ref="AD16">IF(AG16="","",$AG16-$AF16)</f>
-        <v>46402</v>
+        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD16" s="161">
+        <f>IF(AG16="","",$AG16-$AF16)</f>
       </c>
       <c r="AE16" s="160"/>
       <c r="AF16" s="196">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AG16" s="165">
-        <v>46423</v>
+        <v>46366</v>
       </c>
       <c r="AH16" s="164"/>
       <c r="AI16" s="163"/>
@@ -23143,9 +23140,7 @@
       <c r="AK16" s="161"/>
       <c r="AL16" s="160"/>
       <c r="AM16" s="165"/>
-      <c r="AN16" t="s" s="169">
-        <v>112</v>
-      </c>
+      <c r="AN16" s="169"/>
       <c r="AO16" s="10"/>
       <c r="AP16" s="12"/>
       <c r="AQ16" s="12"/>
@@ -23172,37 +23167,48 @@
       <c r="BL16" s="12"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="155" cm="1">
-        <f t="array" ref="A17">A16+1</f>
-        <v>6</v>
-      </c>
-      <c r="B17" t="s" s="167">
-        <v>113</v>
-      </c>
-      <c r="C17" t="s" s="156">
-        <v>114</v>
+      <c r="A17" s="155">
+        <f>A16+1</f>
+      </c>
+      <c r="B17" s="167" t="inlineStr">
+        <is>
+          <t>三友-311</t>
+        </is>
+      </c>
+      <c r="C17" s="156" t="inlineStr">
+        <is>
+          <t>東側　腰壁下地鉄骨</t>
+        </is>
       </c>
       <c r="D17" s="165"/>
       <c r="E17" s="164"/>
-      <c r="F17" t="str" s="195" cm="1">
-        <f t="array" ref="F17">IF(AG17="","",I17-H17)</f>
+      <c r="F17" s="163">
+        <f>IF(AG17="","",I17-H17)</f>
       </c>
       <c r="G17" s="160"/>
-      <c r="H17" s="158"/>
-      <c r="I17" t="str" s="159" cm="1">
-        <f t="array" ref="I17">IF(AG17="","",P17-K17)</f>
+      <c r="H17" s="158">
+        <v>7</v>
+      </c>
+      <c r="I17" s="161">
+        <f>IF(AG17="","",P17-K17)</f>
       </c>
       <c r="J17" s="160"/>
-      <c r="K17" s="158"/>
+      <c r="K17" s="158">
+        <v>7</v>
+      </c>
       <c r="L17" s="161"/>
       <c r="M17" s="161"/>
       <c r="N17" s="161"/>
       <c r="O17" s="161"/>
-      <c r="P17" t="str" s="159" cm="1">
-        <f t="array" ref="P17">IF(AG17="","",AC17-R17-Q17)</f>
-      </c>
-      <c r="Q17" s="162"/>
-      <c r="R17" s="162"/>
+      <c r="P17" s="161">
+        <f>IF(AG17="","",AC17-R17-Q17)</f>
+      </c>
+      <c r="Q17" s="162">
+        <v>7</v>
+      </c>
+      <c r="R17" s="162">
+        <v>14</v>
+      </c>
       <c r="S17" s="161"/>
       <c r="T17" s="161"/>
       <c r="U17" s="161"/>
@@ -23213,20 +23219,30 @@
       <c r="Z17" s="161"/>
       <c r="AA17" s="161"/>
       <c r="AB17" s="160"/>
-      <c r="AC17" s="163"/>
-      <c r="AD17" t="str" s="159" cm="1">
-        <f t="array" ref="AD17">IF(AG17="","",$AG17-$AF17)</f>
+      <c r="AC17" s="163">
+        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD17" s="161">
+        <f>IF(AG17="","",$AG17-$AF17)</f>
       </c>
       <c r="AE17" s="160"/>
-      <c r="AF17" s="196"/>
-      <c r="AG17" s="165"/>
+      <c r="AF17" s="196">
+        <v>21</v>
+      </c>
+      <c r="AG17" s="165">
+        <v>46423</v>
+      </c>
       <c r="AH17" s="164"/>
       <c r="AI17" s="163"/>
       <c r="AJ17" s="161"/>
       <c r="AK17" s="161"/>
       <c r="AL17" s="160"/>
       <c r="AM17" s="165"/>
-      <c r="AN17" s="166"/>
+      <c r="AN17" s="169" t="inlineStr">
+        <is>
+          <t>製作３週間</t>
+        </is>
+      </c>
       <c r="AO17" s="10"/>
       <c r="AP17" s="12"/>
       <c r="AQ17" s="12"/>
@@ -23253,35 +23269,48 @@
       <c r="BL17" s="12"/>
     </row>
     <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="155" cm="1">
-        <f t="array" ref="A18">A17+1</f>
-        <v>7</v>
-      </c>
-      <c r="B18" s="151"/>
-      <c r="C18" t="s" s="156">
-        <v>115</v>
+      <c r="A18" s="155">
+        <f>A17+1</f>
+      </c>
+      <c r="B18" s="167" t="inlineStr">
+        <is>
+          <t>三友-312</t>
+        </is>
+      </c>
+      <c r="C18" s="156" t="inlineStr">
+        <is>
+          <t>東側・西側　窓際カウンター下地</t>
+        </is>
       </c>
       <c r="D18" s="165"/>
       <c r="E18" s="164"/>
-      <c r="F18" t="str" s="195" cm="1">
-        <f t="array" ref="F18">IF(AG18="","",I18-H18)</f>
+      <c r="F18" s="163">
+        <f>IF(AG18="","",I18-H18)</f>
       </c>
       <c r="G18" s="160"/>
-      <c r="H18" s="158"/>
-      <c r="I18" t="str" s="159" cm="1">
-        <f t="array" ref="I18">IF(AG18="","",P18-K18)</f>
+      <c r="H18" s="158">
+        <v>7</v>
+      </c>
+      <c r="I18" s="161">
+        <f>IF(AG18="","",P18-K18)</f>
       </c>
       <c r="J18" s="160"/>
-      <c r="K18" s="158"/>
+      <c r="K18" s="158">
+        <v>7</v>
+      </c>
       <c r="L18" s="161"/>
       <c r="M18" s="161"/>
       <c r="N18" s="161"/>
       <c r="O18" s="161"/>
-      <c r="P18" t="str" s="159" cm="1">
-        <f t="array" ref="P18">IF(AG18="","",AC18-R18-Q18)</f>
-      </c>
-      <c r="Q18" s="162"/>
-      <c r="R18" s="162"/>
+      <c r="P18" s="161">
+        <f>IF(AG18="","",AC18-R18-Q18)</f>
+      </c>
+      <c r="Q18" s="162">
+        <v>7</v>
+      </c>
+      <c r="R18" s="162">
+        <v>14</v>
+      </c>
       <c r="S18" s="161"/>
       <c r="T18" s="161"/>
       <c r="U18" s="161"/>
@@ -23292,20 +23321,26 @@
       <c r="Z18" s="161"/>
       <c r="AA18" s="161"/>
       <c r="AB18" s="160"/>
-      <c r="AC18" s="163"/>
-      <c r="AD18" t="str" s="159" cm="1">
-        <f t="array" ref="AD18">IF(AG18="","",$AG18-$AF18)</f>
+      <c r="AC18" s="163">
+        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD18" s="161">
+        <f>IF(AG18="","",$AG18-$AF18)</f>
       </c>
       <c r="AE18" s="160"/>
-      <c r="AF18" s="196"/>
-      <c r="AG18" s="165"/>
+      <c r="AF18" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG18" s="165">
+        <v>46395</v>
+      </c>
       <c r="AH18" s="164"/>
       <c r="AI18" s="163"/>
       <c r="AJ18" s="161"/>
       <c r="AK18" s="161"/>
       <c r="AL18" s="160"/>
       <c r="AM18" s="165"/>
-      <c r="AN18" s="166"/>
+      <c r="AN18" s="169"/>
       <c r="AO18" s="10"/>
       <c r="AP18" s="12"/>
       <c r="AQ18" s="12"/>
@@ -23332,47 +23367,41 @@
       <c r="BL18" s="12"/>
     </row>
     <row r="19" ht="25.5" customHeight="1">
-      <c r="A19" s="155" cm="1">
-        <f t="array" ref="A19">A18+1</f>
-        <v>8</v>
-      </c>
-      <c r="B19" t="s" s="167">
-        <v>116</v>
-      </c>
-      <c r="C19" t="s" s="156">
-        <v>117</v>
+      <c r="A19" s="155">
+        <f>A18+1</f>
+      </c>
+      <c r="B19" s="167" t="inlineStr">
+        <is>
+          <t>三友-313</t>
+        </is>
+      </c>
+      <c r="C19" s="156" t="inlineStr">
+        <is>
+          <t>東側　壁見切り</t>
+        </is>
       </c>
       <c r="D19" s="165"/>
       <c r="E19" s="164"/>
-      <c r="F19" s="163" cm="1">
-        <f t="array" ref="F19">IF(AG19="","",I19-H19)</f>
-        <v>46275</v>
-      </c>
-      <c r="G19" s="160">
-        <v>46301</v>
-      </c>
+      <c r="F19" s="163">
+        <f>IF(AG19="","",I19-H19)</f>
+      </c>
+      <c r="G19" s="160"/>
       <c r="H19" s="158">
         <v>7</v>
       </c>
-      <c r="I19" s="161" cm="1">
-        <f t="array" ref="I19">IF(AG19="","",P19-K19)</f>
-        <v>46282</v>
-      </c>
-      <c r="J19" s="160">
-        <v>46302</v>
-      </c>
+      <c r="I19" s="161">
+        <f>IF(AG19="","",P19-K19)</f>
+      </c>
+      <c r="J19" s="160"/>
       <c r="K19" s="158">
         <v>7</v>
       </c>
-      <c r="L19" s="161">
-        <v>46302</v>
-      </c>
+      <c r="L19" s="161"/>
       <c r="M19" s="161"/>
       <c r="N19" s="161"/>
       <c r="O19" s="161"/>
-      <c r="P19" s="161" cm="1">
-        <f t="array" ref="P19">IF(AG19="","",AC19-R19-Q19)</f>
-        <v>46289</v>
+      <c r="P19" s="161">
+        <f>IF(AG19="","",AC19-R19-Q19)</f>
       </c>
       <c r="Q19" s="162">
         <v>7</v>
@@ -23391,18 +23420,17 @@
       <c r="AA19" s="161"/>
       <c r="AB19" s="160"/>
       <c r="AC19" s="163">
-        <v>46310</v>
-      </c>
-      <c r="AD19" s="161" cm="1">
-        <f t="array" ref="AD19">IF(AG19="","",$AG19-$AF19)</f>
-        <v>46310</v>
+        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD19" s="161">
+        <f>IF(AG19="","",$AG19-$AF19)</f>
       </c>
       <c r="AE19" s="160"/>
       <c r="AF19" s="196">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AG19" s="165">
-        <v>46370</v>
+        <v>46400</v>
       </c>
       <c r="AH19" s="164"/>
       <c r="AI19" s="163"/>
@@ -23410,9 +23438,7 @@
       <c r="AK19" s="161"/>
       <c r="AL19" s="160"/>
       <c r="AM19" s="165"/>
-      <c r="AN19" t="s" s="198">
-        <v>118</v>
-      </c>
+      <c r="AN19" s="169"/>
       <c r="AO19" s="10"/>
       <c r="AP19" s="12"/>
       <c r="AQ19" s="12"/>
@@ -23439,37 +23465,48 @@
       <c r="BL19" s="12"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="155" cm="1">
-        <f t="array" ref="A20">A19+1</f>
-        <v>9</v>
-      </c>
-      <c r="B20" t="s" s="167">
-        <v>119</v>
-      </c>
-      <c r="C20" t="s" s="197">
-        <v>120</v>
+      <c r="A20" s="155">
+        <f>A19+1</f>
+      </c>
+      <c r="B20" s="167" t="inlineStr">
+        <is>
+          <t>三友-314</t>
+        </is>
+      </c>
+      <c r="C20" s="156" t="inlineStr">
+        <is>
+          <t>東側　自動扉安全柵</t>
+        </is>
       </c>
       <c r="D20" s="165"/>
       <c r="E20" s="164"/>
-      <c r="F20" t="str" s="195" cm="1">
-        <f t="array" ref="F20">IF(AG20="","",I20-H20)</f>
+      <c r="F20" s="163">
+        <f>IF(AG20="","",I20-H20)</f>
       </c>
       <c r="G20" s="160"/>
-      <c r="H20" s="158"/>
-      <c r="I20" t="str" s="159" cm="1">
-        <f t="array" ref="I20">IF(AG20="","",P20-K20)</f>
+      <c r="H20" s="158">
+        <v>7</v>
+      </c>
+      <c r="I20" s="161">
+        <f>IF(AG20="","",P20-K20)</f>
       </c>
       <c r="J20" s="160"/>
-      <c r="K20" s="158"/>
+      <c r="K20" s="158">
+        <v>7</v>
+      </c>
       <c r="L20" s="161"/>
       <c r="M20" s="161"/>
       <c r="N20" s="161"/>
       <c r="O20" s="161"/>
-      <c r="P20" t="str" s="159" cm="1">
-        <f t="array" ref="P20">IF(AG20="","",AC20-R20-Q20)</f>
-      </c>
-      <c r="Q20" s="162"/>
-      <c r="R20" s="162"/>
+      <c r="P20" s="161">
+        <f>IF(AG20="","",AC20-R20-Q20)</f>
+      </c>
+      <c r="Q20" s="162">
+        <v>7</v>
+      </c>
+      <c r="R20" s="162">
+        <v>14</v>
+      </c>
       <c r="S20" s="161"/>
       <c r="T20" s="161"/>
       <c r="U20" s="161"/>
@@ -23480,22 +23517,26 @@
       <c r="Z20" s="161"/>
       <c r="AA20" s="161"/>
       <c r="AB20" s="160"/>
-      <c r="AC20" s="163"/>
-      <c r="AD20" t="str" s="159" cm="1">
-        <f t="array" ref="AD20">IF(AG20="","",$AG20-$AF20)</f>
+      <c r="AC20" s="163">
+        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD20" s="161">
+        <f>IF(AG20="","",$AG20-$AF20)</f>
       </c>
       <c r="AE20" s="160"/>
-      <c r="AF20" s="196"/>
-      <c r="AG20" s="165"/>
+      <c r="AF20" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG20" s="165">
+        <v>46416</v>
+      </c>
       <c r="AH20" s="164"/>
       <c r="AI20" s="163"/>
       <c r="AJ20" s="161"/>
       <c r="AK20" s="161"/>
       <c r="AL20" s="160"/>
       <c r="AM20" s="165"/>
-      <c r="AN20" t="s" s="198">
-        <v>121</v>
-      </c>
+      <c r="AN20" s="169"/>
       <c r="AO20" s="10"/>
       <c r="AP20" s="12"/>
       <c r="AQ20" s="12"/>
@@ -23522,49 +23563,43 @@
       <c r="BL20" s="12"/>
     </row>
     <row r="21" ht="25.5" customHeight="1">
-      <c r="A21" s="155" cm="1">
-        <f t="array" ref="A21">A20+1</f>
-        <v>10</v>
-      </c>
-      <c r="B21" t="s" s="167">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s" s="197">
-        <v>123</v>
+      <c r="A21" s="155">
+        <f>A20+1</f>
+      </c>
+      <c r="B21" s="167" t="inlineStr">
+        <is>
+          <t>三友-315</t>
+        </is>
+      </c>
+      <c r="C21" s="156" t="inlineStr">
+        <is>
+          <t>西側　壁アルミルーバー（天井裏下地込み）</t>
+        </is>
       </c>
       <c r="D21" s="165"/>
       <c r="E21" s="164"/>
-      <c r="F21" s="163" cm="1">
-        <f t="array" ref="F21">IF(AG21="","",I21-H21)</f>
-        <v>46275</v>
-      </c>
-      <c r="G21" s="160">
-        <v>46290</v>
-      </c>
+      <c r="F21" s="163">
+        <f>IF(AG21="","",I21-H21)</f>
+      </c>
+      <c r="G21" s="160"/>
       <c r="H21" s="158">
         <v>7</v>
       </c>
-      <c r="I21" s="161" cm="1">
-        <f t="array" ref="I21">IF(AG21="","",P21-K21)</f>
-        <v>46282</v>
-      </c>
-      <c r="J21" s="160">
-        <v>46290</v>
-      </c>
+      <c r="I21" s="161">
+        <f>IF(AG21="","",P21-K21)</f>
+      </c>
+      <c r="J21" s="160"/>
       <c r="K21" s="158">
         <v>7</v>
       </c>
       <c r="L21" s="161">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="M21" s="161"/>
-      <c r="N21" s="161">
-        <v>46302</v>
-      </c>
+      <c r="N21" s="161"/>
       <c r="O21" s="161"/>
-      <c r="P21" s="161" cm="1">
-        <f t="array" ref="P21">IF(AG21="","",AC21-R21-Q21)</f>
-        <v>46289</v>
+      <c r="P21" s="161">
+        <f>IF(AG21="","",AC21-R21-Q21)</f>
       </c>
       <c r="Q21" s="162">
         <v>7</v>
@@ -23583,18 +23618,17 @@
       <c r="AA21" s="161"/>
       <c r="AB21" s="160"/>
       <c r="AC21" s="163">
-        <v>46310</v>
-      </c>
-      <c r="AD21" s="161" cm="1">
-        <f t="array" ref="AD21">IF(AG21="","",$AG21-$AF21)</f>
-        <v>46310</v>
+        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD21" s="161">
+        <f>IF(AG21="","",$AG21-$AF21)</f>
       </c>
       <c r="AE21" s="160"/>
       <c r="AF21" s="196">
         <v>60</v>
       </c>
       <c r="AG21" s="165">
-        <v>46370</v>
+        <v>46377</v>
       </c>
       <c r="AH21" s="164"/>
       <c r="AI21" s="163"/>
@@ -23602,8 +23636,10 @@
       <c r="AK21" s="161"/>
       <c r="AL21" s="160"/>
       <c r="AM21" s="165"/>
-      <c r="AN21" t="s" s="198">
-        <v>124</v>
+      <c r="AN21" s="169" t="inlineStr">
+        <is>
+          <t>製作２か月、9/30初回作図</t>
+        </is>
       </c>
       <c r="AO21" s="10"/>
       <c r="AP21" s="12"/>
@@ -23631,37 +23667,48 @@
       <c r="BL21" s="12"/>
     </row>
     <row r="22" ht="25.5" customHeight="1">
-      <c r="A22" s="155" cm="1">
-        <f t="array" ref="A22">A21+1</f>
-        <v>11</v>
-      </c>
-      <c r="B22" t="s" s="167">
-        <v>125</v>
-      </c>
-      <c r="C22" t="s" s="199">
-        <v>126</v>
+      <c r="A22" s="155">
+        <f>A21+1</f>
+      </c>
+      <c r="B22" s="167" t="inlineStr">
+        <is>
+          <t>三友-316</t>
+        </is>
+      </c>
+      <c r="C22" s="156" t="inlineStr">
+        <is>
+          <t>西側　ステンレスカウンター</t>
+        </is>
       </c>
       <c r="D22" s="165"/>
       <c r="E22" s="164"/>
-      <c r="F22" t="str" s="195" cm="1">
-        <f t="array" ref="F22">IF(AG22="","",I22-H22)</f>
+      <c r="F22" s="163">
+        <f>IF(AG22="","",I22-H22)</f>
       </c>
       <c r="G22" s="160"/>
-      <c r="H22" s="158"/>
-      <c r="I22" t="str" s="159" cm="1">
-        <f t="array" ref="I22">IF(AG22="","",P22-K22)</f>
+      <c r="H22" s="158">
+        <v>7</v>
+      </c>
+      <c r="I22" s="161">
+        <f>IF(AG22="","",P22-K22)</f>
       </c>
       <c r="J22" s="160"/>
-      <c r="K22" s="158"/>
+      <c r="K22" s="158">
+        <v>7</v>
+      </c>
       <c r="L22" s="161"/>
       <c r="M22" s="161"/>
       <c r="N22" s="161"/>
       <c r="O22" s="161"/>
-      <c r="P22" t="str" s="159" cm="1">
-        <f t="array" ref="P22">IF(AG22="","",AC22-R22-Q22)</f>
-      </c>
-      <c r="Q22" s="162"/>
-      <c r="R22" s="162"/>
+      <c r="P22" s="161">
+        <f>IF(AG22="","",AC22-R22-Q22)</f>
+      </c>
+      <c r="Q22" s="162">
+        <v>7</v>
+      </c>
+      <c r="R22" s="162">
+        <v>14</v>
+      </c>
       <c r="S22" s="161"/>
       <c r="T22" s="161"/>
       <c r="U22" s="161"/>
@@ -23672,22 +23719,26 @@
       <c r="Z22" s="161"/>
       <c r="AA22" s="161"/>
       <c r="AB22" s="160"/>
-      <c r="AC22" s="163"/>
-      <c r="AD22" t="str" s="159" cm="1">
-        <f t="array" ref="AD22">IF(AG22="","",$AG22-$AF22)</f>
+      <c r="AC22" s="163">
+        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD22" s="161">
+        <f>IF(AG22="","",$AG22-$AF22)</f>
       </c>
       <c r="AE22" s="160"/>
-      <c r="AF22" s="196"/>
-      <c r="AG22" s="165"/>
+      <c r="AF22" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG22" s="165">
+        <v>46395</v>
+      </c>
       <c r="AH22" s="164"/>
       <c r="AI22" s="163"/>
       <c r="AJ22" s="161"/>
       <c r="AK22" s="161"/>
       <c r="AL22" s="160"/>
       <c r="AM22" s="165"/>
-      <c r="AN22" t="s" s="169">
-        <v>127</v>
-      </c>
+      <c r="AN22" s="169"/>
       <c r="AO22" s="10"/>
       <c r="AP22" s="12"/>
       <c r="AQ22" s="12"/>
@@ -23714,35 +23765,48 @@
       <c r="BL22" s="12"/>
     </row>
     <row r="23" ht="25.5" customHeight="1">
-      <c r="A23" s="155" cm="1">
-        <f t="array" ref="A23">A22+1</f>
-        <v>12</v>
-      </c>
-      <c r="B23" s="151"/>
-      <c r="C23" t="s" s="156">
-        <v>128</v>
+      <c r="A23" s="155">
+        <f>A22+1</f>
+      </c>
+      <c r="B23" s="167" t="inlineStr">
+        <is>
+          <t>三友-318</t>
+        </is>
+      </c>
+      <c r="C23" s="156" t="inlineStr">
+        <is>
+          <t>チャンバーボックス</t>
+        </is>
       </c>
       <c r="D23" s="165"/>
       <c r="E23" s="164"/>
-      <c r="F23" t="str" s="195" cm="1">
-        <f t="array" ref="F23">IF(AG23="","",I23-H23)</f>
+      <c r="F23" s="163">
+        <f>IF(AG23="","",I23-H23)</f>
       </c>
       <c r="G23" s="160"/>
-      <c r="H23" s="158"/>
-      <c r="I23" t="str" s="159" cm="1">
-        <f t="array" ref="I23">IF(AG23="","",P23-K23)</f>
+      <c r="H23" s="158">
+        <v>7</v>
+      </c>
+      <c r="I23" s="161">
+        <f>IF(AG23="","",P23-K23)</f>
       </c>
       <c r="J23" s="160"/>
-      <c r="K23" s="158"/>
+      <c r="K23" s="158">
+        <v>7</v>
+      </c>
       <c r="L23" s="161"/>
       <c r="M23" s="161"/>
       <c r="N23" s="161"/>
       <c r="O23" s="161"/>
-      <c r="P23" t="str" s="159" cm="1">
-        <f t="array" ref="P23">IF(AG23="","",AC23-R23-Q23)</f>
-      </c>
-      <c r="Q23" s="162"/>
-      <c r="R23" s="162"/>
+      <c r="P23" s="161">
+        <f>IF(AG23="","",AC23-R23-Q23)</f>
+      </c>
+      <c r="Q23" s="162">
+        <v>7</v>
+      </c>
+      <c r="R23" s="162">
+        <v>14</v>
+      </c>
       <c r="S23" s="161"/>
       <c r="T23" s="161"/>
       <c r="U23" s="161"/>
@@ -23753,20 +23817,26 @@
       <c r="Z23" s="161"/>
       <c r="AA23" s="161"/>
       <c r="AB23" s="160"/>
-      <c r="AC23" s="163"/>
-      <c r="AD23" t="str" s="159" cm="1">
-        <f t="array" ref="AD23">IF(AG23="","",$AG23-$AF23)</f>
+      <c r="AC23" s="163">
+        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD23" s="161">
+        <f>IF(AG23="","",$AG23-$AF23)</f>
       </c>
       <c r="AE23" s="160"/>
-      <c r="AF23" s="196"/>
-      <c r="AG23" s="165"/>
+      <c r="AF23" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG23" s="165">
+        <v>46402</v>
+      </c>
       <c r="AH23" s="164"/>
       <c r="AI23" s="163"/>
       <c r="AJ23" s="161"/>
       <c r="AK23" s="161"/>
       <c r="AL23" s="160"/>
       <c r="AM23" s="165"/>
-      <c r="AN23" s="166"/>
+      <c r="AN23" s="169"/>
       <c r="AO23" s="10"/>
       <c r="AP23" s="12"/>
       <c r="AQ23" s="12"/>
@@ -23793,55 +23863,47 @@
       <c r="BL23" s="12"/>
     </row>
     <row r="24" ht="25.5" customHeight="1">
-      <c r="A24" s="155" cm="1">
-        <f t="array" ref="A24">A23+1</f>
-        <v>13</v>
-      </c>
-      <c r="B24" t="s" s="167">
-        <v>129</v>
-      </c>
-      <c r="C24" t="s" s="197">
-        <v>130</v>
+      <c r="A24" s="155">
+        <f>A23+1</f>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>三友-319</t>
+        </is>
+      </c>
+      <c r="C24" s="156" t="inlineStr">
+        <is>
+          <t>チャンバーボックス　グレーチング蓋</t>
+        </is>
       </c>
       <c r="D24" s="165"/>
       <c r="E24" s="164"/>
-      <c r="F24" s="163" cm="1">
-        <f t="array" ref="F24">IF(AG24="","",I24-H24)</f>
-        <v>46269</v>
-      </c>
-      <c r="G24" s="160">
-        <v>46282</v>
-      </c>
+      <c r="F24" s="163">
+        <f>IF(AG24="","",I24-H24)</f>
+      </c>
+      <c r="G24" s="160"/>
       <c r="H24" s="158">
         <v>7</v>
       </c>
-      <c r="I24" s="161" cm="1">
-        <f t="array" ref="I24">IF(AG24="","",P24-K24)</f>
-        <v>46276</v>
-      </c>
-      <c r="J24" s="160">
-        <v>46289</v>
-      </c>
+      <c r="I24" s="161">
+        <f>IF(AG24="","",P24-K24)</f>
+      </c>
+      <c r="J24" s="160"/>
       <c r="K24" s="158">
         <v>7</v>
       </c>
-      <c r="L24" s="161">
-        <v>46293</v>
-      </c>
+      <c r="L24" s="161"/>
       <c r="M24" s="161"/>
-      <c r="N24" s="161">
-        <v>46302</v>
-      </c>
+      <c r="N24" s="161"/>
       <c r="O24" s="161"/>
-      <c r="P24" s="161" cm="1">
-        <f t="array" ref="P24">IF(AG24="","",AC24-R24-Q24)</f>
-        <v>46283</v>
+      <c r="P24" s="161">
+        <f>IF(AG24="","",AC24-R24-Q24)</f>
       </c>
       <c r="Q24" s="162">
         <v>7</v>
       </c>
       <c r="R24" s="162">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S24" s="161"/>
       <c r="T24" s="161"/>
@@ -23854,18 +23916,17 @@
       <c r="AA24" s="161"/>
       <c r="AB24" s="160"/>
       <c r="AC24" s="163">
-        <v>46297</v>
-      </c>
-      <c r="AD24" s="161" cm="1">
-        <f t="array" ref="AD24">IF(AG24="","",$AG24-$AF24)</f>
-        <v>46299</v>
+        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD24" s="161">
+        <f>IF(AG24="","",$AG24-$AF24)</f>
       </c>
       <c r="AE24" s="160"/>
       <c r="AF24" s="196">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AG24" s="165">
-        <v>46379</v>
+        <v>46409</v>
       </c>
       <c r="AH24" s="164"/>
       <c r="AI24" s="163"/>
@@ -23873,9 +23934,7 @@
       <c r="AK24" s="161"/>
       <c r="AL24" s="160"/>
       <c r="AM24" s="165"/>
-      <c r="AN24" t="s" s="198">
-        <v>131</v>
-      </c>
+      <c r="AN24" s="169"/>
       <c r="AO24" s="10"/>
       <c r="AP24" s="12"/>
       <c r="AQ24" s="12"/>
@@ -23902,35 +23961,48 @@
       <c r="BL24" s="12"/>
     </row>
     <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="155" cm="1">
-        <f t="array" ref="A25">A24+1</f>
-        <v>14</v>
-      </c>
-      <c r="B25" s="151"/>
-      <c r="C25" t="s" s="156">
-        <v>132</v>
+      <c r="A25" s="155">
+        <f>A24+1</f>
+      </c>
+      <c r="B25" s="167" t="inlineStr">
+        <is>
+          <t>三友-320</t>
+        </is>
+      </c>
+      <c r="C25" s="156" t="inlineStr">
+        <is>
+          <t>東側　照明ボックススチールパネル</t>
+        </is>
       </c>
       <c r="D25" s="165"/>
       <c r="E25" s="164"/>
-      <c r="F25" t="str" s="195" cm="1">
-        <f t="array" ref="F25">IF(AG25="","",I25-H25)</f>
+      <c r="F25" s="163">
+        <f>IF(AG25="","",I25-H25)</f>
       </c>
       <c r="G25" s="160"/>
-      <c r="H25" s="158"/>
-      <c r="I25" t="str" s="159" cm="1">
-        <f t="array" ref="I25">IF(AG25="","",P25-K25)</f>
+      <c r="H25" s="158">
+        <v>7</v>
+      </c>
+      <c r="I25" s="161">
+        <f>IF(AG25="","",P25-K25)</f>
       </c>
       <c r="J25" s="160"/>
-      <c r="K25" s="158"/>
+      <c r="K25" s="158">
+        <v>7</v>
+      </c>
       <c r="L25" s="161"/>
       <c r="M25" s="161"/>
       <c r="N25" s="161"/>
       <c r="O25" s="161"/>
-      <c r="P25" t="str" s="159" cm="1">
-        <f t="array" ref="P25">IF(AG25="","",AC25-R25-Q25)</f>
-      </c>
-      <c r="Q25" s="162"/>
-      <c r="R25" s="162"/>
+      <c r="P25" s="161">
+        <f>IF(AG25="","",AC25-R25-Q25)</f>
+      </c>
+      <c r="Q25" s="162">
+        <v>7</v>
+      </c>
+      <c r="R25" s="162">
+        <v>14</v>
+      </c>
       <c r="S25" s="161"/>
       <c r="T25" s="161"/>
       <c r="U25" s="161"/>
@@ -23941,20 +24013,26 @@
       <c r="Z25" s="161"/>
       <c r="AA25" s="161"/>
       <c r="AB25" s="160"/>
-      <c r="AC25" s="163"/>
-      <c r="AD25" t="str" s="159" cm="1">
-        <f t="array" ref="AD25">IF(AG25="","",$AG25-$AF25)</f>
+      <c r="AC25" s="163">
+        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD25" s="161">
+        <f>IF(AG25="","",$AG25-$AF25)</f>
       </c>
       <c r="AE25" s="160"/>
-      <c r="AF25" s="196"/>
-      <c r="AG25" s="165"/>
+      <c r="AF25" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG25" s="165">
+        <v>46409</v>
+      </c>
       <c r="AH25" s="164"/>
       <c r="AI25" s="163"/>
       <c r="AJ25" s="161"/>
       <c r="AK25" s="161"/>
       <c r="AL25" s="160"/>
       <c r="AM25" s="165"/>
-      <c r="AN25" s="200"/>
+      <c r="AN25" s="169"/>
       <c r="AO25" s="10"/>
       <c r="AP25" s="12"/>
       <c r="AQ25" s="12"/>
@@ -23981,47 +24059,41 @@
       <c r="BL25" s="12"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
-      <c r="A26" s="155" cm="1">
-        <f t="array" ref="A26">A25+1</f>
-        <v>15</v>
-      </c>
-      <c r="B26" t="s" s="167">
-        <v>133</v>
-      </c>
-      <c r="C26" t="s" s="197">
-        <v>134</v>
+      <c r="A26" s="155">
+        <f>A25+1</f>
+      </c>
+      <c r="B26" s="167" t="inlineStr">
+        <is>
+          <t>三友-321</t>
+        </is>
+      </c>
+      <c r="C26" s="156" t="inlineStr">
+        <is>
+          <t>西側　照明ボックススチールパネル</t>
+        </is>
       </c>
       <c r="D26" s="165"/>
       <c r="E26" s="164"/>
-      <c r="F26" s="163" cm="1">
-        <f t="array" ref="F26">IF(AG26="","",I26-H26)</f>
-        <v>46293</v>
-      </c>
-      <c r="G26" s="160">
-        <v>46300</v>
-      </c>
+      <c r="F26" s="163">
+        <f>IF(AG26="","",I26-H26)</f>
+      </c>
+      <c r="G26" s="160"/>
       <c r="H26" s="158">
         <v>7</v>
       </c>
-      <c r="I26" s="161" cm="1">
-        <f t="array" ref="I26">IF(AG26="","",P26-K26)</f>
-        <v>46300</v>
-      </c>
-      <c r="J26" s="160">
-        <v>46302</v>
-      </c>
+      <c r="I26" s="161">
+        <f>IF(AG26="","",P26-K26)</f>
+      </c>
+      <c r="J26" s="160"/>
       <c r="K26" s="158">
         <v>7</v>
       </c>
-      <c r="L26" s="161">
-        <v>46302</v>
-      </c>
+      <c r="L26" s="161"/>
       <c r="M26" s="161"/>
       <c r="N26" s="161"/>
       <c r="O26" s="161"/>
-      <c r="P26" s="161" cm="1">
-        <f t="array" ref="P26">IF(AG26="","",AC26-R26-Q26)</f>
-        <v>46307</v>
+      <c r="P26" s="161">
+        <f>IF(AG26="","",AC26-R26-Q26)</f>
       </c>
       <c r="Q26" s="162">
         <v>7</v>
@@ -24040,18 +24112,17 @@
       <c r="AA26" s="161"/>
       <c r="AB26" s="160"/>
       <c r="AC26" s="163">
-        <v>46328</v>
-      </c>
-      <c r="AD26" s="161" cm="1">
-        <f t="array" ref="AD26">IF(AG26="","",$AG26-$AF26)</f>
-        <v>46329</v>
+        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+      </c>
+      <c r="AD26" s="161">
+        <f>IF(AG26="","",$AG26-$AF26)</f>
       </c>
       <c r="AE26" s="160"/>
       <c r="AF26" s="196">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AG26" s="165">
-        <v>46419</v>
+        <v>46409</v>
       </c>
       <c r="AH26" s="164"/>
       <c r="AI26" s="163"/>
@@ -24059,9 +24130,7 @@
       <c r="AK26" s="161"/>
       <c r="AL26" s="160"/>
       <c r="AM26" s="165"/>
-      <c r="AN26" t="s" s="198">
-        <v>135</v>
-      </c>
+      <c r="AN26" s="169"/>
       <c r="AO26" s="10"/>
       <c r="AP26" s="12"/>
       <c r="AQ26" s="12"/>
@@ -24090,46 +24159,33 @@
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27" s="155" cm="1">
         <f t="array" ref="A27">A26+1</f>
-        <v>16</v>
-      </c>
-      <c r="B27" t="s" s="167">
-        <v>136</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B27" s="151"/>
       <c r="C27" t="s" s="156">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="D27" s="165"/>
       <c r="E27" s="164"/>
-      <c r="F27" s="163" cm="1">
+      <c r="F27" t="str" s="195" cm="1">
         <f t="array" ref="F27">IF(AG27="","",I27-H27)</f>
-        <v>46346</v>
       </c>
       <c r="G27" s="160"/>
-      <c r="H27" s="158">
-        <v>7</v>
-      </c>
-      <c r="I27" s="161" cm="1">
+      <c r="H27" s="158"/>
+      <c r="I27" t="str" s="159" cm="1">
         <f t="array" ref="I27">IF(AG27="","",P27-K27)</f>
-        <v>46353</v>
       </c>
       <c r="J27" s="160"/>
-      <c r="K27" s="158">
-        <v>7</v>
-      </c>
+      <c r="K27" s="158"/>
       <c r="L27" s="161"/>
       <c r="M27" s="161"/>
       <c r="N27" s="161"/>
       <c r="O27" s="161"/>
-      <c r="P27" s="161" cm="1">
+      <c r="P27" t="str" s="159" cm="1">
         <f t="array" ref="P27">IF(AG27="","",AC27-R27-Q27)</f>
-        <v>46360</v>
-      </c>
-      <c r="Q27" s="162">
-        <v>7</v>
-      </c>
-      <c r="R27" s="162">
-        <v>14</v>
-      </c>
+      </c>
+      <c r="Q27" s="162"/>
+      <c r="R27" s="162"/>
       <c r="S27" s="161"/>
       <c r="T27" s="161"/>
       <c r="U27" s="161"/>
@@ -24140,29 +24196,20 @@
       <c r="Z27" s="161"/>
       <c r="AA27" s="161"/>
       <c r="AB27" s="160"/>
-      <c r="AC27" s="163">
-        <v>46381</v>
-      </c>
-      <c r="AD27" s="161" cm="1">
+      <c r="AC27" s="163"/>
+      <c r="AD27" t="str" s="159" cm="1">
         <f t="array" ref="AD27">IF(AG27="","",$AG27-$AF27)</f>
-        <v>46389</v>
       </c>
       <c r="AE27" s="160"/>
-      <c r="AF27" s="196">
-        <v>30</v>
-      </c>
-      <c r="AG27" s="165">
-        <v>46419</v>
-      </c>
+      <c r="AF27" s="196"/>
+      <c r="AG27" s="165"/>
       <c r="AH27" s="164"/>
       <c r="AI27" s="163"/>
       <c r="AJ27" s="161"/>
       <c r="AK27" s="161"/>
       <c r="AL27" s="160"/>
       <c r="AM27" s="165"/>
-      <c r="AN27" t="s" s="169">
-        <v>138</v>
-      </c>
+      <c r="AN27" s="166"/>
       <c r="AO27" s="10"/>
       <c r="AP27" s="12"/>
       <c r="AQ27" s="12"/>
@@ -24191,39 +24238,45 @@
     <row r="28" ht="25.5" customHeight="1">
       <c r="A28" s="155" cm="1">
         <f t="array" ref="A28">A27+1</f>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s" s="167">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s" s="156">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D28" s="165"/>
       <c r="E28" s="164"/>
       <c r="F28" s="163" cm="1">
         <f t="array" ref="F28">IF(AG28="","",I28-H28)</f>
-        <v>46346</v>
-      </c>
-      <c r="G28" s="160"/>
+        <v>46275</v>
+      </c>
+      <c r="G28" s="160">
+        <v>46301</v>
+      </c>
       <c r="H28" s="158">
         <v>7</v>
       </c>
       <c r="I28" s="161" cm="1">
         <f t="array" ref="I28">IF(AG28="","",P28-K28)</f>
-        <v>46353</v>
-      </c>
-      <c r="J28" s="160"/>
+        <v>46282</v>
+      </c>
+      <c r="J28" s="160">
+        <v>46302</v>
+      </c>
       <c r="K28" s="158">
         <v>7</v>
       </c>
-      <c r="L28" s="161"/>
+      <c r="L28" s="161">
+        <v>46302</v>
+      </c>
       <c r="M28" s="161"/>
       <c r="N28" s="161"/>
       <c r="O28" s="161"/>
       <c r="P28" s="161" cm="1">
         <f t="array" ref="P28">IF(AG28="","",AC28-R28-Q28)</f>
-        <v>46360</v>
+        <v>46289</v>
       </c>
       <c r="Q28" s="162">
         <v>7</v>
@@ -24242,18 +24295,18 @@
       <c r="AA28" s="161"/>
       <c r="AB28" s="160"/>
       <c r="AC28" s="163">
-        <v>46381</v>
+        <v>46310</v>
       </c>
       <c r="AD28" s="161" cm="1">
         <f t="array" ref="AD28">IF(AG28="","",$AG28-$AF28)</f>
-        <v>46389</v>
+        <v>46310</v>
       </c>
       <c r="AE28" s="160"/>
       <c r="AF28" s="196">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AG28" s="165">
-        <v>46419</v>
+        <v>46370</v>
       </c>
       <c r="AH28" s="164"/>
       <c r="AI28" s="163"/>
@@ -24261,8 +24314,8 @@
       <c r="AK28" s="161"/>
       <c r="AL28" s="160"/>
       <c r="AM28" s="165"/>
-      <c r="AN28" t="s" s="169">
-        <v>138</v>
+      <c r="AN28" t="s" s="198">
+        <v>118</v>
       </c>
       <c r="AO28" s="10"/>
       <c r="AP28" s="12"/>
@@ -24292,46 +24345,35 @@
     <row r="29" ht="25.5" customHeight="1">
       <c r="A29" s="155" cm="1">
         <f t="array" ref="A29">A28+1</f>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s" s="167">
-        <v>141</v>
-      </c>
-      <c r="C29" t="s" s="156">
-        <v>142</v>
+        <v>119</v>
+      </c>
+      <c r="C29" t="s" s="197">
+        <v>120</v>
       </c>
       <c r="D29" s="165"/>
       <c r="E29" s="164"/>
-      <c r="F29" s="163" cm="1">
+      <c r="F29" t="str" s="195" cm="1">
         <f t="array" ref="F29">IF(AG29="","",I29-H29)</f>
-        <v>46346</v>
       </c>
       <c r="G29" s="160"/>
-      <c r="H29" s="158">
-        <v>7</v>
-      </c>
-      <c r="I29" s="161" cm="1">
+      <c r="H29" s="158"/>
+      <c r="I29" t="str" s="159" cm="1">
         <f t="array" ref="I29">IF(AG29="","",P29-K29)</f>
-        <v>46353</v>
       </c>
       <c r="J29" s="160"/>
-      <c r="K29" s="158">
-        <v>7</v>
-      </c>
+      <c r="K29" s="158"/>
       <c r="L29" s="161"/>
       <c r="M29" s="161"/>
       <c r="N29" s="161"/>
       <c r="O29" s="161"/>
-      <c r="P29" s="161" cm="1">
+      <c r="P29" t="str" s="159" cm="1">
         <f t="array" ref="P29">IF(AG29="","",AC29-R29-Q29)</f>
-        <v>46360</v>
-      </c>
-      <c r="Q29" s="162">
-        <v>7</v>
-      </c>
-      <c r="R29" s="162">
-        <v>14</v>
-      </c>
+      </c>
+      <c r="Q29" s="162"/>
+      <c r="R29" s="162"/>
       <c r="S29" s="161"/>
       <c r="T29" s="161"/>
       <c r="U29" s="161"/>
@@ -24342,28 +24384,21 @@
       <c r="Z29" s="161"/>
       <c r="AA29" s="161"/>
       <c r="AB29" s="160"/>
-      <c r="AC29" s="163">
-        <v>46381</v>
-      </c>
-      <c r="AD29" s="161" cm="1">
+      <c r="AC29" s="163"/>
+      <c r="AD29" t="str" s="159" cm="1">
         <f t="array" ref="AD29">IF(AG29="","",$AG29-$AF29)</f>
-        <v>46389</v>
       </c>
       <c r="AE29" s="160"/>
-      <c r="AF29" s="196">
-        <v>30</v>
-      </c>
-      <c r="AG29" s="165">
-        <v>46419</v>
-      </c>
+      <c r="AF29" s="196"/>
+      <c r="AG29" s="165"/>
       <c r="AH29" s="164"/>
       <c r="AI29" s="163"/>
       <c r="AJ29" s="161"/>
       <c r="AK29" s="161"/>
       <c r="AL29" s="160"/>
       <c r="AM29" s="165"/>
-      <c r="AN29" t="s" s="169">
-        <v>138</v>
+      <c r="AN29" t="s" s="198">
+        <v>121</v>
       </c>
       <c r="AO29" s="10"/>
       <c r="AP29" s="12"/>
@@ -24393,33 +24428,54 @@
     <row r="30" ht="25.5" customHeight="1">
       <c r="A30" s="155" cm="1">
         <f t="array" ref="A30">A29+1</f>
-        <v>19</v>
-      </c>
-      <c r="B30" s="151"/>
-      <c r="C30" t="s" s="156">
-        <v>143</v>
+        <v>10</v>
+      </c>
+      <c r="B30" t="s" s="167">
+        <v>122</v>
+      </c>
+      <c r="C30" t="s" s="197">
+        <v>123</v>
       </c>
       <c r="D30" s="165"/>
       <c r="E30" s="164"/>
-      <c r="F30" t="str" s="195" cm="1">
+      <c r="F30" s="163" cm="1">
         <f t="array" ref="F30">IF(AG30="","",I30-H30)</f>
-      </c>
-      <c r="G30" s="160"/>
-      <c r="H30" s="158"/>
-      <c r="I30" t="str" s="159" cm="1">
+        <v>46275</v>
+      </c>
+      <c r="G30" s="160">
+        <v>46290</v>
+      </c>
+      <c r="H30" s="158">
+        <v>7</v>
+      </c>
+      <c r="I30" s="161" cm="1">
         <f t="array" ref="I30">IF(AG30="","",P30-K30)</f>
-      </c>
-      <c r="J30" s="160"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="161"/>
+        <v>46282</v>
+      </c>
+      <c r="J30" s="160">
+        <v>46290</v>
+      </c>
+      <c r="K30" s="158">
+        <v>7</v>
+      </c>
+      <c r="L30" s="161">
+        <v>46293</v>
+      </c>
       <c r="M30" s="161"/>
-      <c r="N30" s="161"/>
+      <c r="N30" s="161">
+        <v>46302</v>
+      </c>
       <c r="O30" s="161"/>
-      <c r="P30" t="str" s="159" cm="1">
+      <c r="P30" s="161" cm="1">
         <f t="array" ref="P30">IF(AG30="","",AC30-R30-Q30)</f>
-      </c>
-      <c r="Q30" s="162"/>
-      <c r="R30" s="162"/>
+        <v>46289</v>
+      </c>
+      <c r="Q30" s="162">
+        <v>7</v>
+      </c>
+      <c r="R30" s="162">
+        <v>14</v>
+      </c>
       <c r="S30" s="161"/>
       <c r="T30" s="161"/>
       <c r="U30" s="161"/>
@@ -24430,20 +24486,29 @@
       <c r="Z30" s="161"/>
       <c r="AA30" s="161"/>
       <c r="AB30" s="160"/>
-      <c r="AC30" s="163"/>
-      <c r="AD30" t="str" s="159" cm="1">
+      <c r="AC30" s="163">
+        <v>46310</v>
+      </c>
+      <c r="AD30" s="161" cm="1">
         <f t="array" ref="AD30">IF(AG30="","",$AG30-$AF30)</f>
+        <v>46310</v>
       </c>
       <c r="AE30" s="160"/>
-      <c r="AF30" s="196"/>
-      <c r="AG30" s="165"/>
+      <c r="AF30" s="196">
+        <v>60</v>
+      </c>
+      <c r="AG30" s="165">
+        <v>46370</v>
+      </c>
       <c r="AH30" s="164"/>
       <c r="AI30" s="163"/>
       <c r="AJ30" s="161"/>
       <c r="AK30" s="161"/>
       <c r="AL30" s="160"/>
       <c r="AM30" s="165"/>
-      <c r="AN30" s="166"/>
+      <c r="AN30" t="s" s="198">
+        <v>124</v>
+      </c>
       <c r="AO30" s="10"/>
       <c r="AP30" s="12"/>
       <c r="AQ30" s="12"/>
@@ -24472,50 +24537,35 @@
     <row r="31" ht="25.5" customHeight="1">
       <c r="A31" s="155" cm="1">
         <f t="array" ref="A31">A30+1</f>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s" s="167">
-        <v>144</v>
-      </c>
-      <c r="C31" t="s" s="156">
-        <v>145</v>
+        <v>125</v>
+      </c>
+      <c r="C31" t="s" s="199">
+        <v>126</v>
       </c>
       <c r="D31" s="165"/>
       <c r="E31" s="164"/>
-      <c r="F31" s="163" cm="1">
+      <c r="F31" t="str" s="195" cm="1">
         <f t="array" ref="F31">IF(AG31="","",I31-H31)</f>
-        <v>46345</v>
-      </c>
-      <c r="G31" s="160">
-        <v>46276</v>
-      </c>
-      <c r="H31" s="158">
-        <v>7</v>
-      </c>
-      <c r="I31" s="161" cm="1">
+      </c>
+      <c r="G31" s="160"/>
+      <c r="H31" s="158"/>
+      <c r="I31" t="str" s="159" cm="1">
         <f t="array" ref="I31">IF(AG31="","",P31-K31)</f>
-        <v>46352</v>
-      </c>
-      <c r="J31" s="160">
-        <v>46291</v>
-      </c>
-      <c r="K31" s="158">
-        <v>7</v>
-      </c>
+      </c>
+      <c r="J31" s="160"/>
+      <c r="K31" s="158"/>
       <c r="L31" s="161"/>
       <c r="M31" s="161"/>
       <c r="N31" s="161"/>
       <c r="O31" s="161"/>
-      <c r="P31" s="161" cm="1">
+      <c r="P31" t="str" s="159" cm="1">
         <f t="array" ref="P31">IF(AG31="","",AC31-R31-Q31)</f>
-        <v>46359</v>
-      </c>
-      <c r="Q31" s="162">
-        <v>7</v>
-      </c>
-      <c r="R31" s="162">
-        <v>14</v>
-      </c>
+      </c>
+      <c r="Q31" s="162"/>
+      <c r="R31" s="162"/>
       <c r="S31" s="161"/>
       <c r="T31" s="161"/>
       <c r="U31" s="161"/>
@@ -24526,20 +24576,13 @@
       <c r="Z31" s="161"/>
       <c r="AA31" s="161"/>
       <c r="AB31" s="160"/>
-      <c r="AC31" s="163">
-        <v>46380</v>
-      </c>
-      <c r="AD31" s="161" cm="1">
+      <c r="AC31" s="163"/>
+      <c r="AD31" t="str" s="159" cm="1">
         <f t="array" ref="AD31">IF(AG31="","",$AG31-$AF31)</f>
-        <v>46380</v>
       </c>
       <c r="AE31" s="160"/>
-      <c r="AF31" s="196">
-        <v>60</v>
-      </c>
-      <c r="AG31" s="165">
-        <v>46440</v>
-      </c>
+      <c r="AF31" s="196"/>
+      <c r="AG31" s="165"/>
       <c r="AH31" s="164"/>
       <c r="AI31" s="163"/>
       <c r="AJ31" s="161"/>
@@ -24547,7 +24590,7 @@
       <c r="AL31" s="160"/>
       <c r="AM31" s="165"/>
       <c r="AN31" t="s" s="169">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="AO31" s="10"/>
       <c r="AP31" s="12"/>
@@ -24577,11 +24620,11 @@
     <row r="32" ht="25.5" customHeight="1">
       <c r="A32" s="155" cm="1">
         <f t="array" ref="A32">A31+1</f>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B32" s="151"/>
       <c r="C32" t="s" s="156">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="164"/>
@@ -24656,51 +24699,53 @@
     <row r="33" ht="25.5" customHeight="1">
       <c r="A33" s="155" cm="1">
         <f t="array" ref="A33">A32+1</f>
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s" s="167">
-        <v>148</v>
-      </c>
-      <c r="C33" t="s" s="156">
-        <v>149</v>
+        <v>129</v>
+      </c>
+      <c r="C33" t="s" s="197">
+        <v>130</v>
       </c>
       <c r="D33" s="165"/>
       <c r="E33" s="164"/>
       <c r="F33" s="163" cm="1">
         <f t="array" ref="F33">IF(AG33="","",I33-H33)</f>
-        <v>46381</v>
+        <v>46269</v>
       </c>
       <c r="G33" s="160">
-        <v>46297</v>
+        <v>46282</v>
       </c>
       <c r="H33" s="158">
         <v>7</v>
       </c>
       <c r="I33" s="161" cm="1">
         <f t="array" ref="I33">IF(AG33="","",P33-K33)</f>
-        <v>46388</v>
+        <v>46276</v>
       </c>
       <c r="J33" s="160">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="K33" s="158">
         <v>7</v>
       </c>
       <c r="L33" s="161">
+        <v>46293</v>
+      </c>
+      <c r="M33" s="161"/>
+      <c r="N33" s="161">
         <v>46302</v>
       </c>
-      <c r="M33" s="161"/>
-      <c r="N33" s="161"/>
       <c r="O33" s="161"/>
       <c r="P33" s="161" cm="1">
         <f t="array" ref="P33">IF(AG33="","",AC33-R33-Q33)</f>
-        <v>46395</v>
+        <v>46283</v>
       </c>
       <c r="Q33" s="162">
         <v>7</v>
       </c>
       <c r="R33" s="162">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S33" s="161"/>
       <c r="T33" s="161"/>
@@ -24713,18 +24758,18 @@
       <c r="AA33" s="161"/>
       <c r="AB33" s="160"/>
       <c r="AC33" s="163">
-        <v>46416</v>
+        <v>46297</v>
       </c>
       <c r="AD33" s="161" cm="1">
         <f t="array" ref="AD33">IF(AG33="","",$AG33-$AF33)</f>
-        <v>46417</v>
+        <v>46299</v>
       </c>
       <c r="AE33" s="160"/>
       <c r="AF33" s="196">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AG33" s="165">
-        <v>46447</v>
+        <v>46379</v>
       </c>
       <c r="AH33" s="164"/>
       <c r="AI33" s="163"/>
@@ -24732,8 +24777,8 @@
       <c r="AK33" s="161"/>
       <c r="AL33" s="160"/>
       <c r="AM33" s="165"/>
-      <c r="AN33" t="s" s="169">
-        <v>138</v>
+      <c r="AN33" t="s" s="198">
+        <v>131</v>
       </c>
       <c r="AO33" s="10"/>
       <c r="AP33" s="12"/>
@@ -24763,11 +24808,11 @@
     <row r="34" ht="25.5" customHeight="1">
       <c r="A34" s="155" cm="1">
         <f t="array" ref="A34">A33+1</f>
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B34" s="151"/>
       <c r="C34" t="s" s="156">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D34" s="165"/>
       <c r="E34" s="164"/>
@@ -24813,7 +24858,7 @@
       <c r="AK34" s="161"/>
       <c r="AL34" s="160"/>
       <c r="AM34" s="165"/>
-      <c r="AN34" s="166"/>
+      <c r="AN34" s="200"/>
       <c r="AO34" s="10"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -24842,39 +24887,45 @@
     <row r="35" ht="25.5" customHeight="1">
       <c r="A35" s="155" cm="1">
         <f t="array" ref="A35">A34+1</f>
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s" s="167">
-        <v>151</v>
-      </c>
-      <c r="C35" t="s" s="156">
-        <v>152</v>
+        <v>133</v>
+      </c>
+      <c r="C35" t="s" s="197">
+        <v>134</v>
       </c>
       <c r="D35" s="165"/>
       <c r="E35" s="164"/>
       <c r="F35" s="163" cm="1">
         <f t="array" ref="F35">IF(AG35="","",I35-H35)</f>
-        <v>46395</v>
-      </c>
-      <c r="G35" s="160"/>
+        <v>46293</v>
+      </c>
+      <c r="G35" s="160">
+        <v>46300</v>
+      </c>
       <c r="H35" s="158">
         <v>7</v>
       </c>
       <c r="I35" s="161" cm="1">
         <f t="array" ref="I35">IF(AG35="","",P35-K35)</f>
-        <v>46402</v>
-      </c>
-      <c r="J35" s="160"/>
+        <v>46300</v>
+      </c>
+      <c r="J35" s="160">
+        <v>46302</v>
+      </c>
       <c r="K35" s="158">
         <v>7</v>
       </c>
-      <c r="L35" s="161"/>
+      <c r="L35" s="161">
+        <v>46302</v>
+      </c>
       <c r="M35" s="161"/>
       <c r="N35" s="161"/>
       <c r="O35" s="161"/>
       <c r="P35" s="161" cm="1">
         <f t="array" ref="P35">IF(AG35="","",AC35-R35-Q35)</f>
-        <v>46409</v>
+        <v>46307</v>
       </c>
       <c r="Q35" s="162">
         <v>7</v>
@@ -24893,18 +24944,18 @@
       <c r="AA35" s="161"/>
       <c r="AB35" s="160"/>
       <c r="AC35" s="163">
-        <v>46430</v>
+        <v>46328</v>
       </c>
       <c r="AD35" s="161" cm="1">
         <f t="array" ref="AD35">IF(AG35="","",$AG35-$AF35)</f>
-        <v>46432</v>
+        <v>46329</v>
       </c>
       <c r="AE35" s="160"/>
       <c r="AF35" s="196">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AG35" s="165">
-        <v>46462</v>
+        <v>46419</v>
       </c>
       <c r="AH35" s="164"/>
       <c r="AI35" s="163"/>
@@ -24912,8 +24963,8 @@
       <c r="AK35" s="161"/>
       <c r="AL35" s="160"/>
       <c r="AM35" s="165"/>
-      <c r="AN35" t="s" s="169">
-        <v>153</v>
+      <c r="AN35" t="s" s="198">
+        <v>135</v>
       </c>
       <c r="AO35" s="10"/>
       <c r="AP35" s="12"/>
@@ -24943,31 +24994,46 @@
     <row r="36" ht="25.5" customHeight="1">
       <c r="A36" s="155" cm="1">
         <f t="array" ref="A36">A35+1</f>
-        <v>25</v>
-      </c>
-      <c r="B36" s="151"/>
-      <c r="C36" s="170"/>
+        <v>16</v>
+      </c>
+      <c r="B36" t="s" s="167">
+        <v>136</v>
+      </c>
+      <c r="C36" t="s" s="156">
+        <v>137</v>
+      </c>
       <c r="D36" s="165"/>
       <c r="E36" s="164"/>
-      <c r="F36" t="str" s="195" cm="1">
+      <c r="F36" s="163" cm="1">
         <f t="array" ref="F36">IF(AG36="","",I36-H36)</f>
+        <v>46346</v>
       </c>
       <c r="G36" s="160"/>
-      <c r="H36" s="158"/>
-      <c r="I36" t="str" s="159" cm="1">
+      <c r="H36" s="158">
+        <v>7</v>
+      </c>
+      <c r="I36" s="161" cm="1">
         <f t="array" ref="I36">IF(AG36="","",P36-K36)</f>
+        <v>46353</v>
       </c>
       <c r="J36" s="160"/>
-      <c r="K36" s="158"/>
+      <c r="K36" s="158">
+        <v>7</v>
+      </c>
       <c r="L36" s="161"/>
       <c r="M36" s="161"/>
       <c r="N36" s="161"/>
       <c r="O36" s="161"/>
-      <c r="P36" t="str" s="159" cm="1">
+      <c r="P36" s="161" cm="1">
         <f t="array" ref="P36">IF(AG36="","",AC36-R36-Q36)</f>
-      </c>
-      <c r="Q36" s="162"/>
-      <c r="R36" s="162"/>
+        <v>46360</v>
+      </c>
+      <c r="Q36" s="162">
+        <v>7</v>
+      </c>
+      <c r="R36" s="162">
+        <v>14</v>
+      </c>
       <c r="S36" s="161"/>
       <c r="T36" s="161"/>
       <c r="U36" s="161"/>
@@ -24978,20 +25044,29 @@
       <c r="Z36" s="161"/>
       <c r="AA36" s="161"/>
       <c r="AB36" s="160"/>
-      <c r="AC36" s="163"/>
-      <c r="AD36" t="str" s="159" cm="1">
+      <c r="AC36" s="163">
+        <v>46381</v>
+      </c>
+      <c r="AD36" s="161" cm="1">
         <f t="array" ref="AD36">IF(AG36="","",$AG36-$AF36)</f>
+        <v>46389</v>
       </c>
       <c r="AE36" s="160"/>
-      <c r="AF36" s="196"/>
-      <c r="AG36" s="165"/>
+      <c r="AF36" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG36" s="165">
+        <v>46419</v>
+      </c>
       <c r="AH36" s="164"/>
       <c r="AI36" s="163"/>
       <c r="AJ36" s="161"/>
       <c r="AK36" s="161"/>
       <c r="AL36" s="160"/>
       <c r="AM36" s="165"/>
-      <c r="AN36" s="166"/>
+      <c r="AN36" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO36" s="10"/>
       <c r="AP36" s="12"/>
       <c r="AQ36" s="12"/>
@@ -25020,33 +25095,46 @@
     <row r="37" ht="25.5" customHeight="1">
       <c r="A37" s="155" cm="1">
         <f t="array" ref="A37">A36+1</f>
-        <v>26</v>
-      </c>
-      <c r="B37" s="151"/>
+        <v>17</v>
+      </c>
+      <c r="B37" t="s" s="167">
+        <v>139</v>
+      </c>
       <c r="C37" t="s" s="156">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D37" s="165"/>
       <c r="E37" s="164"/>
-      <c r="F37" t="str" s="195" cm="1">
+      <c r="F37" s="163" cm="1">
         <f t="array" ref="F37">IF(AG37="","",I37-H37)</f>
+        <v>46346</v>
       </c>
       <c r="G37" s="160"/>
-      <c r="H37" s="158"/>
-      <c r="I37" t="str" s="159" cm="1">
+      <c r="H37" s="158">
+        <v>7</v>
+      </c>
+      <c r="I37" s="161" cm="1">
         <f t="array" ref="I37">IF(AG37="","",P37-K37)</f>
+        <v>46353</v>
       </c>
       <c r="J37" s="160"/>
-      <c r="K37" s="158"/>
+      <c r="K37" s="158">
+        <v>7</v>
+      </c>
       <c r="L37" s="161"/>
       <c r="M37" s="161"/>
       <c r="N37" s="161"/>
       <c r="O37" s="161"/>
-      <c r="P37" t="str" s="159" cm="1">
+      <c r="P37" s="161" cm="1">
         <f t="array" ref="P37">IF(AG37="","",AC37-R37-Q37)</f>
-      </c>
-      <c r="Q37" s="162"/>
-      <c r="R37" s="162"/>
+        <v>46360</v>
+      </c>
+      <c r="Q37" s="162">
+        <v>7</v>
+      </c>
+      <c r="R37" s="162">
+        <v>14</v>
+      </c>
       <c r="S37" s="161"/>
       <c r="T37" s="161"/>
       <c r="U37" s="161"/>
@@ -25057,20 +25145,29 @@
       <c r="Z37" s="161"/>
       <c r="AA37" s="161"/>
       <c r="AB37" s="160"/>
-      <c r="AC37" s="163"/>
-      <c r="AD37" t="str" s="159" cm="1">
+      <c r="AC37" s="163">
+        <v>46381</v>
+      </c>
+      <c r="AD37" s="161" cm="1">
         <f t="array" ref="AD37">IF(AG37="","",$AG37-$AF37)</f>
+        <v>46389</v>
       </c>
       <c r="AE37" s="160"/>
-      <c r="AF37" s="196"/>
-      <c r="AG37" s="165"/>
+      <c r="AF37" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG37" s="165">
+        <v>46419</v>
+      </c>
       <c r="AH37" s="164"/>
       <c r="AI37" s="163"/>
       <c r="AJ37" s="161"/>
       <c r="AK37" s="161"/>
       <c r="AL37" s="160"/>
       <c r="AM37" s="165"/>
-      <c r="AN37" s="166"/>
+      <c r="AN37" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO37" s="10"/>
       <c r="AP37" s="12"/>
       <c r="AQ37" s="12"/>
@@ -25099,31 +25196,46 @@
     <row r="38" ht="25.5" customHeight="1">
       <c r="A38" s="155" cm="1">
         <f t="array" ref="A38">A37+1</f>
-        <v>27</v>
-      </c>
-      <c r="B38" s="151"/>
-      <c r="C38" s="170"/>
+        <v>18</v>
+      </c>
+      <c r="B38" t="s" s="167">
+        <v>141</v>
+      </c>
+      <c r="C38" t="s" s="156">
+        <v>142</v>
+      </c>
       <c r="D38" s="165"/>
       <c r="E38" s="164"/>
-      <c r="F38" t="str" s="195" cm="1">
+      <c r="F38" s="163" cm="1">
         <f t="array" ref="F38">IF(AG38="","",I38-H38)</f>
+        <v>46346</v>
       </c>
       <c r="G38" s="160"/>
-      <c r="H38" s="158"/>
-      <c r="I38" t="str" s="159" cm="1">
+      <c r="H38" s="158">
+        <v>7</v>
+      </c>
+      <c r="I38" s="161" cm="1">
         <f t="array" ref="I38">IF(AG38="","",P38-K38)</f>
+        <v>46353</v>
       </c>
       <c r="J38" s="160"/>
-      <c r="K38" s="158"/>
+      <c r="K38" s="158">
+        <v>7</v>
+      </c>
       <c r="L38" s="161"/>
       <c r="M38" s="161"/>
       <c r="N38" s="161"/>
       <c r="O38" s="161"/>
-      <c r="P38" t="str" s="159" cm="1">
+      <c r="P38" s="161" cm="1">
         <f t="array" ref="P38">IF(AG38="","",AC38-R38-Q38)</f>
-      </c>
-      <c r="Q38" s="162"/>
-      <c r="R38" s="162"/>
+        <v>46360</v>
+      </c>
+      <c r="Q38" s="162">
+        <v>7</v>
+      </c>
+      <c r="R38" s="162">
+        <v>14</v>
+      </c>
       <c r="S38" s="161"/>
       <c r="T38" s="161"/>
       <c r="U38" s="161"/>
@@ -25134,20 +25246,29 @@
       <c r="Z38" s="161"/>
       <c r="AA38" s="161"/>
       <c r="AB38" s="160"/>
-      <c r="AC38" s="163"/>
-      <c r="AD38" t="str" s="159" cm="1">
+      <c r="AC38" s="163">
+        <v>46381</v>
+      </c>
+      <c r="AD38" s="161" cm="1">
         <f t="array" ref="AD38">IF(AG38="","",$AG38-$AF38)</f>
+        <v>46389</v>
       </c>
       <c r="AE38" s="160"/>
-      <c r="AF38" s="196"/>
-      <c r="AG38" s="165"/>
+      <c r="AF38" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG38" s="165">
+        <v>46419</v>
+      </c>
       <c r="AH38" s="164"/>
       <c r="AI38" s="163"/>
       <c r="AJ38" s="161"/>
       <c r="AK38" s="161"/>
       <c r="AL38" s="160"/>
       <c r="AM38" s="165"/>
-      <c r="AN38" s="166"/>
+      <c r="AN38" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO38" s="10"/>
       <c r="AP38" s="12"/>
       <c r="AQ38" s="12"/>
@@ -25176,10 +25297,12 @@
     <row r="39" ht="25.5" customHeight="1">
       <c r="A39" s="155" cm="1">
         <f t="array" ref="A39">A38+1</f>
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B39" s="151"/>
-      <c r="C39" s="170"/>
+      <c r="C39" t="s" s="156">
+        <v>143</v>
+      </c>
       <c r="D39" s="165"/>
       <c r="E39" s="164"/>
       <c r="F39" t="str" s="195" cm="1">
@@ -25253,31 +25376,50 @@
     <row r="40" ht="25.5" customHeight="1">
       <c r="A40" s="155" cm="1">
         <f t="array" ref="A40">A39+1</f>
-        <v>29</v>
-      </c>
-      <c r="B40" s="151"/>
-      <c r="C40" s="170"/>
+        <v>20</v>
+      </c>
+      <c r="B40" t="s" s="167">
+        <v>144</v>
+      </c>
+      <c r="C40" t="s" s="156">
+        <v>145</v>
+      </c>
       <c r="D40" s="165"/>
       <c r="E40" s="164"/>
-      <c r="F40" t="str" s="195" cm="1">
+      <c r="F40" s="163" cm="1">
         <f t="array" ref="F40">IF(AG40="","",I40-H40)</f>
-      </c>
-      <c r="G40" s="160"/>
-      <c r="H40" s="158"/>
-      <c r="I40" t="str" s="159" cm="1">
+        <v>46345</v>
+      </c>
+      <c r="G40" s="160">
+        <v>46276</v>
+      </c>
+      <c r="H40" s="158">
+        <v>7</v>
+      </c>
+      <c r="I40" s="161" cm="1">
         <f t="array" ref="I40">IF(AG40="","",P40-K40)</f>
-      </c>
-      <c r="J40" s="160"/>
-      <c r="K40" s="158"/>
+        <v>46352</v>
+      </c>
+      <c r="J40" s="160">
+        <v>46291</v>
+      </c>
+      <c r="K40" s="158">
+        <v>7</v>
+      </c>
       <c r="L40" s="161"/>
       <c r="M40" s="161"/>
       <c r="N40" s="161"/>
       <c r="O40" s="161"/>
-      <c r="P40" t="str" s="159" cm="1">
+      <c r="P40" s="161" cm="1">
         <f t="array" ref="P40">IF(AG40="","",AC40-R40-Q40)</f>
-      </c>
-      <c r="Q40" s="162"/>
-      <c r="R40" s="162"/>
+        <v>46359</v>
+      </c>
+      <c r="Q40" s="162">
+        <v>7</v>
+      </c>
+      <c r="R40" s="162">
+        <v>14</v>
+      </c>
       <c r="S40" s="161"/>
       <c r="T40" s="161"/>
       <c r="U40" s="161"/>
@@ -25288,20 +25430,29 @@
       <c r="Z40" s="161"/>
       <c r="AA40" s="161"/>
       <c r="AB40" s="160"/>
-      <c r="AC40" s="163"/>
-      <c r="AD40" t="str" s="159" cm="1">
+      <c r="AC40" s="163">
+        <v>46380</v>
+      </c>
+      <c r="AD40" s="161" cm="1">
         <f t="array" ref="AD40">IF(AG40="","",$AG40-$AF40)</f>
+        <v>46380</v>
       </c>
       <c r="AE40" s="160"/>
-      <c r="AF40" s="196"/>
-      <c r="AG40" s="165"/>
+      <c r="AF40" s="196">
+        <v>60</v>
+      </c>
+      <c r="AG40" s="165">
+        <v>46440</v>
+      </c>
       <c r="AH40" s="164"/>
       <c r="AI40" s="163"/>
       <c r="AJ40" s="161"/>
       <c r="AK40" s="161"/>
       <c r="AL40" s="160"/>
       <c r="AM40" s="165"/>
-      <c r="AN40" s="166"/>
+      <c r="AN40" t="s" s="169">
+        <v>146</v>
+      </c>
       <c r="AO40" s="10"/>
       <c r="AP40" s="12"/>
       <c r="AQ40" s="12"/>
@@ -25330,10 +25481,12 @@
     <row r="41" ht="25.5" customHeight="1">
       <c r="A41" s="155" cm="1">
         <f t="array" ref="A41">A40+1</f>
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B41" s="151"/>
-      <c r="C41" s="170"/>
+      <c r="C41" t="s" s="156">
+        <v>147</v>
+      </c>
       <c r="D41" s="165"/>
       <c r="E41" s="164"/>
       <c r="F41" t="str" s="195" cm="1">
@@ -25407,31 +25560,52 @@
     <row r="42" ht="25.5" customHeight="1">
       <c r="A42" s="155" cm="1">
         <f t="array" ref="A42">A41+1</f>
-        <v>31</v>
-      </c>
-      <c r="B42" s="151"/>
-      <c r="C42" s="170"/>
+        <v>22</v>
+      </c>
+      <c r="B42" t="s" s="167">
+        <v>148</v>
+      </c>
+      <c r="C42" t="s" s="156">
+        <v>149</v>
+      </c>
       <c r="D42" s="165"/>
       <c r="E42" s="164"/>
-      <c r="F42" t="str" s="195" cm="1">
+      <c r="F42" s="163" cm="1">
         <f t="array" ref="F42">IF(AG42="","",I42-H42)</f>
-      </c>
-      <c r="G42" s="160"/>
-      <c r="H42" s="158"/>
-      <c r="I42" t="str" s="159" cm="1">
+        <v>46381</v>
+      </c>
+      <c r="G42" s="160">
+        <v>46297</v>
+      </c>
+      <c r="H42" s="158">
+        <v>7</v>
+      </c>
+      <c r="I42" s="161" cm="1">
         <f t="array" ref="I42">IF(AG42="","",P42-K42)</f>
-      </c>
-      <c r="J42" s="160"/>
-      <c r="K42" s="158"/>
-      <c r="L42" s="161"/>
+        <v>46388</v>
+      </c>
+      <c r="J42" s="160">
+        <v>46302</v>
+      </c>
+      <c r="K42" s="158">
+        <v>7</v>
+      </c>
+      <c r="L42" s="161">
+        <v>46302</v>
+      </c>
       <c r="M42" s="161"/>
       <c r="N42" s="161"/>
       <c r="O42" s="161"/>
-      <c r="P42" t="str" s="159" cm="1">
+      <c r="P42" s="161" cm="1">
         <f t="array" ref="P42">IF(AG42="","",AC42-R42-Q42)</f>
-      </c>
-      <c r="Q42" s="162"/>
-      <c r="R42" s="162"/>
+        <v>46395</v>
+      </c>
+      <c r="Q42" s="162">
+        <v>7</v>
+      </c>
+      <c r="R42" s="162">
+        <v>14</v>
+      </c>
       <c r="S42" s="161"/>
       <c r="T42" s="161"/>
       <c r="U42" s="161"/>
@@ -25442,20 +25616,29 @@
       <c r="Z42" s="161"/>
       <c r="AA42" s="161"/>
       <c r="AB42" s="160"/>
-      <c r="AC42" s="163"/>
-      <c r="AD42" t="str" s="159" cm="1">
+      <c r="AC42" s="163">
+        <v>46416</v>
+      </c>
+      <c r="AD42" s="161" cm="1">
         <f t="array" ref="AD42">IF(AG42="","",$AG42-$AF42)</f>
+        <v>46417</v>
       </c>
       <c r="AE42" s="160"/>
-      <c r="AF42" s="196"/>
-      <c r="AG42" s="165"/>
+      <c r="AF42" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG42" s="165">
+        <v>46447</v>
+      </c>
       <c r="AH42" s="164"/>
       <c r="AI42" s="163"/>
       <c r="AJ42" s="161"/>
       <c r="AK42" s="161"/>
       <c r="AL42" s="160"/>
       <c r="AM42" s="165"/>
-      <c r="AN42" s="166"/>
+      <c r="AN42" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO42" s="10"/>
       <c r="AP42" s="12"/>
       <c r="AQ42" s="12"/>
@@ -25484,10 +25667,12 @@
     <row r="43" ht="25.5" customHeight="1">
       <c r="A43" s="155" cm="1">
         <f t="array" ref="A43">A42+1</f>
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B43" s="151"/>
-      <c r="C43" s="170"/>
+      <c r="C43" t="s" s="156">
+        <v>150</v>
+      </c>
       <c r="D43" s="165"/>
       <c r="E43" s="164"/>
       <c r="F43" t="str" s="195" cm="1">
@@ -25561,31 +25746,46 @@
     <row r="44" ht="25.5" customHeight="1">
       <c r="A44" s="155" cm="1">
         <f t="array" ref="A44">A43+1</f>
-        <v>33</v>
-      </c>
-      <c r="B44" s="151"/>
-      <c r="C44" s="170"/>
+        <v>24</v>
+      </c>
+      <c r="B44" t="s" s="167">
+        <v>151</v>
+      </c>
+      <c r="C44" t="s" s="156">
+        <v>152</v>
+      </c>
       <c r="D44" s="165"/>
       <c r="E44" s="164"/>
-      <c r="F44" t="str" s="195" cm="1">
+      <c r="F44" s="163" cm="1">
         <f t="array" ref="F44">IF(AG44="","",I44-H44)</f>
+        <v>46395</v>
       </c>
       <c r="G44" s="160"/>
-      <c r="H44" s="158"/>
-      <c r="I44" t="str" s="159" cm="1">
+      <c r="H44" s="158">
+        <v>7</v>
+      </c>
+      <c r="I44" s="161" cm="1">
         <f t="array" ref="I44">IF(AG44="","",P44-K44)</f>
+        <v>46402</v>
       </c>
       <c r="J44" s="160"/>
-      <c r="K44" s="158"/>
+      <c r="K44" s="158">
+        <v>7</v>
+      </c>
       <c r="L44" s="161"/>
       <c r="M44" s="161"/>
       <c r="N44" s="161"/>
       <c r="O44" s="161"/>
-      <c r="P44" t="str" s="159" cm="1">
+      <c r="P44" s="161" cm="1">
         <f t="array" ref="P44">IF(AG44="","",AC44-R44-Q44)</f>
-      </c>
-      <c r="Q44" s="162"/>
-      <c r="R44" s="162"/>
+        <v>46409</v>
+      </c>
+      <c r="Q44" s="162">
+        <v>7</v>
+      </c>
+      <c r="R44" s="162">
+        <v>14</v>
+      </c>
       <c r="S44" s="161"/>
       <c r="T44" s="161"/>
       <c r="U44" s="161"/>
@@ -25596,20 +25796,29 @@
       <c r="Z44" s="161"/>
       <c r="AA44" s="161"/>
       <c r="AB44" s="160"/>
-      <c r="AC44" s="163"/>
-      <c r="AD44" t="str" s="159" cm="1">
+      <c r="AC44" s="163">
+        <v>46430</v>
+      </c>
+      <c r="AD44" s="161" cm="1">
         <f t="array" ref="AD44">IF(AG44="","",$AG44-$AF44)</f>
+        <v>46432</v>
       </c>
       <c r="AE44" s="160"/>
-      <c r="AF44" s="196"/>
-      <c r="AG44" s="165"/>
+      <c r="AF44" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG44" s="165">
+        <v>46462</v>
+      </c>
       <c r="AH44" s="164"/>
       <c r="AI44" s="163"/>
       <c r="AJ44" s="161"/>
       <c r="AK44" s="161"/>
       <c r="AL44" s="160"/>
       <c r="AM44" s="165"/>
-      <c r="AN44" s="166"/>
+      <c r="AN44" t="s" s="169">
+        <v>153</v>
+      </c>
       <c r="AO44" s="10"/>
       <c r="AP44" s="12"/>
       <c r="AQ44" s="12"/>
@@ -25638,7 +25847,7 @@
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" s="155" cm="1">
         <f t="array" ref="A45">A44+1</f>
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B45" s="151"/>
       <c r="C45" s="170"/>
@@ -25715,11 +25924,11 @@
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" s="155" cm="1">
         <f t="array" ref="A46">A45+1</f>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B46" s="151"/>
       <c r="C46" t="s" s="156">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D46" s="165"/>
       <c r="E46" s="164"/>
@@ -25794,7 +26003,7 @@
     <row r="47" ht="25.5" customHeight="1">
       <c r="A47" s="155" cm="1">
         <f t="array" ref="A47">A46+1</f>
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B47" s="151"/>
       <c r="C47" s="170"/>
@@ -25871,7 +26080,7 @@
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" s="155" cm="1">
         <f t="array" ref="A48">A47+1</f>
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B48" s="151"/>
       <c r="C48" s="170"/>
@@ -25948,7 +26157,7 @@
     <row r="49" ht="25.5" customHeight="1">
       <c r="A49" s="155" cm="1">
         <f t="array" ref="A49">A48+1</f>
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B49" s="151"/>
       <c r="C49" s="170"/>
@@ -26025,7 +26234,7 @@
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" s="155" cm="1">
         <f t="array" ref="A50">A49+1</f>
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B50" s="151"/>
       <c r="C50" s="170"/>
@@ -26102,7 +26311,7 @@
     <row r="51" ht="25.5" customHeight="1">
       <c r="A51" s="155" cm="1">
         <f t="array" ref="A51">A50+1</f>
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B51" s="151"/>
       <c r="C51" s="170"/>
@@ -26179,7 +26388,7 @@
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" s="155" cm="1">
         <f t="array" ref="A52">A51+1</f>
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B52" s="151"/>
       <c r="C52" s="170"/>
@@ -26256,7 +26465,7 @@
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" s="155" cm="1">
         <f t="array" ref="A53">A52+1</f>
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B53" s="151"/>
       <c r="C53" s="170"/>
@@ -26333,12 +26542,10 @@
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" s="155" cm="1">
         <f t="array" ref="A54">A53+1</f>
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B54" s="151"/>
-      <c r="C54" t="s" s="156">
-        <v>156</v>
-      </c>
+      <c r="C54" s="170"/>
       <c r="D54" s="165"/>
       <c r="E54" s="164"/>
       <c r="F54" t="str" s="195" cm="1">
@@ -26412,10 +26619,12 @@
     <row r="55" ht="25.5" customHeight="1">
       <c r="A55" s="155" cm="1">
         <f t="array" ref="A55">A54+1</f>
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B55" s="151"/>
-      <c r="C55" s="170"/>
+      <c r="C55" t="s" s="156">
+        <v>155</v>
+      </c>
       <c r="D55" s="165"/>
       <c r="E55" s="164"/>
       <c r="F55" t="str" s="195" cm="1">
@@ -26489,7 +26698,7 @@
     <row r="56" ht="25.5" customHeight="1">
       <c r="A56" s="155" cm="1">
         <f t="array" ref="A56">A55+1</f>
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B56" s="151"/>
       <c r="C56" s="170"/>
@@ -26566,7 +26775,7 @@
     <row r="57" ht="25.5" customHeight="1">
       <c r="A57" s="155" cm="1">
         <f t="array" ref="A57">A56+1</f>
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B57" s="151"/>
       <c r="C57" s="170"/>
@@ -26643,7 +26852,7 @@
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" s="155" cm="1">
         <f t="array" ref="A58">A57+1</f>
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B58" s="151"/>
       <c r="C58" s="170"/>
@@ -26720,7 +26929,7 @@
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="155" cm="1">
         <f t="array" ref="A59">A58+1</f>
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="170"/>
@@ -26797,7 +27006,7 @@
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" s="155" cm="1">
         <f t="array" ref="A60">A59+1</f>
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B60" s="151"/>
       <c r="C60" s="170"/>
@@ -26874,7 +27083,7 @@
     <row r="61" ht="25.5" customHeight="1">
       <c r="A61" s="155" cm="1">
         <f t="array" ref="A61">A60+1</f>
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B61" s="151"/>
       <c r="C61" s="170"/>
@@ -26951,7 +27160,7 @@
     <row r="62" ht="25.5" customHeight="1">
       <c r="A62" s="155" cm="1">
         <f t="array" ref="A62">A61+1</f>
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B62" s="151"/>
       <c r="C62" s="170"/>
@@ -27028,10 +27237,12 @@
     <row r="63" ht="25.5" customHeight="1">
       <c r="A63" s="155" cm="1">
         <f t="array" ref="A63">A62+1</f>
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B63" s="151"/>
-      <c r="C63" s="170"/>
+      <c r="C63" t="s" s="156">
+        <v>156</v>
+      </c>
       <c r="D63" s="165"/>
       <c r="E63" s="164"/>
       <c r="F63" t="str" s="195" cm="1">

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22720,7 +22720,7 @@
       <c r="AA12" s="161"/>
       <c r="AB12" s="160"/>
       <c r="AC12" s="163">
-        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD12" s="161">
         <f>IF(AG12="","",$AG12-$AF12)</f>
@@ -22818,7 +22818,7 @@
       <c r="AA13" s="161"/>
       <c r="AB13" s="160"/>
       <c r="AC13" s="163">
-        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD13" s="161">
         <f>IF(AG13="","",$AG13-$AF13)</f>
@@ -22920,7 +22920,7 @@
       <c r="AA14" s="161"/>
       <c r="AB14" s="160"/>
       <c r="AC14" s="163">
-        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD14" s="161">
         <f>IF(AG14="","",$AG14-$AF14)</f>
@@ -23020,7 +23020,7 @@
       <c r="AA15" s="161"/>
       <c r="AB15" s="160"/>
       <c r="AC15" s="163">
-        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD15" s="161">
         <f>IF(AG15="","",$AG15-$AF15)</f>
@@ -23122,7 +23122,7 @@
       <c r="AA16" s="161"/>
       <c r="AB16" s="160"/>
       <c r="AC16" s="163">
-        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD16" s="161">
         <f>IF(AG16="","",$AG16-$AF16)</f>
@@ -23220,7 +23220,7 @@
       <c r="AA17" s="161"/>
       <c r="AB17" s="160"/>
       <c r="AC17" s="163">
-        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD17" s="161">
         <f>IF(AG17="","",$AG17-$AF17)</f>
@@ -23322,7 +23322,7 @@
       <c r="AA18" s="161"/>
       <c r="AB18" s="160"/>
       <c r="AC18" s="163">
-        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD18" s="161">
         <f>IF(AG18="","",$AG18-$AF18)</f>
@@ -23420,7 +23420,7 @@
       <c r="AA19" s="161"/>
       <c r="AB19" s="160"/>
       <c r="AC19" s="163">
-        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD19" s="161">
         <f>IF(AG19="","",$AG19-$AF19)</f>
@@ -23518,7 +23518,7 @@
       <c r="AA20" s="161"/>
       <c r="AB20" s="160"/>
       <c r="AC20" s="163">
-        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD20" s="161">
         <f>IF(AG20="","",$AG20-$AF20)</f>
@@ -23618,7 +23618,7 @@
       <c r="AA21" s="161"/>
       <c r="AB21" s="160"/>
       <c r="AC21" s="163">
-        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD21" s="161">
         <f>IF(AG21="","",$AG21-$AF21)</f>
@@ -23720,7 +23720,7 @@
       <c r="AA22" s="161"/>
       <c r="AB22" s="160"/>
       <c r="AC22" s="163">
-        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD22" s="161">
         <f>IF(AG22="","",$AG22-$AF22)</f>
@@ -23818,7 +23818,7 @@
       <c r="AA23" s="161"/>
       <c r="AB23" s="160"/>
       <c r="AC23" s="163">
-        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD23" s="161">
         <f>IF(AG23="","",$AG23-$AF23)</f>
@@ -23916,7 +23916,7 @@
       <c r="AA24" s="161"/>
       <c r="AB24" s="160"/>
       <c r="AC24" s="163">
-        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD24" s="161">
         <f>IF(AG24="","",$AG24-$AF24)</f>
@@ -24014,7 +24014,7 @@
       <c r="AA25" s="161"/>
       <c r="AB25" s="160"/>
       <c r="AC25" s="163">
-        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD25" s="161">
         <f>IF(AG25="","",$AG25-$AF25)</f>
@@ -24112,7 +24112,7 @@
       <c r="AA26" s="161"/>
       <c r="AB26" s="160"/>
       <c r="AC26" s="163">
-        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46388,46398,46429,46441,46468}))</f>
+        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD26" s="161">
         <f>IF(AG26="","",$AG26-$AF26)</f>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22720,7 +22720,7 @@
       <c r="AA12" s="161"/>
       <c r="AB12" s="160"/>
       <c r="AC12" s="163">
-        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD12" s="161">
         <f>IF(AG12="","",$AG12-$AF12)</f>
@@ -22818,7 +22818,7 @@
       <c r="AA13" s="161"/>
       <c r="AB13" s="160"/>
       <c r="AC13" s="163">
-        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD13" s="161">
         <f>IF(AG13="","",$AG13-$AF13)</f>
@@ -22920,7 +22920,7 @@
       <c r="AA14" s="161"/>
       <c r="AB14" s="160"/>
       <c r="AC14" s="163">
-        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD14" s="161">
         <f>IF(AG14="","",$AG14-$AF14)</f>
@@ -23020,7 +23020,7 @@
       <c r="AA15" s="161"/>
       <c r="AB15" s="160"/>
       <c r="AC15" s="163">
-        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD15" s="161">
         <f>IF(AG15="","",$AG15-$AF15)</f>
@@ -23122,7 +23122,7 @@
       <c r="AA16" s="161"/>
       <c r="AB16" s="160"/>
       <c r="AC16" s="163">
-        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD16" s="161">
         <f>IF(AG16="","",$AG16-$AF16)</f>
@@ -23220,7 +23220,7 @@
       <c r="AA17" s="161"/>
       <c r="AB17" s="160"/>
       <c r="AC17" s="163">
-        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD17" s="161">
         <f>IF(AG17="","",$AG17-$AF17)</f>
@@ -23322,7 +23322,7 @@
       <c r="AA18" s="161"/>
       <c r="AB18" s="160"/>
       <c r="AC18" s="163">
-        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD18" s="161">
         <f>IF(AG18="","",$AG18-$AF18)</f>
@@ -23420,7 +23420,7 @@
       <c r="AA19" s="161"/>
       <c r="AB19" s="160"/>
       <c r="AC19" s="163">
-        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD19" s="161">
         <f>IF(AG19="","",$AG19-$AF19)</f>
@@ -23518,7 +23518,7 @@
       <c r="AA20" s="161"/>
       <c r="AB20" s="160"/>
       <c r="AC20" s="163">
-        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD20" s="161">
         <f>IF(AG20="","",$AG20-$AF20)</f>
@@ -23618,7 +23618,7 @@
       <c r="AA21" s="161"/>
       <c r="AB21" s="160"/>
       <c r="AC21" s="163">
-        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD21" s="161">
         <f>IF(AG21="","",$AG21-$AF21)</f>
@@ -23720,7 +23720,7 @@
       <c r="AA22" s="161"/>
       <c r="AB22" s="160"/>
       <c r="AC22" s="163">
-        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD22" s="161">
         <f>IF(AG22="","",$AG22-$AF22)</f>
@@ -23818,7 +23818,7 @@
       <c r="AA23" s="161"/>
       <c r="AB23" s="160"/>
       <c r="AC23" s="163">
-        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD23" s="161">
         <f>IF(AG23="","",$AG23-$AF23)</f>
@@ -23916,7 +23916,7 @@
       <c r="AA24" s="161"/>
       <c r="AB24" s="160"/>
       <c r="AC24" s="163">
-        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD24" s="161">
         <f>IF(AG24="","",$AG24-$AF24)</f>
@@ -24014,7 +24014,7 @@
       <c r="AA25" s="161"/>
       <c r="AB25" s="160"/>
       <c r="AC25" s="163">
-        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD25" s="161">
         <f>IF(AG25="","",$AG25-$AF25)</f>
@@ -24112,7 +24112,7 @@
       <c r="AA26" s="161"/>
       <c r="AB26" s="160"/>
       <c r="AC26" s="163">
-        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD26" s="161">
         <f>IF(AG26="","",$AG26-$AF26)</f>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22720,7 +22720,7 @@
       <c r="AA12" s="161"/>
       <c r="AB12" s="160"/>
       <c r="AC12" s="163">
-        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD12" s="161">
         <f>IF(AG12="","",$AG12-$AF12)</f>
@@ -22818,7 +22818,7 @@
       <c r="AA13" s="161"/>
       <c r="AB13" s="160"/>
       <c r="AC13" s="163">
-        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD13" s="161">
         <f>IF(AG13="","",$AG13-$AF13)</f>
@@ -22920,7 +22920,7 @@
       <c r="AA14" s="161"/>
       <c r="AB14" s="160"/>
       <c r="AC14" s="163">
-        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD14" s="161">
         <f>IF(AG14="","",$AG14-$AF14)</f>
@@ -23020,7 +23020,7 @@
       <c r="AA15" s="161"/>
       <c r="AB15" s="160"/>
       <c r="AC15" s="163">
-        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD15" s="161">
         <f>IF(AG15="","",$AG15-$AF15)</f>
@@ -23122,7 +23122,7 @@
       <c r="AA16" s="161"/>
       <c r="AB16" s="160"/>
       <c r="AC16" s="163">
-        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD16" s="161">
         <f>IF(AG16="","",$AG16-$AF16)</f>
@@ -23220,7 +23220,7 @@
       <c r="AA17" s="161"/>
       <c r="AB17" s="160"/>
       <c r="AC17" s="163">
-        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD17" s="161">
         <f>IF(AG17="","",$AG17-$AF17)</f>
@@ -23322,7 +23322,7 @@
       <c r="AA18" s="161"/>
       <c r="AB18" s="160"/>
       <c r="AC18" s="163">
-        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD18" s="161">
         <f>IF(AG18="","",$AG18-$AF18)</f>
@@ -23420,7 +23420,7 @@
       <c r="AA19" s="161"/>
       <c r="AB19" s="160"/>
       <c r="AC19" s="163">
-        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD19" s="161">
         <f>IF(AG19="","",$AG19-$AF19)</f>
@@ -23518,7 +23518,7 @@
       <c r="AA20" s="161"/>
       <c r="AB20" s="160"/>
       <c r="AC20" s="163">
-        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD20" s="161">
         <f>IF(AG20="","",$AG20-$AF20)</f>
@@ -23618,7 +23618,7 @@
       <c r="AA21" s="161"/>
       <c r="AB21" s="160"/>
       <c r="AC21" s="163">
-        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD21" s="161">
         <f>IF(AG21="","",$AG21-$AF21)</f>
@@ -23720,7 +23720,7 @@
       <c r="AA22" s="161"/>
       <c r="AB22" s="160"/>
       <c r="AC22" s="163">
-        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD22" s="161">
         <f>IF(AG22="","",$AG22-$AF22)</f>
@@ -23818,7 +23818,7 @@
       <c r="AA23" s="161"/>
       <c r="AB23" s="160"/>
       <c r="AC23" s="163">
-        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD23" s="161">
         <f>IF(AG23="","",$AG23-$AF23)</f>
@@ -23916,7 +23916,7 @@
       <c r="AA24" s="161"/>
       <c r="AB24" s="160"/>
       <c r="AC24" s="163">
-        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD24" s="161">
         <f>IF(AG24="","",$AG24-$AF24)</f>
@@ -24014,7 +24014,7 @@
       <c r="AA25" s="161"/>
       <c r="AB25" s="160"/>
       <c r="AC25" s="163">
-        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD25" s="161">
         <f>IF(AG25="","",$AG25-$AF25)</f>
@@ -24112,7 +24112,7 @@
       <c r="AA26" s="161"/>
       <c r="AB26" s="160"/>
       <c r="AC26" s="163">
-        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46382,46383,46384,46385,46386,46387,46388,46389,46390,46398,46429,46441,46468}))</f>
+        <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
       </c>
       <c r="AD26" s="161">
         <f>IF(AG26="","",$AG26-$AF26)</f>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -21722,7 +21722,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" t="str" s="172" cm="1">
+      <c r="A1" s="172" cm="1" t="str">
         <f t="array" ref="A1">'①施工図リスト'!A1</f>
         <v>現場／統括：、現場責任者：新地工事長、主任：、担当：</v>
       </c>
@@ -21799,7 +21799,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="14"/>
-      <c r="C2" t="str" s="16" cm="1">
+      <c r="C2" s="16" cm="1" t="str">
         <f t="array" ref="C2">'①施工図リスト'!C2</f>
         <v>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事</v>
       </c>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="BK2" s="32" cm="1">
         <f t="array" ref="BK2">BI3/BH3</f>
-        <v>0.166666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="BL2" s="33"/>
     </row>
@@ -21970,18 +21970,18 @@
       <c r="BG3" s="12"/>
       <c r="BH3" s="60" cm="1">
         <f t="array" ref="BH3">COUNTA($AG$10:$AG$210)*6</f>
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="BI3" s="60" cm="1">
         <f t="array" ref="BI3">COUNTA($G$10:$G$210)+COUNTA($J$10:$J$210)+COUNTA($L$10:$L$210)+COUNTA($M$10:$M$210)+COUNTA($S$10:$S$210)+COUNTA($T$10:$T$210)</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BJ3" t="s" s="31">
         <v>23</v>
       </c>
       <c r="BK3" s="33" cm="1">
         <f t="array" ref="BK3">1-BK2</f>
-        <v>0.833333333333333</v>
+        <v>0.866666666666667</v>
       </c>
       <c r="BL3" s="33"/>
     </row>
@@ -22596,13 +22596,15 @@
       </c>
       <c r="D11" s="165"/>
       <c r="E11" s="164"/>
-      <c r="F11" t="str" s="195" cm="1">
+      <c r="F11" s="195" cm="1" t="str">
         <f t="array" ref="F11">IF(AG11="","",I11-H11)</f>
+        <v/>
       </c>
       <c r="G11" s="160"/>
       <c r="H11" s="158"/>
-      <c r="I11" t="str" s="159" cm="1">
+      <c r="I11" s="159" cm="1" t="str">
         <f t="array" ref="I11">IF(AG11="","",P11-K11)</f>
+        <v/>
       </c>
       <c r="J11" s="160"/>
       <c r="K11" s="158"/>
@@ -22610,8 +22612,9 @@
       <c r="M11" s="161"/>
       <c r="N11" s="161"/>
       <c r="O11" s="161"/>
-      <c r="P11" t="str" s="159" cm="1">
+      <c r="P11" s="159" cm="1" t="str">
         <f t="array" ref="P11">IF(AG11="","",AC11-R11-Q11)</f>
+        <v/>
       </c>
       <c r="Q11" s="162"/>
       <c r="R11" s="162"/>
@@ -22626,8 +22629,9 @@
       <c r="AA11" s="161"/>
       <c r="AB11" s="160"/>
       <c r="AC11" s="163"/>
-      <c r="AD11" t="str" s="159" cm="1">
+      <c r="AD11" s="159" cm="1" t="str">
         <f t="array" ref="AD11">IF(AG11="","",$AG11-$AF11)</f>
+        <v/>
       </c>
       <c r="AE11" s="160"/>
       <c r="AF11" s="196"/>
@@ -22667,6 +22671,7 @@
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" s="155">
         <f>A11+1</f>
+        <v>1</v>
       </c>
       <c r="B12" s="167" t="inlineStr">
         <is>
@@ -22682,6 +22687,7 @@
       <c r="E12" s="164"/>
       <c r="F12" s="163">
         <f>IF(AG12="","",I12-H12)</f>
+        <v>46309</v>
       </c>
       <c r="G12" s="160"/>
       <c r="H12" s="158">
@@ -22689,6 +22695,7 @@
       </c>
       <c r="I12" s="161">
         <f>IF(AG12="","",P12-K12)</f>
+        <v>46316</v>
       </c>
       <c r="J12" s="160"/>
       <c r="K12" s="158">
@@ -22702,6 +22709,7 @@
       <c r="O12" s="161"/>
       <c r="P12" s="161">
         <f>IF(AG12="","",AC12-R12-Q12)</f>
+        <v>46323</v>
       </c>
       <c r="Q12" s="162">
         <v>7</v>
@@ -22721,9 +22729,11 @@
       <c r="AB12" s="160"/>
       <c r="AC12" s="163">
         <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46344</v>
       </c>
       <c r="AD12" s="161">
         <f>IF(AG12="","",$AG12-$AF12)</f>
+        <v>46344</v>
       </c>
       <c r="AE12" s="160"/>
       <c r="AF12" s="196">
@@ -22767,6 +22777,7 @@
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" s="155">
         <f>A12+1</f>
+        <v>2</v>
       </c>
       <c r="B13" s="167" t="inlineStr">
         <is>
@@ -22782,6 +22793,7 @@
       <c r="E13" s="164"/>
       <c r="F13" s="163">
         <f>IF(AG13="","",I13-H13)</f>
+        <v>46308</v>
       </c>
       <c r="G13" s="160"/>
       <c r="H13" s="158">
@@ -22789,6 +22801,7 @@
       </c>
       <c r="I13" s="161">
         <f>IF(AG13="","",P13-K13)</f>
+        <v>46315</v>
       </c>
       <c r="J13" s="160"/>
       <c r="K13" s="158">
@@ -22800,6 +22813,7 @@
       <c r="O13" s="161"/>
       <c r="P13" s="161">
         <f>IF(AG13="","",AC13-R13-Q13)</f>
+        <v>46322</v>
       </c>
       <c r="Q13" s="162">
         <v>7</v>
@@ -22819,9 +22833,11 @@
       <c r="AB13" s="160"/>
       <c r="AC13" s="163">
         <f>IF(AG13="","",WORKDAY(AG13-AF13+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46343</v>
       </c>
       <c r="AD13" s="161">
         <f>IF(AG13="","",$AG13-$AF13)</f>
+        <v>46343</v>
       </c>
       <c r="AE13" s="160"/>
       <c r="AF13" s="196">
@@ -22869,6 +22885,7 @@
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" s="155">
         <f>A13+1</f>
+        <v>3</v>
       </c>
       <c r="B14" s="167" t="inlineStr">
         <is>
@@ -22884,6 +22901,7 @@
       <c r="E14" s="164"/>
       <c r="F14" s="163">
         <f>IF(AG14="","",I14-H14)</f>
+        <v>46343</v>
       </c>
       <c r="G14" s="160"/>
       <c r="H14" s="158">
@@ -22891,6 +22909,7 @@
       </c>
       <c r="I14" s="161">
         <f>IF(AG14="","",P14-K14)</f>
+        <v>46350</v>
       </c>
       <c r="J14" s="160"/>
       <c r="K14" s="158">
@@ -22902,6 +22921,7 @@
       <c r="O14" s="161"/>
       <c r="P14" s="161">
         <f>IF(AG14="","",AC14-R14-Q14)</f>
+        <v>46357</v>
       </c>
       <c r="Q14" s="162">
         <v>7</v>
@@ -22921,9 +22941,11 @@
       <c r="AB14" s="160"/>
       <c r="AC14" s="163">
         <f>IF(AG14="","",WORKDAY(AG14-AF14+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46378</v>
       </c>
       <c r="AD14" s="161">
         <f>IF(AG14="","",$AG14-$AF14)</f>
+        <v>46378</v>
       </c>
       <c r="AE14" s="160"/>
       <c r="AF14" s="196">
@@ -22967,6 +22989,7 @@
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" s="155">
         <f>A14+1</f>
+        <v>4</v>
       </c>
       <c r="B15" s="167" t="inlineStr">
         <is>
@@ -22982,6 +23005,7 @@
       <c r="E15" s="164"/>
       <c r="F15" s="163">
         <f>IF(AG15="","",I15-H15)</f>
+        <v>46346</v>
       </c>
       <c r="G15" s="160"/>
       <c r="H15" s="158">
@@ -22989,6 +23013,7 @@
       </c>
       <c r="I15" s="161">
         <f>IF(AG15="","",P15-K15)</f>
+        <v>46353</v>
       </c>
       <c r="J15" s="160"/>
       <c r="K15" s="158">
@@ -23002,6 +23027,7 @@
       <c r="O15" s="161"/>
       <c r="P15" s="161">
         <f>IF(AG15="","",AC15-R15-Q15)</f>
+        <v>46360</v>
       </c>
       <c r="Q15" s="162">
         <v>7</v>
@@ -23021,9 +23047,11 @@
       <c r="AB15" s="160"/>
       <c r="AC15" s="163">
         <f>IF(AG15="","",WORKDAY(AG15-AF15+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46381</v>
       </c>
       <c r="AD15" s="161">
         <f>IF(AG15="","",$AG15-$AF15)</f>
+        <v>46385</v>
       </c>
       <c r="AE15" s="160"/>
       <c r="AF15" s="196">
@@ -23071,6 +23099,7 @@
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16" s="155">
         <f>A15+1</f>
+        <v>5</v>
       </c>
       <c r="B16" s="167" t="inlineStr">
         <is>
@@ -23086,6 +23115,7 @@
       <c r="E16" s="164"/>
       <c r="F16" s="163">
         <f>IF(AG16="","",I16-H16)</f>
+        <v>46301</v>
       </c>
       <c r="G16" s="160"/>
       <c r="H16" s="158">
@@ -23093,6 +23123,7 @@
       </c>
       <c r="I16" s="161">
         <f>IF(AG16="","",P16-K16)</f>
+        <v>46308</v>
       </c>
       <c r="J16" s="160"/>
       <c r="K16" s="158">
@@ -23104,6 +23135,7 @@
       <c r="O16" s="161"/>
       <c r="P16" s="161">
         <f>IF(AG16="","",AC16-R16-Q16)</f>
+        <v>46315</v>
       </c>
       <c r="Q16" s="162">
         <v>7</v>
@@ -23123,9 +23155,11 @@
       <c r="AB16" s="160"/>
       <c r="AC16" s="163">
         <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46336</v>
       </c>
       <c r="AD16" s="161">
         <f>IF(AG16="","",$AG16-$AF16)</f>
+        <v>46336</v>
       </c>
       <c r="AE16" s="160"/>
       <c r="AF16" s="196">
@@ -23169,6 +23203,7 @@
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" s="155">
         <f>A16+1</f>
+        <v>6</v>
       </c>
       <c r="B17" s="167" t="inlineStr">
         <is>
@@ -23184,6 +23219,7 @@
       <c r="E17" s="164"/>
       <c r="F17" s="163">
         <f>IF(AG17="","",I17-H17)</f>
+        <v>46367</v>
       </c>
       <c r="G17" s="160"/>
       <c r="H17" s="158">
@@ -23191,6 +23227,7 @@
       </c>
       <c r="I17" s="161">
         <f>IF(AG17="","",P17-K17)</f>
+        <v>46374</v>
       </c>
       <c r="J17" s="160"/>
       <c r="K17" s="158">
@@ -23202,6 +23239,7 @@
       <c r="O17" s="161"/>
       <c r="P17" s="161">
         <f>IF(AG17="","",AC17-R17-Q17)</f>
+        <v>46381</v>
       </c>
       <c r="Q17" s="162">
         <v>7</v>
@@ -23221,9 +23259,11 @@
       <c r="AB17" s="160"/>
       <c r="AC17" s="163">
         <f>IF(AG17="","",WORKDAY(AG17-AF17+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46402</v>
       </c>
       <c r="AD17" s="161">
         <f>IF(AG17="","",$AG17-$AF17)</f>
+        <v>46402</v>
       </c>
       <c r="AE17" s="160"/>
       <c r="AF17" s="196">
@@ -23271,6 +23311,7 @@
     <row r="18" ht="25.5" customHeight="1">
       <c r="A18" s="155">
         <f>A17+1</f>
+        <v>7</v>
       </c>
       <c r="B18" s="167" t="inlineStr">
         <is>
@@ -23286,6 +23327,7 @@
       <c r="E18" s="164"/>
       <c r="F18" s="163">
         <f>IF(AG18="","",I18-H18)</f>
+        <v>46330</v>
       </c>
       <c r="G18" s="160"/>
       <c r="H18" s="158">
@@ -23293,6 +23335,7 @@
       </c>
       <c r="I18" s="161">
         <f>IF(AG18="","",P18-K18)</f>
+        <v>46337</v>
       </c>
       <c r="J18" s="160"/>
       <c r="K18" s="158">
@@ -23304,6 +23347,7 @@
       <c r="O18" s="161"/>
       <c r="P18" s="161">
         <f>IF(AG18="","",AC18-R18-Q18)</f>
+        <v>46344</v>
       </c>
       <c r="Q18" s="162">
         <v>7</v>
@@ -23323,9 +23367,11 @@
       <c r="AB18" s="160"/>
       <c r="AC18" s="163">
         <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46365</v>
       </c>
       <c r="AD18" s="161">
         <f>IF(AG18="","",$AG18-$AF18)</f>
+        <v>46365</v>
       </c>
       <c r="AE18" s="160"/>
       <c r="AF18" s="196">
@@ -23369,6 +23415,7 @@
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19" s="155">
         <f>A18+1</f>
+        <v>8</v>
       </c>
       <c r="B19" s="167" t="inlineStr">
         <is>
@@ -23384,6 +23431,7 @@
       <c r="E19" s="164"/>
       <c r="F19" s="163">
         <f>IF(AG19="","",I19-H19)</f>
+        <v>46335</v>
       </c>
       <c r="G19" s="160"/>
       <c r="H19" s="158">
@@ -23391,6 +23439,7 @@
       </c>
       <c r="I19" s="161">
         <f>IF(AG19="","",P19-K19)</f>
+        <v>46342</v>
       </c>
       <c r="J19" s="160"/>
       <c r="K19" s="158">
@@ -23402,6 +23451,7 @@
       <c r="O19" s="161"/>
       <c r="P19" s="161">
         <f>IF(AG19="","",AC19-R19-Q19)</f>
+        <v>46349</v>
       </c>
       <c r="Q19" s="162">
         <v>7</v>
@@ -23421,9 +23471,11 @@
       <c r="AB19" s="160"/>
       <c r="AC19" s="163">
         <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46370</v>
       </c>
       <c r="AD19" s="161">
         <f>IF(AG19="","",$AG19-$AF19)</f>
+        <v>46370</v>
       </c>
       <c r="AE19" s="160"/>
       <c r="AF19" s="196">
@@ -23467,6 +23519,7 @@
     <row r="20" ht="25.5" customHeight="1">
       <c r="A20" s="155">
         <f>A19+1</f>
+        <v>9</v>
       </c>
       <c r="B20" s="167" t="inlineStr">
         <is>
@@ -23482,6 +23535,7 @@
       <c r="E20" s="164"/>
       <c r="F20" s="163">
         <f>IF(AG20="","",I20-H20)</f>
+        <v>46346</v>
       </c>
       <c r="G20" s="160"/>
       <c r="H20" s="158">
@@ -23489,6 +23543,7 @@
       </c>
       <c r="I20" s="161">
         <f>IF(AG20="","",P20-K20)</f>
+        <v>46353</v>
       </c>
       <c r="J20" s="160"/>
       <c r="K20" s="158">
@@ -23500,6 +23555,7 @@
       <c r="O20" s="161"/>
       <c r="P20" s="161">
         <f>IF(AG20="","",AC20-R20-Q20)</f>
+        <v>46360</v>
       </c>
       <c r="Q20" s="162">
         <v>7</v>
@@ -23519,9 +23575,11 @@
       <c r="AB20" s="160"/>
       <c r="AC20" s="163">
         <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46381</v>
       </c>
       <c r="AD20" s="161">
         <f>IF(AG20="","",$AG20-$AF20)</f>
+        <v>46386</v>
       </c>
       <c r="AE20" s="160"/>
       <c r="AF20" s="196">
@@ -23565,6 +23623,7 @@
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="155">
         <f>A20+1</f>
+        <v>10</v>
       </c>
       <c r="B21" s="167" t="inlineStr">
         <is>
@@ -23580,6 +23639,7 @@
       <c r="E21" s="164"/>
       <c r="F21" s="163">
         <f>IF(AG21="","",I21-H21)</f>
+        <v>46282</v>
       </c>
       <c r="G21" s="160"/>
       <c r="H21" s="158">
@@ -23587,6 +23647,7 @@
       </c>
       <c r="I21" s="161">
         <f>IF(AG21="","",P21-K21)</f>
+        <v>46289</v>
       </c>
       <c r="J21" s="160"/>
       <c r="K21" s="158">
@@ -23600,6 +23661,7 @@
       <c r="O21" s="161"/>
       <c r="P21" s="161">
         <f>IF(AG21="","",AC21-R21-Q21)</f>
+        <v>46296</v>
       </c>
       <c r="Q21" s="162">
         <v>7</v>
@@ -23619,9 +23681,11 @@
       <c r="AB21" s="160"/>
       <c r="AC21" s="163">
         <f>IF(AG21="","",WORKDAY(AG21-AF21+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46317</v>
       </c>
       <c r="AD21" s="161">
         <f>IF(AG21="","",$AG21-$AF21)</f>
+        <v>46317</v>
       </c>
       <c r="AE21" s="160"/>
       <c r="AF21" s="196">
@@ -23669,6 +23733,7 @@
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="155">
         <f>A21+1</f>
+        <v>11</v>
       </c>
       <c r="B22" s="167" t="inlineStr">
         <is>
@@ -23684,6 +23749,7 @@
       <c r="E22" s="164"/>
       <c r="F22" s="163">
         <f>IF(AG22="","",I22-H22)</f>
+        <v>46330</v>
       </c>
       <c r="G22" s="160"/>
       <c r="H22" s="158">
@@ -23691,6 +23757,7 @@
       </c>
       <c r="I22" s="161">
         <f>IF(AG22="","",P22-K22)</f>
+        <v>46337</v>
       </c>
       <c r="J22" s="160"/>
       <c r="K22" s="158">
@@ -23702,6 +23769,7 @@
       <c r="O22" s="161"/>
       <c r="P22" s="161">
         <f>IF(AG22="","",AC22-R22-Q22)</f>
+        <v>46344</v>
       </c>
       <c r="Q22" s="162">
         <v>7</v>
@@ -23721,9 +23789,11 @@
       <c r="AB22" s="160"/>
       <c r="AC22" s="163">
         <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46365</v>
       </c>
       <c r="AD22" s="161">
         <f>IF(AG22="","",$AG22-$AF22)</f>
+        <v>46365</v>
       </c>
       <c r="AE22" s="160"/>
       <c r="AF22" s="196">
@@ -23767,6 +23837,7 @@
     <row r="23" ht="25.5" customHeight="1">
       <c r="A23" s="155">
         <f>A22+1</f>
+        <v>12</v>
       </c>
       <c r="B23" s="167" t="inlineStr">
         <is>
@@ -23782,6 +23853,7 @@
       <c r="E23" s="164"/>
       <c r="F23" s="163">
         <f>IF(AG23="","",I23-H23)</f>
+        <v>46337</v>
       </c>
       <c r="G23" s="160"/>
       <c r="H23" s="158">
@@ -23789,6 +23861,7 @@
       </c>
       <c r="I23" s="161">
         <f>IF(AG23="","",P23-K23)</f>
+        <v>46344</v>
       </c>
       <c r="J23" s="160"/>
       <c r="K23" s="158">
@@ -23800,6 +23873,7 @@
       <c r="O23" s="161"/>
       <c r="P23" s="161">
         <f>IF(AG23="","",AC23-R23-Q23)</f>
+        <v>46351</v>
       </c>
       <c r="Q23" s="162">
         <v>7</v>
@@ -23819,9 +23893,11 @@
       <c r="AB23" s="160"/>
       <c r="AC23" s="163">
         <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46372</v>
       </c>
       <c r="AD23" s="161">
         <f>IF(AG23="","",$AG23-$AF23)</f>
+        <v>46372</v>
       </c>
       <c r="AE23" s="160"/>
       <c r="AF23" s="196">
@@ -23865,6 +23941,7 @@
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" s="155">
         <f>A23+1</f>
+        <v>13</v>
       </c>
       <c r="B24" s="167" t="inlineStr">
         <is>
@@ -23880,6 +23957,7 @@
       <c r="E24" s="164"/>
       <c r="F24" s="163">
         <f>IF(AG24="","",I24-H24)</f>
+        <v>46344</v>
       </c>
       <c r="G24" s="160"/>
       <c r="H24" s="158">
@@ -23887,6 +23965,7 @@
       </c>
       <c r="I24" s="161">
         <f>IF(AG24="","",P24-K24)</f>
+        <v>46351</v>
       </c>
       <c r="J24" s="160"/>
       <c r="K24" s="158">
@@ -23898,6 +23977,7 @@
       <c r="O24" s="161"/>
       <c r="P24" s="161">
         <f>IF(AG24="","",AC24-R24-Q24)</f>
+        <v>46358</v>
       </c>
       <c r="Q24" s="162">
         <v>7</v>
@@ -23917,9 +23997,11 @@
       <c r="AB24" s="160"/>
       <c r="AC24" s="163">
         <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46379</v>
       </c>
       <c r="AD24" s="161">
         <f>IF(AG24="","",$AG24-$AF24)</f>
+        <v>46379</v>
       </c>
       <c r="AE24" s="160"/>
       <c r="AF24" s="196">
@@ -23963,6 +24045,7 @@
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" s="155">
         <f>A24+1</f>
+        <v>14</v>
       </c>
       <c r="B25" s="167" t="inlineStr">
         <is>
@@ -23978,6 +24061,7 @@
       <c r="E25" s="164"/>
       <c r="F25" s="163">
         <f>IF(AG25="","",I25-H25)</f>
+        <v>46344</v>
       </c>
       <c r="G25" s="160"/>
       <c r="H25" s="158">
@@ -23985,6 +24069,7 @@
       </c>
       <c r="I25" s="161">
         <f>IF(AG25="","",P25-K25)</f>
+        <v>46351</v>
       </c>
       <c r="J25" s="160"/>
       <c r="K25" s="158">
@@ -23996,6 +24081,7 @@
       <c r="O25" s="161"/>
       <c r="P25" s="161">
         <f>IF(AG25="","",AC25-R25-Q25)</f>
+        <v>46358</v>
       </c>
       <c r="Q25" s="162">
         <v>7</v>
@@ -24015,9 +24101,11 @@
       <c r="AB25" s="160"/>
       <c r="AC25" s="163">
         <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46379</v>
       </c>
       <c r="AD25" s="161">
         <f>IF(AG25="","",$AG25-$AF25)</f>
+        <v>46379</v>
       </c>
       <c r="AE25" s="160"/>
       <c r="AF25" s="196">
@@ -24061,6 +24149,7 @@
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26" s="155">
         <f>A25+1</f>
+        <v>15</v>
       </c>
       <c r="B26" s="167" t="inlineStr">
         <is>
@@ -24076,6 +24165,7 @@
       <c r="E26" s="164"/>
       <c r="F26" s="163">
         <f>IF(AG26="","",I26-H26)</f>
+        <v>46344</v>
       </c>
       <c r="G26" s="160"/>
       <c r="H26" s="158">
@@ -24083,6 +24173,7 @@
       </c>
       <c r="I26" s="161">
         <f>IF(AG26="","",P26-K26)</f>
+        <v>46351</v>
       </c>
       <c r="J26" s="160"/>
       <c r="K26" s="158">
@@ -24094,6 +24185,7 @@
       <c r="O26" s="161"/>
       <c r="P26" s="161">
         <f>IF(AG26="","",AC26-R26-Q26)</f>
+        <v>46358</v>
       </c>
       <c r="Q26" s="162">
         <v>7</v>
@@ -24113,9 +24205,11 @@
       <c r="AB26" s="160"/>
       <c r="AC26" s="163">
         <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46379</v>
       </c>
       <c r="AD26" s="161">
         <f>IF(AG26="","",$AG26-$AF26)</f>
+        <v>46379</v>
       </c>
       <c r="AE26" s="160"/>
       <c r="AF26" s="196">
@@ -24159,7 +24253,7 @@
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27" s="155" cm="1">
         <f t="array" ref="A27">A26+1</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B27" s="151"/>
       <c r="C27" t="s" s="156">
@@ -24167,13 +24261,15 @@
       </c>
       <c r="D27" s="165"/>
       <c r="E27" s="164"/>
-      <c r="F27" t="str" s="195" cm="1">
+      <c r="F27" s="195" cm="1" t="str">
         <f t="array" ref="F27">IF(AG27="","",I27-H27)</f>
+        <v/>
       </c>
       <c r="G27" s="160"/>
       <c r="H27" s="158"/>
-      <c r="I27" t="str" s="159" cm="1">
+      <c r="I27" s="159" cm="1" t="str">
         <f t="array" ref="I27">IF(AG27="","",P27-K27)</f>
+        <v/>
       </c>
       <c r="J27" s="160"/>
       <c r="K27" s="158"/>
@@ -24181,8 +24277,9 @@
       <c r="M27" s="161"/>
       <c r="N27" s="161"/>
       <c r="O27" s="161"/>
-      <c r="P27" t="str" s="159" cm="1">
+      <c r="P27" s="159" cm="1" t="str">
         <f t="array" ref="P27">IF(AG27="","",AC27-R27-Q27)</f>
+        <v/>
       </c>
       <c r="Q27" s="162"/>
       <c r="R27" s="162"/>
@@ -24197,8 +24294,9 @@
       <c r="AA27" s="161"/>
       <c r="AB27" s="160"/>
       <c r="AC27" s="163"/>
-      <c r="AD27" t="str" s="159" cm="1">
+      <c r="AD27" s="159" cm="1" t="str">
         <f t="array" ref="AD27">IF(AG27="","",$AG27-$AF27)</f>
+        <v/>
       </c>
       <c r="AE27" s="160"/>
       <c r="AF27" s="196"/>
@@ -24238,7 +24336,7 @@
     <row r="28" ht="25.5" customHeight="1">
       <c r="A28" s="155" cm="1">
         <f t="array" ref="A28">A27+1</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s" s="167">
         <v>116</v>
@@ -24345,7 +24443,7 @@
     <row r="29" ht="25.5" customHeight="1">
       <c r="A29" s="155" cm="1">
         <f t="array" ref="A29">A28+1</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s" s="167">
         <v>119</v>
@@ -24355,13 +24453,15 @@
       </c>
       <c r="D29" s="165"/>
       <c r="E29" s="164"/>
-      <c r="F29" t="str" s="195" cm="1">
+      <c r="F29" s="195" cm="1" t="str">
         <f t="array" ref="F29">IF(AG29="","",I29-H29)</f>
+        <v/>
       </c>
       <c r="G29" s="160"/>
       <c r="H29" s="158"/>
-      <c r="I29" t="str" s="159" cm="1">
+      <c r="I29" s="159" cm="1" t="str">
         <f t="array" ref="I29">IF(AG29="","",P29-K29)</f>
+        <v/>
       </c>
       <c r="J29" s="160"/>
       <c r="K29" s="158"/>
@@ -24369,8 +24469,9 @@
       <c r="M29" s="161"/>
       <c r="N29" s="161"/>
       <c r="O29" s="161"/>
-      <c r="P29" t="str" s="159" cm="1">
+      <c r="P29" s="159" cm="1" t="str">
         <f t="array" ref="P29">IF(AG29="","",AC29-R29-Q29)</f>
+        <v/>
       </c>
       <c r="Q29" s="162"/>
       <c r="R29" s="162"/>
@@ -24385,8 +24486,9 @@
       <c r="AA29" s="161"/>
       <c r="AB29" s="160"/>
       <c r="AC29" s="163"/>
-      <c r="AD29" t="str" s="159" cm="1">
+      <c r="AD29" s="159" cm="1" t="str">
         <f t="array" ref="AD29">IF(AG29="","",$AG29-$AF29)</f>
+        <v/>
       </c>
       <c r="AE29" s="160"/>
       <c r="AF29" s="196"/>
@@ -24428,7 +24530,7 @@
     <row r="30" ht="25.5" customHeight="1">
       <c r="A30" s="155" cm="1">
         <f t="array" ref="A30">A29+1</f>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s" s="167">
         <v>122</v>
@@ -24537,7 +24639,7 @@
     <row r="31" ht="25.5" customHeight="1">
       <c r="A31" s="155" cm="1">
         <f t="array" ref="A31">A30+1</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s" s="167">
         <v>125</v>
@@ -24547,13 +24649,15 @@
       </c>
       <c r="D31" s="165"/>
       <c r="E31" s="164"/>
-      <c r="F31" t="str" s="195" cm="1">
+      <c r="F31" s="195" cm="1" t="str">
         <f t="array" ref="F31">IF(AG31="","",I31-H31)</f>
+        <v/>
       </c>
       <c r="G31" s="160"/>
       <c r="H31" s="158"/>
-      <c r="I31" t="str" s="159" cm="1">
+      <c r="I31" s="159" cm="1" t="str">
         <f t="array" ref="I31">IF(AG31="","",P31-K31)</f>
+        <v/>
       </c>
       <c r="J31" s="160"/>
       <c r="K31" s="158"/>
@@ -24561,8 +24665,9 @@
       <c r="M31" s="161"/>
       <c r="N31" s="161"/>
       <c r="O31" s="161"/>
-      <c r="P31" t="str" s="159" cm="1">
+      <c r="P31" s="159" cm="1" t="str">
         <f t="array" ref="P31">IF(AG31="","",AC31-R31-Q31)</f>
+        <v/>
       </c>
       <c r="Q31" s="162"/>
       <c r="R31" s="162"/>
@@ -24577,8 +24682,9 @@
       <c r="AA31" s="161"/>
       <c r="AB31" s="160"/>
       <c r="AC31" s="163"/>
-      <c r="AD31" t="str" s="159" cm="1">
+      <c r="AD31" s="159" cm="1" t="str">
         <f t="array" ref="AD31">IF(AG31="","",$AG31-$AF31)</f>
+        <v/>
       </c>
       <c r="AE31" s="160"/>
       <c r="AF31" s="196"/>
@@ -24620,7 +24726,7 @@
     <row r="32" ht="25.5" customHeight="1">
       <c r="A32" s="155" cm="1">
         <f t="array" ref="A32">A31+1</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B32" s="151"/>
       <c r="C32" t="s" s="156">
@@ -24628,13 +24734,15 @@
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="164"/>
-      <c r="F32" t="str" s="195" cm="1">
+      <c r="F32" s="195" cm="1" t="str">
         <f t="array" ref="F32">IF(AG32="","",I32-H32)</f>
+        <v/>
       </c>
       <c r="G32" s="160"/>
       <c r="H32" s="158"/>
-      <c r="I32" t="str" s="159" cm="1">
+      <c r="I32" s="159" cm="1" t="str">
         <f t="array" ref="I32">IF(AG32="","",P32-K32)</f>
+        <v/>
       </c>
       <c r="J32" s="160"/>
       <c r="K32" s="158"/>
@@ -24642,8 +24750,9 @@
       <c r="M32" s="161"/>
       <c r="N32" s="161"/>
       <c r="O32" s="161"/>
-      <c r="P32" t="str" s="159" cm="1">
+      <c r="P32" s="159" cm="1" t="str">
         <f t="array" ref="P32">IF(AG32="","",AC32-R32-Q32)</f>
+        <v/>
       </c>
       <c r="Q32" s="162"/>
       <c r="R32" s="162"/>
@@ -24658,8 +24767,9 @@
       <c r="AA32" s="161"/>
       <c r="AB32" s="160"/>
       <c r="AC32" s="163"/>
-      <c r="AD32" t="str" s="159" cm="1">
+      <c r="AD32" s="159" cm="1" t="str">
         <f t="array" ref="AD32">IF(AG32="","",$AG32-$AF32)</f>
+        <v/>
       </c>
       <c r="AE32" s="160"/>
       <c r="AF32" s="196"/>
@@ -24699,7 +24809,7 @@
     <row r="33" ht="25.5" customHeight="1">
       <c r="A33" s="155" cm="1">
         <f t="array" ref="A33">A32+1</f>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s" s="167">
         <v>129</v>
@@ -24808,7 +24918,7 @@
     <row r="34" ht="25.5" customHeight="1">
       <c r="A34" s="155" cm="1">
         <f t="array" ref="A34">A33+1</f>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B34" s="151"/>
       <c r="C34" t="s" s="156">
@@ -24816,13 +24926,15 @@
       </c>
       <c r="D34" s="165"/>
       <c r="E34" s="164"/>
-      <c r="F34" t="str" s="195" cm="1">
+      <c r="F34" s="195" cm="1" t="str">
         <f t="array" ref="F34">IF(AG34="","",I34-H34)</f>
+        <v/>
       </c>
       <c r="G34" s="160"/>
       <c r="H34" s="158"/>
-      <c r="I34" t="str" s="159" cm="1">
+      <c r="I34" s="159" cm="1" t="str">
         <f t="array" ref="I34">IF(AG34="","",P34-K34)</f>
+        <v/>
       </c>
       <c r="J34" s="160"/>
       <c r="K34" s="158"/>
@@ -24830,8 +24942,9 @@
       <c r="M34" s="161"/>
       <c r="N34" s="161"/>
       <c r="O34" s="161"/>
-      <c r="P34" t="str" s="159" cm="1">
+      <c r="P34" s="159" cm="1" t="str">
         <f t="array" ref="P34">IF(AG34="","",AC34-R34-Q34)</f>
+        <v/>
       </c>
       <c r="Q34" s="162"/>
       <c r="R34" s="162"/>
@@ -24846,8 +24959,9 @@
       <c r="AA34" s="161"/>
       <c r="AB34" s="160"/>
       <c r="AC34" s="163"/>
-      <c r="AD34" t="str" s="159" cm="1">
+      <c r="AD34" s="159" cm="1" t="str">
         <f t="array" ref="AD34">IF(AG34="","",$AG34-$AF34)</f>
+        <v/>
       </c>
       <c r="AE34" s="160"/>
       <c r="AF34" s="196"/>
@@ -24887,7 +25001,7 @@
     <row r="35" ht="25.5" customHeight="1">
       <c r="A35" s="155" cm="1">
         <f t="array" ref="A35">A34+1</f>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s" s="167">
         <v>133</v>
@@ -24994,7 +25108,7 @@
     <row r="36" ht="25.5" customHeight="1">
       <c r="A36" s="155" cm="1">
         <f t="array" ref="A36">A35+1</f>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s" s="167">
         <v>136</v>
@@ -25095,7 +25209,7 @@
     <row r="37" ht="25.5" customHeight="1">
       <c r="A37" s="155" cm="1">
         <f t="array" ref="A37">A36+1</f>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s" s="167">
         <v>139</v>
@@ -25196,7 +25310,7 @@
     <row r="38" ht="25.5" customHeight="1">
       <c r="A38" s="155" cm="1">
         <f t="array" ref="A38">A37+1</f>
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s" s="167">
         <v>141</v>
@@ -25297,7 +25411,7 @@
     <row r="39" ht="25.5" customHeight="1">
       <c r="A39" s="155" cm="1">
         <f t="array" ref="A39">A38+1</f>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" t="s" s="156">
@@ -25305,13 +25419,15 @@
       </c>
       <c r="D39" s="165"/>
       <c r="E39" s="164"/>
-      <c r="F39" t="str" s="195" cm="1">
+      <c r="F39" s="195" cm="1" t="str">
         <f t="array" ref="F39">IF(AG39="","",I39-H39)</f>
+        <v/>
       </c>
       <c r="G39" s="160"/>
       <c r="H39" s="158"/>
-      <c r="I39" t="str" s="159" cm="1">
+      <c r="I39" s="159" cm="1" t="str">
         <f t="array" ref="I39">IF(AG39="","",P39-K39)</f>
+        <v/>
       </c>
       <c r="J39" s="160"/>
       <c r="K39" s="158"/>
@@ -25319,8 +25435,9 @@
       <c r="M39" s="161"/>
       <c r="N39" s="161"/>
       <c r="O39" s="161"/>
-      <c r="P39" t="str" s="159" cm="1">
+      <c r="P39" s="159" cm="1" t="str">
         <f t="array" ref="P39">IF(AG39="","",AC39-R39-Q39)</f>
+        <v/>
       </c>
       <c r="Q39" s="162"/>
       <c r="R39" s="162"/>
@@ -25335,8 +25452,9 @@
       <c r="AA39" s="161"/>
       <c r="AB39" s="160"/>
       <c r="AC39" s="163"/>
-      <c r="AD39" t="str" s="159" cm="1">
+      <c r="AD39" s="159" cm="1" t="str">
         <f t="array" ref="AD39">IF(AG39="","",$AG39-$AF39)</f>
+        <v/>
       </c>
       <c r="AE39" s="160"/>
       <c r="AF39" s="196"/>
@@ -25376,7 +25494,7 @@
     <row r="40" ht="25.5" customHeight="1">
       <c r="A40" s="155" cm="1">
         <f t="array" ref="A40">A39+1</f>
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s" s="167">
         <v>144</v>
@@ -25481,7 +25599,7 @@
     <row r="41" ht="25.5" customHeight="1">
       <c r="A41" s="155" cm="1">
         <f t="array" ref="A41">A40+1</f>
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B41" s="151"/>
       <c r="C41" t="s" s="156">
@@ -25489,13 +25607,15 @@
       </c>
       <c r="D41" s="165"/>
       <c r="E41" s="164"/>
-      <c r="F41" t="str" s="195" cm="1">
+      <c r="F41" s="195" cm="1" t="str">
         <f t="array" ref="F41">IF(AG41="","",I41-H41)</f>
+        <v/>
       </c>
       <c r="G41" s="160"/>
       <c r="H41" s="158"/>
-      <c r="I41" t="str" s="159" cm="1">
+      <c r="I41" s="159" cm="1" t="str">
         <f t="array" ref="I41">IF(AG41="","",P41-K41)</f>
+        <v/>
       </c>
       <c r="J41" s="160"/>
       <c r="K41" s="158"/>
@@ -25503,8 +25623,9 @@
       <c r="M41" s="161"/>
       <c r="N41" s="161"/>
       <c r="O41" s="161"/>
-      <c r="P41" t="str" s="159" cm="1">
+      <c r="P41" s="159" cm="1" t="str">
         <f t="array" ref="P41">IF(AG41="","",AC41-R41-Q41)</f>
+        <v/>
       </c>
       <c r="Q41" s="162"/>
       <c r="R41" s="162"/>
@@ -25519,8 +25640,9 @@
       <c r="AA41" s="161"/>
       <c r="AB41" s="160"/>
       <c r="AC41" s="163"/>
-      <c r="AD41" t="str" s="159" cm="1">
+      <c r="AD41" s="159" cm="1" t="str">
         <f t="array" ref="AD41">IF(AG41="","",$AG41-$AF41)</f>
+        <v/>
       </c>
       <c r="AE41" s="160"/>
       <c r="AF41" s="196"/>
@@ -25560,7 +25682,7 @@
     <row r="42" ht="25.5" customHeight="1">
       <c r="A42" s="155" cm="1">
         <f t="array" ref="A42">A41+1</f>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s" s="167">
         <v>148</v>
@@ -25667,7 +25789,7 @@
     <row r="43" ht="25.5" customHeight="1">
       <c r="A43" s="155" cm="1">
         <f t="array" ref="A43">A42+1</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B43" s="151"/>
       <c r="C43" t="s" s="156">
@@ -25675,13 +25797,15 @@
       </c>
       <c r="D43" s="165"/>
       <c r="E43" s="164"/>
-      <c r="F43" t="str" s="195" cm="1">
+      <c r="F43" s="195" cm="1" t="str">
         <f t="array" ref="F43">IF(AG43="","",I43-H43)</f>
+        <v/>
       </c>
       <c r="G43" s="160"/>
       <c r="H43" s="158"/>
-      <c r="I43" t="str" s="159" cm="1">
+      <c r="I43" s="159" cm="1" t="str">
         <f t="array" ref="I43">IF(AG43="","",P43-K43)</f>
+        <v/>
       </c>
       <c r="J43" s="160"/>
       <c r="K43" s="158"/>
@@ -25689,8 +25813,9 @@
       <c r="M43" s="161"/>
       <c r="N43" s="161"/>
       <c r="O43" s="161"/>
-      <c r="P43" t="str" s="159" cm="1">
+      <c r="P43" s="159" cm="1" t="str">
         <f t="array" ref="P43">IF(AG43="","",AC43-R43-Q43)</f>
+        <v/>
       </c>
       <c r="Q43" s="162"/>
       <c r="R43" s="162"/>
@@ -25705,8 +25830,9 @@
       <c r="AA43" s="161"/>
       <c r="AB43" s="160"/>
       <c r="AC43" s="163"/>
-      <c r="AD43" t="str" s="159" cm="1">
+      <c r="AD43" s="159" cm="1" t="str">
         <f t="array" ref="AD43">IF(AG43="","",$AG43-$AF43)</f>
+        <v/>
       </c>
       <c r="AE43" s="160"/>
       <c r="AF43" s="196"/>
@@ -25746,7 +25872,7 @@
     <row r="44" ht="25.5" customHeight="1">
       <c r="A44" s="155" cm="1">
         <f t="array" ref="A44">A43+1</f>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s" s="167">
         <v>151</v>
@@ -25847,19 +25973,21 @@
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" s="155" cm="1">
         <f t="array" ref="A45">A44+1</f>
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B45" s="151"/>
       <c r="C45" s="170"/>
       <c r="D45" s="165"/>
       <c r="E45" s="164"/>
-      <c r="F45" t="str" s="195" cm="1">
+      <c r="F45" s="195" cm="1" t="str">
         <f t="array" ref="F45">IF(AG45="","",I45-H45)</f>
+        <v/>
       </c>
       <c r="G45" s="160"/>
       <c r="H45" s="158"/>
-      <c r="I45" t="str" s="159" cm="1">
+      <c r="I45" s="159" cm="1" t="str">
         <f t="array" ref="I45">IF(AG45="","",P45-K45)</f>
+        <v/>
       </c>
       <c r="J45" s="160"/>
       <c r="K45" s="158"/>
@@ -25867,8 +25995,9 @@
       <c r="M45" s="161"/>
       <c r="N45" s="161"/>
       <c r="O45" s="161"/>
-      <c r="P45" t="str" s="159" cm="1">
+      <c r="P45" s="159" cm="1" t="str">
         <f t="array" ref="P45">IF(AG45="","",AC45-R45-Q45)</f>
+        <v/>
       </c>
       <c r="Q45" s="162"/>
       <c r="R45" s="162"/>
@@ -25883,8 +26012,9 @@
       <c r="AA45" s="161"/>
       <c r="AB45" s="160"/>
       <c r="AC45" s="163"/>
-      <c r="AD45" t="str" s="159" cm="1">
+      <c r="AD45" s="159" cm="1" t="str">
         <f t="array" ref="AD45">IF(AG45="","",$AG45-$AF45)</f>
+        <v/>
       </c>
       <c r="AE45" s="160"/>
       <c r="AF45" s="196"/>
@@ -25924,7 +26054,7 @@
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" s="155" cm="1">
         <f t="array" ref="A46">A45+1</f>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B46" s="151"/>
       <c r="C46" t="s" s="156">
@@ -25932,13 +26062,15 @@
       </c>
       <c r="D46" s="165"/>
       <c r="E46" s="164"/>
-      <c r="F46" t="str" s="195" cm="1">
+      <c r="F46" s="195" cm="1" t="str">
         <f t="array" ref="F46">IF(AG46="","",I46-H46)</f>
+        <v/>
       </c>
       <c r="G46" s="160"/>
       <c r="H46" s="158"/>
-      <c r="I46" t="str" s="159" cm="1">
+      <c r="I46" s="159" cm="1" t="str">
         <f t="array" ref="I46">IF(AG46="","",P46-K46)</f>
+        <v/>
       </c>
       <c r="J46" s="160"/>
       <c r="K46" s="158"/>
@@ -25946,8 +26078,9 @@
       <c r="M46" s="161"/>
       <c r="N46" s="161"/>
       <c r="O46" s="161"/>
-      <c r="P46" t="str" s="159" cm="1">
+      <c r="P46" s="159" cm="1" t="str">
         <f t="array" ref="P46">IF(AG46="","",AC46-R46-Q46)</f>
+        <v/>
       </c>
       <c r="Q46" s="162"/>
       <c r="R46" s="162"/>
@@ -25962,8 +26095,9 @@
       <c r="AA46" s="161"/>
       <c r="AB46" s="160"/>
       <c r="AC46" s="163"/>
-      <c r="AD46" t="str" s="159" cm="1">
+      <c r="AD46" s="159" cm="1" t="str">
         <f t="array" ref="AD46">IF(AG46="","",$AG46-$AF46)</f>
+        <v/>
       </c>
       <c r="AE46" s="160"/>
       <c r="AF46" s="196"/>
@@ -26003,19 +26137,21 @@
     <row r="47" ht="25.5" customHeight="1">
       <c r="A47" s="155" cm="1">
         <f t="array" ref="A47">A46+1</f>
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B47" s="151"/>
       <c r="C47" s="170"/>
       <c r="D47" s="165"/>
       <c r="E47" s="164"/>
-      <c r="F47" t="str" s="195" cm="1">
+      <c r="F47" s="195" cm="1" t="str">
         <f t="array" ref="F47">IF(AG47="","",I47-H47)</f>
+        <v/>
       </c>
       <c r="G47" s="160"/>
       <c r="H47" s="158"/>
-      <c r="I47" t="str" s="159" cm="1">
+      <c r="I47" s="159" cm="1" t="str">
         <f t="array" ref="I47">IF(AG47="","",P47-K47)</f>
+        <v/>
       </c>
       <c r="J47" s="160"/>
       <c r="K47" s="158"/>
@@ -26023,8 +26159,9 @@
       <c r="M47" s="161"/>
       <c r="N47" s="161"/>
       <c r="O47" s="161"/>
-      <c r="P47" t="str" s="159" cm="1">
+      <c r="P47" s="159" cm="1" t="str">
         <f t="array" ref="P47">IF(AG47="","",AC47-R47-Q47)</f>
+        <v/>
       </c>
       <c r="Q47" s="162"/>
       <c r="R47" s="162"/>
@@ -26039,8 +26176,9 @@
       <c r="AA47" s="161"/>
       <c r="AB47" s="160"/>
       <c r="AC47" s="163"/>
-      <c r="AD47" t="str" s="159" cm="1">
+      <c r="AD47" s="159" cm="1" t="str">
         <f t="array" ref="AD47">IF(AG47="","",$AG47-$AF47)</f>
+        <v/>
       </c>
       <c r="AE47" s="160"/>
       <c r="AF47" s="196"/>
@@ -26080,19 +26218,21 @@
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" s="155" cm="1">
         <f t="array" ref="A48">A47+1</f>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B48" s="151"/>
       <c r="C48" s="170"/>
       <c r="D48" s="165"/>
       <c r="E48" s="164"/>
-      <c r="F48" t="str" s="195" cm="1">
+      <c r="F48" s="195" cm="1" t="str">
         <f t="array" ref="F48">IF(AG48="","",I48-H48)</f>
+        <v/>
       </c>
       <c r="G48" s="160"/>
       <c r="H48" s="158"/>
-      <c r="I48" t="str" s="159" cm="1">
+      <c r="I48" s="159" cm="1" t="str">
         <f t="array" ref="I48">IF(AG48="","",P48-K48)</f>
+        <v/>
       </c>
       <c r="J48" s="160"/>
       <c r="K48" s="158"/>
@@ -26100,8 +26240,9 @@
       <c r="M48" s="161"/>
       <c r="N48" s="161"/>
       <c r="O48" s="161"/>
-      <c r="P48" t="str" s="159" cm="1">
+      <c r="P48" s="159" cm="1" t="str">
         <f t="array" ref="P48">IF(AG48="","",AC48-R48-Q48)</f>
+        <v/>
       </c>
       <c r="Q48" s="162"/>
       <c r="R48" s="162"/>
@@ -26116,8 +26257,9 @@
       <c r="AA48" s="161"/>
       <c r="AB48" s="160"/>
       <c r="AC48" s="163"/>
-      <c r="AD48" t="str" s="159" cm="1">
+      <c r="AD48" s="159" cm="1" t="str">
         <f t="array" ref="AD48">IF(AG48="","",$AG48-$AF48)</f>
+        <v/>
       </c>
       <c r="AE48" s="160"/>
       <c r="AF48" s="196"/>
@@ -26157,19 +26299,21 @@
     <row r="49" ht="25.5" customHeight="1">
       <c r="A49" s="155" cm="1">
         <f t="array" ref="A49">A48+1</f>
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B49" s="151"/>
       <c r="C49" s="170"/>
       <c r="D49" s="165"/>
       <c r="E49" s="164"/>
-      <c r="F49" t="str" s="195" cm="1">
+      <c r="F49" s="195" cm="1" t="str">
         <f t="array" ref="F49">IF(AG49="","",I49-H49)</f>
+        <v/>
       </c>
       <c r="G49" s="160"/>
       <c r="H49" s="158"/>
-      <c r="I49" t="str" s="159" cm="1">
+      <c r="I49" s="159" cm="1" t="str">
         <f t="array" ref="I49">IF(AG49="","",P49-K49)</f>
+        <v/>
       </c>
       <c r="J49" s="160"/>
       <c r="K49" s="158"/>
@@ -26177,8 +26321,9 @@
       <c r="M49" s="161"/>
       <c r="N49" s="161"/>
       <c r="O49" s="161"/>
-      <c r="P49" t="str" s="159" cm="1">
+      <c r="P49" s="159" cm="1" t="str">
         <f t="array" ref="P49">IF(AG49="","",AC49-R49-Q49)</f>
+        <v/>
       </c>
       <c r="Q49" s="162"/>
       <c r="R49" s="162"/>
@@ -26193,8 +26338,9 @@
       <c r="AA49" s="161"/>
       <c r="AB49" s="160"/>
       <c r="AC49" s="163"/>
-      <c r="AD49" t="str" s="159" cm="1">
+      <c r="AD49" s="159" cm="1" t="str">
         <f t="array" ref="AD49">IF(AG49="","",$AG49-$AF49)</f>
+        <v/>
       </c>
       <c r="AE49" s="160"/>
       <c r="AF49" s="196"/>
@@ -26234,19 +26380,21 @@
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" s="155" cm="1">
         <f t="array" ref="A50">A49+1</f>
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B50" s="151"/>
       <c r="C50" s="170"/>
       <c r="D50" s="165"/>
       <c r="E50" s="164"/>
-      <c r="F50" t="str" s="195" cm="1">
+      <c r="F50" s="195" cm="1" t="str">
         <f t="array" ref="F50">IF(AG50="","",I50-H50)</f>
+        <v/>
       </c>
       <c r="G50" s="160"/>
       <c r="H50" s="158"/>
-      <c r="I50" t="str" s="159" cm="1">
+      <c r="I50" s="159" cm="1" t="str">
         <f t="array" ref="I50">IF(AG50="","",P50-K50)</f>
+        <v/>
       </c>
       <c r="J50" s="160"/>
       <c r="K50" s="158"/>
@@ -26254,8 +26402,9 @@
       <c r="M50" s="161"/>
       <c r="N50" s="161"/>
       <c r="O50" s="161"/>
-      <c r="P50" t="str" s="159" cm="1">
+      <c r="P50" s="159" cm="1" t="str">
         <f t="array" ref="P50">IF(AG50="","",AC50-R50-Q50)</f>
+        <v/>
       </c>
       <c r="Q50" s="162"/>
       <c r="R50" s="162"/>
@@ -26270,8 +26419,9 @@
       <c r="AA50" s="161"/>
       <c r="AB50" s="160"/>
       <c r="AC50" s="163"/>
-      <c r="AD50" t="str" s="159" cm="1">
+      <c r="AD50" s="159" cm="1" t="str">
         <f t="array" ref="AD50">IF(AG50="","",$AG50-$AF50)</f>
+        <v/>
       </c>
       <c r="AE50" s="160"/>
       <c r="AF50" s="196"/>
@@ -26311,19 +26461,21 @@
     <row r="51" ht="25.5" customHeight="1">
       <c r="A51" s="155" cm="1">
         <f t="array" ref="A51">A50+1</f>
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B51" s="151"/>
       <c r="C51" s="170"/>
       <c r="D51" s="165"/>
       <c r="E51" s="164"/>
-      <c r="F51" t="str" s="195" cm="1">
+      <c r="F51" s="195" cm="1" t="str">
         <f t="array" ref="F51">IF(AG51="","",I51-H51)</f>
+        <v/>
       </c>
       <c r="G51" s="160"/>
       <c r="H51" s="158"/>
-      <c r="I51" t="str" s="159" cm="1">
+      <c r="I51" s="159" cm="1" t="str">
         <f t="array" ref="I51">IF(AG51="","",P51-K51)</f>
+        <v/>
       </c>
       <c r="J51" s="160"/>
       <c r="K51" s="158"/>
@@ -26331,8 +26483,9 @@
       <c r="M51" s="161"/>
       <c r="N51" s="161"/>
       <c r="O51" s="161"/>
-      <c r="P51" t="str" s="159" cm="1">
+      <c r="P51" s="159" cm="1" t="str">
         <f t="array" ref="P51">IF(AG51="","",AC51-R51-Q51)</f>
+        <v/>
       </c>
       <c r="Q51" s="162"/>
       <c r="R51" s="162"/>
@@ -26347,8 +26500,9 @@
       <c r="AA51" s="161"/>
       <c r="AB51" s="160"/>
       <c r="AC51" s="163"/>
-      <c r="AD51" t="str" s="159" cm="1">
+      <c r="AD51" s="159" cm="1" t="str">
         <f t="array" ref="AD51">IF(AG51="","",$AG51-$AF51)</f>
+        <v/>
       </c>
       <c r="AE51" s="160"/>
       <c r="AF51" s="196"/>
@@ -26388,19 +26542,21 @@
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" s="155" cm="1">
         <f t="array" ref="A52">A51+1</f>
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B52" s="151"/>
       <c r="C52" s="170"/>
       <c r="D52" s="165"/>
       <c r="E52" s="164"/>
-      <c r="F52" t="str" s="195" cm="1">
+      <c r="F52" s="195" cm="1" t="str">
         <f t="array" ref="F52">IF(AG52="","",I52-H52)</f>
+        <v/>
       </c>
       <c r="G52" s="160"/>
       <c r="H52" s="158"/>
-      <c r="I52" t="str" s="159" cm="1">
+      <c r="I52" s="159" cm="1" t="str">
         <f t="array" ref="I52">IF(AG52="","",P52-K52)</f>
+        <v/>
       </c>
       <c r="J52" s="160"/>
       <c r="K52" s="158"/>
@@ -26408,8 +26564,9 @@
       <c r="M52" s="161"/>
       <c r="N52" s="161"/>
       <c r="O52" s="161"/>
-      <c r="P52" t="str" s="159" cm="1">
+      <c r="P52" s="159" cm="1" t="str">
         <f t="array" ref="P52">IF(AG52="","",AC52-R52-Q52)</f>
+        <v/>
       </c>
       <c r="Q52" s="162"/>
       <c r="R52" s="162"/>
@@ -26424,8 +26581,9 @@
       <c r="AA52" s="161"/>
       <c r="AB52" s="160"/>
       <c r="AC52" s="163"/>
-      <c r="AD52" t="str" s="159" cm="1">
+      <c r="AD52" s="159" cm="1" t="str">
         <f t="array" ref="AD52">IF(AG52="","",$AG52-$AF52)</f>
+        <v/>
       </c>
       <c r="AE52" s="160"/>
       <c r="AF52" s="196"/>
@@ -26465,19 +26623,21 @@
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" s="155" cm="1">
         <f t="array" ref="A53">A52+1</f>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B53" s="151"/>
       <c r="C53" s="170"/>
       <c r="D53" s="165"/>
       <c r="E53" s="164"/>
-      <c r="F53" t="str" s="195" cm="1">
+      <c r="F53" s="195" cm="1" t="str">
         <f t="array" ref="F53">IF(AG53="","",I53-H53)</f>
+        <v/>
       </c>
       <c r="G53" s="160"/>
       <c r="H53" s="158"/>
-      <c r="I53" t="str" s="159" cm="1">
+      <c r="I53" s="159" cm="1" t="str">
         <f t="array" ref="I53">IF(AG53="","",P53-K53)</f>
+        <v/>
       </c>
       <c r="J53" s="160"/>
       <c r="K53" s="158"/>
@@ -26485,8 +26645,9 @@
       <c r="M53" s="161"/>
       <c r="N53" s="161"/>
       <c r="O53" s="161"/>
-      <c r="P53" t="str" s="159" cm="1">
+      <c r="P53" s="159" cm="1" t="str">
         <f t="array" ref="P53">IF(AG53="","",AC53-R53-Q53)</f>
+        <v/>
       </c>
       <c r="Q53" s="162"/>
       <c r="R53" s="162"/>
@@ -26501,8 +26662,9 @@
       <c r="AA53" s="161"/>
       <c r="AB53" s="160"/>
       <c r="AC53" s="163"/>
-      <c r="AD53" t="str" s="159" cm="1">
+      <c r="AD53" s="159" cm="1" t="str">
         <f t="array" ref="AD53">IF(AG53="","",$AG53-$AF53)</f>
+        <v/>
       </c>
       <c r="AE53" s="160"/>
       <c r="AF53" s="196"/>
@@ -26542,19 +26704,21 @@
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" s="155" cm="1">
         <f t="array" ref="A54">A53+1</f>
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B54" s="151"/>
       <c r="C54" s="170"/>
       <c r="D54" s="165"/>
       <c r="E54" s="164"/>
-      <c r="F54" t="str" s="195" cm="1">
+      <c r="F54" s="195" cm="1" t="str">
         <f t="array" ref="F54">IF(AG54="","",I54-H54)</f>
+        <v/>
       </c>
       <c r="G54" s="160"/>
       <c r="H54" s="158"/>
-      <c r="I54" t="str" s="159" cm="1">
+      <c r="I54" s="159" cm="1" t="str">
         <f t="array" ref="I54">IF(AG54="","",P54-K54)</f>
+        <v/>
       </c>
       <c r="J54" s="160"/>
       <c r="K54" s="158"/>
@@ -26562,8 +26726,9 @@
       <c r="M54" s="161"/>
       <c r="N54" s="161"/>
       <c r="O54" s="161"/>
-      <c r="P54" t="str" s="159" cm="1">
+      <c r="P54" s="159" cm="1" t="str">
         <f t="array" ref="P54">IF(AG54="","",AC54-R54-Q54)</f>
+        <v/>
       </c>
       <c r="Q54" s="162"/>
       <c r="R54" s="162"/>
@@ -26578,8 +26743,9 @@
       <c r="AA54" s="161"/>
       <c r="AB54" s="160"/>
       <c r="AC54" s="163"/>
-      <c r="AD54" t="str" s="159" cm="1">
+      <c r="AD54" s="159" cm="1" t="str">
         <f t="array" ref="AD54">IF(AG54="","",$AG54-$AF54)</f>
+        <v/>
       </c>
       <c r="AE54" s="160"/>
       <c r="AF54" s="196"/>
@@ -26619,7 +26785,7 @@
     <row r="55" ht="25.5" customHeight="1">
       <c r="A55" s="155" cm="1">
         <f t="array" ref="A55">A54+1</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B55" s="151"/>
       <c r="C55" t="s" s="156">
@@ -26627,13 +26793,15 @@
       </c>
       <c r="D55" s="165"/>
       <c r="E55" s="164"/>
-      <c r="F55" t="str" s="195" cm="1">
+      <c r="F55" s="195" cm="1" t="str">
         <f t="array" ref="F55">IF(AG55="","",I55-H55)</f>
+        <v/>
       </c>
       <c r="G55" s="160"/>
       <c r="H55" s="158"/>
-      <c r="I55" t="str" s="159" cm="1">
+      <c r="I55" s="159" cm="1" t="str">
         <f t="array" ref="I55">IF(AG55="","",P55-K55)</f>
+        <v/>
       </c>
       <c r="J55" s="160"/>
       <c r="K55" s="158"/>
@@ -26641,8 +26809,9 @@
       <c r="M55" s="161"/>
       <c r="N55" s="161"/>
       <c r="O55" s="161"/>
-      <c r="P55" t="str" s="159" cm="1">
+      <c r="P55" s="159" cm="1" t="str">
         <f t="array" ref="P55">IF(AG55="","",AC55-R55-Q55)</f>
+        <v/>
       </c>
       <c r="Q55" s="162"/>
       <c r="R55" s="162"/>
@@ -26657,8 +26826,9 @@
       <c r="AA55" s="161"/>
       <c r="AB55" s="160"/>
       <c r="AC55" s="163"/>
-      <c r="AD55" t="str" s="159" cm="1">
+      <c r="AD55" s="159" cm="1" t="str">
         <f t="array" ref="AD55">IF(AG55="","",$AG55-$AF55)</f>
+        <v/>
       </c>
       <c r="AE55" s="160"/>
       <c r="AF55" s="196"/>
@@ -26698,19 +26868,21 @@
     <row r="56" ht="25.5" customHeight="1">
       <c r="A56" s="155" cm="1">
         <f t="array" ref="A56">A55+1</f>
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B56" s="151"/>
       <c r="C56" s="170"/>
       <c r="D56" s="165"/>
       <c r="E56" s="164"/>
-      <c r="F56" t="str" s="195" cm="1">
+      <c r="F56" s="195" cm="1" t="str">
         <f t="array" ref="F56">IF(AG56="","",I56-H56)</f>
+        <v/>
       </c>
       <c r="G56" s="160"/>
       <c r="H56" s="158"/>
-      <c r="I56" t="str" s="159" cm="1">
+      <c r="I56" s="159" cm="1" t="str">
         <f t="array" ref="I56">IF(AG56="","",P56-K56)</f>
+        <v/>
       </c>
       <c r="J56" s="160"/>
       <c r="K56" s="158"/>
@@ -26718,8 +26890,9 @@
       <c r="M56" s="161"/>
       <c r="N56" s="161"/>
       <c r="O56" s="161"/>
-      <c r="P56" t="str" s="159" cm="1">
+      <c r="P56" s="159" cm="1" t="str">
         <f t="array" ref="P56">IF(AG56="","",AC56-R56-Q56)</f>
+        <v/>
       </c>
       <c r="Q56" s="162"/>
       <c r="R56" s="162"/>
@@ -26734,8 +26907,9 @@
       <c r="AA56" s="161"/>
       <c r="AB56" s="160"/>
       <c r="AC56" s="163"/>
-      <c r="AD56" t="str" s="159" cm="1">
+      <c r="AD56" s="159" cm="1" t="str">
         <f t="array" ref="AD56">IF(AG56="","",$AG56-$AF56)</f>
+        <v/>
       </c>
       <c r="AE56" s="160"/>
       <c r="AF56" s="196"/>
@@ -26775,19 +26949,21 @@
     <row r="57" ht="25.5" customHeight="1">
       <c r="A57" s="155" cm="1">
         <f t="array" ref="A57">A56+1</f>
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B57" s="151"/>
       <c r="C57" s="170"/>
       <c r="D57" s="165"/>
       <c r="E57" s="164"/>
-      <c r="F57" t="str" s="195" cm="1">
+      <c r="F57" s="195" cm="1" t="str">
         <f t="array" ref="F57">IF(AG57="","",I57-H57)</f>
+        <v/>
       </c>
       <c r="G57" s="160"/>
       <c r="H57" s="158"/>
-      <c r="I57" t="str" s="159" cm="1">
+      <c r="I57" s="159" cm="1" t="str">
         <f t="array" ref="I57">IF(AG57="","",P57-K57)</f>
+        <v/>
       </c>
       <c r="J57" s="160"/>
       <c r="K57" s="158"/>
@@ -26795,8 +26971,9 @@
       <c r="M57" s="161"/>
       <c r="N57" s="161"/>
       <c r="O57" s="161"/>
-      <c r="P57" t="str" s="159" cm="1">
+      <c r="P57" s="159" cm="1" t="str">
         <f t="array" ref="P57">IF(AG57="","",AC57-R57-Q57)</f>
+        <v/>
       </c>
       <c r="Q57" s="162"/>
       <c r="R57" s="162"/>
@@ -26811,8 +26988,9 @@
       <c r="AA57" s="161"/>
       <c r="AB57" s="160"/>
       <c r="AC57" s="163"/>
-      <c r="AD57" t="str" s="159" cm="1">
+      <c r="AD57" s="159" cm="1" t="str">
         <f t="array" ref="AD57">IF(AG57="","",$AG57-$AF57)</f>
+        <v/>
       </c>
       <c r="AE57" s="160"/>
       <c r="AF57" s="196"/>
@@ -26852,19 +27030,21 @@
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" s="155" cm="1">
         <f t="array" ref="A58">A57+1</f>
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B58" s="151"/>
       <c r="C58" s="170"/>
       <c r="D58" s="165"/>
       <c r="E58" s="164"/>
-      <c r="F58" t="str" s="195" cm="1">
+      <c r="F58" s="195" cm="1" t="str">
         <f t="array" ref="F58">IF(AG58="","",I58-H58)</f>
+        <v/>
       </c>
       <c r="G58" s="160"/>
       <c r="H58" s="158"/>
-      <c r="I58" t="str" s="159" cm="1">
+      <c r="I58" s="159" cm="1" t="str">
         <f t="array" ref="I58">IF(AG58="","",P58-K58)</f>
+        <v/>
       </c>
       <c r="J58" s="160"/>
       <c r="K58" s="158"/>
@@ -26872,8 +27052,9 @@
       <c r="M58" s="161"/>
       <c r="N58" s="161"/>
       <c r="O58" s="161"/>
-      <c r="P58" t="str" s="159" cm="1">
+      <c r="P58" s="159" cm="1" t="str">
         <f t="array" ref="P58">IF(AG58="","",AC58-R58-Q58)</f>
+        <v/>
       </c>
       <c r="Q58" s="162"/>
       <c r="R58" s="162"/>
@@ -26888,8 +27069,9 @@
       <c r="AA58" s="161"/>
       <c r="AB58" s="160"/>
       <c r="AC58" s="163"/>
-      <c r="AD58" t="str" s="159" cm="1">
+      <c r="AD58" s="159" cm="1" t="str">
         <f t="array" ref="AD58">IF(AG58="","",$AG58-$AF58)</f>
+        <v/>
       </c>
       <c r="AE58" s="160"/>
       <c r="AF58" s="196"/>
@@ -26929,19 +27111,21 @@
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="155" cm="1">
         <f t="array" ref="A59">A58+1</f>
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="170"/>
       <c r="D59" s="165"/>
       <c r="E59" s="164"/>
-      <c r="F59" t="str" s="195" cm="1">
+      <c r="F59" s="195" cm="1" t="str">
         <f t="array" ref="F59">IF(AG59="","",I59-H59)</f>
+        <v/>
       </c>
       <c r="G59" s="160"/>
       <c r="H59" s="158"/>
-      <c r="I59" t="str" s="159" cm="1">
+      <c r="I59" s="159" cm="1" t="str">
         <f t="array" ref="I59">IF(AG59="","",P59-K59)</f>
+        <v/>
       </c>
       <c r="J59" s="160"/>
       <c r="K59" s="158"/>
@@ -26949,8 +27133,9 @@
       <c r="M59" s="161"/>
       <c r="N59" s="161"/>
       <c r="O59" s="161"/>
-      <c r="P59" t="str" s="159" cm="1">
+      <c r="P59" s="159" cm="1" t="str">
         <f t="array" ref="P59">IF(AG59="","",AC59-R59-Q59)</f>
+        <v/>
       </c>
       <c r="Q59" s="162"/>
       <c r="R59" s="162"/>
@@ -26965,8 +27150,9 @@
       <c r="AA59" s="161"/>
       <c r="AB59" s="160"/>
       <c r="AC59" s="163"/>
-      <c r="AD59" t="str" s="159" cm="1">
+      <c r="AD59" s="159" cm="1" t="str">
         <f t="array" ref="AD59">IF(AG59="","",$AG59-$AF59)</f>
+        <v/>
       </c>
       <c r="AE59" s="160"/>
       <c r="AF59" s="196"/>
@@ -27006,19 +27192,21 @@
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" s="155" cm="1">
         <f t="array" ref="A60">A59+1</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B60" s="151"/>
       <c r="C60" s="170"/>
       <c r="D60" s="165"/>
       <c r="E60" s="164"/>
-      <c r="F60" t="str" s="195" cm="1">
+      <c r="F60" s="195" cm="1" t="str">
         <f t="array" ref="F60">IF(AG60="","",I60-H60)</f>
+        <v/>
       </c>
       <c r="G60" s="160"/>
       <c r="H60" s="158"/>
-      <c r="I60" t="str" s="159" cm="1">
+      <c r="I60" s="159" cm="1" t="str">
         <f t="array" ref="I60">IF(AG60="","",P60-K60)</f>
+        <v/>
       </c>
       <c r="J60" s="160"/>
       <c r="K60" s="158"/>
@@ -27026,8 +27214,9 @@
       <c r="M60" s="161"/>
       <c r="N60" s="161"/>
       <c r="O60" s="161"/>
-      <c r="P60" t="str" s="159" cm="1">
+      <c r="P60" s="159" cm="1" t="str">
         <f t="array" ref="P60">IF(AG60="","",AC60-R60-Q60)</f>
+        <v/>
       </c>
       <c r="Q60" s="162"/>
       <c r="R60" s="162"/>
@@ -27042,8 +27231,9 @@
       <c r="AA60" s="161"/>
       <c r="AB60" s="160"/>
       <c r="AC60" s="163"/>
-      <c r="AD60" t="str" s="159" cm="1">
+      <c r="AD60" s="159" cm="1" t="str">
         <f t="array" ref="AD60">IF(AG60="","",$AG60-$AF60)</f>
+        <v/>
       </c>
       <c r="AE60" s="160"/>
       <c r="AF60" s="196"/>
@@ -27083,19 +27273,21 @@
     <row r="61" ht="25.5" customHeight="1">
       <c r="A61" s="155" cm="1">
         <f t="array" ref="A61">A60+1</f>
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B61" s="151"/>
       <c r="C61" s="170"/>
       <c r="D61" s="165"/>
       <c r="E61" s="164"/>
-      <c r="F61" t="str" s="195" cm="1">
+      <c r="F61" s="195" cm="1" t="str">
         <f t="array" ref="F61">IF(AG61="","",I61-H61)</f>
+        <v/>
       </c>
       <c r="G61" s="160"/>
       <c r="H61" s="158"/>
-      <c r="I61" t="str" s="159" cm="1">
+      <c r="I61" s="159" cm="1" t="str">
         <f t="array" ref="I61">IF(AG61="","",P61-K61)</f>
+        <v/>
       </c>
       <c r="J61" s="160"/>
       <c r="K61" s="158"/>
@@ -27103,8 +27295,9 @@
       <c r="M61" s="161"/>
       <c r="N61" s="161"/>
       <c r="O61" s="161"/>
-      <c r="P61" t="str" s="159" cm="1">
+      <c r="P61" s="159" cm="1" t="str">
         <f t="array" ref="P61">IF(AG61="","",AC61-R61-Q61)</f>
+        <v/>
       </c>
       <c r="Q61" s="162"/>
       <c r="R61" s="162"/>
@@ -27119,8 +27312,9 @@
       <c r="AA61" s="161"/>
       <c r="AB61" s="160"/>
       <c r="AC61" s="163"/>
-      <c r="AD61" t="str" s="159" cm="1">
+      <c r="AD61" s="159" cm="1" t="str">
         <f t="array" ref="AD61">IF(AG61="","",$AG61-$AF61)</f>
+        <v/>
       </c>
       <c r="AE61" s="160"/>
       <c r="AF61" s="196"/>
@@ -27160,19 +27354,21 @@
     <row r="62" ht="25.5" customHeight="1">
       <c r="A62" s="155" cm="1">
         <f t="array" ref="A62">A61+1</f>
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B62" s="151"/>
       <c r="C62" s="170"/>
       <c r="D62" s="165"/>
       <c r="E62" s="164"/>
-      <c r="F62" t="str" s="195" cm="1">
+      <c r="F62" s="195" cm="1" t="str">
         <f t="array" ref="F62">IF(AG62="","",I62-H62)</f>
+        <v/>
       </c>
       <c r="G62" s="160"/>
       <c r="H62" s="158"/>
-      <c r="I62" t="str" s="159" cm="1">
+      <c r="I62" s="159" cm="1" t="str">
         <f t="array" ref="I62">IF(AG62="","",P62-K62)</f>
+        <v/>
       </c>
       <c r="J62" s="160"/>
       <c r="K62" s="158"/>
@@ -27180,8 +27376,9 @@
       <c r="M62" s="161"/>
       <c r="N62" s="161"/>
       <c r="O62" s="161"/>
-      <c r="P62" t="str" s="159" cm="1">
+      <c r="P62" s="159" cm="1" t="str">
         <f t="array" ref="P62">IF(AG62="","",AC62-R62-Q62)</f>
+        <v/>
       </c>
       <c r="Q62" s="162"/>
       <c r="R62" s="162"/>
@@ -27196,8 +27393,9 @@
       <c r="AA62" s="161"/>
       <c r="AB62" s="160"/>
       <c r="AC62" s="163"/>
-      <c r="AD62" t="str" s="159" cm="1">
+      <c r="AD62" s="159" cm="1" t="str">
         <f t="array" ref="AD62">IF(AG62="","",$AG62-$AF62)</f>
+        <v/>
       </c>
       <c r="AE62" s="160"/>
       <c r="AF62" s="196"/>
@@ -27237,7 +27435,7 @@
     <row r="63" ht="25.5" customHeight="1">
       <c r="A63" s="155" cm="1">
         <f t="array" ref="A63">A62+1</f>
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B63" s="151"/>
       <c r="C63" t="s" s="156">
@@ -27245,13 +27443,15 @@
       </c>
       <c r="D63" s="165"/>
       <c r="E63" s="164"/>
-      <c r="F63" t="str" s="195" cm="1">
+      <c r="F63" s="195" cm="1" t="str">
         <f t="array" ref="F63">IF(AG63="","",I63-H63)</f>
+        <v/>
       </c>
       <c r="G63" s="160"/>
       <c r="H63" s="158"/>
-      <c r="I63" t="str" s="159" cm="1">
+      <c r="I63" s="159" cm="1" t="str">
         <f t="array" ref="I63">IF(AG63="","",P63-K63)</f>
+        <v/>
       </c>
       <c r="J63" s="160"/>
       <c r="K63" s="158"/>
@@ -27259,8 +27459,9 @@
       <c r="M63" s="161"/>
       <c r="N63" s="161"/>
       <c r="O63" s="161"/>
-      <c r="P63" t="str" s="159" cm="1">
+      <c r="P63" s="159" cm="1" t="str">
         <f t="array" ref="P63">IF(AG63="","",AC63-R63-Q63)</f>
+        <v/>
       </c>
       <c r="Q63" s="162"/>
       <c r="R63" s="162"/>
@@ -27275,8 +27476,9 @@
       <c r="AA63" s="161"/>
       <c r="AB63" s="160"/>
       <c r="AC63" s="163"/>
-      <c r="AD63" t="str" s="159" cm="1">
+      <c r="AD63" s="159" cm="1" t="str">
         <f t="array" ref="AD63">IF(AG63="","",$AG63-$AF63)</f>
+        <v/>
       </c>
       <c r="AE63" s="160"/>
       <c r="AF63" s="196"/>
@@ -27322,13 +27524,15 @@
       <c r="C64" s="170"/>
       <c r="D64" s="165"/>
       <c r="E64" s="164"/>
-      <c r="F64" t="str" s="195" cm="1">
+      <c r="F64" s="195" cm="1" t="str">
         <f t="array" ref="F64">IF(AG64="","",I64-H64)</f>
+        <v/>
       </c>
       <c r="G64" s="160"/>
       <c r="H64" s="158"/>
-      <c r="I64" t="str" s="159" cm="1">
+      <c r="I64" s="159" cm="1" t="str">
         <f t="array" ref="I64">IF(AG64="","",P64-K64)</f>
+        <v/>
       </c>
       <c r="J64" s="160"/>
       <c r="K64" s="158"/>
@@ -27336,8 +27540,9 @@
       <c r="M64" s="161"/>
       <c r="N64" s="161"/>
       <c r="O64" s="161"/>
-      <c r="P64" t="str" s="159" cm="1">
+      <c r="P64" s="159" cm="1" t="str">
         <f t="array" ref="P64">IF(AG64="","",AC64-R64-Q64)</f>
+        <v/>
       </c>
       <c r="Q64" s="162"/>
       <c r="R64" s="162"/>
@@ -27352,8 +27557,9 @@
       <c r="AA64" s="161"/>
       <c r="AB64" s="160"/>
       <c r="AC64" s="163"/>
-      <c r="AD64" t="str" s="159" cm="1">
+      <c r="AD64" s="159" cm="1" t="str">
         <f t="array" ref="AD64">IF(AG64="","",$AG64-$AF64)</f>
+        <v/>
       </c>
       <c r="AE64" s="160"/>
       <c r="AF64" s="196"/>
@@ -27399,13 +27605,15 @@
       <c r="C65" s="170"/>
       <c r="D65" s="165"/>
       <c r="E65" s="164"/>
-      <c r="F65" t="str" s="195" cm="1">
+      <c r="F65" s="195" cm="1" t="str">
         <f t="array" ref="F65">IF(AG65="","",I65-H65)</f>
+        <v/>
       </c>
       <c r="G65" s="160"/>
       <c r="H65" s="158"/>
-      <c r="I65" t="str" s="159" cm="1">
+      <c r="I65" s="159" cm="1" t="str">
         <f t="array" ref="I65">IF(AG65="","",P65-K65)</f>
+        <v/>
       </c>
       <c r="J65" s="160"/>
       <c r="K65" s="158"/>
@@ -27413,8 +27621,9 @@
       <c r="M65" s="161"/>
       <c r="N65" s="161"/>
       <c r="O65" s="161"/>
-      <c r="P65" t="str" s="159" cm="1">
+      <c r="P65" s="159" cm="1" t="str">
         <f t="array" ref="P65">IF(AG65="","",AC65-R65-Q65)</f>
+        <v/>
       </c>
       <c r="Q65" s="162"/>
       <c r="R65" s="162"/>
@@ -27429,8 +27638,9 @@
       <c r="AA65" s="161"/>
       <c r="AB65" s="160"/>
       <c r="AC65" s="163"/>
-      <c r="AD65" t="str" s="159" cm="1">
+      <c r="AD65" s="159" cm="1" t="str">
         <f t="array" ref="AD65">IF(AG65="","",$AG65-$AF65)</f>
+        <v/>
       </c>
       <c r="AE65" s="160"/>
       <c r="AF65" s="196"/>
@@ -27476,13 +27686,15 @@
       <c r="C66" s="170"/>
       <c r="D66" s="165"/>
       <c r="E66" s="164"/>
-      <c r="F66" t="str" s="195" cm="1">
+      <c r="F66" s="195" cm="1" t="str">
         <f t="array" ref="F66">IF(AG66="","",I66-H66)</f>
+        <v/>
       </c>
       <c r="G66" s="160"/>
       <c r="H66" s="158"/>
-      <c r="I66" t="str" s="159" cm="1">
+      <c r="I66" s="159" cm="1" t="str">
         <f t="array" ref="I66">IF(AG66="","",P66-K66)</f>
+        <v/>
       </c>
       <c r="J66" s="160"/>
       <c r="K66" s="158"/>
@@ -27490,8 +27702,9 @@
       <c r="M66" s="161"/>
       <c r="N66" s="161"/>
       <c r="O66" s="161"/>
-      <c r="P66" t="str" s="159" cm="1">
+      <c r="P66" s="159" cm="1" t="str">
         <f t="array" ref="P66">IF(AG66="","",AC66-R66-Q66)</f>
+        <v/>
       </c>
       <c r="Q66" s="162"/>
       <c r="R66" s="162"/>
@@ -27506,8 +27719,9 @@
       <c r="AA66" s="161"/>
       <c r="AB66" s="160"/>
       <c r="AC66" s="163"/>
-      <c r="AD66" t="str" s="159" cm="1">
+      <c r="AD66" s="159" cm="1" t="str">
         <f t="array" ref="AD66">IF(AG66="","",$AG66-$AF66)</f>
+        <v/>
       </c>
       <c r="AE66" s="160"/>
       <c r="AF66" s="196"/>
@@ -27553,13 +27767,15 @@
       <c r="C67" s="170"/>
       <c r="D67" s="165"/>
       <c r="E67" s="164"/>
-      <c r="F67" t="str" s="195" cm="1">
+      <c r="F67" s="195" cm="1" t="str">
         <f t="array" ref="F67">IF(AG67="","",I67-H67)</f>
+        <v/>
       </c>
       <c r="G67" s="160"/>
       <c r="H67" s="158"/>
-      <c r="I67" t="str" s="159" cm="1">
+      <c r="I67" s="159" cm="1" t="str">
         <f t="array" ref="I67">IF(AG67="","",P67-K67)</f>
+        <v/>
       </c>
       <c r="J67" s="160"/>
       <c r="K67" s="158"/>
@@ -27567,8 +27783,9 @@
       <c r="M67" s="161"/>
       <c r="N67" s="161"/>
       <c r="O67" s="161"/>
-      <c r="P67" t="str" s="159" cm="1">
+      <c r="P67" s="159" cm="1" t="str">
         <f t="array" ref="P67">IF(AG67="","",AC67-R67-Q67)</f>
+        <v/>
       </c>
       <c r="Q67" s="162"/>
       <c r="R67" s="162"/>
@@ -27583,8 +27800,9 @@
       <c r="AA67" s="161"/>
       <c r="AB67" s="160"/>
       <c r="AC67" s="163"/>
-      <c r="AD67" t="str" s="159" cm="1">
+      <c r="AD67" s="159" cm="1" t="str">
         <f t="array" ref="AD67">IF(AG67="","",$AG67-$AF67)</f>
+        <v/>
       </c>
       <c r="AE67" s="160"/>
       <c r="AF67" s="196"/>
@@ -27630,13 +27848,15 @@
       <c r="C68" s="170"/>
       <c r="D68" s="165"/>
       <c r="E68" s="164"/>
-      <c r="F68" t="str" s="195" cm="1">
+      <c r="F68" s="195" cm="1" t="str">
         <f t="array" ref="F68">IF(AG68="","",I68-H68)</f>
+        <v/>
       </c>
       <c r="G68" s="160"/>
       <c r="H68" s="158"/>
-      <c r="I68" t="str" s="159" cm="1">
+      <c r="I68" s="159" cm="1" t="str">
         <f t="array" ref="I68">IF(AG68="","",P68-K68)</f>
+        <v/>
       </c>
       <c r="J68" s="160"/>
       <c r="K68" s="158"/>
@@ -27644,8 +27864,9 @@
       <c r="M68" s="161"/>
       <c r="N68" s="161"/>
       <c r="O68" s="161"/>
-      <c r="P68" t="str" s="159" cm="1">
+      <c r="P68" s="159" cm="1" t="str">
         <f t="array" ref="P68">IF(AG68="","",AC68-R68-Q68)</f>
+        <v/>
       </c>
       <c r="Q68" s="162"/>
       <c r="R68" s="162"/>
@@ -27660,8 +27881,9 @@
       <c r="AA68" s="161"/>
       <c r="AB68" s="160"/>
       <c r="AC68" s="163"/>
-      <c r="AD68" t="str" s="159" cm="1">
+      <c r="AD68" s="159" cm="1" t="str">
         <f t="array" ref="AD68">IF(AG68="","",$AG68-$AF68)</f>
+        <v/>
       </c>
       <c r="AE68" s="160"/>
       <c r="AF68" s="196"/>
@@ -27707,13 +27929,15 @@
       <c r="C69" s="170"/>
       <c r="D69" s="165"/>
       <c r="E69" s="164"/>
-      <c r="F69" t="str" s="195" cm="1">
+      <c r="F69" s="195" cm="1" t="str">
         <f t="array" ref="F69">IF(AG69="","",I69-H69)</f>
+        <v/>
       </c>
       <c r="G69" s="160"/>
       <c r="H69" s="158"/>
-      <c r="I69" t="str" s="159" cm="1">
+      <c r="I69" s="159" cm="1" t="str">
         <f t="array" ref="I69">IF(AG69="","",P69-K69)</f>
+        <v/>
       </c>
       <c r="J69" s="160"/>
       <c r="K69" s="158"/>
@@ -27721,8 +27945,9 @@
       <c r="M69" s="161"/>
       <c r="N69" s="161"/>
       <c r="O69" s="161"/>
-      <c r="P69" t="str" s="159" cm="1">
+      <c r="P69" s="159" cm="1" t="str">
         <f t="array" ref="P69">IF(AG69="","",AC69-R69-Q69)</f>
+        <v/>
       </c>
       <c r="Q69" s="162"/>
       <c r="R69" s="162"/>
@@ -27737,8 +27962,9 @@
       <c r="AA69" s="161"/>
       <c r="AB69" s="160"/>
       <c r="AC69" s="163"/>
-      <c r="AD69" t="str" s="159" cm="1">
+      <c r="AD69" s="159" cm="1" t="str">
         <f t="array" ref="AD69">IF(AG69="","",$AG69-$AF69)</f>
+        <v/>
       </c>
       <c r="AE69" s="160"/>
       <c r="AF69" s="196"/>
@@ -27784,13 +28010,15 @@
       <c r="C70" s="170"/>
       <c r="D70" s="165"/>
       <c r="E70" s="164"/>
-      <c r="F70" t="str" s="195" cm="1">
+      <c r="F70" s="195" cm="1" t="str">
         <f t="array" ref="F70">IF(AG70="","",I70-H70)</f>
+        <v/>
       </c>
       <c r="G70" s="160"/>
       <c r="H70" s="158"/>
-      <c r="I70" t="str" s="159" cm="1">
+      <c r="I70" s="159" cm="1" t="str">
         <f t="array" ref="I70">IF(AG70="","",P70-K70)</f>
+        <v/>
       </c>
       <c r="J70" s="160"/>
       <c r="K70" s="158"/>
@@ -27798,8 +28026,9 @@
       <c r="M70" s="161"/>
       <c r="N70" s="161"/>
       <c r="O70" s="161"/>
-      <c r="P70" t="str" s="159" cm="1">
+      <c r="P70" s="159" cm="1" t="str">
         <f t="array" ref="P70">IF(AG70="","",AC70-R70-Q70)</f>
+        <v/>
       </c>
       <c r="Q70" s="162"/>
       <c r="R70" s="162"/>
@@ -27814,8 +28043,9 @@
       <c r="AA70" s="161"/>
       <c r="AB70" s="160"/>
       <c r="AC70" s="163"/>
-      <c r="AD70" t="str" s="159" cm="1">
+      <c r="AD70" s="159" cm="1" t="str">
         <f t="array" ref="AD70">IF(AG70="","",$AG70-$AF70)</f>
+        <v/>
       </c>
       <c r="AE70" s="160"/>
       <c r="AF70" s="196"/>
@@ -27861,13 +28091,15 @@
       <c r="C71" s="170"/>
       <c r="D71" s="165"/>
       <c r="E71" s="164"/>
-      <c r="F71" t="str" s="195" cm="1">
+      <c r="F71" s="195" cm="1" t="str">
         <f t="array" ref="F71">IF(AG71="","",I71-H71)</f>
+        <v/>
       </c>
       <c r="G71" s="160"/>
       <c r="H71" s="158"/>
-      <c r="I71" t="str" s="159" cm="1">
+      <c r="I71" s="159" cm="1" t="str">
         <f t="array" ref="I71">IF(AG71="","",P71-K71)</f>
+        <v/>
       </c>
       <c r="J71" s="160"/>
       <c r="K71" s="158"/>
@@ -27875,8 +28107,9 @@
       <c r="M71" s="161"/>
       <c r="N71" s="161"/>
       <c r="O71" s="161"/>
-      <c r="P71" t="str" s="159" cm="1">
+      <c r="P71" s="159" cm="1" t="str">
         <f t="array" ref="P71">IF(AG71="","",AC71-R71-Q71)</f>
+        <v/>
       </c>
       <c r="Q71" s="162"/>
       <c r="R71" s="162"/>
@@ -27891,8 +28124,9 @@
       <c r="AA71" s="161"/>
       <c r="AB71" s="160"/>
       <c r="AC71" s="163"/>
-      <c r="AD71" t="str" s="159" cm="1">
+      <c r="AD71" s="159" cm="1" t="str">
         <f t="array" ref="AD71">IF(AG71="","",$AG71-$AF71)</f>
+        <v/>
       </c>
       <c r="AE71" s="160"/>
       <c r="AF71" s="196"/>
@@ -27938,13 +28172,15 @@
       <c r="C72" s="170"/>
       <c r="D72" s="165"/>
       <c r="E72" s="164"/>
-      <c r="F72" t="str" s="195" cm="1">
+      <c r="F72" s="195" cm="1" t="str">
         <f t="array" ref="F72">IF(AG72="","",I72-H72)</f>
+        <v/>
       </c>
       <c r="G72" s="160"/>
       <c r="H72" s="158"/>
-      <c r="I72" t="str" s="159" cm="1">
+      <c r="I72" s="159" cm="1" t="str">
         <f t="array" ref="I72">IF(AG72="","",P72-K72)</f>
+        <v/>
       </c>
       <c r="J72" s="160"/>
       <c r="K72" s="158"/>
@@ -27952,8 +28188,9 @@
       <c r="M72" s="161"/>
       <c r="N72" s="161"/>
       <c r="O72" s="161"/>
-      <c r="P72" t="str" s="159" cm="1">
+      <c r="P72" s="159" cm="1" t="str">
         <f t="array" ref="P72">IF(AG72="","",AC72-R72-Q72)</f>
+        <v/>
       </c>
       <c r="Q72" s="162"/>
       <c r="R72" s="162"/>
@@ -27968,8 +28205,9 @@
       <c r="AA72" s="161"/>
       <c r="AB72" s="160"/>
       <c r="AC72" s="163"/>
-      <c r="AD72" t="str" s="159" cm="1">
+      <c r="AD72" s="159" cm="1" t="str">
         <f t="array" ref="AD72">IF(AG72="","",$AG72-$AF72)</f>
+        <v/>
       </c>
       <c r="AE72" s="160"/>
       <c r="AF72" s="196"/>
@@ -28015,13 +28253,15 @@
       <c r="C73" s="170"/>
       <c r="D73" s="165"/>
       <c r="E73" s="164"/>
-      <c r="F73" t="str" s="195" cm="1">
+      <c r="F73" s="195" cm="1" t="str">
         <f t="array" ref="F73">IF(AG73="","",I73-H73)</f>
+        <v/>
       </c>
       <c r="G73" s="160"/>
       <c r="H73" s="158"/>
-      <c r="I73" t="str" s="159" cm="1">
+      <c r="I73" s="159" cm="1" t="str">
         <f t="array" ref="I73">IF(AG73="","",P73-K73)</f>
+        <v/>
       </c>
       <c r="J73" s="160"/>
       <c r="K73" s="158"/>
@@ -28029,8 +28269,9 @@
       <c r="M73" s="161"/>
       <c r="N73" s="161"/>
       <c r="O73" s="161"/>
-      <c r="P73" t="str" s="159" cm="1">
+      <c r="P73" s="159" cm="1" t="str">
         <f t="array" ref="P73">IF(AG73="","",AC73-R73-Q73)</f>
+        <v/>
       </c>
       <c r="Q73" s="162"/>
       <c r="R73" s="162"/>
@@ -28045,8 +28286,9 @@
       <c r="AA73" s="161"/>
       <c r="AB73" s="160"/>
       <c r="AC73" s="163"/>
-      <c r="AD73" t="str" s="159" cm="1">
+      <c r="AD73" s="159" cm="1" t="str">
         <f t="array" ref="AD73">IF(AG73="","",$AG73-$AF73)</f>
+        <v/>
       </c>
       <c r="AE73" s="160"/>
       <c r="AF73" s="196"/>
@@ -28092,13 +28334,15 @@
       <c r="C74" s="170"/>
       <c r="D74" s="165"/>
       <c r="E74" s="164"/>
-      <c r="F74" t="str" s="195" cm="1">
+      <c r="F74" s="195" cm="1" t="str">
         <f t="array" ref="F74">IF(AG74="","",I74-H74)</f>
+        <v/>
       </c>
       <c r="G74" s="160"/>
       <c r="H74" s="158"/>
-      <c r="I74" t="str" s="159" cm="1">
+      <c r="I74" s="159" cm="1" t="str">
         <f t="array" ref="I74">IF(AG74="","",P74-K74)</f>
+        <v/>
       </c>
       <c r="J74" s="160"/>
       <c r="K74" s="158"/>
@@ -28106,8 +28350,9 @@
       <c r="M74" s="161"/>
       <c r="N74" s="161"/>
       <c r="O74" s="161"/>
-      <c r="P74" t="str" s="159" cm="1">
+      <c r="P74" s="159" cm="1" t="str">
         <f t="array" ref="P74">IF(AG74="","",AC74-R74-Q74)</f>
+        <v/>
       </c>
       <c r="Q74" s="162"/>
       <c r="R74" s="162"/>
@@ -28122,8 +28367,9 @@
       <c r="AA74" s="161"/>
       <c r="AB74" s="160"/>
       <c r="AC74" s="163"/>
-      <c r="AD74" t="str" s="159" cm="1">
+      <c r="AD74" s="159" cm="1" t="str">
         <f t="array" ref="AD74">IF(AG74="","",$AG74-$AF74)</f>
+        <v/>
       </c>
       <c r="AE74" s="160"/>
       <c r="AF74" s="196"/>
@@ -28169,13 +28415,15 @@
       <c r="C75" s="170"/>
       <c r="D75" s="165"/>
       <c r="E75" s="164"/>
-      <c r="F75" t="str" s="195" cm="1">
+      <c r="F75" s="195" cm="1" t="str">
         <f t="array" ref="F75">IF(AG75="","",I75-H75)</f>
+        <v/>
       </c>
       <c r="G75" s="160"/>
       <c r="H75" s="158"/>
-      <c r="I75" t="str" s="159" cm="1">
+      <c r="I75" s="159" cm="1" t="str">
         <f t="array" ref="I75">IF(AG75="","",P75-K75)</f>
+        <v/>
       </c>
       <c r="J75" s="160"/>
       <c r="K75" s="158"/>
@@ -28183,8 +28431,9 @@
       <c r="M75" s="161"/>
       <c r="N75" s="161"/>
       <c r="O75" s="161"/>
-      <c r="P75" t="str" s="159" cm="1">
+      <c r="P75" s="159" cm="1" t="str">
         <f t="array" ref="P75">IF(AG75="","",AC75-R75-Q75)</f>
+        <v/>
       </c>
       <c r="Q75" s="162"/>
       <c r="R75" s="162"/>
@@ -28199,8 +28448,9 @@
       <c r="AA75" s="161"/>
       <c r="AB75" s="160"/>
       <c r="AC75" s="163"/>
-      <c r="AD75" t="str" s="159" cm="1">
+      <c r="AD75" s="159" cm="1" t="str">
         <f t="array" ref="AD75">IF(AG75="","",$AG75-$AF75)</f>
+        <v/>
       </c>
       <c r="AE75" s="160"/>
       <c r="AF75" s="196"/>
@@ -28246,13 +28496,15 @@
       <c r="C76" s="170"/>
       <c r="D76" s="165"/>
       <c r="E76" s="164"/>
-      <c r="F76" t="str" s="195" cm="1">
+      <c r="F76" s="195" cm="1" t="str">
         <f t="array" ref="F76">IF(AG76="","",I76-H76)</f>
+        <v/>
       </c>
       <c r="G76" s="160"/>
       <c r="H76" s="158"/>
-      <c r="I76" t="str" s="159" cm="1">
+      <c r="I76" s="159" cm="1" t="str">
         <f t="array" ref="I76">IF(AG76="","",P76-K76)</f>
+        <v/>
       </c>
       <c r="J76" s="160"/>
       <c r="K76" s="158"/>
@@ -28260,8 +28512,9 @@
       <c r="M76" s="161"/>
       <c r="N76" s="161"/>
       <c r="O76" s="161"/>
-      <c r="P76" t="str" s="159" cm="1">
+      <c r="P76" s="159" cm="1" t="str">
         <f t="array" ref="P76">IF(AG76="","",AC76-R76-Q76)</f>
+        <v/>
       </c>
       <c r="Q76" s="162"/>
       <c r="R76" s="162"/>
@@ -28276,8 +28529,9 @@
       <c r="AA76" s="161"/>
       <c r="AB76" s="160"/>
       <c r="AC76" s="163"/>
-      <c r="AD76" t="str" s="159" cm="1">
+      <c r="AD76" s="159" cm="1" t="str">
         <f t="array" ref="AD76">IF(AG76="","",$AG76-$AF76)</f>
+        <v/>
       </c>
       <c r="AE76" s="160"/>
       <c r="AF76" s="196"/>
@@ -28323,13 +28577,15 @@
       <c r="C77" s="170"/>
       <c r="D77" s="165"/>
       <c r="E77" s="164"/>
-      <c r="F77" t="str" s="195" cm="1">
+      <c r="F77" s="195" cm="1" t="str">
         <f t="array" ref="F77">IF(AG77="","",I77-H77)</f>
+        <v/>
       </c>
       <c r="G77" s="160"/>
       <c r="H77" s="158"/>
-      <c r="I77" t="str" s="159" cm="1">
+      <c r="I77" s="159" cm="1" t="str">
         <f t="array" ref="I77">IF(AG77="","",P77-K77)</f>
+        <v/>
       </c>
       <c r="J77" s="160"/>
       <c r="K77" s="158"/>
@@ -28337,8 +28593,9 @@
       <c r="M77" s="161"/>
       <c r="N77" s="161"/>
       <c r="O77" s="161"/>
-      <c r="P77" t="str" s="159" cm="1">
+      <c r="P77" s="159" cm="1" t="str">
         <f t="array" ref="P77">IF(AG77="","",AC77-R77-Q77)</f>
+        <v/>
       </c>
       <c r="Q77" s="162"/>
       <c r="R77" s="162"/>
@@ -28353,8 +28610,9 @@
       <c r="AA77" s="161"/>
       <c r="AB77" s="160"/>
       <c r="AC77" s="163"/>
-      <c r="AD77" t="str" s="159" cm="1">
+      <c r="AD77" s="159" cm="1" t="str">
         <f t="array" ref="AD77">IF(AG77="","",$AG77-$AF77)</f>
+        <v/>
       </c>
       <c r="AE77" s="160"/>
       <c r="AF77" s="196"/>
@@ -28400,13 +28658,15 @@
       <c r="C78" s="170"/>
       <c r="D78" s="165"/>
       <c r="E78" s="164"/>
-      <c r="F78" t="str" s="195" cm="1">
+      <c r="F78" s="195" cm="1" t="str">
         <f t="array" ref="F78">IF(AG78="","",I78-H78)</f>
+        <v/>
       </c>
       <c r="G78" s="160"/>
       <c r="H78" s="158"/>
-      <c r="I78" t="str" s="159" cm="1">
+      <c r="I78" s="159" cm="1" t="str">
         <f t="array" ref="I78">IF(AG78="","",P78-K78)</f>
+        <v/>
       </c>
       <c r="J78" s="160"/>
       <c r="K78" s="158"/>
@@ -28414,8 +28674,9 @@
       <c r="M78" s="161"/>
       <c r="N78" s="161"/>
       <c r="O78" s="161"/>
-      <c r="P78" t="str" s="159" cm="1">
+      <c r="P78" s="159" cm="1" t="str">
         <f t="array" ref="P78">IF(AG78="","",AC78-R78-Q78)</f>
+        <v/>
       </c>
       <c r="Q78" s="162"/>
       <c r="R78" s="162"/>
@@ -28430,8 +28691,9 @@
       <c r="AA78" s="161"/>
       <c r="AB78" s="160"/>
       <c r="AC78" s="163"/>
-      <c r="AD78" t="str" s="159" cm="1">
+      <c r="AD78" s="159" cm="1" t="str">
         <f t="array" ref="AD78">IF(AG78="","",$AG78-$AF78)</f>
+        <v/>
       </c>
       <c r="AE78" s="160"/>
       <c r="AF78" s="196"/>
@@ -28477,13 +28739,15 @@
       <c r="C79" s="170"/>
       <c r="D79" s="165"/>
       <c r="E79" s="164"/>
-      <c r="F79" t="str" s="195" cm="1">
+      <c r="F79" s="195" cm="1" t="str">
         <f t="array" ref="F79">IF(AG79="","",I79-H79)</f>
+        <v/>
       </c>
       <c r="G79" s="160"/>
       <c r="H79" s="158"/>
-      <c r="I79" t="str" s="159" cm="1">
+      <c r="I79" s="159" cm="1" t="str">
         <f t="array" ref="I79">IF(AG79="","",P79-K79)</f>
+        <v/>
       </c>
       <c r="J79" s="160"/>
       <c r="K79" s="158"/>
@@ -28491,8 +28755,9 @@
       <c r="M79" s="161"/>
       <c r="N79" s="161"/>
       <c r="O79" s="161"/>
-      <c r="P79" t="str" s="159" cm="1">
+      <c r="P79" s="159" cm="1" t="str">
         <f t="array" ref="P79">IF(AG79="","",AC79-R79-Q79)</f>
+        <v/>
       </c>
       <c r="Q79" s="162"/>
       <c r="R79" s="162"/>
@@ -28507,8 +28772,9 @@
       <c r="AA79" s="161"/>
       <c r="AB79" s="160"/>
       <c r="AC79" s="163"/>
-      <c r="AD79" t="str" s="159" cm="1">
+      <c r="AD79" s="159" cm="1" t="str">
         <f t="array" ref="AD79">IF(AG79="","",$AG79-$AF79)</f>
+        <v/>
       </c>
       <c r="AE79" s="160"/>
       <c r="AF79" s="196"/>
@@ -28554,13 +28820,15 @@
       <c r="C80" s="170"/>
       <c r="D80" s="165"/>
       <c r="E80" s="164"/>
-      <c r="F80" t="str" s="195" cm="1">
+      <c r="F80" s="195" cm="1" t="str">
         <f t="array" ref="F80">IF(AG80="","",I80-H80)</f>
+        <v/>
       </c>
       <c r="G80" s="160"/>
       <c r="H80" s="158"/>
-      <c r="I80" t="str" s="159" cm="1">
+      <c r="I80" s="159" cm="1" t="str">
         <f t="array" ref="I80">IF(AG80="","",P80-K80)</f>
+        <v/>
       </c>
       <c r="J80" s="160"/>
       <c r="K80" s="158"/>
@@ -28568,8 +28836,9 @@
       <c r="M80" s="161"/>
       <c r="N80" s="161"/>
       <c r="O80" s="161"/>
-      <c r="P80" t="str" s="159" cm="1">
+      <c r="P80" s="159" cm="1" t="str">
         <f t="array" ref="P80">IF(AG80="","",AC80-R80-Q80)</f>
+        <v/>
       </c>
       <c r="Q80" s="162"/>
       <c r="R80" s="162"/>
@@ -28584,8 +28853,9 @@
       <c r="AA80" s="161"/>
       <c r="AB80" s="160"/>
       <c r="AC80" s="163"/>
-      <c r="AD80" t="str" s="159" cm="1">
+      <c r="AD80" s="159" cm="1" t="str">
         <f t="array" ref="AD80">IF(AG80="","",$AG80-$AF80)</f>
+        <v/>
       </c>
       <c r="AE80" s="160"/>
       <c r="AF80" s="196"/>
@@ -28631,13 +28901,15 @@
       <c r="C81" s="170"/>
       <c r="D81" s="165"/>
       <c r="E81" s="164"/>
-      <c r="F81" t="str" s="195" cm="1">
+      <c r="F81" s="195" cm="1" t="str">
         <f t="array" ref="F81">IF(AG81="","",I81-H81)</f>
+        <v/>
       </c>
       <c r="G81" s="160"/>
       <c r="H81" s="158"/>
-      <c r="I81" t="str" s="159" cm="1">
+      <c r="I81" s="159" cm="1" t="str">
         <f t="array" ref="I81">IF(AG81="","",P81-K81)</f>
+        <v/>
       </c>
       <c r="J81" s="160"/>
       <c r="K81" s="158"/>
@@ -28645,8 +28917,9 @@
       <c r="M81" s="161"/>
       <c r="N81" s="161"/>
       <c r="O81" s="161"/>
-      <c r="P81" t="str" s="159" cm="1">
+      <c r="P81" s="159" cm="1" t="str">
         <f t="array" ref="P81">IF(AG81="","",AC81-R81-Q81)</f>
+        <v/>
       </c>
       <c r="Q81" s="162"/>
       <c r="R81" s="162"/>
@@ -28661,8 +28934,9 @@
       <c r="AA81" s="161"/>
       <c r="AB81" s="160"/>
       <c r="AC81" s="163"/>
-      <c r="AD81" t="str" s="159" cm="1">
+      <c r="AD81" s="159" cm="1" t="str">
         <f t="array" ref="AD81">IF(AG81="","",$AG81-$AF81)</f>
+        <v/>
       </c>
       <c r="AE81" s="160"/>
       <c r="AF81" s="196"/>
@@ -28708,13 +28982,15 @@
       <c r="C82" s="170"/>
       <c r="D82" s="165"/>
       <c r="E82" s="164"/>
-      <c r="F82" t="str" s="195" cm="1">
+      <c r="F82" s="195" cm="1" t="str">
         <f t="array" ref="F82">IF(AG82="","",I82-H82)</f>
+        <v/>
       </c>
       <c r="G82" s="160"/>
       <c r="H82" s="158"/>
-      <c r="I82" t="str" s="159" cm="1">
+      <c r="I82" s="159" cm="1" t="str">
         <f t="array" ref="I82">IF(AG82="","",P82-K82)</f>
+        <v/>
       </c>
       <c r="J82" s="160"/>
       <c r="K82" s="158"/>
@@ -28722,8 +28998,9 @@
       <c r="M82" s="161"/>
       <c r="N82" s="161"/>
       <c r="O82" s="161"/>
-      <c r="P82" t="str" s="159" cm="1">
+      <c r="P82" s="159" cm="1" t="str">
         <f t="array" ref="P82">IF(AG82="","",AC82-R82-Q82)</f>
+        <v/>
       </c>
       <c r="Q82" s="162"/>
       <c r="R82" s="162"/>
@@ -28738,8 +29015,9 @@
       <c r="AA82" s="161"/>
       <c r="AB82" s="160"/>
       <c r="AC82" s="163"/>
-      <c r="AD82" t="str" s="159" cm="1">
+      <c r="AD82" s="159" cm="1" t="str">
         <f t="array" ref="AD82">IF(AG82="","",$AG82-$AF82)</f>
+        <v/>
       </c>
       <c r="AE82" s="160"/>
       <c r="AF82" s="196"/>
@@ -28785,13 +29063,15 @@
       <c r="C83" s="170"/>
       <c r="D83" s="165"/>
       <c r="E83" s="164"/>
-      <c r="F83" t="str" s="195" cm="1">
+      <c r="F83" s="195" cm="1" t="str">
         <f t="array" ref="F83">IF(AG83="","",I83-H83)</f>
+        <v/>
       </c>
       <c r="G83" s="160"/>
       <c r="H83" s="158"/>
-      <c r="I83" t="str" s="159" cm="1">
+      <c r="I83" s="159" cm="1" t="str">
         <f t="array" ref="I83">IF(AG83="","",P83-K83)</f>
+        <v/>
       </c>
       <c r="J83" s="160"/>
       <c r="K83" s="158"/>
@@ -28799,8 +29079,9 @@
       <c r="M83" s="161"/>
       <c r="N83" s="161"/>
       <c r="O83" s="161"/>
-      <c r="P83" t="str" s="159" cm="1">
+      <c r="P83" s="159" cm="1" t="str">
         <f t="array" ref="P83">IF(AG83="","",AC83-R83-Q83)</f>
+        <v/>
       </c>
       <c r="Q83" s="162"/>
       <c r="R83" s="162"/>
@@ -28815,8 +29096,9 @@
       <c r="AA83" s="161"/>
       <c r="AB83" s="160"/>
       <c r="AC83" s="163"/>
-      <c r="AD83" t="str" s="159" cm="1">
+      <c r="AD83" s="159" cm="1" t="str">
         <f t="array" ref="AD83">IF(AG83="","",$AG83-$AF83)</f>
+        <v/>
       </c>
       <c r="AE83" s="160"/>
       <c r="AF83" s="196"/>
@@ -28862,13 +29144,15 @@
       <c r="C84" s="170"/>
       <c r="D84" s="165"/>
       <c r="E84" s="164"/>
-      <c r="F84" t="str" s="195" cm="1">
+      <c r="F84" s="195" cm="1" t="str">
         <f t="array" ref="F84">IF(AG84="","",I84-H84)</f>
+        <v/>
       </c>
       <c r="G84" s="160"/>
       <c r="H84" s="158"/>
-      <c r="I84" t="str" s="159" cm="1">
+      <c r="I84" s="159" cm="1" t="str">
         <f t="array" ref="I84">IF(AG84="","",P84-K84)</f>
+        <v/>
       </c>
       <c r="J84" s="160"/>
       <c r="K84" s="158"/>
@@ -28876,8 +29160,9 @@
       <c r="M84" s="161"/>
       <c r="N84" s="161"/>
       <c r="O84" s="161"/>
-      <c r="P84" t="str" s="159" cm="1">
+      <c r="P84" s="159" cm="1" t="str">
         <f t="array" ref="P84">IF(AG84="","",AC84-R84-Q84)</f>
+        <v/>
       </c>
       <c r="Q84" s="162"/>
       <c r="R84" s="162"/>
@@ -28892,8 +29177,9 @@
       <c r="AA84" s="161"/>
       <c r="AB84" s="160"/>
       <c r="AC84" s="163"/>
-      <c r="AD84" t="str" s="159" cm="1">
+      <c r="AD84" s="159" cm="1" t="str">
         <f t="array" ref="AD84">IF(AG84="","",$AG84-$AF84)</f>
+        <v/>
       </c>
       <c r="AE84" s="160"/>
       <c r="AF84" s="196"/>
@@ -28939,13 +29225,15 @@
       <c r="C85" s="170"/>
       <c r="D85" s="165"/>
       <c r="E85" s="164"/>
-      <c r="F85" t="str" s="195" cm="1">
+      <c r="F85" s="195" cm="1" t="str">
         <f t="array" ref="F85">IF(AG85="","",I85-H85)</f>
+        <v/>
       </c>
       <c r="G85" s="160"/>
       <c r="H85" s="158"/>
-      <c r="I85" t="str" s="159" cm="1">
+      <c r="I85" s="159" cm="1" t="str">
         <f t="array" ref="I85">IF(AG85="","",P85-K85)</f>
+        <v/>
       </c>
       <c r="J85" s="160"/>
       <c r="K85" s="158"/>
@@ -28953,8 +29241,9 @@
       <c r="M85" s="161"/>
       <c r="N85" s="161"/>
       <c r="O85" s="161"/>
-      <c r="P85" t="str" s="159" cm="1">
+      <c r="P85" s="159" cm="1" t="str">
         <f t="array" ref="P85">IF(AG85="","",AC85-R85-Q85)</f>
+        <v/>
       </c>
       <c r="Q85" s="162"/>
       <c r="R85" s="162"/>
@@ -28969,8 +29258,9 @@
       <c r="AA85" s="161"/>
       <c r="AB85" s="160"/>
       <c r="AC85" s="163"/>
-      <c r="AD85" t="str" s="159" cm="1">
+      <c r="AD85" s="159" cm="1" t="str">
         <f t="array" ref="AD85">IF(AG85="","",$AG85-$AF85)</f>
+        <v/>
       </c>
       <c r="AE85" s="160"/>
       <c r="AF85" s="196"/>
@@ -29016,13 +29306,15 @@
       <c r="C86" s="170"/>
       <c r="D86" s="165"/>
       <c r="E86" s="164"/>
-      <c r="F86" t="str" s="195" cm="1">
+      <c r="F86" s="195" cm="1" t="str">
         <f t="array" ref="F86">IF(AG86="","",I86-H86)</f>
+        <v/>
       </c>
       <c r="G86" s="160"/>
       <c r="H86" s="158"/>
-      <c r="I86" t="str" s="159" cm="1">
+      <c r="I86" s="159" cm="1" t="str">
         <f t="array" ref="I86">IF(AG86="","",P86-K86)</f>
+        <v/>
       </c>
       <c r="J86" s="160"/>
       <c r="K86" s="158"/>
@@ -29030,8 +29322,9 @@
       <c r="M86" s="161"/>
       <c r="N86" s="161"/>
       <c r="O86" s="161"/>
-      <c r="P86" t="str" s="159" cm="1">
+      <c r="P86" s="159" cm="1" t="str">
         <f t="array" ref="P86">IF(AG86="","",AC86-R86-Q86)</f>
+        <v/>
       </c>
       <c r="Q86" s="162"/>
       <c r="R86" s="162"/>
@@ -29046,8 +29339,9 @@
       <c r="AA86" s="161"/>
       <c r="AB86" s="160"/>
       <c r="AC86" s="163"/>
-      <c r="AD86" t="str" s="159" cm="1">
+      <c r="AD86" s="159" cm="1" t="str">
         <f t="array" ref="AD86">IF(AG86="","",$AG86-$AF86)</f>
+        <v/>
       </c>
       <c r="AE86" s="160"/>
       <c r="AF86" s="196"/>
@@ -29093,13 +29387,15 @@
       <c r="C87" s="170"/>
       <c r="D87" s="165"/>
       <c r="E87" s="164"/>
-      <c r="F87" t="str" s="195" cm="1">
+      <c r="F87" s="195" cm="1" t="str">
         <f t="array" ref="F87">IF(AG87="","",I87-H87)</f>
+        <v/>
       </c>
       <c r="G87" s="160"/>
       <c r="H87" s="158"/>
-      <c r="I87" t="str" s="159" cm="1">
+      <c r="I87" s="159" cm="1" t="str">
         <f t="array" ref="I87">IF(AG87="","",P87-K87)</f>
+        <v/>
       </c>
       <c r="J87" s="160"/>
       <c r="K87" s="158"/>
@@ -29107,8 +29403,9 @@
       <c r="M87" s="161"/>
       <c r="N87" s="161"/>
       <c r="O87" s="161"/>
-      <c r="P87" t="str" s="159" cm="1">
+      <c r="P87" s="159" cm="1" t="str">
         <f t="array" ref="P87">IF(AG87="","",AC87-R87-Q87)</f>
+        <v/>
       </c>
       <c r="Q87" s="162"/>
       <c r="R87" s="162"/>
@@ -29123,8 +29420,9 @@
       <c r="AA87" s="161"/>
       <c r="AB87" s="160"/>
       <c r="AC87" s="163"/>
-      <c r="AD87" t="str" s="159" cm="1">
+      <c r="AD87" s="159" cm="1" t="str">
         <f t="array" ref="AD87">IF(AG87="","",$AG87-$AF87)</f>
+        <v/>
       </c>
       <c r="AE87" s="160"/>
       <c r="AF87" s="196"/>
@@ -29170,13 +29468,15 @@
       <c r="C88" s="170"/>
       <c r="D88" s="165"/>
       <c r="E88" s="164"/>
-      <c r="F88" t="str" s="195" cm="1">
+      <c r="F88" s="195" cm="1" t="str">
         <f t="array" ref="F88">IF(AG88="","",I88-H88)</f>
+        <v/>
       </c>
       <c r="G88" s="160"/>
       <c r="H88" s="158"/>
-      <c r="I88" t="str" s="159" cm="1">
+      <c r="I88" s="159" cm="1" t="str">
         <f t="array" ref="I88">IF(AG88="","",P88-K88)</f>
+        <v/>
       </c>
       <c r="J88" s="160"/>
       <c r="K88" s="158"/>
@@ -29184,8 +29484,9 @@
       <c r="M88" s="161"/>
       <c r="N88" s="161"/>
       <c r="O88" s="161"/>
-      <c r="P88" t="str" s="159" cm="1">
+      <c r="P88" s="159" cm="1" t="str">
         <f t="array" ref="P88">IF(AG88="","",AC88-R88-Q88)</f>
+        <v/>
       </c>
       <c r="Q88" s="162"/>
       <c r="R88" s="162"/>
@@ -29200,8 +29501,9 @@
       <c r="AA88" s="161"/>
       <c r="AB88" s="160"/>
       <c r="AC88" s="163"/>
-      <c r="AD88" t="str" s="159" cm="1">
+      <c r="AD88" s="159" cm="1" t="str">
         <f t="array" ref="AD88">IF(AG88="","",$AG88-$AF88)</f>
+        <v/>
       </c>
       <c r="AE88" s="160"/>
       <c r="AF88" s="196"/>
@@ -29247,13 +29549,15 @@
       <c r="C89" s="170"/>
       <c r="D89" s="165"/>
       <c r="E89" s="164"/>
-      <c r="F89" t="str" s="195" cm="1">
+      <c r="F89" s="195" cm="1" t="str">
         <f t="array" ref="F89">IF(AG89="","",I89-H89)</f>
+        <v/>
       </c>
       <c r="G89" s="160"/>
       <c r="H89" s="158"/>
-      <c r="I89" t="str" s="159" cm="1">
+      <c r="I89" s="159" cm="1" t="str">
         <f t="array" ref="I89">IF(AG89="","",P89-K89)</f>
+        <v/>
       </c>
       <c r="J89" s="160"/>
       <c r="K89" s="158"/>
@@ -29261,8 +29565,9 @@
       <c r="M89" s="161"/>
       <c r="N89" s="161"/>
       <c r="O89" s="161"/>
-      <c r="P89" t="str" s="159" cm="1">
+      <c r="P89" s="159" cm="1" t="str">
         <f t="array" ref="P89">IF(AG89="","",AC89-R89-Q89)</f>
+        <v/>
       </c>
       <c r="Q89" s="162"/>
       <c r="R89" s="162"/>
@@ -29277,8 +29582,9 @@
       <c r="AA89" s="161"/>
       <c r="AB89" s="160"/>
       <c r="AC89" s="163"/>
-      <c r="AD89" t="str" s="159" cm="1">
+      <c r="AD89" s="159" cm="1" t="str">
         <f t="array" ref="AD89">IF(AG89="","",$AG89-$AF89)</f>
+        <v/>
       </c>
       <c r="AE89" s="160"/>
       <c r="AF89" s="196"/>
@@ -29324,13 +29630,15 @@
       <c r="C90" s="170"/>
       <c r="D90" s="165"/>
       <c r="E90" s="164"/>
-      <c r="F90" t="str" s="195" cm="1">
+      <c r="F90" s="195" cm="1" t="str">
         <f t="array" ref="F90">IF(AG90="","",I90-H90)</f>
+        <v/>
       </c>
       <c r="G90" s="160"/>
       <c r="H90" s="158"/>
-      <c r="I90" t="str" s="159" cm="1">
+      <c r="I90" s="159" cm="1" t="str">
         <f t="array" ref="I90">IF(AG90="","",P90-K90)</f>
+        <v/>
       </c>
       <c r="J90" s="160"/>
       <c r="K90" s="158"/>
@@ -29338,8 +29646,9 @@
       <c r="M90" s="161"/>
       <c r="N90" s="161"/>
       <c r="O90" s="161"/>
-      <c r="P90" t="str" s="159" cm="1">
+      <c r="P90" s="159" cm="1" t="str">
         <f t="array" ref="P90">IF(AG90="","",AC90-R90-Q90)</f>
+        <v/>
       </c>
       <c r="Q90" s="162"/>
       <c r="R90" s="162"/>
@@ -29354,8 +29663,9 @@
       <c r="AA90" s="161"/>
       <c r="AB90" s="160"/>
       <c r="AC90" s="163"/>
-      <c r="AD90" t="str" s="159" cm="1">
+      <c r="AD90" s="159" cm="1" t="str">
         <f t="array" ref="AD90">IF(AG90="","",$AG90-$AF90)</f>
+        <v/>
       </c>
       <c r="AE90" s="160"/>
       <c r="AF90" s="196"/>
@@ -29401,13 +29711,15 @@
       <c r="C91" s="170"/>
       <c r="D91" s="165"/>
       <c r="E91" s="164"/>
-      <c r="F91" t="str" s="195" cm="1">
+      <c r="F91" s="195" cm="1" t="str">
         <f t="array" ref="F91">IF(AG91="","",I91-H91)</f>
+        <v/>
       </c>
       <c r="G91" s="160"/>
       <c r="H91" s="158"/>
-      <c r="I91" t="str" s="159" cm="1">
+      <c r="I91" s="159" cm="1" t="str">
         <f t="array" ref="I91">IF(AG91="","",P91-K91)</f>
+        <v/>
       </c>
       <c r="J91" s="160"/>
       <c r="K91" s="158"/>
@@ -29415,8 +29727,9 @@
       <c r="M91" s="161"/>
       <c r="N91" s="161"/>
       <c r="O91" s="161"/>
-      <c r="P91" t="str" s="159" cm="1">
+      <c r="P91" s="159" cm="1" t="str">
         <f t="array" ref="P91">IF(AG91="","",AC91-R91-Q91)</f>
+        <v/>
       </c>
       <c r="Q91" s="162"/>
       <c r="R91" s="162"/>
@@ -29431,8 +29744,9 @@
       <c r="AA91" s="161"/>
       <c r="AB91" s="160"/>
       <c r="AC91" s="163"/>
-      <c r="AD91" t="str" s="159" cm="1">
+      <c r="AD91" s="159" cm="1" t="str">
         <f t="array" ref="AD91">IF(AG91="","",$AG91-$AF91)</f>
+        <v/>
       </c>
       <c r="AE91" s="160"/>
       <c r="AF91" s="196"/>
@@ -29478,13 +29792,15 @@
       <c r="C92" s="170"/>
       <c r="D92" s="165"/>
       <c r="E92" s="164"/>
-      <c r="F92" t="str" s="195" cm="1">
+      <c r="F92" s="195" cm="1" t="str">
         <f t="array" ref="F92">IF(AG92="","",I92-H92)</f>
+        <v/>
       </c>
       <c r="G92" s="160"/>
       <c r="H92" s="158"/>
-      <c r="I92" t="str" s="159" cm="1">
+      <c r="I92" s="159" cm="1" t="str">
         <f t="array" ref="I92">IF(AG92="","",P92-K92)</f>
+        <v/>
       </c>
       <c r="J92" s="160"/>
       <c r="K92" s="158"/>
@@ -29492,8 +29808,9 @@
       <c r="M92" s="161"/>
       <c r="N92" s="161"/>
       <c r="O92" s="161"/>
-      <c r="P92" t="str" s="159" cm="1">
+      <c r="P92" s="159" cm="1" t="str">
         <f t="array" ref="P92">IF(AG92="","",AC92-R92-Q92)</f>
+        <v/>
       </c>
       <c r="Q92" s="162"/>
       <c r="R92" s="162"/>
@@ -29508,8 +29825,9 @@
       <c r="AA92" s="161"/>
       <c r="AB92" s="160"/>
       <c r="AC92" s="163"/>
-      <c r="AD92" t="str" s="159" cm="1">
+      <c r="AD92" s="159" cm="1" t="str">
         <f t="array" ref="AD92">IF(AG92="","",$AG92-$AF92)</f>
+        <v/>
       </c>
       <c r="AE92" s="160"/>
       <c r="AF92" s="196"/>
@@ -29555,13 +29873,15 @@
       <c r="C93" s="170"/>
       <c r="D93" s="165"/>
       <c r="E93" s="164"/>
-      <c r="F93" t="str" s="195" cm="1">
+      <c r="F93" s="195" cm="1" t="str">
         <f t="array" ref="F93">IF(AG93="","",I93-H93)</f>
+        <v/>
       </c>
       <c r="G93" s="160"/>
       <c r="H93" s="158"/>
-      <c r="I93" t="str" s="159" cm="1">
+      <c r="I93" s="159" cm="1" t="str">
         <f t="array" ref="I93">IF(AG93="","",P93-K93)</f>
+        <v/>
       </c>
       <c r="J93" s="160"/>
       <c r="K93" s="158"/>
@@ -29569,8 +29889,9 @@
       <c r="M93" s="161"/>
       <c r="N93" s="161"/>
       <c r="O93" s="161"/>
-      <c r="P93" t="str" s="159" cm="1">
+      <c r="P93" s="159" cm="1" t="str">
         <f t="array" ref="P93">IF(AG93="","",AC93-R93-Q93)</f>
+        <v/>
       </c>
       <c r="Q93" s="162"/>
       <c r="R93" s="162"/>
@@ -29585,8 +29906,9 @@
       <c r="AA93" s="161"/>
       <c r="AB93" s="160"/>
       <c r="AC93" s="163"/>
-      <c r="AD93" t="str" s="159" cm="1">
+      <c r="AD93" s="159" cm="1" t="str">
         <f t="array" ref="AD93">IF(AG93="","",$AG93-$AF93)</f>
+        <v/>
       </c>
       <c r="AE93" s="160"/>
       <c r="AF93" s="196"/>
@@ -29632,13 +29954,15 @@
       <c r="C94" s="170"/>
       <c r="D94" s="165"/>
       <c r="E94" s="164"/>
-      <c r="F94" t="str" s="195" cm="1">
+      <c r="F94" s="195" cm="1" t="str">
         <f t="array" ref="F94">IF(AG94="","",I94-H94)</f>
+        <v/>
       </c>
       <c r="G94" s="160"/>
       <c r="H94" s="158"/>
-      <c r="I94" t="str" s="159" cm="1">
+      <c r="I94" s="159" cm="1" t="str">
         <f t="array" ref="I94">IF(AG94="","",P94-K94)</f>
+        <v/>
       </c>
       <c r="J94" s="160"/>
       <c r="K94" s="158"/>
@@ -29646,8 +29970,9 @@
       <c r="M94" s="161"/>
       <c r="N94" s="161"/>
       <c r="O94" s="161"/>
-      <c r="P94" t="str" s="159" cm="1">
+      <c r="P94" s="159" cm="1" t="str">
         <f t="array" ref="P94">IF(AG94="","",AC94-R94-Q94)</f>
+        <v/>
       </c>
       <c r="Q94" s="162"/>
       <c r="R94" s="162"/>
@@ -29662,8 +29987,9 @@
       <c r="AA94" s="161"/>
       <c r="AB94" s="160"/>
       <c r="AC94" s="163"/>
-      <c r="AD94" t="str" s="159" cm="1">
+      <c r="AD94" s="159" cm="1" t="str">
         <f t="array" ref="AD94">IF(AG94="","",$AG94-$AF94)</f>
+        <v/>
       </c>
       <c r="AE94" s="160"/>
       <c r="AF94" s="196"/>
@@ -29709,13 +30035,15 @@
       <c r="C95" s="170"/>
       <c r="D95" s="165"/>
       <c r="E95" s="164"/>
-      <c r="F95" t="str" s="195" cm="1">
+      <c r="F95" s="195" cm="1" t="str">
         <f t="array" ref="F95">IF(AG95="","",I95-H95)</f>
+        <v/>
       </c>
       <c r="G95" s="160"/>
       <c r="H95" s="158"/>
-      <c r="I95" t="str" s="159" cm="1">
+      <c r="I95" s="159" cm="1" t="str">
         <f t="array" ref="I95">IF(AG95="","",P95-K95)</f>
+        <v/>
       </c>
       <c r="J95" s="160"/>
       <c r="K95" s="158"/>
@@ -29723,8 +30051,9 @@
       <c r="M95" s="161"/>
       <c r="N95" s="161"/>
       <c r="O95" s="161"/>
-      <c r="P95" t="str" s="159" cm="1">
+      <c r="P95" s="159" cm="1" t="str">
         <f t="array" ref="P95">IF(AG95="","",AC95-R95-Q95)</f>
+        <v/>
       </c>
       <c r="Q95" s="162"/>
       <c r="R95" s="162"/>
@@ -29739,8 +30068,9 @@
       <c r="AA95" s="161"/>
       <c r="AB95" s="160"/>
       <c r="AC95" s="163"/>
-      <c r="AD95" t="str" s="159" cm="1">
+      <c r="AD95" s="159" cm="1" t="str">
         <f t="array" ref="AD95">IF(AG95="","",$AG95-$AF95)</f>
+        <v/>
       </c>
       <c r="AE95" s="160"/>
       <c r="AF95" s="196"/>
@@ -29786,13 +30116,15 @@
       <c r="C96" s="170"/>
       <c r="D96" s="165"/>
       <c r="E96" s="164"/>
-      <c r="F96" t="str" s="195" cm="1">
+      <c r="F96" s="195" cm="1" t="str">
         <f t="array" ref="F96">IF(AG96="","",I96-H96)</f>
+        <v/>
       </c>
       <c r="G96" s="160"/>
       <c r="H96" s="158"/>
-      <c r="I96" t="str" s="159" cm="1">
+      <c r="I96" s="159" cm="1" t="str">
         <f t="array" ref="I96">IF(AG96="","",P96-K96)</f>
+        <v/>
       </c>
       <c r="J96" s="160"/>
       <c r="K96" s="158"/>
@@ -29800,8 +30132,9 @@
       <c r="M96" s="161"/>
       <c r="N96" s="161"/>
       <c r="O96" s="161"/>
-      <c r="P96" t="str" s="159" cm="1">
+      <c r="P96" s="159" cm="1" t="str">
         <f t="array" ref="P96">IF(AG96="","",AC96-R96-Q96)</f>
+        <v/>
       </c>
       <c r="Q96" s="162"/>
       <c r="R96" s="162"/>
@@ -29816,8 +30149,9 @@
       <c r="AA96" s="161"/>
       <c r="AB96" s="160"/>
       <c r="AC96" s="163"/>
-      <c r="AD96" t="str" s="159" cm="1">
+      <c r="AD96" s="159" cm="1" t="str">
         <f t="array" ref="AD96">IF(AG96="","",$AG96-$AF96)</f>
+        <v/>
       </c>
       <c r="AE96" s="160"/>
       <c r="AF96" s="196"/>
@@ -29863,13 +30197,15 @@
       <c r="C97" s="170"/>
       <c r="D97" s="165"/>
       <c r="E97" s="164"/>
-      <c r="F97" t="str" s="195" cm="1">
+      <c r="F97" s="195" cm="1" t="str">
         <f t="array" ref="F97">IF(AG97="","",I97-H97)</f>
+        <v/>
       </c>
       <c r="G97" s="160"/>
       <c r="H97" s="158"/>
-      <c r="I97" t="str" s="159" cm="1">
+      <c r="I97" s="159" cm="1" t="str">
         <f t="array" ref="I97">IF(AG97="","",P97-K97)</f>
+        <v/>
       </c>
       <c r="J97" s="160"/>
       <c r="K97" s="158"/>
@@ -29877,8 +30213,9 @@
       <c r="M97" s="161"/>
       <c r="N97" s="161"/>
       <c r="O97" s="161"/>
-      <c r="P97" t="str" s="159" cm="1">
+      <c r="P97" s="159" cm="1" t="str">
         <f t="array" ref="P97">IF(AG97="","",AC97-R97-Q97)</f>
+        <v/>
       </c>
       <c r="Q97" s="162"/>
       <c r="R97" s="162"/>
@@ -29893,8 +30230,9 @@
       <c r="AA97" s="161"/>
       <c r="AB97" s="160"/>
       <c r="AC97" s="163"/>
-      <c r="AD97" t="str" s="159" cm="1">
+      <c r="AD97" s="159" cm="1" t="str">
         <f t="array" ref="AD97">IF(AG97="","",$AG97-$AF97)</f>
+        <v/>
       </c>
       <c r="AE97" s="160"/>
       <c r="AF97" s="196"/>
@@ -29940,13 +30278,15 @@
       <c r="C98" s="170"/>
       <c r="D98" s="165"/>
       <c r="E98" s="164"/>
-      <c r="F98" t="str" s="195" cm="1">
+      <c r="F98" s="195" cm="1" t="str">
         <f t="array" ref="F98">IF(AG98="","",I98-H98)</f>
+        <v/>
       </c>
       <c r="G98" s="160"/>
       <c r="H98" s="158"/>
-      <c r="I98" t="str" s="159" cm="1">
+      <c r="I98" s="159" cm="1" t="str">
         <f t="array" ref="I98">IF(AG98="","",P98-K98)</f>
+        <v/>
       </c>
       <c r="J98" s="160"/>
       <c r="K98" s="158"/>
@@ -29954,8 +30294,9 @@
       <c r="M98" s="161"/>
       <c r="N98" s="161"/>
       <c r="O98" s="161"/>
-      <c r="P98" t="str" s="159" cm="1">
+      <c r="P98" s="159" cm="1" t="str">
         <f t="array" ref="P98">IF(AG98="","",AC98-R98-Q98)</f>
+        <v/>
       </c>
       <c r="Q98" s="162"/>
       <c r="R98" s="162"/>
@@ -29970,8 +30311,9 @@
       <c r="AA98" s="161"/>
       <c r="AB98" s="160"/>
       <c r="AC98" s="163"/>
-      <c r="AD98" t="str" s="159" cm="1">
+      <c r="AD98" s="159" cm="1" t="str">
         <f t="array" ref="AD98">IF(AG98="","",$AG98-$AF98)</f>
+        <v/>
       </c>
       <c r="AE98" s="160"/>
       <c r="AF98" s="196"/>
@@ -30017,13 +30359,15 @@
       <c r="C99" s="170"/>
       <c r="D99" s="165"/>
       <c r="E99" s="164"/>
-      <c r="F99" t="str" s="195" cm="1">
+      <c r="F99" s="195" cm="1" t="str">
         <f t="array" ref="F99">IF(AG99="","",I99-H99)</f>
+        <v/>
       </c>
       <c r="G99" s="160"/>
       <c r="H99" s="158"/>
-      <c r="I99" t="str" s="159" cm="1">
+      <c r="I99" s="159" cm="1" t="str">
         <f t="array" ref="I99">IF(AG99="","",P99-K99)</f>
+        <v/>
       </c>
       <c r="J99" s="160"/>
       <c r="K99" s="158"/>
@@ -30031,8 +30375,9 @@
       <c r="M99" s="161"/>
       <c r="N99" s="161"/>
       <c r="O99" s="161"/>
-      <c r="P99" t="str" s="159" cm="1">
+      <c r="P99" s="159" cm="1" t="str">
         <f t="array" ref="P99">IF(AG99="","",AC99-R99-Q99)</f>
+        <v/>
       </c>
       <c r="Q99" s="162"/>
       <c r="R99" s="162"/>
@@ -30047,8 +30392,9 @@
       <c r="AA99" s="161"/>
       <c r="AB99" s="160"/>
       <c r="AC99" s="163"/>
-      <c r="AD99" t="str" s="159" cm="1">
+      <c r="AD99" s="159" cm="1" t="str">
         <f t="array" ref="AD99">IF(AG99="","",$AG99-$AF99)</f>
+        <v/>
       </c>
       <c r="AE99" s="160"/>
       <c r="AF99" s="196"/>
@@ -30094,13 +30440,15 @@
       <c r="C100" s="170"/>
       <c r="D100" s="165"/>
       <c r="E100" s="164"/>
-      <c r="F100" t="str" s="195" cm="1">
+      <c r="F100" s="195" cm="1" t="str">
         <f t="array" ref="F100">IF(AG100="","",I100-H100)</f>
+        <v/>
       </c>
       <c r="G100" s="160"/>
       <c r="H100" s="158"/>
-      <c r="I100" t="str" s="159" cm="1">
+      <c r="I100" s="159" cm="1" t="str">
         <f t="array" ref="I100">IF(AG100="","",P100-K100)</f>
+        <v/>
       </c>
       <c r="J100" s="160"/>
       <c r="K100" s="158"/>
@@ -30108,8 +30456,9 @@
       <c r="M100" s="161"/>
       <c r="N100" s="161"/>
       <c r="O100" s="161"/>
-      <c r="P100" t="str" s="159" cm="1">
+      <c r="P100" s="159" cm="1" t="str">
         <f t="array" ref="P100">IF(AG100="","",AC100-R100-Q100)</f>
+        <v/>
       </c>
       <c r="Q100" s="162"/>
       <c r="R100" s="162"/>
@@ -30124,8 +30473,9 @@
       <c r="AA100" s="161"/>
       <c r="AB100" s="160"/>
       <c r="AC100" s="163"/>
-      <c r="AD100" t="str" s="159" cm="1">
+      <c r="AD100" s="159" cm="1" t="str">
         <f t="array" ref="AD100">IF(AG100="","",$AG100-$AF100)</f>
+        <v/>
       </c>
       <c r="AE100" s="160"/>
       <c r="AF100" s="196"/>
@@ -30171,13 +30521,15 @@
       <c r="C101" s="170"/>
       <c r="D101" s="165"/>
       <c r="E101" s="164"/>
-      <c r="F101" t="str" s="195" cm="1">
+      <c r="F101" s="195" cm="1" t="str">
         <f t="array" ref="F101">IF(AG101="","",I101-H101)</f>
+        <v/>
       </c>
       <c r="G101" s="160"/>
       <c r="H101" s="158"/>
-      <c r="I101" t="str" s="159" cm="1">
+      <c r="I101" s="159" cm="1" t="str">
         <f t="array" ref="I101">IF(AG101="","",P101-K101)</f>
+        <v/>
       </c>
       <c r="J101" s="160"/>
       <c r="K101" s="158"/>
@@ -30185,8 +30537,9 @@
       <c r="M101" s="161"/>
       <c r="N101" s="161"/>
       <c r="O101" s="161"/>
-      <c r="P101" t="str" s="159" cm="1">
+      <c r="P101" s="159" cm="1" t="str">
         <f t="array" ref="P101">IF(AG101="","",AC101-R101-Q101)</f>
+        <v/>
       </c>
       <c r="Q101" s="162"/>
       <c r="R101" s="162"/>
@@ -30201,8 +30554,9 @@
       <c r="AA101" s="161"/>
       <c r="AB101" s="160"/>
       <c r="AC101" s="163"/>
-      <c r="AD101" t="str" s="159" cm="1">
+      <c r="AD101" s="159" cm="1" t="str">
         <f t="array" ref="AD101">IF(AG101="","",$AG101-$AF101)</f>
+        <v/>
       </c>
       <c r="AE101" s="160"/>
       <c r="AF101" s="196"/>
@@ -30248,13 +30602,15 @@
       <c r="C102" s="170"/>
       <c r="D102" s="165"/>
       <c r="E102" s="164"/>
-      <c r="F102" t="str" s="195" cm="1">
+      <c r="F102" s="195" cm="1" t="str">
         <f t="array" ref="F102">IF(AG102="","",I102-H102)</f>
+        <v/>
       </c>
       <c r="G102" s="160"/>
       <c r="H102" s="158"/>
-      <c r="I102" t="str" s="159" cm="1">
+      <c r="I102" s="159" cm="1" t="str">
         <f t="array" ref="I102">IF(AG102="","",P102-K102)</f>
+        <v/>
       </c>
       <c r="J102" s="160"/>
       <c r="K102" s="158"/>
@@ -30262,8 +30618,9 @@
       <c r="M102" s="161"/>
       <c r="N102" s="161"/>
       <c r="O102" s="161"/>
-      <c r="P102" t="str" s="159" cm="1">
+      <c r="P102" s="159" cm="1" t="str">
         <f t="array" ref="P102">IF(AG102="","",AC102-R102-Q102)</f>
+        <v/>
       </c>
       <c r="Q102" s="162"/>
       <c r="R102" s="162"/>
@@ -30278,8 +30635,9 @@
       <c r="AA102" s="161"/>
       <c r="AB102" s="160"/>
       <c r="AC102" s="163"/>
-      <c r="AD102" t="str" s="159" cm="1">
+      <c r="AD102" s="159" cm="1" t="str">
         <f t="array" ref="AD102">IF(AG102="","",$AG102-$AF102)</f>
+        <v/>
       </c>
       <c r="AE102" s="160"/>
       <c r="AF102" s="196"/>
@@ -30325,13 +30683,15 @@
       <c r="C103" s="170"/>
       <c r="D103" s="165"/>
       <c r="E103" s="164"/>
-      <c r="F103" t="str" s="195" cm="1">
+      <c r="F103" s="195" cm="1" t="str">
         <f t="array" ref="F103">IF(AG103="","",I103-H103)</f>
+        <v/>
       </c>
       <c r="G103" s="160"/>
       <c r="H103" s="158"/>
-      <c r="I103" t="str" s="159" cm="1">
+      <c r="I103" s="159" cm="1" t="str">
         <f t="array" ref="I103">IF(AG103="","",P103-K103)</f>
+        <v/>
       </c>
       <c r="J103" s="160"/>
       <c r="K103" s="158"/>
@@ -30339,8 +30699,9 @@
       <c r="M103" s="161"/>
       <c r="N103" s="161"/>
       <c r="O103" s="161"/>
-      <c r="P103" t="str" s="159" cm="1">
+      <c r="P103" s="159" cm="1" t="str">
         <f t="array" ref="P103">IF(AG103="","",AC103-R103-Q103)</f>
+        <v/>
       </c>
       <c r="Q103" s="162"/>
       <c r="R103" s="162"/>
@@ -30355,8 +30716,9 @@
       <c r="AA103" s="161"/>
       <c r="AB103" s="160"/>
       <c r="AC103" s="163"/>
-      <c r="AD103" t="str" s="159" cm="1">
+      <c r="AD103" s="159" cm="1" t="str">
         <f t="array" ref="AD103">IF(AG103="","",$AG103-$AF103)</f>
+        <v/>
       </c>
       <c r="AE103" s="160"/>
       <c r="AF103" s="196"/>
@@ -30402,13 +30764,15 @@
       <c r="C104" s="170"/>
       <c r="D104" s="165"/>
       <c r="E104" s="164"/>
-      <c r="F104" t="str" s="195" cm="1">
+      <c r="F104" s="195" cm="1" t="str">
         <f t="array" ref="F104">IF(AG104="","",I104-H104)</f>
+        <v/>
       </c>
       <c r="G104" s="160"/>
       <c r="H104" s="158"/>
-      <c r="I104" t="str" s="159" cm="1">
+      <c r="I104" s="159" cm="1" t="str">
         <f t="array" ref="I104">IF(AG104="","",P104-K104)</f>
+        <v/>
       </c>
       <c r="J104" s="160"/>
       <c r="K104" s="158"/>
@@ -30416,8 +30780,9 @@
       <c r="M104" s="161"/>
       <c r="N104" s="161"/>
       <c r="O104" s="161"/>
-      <c r="P104" t="str" s="159" cm="1">
+      <c r="P104" s="159" cm="1" t="str">
         <f t="array" ref="P104">IF(AG104="","",AC104-R104-Q104)</f>
+        <v/>
       </c>
       <c r="Q104" s="162"/>
       <c r="R104" s="162"/>
@@ -30432,8 +30797,9 @@
       <c r="AA104" s="161"/>
       <c r="AB104" s="160"/>
       <c r="AC104" s="163"/>
-      <c r="AD104" t="str" s="159" cm="1">
+      <c r="AD104" s="159" cm="1" t="str">
         <f t="array" ref="AD104">IF(AG104="","",$AG104-$AF104)</f>
+        <v/>
       </c>
       <c r="AE104" s="160"/>
       <c r="AF104" s="196"/>
@@ -30479,13 +30845,15 @@
       <c r="C105" s="170"/>
       <c r="D105" s="165"/>
       <c r="E105" s="164"/>
-      <c r="F105" t="str" s="195" cm="1">
+      <c r="F105" s="195" cm="1" t="str">
         <f t="array" ref="F105">IF(AG105="","",I105-H105)</f>
+        <v/>
       </c>
       <c r="G105" s="160"/>
       <c r="H105" s="158"/>
-      <c r="I105" t="str" s="159" cm="1">
+      <c r="I105" s="159" cm="1" t="str">
         <f t="array" ref="I105">IF(AG105="","",P105-K105)</f>
+        <v/>
       </c>
       <c r="J105" s="160"/>
       <c r="K105" s="158"/>
@@ -30493,8 +30861,9 @@
       <c r="M105" s="161"/>
       <c r="N105" s="161"/>
       <c r="O105" s="161"/>
-      <c r="P105" t="str" s="159" cm="1">
+      <c r="P105" s="159" cm="1" t="str">
         <f t="array" ref="P105">IF(AG105="","",AC105-R105-Q105)</f>
+        <v/>
       </c>
       <c r="Q105" s="162"/>
       <c r="R105" s="162"/>
@@ -30509,8 +30878,9 @@
       <c r="AA105" s="161"/>
       <c r="AB105" s="160"/>
       <c r="AC105" s="163"/>
-      <c r="AD105" t="str" s="159" cm="1">
+      <c r="AD105" s="159" cm="1" t="str">
         <f t="array" ref="AD105">IF(AG105="","",$AG105-$AF105)</f>
+        <v/>
       </c>
       <c r="AE105" s="160"/>
       <c r="AF105" s="196"/>
@@ -30556,13 +30926,15 @@
       <c r="C106" s="170"/>
       <c r="D106" s="165"/>
       <c r="E106" s="164"/>
-      <c r="F106" t="str" s="195" cm="1">
+      <c r="F106" s="195" cm="1" t="str">
         <f t="array" ref="F106">IF(AG106="","",I106-H106)</f>
+        <v/>
       </c>
       <c r="G106" s="160"/>
       <c r="H106" s="158"/>
-      <c r="I106" t="str" s="159" cm="1">
+      <c r="I106" s="159" cm="1" t="str">
         <f t="array" ref="I106">IF(AG106="","",P106-K106)</f>
+        <v/>
       </c>
       <c r="J106" s="160"/>
       <c r="K106" s="158"/>
@@ -30570,8 +30942,9 @@
       <c r="M106" s="161"/>
       <c r="N106" s="161"/>
       <c r="O106" s="161"/>
-      <c r="P106" t="str" s="159" cm="1">
+      <c r="P106" s="159" cm="1" t="str">
         <f t="array" ref="P106">IF(AG106="","",AC106-R106-Q106)</f>
+        <v/>
       </c>
       <c r="Q106" s="162"/>
       <c r="R106" s="162"/>
@@ -30631,13 +31004,15 @@
       <c r="C107" s="170"/>
       <c r="D107" s="165"/>
       <c r="E107" s="164"/>
-      <c r="F107" t="str" s="195" cm="1">
+      <c r="F107" s="195" cm="1" t="str">
         <f t="array" ref="F107">IF(AG107="","",I107-H107)</f>
+        <v/>
       </c>
       <c r="G107" s="160"/>
       <c r="H107" s="158"/>
-      <c r="I107" t="str" s="159" cm="1">
+      <c r="I107" s="159" cm="1" t="str">
         <f t="array" ref="I107">IF(AG107="","",P107-K107)</f>
+        <v/>
       </c>
       <c r="J107" s="160"/>
       <c r="K107" s="158"/>
@@ -30645,8 +31020,9 @@
       <c r="M107" s="161"/>
       <c r="N107" s="161"/>
       <c r="O107" s="161"/>
-      <c r="P107" t="str" s="159" cm="1">
+      <c r="P107" s="159" cm="1" t="str">
         <f t="array" ref="P107">IF(AG107="","",AC107-R107-Q107)</f>
+        <v/>
       </c>
       <c r="Q107" s="162"/>
       <c r="R107" s="162"/>
@@ -30706,13 +31082,15 @@
       <c r="C108" s="170"/>
       <c r="D108" s="165"/>
       <c r="E108" s="164"/>
-      <c r="F108" t="str" s="195" cm="1">
+      <c r="F108" s="195" cm="1" t="str">
         <f t="array" ref="F108">IF(AG108="","",I108-H108)</f>
+        <v/>
       </c>
       <c r="G108" s="160"/>
       <c r="H108" s="158"/>
-      <c r="I108" t="str" s="159" cm="1">
+      <c r="I108" s="159" cm="1" t="str">
         <f t="array" ref="I108">IF(AG108="","",P108-K108)</f>
+        <v/>
       </c>
       <c r="J108" s="160"/>
       <c r="K108" s="158"/>
@@ -30720,8 +31098,9 @@
       <c r="M108" s="161"/>
       <c r="N108" s="161"/>
       <c r="O108" s="161"/>
-      <c r="P108" t="str" s="159" cm="1">
+      <c r="P108" s="159" cm="1" t="str">
         <f t="array" ref="P108">IF(AG108="","",AC108-R108-Q108)</f>
+        <v/>
       </c>
       <c r="Q108" s="162"/>
       <c r="R108" s="162"/>
@@ -30781,13 +31160,15 @@
       <c r="C109" s="170"/>
       <c r="D109" s="165"/>
       <c r="E109" s="164"/>
-      <c r="F109" t="str" s="195" cm="1">
+      <c r="F109" s="195" cm="1" t="str">
         <f t="array" ref="F109">IF(AG109="","",I109-H109)</f>
+        <v/>
       </c>
       <c r="G109" s="160"/>
       <c r="H109" s="158"/>
-      <c r="I109" t="str" s="159" cm="1">
+      <c r="I109" s="159" cm="1" t="str">
         <f t="array" ref="I109">IF(AG109="","",P109-K109)</f>
+        <v/>
       </c>
       <c r="J109" s="160"/>
       <c r="K109" s="158"/>
@@ -30795,8 +31176,9 @@
       <c r="M109" s="161"/>
       <c r="N109" s="161"/>
       <c r="O109" s="161"/>
-      <c r="P109" t="str" s="159" cm="1">
+      <c r="P109" s="159" cm="1" t="str">
         <f t="array" ref="P109">IF(AG109="","",AC109-R109-Q109)</f>
+        <v/>
       </c>
       <c r="Q109" s="162"/>
       <c r="R109" s="162"/>
@@ -30856,13 +31238,15 @@
       <c r="C110" s="170"/>
       <c r="D110" s="165"/>
       <c r="E110" s="164"/>
-      <c r="F110" t="str" s="195" cm="1">
+      <c r="F110" s="195" cm="1" t="str">
         <f t="array" ref="F110">IF(AG110="","",I110-H110)</f>
+        <v/>
       </c>
       <c r="G110" s="160"/>
       <c r="H110" s="158"/>
-      <c r="I110" t="str" s="159" cm="1">
+      <c r="I110" s="159" cm="1" t="str">
         <f t="array" ref="I110">IF(AG110="","",P110-K110)</f>
+        <v/>
       </c>
       <c r="J110" s="160"/>
       <c r="K110" s="158"/>
@@ -30870,8 +31254,9 @@
       <c r="M110" s="161"/>
       <c r="N110" s="161"/>
       <c r="O110" s="161"/>
-      <c r="P110" t="str" s="159" cm="1">
+      <c r="P110" s="159" cm="1" t="str">
         <f t="array" ref="P110">IF(AG110="","",AC110-R110-Q110)</f>
+        <v/>
       </c>
       <c r="Q110" s="162"/>
       <c r="R110" s="162"/>
@@ -30931,13 +31316,15 @@
       <c r="C111" s="170"/>
       <c r="D111" s="165"/>
       <c r="E111" s="164"/>
-      <c r="F111" t="str" s="195" cm="1">
+      <c r="F111" s="195" cm="1" t="str">
         <f t="array" ref="F111">IF(AG111="","",I111-H111)</f>
+        <v/>
       </c>
       <c r="G111" s="160"/>
       <c r="H111" s="158"/>
-      <c r="I111" t="str" s="159" cm="1">
+      <c r="I111" s="159" cm="1" t="str">
         <f t="array" ref="I111">IF(AG111="","",P111-K111)</f>
+        <v/>
       </c>
       <c r="J111" s="160"/>
       <c r="K111" s="158"/>
@@ -30945,8 +31332,9 @@
       <c r="M111" s="161"/>
       <c r="N111" s="161"/>
       <c r="O111" s="161"/>
-      <c r="P111" t="str" s="159" cm="1">
+      <c r="P111" s="159" cm="1" t="str">
         <f t="array" ref="P111">IF(AG111="","",AC111-R111-Q111)</f>
+        <v/>
       </c>
       <c r="Q111" s="162"/>
       <c r="R111" s="162"/>
@@ -31006,13 +31394,15 @@
       <c r="C112" s="170"/>
       <c r="D112" s="165"/>
       <c r="E112" s="164"/>
-      <c r="F112" t="str" s="195" cm="1">
+      <c r="F112" s="195" cm="1" t="str">
         <f t="array" ref="F112">IF(AG112="","",I112-H112)</f>
+        <v/>
       </c>
       <c r="G112" s="160"/>
       <c r="H112" s="158"/>
-      <c r="I112" t="str" s="159" cm="1">
+      <c r="I112" s="159" cm="1" t="str">
         <f t="array" ref="I112">IF(AG112="","",P112-K112)</f>
+        <v/>
       </c>
       <c r="J112" s="160"/>
       <c r="K112" s="158"/>
@@ -31020,8 +31410,9 @@
       <c r="M112" s="161"/>
       <c r="N112" s="161"/>
       <c r="O112" s="161"/>
-      <c r="P112" t="str" s="159" cm="1">
+      <c r="P112" s="159" cm="1" t="str">
         <f t="array" ref="P112">IF(AG112="","",AC112-R112-Q112)</f>
+        <v/>
       </c>
       <c r="Q112" s="162"/>
       <c r="R112" s="162"/>
@@ -31081,13 +31472,15 @@
       <c r="C113" s="170"/>
       <c r="D113" s="165"/>
       <c r="E113" s="164"/>
-      <c r="F113" t="str" s="195" cm="1">
+      <c r="F113" s="195" cm="1" t="str">
         <f t="array" ref="F113">IF(AG113="","",I113-H113)</f>
+        <v/>
       </c>
       <c r="G113" s="160"/>
       <c r="H113" s="158"/>
-      <c r="I113" t="str" s="159" cm="1">
+      <c r="I113" s="159" cm="1" t="str">
         <f t="array" ref="I113">IF(AG113="","",P113-K113)</f>
+        <v/>
       </c>
       <c r="J113" s="160"/>
       <c r="K113" s="158"/>
@@ -31095,8 +31488,9 @@
       <c r="M113" s="161"/>
       <c r="N113" s="161"/>
       <c r="O113" s="161"/>
-      <c r="P113" t="str" s="159" cm="1">
+      <c r="P113" s="159" cm="1" t="str">
         <f t="array" ref="P113">IF(AG113="","",AC113-R113-Q113)</f>
+        <v/>
       </c>
       <c r="Q113" s="162"/>
       <c r="R113" s="162"/>
@@ -31156,13 +31550,15 @@
       <c r="C114" s="170"/>
       <c r="D114" s="165"/>
       <c r="E114" s="164"/>
-      <c r="F114" t="str" s="195" cm="1">
+      <c r="F114" s="195" cm="1" t="str">
         <f t="array" ref="F114">IF(AG114="","",I114-H114)</f>
+        <v/>
       </c>
       <c r="G114" s="160"/>
       <c r="H114" s="158"/>
-      <c r="I114" t="str" s="159" cm="1">
+      <c r="I114" s="159" cm="1" t="str">
         <f t="array" ref="I114">IF(AG114="","",P114-K114)</f>
+        <v/>
       </c>
       <c r="J114" s="160"/>
       <c r="K114" s="158"/>
@@ -31170,8 +31566,9 @@
       <c r="M114" s="161"/>
       <c r="N114" s="161"/>
       <c r="O114" s="161"/>
-      <c r="P114" t="str" s="159" cm="1">
+      <c r="P114" s="159" cm="1" t="str">
         <f t="array" ref="P114">IF(AG114="","",AC114-R114-Q114)</f>
+        <v/>
       </c>
       <c r="Q114" s="162"/>
       <c r="R114" s="162"/>
@@ -31231,13 +31628,15 @@
       <c r="C115" s="170"/>
       <c r="D115" s="165"/>
       <c r="E115" s="164"/>
-      <c r="F115" t="str" s="195" cm="1">
+      <c r="F115" s="195" cm="1" t="str">
         <f t="array" ref="F115">IF(AG115="","",I115-H115)</f>
+        <v/>
       </c>
       <c r="G115" s="160"/>
       <c r="H115" s="158"/>
-      <c r="I115" t="str" s="159" cm="1">
+      <c r="I115" s="159" cm="1" t="str">
         <f t="array" ref="I115">IF(AG115="","",P115-K115)</f>
+        <v/>
       </c>
       <c r="J115" s="160"/>
       <c r="K115" s="158"/>
@@ -31245,8 +31644,9 @@
       <c r="M115" s="161"/>
       <c r="N115" s="161"/>
       <c r="O115" s="161"/>
-      <c r="P115" t="str" s="159" cm="1">
+      <c r="P115" s="159" cm="1" t="str">
         <f t="array" ref="P115">IF(AG115="","",AC115-R115-Q115)</f>
+        <v/>
       </c>
       <c r="Q115" s="162"/>
       <c r="R115" s="162"/>
@@ -31306,13 +31706,15 @@
       <c r="C116" s="170"/>
       <c r="D116" s="165"/>
       <c r="E116" s="164"/>
-      <c r="F116" t="str" s="195" cm="1">
+      <c r="F116" s="195" cm="1" t="str">
         <f t="array" ref="F116">IF(AG116="","",I116-H116)</f>
+        <v/>
       </c>
       <c r="G116" s="160"/>
       <c r="H116" s="158"/>
-      <c r="I116" t="str" s="159" cm="1">
+      <c r="I116" s="159" cm="1" t="str">
         <f t="array" ref="I116">IF(AG116="","",P116-K116)</f>
+        <v/>
       </c>
       <c r="J116" s="160"/>
       <c r="K116" s="158"/>
@@ -31320,8 +31722,9 @@
       <c r="M116" s="161"/>
       <c r="N116" s="161"/>
       <c r="O116" s="161"/>
-      <c r="P116" t="str" s="159" cm="1">
+      <c r="P116" s="159" cm="1" t="str">
         <f t="array" ref="P116">IF(AG116="","",AC116-R116-Q116)</f>
+        <v/>
       </c>
       <c r="Q116" s="162"/>
       <c r="R116" s="162"/>
@@ -31381,13 +31784,15 @@
       <c r="C117" s="170"/>
       <c r="D117" s="165"/>
       <c r="E117" s="164"/>
-      <c r="F117" t="str" s="195" cm="1">
+      <c r="F117" s="195" cm="1" t="str">
         <f t="array" ref="F117">IF(AG117="","",I117-H117)</f>
+        <v/>
       </c>
       <c r="G117" s="160"/>
       <c r="H117" s="158"/>
-      <c r="I117" t="str" s="159" cm="1">
+      <c r="I117" s="159" cm="1" t="str">
         <f t="array" ref="I117">IF(AG117="","",P117-K117)</f>
+        <v/>
       </c>
       <c r="J117" s="160"/>
       <c r="K117" s="158"/>
@@ -31395,8 +31800,9 @@
       <c r="M117" s="161"/>
       <c r="N117" s="161"/>
       <c r="O117" s="161"/>
-      <c r="P117" t="str" s="159" cm="1">
+      <c r="P117" s="159" cm="1" t="str">
         <f t="array" ref="P117">IF(AG117="","",AC117-R117-Q117)</f>
+        <v/>
       </c>
       <c r="Q117" s="162"/>
       <c r="R117" s="162"/>
@@ -31456,13 +31862,15 @@
       <c r="C118" s="170"/>
       <c r="D118" s="165"/>
       <c r="E118" s="164"/>
-      <c r="F118" t="str" s="195" cm="1">
+      <c r="F118" s="195" cm="1" t="str">
         <f t="array" ref="F118">IF(AG118="","",I118-H118)</f>
+        <v/>
       </c>
       <c r="G118" s="160"/>
       <c r="H118" s="158"/>
-      <c r="I118" t="str" s="159" cm="1">
+      <c r="I118" s="159" cm="1" t="str">
         <f t="array" ref="I118">IF(AG118="","",P118-K118)</f>
+        <v/>
       </c>
       <c r="J118" s="160"/>
       <c r="K118" s="158"/>
@@ -31470,8 +31878,9 @@
       <c r="M118" s="161"/>
       <c r="N118" s="161"/>
       <c r="O118" s="161"/>
-      <c r="P118" t="str" s="159" cm="1">
+      <c r="P118" s="159" cm="1" t="str">
         <f t="array" ref="P118">IF(AG118="","",AC118-R118-Q118)</f>
+        <v/>
       </c>
       <c r="Q118" s="162"/>
       <c r="R118" s="162"/>
@@ -31531,13 +31940,15 @@
       <c r="C119" s="170"/>
       <c r="D119" s="165"/>
       <c r="E119" s="164"/>
-      <c r="F119" t="str" s="195" cm="1">
+      <c r="F119" s="195" cm="1" t="str">
         <f t="array" ref="F119">IF(AG119="","",I119-H119)</f>
+        <v/>
       </c>
       <c r="G119" s="160"/>
       <c r="H119" s="158"/>
-      <c r="I119" t="str" s="159" cm="1">
+      <c r="I119" s="159" cm="1" t="str">
         <f t="array" ref="I119">IF(AG119="","",P119-K119)</f>
+        <v/>
       </c>
       <c r="J119" s="160"/>
       <c r="K119" s="158"/>
@@ -31545,8 +31956,9 @@
       <c r="M119" s="161"/>
       <c r="N119" s="161"/>
       <c r="O119" s="161"/>
-      <c r="P119" t="str" s="159" cm="1">
+      <c r="P119" s="159" cm="1" t="str">
         <f t="array" ref="P119">IF(AG119="","",AC119-R119-Q119)</f>
+        <v/>
       </c>
       <c r="Q119" s="162"/>
       <c r="R119" s="162"/>
@@ -31606,13 +32018,15 @@
       <c r="C120" s="170"/>
       <c r="D120" s="165"/>
       <c r="E120" s="164"/>
-      <c r="F120" t="str" s="195" cm="1">
+      <c r="F120" s="195" cm="1" t="str">
         <f t="array" ref="F120">IF(AG120="","",I120-H120)</f>
+        <v/>
       </c>
       <c r="G120" s="160"/>
       <c r="H120" s="158"/>
-      <c r="I120" t="str" s="159" cm="1">
+      <c r="I120" s="159" cm="1" t="str">
         <f t="array" ref="I120">IF(AG120="","",P120-K120)</f>
+        <v/>
       </c>
       <c r="J120" s="160"/>
       <c r="K120" s="158"/>
@@ -31620,8 +32034,9 @@
       <c r="M120" s="161"/>
       <c r="N120" s="161"/>
       <c r="O120" s="161"/>
-      <c r="P120" t="str" s="159" cm="1">
+      <c r="P120" s="159" cm="1" t="str">
         <f t="array" ref="P120">IF(AG120="","",AC120-R120-Q120)</f>
+        <v/>
       </c>
       <c r="Q120" s="162"/>
       <c r="R120" s="162"/>
@@ -31681,13 +32096,15 @@
       <c r="C121" s="170"/>
       <c r="D121" s="165"/>
       <c r="E121" s="164"/>
-      <c r="F121" t="str" s="195" cm="1">
+      <c r="F121" s="195" cm="1" t="str">
         <f t="array" ref="F121">IF(AG121="","",I121-H121)</f>
+        <v/>
       </c>
       <c r="G121" s="160"/>
       <c r="H121" s="158"/>
-      <c r="I121" t="str" s="159" cm="1">
+      <c r="I121" s="159" cm="1" t="str">
         <f t="array" ref="I121">IF(AG121="","",P121-K121)</f>
+        <v/>
       </c>
       <c r="J121" s="160"/>
       <c r="K121" s="158"/>
@@ -31695,8 +32112,9 @@
       <c r="M121" s="161"/>
       <c r="N121" s="161"/>
       <c r="O121" s="161"/>
-      <c r="P121" t="str" s="159" cm="1">
+      <c r="P121" s="159" cm="1" t="str">
         <f t="array" ref="P121">IF(AG121="","",AC121-R121-Q121)</f>
+        <v/>
       </c>
       <c r="Q121" s="162"/>
       <c r="R121" s="162"/>
@@ -31756,13 +32174,15 @@
       <c r="C122" s="170"/>
       <c r="D122" s="165"/>
       <c r="E122" s="164"/>
-      <c r="F122" t="str" s="195" cm="1">
+      <c r="F122" s="195" cm="1" t="str">
         <f t="array" ref="F122">IF(AG122="","",I122-H122)</f>
+        <v/>
       </c>
       <c r="G122" s="160"/>
       <c r="H122" s="158"/>
-      <c r="I122" t="str" s="159" cm="1">
+      <c r="I122" s="159" cm="1" t="str">
         <f t="array" ref="I122">IF(AG122="","",P122-K122)</f>
+        <v/>
       </c>
       <c r="J122" s="160"/>
       <c r="K122" s="158"/>
@@ -31770,8 +32190,9 @@
       <c r="M122" s="161"/>
       <c r="N122" s="161"/>
       <c r="O122" s="161"/>
-      <c r="P122" t="str" s="159" cm="1">
+      <c r="P122" s="159" cm="1" t="str">
         <f t="array" ref="P122">IF(AG122="","",AC122-R122-Q122)</f>
+        <v/>
       </c>
       <c r="Q122" s="162"/>
       <c r="R122" s="162"/>
@@ -31831,13 +32252,15 @@
       <c r="C123" s="170"/>
       <c r="D123" s="165"/>
       <c r="E123" s="164"/>
-      <c r="F123" t="str" s="195" cm="1">
+      <c r="F123" s="195" cm="1" t="str">
         <f t="array" ref="F123">IF(AG123="","",I123-H123)</f>
+        <v/>
       </c>
       <c r="G123" s="160"/>
       <c r="H123" s="158"/>
-      <c r="I123" t="str" s="159" cm="1">
+      <c r="I123" s="159" cm="1" t="str">
         <f t="array" ref="I123">IF(AG123="","",P123-K123)</f>
+        <v/>
       </c>
       <c r="J123" s="160"/>
       <c r="K123" s="158"/>
@@ -31845,8 +32268,9 @@
       <c r="M123" s="161"/>
       <c r="N123" s="161"/>
       <c r="O123" s="161"/>
-      <c r="P123" t="str" s="159" cm="1">
+      <c r="P123" s="159" cm="1" t="str">
         <f t="array" ref="P123">IF(AG123="","",AC123-R123-Q123)</f>
+        <v/>
       </c>
       <c r="Q123" s="162"/>
       <c r="R123" s="162"/>
@@ -31906,13 +32330,15 @@
       <c r="C124" s="170"/>
       <c r="D124" s="165"/>
       <c r="E124" s="164"/>
-      <c r="F124" t="str" s="195" cm="1">
+      <c r="F124" s="195" cm="1" t="str">
         <f t="array" ref="F124">IF(AG124="","",I124-H124)</f>
+        <v/>
       </c>
       <c r="G124" s="160"/>
       <c r="H124" s="158"/>
-      <c r="I124" t="str" s="159" cm="1">
+      <c r="I124" s="159" cm="1" t="str">
         <f t="array" ref="I124">IF(AG124="","",P124-K124)</f>
+        <v/>
       </c>
       <c r="J124" s="160"/>
       <c r="K124" s="158"/>
@@ -31920,8 +32346,9 @@
       <c r="M124" s="161"/>
       <c r="N124" s="161"/>
       <c r="O124" s="161"/>
-      <c r="P124" t="str" s="159" cm="1">
+      <c r="P124" s="159" cm="1" t="str">
         <f t="array" ref="P124">IF(AG124="","",AC124-R124-Q124)</f>
+        <v/>
       </c>
       <c r="Q124" s="162"/>
       <c r="R124" s="162"/>
@@ -31981,13 +32408,15 @@
       <c r="C125" s="170"/>
       <c r="D125" s="165"/>
       <c r="E125" s="164"/>
-      <c r="F125" t="str" s="195" cm="1">
+      <c r="F125" s="195" cm="1" t="str">
         <f t="array" ref="F125">IF(AG125="","",I125-H125)</f>
+        <v/>
       </c>
       <c r="G125" s="160"/>
       <c r="H125" s="158"/>
-      <c r="I125" t="str" s="159" cm="1">
+      <c r="I125" s="159" cm="1" t="str">
         <f t="array" ref="I125">IF(AG125="","",P125-K125)</f>
+        <v/>
       </c>
       <c r="J125" s="160"/>
       <c r="K125" s="158"/>
@@ -31995,8 +32424,9 @@
       <c r="M125" s="161"/>
       <c r="N125" s="161"/>
       <c r="O125" s="161"/>
-      <c r="P125" t="str" s="159" cm="1">
+      <c r="P125" s="159" cm="1" t="str">
         <f t="array" ref="P125">IF(AG125="","",AC125-R125-Q125)</f>
+        <v/>
       </c>
       <c r="Q125" s="162"/>
       <c r="R125" s="162"/>
@@ -32056,13 +32486,15 @@
       <c r="C126" s="170"/>
       <c r="D126" s="165"/>
       <c r="E126" s="164"/>
-      <c r="F126" t="str" s="195" cm="1">
+      <c r="F126" s="195" cm="1" t="str">
         <f t="array" ref="F126">IF(AG126="","",I126-H126)</f>
+        <v/>
       </c>
       <c r="G126" s="160"/>
       <c r="H126" s="158"/>
-      <c r="I126" t="str" s="159" cm="1">
+      <c r="I126" s="159" cm="1" t="str">
         <f t="array" ref="I126">IF(AG126="","",P126-K126)</f>
+        <v/>
       </c>
       <c r="J126" s="160"/>
       <c r="K126" s="158"/>
@@ -32070,8 +32502,9 @@
       <c r="M126" s="161"/>
       <c r="N126" s="161"/>
       <c r="O126" s="161"/>
-      <c r="P126" t="str" s="159" cm="1">
+      <c r="P126" s="159" cm="1" t="str">
         <f t="array" ref="P126">IF(AG126="","",AC126-R126-Q126)</f>
+        <v/>
       </c>
       <c r="Q126" s="162"/>
       <c r="R126" s="162"/>
@@ -32131,13 +32564,15 @@
       <c r="C127" s="170"/>
       <c r="D127" s="165"/>
       <c r="E127" s="164"/>
-      <c r="F127" t="str" s="195" cm="1">
+      <c r="F127" s="195" cm="1" t="str">
         <f t="array" ref="F127">IF(AG127="","",I127-H127)</f>
+        <v/>
       </c>
       <c r="G127" s="160"/>
       <c r="H127" s="158"/>
-      <c r="I127" t="str" s="159" cm="1">
+      <c r="I127" s="159" cm="1" t="str">
         <f t="array" ref="I127">IF(AG127="","",P127-K127)</f>
+        <v/>
       </c>
       <c r="J127" s="160"/>
       <c r="K127" s="158"/>
@@ -32145,8 +32580,9 @@
       <c r="M127" s="161"/>
       <c r="N127" s="161"/>
       <c r="O127" s="161"/>
-      <c r="P127" t="str" s="159" cm="1">
+      <c r="P127" s="159" cm="1" t="str">
         <f t="array" ref="P127">IF(AG127="","",AC127-R127-Q127)</f>
+        <v/>
       </c>
       <c r="Q127" s="162"/>
       <c r="R127" s="162"/>
@@ -32206,13 +32642,15 @@
       <c r="C128" s="170"/>
       <c r="D128" s="165"/>
       <c r="E128" s="164"/>
-      <c r="F128" t="str" s="195" cm="1">
+      <c r="F128" s="195" cm="1" t="str">
         <f t="array" ref="F128">IF(AG128="","",I128-H128)</f>
+        <v/>
       </c>
       <c r="G128" s="160"/>
       <c r="H128" s="158"/>
-      <c r="I128" t="str" s="159" cm="1">
+      <c r="I128" s="159" cm="1" t="str">
         <f t="array" ref="I128">IF(AG128="","",P128-K128)</f>
+        <v/>
       </c>
       <c r="J128" s="160"/>
       <c r="K128" s="158"/>
@@ -32220,8 +32658,9 @@
       <c r="M128" s="161"/>
       <c r="N128" s="161"/>
       <c r="O128" s="161"/>
-      <c r="P128" t="str" s="159" cm="1">
+      <c r="P128" s="159" cm="1" t="str">
         <f t="array" ref="P128">IF(AG128="","",AC128-R128-Q128)</f>
+        <v/>
       </c>
       <c r="Q128" s="162"/>
       <c r="R128" s="162"/>
@@ -32281,13 +32720,15 @@
       <c r="C129" s="170"/>
       <c r="D129" s="165"/>
       <c r="E129" s="164"/>
-      <c r="F129" t="str" s="195" cm="1">
+      <c r="F129" s="195" cm="1" t="str">
         <f t="array" ref="F129">IF(AG129="","",I129-H129)</f>
+        <v/>
       </c>
       <c r="G129" s="160"/>
       <c r="H129" s="158"/>
-      <c r="I129" t="str" s="159" cm="1">
+      <c r="I129" s="159" cm="1" t="str">
         <f t="array" ref="I129">IF(AG129="","",P129-K129)</f>
+        <v/>
       </c>
       <c r="J129" s="160"/>
       <c r="K129" s="158"/>
@@ -32295,8 +32736,9 @@
       <c r="M129" s="161"/>
       <c r="N129" s="161"/>
       <c r="O129" s="161"/>
-      <c r="P129" t="str" s="159" cm="1">
+      <c r="P129" s="159" cm="1" t="str">
         <f t="array" ref="P129">IF(AG129="","",AC129-R129-Q129)</f>
+        <v/>
       </c>
       <c r="Q129" s="162"/>
       <c r="R129" s="162"/>
@@ -32356,13 +32798,15 @@
       <c r="C130" s="170"/>
       <c r="D130" s="165"/>
       <c r="E130" s="164"/>
-      <c r="F130" t="str" s="195" cm="1">
+      <c r="F130" s="195" cm="1" t="str">
         <f t="array" ref="F130">IF(AG130="","",I130-H130)</f>
+        <v/>
       </c>
       <c r="G130" s="160"/>
       <c r="H130" s="158"/>
-      <c r="I130" t="str" s="159" cm="1">
+      <c r="I130" s="159" cm="1" t="str">
         <f t="array" ref="I130">IF(AG130="","",P130-K130)</f>
+        <v/>
       </c>
       <c r="J130" s="160"/>
       <c r="K130" s="158"/>
@@ -32370,8 +32814,9 @@
       <c r="M130" s="161"/>
       <c r="N130" s="161"/>
       <c r="O130" s="161"/>
-      <c r="P130" t="str" s="159" cm="1">
+      <c r="P130" s="159" cm="1" t="str">
         <f t="array" ref="P130">IF(AG130="","",AC130-R130-Q130)</f>
+        <v/>
       </c>
       <c r="Q130" s="162"/>
       <c r="R130" s="162"/>
@@ -32431,13 +32876,15 @@
       <c r="C131" s="170"/>
       <c r="D131" s="165"/>
       <c r="E131" s="164"/>
-      <c r="F131" t="str" s="195" cm="1">
+      <c r="F131" s="195" cm="1" t="str">
         <f t="array" ref="F131">IF(AG131="","",I131-H131)</f>
+        <v/>
       </c>
       <c r="G131" s="160"/>
       <c r="H131" s="158"/>
-      <c r="I131" t="str" s="159" cm="1">
+      <c r="I131" s="159" cm="1" t="str">
         <f t="array" ref="I131">IF(AG131="","",P131-K131)</f>
+        <v/>
       </c>
       <c r="J131" s="160"/>
       <c r="K131" s="158"/>
@@ -32445,8 +32892,9 @@
       <c r="M131" s="161"/>
       <c r="N131" s="161"/>
       <c r="O131" s="161"/>
-      <c r="P131" t="str" s="159" cm="1">
+      <c r="P131" s="159" cm="1" t="str">
         <f t="array" ref="P131">IF(AG131="","",AC131-R131-Q131)</f>
+        <v/>
       </c>
       <c r="Q131" s="162"/>
       <c r="R131" s="162"/>
@@ -32506,13 +32954,15 @@
       <c r="C132" s="170"/>
       <c r="D132" s="165"/>
       <c r="E132" s="164"/>
-      <c r="F132" t="str" s="195" cm="1">
+      <c r="F132" s="195" cm="1" t="str">
         <f t="array" ref="F132">IF(AG132="","",I132-H132)</f>
+        <v/>
       </c>
       <c r="G132" s="160"/>
       <c r="H132" s="158"/>
-      <c r="I132" t="str" s="159" cm="1">
+      <c r="I132" s="159" cm="1" t="str">
         <f t="array" ref="I132">IF(AG132="","",P132-K132)</f>
+        <v/>
       </c>
       <c r="J132" s="160"/>
       <c r="K132" s="158"/>
@@ -32520,8 +32970,9 @@
       <c r="M132" s="161"/>
       <c r="N132" s="161"/>
       <c r="O132" s="161"/>
-      <c r="P132" t="str" s="159" cm="1">
+      <c r="P132" s="159" cm="1" t="str">
         <f t="array" ref="P132">IF(AG132="","",AC132-R132-Q132)</f>
+        <v/>
       </c>
       <c r="Q132" s="162"/>
       <c r="R132" s="162"/>
@@ -32581,13 +33032,15 @@
       <c r="C133" s="170"/>
       <c r="D133" s="165"/>
       <c r="E133" s="164"/>
-      <c r="F133" t="str" s="195" cm="1">
+      <c r="F133" s="195" cm="1" t="str">
         <f t="array" ref="F133">IF(AG133="","",I133-H133)</f>
+        <v/>
       </c>
       <c r="G133" s="160"/>
       <c r="H133" s="158"/>
-      <c r="I133" t="str" s="159" cm="1">
+      <c r="I133" s="159" cm="1" t="str">
         <f t="array" ref="I133">IF(AG133="","",P133-K133)</f>
+        <v/>
       </c>
       <c r="J133" s="160"/>
       <c r="K133" s="158"/>
@@ -32595,8 +33048,9 @@
       <c r="M133" s="161"/>
       <c r="N133" s="161"/>
       <c r="O133" s="161"/>
-      <c r="P133" t="str" s="159" cm="1">
+      <c r="P133" s="159" cm="1" t="str">
         <f t="array" ref="P133">IF(AG133="","",AC133-R133-Q133)</f>
+        <v/>
       </c>
       <c r="Q133" s="162"/>
       <c r="R133" s="162"/>
@@ -32656,13 +33110,15 @@
       <c r="C134" s="170"/>
       <c r="D134" s="165"/>
       <c r="E134" s="164"/>
-      <c r="F134" t="str" s="195" cm="1">
+      <c r="F134" s="195" cm="1" t="str">
         <f t="array" ref="F134">IF(AG134="","",I134-H134)</f>
+        <v/>
       </c>
       <c r="G134" s="160"/>
       <c r="H134" s="158"/>
-      <c r="I134" t="str" s="159" cm="1">
+      <c r="I134" s="159" cm="1" t="str">
         <f t="array" ref="I134">IF(AG134="","",P134-K134)</f>
+        <v/>
       </c>
       <c r="J134" s="160"/>
       <c r="K134" s="158"/>
@@ -32670,8 +33126,9 @@
       <c r="M134" s="161"/>
       <c r="N134" s="161"/>
       <c r="O134" s="161"/>
-      <c r="P134" t="str" s="159" cm="1">
+      <c r="P134" s="159" cm="1" t="str">
         <f t="array" ref="P134">IF(AG134="","",AC134-R134-Q134)</f>
+        <v/>
       </c>
       <c r="Q134" s="162"/>
       <c r="R134" s="162"/>
@@ -32731,13 +33188,15 @@
       <c r="C135" s="170"/>
       <c r="D135" s="165"/>
       <c r="E135" s="164"/>
-      <c r="F135" t="str" s="195" cm="1">
+      <c r="F135" s="195" cm="1" t="str">
         <f t="array" ref="F135">IF(AG135="","",I135-H135)</f>
+        <v/>
       </c>
       <c r="G135" s="160"/>
       <c r="H135" s="158"/>
-      <c r="I135" t="str" s="159" cm="1">
+      <c r="I135" s="159" cm="1" t="str">
         <f t="array" ref="I135">IF(AG135="","",P135-K135)</f>
+        <v/>
       </c>
       <c r="J135" s="160"/>
       <c r="K135" s="158"/>
@@ -32745,8 +33204,9 @@
       <c r="M135" s="161"/>
       <c r="N135" s="161"/>
       <c r="O135" s="161"/>
-      <c r="P135" t="str" s="159" cm="1">
+      <c r="P135" s="159" cm="1" t="str">
         <f t="array" ref="P135">IF(AG135="","",AC135-R135-Q135)</f>
+        <v/>
       </c>
       <c r="Q135" s="162"/>
       <c r="R135" s="162"/>
@@ -32806,13 +33266,15 @@
       <c r="C136" s="170"/>
       <c r="D136" s="165"/>
       <c r="E136" s="164"/>
-      <c r="F136" t="str" s="195" cm="1">
+      <c r="F136" s="195" cm="1" t="str">
         <f t="array" ref="F136">IF(AG136="","",I136-H136)</f>
+        <v/>
       </c>
       <c r="G136" s="160"/>
       <c r="H136" s="158"/>
-      <c r="I136" t="str" s="159" cm="1">
+      <c r="I136" s="159" cm="1" t="str">
         <f t="array" ref="I136">IF(AG136="","",P136-K136)</f>
+        <v/>
       </c>
       <c r="J136" s="160"/>
       <c r="K136" s="158"/>
@@ -32820,8 +33282,9 @@
       <c r="M136" s="161"/>
       <c r="N136" s="161"/>
       <c r="O136" s="161"/>
-      <c r="P136" t="str" s="159" cm="1">
+      <c r="P136" s="159" cm="1" t="str">
         <f t="array" ref="P136">IF(AG136="","",AC136-R136-Q136)</f>
+        <v/>
       </c>
       <c r="Q136" s="162"/>
       <c r="R136" s="162"/>
@@ -32881,13 +33344,15 @@
       <c r="C137" s="170"/>
       <c r="D137" s="165"/>
       <c r="E137" s="164"/>
-      <c r="F137" t="str" s="195" cm="1">
+      <c r="F137" s="195" cm="1" t="str">
         <f t="array" ref="F137">IF(AG137="","",I137-H137)</f>
+        <v/>
       </c>
       <c r="G137" s="160"/>
       <c r="H137" s="158"/>
-      <c r="I137" t="str" s="159" cm="1">
+      <c r="I137" s="159" cm="1" t="str">
         <f t="array" ref="I137">IF(AG137="","",P137-K137)</f>
+        <v/>
       </c>
       <c r="J137" s="160"/>
       <c r="K137" s="158"/>
@@ -32895,8 +33360,9 @@
       <c r="M137" s="161"/>
       <c r="N137" s="161"/>
       <c r="O137" s="161"/>
-      <c r="P137" t="str" s="159" cm="1">
+      <c r="P137" s="159" cm="1" t="str">
         <f t="array" ref="P137">IF(AG137="","",AC137-R137-Q137)</f>
+        <v/>
       </c>
       <c r="Q137" s="162"/>
       <c r="R137" s="162"/>
@@ -32956,13 +33422,15 @@
       <c r="C138" s="170"/>
       <c r="D138" s="165"/>
       <c r="E138" s="164"/>
-      <c r="F138" t="str" s="195" cm="1">
+      <c r="F138" s="195" cm="1" t="str">
         <f t="array" ref="F138">IF(AG138="","",I138-H138)</f>
+        <v/>
       </c>
       <c r="G138" s="160"/>
       <c r="H138" s="158"/>
-      <c r="I138" t="str" s="159" cm="1">
+      <c r="I138" s="159" cm="1" t="str">
         <f t="array" ref="I138">IF(AG138="","",P138-K138)</f>
+        <v/>
       </c>
       <c r="J138" s="160"/>
       <c r="K138" s="158"/>
@@ -32970,8 +33438,9 @@
       <c r="M138" s="161"/>
       <c r="N138" s="161"/>
       <c r="O138" s="161"/>
-      <c r="P138" t="str" s="159" cm="1">
+      <c r="P138" s="159" cm="1" t="str">
         <f t="array" ref="P138">IF(AG138="","",AC138-R138-Q138)</f>
+        <v/>
       </c>
       <c r="Q138" s="162"/>
       <c r="R138" s="162"/>
@@ -33031,13 +33500,15 @@
       <c r="C139" s="170"/>
       <c r="D139" s="165"/>
       <c r="E139" s="164"/>
-      <c r="F139" t="str" s="195" cm="1">
+      <c r="F139" s="195" cm="1" t="str">
         <f t="array" ref="F139">IF(AG139="","",I139-H139)</f>
+        <v/>
       </c>
       <c r="G139" s="160"/>
       <c r="H139" s="158"/>
-      <c r="I139" t="str" s="159" cm="1">
+      <c r="I139" s="159" cm="1" t="str">
         <f t="array" ref="I139">IF(AG139="","",P139-K139)</f>
+        <v/>
       </c>
       <c r="J139" s="160"/>
       <c r="K139" s="158"/>
@@ -33045,8 +33516,9 @@
       <c r="M139" s="161"/>
       <c r="N139" s="161"/>
       <c r="O139" s="161"/>
-      <c r="P139" t="str" s="159" cm="1">
+      <c r="P139" s="159" cm="1" t="str">
         <f t="array" ref="P139">IF(AG139="","",AC139-R139-Q139)</f>
+        <v/>
       </c>
       <c r="Q139" s="162"/>
       <c r="R139" s="162"/>
@@ -33106,13 +33578,15 @@
       <c r="C140" s="170"/>
       <c r="D140" s="165"/>
       <c r="E140" s="164"/>
-      <c r="F140" t="str" s="195" cm="1">
+      <c r="F140" s="195" cm="1" t="str">
         <f t="array" ref="F140">IF(AG140="","",I140-H140)</f>
+        <v/>
       </c>
       <c r="G140" s="160"/>
       <c r="H140" s="158"/>
-      <c r="I140" t="str" s="159" cm="1">
+      <c r="I140" s="159" cm="1" t="str">
         <f t="array" ref="I140">IF(AG140="","",P140-K140)</f>
+        <v/>
       </c>
       <c r="J140" s="160"/>
       <c r="K140" s="158"/>
@@ -33120,8 +33594,9 @@
       <c r="M140" s="161"/>
       <c r="N140" s="161"/>
       <c r="O140" s="161"/>
-      <c r="P140" t="str" s="159" cm="1">
+      <c r="P140" s="159" cm="1" t="str">
         <f t="array" ref="P140">IF(AG140="","",AC140-R140-Q140)</f>
+        <v/>
       </c>
       <c r="Q140" s="162"/>
       <c r="R140" s="162"/>
@@ -33181,13 +33656,15 @@
       <c r="C141" s="170"/>
       <c r="D141" s="165"/>
       <c r="E141" s="164"/>
-      <c r="F141" t="str" s="195" cm="1">
+      <c r="F141" s="195" cm="1" t="str">
         <f t="array" ref="F141">IF(AG141="","",I141-H141)</f>
+        <v/>
       </c>
       <c r="G141" s="160"/>
       <c r="H141" s="158"/>
-      <c r="I141" t="str" s="159" cm="1">
+      <c r="I141" s="159" cm="1" t="str">
         <f t="array" ref="I141">IF(AG141="","",P141-K141)</f>
+        <v/>
       </c>
       <c r="J141" s="160"/>
       <c r="K141" s="158"/>
@@ -33195,8 +33672,9 @@
       <c r="M141" s="161"/>
       <c r="N141" s="161"/>
       <c r="O141" s="161"/>
-      <c r="P141" t="str" s="159" cm="1">
+      <c r="P141" s="159" cm="1" t="str">
         <f t="array" ref="P141">IF(AG141="","",AC141-R141-Q141)</f>
+        <v/>
       </c>
       <c r="Q141" s="162"/>
       <c r="R141" s="162"/>
@@ -33256,13 +33734,15 @@
       <c r="C142" s="170"/>
       <c r="D142" s="165"/>
       <c r="E142" s="164"/>
-      <c r="F142" t="str" s="195" cm="1">
+      <c r="F142" s="195" cm="1" t="str">
         <f t="array" ref="F142">IF(AG142="","",I142-H142)</f>
+        <v/>
       </c>
       <c r="G142" s="160"/>
       <c r="H142" s="158"/>
-      <c r="I142" t="str" s="159" cm="1">
+      <c r="I142" s="159" cm="1" t="str">
         <f t="array" ref="I142">IF(AG142="","",P142-K142)</f>
+        <v/>
       </c>
       <c r="J142" s="160"/>
       <c r="K142" s="158"/>
@@ -33270,8 +33750,9 @@
       <c r="M142" s="161"/>
       <c r="N142" s="161"/>
       <c r="O142" s="161"/>
-      <c r="P142" t="str" s="159" cm="1">
+      <c r="P142" s="159" cm="1" t="str">
         <f t="array" ref="P142">IF(AG142="","",AC142-R142-Q142)</f>
+        <v/>
       </c>
       <c r="Q142" s="162"/>
       <c r="R142" s="162"/>
@@ -33331,13 +33812,15 @@
       <c r="C143" s="170"/>
       <c r="D143" s="165"/>
       <c r="E143" s="164"/>
-      <c r="F143" t="str" s="195" cm="1">
+      <c r="F143" s="195" cm="1" t="str">
         <f t="array" ref="F143">IF(AG143="","",I143-H143)</f>
+        <v/>
       </c>
       <c r="G143" s="160"/>
       <c r="H143" s="158"/>
-      <c r="I143" t="str" s="159" cm="1">
+      <c r="I143" s="159" cm="1" t="str">
         <f t="array" ref="I143">IF(AG143="","",P143-K143)</f>
+        <v/>
       </c>
       <c r="J143" s="160"/>
       <c r="K143" s="158"/>
@@ -33345,8 +33828,9 @@
       <c r="M143" s="161"/>
       <c r="N143" s="161"/>
       <c r="O143" s="161"/>
-      <c r="P143" t="str" s="159" cm="1">
+      <c r="P143" s="159" cm="1" t="str">
         <f t="array" ref="P143">IF(AG143="","",AC143-R143-Q143)</f>
+        <v/>
       </c>
       <c r="Q143" s="162"/>
       <c r="R143" s="162"/>
@@ -33406,13 +33890,15 @@
       <c r="C144" s="170"/>
       <c r="D144" s="165"/>
       <c r="E144" s="164"/>
-      <c r="F144" t="str" s="195" cm="1">
+      <c r="F144" s="195" cm="1" t="str">
         <f t="array" ref="F144">IF(AG144="","",I144-H144)</f>
+        <v/>
       </c>
       <c r="G144" s="160"/>
       <c r="H144" s="158"/>
-      <c r="I144" t="str" s="159" cm="1">
+      <c r="I144" s="159" cm="1" t="str">
         <f t="array" ref="I144">IF(AG144="","",P144-K144)</f>
+        <v/>
       </c>
       <c r="J144" s="160"/>
       <c r="K144" s="158"/>
@@ -33420,8 +33906,9 @@
       <c r="M144" s="161"/>
       <c r="N144" s="161"/>
       <c r="O144" s="161"/>
-      <c r="P144" t="str" s="159" cm="1">
+      <c r="P144" s="159" cm="1" t="str">
         <f t="array" ref="P144">IF(AG144="","",AC144-R144-Q144)</f>
+        <v/>
       </c>
       <c r="Q144" s="162"/>
       <c r="R144" s="162"/>
@@ -33481,13 +33968,15 @@
       <c r="C145" s="170"/>
       <c r="D145" s="165"/>
       <c r="E145" s="164"/>
-      <c r="F145" t="str" s="195" cm="1">
+      <c r="F145" s="195" cm="1" t="str">
         <f t="array" ref="F145">IF(AG145="","",I145-H145)</f>
+        <v/>
       </c>
       <c r="G145" s="160"/>
       <c r="H145" s="158"/>
-      <c r="I145" t="str" s="159" cm="1">
+      <c r="I145" s="159" cm="1" t="str">
         <f t="array" ref="I145">IF(AG145="","",P145-K145)</f>
+        <v/>
       </c>
       <c r="J145" s="160"/>
       <c r="K145" s="158"/>
@@ -33495,8 +33984,9 @@
       <c r="M145" s="161"/>
       <c r="N145" s="161"/>
       <c r="O145" s="161"/>
-      <c r="P145" t="str" s="159" cm="1">
+      <c r="P145" s="159" cm="1" t="str">
         <f t="array" ref="P145">IF(AG145="","",AC145-R145-Q145)</f>
+        <v/>
       </c>
       <c r="Q145" s="162"/>
       <c r="R145" s="162"/>
@@ -33556,13 +34046,15 @@
       <c r="C146" s="170"/>
       <c r="D146" s="165"/>
       <c r="E146" s="164"/>
-      <c r="F146" t="str" s="195" cm="1">
+      <c r="F146" s="195" cm="1" t="str">
         <f t="array" ref="F146">IF(AG146="","",I146-H146)</f>
+        <v/>
       </c>
       <c r="G146" s="160"/>
       <c r="H146" s="158"/>
-      <c r="I146" t="str" s="159" cm="1">
+      <c r="I146" s="159" cm="1" t="str">
         <f t="array" ref="I146">IF(AG146="","",P146-K146)</f>
+        <v/>
       </c>
       <c r="J146" s="160"/>
       <c r="K146" s="158"/>
@@ -33570,8 +34062,9 @@
       <c r="M146" s="161"/>
       <c r="N146" s="161"/>
       <c r="O146" s="161"/>
-      <c r="P146" t="str" s="159" cm="1">
+      <c r="P146" s="159" cm="1" t="str">
         <f t="array" ref="P146">IF(AG146="","",AC146-R146-Q146)</f>
+        <v/>
       </c>
       <c r="Q146" s="162"/>
       <c r="R146" s="162"/>
@@ -33631,13 +34124,15 @@
       <c r="C147" s="170"/>
       <c r="D147" s="165"/>
       <c r="E147" s="164"/>
-      <c r="F147" t="str" s="195" cm="1">
+      <c r="F147" s="195" cm="1" t="str">
         <f t="array" ref="F147">IF(AG147="","",I147-H147)</f>
+        <v/>
       </c>
       <c r="G147" s="160"/>
       <c r="H147" s="158"/>
-      <c r="I147" t="str" s="159" cm="1">
+      <c r="I147" s="159" cm="1" t="str">
         <f t="array" ref="I147">IF(AG147="","",P147-K147)</f>
+        <v/>
       </c>
       <c r="J147" s="160"/>
       <c r="K147" s="158"/>
@@ -33645,8 +34140,9 @@
       <c r="M147" s="161"/>
       <c r="N147" s="161"/>
       <c r="O147" s="161"/>
-      <c r="P147" t="str" s="159" cm="1">
+      <c r="P147" s="159" cm="1" t="str">
         <f t="array" ref="P147">IF(AG147="","",AC147-R147-Q147)</f>
+        <v/>
       </c>
       <c r="Q147" s="162"/>
       <c r="R147" s="162"/>
@@ -33706,13 +34202,15 @@
       <c r="C148" s="170"/>
       <c r="D148" s="165"/>
       <c r="E148" s="164"/>
-      <c r="F148" t="str" s="195" cm="1">
+      <c r="F148" s="195" cm="1" t="str">
         <f t="array" ref="F148">IF(AG148="","",I148-H148)</f>
+        <v/>
       </c>
       <c r="G148" s="160"/>
       <c r="H148" s="158"/>
-      <c r="I148" t="str" s="159" cm="1">
+      <c r="I148" s="159" cm="1" t="str">
         <f t="array" ref="I148">IF(AG148="","",P148-K148)</f>
+        <v/>
       </c>
       <c r="J148" s="160"/>
       <c r="K148" s="158"/>
@@ -33720,8 +34218,9 @@
       <c r="M148" s="161"/>
       <c r="N148" s="161"/>
       <c r="O148" s="161"/>
-      <c r="P148" t="str" s="159" cm="1">
+      <c r="P148" s="159" cm="1" t="str">
         <f t="array" ref="P148">IF(AG148="","",AC148-R148-Q148)</f>
+        <v/>
       </c>
       <c r="Q148" s="162"/>
       <c r="R148" s="162"/>
@@ -33781,13 +34280,15 @@
       <c r="C149" s="170"/>
       <c r="D149" s="165"/>
       <c r="E149" s="164"/>
-      <c r="F149" t="str" s="195" cm="1">
+      <c r="F149" s="195" cm="1" t="str">
         <f t="array" ref="F149">IF(AG149="","",I149-H149)</f>
+        <v/>
       </c>
       <c r="G149" s="160"/>
       <c r="H149" s="158"/>
-      <c r="I149" t="str" s="159" cm="1">
+      <c r="I149" s="159" cm="1" t="str">
         <f t="array" ref="I149">IF(AG149="","",P149-K149)</f>
+        <v/>
       </c>
       <c r="J149" s="160"/>
       <c r="K149" s="158"/>
@@ -33795,8 +34296,9 @@
       <c r="M149" s="161"/>
       <c r="N149" s="161"/>
       <c r="O149" s="161"/>
-      <c r="P149" t="str" s="159" cm="1">
+      <c r="P149" s="159" cm="1" t="str">
         <f t="array" ref="P149">IF(AG149="","",AC149-R149-Q149)</f>
+        <v/>
       </c>
       <c r="Q149" s="162"/>
       <c r="R149" s="162"/>
@@ -33856,13 +34358,15 @@
       <c r="C150" s="170"/>
       <c r="D150" s="165"/>
       <c r="E150" s="164"/>
-      <c r="F150" t="str" s="195" cm="1">
+      <c r="F150" s="195" cm="1" t="str">
         <f t="array" ref="F150">IF(AG150="","",I150-H150)</f>
+        <v/>
       </c>
       <c r="G150" s="160"/>
       <c r="H150" s="158"/>
-      <c r="I150" t="str" s="159" cm="1">
+      <c r="I150" s="159" cm="1" t="str">
         <f t="array" ref="I150">IF(AG150="","",P150-K150)</f>
+        <v/>
       </c>
       <c r="J150" s="160"/>
       <c r="K150" s="158"/>
@@ -33870,8 +34374,9 @@
       <c r="M150" s="161"/>
       <c r="N150" s="161"/>
       <c r="O150" s="161"/>
-      <c r="P150" t="str" s="159" cm="1">
+      <c r="P150" s="159" cm="1" t="str">
         <f t="array" ref="P150">IF(AG150="","",AC150-R150-Q150)</f>
+        <v/>
       </c>
       <c r="Q150" s="162"/>
       <c r="R150" s="162"/>
@@ -33931,13 +34436,15 @@
       <c r="C151" s="170"/>
       <c r="D151" s="165"/>
       <c r="E151" s="164"/>
-      <c r="F151" t="str" s="195" cm="1">
+      <c r="F151" s="195" cm="1" t="str">
         <f t="array" ref="F151">IF(AG151="","",I151-H151)</f>
+        <v/>
       </c>
       <c r="G151" s="160"/>
       <c r="H151" s="158"/>
-      <c r="I151" t="str" s="159" cm="1">
+      <c r="I151" s="159" cm="1" t="str">
         <f t="array" ref="I151">IF(AG151="","",P151-K151)</f>
+        <v/>
       </c>
       <c r="J151" s="160"/>
       <c r="K151" s="158"/>
@@ -33945,8 +34452,9 @@
       <c r="M151" s="161"/>
       <c r="N151" s="161"/>
       <c r="O151" s="161"/>
-      <c r="P151" t="str" s="159" cm="1">
+      <c r="P151" s="159" cm="1" t="str">
         <f t="array" ref="P151">IF(AG151="","",AC151-R151-Q151)</f>
+        <v/>
       </c>
       <c r="Q151" s="162"/>
       <c r="R151" s="162"/>
@@ -34006,13 +34514,15 @@
       <c r="C152" s="170"/>
       <c r="D152" s="165"/>
       <c r="E152" s="164"/>
-      <c r="F152" t="str" s="195" cm="1">
+      <c r="F152" s="195" cm="1" t="str">
         <f t="array" ref="F152">IF(AG152="","",I152-H152)</f>
+        <v/>
       </c>
       <c r="G152" s="160"/>
       <c r="H152" s="158"/>
-      <c r="I152" t="str" s="159" cm="1">
+      <c r="I152" s="159" cm="1" t="str">
         <f t="array" ref="I152">IF(AG152="","",P152-K152)</f>
+        <v/>
       </c>
       <c r="J152" s="160"/>
       <c r="K152" s="158"/>
@@ -34020,8 +34530,9 @@
       <c r="M152" s="161"/>
       <c r="N152" s="161"/>
       <c r="O152" s="161"/>
-      <c r="P152" t="str" s="159" cm="1">
+      <c r="P152" s="159" cm="1" t="str">
         <f t="array" ref="P152">IF(AG152="","",AC152-R152-Q152)</f>
+        <v/>
       </c>
       <c r="Q152" s="162"/>
       <c r="R152" s="162"/>
@@ -34035,8 +34546,9 @@
       <c r="Z152" s="161"/>
       <c r="AA152" s="161"/>
       <c r="AB152" s="160"/>
-      <c r="AC152" t="str" s="195" cm="1">
+      <c r="AC152" s="195" cm="1" t="str">
         <f t="array" ref="AC152">IF(AG152="","",AG152-AF152)</f>
+        <v/>
       </c>
       <c r="AD152" s="161"/>
       <c r="AE152" s="160"/>
@@ -34083,13 +34595,15 @@
       <c r="C153" s="170"/>
       <c r="D153" s="165"/>
       <c r="E153" s="164"/>
-      <c r="F153" t="str" s="195" cm="1">
+      <c r="F153" s="195" cm="1" t="str">
         <f t="array" ref="F153">IF(AG153="","",I153-H153)</f>
+        <v/>
       </c>
       <c r="G153" s="160"/>
       <c r="H153" s="158"/>
-      <c r="I153" t="str" s="159" cm="1">
+      <c r="I153" s="159" cm="1" t="str">
         <f t="array" ref="I153">IF(AG153="","",P153-K153)</f>
+        <v/>
       </c>
       <c r="J153" s="160"/>
       <c r="K153" s="158"/>
@@ -34097,8 +34611,9 @@
       <c r="M153" s="161"/>
       <c r="N153" s="161"/>
       <c r="O153" s="161"/>
-      <c r="P153" t="str" s="159" cm="1">
+      <c r="P153" s="159" cm="1" t="str">
         <f t="array" ref="P153">IF(AG153="","",AC153-R153-Q153)</f>
+        <v/>
       </c>
       <c r="Q153" s="162"/>
       <c r="R153" s="162"/>
@@ -34112,8 +34627,9 @@
       <c r="Z153" s="161"/>
       <c r="AA153" s="161"/>
       <c r="AB153" s="160"/>
-      <c r="AC153" t="str" s="195" cm="1">
+      <c r="AC153" s="195" cm="1" t="str">
         <f t="array" ref="AC153">IF(AG153="","",AG153-AF153)</f>
+        <v/>
       </c>
       <c r="AD153" s="161"/>
       <c r="AE153" s="160"/>
@@ -34160,13 +34676,15 @@
       <c r="C154" s="170"/>
       <c r="D154" s="165"/>
       <c r="E154" s="164"/>
-      <c r="F154" t="str" s="195" cm="1">
+      <c r="F154" s="195" cm="1" t="str">
         <f t="array" ref="F154">IF(AG154="","",I154-H154)</f>
+        <v/>
       </c>
       <c r="G154" s="160"/>
       <c r="H154" s="158"/>
-      <c r="I154" t="str" s="159" cm="1">
+      <c r="I154" s="159" cm="1" t="str">
         <f t="array" ref="I154">IF(AG154="","",P154-K154)</f>
+        <v/>
       </c>
       <c r="J154" s="160"/>
       <c r="K154" s="158"/>
@@ -34174,8 +34692,9 @@
       <c r="M154" s="161"/>
       <c r="N154" s="161"/>
       <c r="O154" s="161"/>
-      <c r="P154" t="str" s="159" cm="1">
+      <c r="P154" s="159" cm="1" t="str">
         <f t="array" ref="P154">IF(AG154="","",AC154-R154-Q154)</f>
+        <v/>
       </c>
       <c r="Q154" s="162"/>
       <c r="R154" s="162"/>
@@ -34189,8 +34708,9 @@
       <c r="Z154" s="161"/>
       <c r="AA154" s="161"/>
       <c r="AB154" s="160"/>
-      <c r="AC154" t="str" s="195" cm="1">
+      <c r="AC154" s="195" cm="1" t="str">
         <f t="array" ref="AC154">IF(AG154="","",AG154-AF154)</f>
+        <v/>
       </c>
       <c r="AD154" s="161"/>
       <c r="AE154" s="160"/>
@@ -34237,13 +34757,15 @@
       <c r="C155" s="170"/>
       <c r="D155" s="165"/>
       <c r="E155" s="164"/>
-      <c r="F155" t="str" s="195" cm="1">
+      <c r="F155" s="195" cm="1" t="str">
         <f t="array" ref="F155">IF(AG155="","",I155-H155)</f>
+        <v/>
       </c>
       <c r="G155" s="160"/>
       <c r="H155" s="158"/>
-      <c r="I155" t="str" s="159" cm="1">
+      <c r="I155" s="159" cm="1" t="str">
         <f t="array" ref="I155">IF(AG155="","",P155-K155)</f>
+        <v/>
       </c>
       <c r="J155" s="160"/>
       <c r="K155" s="158"/>
@@ -34251,8 +34773,9 @@
       <c r="M155" s="161"/>
       <c r="N155" s="161"/>
       <c r="O155" s="161"/>
-      <c r="P155" t="str" s="159" cm="1">
+      <c r="P155" s="159" cm="1" t="str">
         <f t="array" ref="P155">IF(AG155="","",AC155-R155-Q155)</f>
+        <v/>
       </c>
       <c r="Q155" s="162"/>
       <c r="R155" s="162"/>
@@ -34266,8 +34789,9 @@
       <c r="Z155" s="161"/>
       <c r="AA155" s="161"/>
       <c r="AB155" s="160"/>
-      <c r="AC155" t="str" s="195" cm="1">
+      <c r="AC155" s="195" cm="1" t="str">
         <f t="array" ref="AC155">IF(AG155="","",AG155-AF155)</f>
+        <v/>
       </c>
       <c r="AD155" s="161"/>
       <c r="AE155" s="160"/>
@@ -34314,13 +34838,15 @@
       <c r="C156" s="170"/>
       <c r="D156" s="165"/>
       <c r="E156" s="164"/>
-      <c r="F156" t="str" s="195" cm="1">
+      <c r="F156" s="195" cm="1" t="str">
         <f t="array" ref="F156">IF(AG156="","",I156-H156)</f>
+        <v/>
       </c>
       <c r="G156" s="160"/>
       <c r="H156" s="158"/>
-      <c r="I156" t="str" s="159" cm="1">
+      <c r="I156" s="159" cm="1" t="str">
         <f t="array" ref="I156">IF(AG156="","",P156-K156)</f>
+        <v/>
       </c>
       <c r="J156" s="160"/>
       <c r="K156" s="158"/>
@@ -34328,8 +34854,9 @@
       <c r="M156" s="161"/>
       <c r="N156" s="161"/>
       <c r="O156" s="161"/>
-      <c r="P156" t="str" s="159" cm="1">
+      <c r="P156" s="159" cm="1" t="str">
         <f t="array" ref="P156">IF(AG156="","",AC156-R156-Q156)</f>
+        <v/>
       </c>
       <c r="Q156" s="162"/>
       <c r="R156" s="162"/>
@@ -34343,8 +34870,9 @@
       <c r="Z156" s="161"/>
       <c r="AA156" s="161"/>
       <c r="AB156" s="160"/>
-      <c r="AC156" t="str" s="195" cm="1">
+      <c r="AC156" s="195" cm="1" t="str">
         <f t="array" ref="AC156">IF(AG156="","",AG156-AF156)</f>
+        <v/>
       </c>
       <c r="AD156" s="161"/>
       <c r="AE156" s="160"/>
@@ -34391,13 +34919,15 @@
       <c r="C157" s="170"/>
       <c r="D157" s="165"/>
       <c r="E157" s="164"/>
-      <c r="F157" t="str" s="195" cm="1">
+      <c r="F157" s="195" cm="1" t="str">
         <f t="array" ref="F157">IF(AG157="","",I157-H157)</f>
+        <v/>
       </c>
       <c r="G157" s="160"/>
       <c r="H157" s="158"/>
-      <c r="I157" t="str" s="159" cm="1">
+      <c r="I157" s="159" cm="1" t="str">
         <f t="array" ref="I157">IF(AG157="","",P157-K157)</f>
+        <v/>
       </c>
       <c r="J157" s="160"/>
       <c r="K157" s="158"/>
@@ -34405,8 +34935,9 @@
       <c r="M157" s="161"/>
       <c r="N157" s="161"/>
       <c r="O157" s="161"/>
-      <c r="P157" t="str" s="159" cm="1">
+      <c r="P157" s="159" cm="1" t="str">
         <f t="array" ref="P157">IF(AG157="","",AC157-R157-Q157)</f>
+        <v/>
       </c>
       <c r="Q157" s="162"/>
       <c r="R157" s="162"/>
@@ -34420,8 +34951,9 @@
       <c r="Z157" s="161"/>
       <c r="AA157" s="161"/>
       <c r="AB157" s="160"/>
-      <c r="AC157" t="str" s="195" cm="1">
+      <c r="AC157" s="195" cm="1" t="str">
         <f t="array" ref="AC157">IF(AG157="","",AG157-AF157)</f>
+        <v/>
       </c>
       <c r="AD157" s="161"/>
       <c r="AE157" s="160"/>
@@ -34468,13 +35000,15 @@
       <c r="C158" s="170"/>
       <c r="D158" s="165"/>
       <c r="E158" s="164"/>
-      <c r="F158" t="str" s="195" cm="1">
+      <c r="F158" s="195" cm="1" t="str">
         <f t="array" ref="F158">IF(AG158="","",I158-H158)</f>
+        <v/>
       </c>
       <c r="G158" s="160"/>
       <c r="H158" s="158"/>
-      <c r="I158" t="str" s="159" cm="1">
+      <c r="I158" s="159" cm="1" t="str">
         <f t="array" ref="I158">IF(AG158="","",P158-K158)</f>
+        <v/>
       </c>
       <c r="J158" s="160"/>
       <c r="K158" s="158"/>
@@ -34482,8 +35016,9 @@
       <c r="M158" s="161"/>
       <c r="N158" s="161"/>
       <c r="O158" s="161"/>
-      <c r="P158" t="str" s="159" cm="1">
+      <c r="P158" s="159" cm="1" t="str">
         <f t="array" ref="P158">IF(AG158="","",AC158-R158-Q158)</f>
+        <v/>
       </c>
       <c r="Q158" s="162"/>
       <c r="R158" s="162"/>
@@ -34497,8 +35032,9 @@
       <c r="Z158" s="161"/>
       <c r="AA158" s="161"/>
       <c r="AB158" s="160"/>
-      <c r="AC158" t="str" s="195" cm="1">
+      <c r="AC158" s="195" cm="1" t="str">
         <f t="array" ref="AC158">IF(AG158="","",AG158-AF158)</f>
+        <v/>
       </c>
       <c r="AD158" s="161"/>
       <c r="AE158" s="160"/>
@@ -34545,13 +35081,15 @@
       <c r="C159" s="170"/>
       <c r="D159" s="165"/>
       <c r="E159" s="164"/>
-      <c r="F159" t="str" s="195" cm="1">
+      <c r="F159" s="195" cm="1" t="str">
         <f t="array" ref="F159">IF(AG159="","",I159-H159)</f>
+        <v/>
       </c>
       <c r="G159" s="160"/>
       <c r="H159" s="158"/>
-      <c r="I159" t="str" s="159" cm="1">
+      <c r="I159" s="159" cm="1" t="str">
         <f t="array" ref="I159">IF(AG159="","",P159-K159)</f>
+        <v/>
       </c>
       <c r="J159" s="160"/>
       <c r="K159" s="158"/>
@@ -34559,8 +35097,9 @@
       <c r="M159" s="161"/>
       <c r="N159" s="161"/>
       <c r="O159" s="161"/>
-      <c r="P159" t="str" s="159" cm="1">
+      <c r="P159" s="159" cm="1" t="str">
         <f t="array" ref="P159">IF(AG159="","",AC159-R159-Q159)</f>
+        <v/>
       </c>
       <c r="Q159" s="162"/>
       <c r="R159" s="162"/>
@@ -34574,8 +35113,9 @@
       <c r="Z159" s="161"/>
       <c r="AA159" s="161"/>
       <c r="AB159" s="160"/>
-      <c r="AC159" t="str" s="195" cm="1">
+      <c r="AC159" s="195" cm="1" t="str">
         <f t="array" ref="AC159">IF(AG159="","",AG159-AF159)</f>
+        <v/>
       </c>
       <c r="AD159" s="161"/>
       <c r="AE159" s="160"/>
@@ -34622,13 +35162,15 @@
       <c r="C160" s="170"/>
       <c r="D160" s="165"/>
       <c r="E160" s="164"/>
-      <c r="F160" t="str" s="195" cm="1">
+      <c r="F160" s="195" cm="1" t="str">
         <f t="array" ref="F160">IF(AG160="","",I160-H160)</f>
+        <v/>
       </c>
       <c r="G160" s="160"/>
       <c r="H160" s="158"/>
-      <c r="I160" t="str" s="159" cm="1">
+      <c r="I160" s="159" cm="1" t="str">
         <f t="array" ref="I160">IF(AG160="","",P160-K160)</f>
+        <v/>
       </c>
       <c r="J160" s="160"/>
       <c r="K160" s="158"/>
@@ -34636,8 +35178,9 @@
       <c r="M160" s="161"/>
       <c r="N160" s="161"/>
       <c r="O160" s="161"/>
-      <c r="P160" t="str" s="159" cm="1">
+      <c r="P160" s="159" cm="1" t="str">
         <f t="array" ref="P160">IF(AG160="","",AC160-R160-Q160)</f>
+        <v/>
       </c>
       <c r="Q160" s="162"/>
       <c r="R160" s="162"/>
@@ -34651,8 +35194,9 @@
       <c r="Z160" s="161"/>
       <c r="AA160" s="161"/>
       <c r="AB160" s="160"/>
-      <c r="AC160" t="str" s="195" cm="1">
+      <c r="AC160" s="195" cm="1" t="str">
         <f t="array" ref="AC160">IF(AG160="","",AG160-AF160)</f>
+        <v/>
       </c>
       <c r="AD160" s="161"/>
       <c r="AE160" s="160"/>
@@ -34699,13 +35243,15 @@
       <c r="C161" s="170"/>
       <c r="D161" s="165"/>
       <c r="E161" s="164"/>
-      <c r="F161" t="str" s="195" cm="1">
+      <c r="F161" s="195" cm="1" t="str">
         <f t="array" ref="F161">IF(AG161="","",I161-H161)</f>
+        <v/>
       </c>
       <c r="G161" s="160"/>
       <c r="H161" s="158"/>
-      <c r="I161" t="str" s="159" cm="1">
+      <c r="I161" s="159" cm="1" t="str">
         <f t="array" ref="I161">IF(AG161="","",P161-K161)</f>
+        <v/>
       </c>
       <c r="J161" s="160"/>
       <c r="K161" s="158"/>
@@ -34713,8 +35259,9 @@
       <c r="M161" s="161"/>
       <c r="N161" s="161"/>
       <c r="O161" s="161"/>
-      <c r="P161" t="str" s="159" cm="1">
+      <c r="P161" s="159" cm="1" t="str">
         <f t="array" ref="P161">IF(AG161="","",AC161-R161-Q161)</f>
+        <v/>
       </c>
       <c r="Q161" s="162"/>
       <c r="R161" s="162"/>
@@ -34728,8 +35275,9 @@
       <c r="Z161" s="161"/>
       <c r="AA161" s="161"/>
       <c r="AB161" s="160"/>
-      <c r="AC161" t="str" s="195" cm="1">
+      <c r="AC161" s="195" cm="1" t="str">
         <f t="array" ref="AC161">IF(AG161="","",AG161-AF161)</f>
+        <v/>
       </c>
       <c r="AD161" s="161"/>
       <c r="AE161" s="160"/>
@@ -34776,13 +35324,15 @@
       <c r="C162" s="170"/>
       <c r="D162" s="165"/>
       <c r="E162" s="164"/>
-      <c r="F162" t="str" s="195" cm="1">
+      <c r="F162" s="195" cm="1" t="str">
         <f t="array" ref="F162">IF(AG162="","",I162-H162)</f>
+        <v/>
       </c>
       <c r="G162" s="160"/>
       <c r="H162" s="158"/>
-      <c r="I162" t="str" s="159" cm="1">
+      <c r="I162" s="159" cm="1" t="str">
         <f t="array" ref="I162">IF(AG162="","",P162-K162)</f>
+        <v/>
       </c>
       <c r="J162" s="160"/>
       <c r="K162" s="158"/>
@@ -34790,8 +35340,9 @@
       <c r="M162" s="161"/>
       <c r="N162" s="161"/>
       <c r="O162" s="161"/>
-      <c r="P162" t="str" s="159" cm="1">
+      <c r="P162" s="159" cm="1" t="str">
         <f t="array" ref="P162">IF(AG162="","",AC162-R162-Q162)</f>
+        <v/>
       </c>
       <c r="Q162" s="162"/>
       <c r="R162" s="162"/>
@@ -34805,8 +35356,9 @@
       <c r="Z162" s="161"/>
       <c r="AA162" s="161"/>
       <c r="AB162" s="160"/>
-      <c r="AC162" t="str" s="195" cm="1">
+      <c r="AC162" s="195" cm="1" t="str">
         <f t="array" ref="AC162">IF(AG162="","",AG162-AF162)</f>
+        <v/>
       </c>
       <c r="AD162" s="161"/>
       <c r="AE162" s="160"/>
@@ -34853,13 +35405,15 @@
       <c r="C163" s="170"/>
       <c r="D163" s="165"/>
       <c r="E163" s="164"/>
-      <c r="F163" t="str" s="195" cm="1">
+      <c r="F163" s="195" cm="1" t="str">
         <f t="array" ref="F163">IF(AG163="","",I163-H163)</f>
+        <v/>
       </c>
       <c r="G163" s="160"/>
       <c r="H163" s="158"/>
-      <c r="I163" t="str" s="159" cm="1">
+      <c r="I163" s="159" cm="1" t="str">
         <f t="array" ref="I163">IF(AG163="","",P163-K163)</f>
+        <v/>
       </c>
       <c r="J163" s="160"/>
       <c r="K163" s="158"/>
@@ -34867,8 +35421,9 @@
       <c r="M163" s="161"/>
       <c r="N163" s="161"/>
       <c r="O163" s="161"/>
-      <c r="P163" t="str" s="159" cm="1">
+      <c r="P163" s="159" cm="1" t="str">
         <f t="array" ref="P163">IF(AG163="","",AC163-R163-Q163)</f>
+        <v/>
       </c>
       <c r="Q163" s="162"/>
       <c r="R163" s="162"/>
@@ -34882,8 +35437,9 @@
       <c r="Z163" s="161"/>
       <c r="AA163" s="161"/>
       <c r="AB163" s="160"/>
-      <c r="AC163" t="str" s="195" cm="1">
+      <c r="AC163" s="195" cm="1" t="str">
         <f t="array" ref="AC163">IF(AG163="","",AG163-AF163)</f>
+        <v/>
       </c>
       <c r="AD163" s="161"/>
       <c r="AE163" s="160"/>
@@ -34930,13 +35486,15 @@
       <c r="C164" s="170"/>
       <c r="D164" s="165"/>
       <c r="E164" s="164"/>
-      <c r="F164" t="str" s="195" cm="1">
+      <c r="F164" s="195" cm="1" t="str">
         <f t="array" ref="F164">IF(AG164="","",I164-H164)</f>
+        <v/>
       </c>
       <c r="G164" s="160"/>
       <c r="H164" s="158"/>
-      <c r="I164" t="str" s="159" cm="1">
+      <c r="I164" s="159" cm="1" t="str">
         <f t="array" ref="I164">IF(AG164="","",P164-K164)</f>
+        <v/>
       </c>
       <c r="J164" s="160"/>
       <c r="K164" s="158"/>
@@ -34944,8 +35502,9 @@
       <c r="M164" s="161"/>
       <c r="N164" s="161"/>
       <c r="O164" s="161"/>
-      <c r="P164" t="str" s="159" cm="1">
+      <c r="P164" s="159" cm="1" t="str">
         <f t="array" ref="P164">IF(AG164="","",AC164-R164-Q164)</f>
+        <v/>
       </c>
       <c r="Q164" s="162"/>
       <c r="R164" s="162"/>
@@ -34959,8 +35518,9 @@
       <c r="Z164" s="161"/>
       <c r="AA164" s="161"/>
       <c r="AB164" s="160"/>
-      <c r="AC164" t="str" s="195" cm="1">
+      <c r="AC164" s="195" cm="1" t="str">
         <f t="array" ref="AC164">IF(AG164="","",AG164-AF164)</f>
+        <v/>
       </c>
       <c r="AD164" s="161"/>
       <c r="AE164" s="160"/>
@@ -35007,13 +35567,15 @@
       <c r="C165" s="170"/>
       <c r="D165" s="165"/>
       <c r="E165" s="164"/>
-      <c r="F165" t="str" s="195" cm="1">
+      <c r="F165" s="195" cm="1" t="str">
         <f t="array" ref="F165">IF(AG165="","",I165-H165)</f>
+        <v/>
       </c>
       <c r="G165" s="160"/>
       <c r="H165" s="158"/>
-      <c r="I165" t="str" s="159" cm="1">
+      <c r="I165" s="159" cm="1" t="str">
         <f t="array" ref="I165">IF(AG165="","",P165-K165)</f>
+        <v/>
       </c>
       <c r="J165" s="160"/>
       <c r="K165" s="158"/>
@@ -35021,8 +35583,9 @@
       <c r="M165" s="161"/>
       <c r="N165" s="161"/>
       <c r="O165" s="161"/>
-      <c r="P165" t="str" s="159" cm="1">
+      <c r="P165" s="159" cm="1" t="str">
         <f t="array" ref="P165">IF(AG165="","",AC165-R165-Q165)</f>
+        <v/>
       </c>
       <c r="Q165" s="162"/>
       <c r="R165" s="162"/>
@@ -35036,8 +35599,9 @@
       <c r="Z165" s="161"/>
       <c r="AA165" s="161"/>
       <c r="AB165" s="160"/>
-      <c r="AC165" t="str" s="195" cm="1">
+      <c r="AC165" s="195" cm="1" t="str">
         <f t="array" ref="AC165">IF(AG165="","",AG165-AF165)</f>
+        <v/>
       </c>
       <c r="AD165" s="161"/>
       <c r="AE165" s="160"/>
@@ -35084,13 +35648,15 @@
       <c r="C166" s="170"/>
       <c r="D166" s="165"/>
       <c r="E166" s="164"/>
-      <c r="F166" t="str" s="195" cm="1">
+      <c r="F166" s="195" cm="1" t="str">
         <f t="array" ref="F166">IF(AG166="","",I166-H166)</f>
+        <v/>
       </c>
       <c r="G166" s="160"/>
       <c r="H166" s="158"/>
-      <c r="I166" t="str" s="159" cm="1">
+      <c r="I166" s="159" cm="1" t="str">
         <f t="array" ref="I166">IF(AG166="","",P166-K166)</f>
+        <v/>
       </c>
       <c r="J166" s="160"/>
       <c r="K166" s="158"/>
@@ -35098,8 +35664,9 @@
       <c r="M166" s="161"/>
       <c r="N166" s="161"/>
       <c r="O166" s="161"/>
-      <c r="P166" t="str" s="159" cm="1">
+      <c r="P166" s="159" cm="1" t="str">
         <f t="array" ref="P166">IF(AG166="","",AC166-R166-Q166)</f>
+        <v/>
       </c>
       <c r="Q166" s="162"/>
       <c r="R166" s="162"/>
@@ -35113,8 +35680,9 @@
       <c r="Z166" s="161"/>
       <c r="AA166" s="161"/>
       <c r="AB166" s="160"/>
-      <c r="AC166" t="str" s="195" cm="1">
+      <c r="AC166" s="195" cm="1" t="str">
         <f t="array" ref="AC166">IF(AG166="","",AG166-AF166)</f>
+        <v/>
       </c>
       <c r="AD166" s="161"/>
       <c r="AE166" s="160"/>
@@ -35161,13 +35729,15 @@
       <c r="C167" s="170"/>
       <c r="D167" s="165"/>
       <c r="E167" s="164"/>
-      <c r="F167" t="str" s="195" cm="1">
+      <c r="F167" s="195" cm="1" t="str">
         <f t="array" ref="F167">IF(AG167="","",I167-H167)</f>
+        <v/>
       </c>
       <c r="G167" s="160"/>
       <c r="H167" s="158"/>
-      <c r="I167" t="str" s="159" cm="1">
+      <c r="I167" s="159" cm="1" t="str">
         <f t="array" ref="I167">IF(AG167="","",P167-K167)</f>
+        <v/>
       </c>
       <c r="J167" s="160"/>
       <c r="K167" s="158"/>
@@ -35175,8 +35745,9 @@
       <c r="M167" s="161"/>
       <c r="N167" s="161"/>
       <c r="O167" s="161"/>
-      <c r="P167" t="str" s="159" cm="1">
+      <c r="P167" s="159" cm="1" t="str">
         <f t="array" ref="P167">IF(AG167="","",AC167-R167-Q167)</f>
+        <v/>
       </c>
       <c r="Q167" s="162"/>
       <c r="R167" s="162"/>
@@ -35190,8 +35761,9 @@
       <c r="Z167" s="161"/>
       <c r="AA167" s="161"/>
       <c r="AB167" s="160"/>
-      <c r="AC167" t="str" s="195" cm="1">
+      <c r="AC167" s="195" cm="1" t="str">
         <f t="array" ref="AC167">IF(AG167="","",AG167-AF167)</f>
+        <v/>
       </c>
       <c r="AD167" s="161"/>
       <c r="AE167" s="160"/>
@@ -35238,13 +35810,15 @@
       <c r="C168" s="170"/>
       <c r="D168" s="165"/>
       <c r="E168" s="164"/>
-      <c r="F168" t="str" s="195" cm="1">
+      <c r="F168" s="195" cm="1" t="str">
         <f t="array" ref="F168">IF(AG168="","",I168-H168)</f>
+        <v/>
       </c>
       <c r="G168" s="160"/>
       <c r="H168" s="158"/>
-      <c r="I168" t="str" s="159" cm="1">
+      <c r="I168" s="159" cm="1" t="str">
         <f t="array" ref="I168">IF(AG168="","",P168-K168)</f>
+        <v/>
       </c>
       <c r="J168" s="160"/>
       <c r="K168" s="158"/>
@@ -35252,8 +35826,9 @@
       <c r="M168" s="161"/>
       <c r="N168" s="161"/>
       <c r="O168" s="161"/>
-      <c r="P168" t="str" s="159" cm="1">
+      <c r="P168" s="159" cm="1" t="str">
         <f t="array" ref="P168">IF(AG168="","",AC168-R168-Q168)</f>
+        <v/>
       </c>
       <c r="Q168" s="162"/>
       <c r="R168" s="162"/>
@@ -35267,8 +35842,9 @@
       <c r="Z168" s="161"/>
       <c r="AA168" s="161"/>
       <c r="AB168" s="160"/>
-      <c r="AC168" t="str" s="195" cm="1">
+      <c r="AC168" s="195" cm="1" t="str">
         <f t="array" ref="AC168">IF(AG168="","",AG168-AF168)</f>
+        <v/>
       </c>
       <c r="AD168" s="161"/>
       <c r="AE168" s="160"/>
@@ -35315,13 +35891,15 @@
       <c r="C169" s="170"/>
       <c r="D169" s="165"/>
       <c r="E169" s="164"/>
-      <c r="F169" t="str" s="195" cm="1">
+      <c r="F169" s="195" cm="1" t="str">
         <f t="array" ref="F169">IF(AG169="","",I169-H169)</f>
+        <v/>
       </c>
       <c r="G169" s="160"/>
       <c r="H169" s="158"/>
-      <c r="I169" t="str" s="159" cm="1">
+      <c r="I169" s="159" cm="1" t="str">
         <f t="array" ref="I169">IF(AG169="","",P169-K169)</f>
+        <v/>
       </c>
       <c r="J169" s="160"/>
       <c r="K169" s="158"/>
@@ -35329,8 +35907,9 @@
       <c r="M169" s="161"/>
       <c r="N169" s="161"/>
       <c r="O169" s="161"/>
-      <c r="P169" t="str" s="159" cm="1">
+      <c r="P169" s="159" cm="1" t="str">
         <f t="array" ref="P169">IF(AG169="","",AC169-R169-Q169)</f>
+        <v/>
       </c>
       <c r="Q169" s="162"/>
       <c r="R169" s="162"/>
@@ -35344,8 +35923,9 @@
       <c r="Z169" s="161"/>
       <c r="AA169" s="161"/>
       <c r="AB169" s="160"/>
-      <c r="AC169" t="str" s="195" cm="1">
+      <c r="AC169" s="195" cm="1" t="str">
         <f t="array" ref="AC169">IF(AG169="","",AG169-AF169)</f>
+        <v/>
       </c>
       <c r="AD169" s="161"/>
       <c r="AE169" s="160"/>
@@ -35392,13 +35972,15 @@
       <c r="C170" s="170"/>
       <c r="D170" s="165"/>
       <c r="E170" s="164"/>
-      <c r="F170" t="str" s="195" cm="1">
+      <c r="F170" s="195" cm="1" t="str">
         <f t="array" ref="F170">IF(AG170="","",I170-H170)</f>
+        <v/>
       </c>
       <c r="G170" s="160"/>
       <c r="H170" s="158"/>
-      <c r="I170" t="str" s="159" cm="1">
+      <c r="I170" s="159" cm="1" t="str">
         <f t="array" ref="I170">IF(AG170="","",P170-K170)</f>
+        <v/>
       </c>
       <c r="J170" s="160"/>
       <c r="K170" s="158"/>
@@ -35406,8 +35988,9 @@
       <c r="M170" s="161"/>
       <c r="N170" s="161"/>
       <c r="O170" s="161"/>
-      <c r="P170" t="str" s="159" cm="1">
+      <c r="P170" s="159" cm="1" t="str">
         <f t="array" ref="P170">IF(AG170="","",AC170-R170-Q170)</f>
+        <v/>
       </c>
       <c r="Q170" s="162"/>
       <c r="R170" s="162"/>
@@ -35421,8 +36004,9 @@
       <c r="Z170" s="161"/>
       <c r="AA170" s="161"/>
       <c r="AB170" s="160"/>
-      <c r="AC170" t="str" s="195" cm="1">
+      <c r="AC170" s="195" cm="1" t="str">
         <f t="array" ref="AC170">IF(AG170="","",AG170-AF170)</f>
+        <v/>
       </c>
       <c r="AD170" s="161"/>
       <c r="AE170" s="160"/>
@@ -35469,13 +36053,15 @@
       <c r="C171" s="170"/>
       <c r="D171" s="165"/>
       <c r="E171" s="164"/>
-      <c r="F171" t="str" s="195" cm="1">
+      <c r="F171" s="195" cm="1" t="str">
         <f t="array" ref="F171">IF(AG171="","",I171-H171)</f>
+        <v/>
       </c>
       <c r="G171" s="160"/>
       <c r="H171" s="158"/>
-      <c r="I171" t="str" s="159" cm="1">
+      <c r="I171" s="159" cm="1" t="str">
         <f t="array" ref="I171">IF(AG171="","",P171-K171)</f>
+        <v/>
       </c>
       <c r="J171" s="160"/>
       <c r="K171" s="158"/>
@@ -35483,8 +36069,9 @@
       <c r="M171" s="161"/>
       <c r="N171" s="161"/>
       <c r="O171" s="161"/>
-      <c r="P171" t="str" s="159" cm="1">
+      <c r="P171" s="159" cm="1" t="str">
         <f t="array" ref="P171">IF(AG171="","",AC171-R171-Q171)</f>
+        <v/>
       </c>
       <c r="Q171" s="162"/>
       <c r="R171" s="162"/>
@@ -35498,8 +36085,9 @@
       <c r="Z171" s="161"/>
       <c r="AA171" s="161"/>
       <c r="AB171" s="160"/>
-      <c r="AC171" t="str" s="195" cm="1">
+      <c r="AC171" s="195" cm="1" t="str">
         <f t="array" ref="AC171">IF(AG171="","",AG171-AF171)</f>
+        <v/>
       </c>
       <c r="AD171" s="161"/>
       <c r="AE171" s="160"/>
@@ -35546,13 +36134,15 @@
       <c r="C172" s="170"/>
       <c r="D172" s="165"/>
       <c r="E172" s="164"/>
-      <c r="F172" t="str" s="195" cm="1">
+      <c r="F172" s="195" cm="1" t="str">
         <f t="array" ref="F172">IF(AG172="","",I172-H172)</f>
+        <v/>
       </c>
       <c r="G172" s="160"/>
       <c r="H172" s="158"/>
-      <c r="I172" t="str" s="159" cm="1">
+      <c r="I172" s="159" cm="1" t="str">
         <f t="array" ref="I172">IF(AG172="","",P172-K172)</f>
+        <v/>
       </c>
       <c r="J172" s="160"/>
       <c r="K172" s="158"/>
@@ -35560,8 +36150,9 @@
       <c r="M172" s="161"/>
       <c r="N172" s="161"/>
       <c r="O172" s="161"/>
-      <c r="P172" t="str" s="159" cm="1">
+      <c r="P172" s="159" cm="1" t="str">
         <f t="array" ref="P172">IF(AG172="","",AC172-R172-Q172)</f>
+        <v/>
       </c>
       <c r="Q172" s="162"/>
       <c r="R172" s="162"/>
@@ -35575,8 +36166,9 @@
       <c r="Z172" s="161"/>
       <c r="AA172" s="161"/>
       <c r="AB172" s="160"/>
-      <c r="AC172" t="str" s="195" cm="1">
+      <c r="AC172" s="195" cm="1" t="str">
         <f t="array" ref="AC172">IF(AG172="","",AG172-AF172)</f>
+        <v/>
       </c>
       <c r="AD172" s="161"/>
       <c r="AE172" s="160"/>
@@ -35623,13 +36215,15 @@
       <c r="C173" s="170"/>
       <c r="D173" s="165"/>
       <c r="E173" s="164"/>
-      <c r="F173" t="str" s="195" cm="1">
+      <c r="F173" s="195" cm="1" t="str">
         <f t="array" ref="F173">IF(AG173="","",I173-H173)</f>
+        <v/>
       </c>
       <c r="G173" s="160"/>
       <c r="H173" s="158"/>
-      <c r="I173" t="str" s="159" cm="1">
+      <c r="I173" s="159" cm="1" t="str">
         <f t="array" ref="I173">IF(AG173="","",P173-K173)</f>
+        <v/>
       </c>
       <c r="J173" s="160"/>
       <c r="K173" s="158"/>
@@ -35637,8 +36231,9 @@
       <c r="M173" s="161"/>
       <c r="N173" s="161"/>
       <c r="O173" s="161"/>
-      <c r="P173" t="str" s="159" cm="1">
+      <c r="P173" s="159" cm="1" t="str">
         <f t="array" ref="P173">IF(AG173="","",AC173-R173-Q173)</f>
+        <v/>
       </c>
       <c r="Q173" s="162"/>
       <c r="R173" s="162"/>
@@ -35652,8 +36247,9 @@
       <c r="Z173" s="161"/>
       <c r="AA173" s="161"/>
       <c r="AB173" s="160"/>
-      <c r="AC173" t="str" s="195" cm="1">
+      <c r="AC173" s="195" cm="1" t="str">
         <f t="array" ref="AC173">IF(AG173="","",AG173-AF173)</f>
+        <v/>
       </c>
       <c r="AD173" s="161"/>
       <c r="AE173" s="160"/>
@@ -35700,13 +36296,15 @@
       <c r="C174" s="170"/>
       <c r="D174" s="165"/>
       <c r="E174" s="164"/>
-      <c r="F174" t="str" s="195" cm="1">
+      <c r="F174" s="195" cm="1" t="str">
         <f t="array" ref="F174">IF(AG174="","",I174-H174)</f>
+        <v/>
       </c>
       <c r="G174" s="160"/>
       <c r="H174" s="158"/>
-      <c r="I174" t="str" s="159" cm="1">
+      <c r="I174" s="159" cm="1" t="str">
         <f t="array" ref="I174">IF(AG174="","",P174-K174)</f>
+        <v/>
       </c>
       <c r="J174" s="160"/>
       <c r="K174" s="158"/>
@@ -35714,8 +36312,9 @@
       <c r="M174" s="161"/>
       <c r="N174" s="161"/>
       <c r="O174" s="161"/>
-      <c r="P174" t="str" s="159" cm="1">
+      <c r="P174" s="159" cm="1" t="str">
         <f t="array" ref="P174">IF(AG174="","",AC174-R174-Q174)</f>
+        <v/>
       </c>
       <c r="Q174" s="162"/>
       <c r="R174" s="162"/>
@@ -35729,8 +36328,9 @@
       <c r="Z174" s="161"/>
       <c r="AA174" s="161"/>
       <c r="AB174" s="160"/>
-      <c r="AC174" t="str" s="195" cm="1">
+      <c r="AC174" s="195" cm="1" t="str">
         <f t="array" ref="AC174">IF(AG174="","",AG174-AF174)</f>
+        <v/>
       </c>
       <c r="AD174" s="161"/>
       <c r="AE174" s="160"/>
@@ -35777,13 +36377,15 @@
       <c r="C175" s="170"/>
       <c r="D175" s="165"/>
       <c r="E175" s="164"/>
-      <c r="F175" t="str" s="195" cm="1">
+      <c r="F175" s="195" cm="1" t="str">
         <f t="array" ref="F175">IF(AG175="","",I175-H175)</f>
+        <v/>
       </c>
       <c r="G175" s="160"/>
       <c r="H175" s="158"/>
-      <c r="I175" t="str" s="159" cm="1">
+      <c r="I175" s="159" cm="1" t="str">
         <f t="array" ref="I175">IF(AG175="","",P175-K175)</f>
+        <v/>
       </c>
       <c r="J175" s="160"/>
       <c r="K175" s="158"/>
@@ -35791,8 +36393,9 @@
       <c r="M175" s="161"/>
       <c r="N175" s="161"/>
       <c r="O175" s="161"/>
-      <c r="P175" t="str" s="159" cm="1">
+      <c r="P175" s="159" cm="1" t="str">
         <f t="array" ref="P175">IF(AG175="","",AC175-R175-Q175)</f>
+        <v/>
       </c>
       <c r="Q175" s="162"/>
       <c r="R175" s="162"/>
@@ -35806,8 +36409,9 @@
       <c r="Z175" s="161"/>
       <c r="AA175" s="161"/>
       <c r="AB175" s="160"/>
-      <c r="AC175" t="str" s="195" cm="1">
+      <c r="AC175" s="195" cm="1" t="str">
         <f t="array" ref="AC175">IF(AG175="","",AG175-AF175)</f>
+        <v/>
       </c>
       <c r="AD175" s="161"/>
       <c r="AE175" s="160"/>
@@ -35854,13 +36458,15 @@
       <c r="C176" s="170"/>
       <c r="D176" s="165"/>
       <c r="E176" s="164"/>
-      <c r="F176" t="str" s="195" cm="1">
+      <c r="F176" s="195" cm="1" t="str">
         <f t="array" ref="F176">IF(AG176="","",I176-H176)</f>
+        <v/>
       </c>
       <c r="G176" s="160"/>
       <c r="H176" s="158"/>
-      <c r="I176" t="str" s="159" cm="1">
+      <c r="I176" s="159" cm="1" t="str">
         <f t="array" ref="I176">IF(AG176="","",P176-K176)</f>
+        <v/>
       </c>
       <c r="J176" s="160"/>
       <c r="K176" s="158"/>
@@ -35868,8 +36474,9 @@
       <c r="M176" s="161"/>
       <c r="N176" s="161"/>
       <c r="O176" s="161"/>
-      <c r="P176" t="str" s="159" cm="1">
+      <c r="P176" s="159" cm="1" t="str">
         <f t="array" ref="P176">IF(AG176="","",AC176-R176-Q176)</f>
+        <v/>
       </c>
       <c r="Q176" s="162"/>
       <c r="R176" s="162"/>
@@ -35883,8 +36490,9 @@
       <c r="Z176" s="161"/>
       <c r="AA176" s="161"/>
       <c r="AB176" s="160"/>
-      <c r="AC176" t="str" s="195" cm="1">
+      <c r="AC176" s="195" cm="1" t="str">
         <f t="array" ref="AC176">IF(AG176="","",AG176-AF176)</f>
+        <v/>
       </c>
       <c r="AD176" s="161"/>
       <c r="AE176" s="160"/>
@@ -35931,13 +36539,15 @@
       <c r="C177" s="170"/>
       <c r="D177" s="165"/>
       <c r="E177" s="164"/>
-      <c r="F177" t="str" s="195" cm="1">
+      <c r="F177" s="195" cm="1" t="str">
         <f t="array" ref="F177">IF(AG177="","",I177-H177)</f>
+        <v/>
       </c>
       <c r="G177" s="160"/>
       <c r="H177" s="158"/>
-      <c r="I177" t="str" s="159" cm="1">
+      <c r="I177" s="159" cm="1" t="str">
         <f t="array" ref="I177">IF(AG177="","",P177-K177)</f>
+        <v/>
       </c>
       <c r="J177" s="160"/>
       <c r="K177" s="158"/>
@@ -35945,8 +36555,9 @@
       <c r="M177" s="161"/>
       <c r="N177" s="161"/>
       <c r="O177" s="161"/>
-      <c r="P177" t="str" s="159" cm="1">
+      <c r="P177" s="159" cm="1" t="str">
         <f t="array" ref="P177">IF(AG177="","",AC177-R177-Q177)</f>
+        <v/>
       </c>
       <c r="Q177" s="162"/>
       <c r="R177" s="162"/>
@@ -35960,8 +36571,9 @@
       <c r="Z177" s="161"/>
       <c r="AA177" s="161"/>
       <c r="AB177" s="160"/>
-      <c r="AC177" t="str" s="195" cm="1">
+      <c r="AC177" s="195" cm="1" t="str">
         <f t="array" ref="AC177">IF(AG177="","",AG177-AF177)</f>
+        <v/>
       </c>
       <c r="AD177" s="161"/>
       <c r="AE177" s="160"/>
@@ -36008,13 +36620,15 @@
       <c r="C178" s="170"/>
       <c r="D178" s="165"/>
       <c r="E178" s="164"/>
-      <c r="F178" t="str" s="195" cm="1">
+      <c r="F178" s="195" cm="1" t="str">
         <f t="array" ref="F178">IF(AG178="","",I178-H178)</f>
+        <v/>
       </c>
       <c r="G178" s="160"/>
       <c r="H178" s="158"/>
-      <c r="I178" t="str" s="159" cm="1">
+      <c r="I178" s="159" cm="1" t="str">
         <f t="array" ref="I178">IF(AG178="","",P178-K178)</f>
+        <v/>
       </c>
       <c r="J178" s="160"/>
       <c r="K178" s="158"/>
@@ -36022,8 +36636,9 @@
       <c r="M178" s="161"/>
       <c r="N178" s="161"/>
       <c r="O178" s="161"/>
-      <c r="P178" t="str" s="159" cm="1">
+      <c r="P178" s="159" cm="1" t="str">
         <f t="array" ref="P178">IF(AG178="","",AC178-R178-Q178)</f>
+        <v/>
       </c>
       <c r="Q178" s="162"/>
       <c r="R178" s="162"/>
@@ -36037,8 +36652,9 @@
       <c r="Z178" s="161"/>
       <c r="AA178" s="161"/>
       <c r="AB178" s="160"/>
-      <c r="AC178" t="str" s="195" cm="1">
+      <c r="AC178" s="195" cm="1" t="str">
         <f t="array" ref="AC178">IF(AG178="","",AG178-AF178)</f>
+        <v/>
       </c>
       <c r="AD178" s="161"/>
       <c r="AE178" s="160"/>
@@ -36085,13 +36701,15 @@
       <c r="C179" s="170"/>
       <c r="D179" s="165"/>
       <c r="E179" s="164"/>
-      <c r="F179" t="str" s="195" cm="1">
+      <c r="F179" s="195" cm="1" t="str">
         <f t="array" ref="F179">IF(AG179="","",I179-H179)</f>
+        <v/>
       </c>
       <c r="G179" s="160"/>
       <c r="H179" s="158"/>
-      <c r="I179" t="str" s="159" cm="1">
+      <c r="I179" s="159" cm="1" t="str">
         <f t="array" ref="I179">IF(AG179="","",P179-K179)</f>
+        <v/>
       </c>
       <c r="J179" s="160"/>
       <c r="K179" s="158"/>
@@ -36099,8 +36717,9 @@
       <c r="M179" s="161"/>
       <c r="N179" s="161"/>
       <c r="O179" s="161"/>
-      <c r="P179" t="str" s="159" cm="1">
+      <c r="P179" s="159" cm="1" t="str">
         <f t="array" ref="P179">IF(AG179="","",AC179-R179-Q179)</f>
+        <v/>
       </c>
       <c r="Q179" s="162"/>
       <c r="R179" s="162"/>
@@ -36114,8 +36733,9 @@
       <c r="Z179" s="161"/>
       <c r="AA179" s="161"/>
       <c r="AB179" s="160"/>
-      <c r="AC179" t="str" s="195" cm="1">
+      <c r="AC179" s="195" cm="1" t="str">
         <f t="array" ref="AC179">IF(AG179="","",AG179-AF179)</f>
+        <v/>
       </c>
       <c r="AD179" s="161"/>
       <c r="AE179" s="160"/>
@@ -36162,13 +36782,15 @@
       <c r="C180" s="170"/>
       <c r="D180" s="165"/>
       <c r="E180" s="164"/>
-      <c r="F180" t="str" s="195" cm="1">
+      <c r="F180" s="195" cm="1" t="str">
         <f t="array" ref="F180">IF(AG180="","",I180-H180)</f>
+        <v/>
       </c>
       <c r="G180" s="160"/>
       <c r="H180" s="158"/>
-      <c r="I180" t="str" s="159" cm="1">
+      <c r="I180" s="159" cm="1" t="str">
         <f t="array" ref="I180">IF(AG180="","",P180-K180)</f>
+        <v/>
       </c>
       <c r="J180" s="160"/>
       <c r="K180" s="158"/>
@@ -36176,8 +36798,9 @@
       <c r="M180" s="161"/>
       <c r="N180" s="161"/>
       <c r="O180" s="161"/>
-      <c r="P180" t="str" s="159" cm="1">
+      <c r="P180" s="159" cm="1" t="str">
         <f t="array" ref="P180">IF(AG180="","",AC180-R180-Q180)</f>
+        <v/>
       </c>
       <c r="Q180" s="162"/>
       <c r="R180" s="162"/>
@@ -36191,8 +36814,9 @@
       <c r="Z180" s="161"/>
       <c r="AA180" s="161"/>
       <c r="AB180" s="160"/>
-      <c r="AC180" t="str" s="195" cm="1">
+      <c r="AC180" s="195" cm="1" t="str">
         <f t="array" ref="AC180">IF(AG180="","",AG180-AF180)</f>
+        <v/>
       </c>
       <c r="AD180" s="161"/>
       <c r="AE180" s="160"/>
@@ -36239,13 +36863,15 @@
       <c r="C181" s="170"/>
       <c r="D181" s="165"/>
       <c r="E181" s="164"/>
-      <c r="F181" t="str" s="195" cm="1">
+      <c r="F181" s="195" cm="1" t="str">
         <f t="array" ref="F181">IF(AG181="","",I181-H181)</f>
+        <v/>
       </c>
       <c r="G181" s="160"/>
       <c r="H181" s="158"/>
-      <c r="I181" t="str" s="159" cm="1">
+      <c r="I181" s="159" cm="1" t="str">
         <f t="array" ref="I181">IF(AG181="","",P181-K181)</f>
+        <v/>
       </c>
       <c r="J181" s="160"/>
       <c r="K181" s="158"/>
@@ -36253,8 +36879,9 @@
       <c r="M181" s="161"/>
       <c r="N181" s="161"/>
       <c r="O181" s="161"/>
-      <c r="P181" t="str" s="159" cm="1">
+      <c r="P181" s="159" cm="1" t="str">
         <f t="array" ref="P181">IF(AG181="","",AC181-R181-Q181)</f>
+        <v/>
       </c>
       <c r="Q181" s="162"/>
       <c r="R181" s="162"/>
@@ -36268,8 +36895,9 @@
       <c r="Z181" s="161"/>
       <c r="AA181" s="161"/>
       <c r="AB181" s="160"/>
-      <c r="AC181" t="str" s="195" cm="1">
+      <c r="AC181" s="195" cm="1" t="str">
         <f t="array" ref="AC181">IF(AG181="","",AG181-AF181)</f>
+        <v/>
       </c>
       <c r="AD181" s="161"/>
       <c r="AE181" s="160"/>
@@ -36316,13 +36944,15 @@
       <c r="C182" s="170"/>
       <c r="D182" s="165"/>
       <c r="E182" s="164"/>
-      <c r="F182" t="str" s="195" cm="1">
+      <c r="F182" s="195" cm="1" t="str">
         <f t="array" ref="F182">IF(AG182="","",I182-H182)</f>
+        <v/>
       </c>
       <c r="G182" s="160"/>
       <c r="H182" s="158"/>
-      <c r="I182" t="str" s="159" cm="1">
+      <c r="I182" s="159" cm="1" t="str">
         <f t="array" ref="I182">IF(AG182="","",P182-K182)</f>
+        <v/>
       </c>
       <c r="J182" s="160"/>
       <c r="K182" s="158"/>
@@ -36330,8 +36960,9 @@
       <c r="M182" s="161"/>
       <c r="N182" s="161"/>
       <c r="O182" s="161"/>
-      <c r="P182" t="str" s="159" cm="1">
+      <c r="P182" s="159" cm="1" t="str">
         <f t="array" ref="P182">IF(AG182="","",AC182-R182-Q182)</f>
+        <v/>
       </c>
       <c r="Q182" s="162"/>
       <c r="R182" s="162"/>
@@ -36345,8 +36976,9 @@
       <c r="Z182" s="161"/>
       <c r="AA182" s="161"/>
       <c r="AB182" s="160"/>
-      <c r="AC182" t="str" s="195" cm="1">
+      <c r="AC182" s="195" cm="1" t="str">
         <f t="array" ref="AC182">IF(AG182="","",AG182-AF182)</f>
+        <v/>
       </c>
       <c r="AD182" s="161"/>
       <c r="AE182" s="160"/>
@@ -36393,13 +37025,15 @@
       <c r="C183" s="170"/>
       <c r="D183" s="165"/>
       <c r="E183" s="164"/>
-      <c r="F183" t="str" s="195" cm="1">
+      <c r="F183" s="195" cm="1" t="str">
         <f t="array" ref="F183">IF(AG183="","",I183-H183)</f>
+        <v/>
       </c>
       <c r="G183" s="160"/>
       <c r="H183" s="158"/>
-      <c r="I183" t="str" s="159" cm="1">
+      <c r="I183" s="159" cm="1" t="str">
         <f t="array" ref="I183">IF(AG183="","",P183-K183)</f>
+        <v/>
       </c>
       <c r="J183" s="160"/>
       <c r="K183" s="158"/>
@@ -36407,8 +37041,9 @@
       <c r="M183" s="161"/>
       <c r="N183" s="161"/>
       <c r="O183" s="161"/>
-      <c r="P183" t="str" s="159" cm="1">
+      <c r="P183" s="159" cm="1" t="str">
         <f t="array" ref="P183">IF(AG183="","",AC183-R183-Q183)</f>
+        <v/>
       </c>
       <c r="Q183" s="162"/>
       <c r="R183" s="162"/>
@@ -36422,8 +37057,9 @@
       <c r="Z183" s="161"/>
       <c r="AA183" s="161"/>
       <c r="AB183" s="160"/>
-      <c r="AC183" t="str" s="195" cm="1">
+      <c r="AC183" s="195" cm="1" t="str">
         <f t="array" ref="AC183">IF(AG183="","",AG183-AF183)</f>
+        <v/>
       </c>
       <c r="AD183" s="161"/>
       <c r="AE183" s="160"/>
@@ -36470,13 +37106,15 @@
       <c r="C184" s="170"/>
       <c r="D184" s="165"/>
       <c r="E184" s="164"/>
-      <c r="F184" t="str" s="195" cm="1">
+      <c r="F184" s="195" cm="1" t="str">
         <f t="array" ref="F184">IF(AG184="","",I184-H184)</f>
+        <v/>
       </c>
       <c r="G184" s="160"/>
       <c r="H184" s="158"/>
-      <c r="I184" t="str" s="159" cm="1">
+      <c r="I184" s="159" cm="1" t="str">
         <f t="array" ref="I184">IF(AG184="","",P184-K184)</f>
+        <v/>
       </c>
       <c r="J184" s="160"/>
       <c r="K184" s="158"/>
@@ -36484,8 +37122,9 @@
       <c r="M184" s="161"/>
       <c r="N184" s="161"/>
       <c r="O184" s="161"/>
-      <c r="P184" t="str" s="159" cm="1">
+      <c r="P184" s="159" cm="1" t="str">
         <f t="array" ref="P184">IF(AG184="","",AC184-R184-Q184)</f>
+        <v/>
       </c>
       <c r="Q184" s="162"/>
       <c r="R184" s="162"/>
@@ -36499,8 +37138,9 @@
       <c r="Z184" s="161"/>
       <c r="AA184" s="161"/>
       <c r="AB184" s="160"/>
-      <c r="AC184" t="str" s="195" cm="1">
+      <c r="AC184" s="195" cm="1" t="str">
         <f t="array" ref="AC184">IF(AG184="","",AG184-AF184)</f>
+        <v/>
       </c>
       <c r="AD184" s="161"/>
       <c r="AE184" s="160"/>
@@ -36547,13 +37187,15 @@
       <c r="C185" s="170"/>
       <c r="D185" s="165"/>
       <c r="E185" s="164"/>
-      <c r="F185" t="str" s="195" cm="1">
+      <c r="F185" s="195" cm="1" t="str">
         <f t="array" ref="F185">IF(AG185="","",I185-H185)</f>
+        <v/>
       </c>
       <c r="G185" s="160"/>
       <c r="H185" s="158"/>
-      <c r="I185" t="str" s="159" cm="1">
+      <c r="I185" s="159" cm="1" t="str">
         <f t="array" ref="I185">IF(AG185="","",P185-K185)</f>
+        <v/>
       </c>
       <c r="J185" s="160"/>
       <c r="K185" s="158"/>
@@ -36561,8 +37203,9 @@
       <c r="M185" s="161"/>
       <c r="N185" s="161"/>
       <c r="O185" s="161"/>
-      <c r="P185" t="str" s="159" cm="1">
+      <c r="P185" s="159" cm="1" t="str">
         <f t="array" ref="P185">IF(AG185="","",AC185-R185-Q185)</f>
+        <v/>
       </c>
       <c r="Q185" s="162"/>
       <c r="R185" s="162"/>
@@ -36576,8 +37219,9 @@
       <c r="Z185" s="161"/>
       <c r="AA185" s="161"/>
       <c r="AB185" s="160"/>
-      <c r="AC185" t="str" s="195" cm="1">
+      <c r="AC185" s="195" cm="1" t="str">
         <f t="array" ref="AC185">IF(AG185="","",AG185-AF185)</f>
+        <v/>
       </c>
       <c r="AD185" s="161"/>
       <c r="AE185" s="160"/>
@@ -36624,13 +37268,15 @@
       <c r="C186" s="170"/>
       <c r="D186" s="165"/>
       <c r="E186" s="164"/>
-      <c r="F186" t="str" s="195" cm="1">
+      <c r="F186" s="195" cm="1" t="str">
         <f t="array" ref="F186">IF(AG186="","",I186-H186)</f>
+        <v/>
       </c>
       <c r="G186" s="160"/>
       <c r="H186" s="158"/>
-      <c r="I186" t="str" s="159" cm="1">
+      <c r="I186" s="159" cm="1" t="str">
         <f t="array" ref="I186">IF(AG186="","",P186-K186)</f>
+        <v/>
       </c>
       <c r="J186" s="160"/>
       <c r="K186" s="158"/>
@@ -36638,8 +37284,9 @@
       <c r="M186" s="161"/>
       <c r="N186" s="161"/>
       <c r="O186" s="161"/>
-      <c r="P186" t="str" s="159" cm="1">
+      <c r="P186" s="159" cm="1" t="str">
         <f t="array" ref="P186">IF(AG186="","",AC186-R186-Q186)</f>
+        <v/>
       </c>
       <c r="Q186" s="162"/>
       <c r="R186" s="162"/>
@@ -36653,8 +37300,9 @@
       <c r="Z186" s="161"/>
       <c r="AA186" s="161"/>
       <c r="AB186" s="160"/>
-      <c r="AC186" t="str" s="195" cm="1">
+      <c r="AC186" s="195" cm="1" t="str">
         <f t="array" ref="AC186">IF(AG186="","",AG186-AF186)</f>
+        <v/>
       </c>
       <c r="AD186" s="161"/>
       <c r="AE186" s="160"/>
@@ -36701,13 +37349,15 @@
       <c r="C187" s="170"/>
       <c r="D187" s="165"/>
       <c r="E187" s="164"/>
-      <c r="F187" t="str" s="195" cm="1">
+      <c r="F187" s="195" cm="1" t="str">
         <f t="array" ref="F187">IF(AG187="","",I187-H187)</f>
+        <v/>
       </c>
       <c r="G187" s="160"/>
       <c r="H187" s="158"/>
-      <c r="I187" t="str" s="159" cm="1">
+      <c r="I187" s="159" cm="1" t="str">
         <f t="array" ref="I187">IF(AG187="","",P187-K187)</f>
+        <v/>
       </c>
       <c r="J187" s="160"/>
       <c r="K187" s="158"/>
@@ -36715,8 +37365,9 @@
       <c r="M187" s="161"/>
       <c r="N187" s="161"/>
       <c r="O187" s="161"/>
-      <c r="P187" t="str" s="159" cm="1">
+      <c r="P187" s="159" cm="1" t="str">
         <f t="array" ref="P187">IF(AG187="","",AC187-R187-Q187)</f>
+        <v/>
       </c>
       <c r="Q187" s="162"/>
       <c r="R187" s="162"/>
@@ -36730,8 +37381,9 @@
       <c r="Z187" s="161"/>
       <c r="AA187" s="161"/>
       <c r="AB187" s="160"/>
-      <c r="AC187" t="str" s="195" cm="1">
+      <c r="AC187" s="195" cm="1" t="str">
         <f t="array" ref="AC187">IF(AG187="","",AG187-AF187)</f>
+        <v/>
       </c>
       <c r="AD187" s="161"/>
       <c r="AE187" s="160"/>
@@ -36778,13 +37430,15 @@
       <c r="C188" s="170"/>
       <c r="D188" s="165"/>
       <c r="E188" s="164"/>
-      <c r="F188" t="str" s="195" cm="1">
+      <c r="F188" s="195" cm="1" t="str">
         <f t="array" ref="F188">IF(AG188="","",I188-H188)</f>
+        <v/>
       </c>
       <c r="G188" s="160"/>
       <c r="H188" s="158"/>
-      <c r="I188" t="str" s="159" cm="1">
+      <c r="I188" s="159" cm="1" t="str">
         <f t="array" ref="I188">IF(AG188="","",P188-K188)</f>
+        <v/>
       </c>
       <c r="J188" s="160"/>
       <c r="K188" s="158"/>
@@ -36792,8 +37446,9 @@
       <c r="M188" s="161"/>
       <c r="N188" s="161"/>
       <c r="O188" s="161"/>
-      <c r="P188" t="str" s="159" cm="1">
+      <c r="P188" s="159" cm="1" t="str">
         <f t="array" ref="P188">IF(AG188="","",AC188-R188-Q188)</f>
+        <v/>
       </c>
       <c r="Q188" s="162"/>
       <c r="R188" s="162"/>
@@ -36807,8 +37462,9 @@
       <c r="Z188" s="161"/>
       <c r="AA188" s="161"/>
       <c r="AB188" s="160"/>
-      <c r="AC188" t="str" s="195" cm="1">
+      <c r="AC188" s="195" cm="1" t="str">
         <f t="array" ref="AC188">IF(AG188="","",AG188-AF188)</f>
+        <v/>
       </c>
       <c r="AD188" s="161"/>
       <c r="AE188" s="160"/>
@@ -36855,13 +37511,15 @@
       <c r="C189" s="170"/>
       <c r="D189" s="165"/>
       <c r="E189" s="164"/>
-      <c r="F189" t="str" s="195" cm="1">
+      <c r="F189" s="195" cm="1" t="str">
         <f t="array" ref="F189">IF(AG189="","",I189-H189)</f>
+        <v/>
       </c>
       <c r="G189" s="160"/>
       <c r="H189" s="158"/>
-      <c r="I189" t="str" s="159" cm="1">
+      <c r="I189" s="159" cm="1" t="str">
         <f t="array" ref="I189">IF(AG189="","",P189-K189)</f>
+        <v/>
       </c>
       <c r="J189" s="160"/>
       <c r="K189" s="158"/>
@@ -36869,8 +37527,9 @@
       <c r="M189" s="161"/>
       <c r="N189" s="161"/>
       <c r="O189" s="161"/>
-      <c r="P189" t="str" s="159" cm="1">
+      <c r="P189" s="159" cm="1" t="str">
         <f t="array" ref="P189">IF(AG189="","",AC189-R189-Q189)</f>
+        <v/>
       </c>
       <c r="Q189" s="162"/>
       <c r="R189" s="162"/>
@@ -36884,8 +37543,9 @@
       <c r="Z189" s="161"/>
       <c r="AA189" s="161"/>
       <c r="AB189" s="160"/>
-      <c r="AC189" t="str" s="195" cm="1">
+      <c r="AC189" s="195" cm="1" t="str">
         <f t="array" ref="AC189">IF(AG189="","",AG189-AF189)</f>
+        <v/>
       </c>
       <c r="AD189" s="161"/>
       <c r="AE189" s="160"/>
@@ -36932,13 +37592,15 @@
       <c r="C190" s="170"/>
       <c r="D190" s="165"/>
       <c r="E190" s="164"/>
-      <c r="F190" t="str" s="195" cm="1">
+      <c r="F190" s="195" cm="1" t="str">
         <f t="array" ref="F190">IF(AG190="","",I190-H190)</f>
+        <v/>
       </c>
       <c r="G190" s="160"/>
       <c r="H190" s="158"/>
-      <c r="I190" t="str" s="159" cm="1">
+      <c r="I190" s="159" cm="1" t="str">
         <f t="array" ref="I190">IF(AG190="","",P190-K190)</f>
+        <v/>
       </c>
       <c r="J190" s="160"/>
       <c r="K190" s="158"/>
@@ -36946,8 +37608,9 @@
       <c r="M190" s="161"/>
       <c r="N190" s="161"/>
       <c r="O190" s="161"/>
-      <c r="P190" t="str" s="159" cm="1">
+      <c r="P190" s="159" cm="1" t="str">
         <f t="array" ref="P190">IF(AG190="","",AC190-R190-Q190)</f>
+        <v/>
       </c>
       <c r="Q190" s="162"/>
       <c r="R190" s="162"/>
@@ -36961,8 +37624,9 @@
       <c r="Z190" s="161"/>
       <c r="AA190" s="161"/>
       <c r="AB190" s="160"/>
-      <c r="AC190" t="str" s="195" cm="1">
+      <c r="AC190" s="195" cm="1" t="str">
         <f t="array" ref="AC190">IF(AG190="","",AG190-AF190)</f>
+        <v/>
       </c>
       <c r="AD190" s="161"/>
       <c r="AE190" s="160"/>
@@ -37009,13 +37673,15 @@
       <c r="C191" s="170"/>
       <c r="D191" s="165"/>
       <c r="E191" s="164"/>
-      <c r="F191" t="str" s="195" cm="1">
+      <c r="F191" s="195" cm="1" t="str">
         <f t="array" ref="F191">IF(AG191="","",I191-H191)</f>
+        <v/>
       </c>
       <c r="G191" s="160"/>
       <c r="H191" s="158"/>
-      <c r="I191" t="str" s="159" cm="1">
+      <c r="I191" s="159" cm="1" t="str">
         <f t="array" ref="I191">IF(AG191="","",P191-K191)</f>
+        <v/>
       </c>
       <c r="J191" s="160"/>
       <c r="K191" s="158"/>
@@ -37023,8 +37689,9 @@
       <c r="M191" s="161"/>
       <c r="N191" s="161"/>
       <c r="O191" s="161"/>
-      <c r="P191" t="str" s="159" cm="1">
+      <c r="P191" s="159" cm="1" t="str">
         <f t="array" ref="P191">IF(AG191="","",AC191-R191-Q191)</f>
+        <v/>
       </c>
       <c r="Q191" s="162"/>
       <c r="R191" s="162"/>
@@ -37038,8 +37705,9 @@
       <c r="Z191" s="161"/>
       <c r="AA191" s="161"/>
       <c r="AB191" s="160"/>
-      <c r="AC191" t="str" s="195" cm="1">
+      <c r="AC191" s="195" cm="1" t="str">
         <f t="array" ref="AC191">IF(AG191="","",AG191-AF191)</f>
+        <v/>
       </c>
       <c r="AD191" s="161"/>
       <c r="AE191" s="160"/>
@@ -37086,13 +37754,15 @@
       <c r="C192" s="170"/>
       <c r="D192" s="165"/>
       <c r="E192" s="164"/>
-      <c r="F192" t="str" s="195" cm="1">
+      <c r="F192" s="195" cm="1" t="str">
         <f t="array" ref="F192">IF(AG192="","",I192-H192)</f>
+        <v/>
       </c>
       <c r="G192" s="160"/>
       <c r="H192" s="158"/>
-      <c r="I192" t="str" s="159" cm="1">
+      <c r="I192" s="159" cm="1" t="str">
         <f t="array" ref="I192">IF(AG192="","",P192-K192)</f>
+        <v/>
       </c>
       <c r="J192" s="160"/>
       <c r="K192" s="158"/>
@@ -37100,8 +37770,9 @@
       <c r="M192" s="161"/>
       <c r="N192" s="161"/>
       <c r="O192" s="161"/>
-      <c r="P192" t="str" s="159" cm="1">
+      <c r="P192" s="159" cm="1" t="str">
         <f t="array" ref="P192">IF(AG192="","",AC192-R192-Q192)</f>
+        <v/>
       </c>
       <c r="Q192" s="162"/>
       <c r="R192" s="162"/>
@@ -37115,8 +37786,9 @@
       <c r="Z192" s="161"/>
       <c r="AA192" s="161"/>
       <c r="AB192" s="160"/>
-      <c r="AC192" t="str" s="195" cm="1">
+      <c r="AC192" s="195" cm="1" t="str">
         <f t="array" ref="AC192">IF(AG192="","",AG192-AF192)</f>
+        <v/>
       </c>
       <c r="AD192" s="161"/>
       <c r="AE192" s="160"/>
@@ -37163,13 +37835,15 @@
       <c r="C193" s="170"/>
       <c r="D193" s="165"/>
       <c r="E193" s="164"/>
-      <c r="F193" t="str" s="195" cm="1">
+      <c r="F193" s="195" cm="1" t="str">
         <f t="array" ref="F193">IF(AG193="","",I193-H193)</f>
+        <v/>
       </c>
       <c r="G193" s="160"/>
       <c r="H193" s="158"/>
-      <c r="I193" t="str" s="159" cm="1">
+      <c r="I193" s="159" cm="1" t="str">
         <f t="array" ref="I193">IF(AG193="","",P193-K193)</f>
+        <v/>
       </c>
       <c r="J193" s="160"/>
       <c r="K193" s="158"/>
@@ -37177,8 +37851,9 @@
       <c r="M193" s="161"/>
       <c r="N193" s="161"/>
       <c r="O193" s="161"/>
-      <c r="P193" t="str" s="159" cm="1">
+      <c r="P193" s="159" cm="1" t="str">
         <f t="array" ref="P193">IF(AG193="","",AC193-R193-Q193)</f>
+        <v/>
       </c>
       <c r="Q193" s="162"/>
       <c r="R193" s="162"/>
@@ -37192,8 +37867,9 @@
       <c r="Z193" s="161"/>
       <c r="AA193" s="161"/>
       <c r="AB193" s="160"/>
-      <c r="AC193" t="str" s="195" cm="1">
+      <c r="AC193" s="195" cm="1" t="str">
         <f t="array" ref="AC193">IF(AG193="","",AG193-AF193)</f>
+        <v/>
       </c>
       <c r="AD193" s="161"/>
       <c r="AE193" s="160"/>
@@ -37240,13 +37916,15 @@
       <c r="C194" s="170"/>
       <c r="D194" s="165"/>
       <c r="E194" s="164"/>
-      <c r="F194" t="str" s="195" cm="1">
+      <c r="F194" s="195" cm="1" t="str">
         <f t="array" ref="F194">IF(AG194="","",I194-H194)</f>
+        <v/>
       </c>
       <c r="G194" s="160"/>
       <c r="H194" s="158"/>
-      <c r="I194" t="str" s="159" cm="1">
+      <c r="I194" s="159" cm="1" t="str">
         <f t="array" ref="I194">IF(AG194="","",P194-K194)</f>
+        <v/>
       </c>
       <c r="J194" s="160"/>
       <c r="K194" s="158"/>
@@ -37254,8 +37932,9 @@
       <c r="M194" s="161"/>
       <c r="N194" s="161"/>
       <c r="O194" s="161"/>
-      <c r="P194" t="str" s="159" cm="1">
+      <c r="P194" s="159" cm="1" t="str">
         <f t="array" ref="P194">IF(AG194="","",AC194-R194-Q194)</f>
+        <v/>
       </c>
       <c r="Q194" s="162"/>
       <c r="R194" s="162"/>
@@ -37269,8 +37948,9 @@
       <c r="Z194" s="161"/>
       <c r="AA194" s="161"/>
       <c r="AB194" s="160"/>
-      <c r="AC194" t="str" s="195" cm="1">
+      <c r="AC194" s="195" cm="1" t="str">
         <f t="array" ref="AC194">IF(AG194="","",AG194-AF194)</f>
+        <v/>
       </c>
       <c r="AD194" s="161"/>
       <c r="AE194" s="160"/>
@@ -37317,13 +37997,15 @@
       <c r="C195" s="170"/>
       <c r="D195" s="165"/>
       <c r="E195" s="164"/>
-      <c r="F195" t="str" s="195" cm="1">
+      <c r="F195" s="195" cm="1" t="str">
         <f t="array" ref="F195">IF(AG195="","",I195-H195)</f>
+        <v/>
       </c>
       <c r="G195" s="160"/>
       <c r="H195" s="158"/>
-      <c r="I195" t="str" s="159" cm="1">
+      <c r="I195" s="159" cm="1" t="str">
         <f t="array" ref="I195">IF(AG195="","",P195-K195)</f>
+        <v/>
       </c>
       <c r="J195" s="160"/>
       <c r="K195" s="158"/>
@@ -37331,8 +38013,9 @@
       <c r="M195" s="161"/>
       <c r="N195" s="161"/>
       <c r="O195" s="161"/>
-      <c r="P195" t="str" s="159" cm="1">
+      <c r="P195" s="159" cm="1" t="str">
         <f t="array" ref="P195">IF(AG195="","",AC195-R195-Q195)</f>
+        <v/>
       </c>
       <c r="Q195" s="162"/>
       <c r="R195" s="162"/>
@@ -37346,8 +38029,9 @@
       <c r="Z195" s="161"/>
       <c r="AA195" s="161"/>
       <c r="AB195" s="160"/>
-      <c r="AC195" t="str" s="195" cm="1">
+      <c r="AC195" s="195" cm="1" t="str">
         <f t="array" ref="AC195">IF(AG195="","",AG195-AF195)</f>
+        <v/>
       </c>
       <c r="AD195" s="161"/>
       <c r="AE195" s="160"/>
@@ -37394,13 +38078,15 @@
       <c r="C196" s="170"/>
       <c r="D196" s="165"/>
       <c r="E196" s="164"/>
-      <c r="F196" t="str" s="195" cm="1">
+      <c r="F196" s="195" cm="1" t="str">
         <f t="array" ref="F196">IF(AG196="","",I196-H196)</f>
+        <v/>
       </c>
       <c r="G196" s="160"/>
       <c r="H196" s="158"/>
-      <c r="I196" t="str" s="159" cm="1">
+      <c r="I196" s="159" cm="1" t="str">
         <f t="array" ref="I196">IF(AG196="","",P196-K196)</f>
+        <v/>
       </c>
       <c r="J196" s="160"/>
       <c r="K196" s="158"/>
@@ -37408,8 +38094,9 @@
       <c r="M196" s="161"/>
       <c r="N196" s="161"/>
       <c r="O196" s="161"/>
-      <c r="P196" t="str" s="159" cm="1">
+      <c r="P196" s="159" cm="1" t="str">
         <f t="array" ref="P196">IF(AG196="","",AC196-R196-Q196)</f>
+        <v/>
       </c>
       <c r="Q196" s="162"/>
       <c r="R196" s="162"/>
@@ -37423,8 +38110,9 @@
       <c r="Z196" s="161"/>
       <c r="AA196" s="161"/>
       <c r="AB196" s="160"/>
-      <c r="AC196" t="str" s="195" cm="1">
+      <c r="AC196" s="195" cm="1" t="str">
         <f t="array" ref="AC196">IF(AG196="","",AG196-AF196)</f>
+        <v/>
       </c>
       <c r="AD196" s="161"/>
       <c r="AE196" s="160"/>
@@ -37471,13 +38159,15 @@
       <c r="C197" s="170"/>
       <c r="D197" s="165"/>
       <c r="E197" s="164"/>
-      <c r="F197" t="str" s="195" cm="1">
+      <c r="F197" s="195" cm="1" t="str">
         <f t="array" ref="F197">IF(AG197="","",I197-H197)</f>
+        <v/>
       </c>
       <c r="G197" s="160"/>
       <c r="H197" s="158"/>
-      <c r="I197" t="str" s="159" cm="1">
+      <c r="I197" s="159" cm="1" t="str">
         <f t="array" ref="I197">IF(AG197="","",P197-K197)</f>
+        <v/>
       </c>
       <c r="J197" s="160"/>
       <c r="K197" s="158"/>
@@ -37485,8 +38175,9 @@
       <c r="M197" s="161"/>
       <c r="N197" s="161"/>
       <c r="O197" s="161"/>
-      <c r="P197" t="str" s="159" cm="1">
+      <c r="P197" s="159" cm="1" t="str">
         <f t="array" ref="P197">IF(AG197="","",AC197-R197-Q197)</f>
+        <v/>
       </c>
       <c r="Q197" s="162"/>
       <c r="R197" s="162"/>
@@ -37500,8 +38191,9 @@
       <c r="Z197" s="161"/>
       <c r="AA197" s="161"/>
       <c r="AB197" s="160"/>
-      <c r="AC197" t="str" s="195" cm="1">
+      <c r="AC197" s="195" cm="1" t="str">
         <f t="array" ref="AC197">IF(AG197="","",AG197-AF197)</f>
+        <v/>
       </c>
       <c r="AD197" s="161"/>
       <c r="AE197" s="160"/>
@@ -37548,13 +38240,15 @@
       <c r="C198" s="170"/>
       <c r="D198" s="165"/>
       <c r="E198" s="164"/>
-      <c r="F198" t="str" s="195" cm="1">
+      <c r="F198" s="195" cm="1" t="str">
         <f t="array" ref="F198">IF(AG198="","",I198-H198)</f>
+        <v/>
       </c>
       <c r="G198" s="160"/>
       <c r="H198" s="158"/>
-      <c r="I198" t="str" s="159" cm="1">
+      <c r="I198" s="159" cm="1" t="str">
         <f t="array" ref="I198">IF(AG198="","",P198-K198)</f>
+        <v/>
       </c>
       <c r="J198" s="160"/>
       <c r="K198" s="158"/>
@@ -37562,8 +38256,9 @@
       <c r="M198" s="161"/>
       <c r="N198" s="161"/>
       <c r="O198" s="161"/>
-      <c r="P198" t="str" s="159" cm="1">
+      <c r="P198" s="159" cm="1" t="str">
         <f t="array" ref="P198">IF(AG198="","",AC198-R198-Q198)</f>
+        <v/>
       </c>
       <c r="Q198" s="162"/>
       <c r="R198" s="162"/>
@@ -37577,8 +38272,9 @@
       <c r="Z198" s="161"/>
       <c r="AA198" s="161"/>
       <c r="AB198" s="160"/>
-      <c r="AC198" t="str" s="195" cm="1">
+      <c r="AC198" s="195" cm="1" t="str">
         <f t="array" ref="AC198">IF(AG198="","",AG198-AF198)</f>
+        <v/>
       </c>
       <c r="AD198" s="161"/>
       <c r="AE198" s="160"/>
@@ -37625,13 +38321,15 @@
       <c r="C199" s="170"/>
       <c r="D199" s="165"/>
       <c r="E199" s="164"/>
-      <c r="F199" t="str" s="195" cm="1">
+      <c r="F199" s="195" cm="1" t="str">
         <f t="array" ref="F199">IF(AG199="","",I199-H199)</f>
+        <v/>
       </c>
       <c r="G199" s="160"/>
       <c r="H199" s="158"/>
-      <c r="I199" t="str" s="159" cm="1">
+      <c r="I199" s="159" cm="1" t="str">
         <f t="array" ref="I199">IF(AG199="","",P199-K199)</f>
+        <v/>
       </c>
       <c r="J199" s="160"/>
       <c r="K199" s="158"/>
@@ -37639,8 +38337,9 @@
       <c r="M199" s="161"/>
       <c r="N199" s="161"/>
       <c r="O199" s="161"/>
-      <c r="P199" t="str" s="159" cm="1">
+      <c r="P199" s="159" cm="1" t="str">
         <f t="array" ref="P199">IF(AG199="","",AC199-R199-Q199)</f>
+        <v/>
       </c>
       <c r="Q199" s="162"/>
       <c r="R199" s="162"/>
@@ -37654,8 +38353,9 @@
       <c r="Z199" s="161"/>
       <c r="AA199" s="161"/>
       <c r="AB199" s="160"/>
-      <c r="AC199" t="str" s="195" cm="1">
+      <c r="AC199" s="195" cm="1" t="str">
         <f t="array" ref="AC199">IF(AG199="","",AG199-AF199)</f>
+        <v/>
       </c>
       <c r="AD199" s="161"/>
       <c r="AE199" s="160"/>
@@ -37702,13 +38402,15 @@
       <c r="C200" s="170"/>
       <c r="D200" s="165"/>
       <c r="E200" s="164"/>
-      <c r="F200" t="str" s="195" cm="1">
+      <c r="F200" s="195" cm="1" t="str">
         <f t="array" ref="F200">IF(AG200="","",I200-H200)</f>
+        <v/>
       </c>
       <c r="G200" s="160"/>
       <c r="H200" s="158"/>
-      <c r="I200" t="str" s="159" cm="1">
+      <c r="I200" s="159" cm="1" t="str">
         <f t="array" ref="I200">IF(AG200="","",P200-K200)</f>
+        <v/>
       </c>
       <c r="J200" s="160"/>
       <c r="K200" s="158"/>
@@ -37716,8 +38418,9 @@
       <c r="M200" s="161"/>
       <c r="N200" s="161"/>
       <c r="O200" s="161"/>
-      <c r="P200" t="str" s="159" cm="1">
+      <c r="P200" s="159" cm="1" t="str">
         <f t="array" ref="P200">IF(AG200="","",AC200-R200-Q200)</f>
+        <v/>
       </c>
       <c r="Q200" s="162"/>
       <c r="R200" s="162"/>
@@ -37731,8 +38434,9 @@
       <c r="Z200" s="161"/>
       <c r="AA200" s="161"/>
       <c r="AB200" s="160"/>
-      <c r="AC200" t="str" s="195" cm="1">
+      <c r="AC200" s="195" cm="1" t="str">
         <f t="array" ref="AC200">IF(AG200="","",AG200-AF200)</f>
+        <v/>
       </c>
       <c r="AD200" s="161"/>
       <c r="AE200" s="160"/>
@@ -37779,13 +38483,15 @@
       <c r="C201" s="170"/>
       <c r="D201" s="165"/>
       <c r="E201" s="164"/>
-      <c r="F201" t="str" s="195" cm="1">
+      <c r="F201" s="195" cm="1" t="str">
         <f t="array" ref="F201">IF(AG201="","",I201-H201)</f>
+        <v/>
       </c>
       <c r="G201" s="160"/>
       <c r="H201" s="158"/>
-      <c r="I201" t="str" s="159" cm="1">
+      <c r="I201" s="159" cm="1" t="str">
         <f t="array" ref="I201">IF(AG201="","",P201-K201)</f>
+        <v/>
       </c>
       <c r="J201" s="160"/>
       <c r="K201" s="158"/>
@@ -37793,8 +38499,9 @@
       <c r="M201" s="161"/>
       <c r="N201" s="161"/>
       <c r="O201" s="161"/>
-      <c r="P201" t="str" s="159" cm="1">
+      <c r="P201" s="159" cm="1" t="str">
         <f t="array" ref="P201">IF(AG201="","",AC201-R201-Q201)</f>
+        <v/>
       </c>
       <c r="Q201" s="162"/>
       <c r="R201" s="162"/>
@@ -37808,8 +38515,9 @@
       <c r="Z201" s="161"/>
       <c r="AA201" s="161"/>
       <c r="AB201" s="160"/>
-      <c r="AC201" t="str" s="195" cm="1">
+      <c r="AC201" s="195" cm="1" t="str">
         <f t="array" ref="AC201">IF(AG201="","",AG201-AF201)</f>
+        <v/>
       </c>
       <c r="AD201" s="161"/>
       <c r="AE201" s="160"/>
@@ -37856,13 +38564,15 @@
       <c r="C202" s="170"/>
       <c r="D202" s="165"/>
       <c r="E202" s="164"/>
-      <c r="F202" t="str" s="195" cm="1">
+      <c r="F202" s="195" cm="1" t="str">
         <f t="array" ref="F202">IF(AG202="","",I202-H202)</f>
+        <v/>
       </c>
       <c r="G202" s="160"/>
       <c r="H202" s="158"/>
-      <c r="I202" t="str" s="159" cm="1">
+      <c r="I202" s="159" cm="1" t="str">
         <f t="array" ref="I202">IF(AG202="","",P202-K202)</f>
+        <v/>
       </c>
       <c r="J202" s="160"/>
       <c r="K202" s="158"/>
@@ -37870,8 +38580,9 @@
       <c r="M202" s="161"/>
       <c r="N202" s="161"/>
       <c r="O202" s="161"/>
-      <c r="P202" t="str" s="159" cm="1">
+      <c r="P202" s="159" cm="1" t="str">
         <f t="array" ref="P202">IF(AG202="","",AC202-R202-Q202)</f>
+        <v/>
       </c>
       <c r="Q202" s="162"/>
       <c r="R202" s="162"/>
@@ -37885,8 +38596,9 @@
       <c r="Z202" s="161"/>
       <c r="AA202" s="161"/>
       <c r="AB202" s="160"/>
-      <c r="AC202" t="str" s="195" cm="1">
+      <c r="AC202" s="195" cm="1" t="str">
         <f t="array" ref="AC202">IF(AG202="","",AG202-AF202)</f>
+        <v/>
       </c>
       <c r="AD202" s="161"/>
       <c r="AE202" s="160"/>
@@ -37933,13 +38645,15 @@
       <c r="C203" s="170"/>
       <c r="D203" s="165"/>
       <c r="E203" s="164"/>
-      <c r="F203" t="str" s="195" cm="1">
+      <c r="F203" s="195" cm="1" t="str">
         <f t="array" ref="F203">IF(AG203="","",I203-H203)</f>
+        <v/>
       </c>
       <c r="G203" s="160"/>
       <c r="H203" s="158"/>
-      <c r="I203" t="str" s="159" cm="1">
+      <c r="I203" s="159" cm="1" t="str">
         <f t="array" ref="I203">IF(AG203="","",P203-K203)</f>
+        <v/>
       </c>
       <c r="J203" s="160"/>
       <c r="K203" s="158"/>
@@ -37947,8 +38661,9 @@
       <c r="M203" s="161"/>
       <c r="N203" s="161"/>
       <c r="O203" s="161"/>
-      <c r="P203" t="str" s="159" cm="1">
+      <c r="P203" s="159" cm="1" t="str">
         <f t="array" ref="P203">IF(AG203="","",AC203-R203-Q203)</f>
+        <v/>
       </c>
       <c r="Q203" s="162"/>
       <c r="R203" s="162"/>
@@ -37962,8 +38677,9 @@
       <c r="Z203" s="161"/>
       <c r="AA203" s="161"/>
       <c r="AB203" s="160"/>
-      <c r="AC203" t="str" s="195" cm="1">
+      <c r="AC203" s="195" cm="1" t="str">
         <f t="array" ref="AC203">IF(AG203="","",AG203-AF203)</f>
+        <v/>
       </c>
       <c r="AD203" s="161"/>
       <c r="AE203" s="160"/>
@@ -38010,13 +38726,15 @@
       <c r="C204" s="170"/>
       <c r="D204" s="165"/>
       <c r="E204" s="164"/>
-      <c r="F204" t="str" s="195" cm="1">
+      <c r="F204" s="195" cm="1" t="str">
         <f t="array" ref="F204">IF(AG204="","",I204-H204)</f>
+        <v/>
       </c>
       <c r="G204" s="160"/>
       <c r="H204" s="158"/>
-      <c r="I204" t="str" s="159" cm="1">
+      <c r="I204" s="159" cm="1" t="str">
         <f t="array" ref="I204">IF(AG204="","",P204-K204)</f>
+        <v/>
       </c>
       <c r="J204" s="160"/>
       <c r="K204" s="158"/>
@@ -38024,8 +38742,9 @@
       <c r="M204" s="161"/>
       <c r="N204" s="161"/>
       <c r="O204" s="161"/>
-      <c r="P204" t="str" s="159" cm="1">
+      <c r="P204" s="159" cm="1" t="str">
         <f t="array" ref="P204">IF(AG204="","",AC204-R204-Q204)</f>
+        <v/>
       </c>
       <c r="Q204" s="162"/>
       <c r="R204" s="162"/>
@@ -38039,8 +38758,9 @@
       <c r="Z204" s="161"/>
       <c r="AA204" s="161"/>
       <c r="AB204" s="160"/>
-      <c r="AC204" t="str" s="195" cm="1">
+      <c r="AC204" s="195" cm="1" t="str">
         <f t="array" ref="AC204">IF(AG204="","",AG204-AF204)</f>
+        <v/>
       </c>
       <c r="AD204" s="161"/>
       <c r="AE204" s="160"/>
@@ -38087,13 +38807,15 @@
       <c r="C205" s="170"/>
       <c r="D205" s="165"/>
       <c r="E205" s="164"/>
-      <c r="F205" t="str" s="195" cm="1">
+      <c r="F205" s="195" cm="1" t="str">
         <f t="array" ref="F205">IF(AG205="","",I205-H205)</f>
+        <v/>
       </c>
       <c r="G205" s="160"/>
       <c r="H205" s="158"/>
-      <c r="I205" t="str" s="159" cm="1">
+      <c r="I205" s="159" cm="1" t="str">
         <f t="array" ref="I205">IF(AG205="","",P205-K205)</f>
+        <v/>
       </c>
       <c r="J205" s="160"/>
       <c r="K205" s="158"/>
@@ -38101,8 +38823,9 @@
       <c r="M205" s="161"/>
       <c r="N205" s="161"/>
       <c r="O205" s="161"/>
-      <c r="P205" t="str" s="159" cm="1">
+      <c r="P205" s="159" cm="1" t="str">
         <f t="array" ref="P205">IF(AG205="","",AC205-R205-Q205)</f>
+        <v/>
       </c>
       <c r="Q205" s="162"/>
       <c r="R205" s="162"/>
@@ -38116,8 +38839,9 @@
       <c r="Z205" s="161"/>
       <c r="AA205" s="161"/>
       <c r="AB205" s="160"/>
-      <c r="AC205" t="str" s="195" cm="1">
+      <c r="AC205" s="195" cm="1" t="str">
         <f t="array" ref="AC205">IF(AG205="","",AG205-AF205)</f>
+        <v/>
       </c>
       <c r="AD205" s="161"/>
       <c r="AE205" s="160"/>
@@ -38164,13 +38888,15 @@
       <c r="C206" s="170"/>
       <c r="D206" s="165"/>
       <c r="E206" s="164"/>
-      <c r="F206" t="str" s="195" cm="1">
+      <c r="F206" s="195" cm="1" t="str">
         <f t="array" ref="F206">IF(AG206="","",I206-H206)</f>
+        <v/>
       </c>
       <c r="G206" s="160"/>
       <c r="H206" s="158"/>
-      <c r="I206" t="str" s="159" cm="1">
+      <c r="I206" s="159" cm="1" t="str">
         <f t="array" ref="I206">IF(AG206="","",P206-K206)</f>
+        <v/>
       </c>
       <c r="J206" s="160"/>
       <c r="K206" s="158"/>
@@ -38178,8 +38904,9 @@
       <c r="M206" s="161"/>
       <c r="N206" s="161"/>
       <c r="O206" s="161"/>
-      <c r="P206" t="str" s="159" cm="1">
+      <c r="P206" s="159" cm="1" t="str">
         <f t="array" ref="P206">IF(AG206="","",AC206-R206-Q206)</f>
+        <v/>
       </c>
       <c r="Q206" s="162"/>
       <c r="R206" s="162"/>
@@ -38193,8 +38920,9 @@
       <c r="Z206" s="161"/>
       <c r="AA206" s="161"/>
       <c r="AB206" s="160"/>
-      <c r="AC206" t="str" s="195" cm="1">
+      <c r="AC206" s="195" cm="1" t="str">
         <f t="array" ref="AC206">IF(AG206="","",AG206-AF206)</f>
+        <v/>
       </c>
       <c r="AD206" s="161"/>
       <c r="AE206" s="160"/>
@@ -38241,13 +38969,15 @@
       <c r="C207" s="170"/>
       <c r="D207" s="165"/>
       <c r="E207" s="164"/>
-      <c r="F207" t="str" s="195" cm="1">
+      <c r="F207" s="195" cm="1" t="str">
         <f t="array" ref="F207">IF(AG207="","",I207-H207)</f>
+        <v/>
       </c>
       <c r="G207" s="160"/>
       <c r="H207" s="158"/>
-      <c r="I207" t="str" s="159" cm="1">
+      <c r="I207" s="159" cm="1" t="str">
         <f t="array" ref="I207">IF(AG207="","",P207-K207)</f>
+        <v/>
       </c>
       <c r="J207" s="160"/>
       <c r="K207" s="158"/>
@@ -38255,8 +38985,9 @@
       <c r="M207" s="161"/>
       <c r="N207" s="161"/>
       <c r="O207" s="161"/>
-      <c r="P207" t="str" s="159" cm="1">
+      <c r="P207" s="159" cm="1" t="str">
         <f t="array" ref="P207">IF(AG207="","",AC207-R207-Q207)</f>
+        <v/>
       </c>
       <c r="Q207" s="162"/>
       <c r="R207" s="162"/>
@@ -38270,8 +39001,9 @@
       <c r="Z207" s="161"/>
       <c r="AA207" s="161"/>
       <c r="AB207" s="160"/>
-      <c r="AC207" t="str" s="195" cm="1">
+      <c r="AC207" s="195" cm="1" t="str">
         <f t="array" ref="AC207">IF(AG207="","",AG207-AF207)</f>
+        <v/>
       </c>
       <c r="AD207" s="161"/>
       <c r="AE207" s="160"/>
@@ -38318,13 +39050,15 @@
       <c r="C208" s="170"/>
       <c r="D208" s="165"/>
       <c r="E208" s="164"/>
-      <c r="F208" t="str" s="195" cm="1">
+      <c r="F208" s="195" cm="1" t="str">
         <f t="array" ref="F208">IF(AG208="","",I208-H208)</f>
+        <v/>
       </c>
       <c r="G208" s="160"/>
       <c r="H208" s="158"/>
-      <c r="I208" t="str" s="159" cm="1">
+      <c r="I208" s="159" cm="1" t="str">
         <f t="array" ref="I208">IF(AG208="","",P208-K208)</f>
+        <v/>
       </c>
       <c r="J208" s="160"/>
       <c r="K208" s="158"/>
@@ -38332,8 +39066,9 @@
       <c r="M208" s="161"/>
       <c r="N208" s="161"/>
       <c r="O208" s="161"/>
-      <c r="P208" t="str" s="159" cm="1">
+      <c r="P208" s="159" cm="1" t="str">
         <f t="array" ref="P208">IF(AG208="","",AC208-R208-Q208)</f>
+        <v/>
       </c>
       <c r="Q208" s="162"/>
       <c r="R208" s="162"/>
@@ -38347,8 +39082,9 @@
       <c r="Z208" s="161"/>
       <c r="AA208" s="161"/>
       <c r="AB208" s="160"/>
-      <c r="AC208" t="str" s="195" cm="1">
+      <c r="AC208" s="195" cm="1" t="str">
         <f t="array" ref="AC208">IF(AG208="","",AG208-AF208)</f>
+        <v/>
       </c>
       <c r="AD208" s="161"/>
       <c r="AE208" s="160"/>
@@ -38395,13 +39131,15 @@
       <c r="C209" s="170"/>
       <c r="D209" s="165"/>
       <c r="E209" s="164"/>
-      <c r="F209" t="str" s="195" cm="1">
+      <c r="F209" s="195" cm="1" t="str">
         <f t="array" ref="F209">IF(AG209="","",I209-H209)</f>
+        <v/>
       </c>
       <c r="G209" s="160"/>
       <c r="H209" s="158"/>
-      <c r="I209" t="str" s="159" cm="1">
+      <c r="I209" s="159" cm="1" t="str">
         <f t="array" ref="I209">IF(AG209="","",P209-K209)</f>
+        <v/>
       </c>
       <c r="J209" s="160"/>
       <c r="K209" s="158"/>
@@ -38409,8 +39147,9 @@
       <c r="M209" s="161"/>
       <c r="N209" s="161"/>
       <c r="O209" s="161"/>
-      <c r="P209" t="str" s="159" cm="1">
+      <c r="P209" s="159" cm="1" t="str">
         <f t="array" ref="P209">IF(AG209="","",AC209-R209-Q209)</f>
+        <v/>
       </c>
       <c r="Q209" s="162"/>
       <c r="R209" s="162"/>
@@ -38424,8 +39163,9 @@
       <c r="Z209" s="161"/>
       <c r="AA209" s="161"/>
       <c r="AB209" s="160"/>
-      <c r="AC209" t="str" s="195" cm="1">
+      <c r="AC209" s="195" cm="1" t="str">
         <f t="array" ref="AC209">IF(AG209="","",AG209-AF209)</f>
+        <v/>
       </c>
       <c r="AD209" s="161"/>
       <c r="AE209" s="160"/>
@@ -38472,13 +39212,15 @@
       <c r="C210" s="170"/>
       <c r="D210" s="165"/>
       <c r="E210" s="164"/>
-      <c r="F210" t="str" s="195" cm="1">
+      <c r="F210" s="195" cm="1" t="str">
         <f t="array" ref="F210">IF(AG210="","",I210-H210)</f>
+        <v/>
       </c>
       <c r="G210" s="160"/>
       <c r="H210" s="158"/>
-      <c r="I210" t="str" s="159" cm="1">
+      <c r="I210" s="159" cm="1" t="str">
         <f t="array" ref="I210">IF(AG210="","",P210-K210)</f>
+        <v/>
       </c>
       <c r="J210" s="160"/>
       <c r="K210" s="158"/>
@@ -38486,8 +39228,9 @@
       <c r="M210" s="161"/>
       <c r="N210" s="161"/>
       <c r="O210" s="161"/>
-      <c r="P210" t="str" s="159" cm="1">
+      <c r="P210" s="159" cm="1" t="str">
         <f t="array" ref="P210">IF(AG210="","",AC210-R210-Q210)</f>
+        <v/>
       </c>
       <c r="Q210" s="162"/>
       <c r="R210" s="162"/>
@@ -38501,8 +39244,9 @@
       <c r="Z210" s="161"/>
       <c r="AA210" s="161"/>
       <c r="AB210" s="160"/>
-      <c r="AC210" t="str" s="195" cm="1">
+      <c r="AC210" s="195" cm="1" t="str">
         <f t="array" ref="AC210">IF(AG210="","",AG210-AF210)</f>
+        <v/>
       </c>
       <c r="AD210" s="161"/>
       <c r="AE210" s="160"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -4994,7 +4994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -5005,19 +5005,19 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="1" vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="1" vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="1" vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="1" vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="1" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5083,10 +5083,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="7" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="7" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
@@ -5161,7 +5161,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5170,10 +5170,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
@@ -5254,7 +5254,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5266,10 +5266,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="5" borderId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="5" borderId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="46" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
@@ -5452,13 +5452,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="67" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="68" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5476,22 +5476,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="12" fillId="2" borderId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="12" fillId="2" borderId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="62" fontId="12" fillId="2" borderId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="12" fillId="2" borderId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="59" fontId="12" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5533,7 +5533,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="69" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="70" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5554,7 +5554,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="4" borderId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="41" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5566,7 +5566,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="4" borderId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="61" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5575,7 +5575,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5848,7 +5848,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="13" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="62" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5857,13 +5857,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="13" fillId="2" borderId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="13" fillId="2" borderId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="13" fillId="2" borderId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="63" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5893,10 +5893,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="23" fillId="2" borderId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="59" fontId="23" fillId="2" borderId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5924,6 +5924,123 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="67" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="40" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="70" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="71" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="64" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="79" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="80" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="81" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8791,13 +8908,13 @@
       </c>
       <c r="AD3" s="48"/>
       <c r="AE3" s="49"/>
-      <c r="AF3" t="s" s="50">
+      <c r="AF3" t="s" s="310">
         <v>12</v>
       </c>
-      <c r="AG3" t="s" s="51">
+      <c r="AG3" t="s" s="311">
         <v>13</v>
       </c>
-      <c r="AH3" t="s" s="52">
+      <c r="AH3" t="s" s="312">
         <v>14</v>
       </c>
       <c r="AI3" t="s" s="47">
@@ -8806,7 +8923,7 @@
       <c r="AJ3" s="48"/>
       <c r="AK3" s="48"/>
       <c r="AL3" s="49"/>
-      <c r="AM3" t="s" s="53">
+      <c r="AM3" t="s" s="313">
         <v>16</v>
       </c>
       <c r="AN3" t="s" s="54">
@@ -8814,13 +8931,13 @@
       </c>
       <c r="AO3" s="10"/>
       <c r="AP3" s="55"/>
-      <c r="AQ3" t="s" s="54">
+      <c r="AQ3" t="s" s="314">
         <v>18</v>
       </c>
-      <c r="AR3" t="s" s="54">
+      <c r="AR3" t="s" s="314">
         <v>19</v>
       </c>
-      <c r="AS3" t="s" s="54">
+      <c r="AS3" t="s" s="314">
         <v>20</v>
       </c>
       <c r="AT3" t="s" s="56">
@@ -8860,37 +8977,37 @@
       <c r="BM3" s="12"/>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" t="s" s="61">
+      <c r="A4" t="s" s="315">
         <v>24</v>
       </c>
-      <c r="B4" t="s" s="54">
+      <c r="B4" t="s" s="314">
         <v>25</v>
       </c>
       <c r="C4" t="s" s="62">
         <v>26</v>
       </c>
-      <c r="D4" t="s" s="63">
+      <c r="D4" t="s" s="316">
         <v>27</v>
       </c>
-      <c r="E4" t="s" s="64">
+      <c r="E4" t="s" s="317">
         <v>28</v>
       </c>
-      <c r="F4" t="s" s="65">
+      <c r="F4" t="s" s="318">
         <v>29</v>
       </c>
-      <c r="G4" t="s" s="66">
+      <c r="G4" t="s" s="319">
         <v>30</v>
       </c>
-      <c r="H4" t="s" s="67">
+      <c r="H4" t="s" s="320">
         <v>28</v>
       </c>
-      <c r="I4" t="s" s="65">
+      <c r="I4" t="s" s="318">
         <v>31</v>
       </c>
-      <c r="J4" t="s" s="66">
+      <c r="J4" t="s" s="319">
         <v>32</v>
       </c>
-      <c r="K4" t="s" s="68">
+      <c r="K4" t="s" s="321">
         <v>33</v>
       </c>
       <c r="L4" t="s" s="69">
@@ -8901,13 +9018,13 @@
         <v>35</v>
       </c>
       <c r="O4" s="70"/>
-      <c r="P4" t="s" s="71">
+      <c r="P4" t="s" s="322">
         <v>36</v>
       </c>
-      <c r="Q4" t="s" s="72">
+      <c r="Q4" t="s" s="323">
         <v>37</v>
       </c>
-      <c r="R4" t="s" s="72">
+      <c r="R4" t="s" s="323">
         <v>33</v>
       </c>
       <c r="S4" t="s" s="73">
@@ -8930,13 +9047,13 @@
         <v>42</v>
       </c>
       <c r="AB4" s="75"/>
-      <c r="AC4" t="s" s="76">
+      <c r="AC4" t="s" s="324">
         <v>43</v>
       </c>
-      <c r="AD4" t="s" s="71">
+      <c r="AD4" t="s" s="322">
         <v>44</v>
       </c>
-      <c r="AE4" t="s" s="77">
+      <c r="AE4" t="s" s="325">
         <v>45</v>
       </c>
       <c r="AF4" s="78"/>
@@ -9000,49 +9117,49 @@
       <c r="I5" s="96"/>
       <c r="J5" s="97"/>
       <c r="K5" s="99"/>
-      <c r="L5" t="s" s="100">
+      <c r="L5" t="s" s="326">
         <v>49</v>
       </c>
-      <c r="M5" t="s" s="100">
+      <c r="M5" t="s" s="326">
         <v>50</v>
       </c>
-      <c r="N5" t="s" s="100">
+      <c r="N5" t="s" s="326">
         <v>49</v>
       </c>
-      <c r="O5" t="s" s="100">
+      <c r="O5" t="s" s="326">
         <v>50</v>
       </c>
       <c r="P5" s="101"/>
       <c r="Q5" s="102"/>
       <c r="R5" s="102"/>
-      <c r="S5" t="s" s="103">
+      <c r="S5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="T5" t="s" s="103">
+      <c r="T5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="U5" t="s" s="103">
+      <c r="U5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="V5" t="s" s="103">
+      <c r="V5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="W5" t="s" s="103">
+      <c r="W5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="X5" t="s" s="103">
+      <c r="X5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="Y5" t="s" s="103">
+      <c r="Y5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="Z5" t="s" s="103">
+      <c r="Z5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="AA5" t="s" s="103">
+      <c r="AA5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="AB5" t="s" s="104">
+      <c r="AB5" t="s" s="328">
         <v>50</v>
       </c>
       <c r="AC5" s="105"/>
@@ -9051,16 +9168,16 @@
       <c r="AF5" s="78"/>
       <c r="AG5" s="79"/>
       <c r="AH5" s="80"/>
-      <c r="AI5" t="s" s="106">
+      <c r="AI5" t="s" s="329">
         <v>49</v>
       </c>
-      <c r="AJ5" t="s" s="100">
+      <c r="AJ5" t="s" s="326">
         <v>50</v>
       </c>
-      <c r="AK5" t="s" s="100">
+      <c r="AK5" t="s" s="326">
         <v>49</v>
       </c>
-      <c r="AL5" t="s" s="66">
+      <c r="AL5" t="s" s="319">
         <v>50</v>
       </c>
       <c r="AM5" s="84"/>
@@ -9070,16 +9187,16 @@
       <c r="AQ5" s="87"/>
       <c r="AR5" s="87"/>
       <c r="AS5" s="87"/>
-      <c r="AT5" t="s" s="107">
+      <c r="AT5" t="s" s="330">
         <v>51</v>
       </c>
-      <c r="AU5" t="s" s="107">
+      <c r="AU5" t="s" s="330">
         <v>52</v>
       </c>
-      <c r="AV5" t="s" s="107">
+      <c r="AV5" t="s" s="330">
         <v>51</v>
       </c>
-      <c r="AW5" t="s" s="107">
+      <c r="AW5" t="s" s="330">
         <v>52</v>
       </c>
       <c r="AX5" s="90"/>
@@ -21918,13 +22035,13 @@
       </c>
       <c r="AD3" s="48"/>
       <c r="AE3" s="49"/>
-      <c r="AF3" t="s" s="50">
+      <c r="AF3" t="s" s="310">
         <v>12</v>
       </c>
-      <c r="AG3" t="s" s="178">
+      <c r="AG3" t="s" s="331">
         <v>13</v>
       </c>
-      <c r="AH3" t="s" s="52">
+      <c r="AH3" t="s" s="312">
         <v>14</v>
       </c>
       <c r="AI3" t="s" s="47">
@@ -21933,7 +22050,7 @@
       <c r="AJ3" s="48"/>
       <c r="AK3" s="48"/>
       <c r="AL3" s="49"/>
-      <c r="AM3" t="s" s="53">
+      <c r="AM3" t="s" s="313">
         <v>16</v>
       </c>
       <c r="AN3" t="s" s="54">
@@ -21941,13 +22058,13 @@
       </c>
       <c r="AO3" s="10"/>
       <c r="AP3" s="55"/>
-      <c r="AQ3" t="s" s="54">
+      <c r="AQ3" t="s" s="314">
         <v>18</v>
       </c>
-      <c r="AR3" t="s" s="54">
+      <c r="AR3" t="s" s="314">
         <v>19</v>
       </c>
-      <c r="AS3" t="s" s="54">
+      <c r="AS3" t="s" s="314">
         <v>20</v>
       </c>
       <c r="AT3" t="s" s="56">
@@ -21986,37 +22103,37 @@
       <c r="BL3" s="33"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="s" s="61">
+      <c r="A4" t="s" s="315">
         <v>24</v>
       </c>
-      <c r="B4" t="s" s="54">
+      <c r="B4" t="s" s="314">
         <v>25</v>
       </c>
       <c r="C4" t="s" s="62">
         <v>26</v>
       </c>
-      <c r="D4" t="s" s="180">
+      <c r="D4" t="s" s="332">
         <v>88</v>
       </c>
-      <c r="E4" t="s" s="181">
+      <c r="E4" t="s" s="333">
         <v>89</v>
       </c>
-      <c r="F4" t="s" s="182">
+      <c r="F4" t="s" s="334">
         <v>29</v>
       </c>
-      <c r="G4" t="s" s="66">
+      <c r="G4" t="s" s="319">
         <v>90</v>
       </c>
-      <c r="H4" t="s" s="67">
+      <c r="H4" t="s" s="320">
         <v>28</v>
       </c>
-      <c r="I4" t="s" s="65">
+      <c r="I4" t="s" s="318">
         <v>31</v>
       </c>
-      <c r="J4" t="s" s="66">
+      <c r="J4" t="s" s="319">
         <v>32</v>
       </c>
-      <c r="K4" t="s" s="68">
+      <c r="K4" t="s" s="321">
         <v>33</v>
       </c>
       <c r="L4" t="s" s="69">
@@ -22027,13 +22144,13 @@
         <v>35</v>
       </c>
       <c r="O4" s="70"/>
-      <c r="P4" t="s" s="71">
+      <c r="P4" t="s" s="322">
         <v>36</v>
       </c>
-      <c r="Q4" t="s" s="72">
+      <c r="Q4" t="s" s="323">
         <v>37</v>
       </c>
-      <c r="R4" t="s" s="72">
+      <c r="R4" t="s" s="323">
         <v>33</v>
       </c>
       <c r="S4" t="s" s="73">
@@ -22056,13 +22173,13 @@
         <v>95</v>
       </c>
       <c r="AB4" s="184"/>
-      <c r="AC4" t="s" s="76">
+      <c r="AC4" t="s" s="324">
         <v>43</v>
       </c>
-      <c r="AD4" t="s" s="65">
+      <c r="AD4" t="s" s="318">
         <v>44</v>
       </c>
-      <c r="AE4" t="s" s="77">
+      <c r="AE4" t="s" s="325">
         <v>45</v>
       </c>
       <c r="AF4" s="78"/>
@@ -22125,49 +22242,49 @@
       <c r="I5" s="96"/>
       <c r="J5" s="97"/>
       <c r="K5" s="99"/>
-      <c r="L5" t="s" s="100">
+      <c r="L5" t="s" s="326">
         <v>49</v>
       </c>
-      <c r="M5" t="s" s="100">
+      <c r="M5" t="s" s="326">
         <v>50</v>
       </c>
-      <c r="N5" t="s" s="100">
+      <c r="N5" t="s" s="326">
         <v>49</v>
       </c>
-      <c r="O5" t="s" s="100">
+      <c r="O5" t="s" s="326">
         <v>50</v>
       </c>
       <c r="P5" s="101"/>
       <c r="Q5" s="102"/>
       <c r="R5" s="102"/>
-      <c r="S5" t="s" s="103">
+      <c r="S5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="T5" t="s" s="103">
+      <c r="T5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="U5" t="s" s="103">
+      <c r="U5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="V5" t="s" s="103">
+      <c r="V5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="W5" t="s" s="103">
+      <c r="W5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="X5" t="s" s="103">
+      <c r="X5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="Y5" t="s" s="103">
+      <c r="Y5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="Z5" t="s" s="103">
+      <c r="Z5" t="s" s="327">
         <v>50</v>
       </c>
-      <c r="AA5" t="s" s="103">
+      <c r="AA5" t="s" s="327">
         <v>49</v>
       </c>
-      <c r="AB5" t="s" s="104">
+      <c r="AB5" t="s" s="328">
         <v>50</v>
       </c>
       <c r="AC5" s="105"/>
@@ -22176,16 +22293,16 @@
       <c r="AF5" s="78"/>
       <c r="AG5" s="185"/>
       <c r="AH5" s="80"/>
-      <c r="AI5" t="s" s="106">
+      <c r="AI5" t="s" s="329">
         <v>49</v>
       </c>
-      <c r="AJ5" t="s" s="100">
+      <c r="AJ5" t="s" s="326">
         <v>50</v>
       </c>
-      <c r="AK5" t="s" s="100">
+      <c r="AK5" t="s" s="326">
         <v>49</v>
       </c>
-      <c r="AL5" t="s" s="66">
+      <c r="AL5" t="s" s="319">
         <v>50</v>
       </c>
       <c r="AM5" s="84"/>
@@ -22195,16 +22312,16 @@
       <c r="AQ5" s="87"/>
       <c r="AR5" s="87"/>
       <c r="AS5" s="87"/>
-      <c r="AT5" t="s" s="107">
+      <c r="AT5" t="s" s="330">
         <v>51</v>
       </c>
-      <c r="AU5" t="s" s="107">
+      <c r="AU5" t="s" s="330">
         <v>52</v>
       </c>
-      <c r="AV5" t="s" s="107">
+      <c r="AV5" t="s" s="330">
         <v>51</v>
       </c>
-      <c r="AW5" t="s" s="107">
+      <c r="AW5" t="s" s="330">
         <v>52</v>
       </c>
       <c r="AX5" s="90"/>
@@ -22675,7 +22792,7 @@
       </c>
       <c r="B12" s="167" t="inlineStr">
         <is>
-          <t>三友-304</t>
+          <t>三友-4</t>
         </is>
       </c>
       <c r="C12" s="156" t="inlineStr">
@@ -22781,7 +22898,7 @@
       </c>
       <c r="B13" s="167" t="inlineStr">
         <is>
-          <t>三友-307</t>
+          <t>三友-7</t>
         </is>
       </c>
       <c r="C13" s="156" t="inlineStr">
@@ -22889,7 +23006,7 @@
       </c>
       <c r="B14" s="167" t="inlineStr">
         <is>
-          <t>三友-308</t>
+          <t>三友-8</t>
         </is>
       </c>
       <c r="C14" s="156" t="inlineStr">
@@ -22993,7 +23110,7 @@
       </c>
       <c r="B15" s="167" t="inlineStr">
         <is>
-          <t>三友-309</t>
+          <t>三友-9</t>
         </is>
       </c>
       <c r="C15" s="156" t="inlineStr">
@@ -23103,7 +23220,7 @@
       </c>
       <c r="B16" s="167" t="inlineStr">
         <is>
-          <t>三友-310</t>
+          <t>三友-10</t>
         </is>
       </c>
       <c r="C16" s="156" t="inlineStr">
@@ -23207,7 +23324,7 @@
       </c>
       <c r="B17" s="167" t="inlineStr">
         <is>
-          <t>三友-311</t>
+          <t>三友-11</t>
         </is>
       </c>
       <c r="C17" s="156" t="inlineStr">
@@ -23315,7 +23432,7 @@
       </c>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>三友-312</t>
+          <t>三友-12</t>
         </is>
       </c>
       <c r="C18" s="156" t="inlineStr">
@@ -23419,7 +23536,7 @@
       </c>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>三友-313</t>
+          <t>三友-13</t>
         </is>
       </c>
       <c r="C19" s="156" t="inlineStr">
@@ -23523,7 +23640,7 @@
       </c>
       <c r="B20" s="167" t="inlineStr">
         <is>
-          <t>三友-314</t>
+          <t>三友-14</t>
         </is>
       </c>
       <c r="C20" s="156" t="inlineStr">
@@ -23627,7 +23744,7 @@
       </c>
       <c r="B21" s="167" t="inlineStr">
         <is>
-          <t>三友-315</t>
+          <t>三友-15</t>
         </is>
       </c>
       <c r="C21" s="156" t="inlineStr">
@@ -23737,7 +23854,7 @@
       </c>
       <c r="B22" s="167" t="inlineStr">
         <is>
-          <t>三友-316</t>
+          <t>三友-16</t>
         </is>
       </c>
       <c r="C22" s="156" t="inlineStr">
@@ -23841,7 +23958,7 @@
       </c>
       <c r="B23" s="167" t="inlineStr">
         <is>
-          <t>三友-318</t>
+          <t>三友-18</t>
         </is>
       </c>
       <c r="C23" s="156" t="inlineStr">
@@ -23945,7 +24062,7 @@
       </c>
       <c r="B24" s="167" t="inlineStr">
         <is>
-          <t>三友-319</t>
+          <t>三友-19</t>
         </is>
       </c>
       <c r="C24" s="156" t="inlineStr">
@@ -24049,7 +24166,7 @@
       </c>
       <c r="B25" s="167" t="inlineStr">
         <is>
-          <t>三友-320</t>
+          <t>三友-20</t>
         </is>
       </c>
       <c r="C25" s="156" t="inlineStr">
@@ -24153,7 +24270,7 @@
       </c>
       <c r="B26" s="167" t="inlineStr">
         <is>
-          <t>三友-321</t>
+          <t>三友-21</t>
         </is>
       </c>
       <c r="C26" s="156" t="inlineStr">
@@ -24256,9 +24373,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="151"/>
-      <c r="C27" t="s" s="156">
-        <v>115</v>
-      </c>
+      <c r="C27" s="170"/>
       <c r="D27" s="165"/>
       <c r="E27" s="164"/>
       <c r="F27" s="195" cm="1" t="str">
@@ -24338,50 +24453,34 @@
         <f t="array" ref="A28">A27+1</f>
         <v>17</v>
       </c>
-      <c r="B28" t="s" s="167">
-        <v>116</v>
-      </c>
+      <c r="B28" s="151"/>
       <c r="C28" t="s" s="156">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D28" s="165"/>
       <c r="E28" s="164"/>
-      <c r="F28" s="163" cm="1">
+      <c r="F28" s="195" cm="1" t="str">
         <f t="array" ref="F28">IF(AG28="","",I28-H28)</f>
-        <v>46275</v>
-      </c>
-      <c r="G28" s="160">
-        <v>46301</v>
-      </c>
-      <c r="H28" s="158">
-        <v>7</v>
-      </c>
-      <c r="I28" s="161" cm="1">
+        <v/>
+      </c>
+      <c r="G28" s="160"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="159" cm="1" t="str">
         <f t="array" ref="I28">IF(AG28="","",P28-K28)</f>
-        <v>46282</v>
-      </c>
-      <c r="J28" s="160">
-        <v>46302</v>
-      </c>
-      <c r="K28" s="158">
-        <v>7</v>
-      </c>
-      <c r="L28" s="161">
-        <v>46302</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J28" s="160"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="161"/>
       <c r="M28" s="161"/>
       <c r="N28" s="161"/>
       <c r="O28" s="161"/>
-      <c r="P28" s="161" cm="1">
+      <c r="P28" s="159" cm="1" t="str">
         <f t="array" ref="P28">IF(AG28="","",AC28-R28-Q28)</f>
-        <v>46289</v>
-      </c>
-      <c r="Q28" s="162">
-        <v>7</v>
-      </c>
-      <c r="R28" s="162">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q28" s="162"/>
+      <c r="R28" s="162"/>
       <c r="S28" s="161"/>
       <c r="T28" s="161"/>
       <c r="U28" s="161"/>
@@ -24392,29 +24491,21 @@
       <c r="Z28" s="161"/>
       <c r="AA28" s="161"/>
       <c r="AB28" s="160"/>
-      <c r="AC28" s="163">
-        <v>46310</v>
-      </c>
-      <c r="AD28" s="161" cm="1">
+      <c r="AC28" s="163"/>
+      <c r="AD28" s="159" cm="1" t="str">
         <f t="array" ref="AD28">IF(AG28="","",$AG28-$AF28)</f>
-        <v>46310</v>
+        <v/>
       </c>
       <c r="AE28" s="160"/>
-      <c r="AF28" s="196">
-        <v>60</v>
-      </c>
-      <c r="AG28" s="165">
-        <v>46370</v>
-      </c>
+      <c r="AF28" s="196"/>
+      <c r="AG28" s="165"/>
       <c r="AH28" s="164"/>
       <c r="AI28" s="163"/>
       <c r="AJ28" s="161"/>
       <c r="AK28" s="161"/>
       <c r="AL28" s="160"/>
       <c r="AM28" s="165"/>
-      <c r="AN28" t="s" s="198">
-        <v>118</v>
-      </c>
+      <c r="AN28" s="166"/>
       <c r="AO28" s="10"/>
       <c r="AP28" s="12"/>
       <c r="AQ28" s="12"/>
@@ -24446,35 +24537,49 @@
         <v>18</v>
       </c>
       <c r="B29" t="s" s="167">
-        <v>119</v>
-      </c>
-      <c r="C29" t="s" s="197">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="C29" t="s" s="156">
+        <v>117</v>
       </c>
       <c r="D29" s="165"/>
       <c r="E29" s="164"/>
-      <c r="F29" s="195" cm="1" t="str">
+      <c r="F29" s="163" cm="1">
         <f t="array" ref="F29">IF(AG29="","",I29-H29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="160"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="159" cm="1" t="str">
+        <v>46275</v>
+      </c>
+      <c r="G29" s="160">
+        <v>46301</v>
+      </c>
+      <c r="H29" s="158">
+        <v>7</v>
+      </c>
+      <c r="I29" s="161" cm="1">
         <f t="array" ref="I29">IF(AG29="","",P29-K29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="160"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="161"/>
+        <v>46282</v>
+      </c>
+      <c r="J29" s="160">
+        <v>46302</v>
+      </c>
+      <c r="K29" s="158">
+        <v>7</v>
+      </c>
+      <c r="L29" s="161">
+        <v>46302</v>
+      </c>
       <c r="M29" s="161"/>
       <c r="N29" s="161"/>
       <c r="O29" s="161"/>
-      <c r="P29" s="159" cm="1" t="str">
+      <c r="P29" s="161" cm="1">
         <f t="array" ref="P29">IF(AG29="","",AC29-R29-Q29)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="162"/>
-      <c r="R29" s="162"/>
+        <v>46289</v>
+      </c>
+      <c r="Q29" s="162">
+        <v>7</v>
+      </c>
+      <c r="R29" s="162">
+        <v>14</v>
+      </c>
       <c r="S29" s="161"/>
       <c r="T29" s="161"/>
       <c r="U29" s="161"/>
@@ -24485,14 +24590,20 @@
       <c r="Z29" s="161"/>
       <c r="AA29" s="161"/>
       <c r="AB29" s="160"/>
-      <c r="AC29" s="163"/>
-      <c r="AD29" s="159" cm="1" t="str">
+      <c r="AC29" s="163">
+        <v>46310</v>
+      </c>
+      <c r="AD29" s="161" cm="1">
         <f t="array" ref="AD29">IF(AG29="","",$AG29-$AF29)</f>
-        <v/>
+        <v>46310</v>
       </c>
       <c r="AE29" s="160"/>
-      <c r="AF29" s="196"/>
-      <c r="AG29" s="165"/>
+      <c r="AF29" s="196">
+        <v>60</v>
+      </c>
+      <c r="AG29" s="165">
+        <v>46370</v>
+      </c>
       <c r="AH29" s="164"/>
       <c r="AI29" s="163"/>
       <c r="AJ29" s="161"/>
@@ -24500,7 +24611,7 @@
       <c r="AL29" s="160"/>
       <c r="AM29" s="165"/>
       <c r="AN29" t="s" s="198">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AO29" s="10"/>
       <c r="AP29" s="12"/>
@@ -24533,51 +24644,35 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="167">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s" s="197">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D30" s="165"/>
       <c r="E30" s="164"/>
-      <c r="F30" s="163" cm="1">
+      <c r="F30" s="195" cm="1" t="str">
         <f t="array" ref="F30">IF(AG30="","",I30-H30)</f>
-        <v>46275</v>
-      </c>
-      <c r="G30" s="160">
-        <v>46290</v>
-      </c>
-      <c r="H30" s="158">
-        <v>7</v>
-      </c>
-      <c r="I30" s="161" cm="1">
+        <v/>
+      </c>
+      <c r="G30" s="160"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="159" cm="1" t="str">
         <f t="array" ref="I30">IF(AG30="","",P30-K30)</f>
-        <v>46282</v>
-      </c>
-      <c r="J30" s="160">
-        <v>46290</v>
-      </c>
-      <c r="K30" s="158">
-        <v>7</v>
-      </c>
-      <c r="L30" s="161">
-        <v>46293</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J30" s="160"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="161"/>
       <c r="M30" s="161"/>
-      <c r="N30" s="161">
-        <v>46302</v>
-      </c>
+      <c r="N30" s="161"/>
       <c r="O30" s="161"/>
-      <c r="P30" s="161" cm="1">
+      <c r="P30" s="159" cm="1" t="str">
         <f t="array" ref="P30">IF(AG30="","",AC30-R30-Q30)</f>
-        <v>46289</v>
-      </c>
-      <c r="Q30" s="162">
-        <v>7</v>
-      </c>
-      <c r="R30" s="162">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q30" s="162"/>
+      <c r="R30" s="162"/>
       <c r="S30" s="161"/>
       <c r="T30" s="161"/>
       <c r="U30" s="161"/>
@@ -24588,20 +24683,14 @@
       <c r="Z30" s="161"/>
       <c r="AA30" s="161"/>
       <c r="AB30" s="160"/>
-      <c r="AC30" s="163">
-        <v>46310</v>
-      </c>
-      <c r="AD30" s="161" cm="1">
+      <c r="AC30" s="163"/>
+      <c r="AD30" s="159" cm="1" t="str">
         <f t="array" ref="AD30">IF(AG30="","",$AG30-$AF30)</f>
-        <v>46310</v>
+        <v/>
       </c>
       <c r="AE30" s="160"/>
-      <c r="AF30" s="196">
-        <v>60</v>
-      </c>
-      <c r="AG30" s="165">
-        <v>46370</v>
-      </c>
+      <c r="AF30" s="196"/>
+      <c r="AG30" s="165"/>
       <c r="AH30" s="164"/>
       <c r="AI30" s="163"/>
       <c r="AJ30" s="161"/>
@@ -24609,7 +24698,7 @@
       <c r="AL30" s="160"/>
       <c r="AM30" s="165"/>
       <c r="AN30" t="s" s="198">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AO30" s="10"/>
       <c r="AP30" s="12"/>
@@ -24642,35 +24731,51 @@
         <v>20</v>
       </c>
       <c r="B31" t="s" s="167">
-        <v>125</v>
-      </c>
-      <c r="C31" t="s" s="199">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="C31" t="s" s="197">
+        <v>123</v>
       </c>
       <c r="D31" s="165"/>
       <c r="E31" s="164"/>
-      <c r="F31" s="195" cm="1" t="str">
+      <c r="F31" s="163" cm="1">
         <f t="array" ref="F31">IF(AG31="","",I31-H31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="160"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="159" cm="1" t="str">
+        <v>46275</v>
+      </c>
+      <c r="G31" s="160">
+        <v>46290</v>
+      </c>
+      <c r="H31" s="158">
+        <v>7</v>
+      </c>
+      <c r="I31" s="161" cm="1">
         <f t="array" ref="I31">IF(AG31="","",P31-K31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="160"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="161"/>
+        <v>46282</v>
+      </c>
+      <c r="J31" s="160">
+        <v>46290</v>
+      </c>
+      <c r="K31" s="158">
+        <v>7</v>
+      </c>
+      <c r="L31" s="161">
+        <v>46293</v>
+      </c>
       <c r="M31" s="161"/>
-      <c r="N31" s="161"/>
+      <c r="N31" s="161">
+        <v>46302</v>
+      </c>
       <c r="O31" s="161"/>
-      <c r="P31" s="159" cm="1" t="str">
+      <c r="P31" s="161" cm="1">
         <f t="array" ref="P31">IF(AG31="","",AC31-R31-Q31)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="162"/>
-      <c r="R31" s="162"/>
+        <v>46289</v>
+      </c>
+      <c r="Q31" s="162">
+        <v>7</v>
+      </c>
+      <c r="R31" s="162">
+        <v>14</v>
+      </c>
       <c r="S31" s="161"/>
       <c r="T31" s="161"/>
       <c r="U31" s="161"/>
@@ -24681,22 +24786,28 @@
       <c r="Z31" s="161"/>
       <c r="AA31" s="161"/>
       <c r="AB31" s="160"/>
-      <c r="AC31" s="163"/>
-      <c r="AD31" s="159" cm="1" t="str">
+      <c r="AC31" s="163">
+        <v>46310</v>
+      </c>
+      <c r="AD31" s="161" cm="1">
         <f t="array" ref="AD31">IF(AG31="","",$AG31-$AF31)</f>
-        <v/>
+        <v>46310</v>
       </c>
       <c r="AE31" s="160"/>
-      <c r="AF31" s="196"/>
-      <c r="AG31" s="165"/>
+      <c r="AF31" s="196">
+        <v>60</v>
+      </c>
+      <c r="AG31" s="165">
+        <v>46370</v>
+      </c>
       <c r="AH31" s="164"/>
       <c r="AI31" s="163"/>
       <c r="AJ31" s="161"/>
       <c r="AK31" s="161"/>
       <c r="AL31" s="160"/>
       <c r="AM31" s="165"/>
-      <c r="AN31" t="s" s="169">
-        <v>127</v>
+      <c r="AN31" t="s" s="198">
+        <v>124</v>
       </c>
       <c r="AO31" s="10"/>
       <c r="AP31" s="12"/>
@@ -24728,9 +24839,11 @@
         <f t="array" ref="A32">A31+1</f>
         <v>21</v>
       </c>
-      <c r="B32" s="151"/>
-      <c r="C32" t="s" s="156">
-        <v>128</v>
+      <c r="B32" t="s" s="167">
+        <v>125</v>
+      </c>
+      <c r="C32" t="s" s="199">
+        <v>126</v>
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="164"/>
@@ -24780,7 +24893,9 @@
       <c r="AK32" s="161"/>
       <c r="AL32" s="160"/>
       <c r="AM32" s="165"/>
-      <c r="AN32" s="166"/>
+      <c r="AN32" t="s" s="169">
+        <v>127</v>
+      </c>
       <c r="AO32" s="10"/>
       <c r="AP32" s="12"/>
       <c r="AQ32" s="12"/>
@@ -24811,52 +24926,32 @@
         <f t="array" ref="A33">A32+1</f>
         <v>22</v>
       </c>
-      <c r="B33" t="s" s="167">
-        <v>129</v>
-      </c>
-      <c r="C33" t="s" s="197">
-        <v>130</v>
-      </c>
+      <c r="B33" s="151"/>
+      <c r="C33" s="170"/>
       <c r="D33" s="165"/>
       <c r="E33" s="164"/>
-      <c r="F33" s="163" cm="1">
+      <c r="F33" s="195" cm="1" t="str">
         <f t="array" ref="F33">IF(AG33="","",I33-H33)</f>
-        <v>46269</v>
-      </c>
-      <c r="G33" s="160">
-        <v>46282</v>
-      </c>
-      <c r="H33" s="158">
-        <v>7</v>
-      </c>
-      <c r="I33" s="161" cm="1">
+        <v/>
+      </c>
+      <c r="G33" s="160"/>
+      <c r="H33" s="158"/>
+      <c r="I33" s="159" cm="1" t="str">
         <f t="array" ref="I33">IF(AG33="","",P33-K33)</f>
-        <v>46276</v>
-      </c>
-      <c r="J33" s="160">
-        <v>46289</v>
-      </c>
-      <c r="K33" s="158">
-        <v>7</v>
-      </c>
-      <c r="L33" s="161">
-        <v>46293</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J33" s="160"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="161"/>
       <c r="M33" s="161"/>
-      <c r="N33" s="161">
-        <v>46302</v>
-      </c>
+      <c r="N33" s="161"/>
       <c r="O33" s="161"/>
-      <c r="P33" s="161" cm="1">
+      <c r="P33" s="159" cm="1" t="str">
         <f t="array" ref="P33">IF(AG33="","",AC33-R33-Q33)</f>
-        <v>46283</v>
-      </c>
-      <c r="Q33" s="162">
-        <v>7</v>
-      </c>
-      <c r="R33" s="162">
-        <v>7</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q33" s="162"/>
+      <c r="R33" s="162"/>
       <c r="S33" s="161"/>
       <c r="T33" s="161"/>
       <c r="U33" s="161"/>
@@ -24867,29 +24962,21 @@
       <c r="Z33" s="161"/>
       <c r="AA33" s="161"/>
       <c r="AB33" s="160"/>
-      <c r="AC33" s="163">
-        <v>46297</v>
-      </c>
-      <c r="AD33" s="161" cm="1">
+      <c r="AC33" s="163"/>
+      <c r="AD33" s="159" cm="1" t="str">
         <f t="array" ref="AD33">IF(AG33="","",$AG33-$AF33)</f>
-        <v>46299</v>
+        <v/>
       </c>
       <c r="AE33" s="160"/>
-      <c r="AF33" s="196">
-        <v>80</v>
-      </c>
-      <c r="AG33" s="165">
-        <v>46379</v>
-      </c>
+      <c r="AF33" s="196"/>
+      <c r="AG33" s="165"/>
       <c r="AH33" s="164"/>
       <c r="AI33" s="163"/>
       <c r="AJ33" s="161"/>
       <c r="AK33" s="161"/>
       <c r="AL33" s="160"/>
       <c r="AM33" s="165"/>
-      <c r="AN33" t="s" s="198">
-        <v>131</v>
-      </c>
+      <c r="AN33" s="166"/>
       <c r="AO33" s="10"/>
       <c r="AP33" s="12"/>
       <c r="AQ33" s="12"/>
@@ -24922,7 +25009,7 @@
       </c>
       <c r="B34" s="151"/>
       <c r="C34" t="s" s="156">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D34" s="165"/>
       <c r="E34" s="164"/>
@@ -24972,7 +25059,7 @@
       <c r="AK34" s="161"/>
       <c r="AL34" s="160"/>
       <c r="AM34" s="165"/>
-      <c r="AN34" s="200"/>
+      <c r="AN34" s="166"/>
       <c r="AO34" s="10"/>
       <c r="AP34" s="12"/>
       <c r="AQ34" s="12"/>
@@ -25004,48 +25091,50 @@
         <v>24</v>
       </c>
       <c r="B35" t="s" s="167">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s" s="197">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D35" s="165"/>
       <c r="E35" s="164"/>
       <c r="F35" s="163" cm="1">
         <f t="array" ref="F35">IF(AG35="","",I35-H35)</f>
-        <v>46293</v>
+        <v>46269</v>
       </c>
       <c r="G35" s="160">
-        <v>46300</v>
+        <v>46282</v>
       </c>
       <c r="H35" s="158">
         <v>7</v>
       </c>
       <c r="I35" s="161" cm="1">
         <f t="array" ref="I35">IF(AG35="","",P35-K35)</f>
-        <v>46300</v>
+        <v>46276</v>
       </c>
       <c r="J35" s="160">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="K35" s="158">
         <v>7</v>
       </c>
       <c r="L35" s="161">
+        <v>46293</v>
+      </c>
+      <c r="M35" s="161"/>
+      <c r="N35" s="161">
         <v>46302</v>
       </c>
-      <c r="M35" s="161"/>
-      <c r="N35" s="161"/>
       <c r="O35" s="161"/>
       <c r="P35" s="161" cm="1">
         <f t="array" ref="P35">IF(AG35="","",AC35-R35-Q35)</f>
-        <v>46307</v>
+        <v>46283</v>
       </c>
       <c r="Q35" s="162">
         <v>7</v>
       </c>
       <c r="R35" s="162">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S35" s="161"/>
       <c r="T35" s="161"/>
@@ -25058,18 +25147,18 @@
       <c r="AA35" s="161"/>
       <c r="AB35" s="160"/>
       <c r="AC35" s="163">
-        <v>46328</v>
+        <v>46297</v>
       </c>
       <c r="AD35" s="161" cm="1">
         <f t="array" ref="AD35">IF(AG35="","",$AG35-$AF35)</f>
-        <v>46329</v>
+        <v>46299</v>
       </c>
       <c r="AE35" s="160"/>
       <c r="AF35" s="196">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG35" s="165">
-        <v>46419</v>
+        <v>46379</v>
       </c>
       <c r="AH35" s="164"/>
       <c r="AI35" s="163"/>
@@ -25078,7 +25167,7 @@
       <c r="AL35" s="160"/>
       <c r="AM35" s="165"/>
       <c r="AN35" t="s" s="198">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AO35" s="10"/>
       <c r="AP35" s="12"/>
@@ -25110,44 +25199,32 @@
         <f t="array" ref="A36">A35+1</f>
         <v>25</v>
       </c>
-      <c r="B36" t="s" s="167">
-        <v>136</v>
-      </c>
-      <c r="C36" t="s" s="156">
-        <v>137</v>
-      </c>
+      <c r="B36" s="151"/>
+      <c r="C36" s="170"/>
       <c r="D36" s="165"/>
       <c r="E36" s="164"/>
-      <c r="F36" s="163" cm="1">
+      <c r="F36" s="195" cm="1" t="str">
         <f t="array" ref="F36">IF(AG36="","",I36-H36)</f>
-        <v>46346</v>
+        <v/>
       </c>
       <c r="G36" s="160"/>
-      <c r="H36" s="158">
-        <v>7</v>
-      </c>
-      <c r="I36" s="161" cm="1">
+      <c r="H36" s="158"/>
+      <c r="I36" s="159" cm="1" t="str">
         <f t="array" ref="I36">IF(AG36="","",P36-K36)</f>
-        <v>46353</v>
+        <v/>
       </c>
       <c r="J36" s="160"/>
-      <c r="K36" s="158">
-        <v>7</v>
-      </c>
+      <c r="K36" s="158"/>
       <c r="L36" s="161"/>
       <c r="M36" s="161"/>
       <c r="N36" s="161"/>
       <c r="O36" s="161"/>
-      <c r="P36" s="161" cm="1">
+      <c r="P36" s="159" cm="1" t="str">
         <f t="array" ref="P36">IF(AG36="","",AC36-R36-Q36)</f>
-        <v>46360</v>
-      </c>
-      <c r="Q36" s="162">
-        <v>7</v>
-      </c>
-      <c r="R36" s="162">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q36" s="162"/>
+      <c r="R36" s="162"/>
       <c r="S36" s="161"/>
       <c r="T36" s="161"/>
       <c r="U36" s="161"/>
@@ -25158,29 +25235,21 @@
       <c r="Z36" s="161"/>
       <c r="AA36" s="161"/>
       <c r="AB36" s="160"/>
-      <c r="AC36" s="163">
-        <v>46381</v>
-      </c>
-      <c r="AD36" s="161" cm="1">
+      <c r="AC36" s="163"/>
+      <c r="AD36" s="159" cm="1" t="str">
         <f t="array" ref="AD36">IF(AG36="","",$AG36-$AF36)</f>
-        <v>46389</v>
+        <v/>
       </c>
       <c r="AE36" s="160"/>
-      <c r="AF36" s="196">
-        <v>30</v>
-      </c>
-      <c r="AG36" s="165">
-        <v>46419</v>
-      </c>
+      <c r="AF36" s="196"/>
+      <c r="AG36" s="165"/>
       <c r="AH36" s="164"/>
       <c r="AI36" s="163"/>
       <c r="AJ36" s="161"/>
       <c r="AK36" s="161"/>
       <c r="AL36" s="160"/>
       <c r="AM36" s="165"/>
-      <c r="AN36" t="s" s="169">
-        <v>138</v>
-      </c>
+      <c r="AN36" s="166"/>
       <c r="AO36" s="10"/>
       <c r="AP36" s="12"/>
       <c r="AQ36" s="12"/>
@@ -25211,44 +25280,34 @@
         <f t="array" ref="A37">A36+1</f>
         <v>26</v>
       </c>
-      <c r="B37" t="s" s="167">
-        <v>139</v>
-      </c>
+      <c r="B37" s="151"/>
       <c r="C37" t="s" s="156">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D37" s="165"/>
       <c r="E37" s="164"/>
-      <c r="F37" s="163" cm="1">
+      <c r="F37" s="195" cm="1" t="str">
         <f t="array" ref="F37">IF(AG37="","",I37-H37)</f>
-        <v>46346</v>
+        <v/>
       </c>
       <c r="G37" s="160"/>
-      <c r="H37" s="158">
-        <v>7</v>
-      </c>
-      <c r="I37" s="161" cm="1">
+      <c r="H37" s="158"/>
+      <c r="I37" s="159" cm="1" t="str">
         <f t="array" ref="I37">IF(AG37="","",P37-K37)</f>
-        <v>46353</v>
+        <v/>
       </c>
       <c r="J37" s="160"/>
-      <c r="K37" s="158">
-        <v>7</v>
-      </c>
+      <c r="K37" s="158"/>
       <c r="L37" s="161"/>
       <c r="M37" s="161"/>
       <c r="N37" s="161"/>
       <c r="O37" s="161"/>
-      <c r="P37" s="161" cm="1">
+      <c r="P37" s="159" cm="1" t="str">
         <f t="array" ref="P37">IF(AG37="","",AC37-R37-Q37)</f>
-        <v>46360</v>
-      </c>
-      <c r="Q37" s="162">
-        <v>7</v>
-      </c>
-      <c r="R37" s="162">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q37" s="162"/>
+      <c r="R37" s="162"/>
       <c r="S37" s="161"/>
       <c r="T37" s="161"/>
       <c r="U37" s="161"/>
@@ -25259,29 +25318,21 @@
       <c r="Z37" s="161"/>
       <c r="AA37" s="161"/>
       <c r="AB37" s="160"/>
-      <c r="AC37" s="163">
-        <v>46381</v>
-      </c>
-      <c r="AD37" s="161" cm="1">
+      <c r="AC37" s="163"/>
+      <c r="AD37" s="159" cm="1" t="str">
         <f t="array" ref="AD37">IF(AG37="","",$AG37-$AF37)</f>
-        <v>46389</v>
+        <v/>
       </c>
       <c r="AE37" s="160"/>
-      <c r="AF37" s="196">
-        <v>30</v>
-      </c>
-      <c r="AG37" s="165">
-        <v>46419</v>
-      </c>
+      <c r="AF37" s="196"/>
+      <c r="AG37" s="165"/>
       <c r="AH37" s="164"/>
       <c r="AI37" s="163"/>
       <c r="AJ37" s="161"/>
       <c r="AK37" s="161"/>
       <c r="AL37" s="160"/>
       <c r="AM37" s="165"/>
-      <c r="AN37" t="s" s="169">
-        <v>138</v>
-      </c>
+      <c r="AN37" s="200"/>
       <c r="AO37" s="10"/>
       <c r="AP37" s="12"/>
       <c r="AQ37" s="12"/>
@@ -25313,36 +25364,42 @@
         <v>27</v>
       </c>
       <c r="B38" t="s" s="167">
-        <v>141</v>
-      </c>
-      <c r="C38" t="s" s="156">
-        <v>142</v>
+        <v>133</v>
+      </c>
+      <c r="C38" t="s" s="197">
+        <v>134</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="164"/>
       <c r="F38" s="163" cm="1">
         <f t="array" ref="F38">IF(AG38="","",I38-H38)</f>
-        <v>46346</v>
-      </c>
-      <c r="G38" s="160"/>
+        <v>46293</v>
+      </c>
+      <c r="G38" s="160">
+        <v>46300</v>
+      </c>
       <c r="H38" s="158">
         <v>7</v>
       </c>
       <c r="I38" s="161" cm="1">
         <f t="array" ref="I38">IF(AG38="","",P38-K38)</f>
-        <v>46353</v>
-      </c>
-      <c r="J38" s="160"/>
+        <v>46300</v>
+      </c>
+      <c r="J38" s="160">
+        <v>46302</v>
+      </c>
       <c r="K38" s="158">
         <v>7</v>
       </c>
-      <c r="L38" s="161"/>
+      <c r="L38" s="161">
+        <v>46302</v>
+      </c>
       <c r="M38" s="161"/>
       <c r="N38" s="161"/>
       <c r="O38" s="161"/>
       <c r="P38" s="161" cm="1">
         <f t="array" ref="P38">IF(AG38="","",AC38-R38-Q38)</f>
-        <v>46360</v>
+        <v>46307</v>
       </c>
       <c r="Q38" s="162">
         <v>7</v>
@@ -25361,15 +25418,15 @@
       <c r="AA38" s="161"/>
       <c r="AB38" s="160"/>
       <c r="AC38" s="163">
-        <v>46381</v>
+        <v>46328</v>
       </c>
       <c r="AD38" s="161" cm="1">
         <f t="array" ref="AD38">IF(AG38="","",$AG38-$AF38)</f>
-        <v>46389</v>
+        <v>46329</v>
       </c>
       <c r="AE38" s="160"/>
       <c r="AF38" s="196">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AG38" s="165">
         <v>46419</v>
@@ -25380,8 +25437,8 @@
       <c r="AK38" s="161"/>
       <c r="AL38" s="160"/>
       <c r="AM38" s="165"/>
-      <c r="AN38" t="s" s="169">
-        <v>138</v>
+      <c r="AN38" t="s" s="198">
+        <v>135</v>
       </c>
       <c r="AO38" s="10"/>
       <c r="AP38" s="12"/>
@@ -25413,34 +25470,44 @@
         <f t="array" ref="A39">A38+1</f>
         <v>28</v>
       </c>
-      <c r="B39" s="151"/>
+      <c r="B39" t="s" s="167">
+        <v>136</v>
+      </c>
       <c r="C39" t="s" s="156">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D39" s="165"/>
       <c r="E39" s="164"/>
-      <c r="F39" s="195" cm="1" t="str">
+      <c r="F39" s="163" cm="1">
         <f t="array" ref="F39">IF(AG39="","",I39-H39)</f>
-        <v/>
+        <v>46346</v>
       </c>
       <c r="G39" s="160"/>
-      <c r="H39" s="158"/>
-      <c r="I39" s="159" cm="1" t="str">
+      <c r="H39" s="158">
+        <v>7</v>
+      </c>
+      <c r="I39" s="161" cm="1">
         <f t="array" ref="I39">IF(AG39="","",P39-K39)</f>
-        <v/>
+        <v>46353</v>
       </c>
       <c r="J39" s="160"/>
-      <c r="K39" s="158"/>
+      <c r="K39" s="158">
+        <v>7</v>
+      </c>
       <c r="L39" s="161"/>
       <c r="M39" s="161"/>
       <c r="N39" s="161"/>
       <c r="O39" s="161"/>
-      <c r="P39" s="159" cm="1" t="str">
+      <c r="P39" s="161" cm="1">
         <f t="array" ref="P39">IF(AG39="","",AC39-R39-Q39)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="162"/>
-      <c r="R39" s="162"/>
+        <v>46360</v>
+      </c>
+      <c r="Q39" s="162">
+        <v>7</v>
+      </c>
+      <c r="R39" s="162">
+        <v>14</v>
+      </c>
       <c r="S39" s="161"/>
       <c r="T39" s="161"/>
       <c r="U39" s="161"/>
@@ -25451,21 +25518,29 @@
       <c r="Z39" s="161"/>
       <c r="AA39" s="161"/>
       <c r="AB39" s="160"/>
-      <c r="AC39" s="163"/>
-      <c r="AD39" s="159" cm="1" t="str">
+      <c r="AC39" s="163">
+        <v>46381</v>
+      </c>
+      <c r="AD39" s="161" cm="1">
         <f t="array" ref="AD39">IF(AG39="","",$AG39-$AF39)</f>
-        <v/>
+        <v>46389</v>
       </c>
       <c r="AE39" s="160"/>
-      <c r="AF39" s="196"/>
-      <c r="AG39" s="165"/>
+      <c r="AF39" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG39" s="165">
+        <v>46419</v>
+      </c>
       <c r="AH39" s="164"/>
       <c r="AI39" s="163"/>
       <c r="AJ39" s="161"/>
       <c r="AK39" s="161"/>
       <c r="AL39" s="160"/>
       <c r="AM39" s="165"/>
-      <c r="AN39" s="166"/>
+      <c r="AN39" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO39" s="10"/>
       <c r="AP39" s="12"/>
       <c r="AQ39" s="12"/>
@@ -25497,30 +25572,26 @@
         <v>29</v>
       </c>
       <c r="B40" t="s" s="167">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s" s="156">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D40" s="165"/>
       <c r="E40" s="164"/>
       <c r="F40" s="163" cm="1">
         <f t="array" ref="F40">IF(AG40="","",I40-H40)</f>
-        <v>46345</v>
-      </c>
-      <c r="G40" s="160">
-        <v>46276</v>
-      </c>
+        <v>46346</v>
+      </c>
+      <c r="G40" s="160"/>
       <c r="H40" s="158">
         <v>7</v>
       </c>
       <c r="I40" s="161" cm="1">
         <f t="array" ref="I40">IF(AG40="","",P40-K40)</f>
-        <v>46352</v>
-      </c>
-      <c r="J40" s="160">
-        <v>46291</v>
-      </c>
+        <v>46353</v>
+      </c>
+      <c r="J40" s="160"/>
       <c r="K40" s="158">
         <v>7</v>
       </c>
@@ -25530,7 +25601,7 @@
       <c r="O40" s="161"/>
       <c r="P40" s="161" cm="1">
         <f t="array" ref="P40">IF(AG40="","",AC40-R40-Q40)</f>
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="Q40" s="162">
         <v>7</v>
@@ -25549,18 +25620,18 @@
       <c r="AA40" s="161"/>
       <c r="AB40" s="160"/>
       <c r="AC40" s="163">
-        <v>46380</v>
+        <v>46381</v>
       </c>
       <c r="AD40" s="161" cm="1">
         <f t="array" ref="AD40">IF(AG40="","",$AG40-$AF40)</f>
-        <v>46380</v>
+        <v>46389</v>
       </c>
       <c r="AE40" s="160"/>
       <c r="AF40" s="196">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AG40" s="165">
-        <v>46440</v>
+        <v>46419</v>
       </c>
       <c r="AH40" s="164"/>
       <c r="AI40" s="163"/>
@@ -25569,7 +25640,7 @@
       <c r="AL40" s="160"/>
       <c r="AM40" s="165"/>
       <c r="AN40" t="s" s="169">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="AO40" s="10"/>
       <c r="AP40" s="12"/>
@@ -25601,34 +25672,44 @@
         <f t="array" ref="A41">A40+1</f>
         <v>30</v>
       </c>
-      <c r="B41" s="151"/>
+      <c r="B41" t="s" s="167">
+        <v>141</v>
+      </c>
       <c r="C41" t="s" s="156">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D41" s="165"/>
       <c r="E41" s="164"/>
-      <c r="F41" s="195" cm="1" t="str">
+      <c r="F41" s="163" cm="1">
         <f t="array" ref="F41">IF(AG41="","",I41-H41)</f>
-        <v/>
+        <v>46346</v>
       </c>
       <c r="G41" s="160"/>
-      <c r="H41" s="158"/>
-      <c r="I41" s="159" cm="1" t="str">
+      <c r="H41" s="158">
+        <v>7</v>
+      </c>
+      <c r="I41" s="161" cm="1">
         <f t="array" ref="I41">IF(AG41="","",P41-K41)</f>
-        <v/>
+        <v>46353</v>
       </c>
       <c r="J41" s="160"/>
-      <c r="K41" s="158"/>
+      <c r="K41" s="158">
+        <v>7</v>
+      </c>
       <c r="L41" s="161"/>
       <c r="M41" s="161"/>
       <c r="N41" s="161"/>
       <c r="O41" s="161"/>
-      <c r="P41" s="159" cm="1" t="str">
+      <c r="P41" s="161" cm="1">
         <f t="array" ref="P41">IF(AG41="","",AC41-R41-Q41)</f>
-        <v/>
-      </c>
-      <c r="Q41" s="162"/>
-      <c r="R41" s="162"/>
+        <v>46360</v>
+      </c>
+      <c r="Q41" s="162">
+        <v>7</v>
+      </c>
+      <c r="R41" s="162">
+        <v>14</v>
+      </c>
       <c r="S41" s="161"/>
       <c r="T41" s="161"/>
       <c r="U41" s="161"/>
@@ -25639,21 +25720,29 @@
       <c r="Z41" s="161"/>
       <c r="AA41" s="161"/>
       <c r="AB41" s="160"/>
-      <c r="AC41" s="163"/>
-      <c r="AD41" s="159" cm="1" t="str">
+      <c r="AC41" s="163">
+        <v>46381</v>
+      </c>
+      <c r="AD41" s="161" cm="1">
         <f t="array" ref="AD41">IF(AG41="","",$AG41-$AF41)</f>
-        <v/>
+        <v>46389</v>
       </c>
       <c r="AE41" s="160"/>
-      <c r="AF41" s="196"/>
-      <c r="AG41" s="165"/>
+      <c r="AF41" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG41" s="165">
+        <v>46419</v>
+      </c>
       <c r="AH41" s="164"/>
       <c r="AI41" s="163"/>
       <c r="AJ41" s="161"/>
       <c r="AK41" s="161"/>
       <c r="AL41" s="160"/>
       <c r="AM41" s="165"/>
-      <c r="AN41" s="166"/>
+      <c r="AN41" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO41" s="10"/>
       <c r="AP41" s="12"/>
       <c r="AQ41" s="12"/>
@@ -25684,50 +25773,32 @@
         <f t="array" ref="A42">A41+1</f>
         <v>31</v>
       </c>
-      <c r="B42" t="s" s="167">
-        <v>148</v>
-      </c>
-      <c r="C42" t="s" s="156">
-        <v>149</v>
-      </c>
+      <c r="B42" s="151"/>
+      <c r="C42" s="170"/>
       <c r="D42" s="165"/>
       <c r="E42" s="164"/>
-      <c r="F42" s="163" cm="1">
+      <c r="F42" s="195" cm="1" t="str">
         <f t="array" ref="F42">IF(AG42="","",I42-H42)</f>
-        <v>46381</v>
-      </c>
-      <c r="G42" s="160">
-        <v>46297</v>
-      </c>
-      <c r="H42" s="158">
-        <v>7</v>
-      </c>
-      <c r="I42" s="161" cm="1">
+        <v/>
+      </c>
+      <c r="G42" s="160"/>
+      <c r="H42" s="158"/>
+      <c r="I42" s="159" cm="1" t="str">
         <f t="array" ref="I42">IF(AG42="","",P42-K42)</f>
-        <v>46388</v>
-      </c>
-      <c r="J42" s="160">
-        <v>46302</v>
-      </c>
-      <c r="K42" s="158">
-        <v>7</v>
-      </c>
-      <c r="L42" s="161">
-        <v>46302</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J42" s="160"/>
+      <c r="K42" s="158"/>
+      <c r="L42" s="161"/>
       <c r="M42" s="161"/>
       <c r="N42" s="161"/>
       <c r="O42" s="161"/>
-      <c r="P42" s="161" cm="1">
+      <c r="P42" s="159" cm="1" t="str">
         <f t="array" ref="P42">IF(AG42="","",AC42-R42-Q42)</f>
-        <v>46395</v>
-      </c>
-      <c r="Q42" s="162">
-        <v>7</v>
-      </c>
-      <c r="R42" s="162">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="Q42" s="162"/>
+      <c r="R42" s="162"/>
       <c r="S42" s="161"/>
       <c r="T42" s="161"/>
       <c r="U42" s="161"/>
@@ -25738,29 +25809,21 @@
       <c r="Z42" s="161"/>
       <c r="AA42" s="161"/>
       <c r="AB42" s="160"/>
-      <c r="AC42" s="163">
-        <v>46416</v>
-      </c>
-      <c r="AD42" s="161" cm="1">
+      <c r="AC42" s="163"/>
+      <c r="AD42" s="159" cm="1" t="str">
         <f t="array" ref="AD42">IF(AG42="","",$AG42-$AF42)</f>
-        <v>46417</v>
+        <v/>
       </c>
       <c r="AE42" s="160"/>
-      <c r="AF42" s="196">
-        <v>30</v>
-      </c>
-      <c r="AG42" s="165">
-        <v>46447</v>
-      </c>
+      <c r="AF42" s="196"/>
+      <c r="AG42" s="165"/>
       <c r="AH42" s="164"/>
       <c r="AI42" s="163"/>
       <c r="AJ42" s="161"/>
       <c r="AK42" s="161"/>
       <c r="AL42" s="160"/>
       <c r="AM42" s="165"/>
-      <c r="AN42" t="s" s="169">
-        <v>138</v>
-      </c>
+      <c r="AN42" s="166"/>
       <c r="AO42" s="10"/>
       <c r="AP42" s="12"/>
       <c r="AQ42" s="12"/>
@@ -25793,7 +25856,7 @@
       </c>
       <c r="B43" s="151"/>
       <c r="C43" t="s" s="156">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D43" s="165"/>
       <c r="E43" s="164"/>
@@ -25875,26 +25938,30 @@
         <v>33</v>
       </c>
       <c r="B44" t="s" s="167">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C44" t="s" s="156">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D44" s="165"/>
       <c r="E44" s="164"/>
       <c r="F44" s="163" cm="1">
         <f t="array" ref="F44">IF(AG44="","",I44-H44)</f>
-        <v>46395</v>
-      </c>
-      <c r="G44" s="160"/>
+        <v>46345</v>
+      </c>
+      <c r="G44" s="160">
+        <v>46276</v>
+      </c>
       <c r="H44" s="158">
         <v>7</v>
       </c>
       <c r="I44" s="161" cm="1">
         <f t="array" ref="I44">IF(AG44="","",P44-K44)</f>
-        <v>46402</v>
-      </c>
-      <c r="J44" s="160"/>
+        <v>46352</v>
+      </c>
+      <c r="J44" s="160">
+        <v>46291</v>
+      </c>
       <c r="K44" s="158">
         <v>7</v>
       </c>
@@ -25904,7 +25971,7 @@
       <c r="O44" s="161"/>
       <c r="P44" s="161" cm="1">
         <f t="array" ref="P44">IF(AG44="","",AC44-R44-Q44)</f>
-        <v>46409</v>
+        <v>46359</v>
       </c>
       <c r="Q44" s="162">
         <v>7</v>
@@ -25923,18 +25990,18 @@
       <c r="AA44" s="161"/>
       <c r="AB44" s="160"/>
       <c r="AC44" s="163">
-        <v>46430</v>
+        <v>46380</v>
       </c>
       <c r="AD44" s="161" cm="1">
         <f t="array" ref="AD44">IF(AG44="","",$AG44-$AF44)</f>
-        <v>46432</v>
+        <v>46380</v>
       </c>
       <c r="AE44" s="160"/>
       <c r="AF44" s="196">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AG44" s="165">
-        <v>46462</v>
+        <v>46440</v>
       </c>
       <c r="AH44" s="164"/>
       <c r="AI44" s="163"/>
@@ -25943,7 +26010,7 @@
       <c r="AL44" s="160"/>
       <c r="AM44" s="165"/>
       <c r="AN44" t="s" s="169">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AO44" s="10"/>
       <c r="AP44" s="12"/>
@@ -26058,7 +26125,7 @@
       </c>
       <c r="B46" s="151"/>
       <c r="C46" t="s" s="156">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D46" s="165"/>
       <c r="E46" s="164"/>
@@ -26139,32 +26206,50 @@
         <f t="array" ref="A47">A46+1</f>
         <v>36</v>
       </c>
-      <c r="B47" s="151"/>
-      <c r="C47" s="170"/>
+      <c r="B47" t="s" s="167">
+        <v>148</v>
+      </c>
+      <c r="C47" t="s" s="156">
+        <v>149</v>
+      </c>
       <c r="D47" s="165"/>
       <c r="E47" s="164"/>
-      <c r="F47" s="195" cm="1" t="str">
+      <c r="F47" s="163" cm="1">
         <f t="array" ref="F47">IF(AG47="","",I47-H47)</f>
-        <v/>
-      </c>
-      <c r="G47" s="160"/>
-      <c r="H47" s="158"/>
-      <c r="I47" s="159" cm="1" t="str">
+        <v>46381</v>
+      </c>
+      <c r="G47" s="160">
+        <v>46297</v>
+      </c>
+      <c r="H47" s="158">
+        <v>7</v>
+      </c>
+      <c r="I47" s="161" cm="1">
         <f t="array" ref="I47">IF(AG47="","",P47-K47)</f>
-        <v/>
-      </c>
-      <c r="J47" s="160"/>
-      <c r="K47" s="158"/>
-      <c r="L47" s="161"/>
+        <v>46388</v>
+      </c>
+      <c r="J47" s="160">
+        <v>46302</v>
+      </c>
+      <c r="K47" s="158">
+        <v>7</v>
+      </c>
+      <c r="L47" s="161">
+        <v>46302</v>
+      </c>
       <c r="M47" s="161"/>
       <c r="N47" s="161"/>
       <c r="O47" s="161"/>
-      <c r="P47" s="159" cm="1" t="str">
+      <c r="P47" s="161" cm="1">
         <f t="array" ref="P47">IF(AG47="","",AC47-R47-Q47)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="162"/>
-      <c r="R47" s="162"/>
+        <v>46395</v>
+      </c>
+      <c r="Q47" s="162">
+        <v>7</v>
+      </c>
+      <c r="R47" s="162">
+        <v>14</v>
+      </c>
       <c r="S47" s="161"/>
       <c r="T47" s="161"/>
       <c r="U47" s="161"/>
@@ -26175,21 +26260,29 @@
       <c r="Z47" s="161"/>
       <c r="AA47" s="161"/>
       <c r="AB47" s="160"/>
-      <c r="AC47" s="163"/>
-      <c r="AD47" s="159" cm="1" t="str">
+      <c r="AC47" s="163">
+        <v>46416</v>
+      </c>
+      <c r="AD47" s="161" cm="1">
         <f t="array" ref="AD47">IF(AG47="","",$AG47-$AF47)</f>
-        <v/>
+        <v>46417</v>
       </c>
       <c r="AE47" s="160"/>
-      <c r="AF47" s="196"/>
-      <c r="AG47" s="165"/>
+      <c r="AF47" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG47" s="165">
+        <v>46447</v>
+      </c>
       <c r="AH47" s="164"/>
       <c r="AI47" s="163"/>
       <c r="AJ47" s="161"/>
       <c r="AK47" s="161"/>
       <c r="AL47" s="160"/>
       <c r="AM47" s="165"/>
-      <c r="AN47" s="166"/>
+      <c r="AN47" t="s" s="169">
+        <v>138</v>
+      </c>
       <c r="AO47" s="10"/>
       <c r="AP47" s="12"/>
       <c r="AQ47" s="12"/>
@@ -26302,7 +26395,9 @@
         <v>38</v>
       </c>
       <c r="B49" s="151"/>
-      <c r="C49" s="170"/>
+      <c r="C49" t="s" s="156">
+        <v>150</v>
+      </c>
       <c r="D49" s="165"/>
       <c r="E49" s="164"/>
       <c r="F49" s="195" cm="1" t="str">
@@ -26382,32 +26477,44 @@
         <f t="array" ref="A50">A49+1</f>
         <v>39</v>
       </c>
-      <c r="B50" s="151"/>
-      <c r="C50" s="170"/>
+      <c r="B50" t="s" s="167">
+        <v>151</v>
+      </c>
+      <c r="C50" t="s" s="156">
+        <v>152</v>
+      </c>
       <c r="D50" s="165"/>
       <c r="E50" s="164"/>
-      <c r="F50" s="195" cm="1" t="str">
+      <c r="F50" s="163" cm="1">
         <f t="array" ref="F50">IF(AG50="","",I50-H50)</f>
-        <v/>
+        <v>46395</v>
       </c>
       <c r="G50" s="160"/>
-      <c r="H50" s="158"/>
-      <c r="I50" s="159" cm="1" t="str">
+      <c r="H50" s="158">
+        <v>7</v>
+      </c>
+      <c r="I50" s="161" cm="1">
         <f t="array" ref="I50">IF(AG50="","",P50-K50)</f>
-        <v/>
+        <v>46402</v>
       </c>
       <c r="J50" s="160"/>
-      <c r="K50" s="158"/>
+      <c r="K50" s="158">
+        <v>7</v>
+      </c>
       <c r="L50" s="161"/>
       <c r="M50" s="161"/>
       <c r="N50" s="161"/>
       <c r="O50" s="161"/>
-      <c r="P50" s="159" cm="1" t="str">
+      <c r="P50" s="161" cm="1">
         <f t="array" ref="P50">IF(AG50="","",AC50-R50-Q50)</f>
-        <v/>
-      </c>
-      <c r="Q50" s="162"/>
-      <c r="R50" s="162"/>
+        <v>46409</v>
+      </c>
+      <c r="Q50" s="162">
+        <v>7</v>
+      </c>
+      <c r="R50" s="162">
+        <v>14</v>
+      </c>
       <c r="S50" s="161"/>
       <c r="T50" s="161"/>
       <c r="U50" s="161"/>
@@ -26418,21 +26525,29 @@
       <c r="Z50" s="161"/>
       <c r="AA50" s="161"/>
       <c r="AB50" s="160"/>
-      <c r="AC50" s="163"/>
-      <c r="AD50" s="159" cm="1" t="str">
+      <c r="AC50" s="163">
+        <v>46430</v>
+      </c>
+      <c r="AD50" s="161" cm="1">
         <f t="array" ref="AD50">IF(AG50="","",$AG50-$AF50)</f>
-        <v/>
+        <v>46432</v>
       </c>
       <c r="AE50" s="160"/>
-      <c r="AF50" s="196"/>
-      <c r="AG50" s="165"/>
+      <c r="AF50" s="196">
+        <v>30</v>
+      </c>
+      <c r="AG50" s="165">
+        <v>46462</v>
+      </c>
       <c r="AH50" s="164"/>
       <c r="AI50" s="163"/>
       <c r="AJ50" s="161"/>
       <c r="AK50" s="161"/>
       <c r="AL50" s="160"/>
       <c r="AM50" s="165"/>
-      <c r="AN50" s="166"/>
+      <c r="AN50" t="s" s="169">
+        <v>153</v>
+      </c>
       <c r="AO50" s="10"/>
       <c r="AP50" s="12"/>
       <c r="AQ50" s="12"/>
@@ -26545,7 +26660,9 @@
         <v>41</v>
       </c>
       <c r="B52" s="151"/>
-      <c r="C52" s="170"/>
+      <c r="C52" t="s" s="156">
+        <v>154</v>
+      </c>
       <c r="D52" s="165"/>
       <c r="E52" s="164"/>
       <c r="F52" s="195" cm="1" t="str">
@@ -26788,9 +26905,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="151"/>
-      <c r="C55" t="s" s="156">
-        <v>155</v>
-      </c>
+      <c r="C55" s="170"/>
       <c r="D55" s="165"/>
       <c r="E55" s="164"/>
       <c r="F55" s="195" cm="1" t="str">
@@ -27276,7 +27391,9 @@
         <v>50</v>
       </c>
       <c r="B61" s="151"/>
-      <c r="C61" s="170"/>
+      <c r="C61" t="s" s="156">
+        <v>155</v>
+      </c>
       <c r="D61" s="165"/>
       <c r="E61" s="164"/>
       <c r="F61" s="195" cm="1" t="str">
@@ -27438,9 +27555,7 @@
         <v>52</v>
       </c>
       <c r="B63" s="151"/>
-      <c r="C63" t="s" s="156">
-        <v>156</v>
-      </c>
+      <c r="C63" s="170"/>
       <c r="D63" s="165"/>
       <c r="E63" s="164"/>
       <c r="F63" s="195" cm="1" t="str">
@@ -27926,7 +28041,9 @@
         <v>58</v>
       </c>
       <c r="B69" s="151"/>
-      <c r="C69" s="170"/>
+      <c r="C69" t="s" s="156">
+        <v>156</v>
+      </c>
       <c r="D69" s="165"/>
       <c r="E69" s="164"/>
       <c r="F69" s="195" cm="1" t="str">
@@ -39606,34 +39723,34 @@
       </c>
     </row>
     <row r="4" ht="40.15" customHeight="1">
-      <c r="A4" t="s" s="233">
+      <c r="A4" t="s" s="335">
         <v>158</v>
       </c>
-      <c r="B4" t="s" s="233">
+      <c r="B4" t="s" s="335">
         <v>159</v>
       </c>
       <c r="C4" t="s" s="234">
         <v>160</v>
       </c>
-      <c r="D4" t="s" s="234">
+      <c r="D4" t="s" s="336">
         <v>161</v>
       </c>
-      <c r="E4" t="s" s="235">
+      <c r="E4" t="s" s="337">
         <v>162</v>
       </c>
-      <c r="F4" t="s" s="236">
+      <c r="F4" t="s" s="338">
         <v>163</v>
       </c>
-      <c r="G4" t="s" s="237">
+      <c r="G4" t="s" s="339">
         <v>164</v>
       </c>
-      <c r="H4" t="s" s="236">
+      <c r="H4" t="s" s="338">
         <v>165</v>
       </c>
-      <c r="I4" t="s" s="238">
+      <c r="I4" t="s" s="340">
         <v>166</v>
       </c>
-      <c r="J4" t="s" s="237">
+      <c r="J4" t="s" s="339">
         <v>33</v>
       </c>
       <c r="K4" t="s" s="239">
@@ -39642,10 +39759,10 @@
       <c r="L4" s="240"/>
       <c r="M4" s="240"/>
       <c r="N4" s="241"/>
-      <c r="O4" t="s" s="242">
+      <c r="O4" t="s" s="341">
         <v>168</v>
       </c>
-      <c r="P4" t="s" s="237">
+      <c r="P4" t="s" s="339">
         <v>33</v>
       </c>
       <c r="Q4" t="s" s="243">
@@ -39668,16 +39785,16 @@
         <v>169</v>
       </c>
       <c r="Z4" s="246"/>
-      <c r="AA4" t="s" s="236">
+      <c r="AA4" t="s" s="338">
         <v>170</v>
       </c>
-      <c r="AB4" t="s" s="247">
+      <c r="AB4" t="s" s="342">
         <v>171</v>
       </c>
-      <c r="AC4" t="s" s="248">
+      <c r="AC4" t="s" s="343">
         <v>12</v>
       </c>
-      <c r="AD4" t="s" s="234">
+      <c r="AD4" t="s" s="336">
         <v>172</v>
       </c>
       <c r="AE4" t="s" s="249">
@@ -39685,13 +39802,13 @@
       </c>
       <c r="AF4" s="250"/>
       <c r="AG4" s="251"/>
-      <c r="AH4" t="s" s="252">
+      <c r="AH4" t="s" s="344">
         <v>18</v>
       </c>
-      <c r="AI4" t="s" s="253">
+      <c r="AI4" t="s" s="345">
         <v>19</v>
       </c>
-      <c r="AJ4" t="s" s="253">
+      <c r="AJ4" t="s" s="345">
         <v>20</v>
       </c>
       <c r="AK4" t="s" s="243">
@@ -39739,34 +39856,34 @@
       <c r="N5" s="263"/>
       <c r="O5" s="264"/>
       <c r="P5" s="259"/>
-      <c r="Q5" t="s" s="265">
+      <c r="Q5" t="s" s="346">
         <v>51</v>
       </c>
-      <c r="R5" t="s" s="266">
+      <c r="R5" t="s" s="347">
         <v>52</v>
       </c>
-      <c r="S5" t="s" s="266">
+      <c r="S5" t="s" s="347">
         <v>51</v>
       </c>
-      <c r="T5" t="s" s="266">
+      <c r="T5" t="s" s="347">
         <v>52</v>
       </c>
-      <c r="U5" t="s" s="266">
+      <c r="U5" t="s" s="347">
         <v>51</v>
       </c>
-      <c r="V5" t="s" s="266">
+      <c r="V5" t="s" s="347">
         <v>52</v>
       </c>
-      <c r="W5" t="s" s="266">
+      <c r="W5" t="s" s="347">
         <v>51</v>
       </c>
-      <c r="X5" t="s" s="266">
+      <c r="X5" t="s" s="347">
         <v>52</v>
       </c>
-      <c r="Y5" t="s" s="266">
+      <c r="Y5" t="s" s="347">
         <v>51</v>
       </c>
-      <c r="Z5" t="s" s="267">
+      <c r="Z5" t="s" s="348">
         <v>52</v>
       </c>
       <c r="AA5" s="258"/>
@@ -39779,16 +39896,16 @@
       <c r="AH5" s="149"/>
       <c r="AI5" s="271"/>
       <c r="AJ5" s="271"/>
-      <c r="AK5" t="s" s="265">
+      <c r="AK5" t="s" s="346">
         <v>51</v>
       </c>
-      <c r="AL5" t="s" s="267">
+      <c r="AL5" t="s" s="348">
         <v>52</v>
       </c>
-      <c r="AM5" t="s" s="265">
+      <c r="AM5" t="s" s="346">
         <v>51</v>
       </c>
-      <c r="AN5" t="s" s="267">
+      <c r="AN5" t="s" s="348">
         <v>52</v>
       </c>
       <c r="AO5" s="250"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -6046,7 +6046,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="ffff0000"/>
@@ -6179,6 +6179,22 @@
         <patternFill patternType="solid">
           <fgColor indexed="18"/>
           <bgColor indexed="14"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF7C80"/>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF66"/>
+          <bgColor rgb="FFFFFF66"/>
         </patternFill>
       </fill>
     </dxf>
@@ -21792,6 +21808,38 @@
       <formula>NOT(ISBLANK(S11))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F159">
+    <cfRule type="expression" dxfId="18" priority="50" stopIfTrue="1">
+      <formula>AND(ISNUMBER(F11),F11&lt;=TODAY(),G11="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="51" stopIfTrue="1">
+      <formula>AND(ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7,G11="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I159">
+    <cfRule type="expression" dxfId="18" priority="52" stopIfTrue="1">
+      <formula>AND(ISNUMBER(I11),I11&lt;=TODAY(),J11="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="53" stopIfTrue="1">
+      <formula>AND(ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7,J11="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P11:P159">
+    <cfRule type="expression" dxfId="18" priority="54" stopIfTrue="1">
+      <formula>AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11=""))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="55" stopIfTrue="1">
+      <formula>AND(ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7,OR(L11="",M11=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC11:AC159">
+    <cfRule type="expression" dxfId="18" priority="56" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11=""))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="57" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7,OR(S11="",T11=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.472441" right="0.19685" top="0.787402" bottom="0.19685" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>
@@ -39520,6 +39568,38 @@
       <formula>NOT(ISBLANK(S12))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F210">
+    <cfRule type="expression" dxfId="18" priority="50" stopIfTrue="1">
+      <formula>AND(ISNUMBER(F11),F11&lt;=TODAY(),G11="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="51" stopIfTrue="1">
+      <formula>AND(ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7,G11="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I210">
+    <cfRule type="expression" dxfId="18" priority="52" stopIfTrue="1">
+      <formula>AND(ISNUMBER(I11),I11&lt;=TODAY(),J11="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="53" stopIfTrue="1">
+      <formula>AND(ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7,J11="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P11:P210">
+    <cfRule type="expression" dxfId="18" priority="54" stopIfTrue="1">
+      <formula>AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11=""))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="55" stopIfTrue="1">
+      <formula>AND(ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7,OR(L11="",M11=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC11:AC210">
+    <cfRule type="expression" dxfId="18" priority="56" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11=""))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="57" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7,OR(S11="",T11=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.472441" right="0.19685" top="0.787402" bottom="0.19685" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -11716,9 +11716,7 @@
         <v>23</v>
       </c>
       <c r="B35" s="151"/>
-      <c r="C35" t="s" s="156">
-        <v>78</v>
-      </c>
+      <c r="C35" s="156"/>
       <c r="D35" t="str" s="157" cm="1">
         <f t="array" ref="D35">IF(F35="","",F35-E35)</f>
       </c>
@@ -12118,9 +12116,7 @@
         <v>28</v>
       </c>
       <c r="B40" s="151"/>
-      <c r="C40" t="s" s="156">
-        <v>79</v>
-      </c>
+      <c r="C40" s="156"/>
       <c r="D40" t="str" s="157" cm="1">
         <f t="array" ref="D40">IF(F40="","",F40-E40)</f>
       </c>
@@ -12520,9 +12516,7 @@
         <v>33</v>
       </c>
       <c r="B45" s="151"/>
-      <c r="C45" t="s" s="156">
-        <v>80</v>
-      </c>
+      <c r="C45" s="156"/>
       <c r="D45" t="str" s="157" cm="1">
         <f t="array" ref="D45">IF(F45="","",F45-E45)</f>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -26702,9 +26702,7 @@
         <v>41</v>
       </c>
       <c r="B52" s="151"/>
-      <c r="C52" t="s" s="156">
-        <v>154</v>
-      </c>
+      <c r="C52" s="156"/>
       <c r="D52" s="165"/>
       <c r="E52" s="164"/>
       <c r="F52" s="195" cm="1" t="str">
@@ -27433,9 +27431,7 @@
         <v>50</v>
       </c>
       <c r="B61" s="151"/>
-      <c r="C61" t="s" s="156">
-        <v>155</v>
-      </c>
+      <c r="C61" s="156"/>
       <c r="D61" s="165"/>
       <c r="E61" s="164"/>
       <c r="F61" s="195" cm="1" t="str">
@@ -28083,9 +28079,7 @@
         <v>58</v>
       </c>
       <c r="B69" s="151"/>
-      <c r="C69" t="s" s="156">
-        <v>156</v>
-      </c>
+      <c r="C69" s="156"/>
       <c r="D69" s="165"/>
       <c r="E69" s="164"/>
       <c r="F69" s="195" cm="1" t="str">

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -4994,7 +4994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="356">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -6041,6 +6041,27 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="5" borderId="81" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="10" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9608,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="151"/>
-      <c r="C11" t="s" s="156">
+      <c r="C11" t="s" s="349">
         <v>59</v>
       </c>
       <c r="D11" t="str" s="157" cm="1">
@@ -9692,7 +9713,7 @@
       <c r="B12" t="s" s="167">
         <v>60</v>
       </c>
-      <c r="C12" t="s" s="156">
+      <c r="C12" t="s" s="349">
         <v>61</v>
       </c>
       <c r="D12" s="165" cm="1">
@@ -9805,7 +9826,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="151"/>
-      <c r="C13" s="170"/>
+      <c r="C13" s="350"/>
       <c r="D13" t="str" s="157" cm="1">
         <f t="array" ref="D13">IF(F13="","",F13-E13)</f>
       </c>
@@ -9889,7 +9910,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="151"/>
-      <c r="C14" s="170"/>
+      <c r="C14" s="350"/>
       <c r="D14" t="str" s="157" cm="1">
         <f t="array" ref="D14">IF(F14="","",F14-E14)</f>
       </c>
@@ -9969,7 +9990,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="151"/>
-      <c r="C15" t="s" s="156">
+      <c r="C15" t="s" s="349">
         <v>64</v>
       </c>
       <c r="D15" t="str" s="157" cm="1">
@@ -10053,7 +10074,7 @@
       <c r="B16" t="s" s="167">
         <v>65</v>
       </c>
-      <c r="C16" t="s" s="156">
+      <c r="C16" t="s" s="349">
         <v>66</v>
       </c>
       <c r="D16" s="165" cm="1">
@@ -10166,7 +10187,7 @@
       <c r="B17" t="s" s="167">
         <v>68</v>
       </c>
-      <c r="C17" t="s" s="156">
+      <c r="C17" t="s" s="349">
         <v>69</v>
       </c>
       <c r="D17" s="165" cm="1">
@@ -10273,7 +10294,7 @@
       <c r="B18" t="s" s="167">
         <v>70</v>
       </c>
-      <c r="C18" t="s" s="156">
+      <c r="C18" t="s" s="349">
         <v>71</v>
       </c>
       <c r="D18" s="165" cm="1">
@@ -10380,7 +10401,7 @@
       <c r="B19" t="s" s="167">
         <v>72</v>
       </c>
-      <c r="C19" t="s" s="156">
+      <c r="C19" t="s" s="349">
         <v>73</v>
       </c>
       <c r="D19" s="165" cm="1">
@@ -10489,7 +10510,7 @@
       <c r="B20" t="s" s="167">
         <v>75</v>
       </c>
-      <c r="C20" t="s" s="156">
+      <c r="C20" t="s" s="349">
         <v>76</v>
       </c>
       <c r="D20" s="165" cm="1">
@@ -10596,7 +10617,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="151"/>
-      <c r="C21" s="170"/>
+      <c r="C21" s="350"/>
       <c r="D21" t="str" s="157" cm="1">
         <f t="array" ref="D21">IF(F21="","",F21-E21)</f>
       </c>
@@ -10676,7 +10697,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="151"/>
-      <c r="C22" s="170"/>
+      <c r="C22" s="350"/>
       <c r="D22" t="str" s="157" cm="1">
         <f t="array" ref="D22">IF(F22="","",F22-E22)</f>
       </c>
@@ -10756,7 +10777,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="151"/>
-      <c r="C23" s="170"/>
+      <c r="C23" s="350"/>
       <c r="D23" t="str" s="157" cm="1">
         <f t="array" ref="D23">IF(F23="","",F23-E23)</f>
       </c>
@@ -10836,7 +10857,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="151"/>
-      <c r="C24" s="170"/>
+      <c r="C24" s="350"/>
       <c r="D24" t="str" s="157" cm="1">
         <f t="array" ref="D24">IF(F24="","",F24-E24)</f>
       </c>
@@ -10916,7 +10937,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="151"/>
-      <c r="C25" s="170"/>
+      <c r="C25" s="350"/>
       <c r="D25" t="str" s="157" cm="1">
         <f t="array" ref="D25">IF(F25="","",F25-E25)</f>
       </c>
@@ -10996,7 +11017,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="151"/>
-      <c r="C26" s="170"/>
+      <c r="C26" s="350"/>
       <c r="D26" t="str" s="157" cm="1">
         <f t="array" ref="D26">IF(F26="","",F26-E26)</f>
       </c>
@@ -11076,7 +11097,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="151"/>
-      <c r="C27" s="170"/>
+      <c r="C27" s="350"/>
       <c r="D27" t="str" s="157" cm="1">
         <f t="array" ref="D27">IF(F27="","",F27-E27)</f>
       </c>
@@ -11156,7 +11177,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="151"/>
-      <c r="C28" s="170"/>
+      <c r="C28" s="350"/>
       <c r="D28" t="str" s="157" cm="1">
         <f t="array" ref="D28">IF(F28="","",F28-E28)</f>
       </c>
@@ -11236,7 +11257,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="151"/>
-      <c r="C29" s="170"/>
+      <c r="C29" s="350"/>
       <c r="D29" t="str" s="157" cm="1">
         <f t="array" ref="D29">IF(F29="","",F29-E29)</f>
       </c>
@@ -11316,7 +11337,7 @@
         <v>18</v>
       </c>
       <c r="B30" s="151"/>
-      <c r="C30" s="170"/>
+      <c r="C30" s="350"/>
       <c r="D30" t="str" s="157" cm="1">
         <f t="array" ref="D30">IF(F30="","",F30-E30)</f>
       </c>
@@ -11396,7 +11417,7 @@
         <v>19</v>
       </c>
       <c r="B31" s="151"/>
-      <c r="C31" s="170"/>
+      <c r="C31" s="350"/>
       <c r="D31" t="str" s="157" cm="1">
         <f t="array" ref="D31">IF(F31="","",F31-E31)</f>
       </c>
@@ -11476,7 +11497,7 @@
         <v>20</v>
       </c>
       <c r="B32" s="151"/>
-      <c r="C32" s="170"/>
+      <c r="C32" s="350"/>
       <c r="D32" t="str" s="157" cm="1">
         <f t="array" ref="D32">IF(F32="","",F32-E32)</f>
       </c>
@@ -11556,7 +11577,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="151"/>
-      <c r="C33" s="170"/>
+      <c r="C33" s="350"/>
       <c r="D33" t="str" s="157" cm="1">
         <f t="array" ref="D33">IF(F33="","",F33-E33)</f>
       </c>
@@ -11636,7 +11657,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="151"/>
-      <c r="C34" s="170"/>
+      <c r="C34" s="350"/>
       <c r="D34" t="str" s="157" cm="1">
         <f t="array" ref="D34">IF(F34="","",F34-E34)</f>
       </c>
@@ -11716,7 +11737,7 @@
         <v>23</v>
       </c>
       <c r="B35" s="151"/>
-      <c r="C35" s="156"/>
+      <c r="C35" s="349"/>
       <c r="D35" t="str" s="157" cm="1">
         <f t="array" ref="D35">IF(F35="","",F35-E35)</f>
       </c>
@@ -11796,7 +11817,7 @@
         <v>24</v>
       </c>
       <c r="B36" s="151"/>
-      <c r="C36" s="170"/>
+      <c r="C36" s="350"/>
       <c r="D36" t="str" s="157" cm="1">
         <f t="array" ref="D36">IF(F36="","",F36-E36)</f>
       </c>
@@ -11876,7 +11897,7 @@
         <v>25</v>
       </c>
       <c r="B37" s="151"/>
-      <c r="C37" s="170"/>
+      <c r="C37" s="350"/>
       <c r="D37" t="str" s="157" cm="1">
         <f t="array" ref="D37">IF(F37="","",F37-E37)</f>
       </c>
@@ -11956,7 +11977,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="151"/>
-      <c r="C38" s="170"/>
+      <c r="C38" s="350"/>
       <c r="D38" t="str" s="157" cm="1">
         <f t="array" ref="D38">IF(F38="","",F38-E38)</f>
       </c>
@@ -12036,7 +12057,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="151"/>
-      <c r="C39" s="170"/>
+      <c r="C39" s="350"/>
       <c r="D39" t="str" s="157" cm="1">
         <f t="array" ref="D39">IF(F39="","",F39-E39)</f>
       </c>
@@ -12116,7 +12137,7 @@
         <v>28</v>
       </c>
       <c r="B40" s="151"/>
-      <c r="C40" s="156"/>
+      <c r="C40" s="349"/>
       <c r="D40" t="str" s="157" cm="1">
         <f t="array" ref="D40">IF(F40="","",F40-E40)</f>
       </c>
@@ -12196,7 +12217,7 @@
         <v>29</v>
       </c>
       <c r="B41" s="151"/>
-      <c r="C41" s="170"/>
+      <c r="C41" s="350"/>
       <c r="D41" t="str" s="157" cm="1">
         <f t="array" ref="D41">IF(F41="","",F41-E41)</f>
       </c>
@@ -12276,7 +12297,7 @@
         <v>30</v>
       </c>
       <c r="B42" s="151"/>
-      <c r="C42" s="170"/>
+      <c r="C42" s="350"/>
       <c r="D42" t="str" s="157" cm="1">
         <f t="array" ref="D42">IF(F42="","",F42-E42)</f>
       </c>
@@ -12356,7 +12377,7 @@
         <v>31</v>
       </c>
       <c r="B43" s="151"/>
-      <c r="C43" s="170"/>
+      <c r="C43" s="350"/>
       <c r="D43" t="str" s="157" cm="1">
         <f t="array" ref="D43">IF(F43="","",F43-E43)</f>
       </c>
@@ -12436,7 +12457,7 @@
         <v>32</v>
       </c>
       <c r="B44" s="151"/>
-      <c r="C44" s="170"/>
+      <c r="C44" s="350"/>
       <c r="D44" t="str" s="157" cm="1">
         <f t="array" ref="D44">IF(F44="","",F44-E44)</f>
       </c>
@@ -12516,7 +12537,7 @@
         <v>33</v>
       </c>
       <c r="B45" s="151"/>
-      <c r="C45" s="156"/>
+      <c r="C45" s="349"/>
       <c r="D45" t="str" s="157" cm="1">
         <f t="array" ref="D45">IF(F45="","",F45-E45)</f>
       </c>
@@ -12596,7 +12617,7 @@
         <v>34</v>
       </c>
       <c r="B46" s="151"/>
-      <c r="C46" s="170"/>
+      <c r="C46" s="350"/>
       <c r="D46" t="str" s="157" cm="1">
         <f t="array" ref="D46">IF(F46="","",F46-E46)</f>
       </c>
@@ -12676,7 +12697,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="151"/>
-      <c r="C47" s="170"/>
+      <c r="C47" s="350"/>
       <c r="D47" t="str" s="157" cm="1">
         <f t="array" ref="D47">IF(F47="","",F47-E47)</f>
       </c>
@@ -12756,7 +12777,7 @@
         <v>36</v>
       </c>
       <c r="B48" s="151"/>
-      <c r="C48" s="170"/>
+      <c r="C48" s="350"/>
       <c r="D48" t="str" s="157" cm="1">
         <f t="array" ref="D48">IF(F48="","",F48-E48)</f>
       </c>
@@ -12836,7 +12857,7 @@
         <v>37</v>
       </c>
       <c r="B49" s="151"/>
-      <c r="C49" s="170"/>
+      <c r="C49" s="350"/>
       <c r="D49" t="str" s="157" cm="1">
         <f t="array" ref="D49">IF(F49="","",F49-E49)</f>
       </c>
@@ -12916,7 +12937,7 @@
         <v>38</v>
       </c>
       <c r="B50" s="151"/>
-      <c r="C50" s="170"/>
+      <c r="C50" s="350"/>
       <c r="D50" t="str" s="157" cm="1">
         <f t="array" ref="D50">IF(F50="","",F50-E50)</f>
       </c>
@@ -12996,7 +13017,7 @@
         <v>39</v>
       </c>
       <c r="B51" s="151"/>
-      <c r="C51" s="170"/>
+      <c r="C51" s="350"/>
       <c r="D51" t="str" s="157" cm="1">
         <f t="array" ref="D51">IF(F51="","",F51-E51)</f>
       </c>
@@ -13076,7 +13097,7 @@
         <v>40</v>
       </c>
       <c r="B52" s="151"/>
-      <c r="C52" s="170"/>
+      <c r="C52" s="350"/>
       <c r="D52" t="str" s="157" cm="1">
         <f t="array" ref="D52">IF(F52="","",F52-E52)</f>
       </c>
@@ -13156,7 +13177,7 @@
         <v>41</v>
       </c>
       <c r="B53" s="151"/>
-      <c r="C53" s="170"/>
+      <c r="C53" s="350"/>
       <c r="D53" t="str" s="157" cm="1">
         <f t="array" ref="D53">IF(F53="","",F53-E53)</f>
       </c>
@@ -13236,7 +13257,7 @@
         <v>42</v>
       </c>
       <c r="B54" s="151"/>
-      <c r="C54" s="170"/>
+      <c r="C54" s="350"/>
       <c r="D54" t="str" s="157" cm="1">
         <f t="array" ref="D54">IF(F54="","",F54-E54)</f>
       </c>
@@ -13316,7 +13337,7 @@
         <v>43</v>
       </c>
       <c r="B55" s="151"/>
-      <c r="C55" s="170"/>
+      <c r="C55" s="350"/>
       <c r="D55" t="str" s="157" cm="1">
         <f t="array" ref="D55">IF(F55="","",F55-E55)</f>
       </c>
@@ -13396,7 +13417,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="151"/>
-      <c r="C56" s="170"/>
+      <c r="C56" s="350"/>
       <c r="D56" t="str" s="157" cm="1">
         <f t="array" ref="D56">IF(F56="","",F56-E56)</f>
       </c>
@@ -13476,7 +13497,7 @@
         <v>45</v>
       </c>
       <c r="B57" s="151"/>
-      <c r="C57" s="170"/>
+      <c r="C57" s="350"/>
       <c r="D57" t="str" s="157" cm="1">
         <f t="array" ref="D57">IF(F57="","",F57-E57)</f>
       </c>
@@ -13556,7 +13577,7 @@
         <v>46</v>
       </c>
       <c r="B58" s="151"/>
-      <c r="C58" s="170"/>
+      <c r="C58" s="350"/>
       <c r="D58" t="str" s="157" cm="1">
         <f t="array" ref="D58">IF(F58="","",F58-E58)</f>
       </c>
@@ -13636,7 +13657,7 @@
         <v>47</v>
       </c>
       <c r="B59" s="151"/>
-      <c r="C59" s="170"/>
+      <c r="C59" s="350"/>
       <c r="D59" t="str" s="157" cm="1">
         <f t="array" ref="D59">IF(F59="","",F59-E59)</f>
       </c>
@@ -13716,7 +13737,7 @@
         <v>48</v>
       </c>
       <c r="B60" s="151"/>
-      <c r="C60" s="170"/>
+      <c r="C60" s="350"/>
       <c r="D60" t="str" s="157" cm="1">
         <f t="array" ref="D60">IF(F60="","",F60-E60)</f>
       </c>
@@ -13796,7 +13817,7 @@
         <v>49</v>
       </c>
       <c r="B61" s="151"/>
-      <c r="C61" s="170"/>
+      <c r="C61" s="350"/>
       <c r="D61" t="str" s="157" cm="1">
         <f t="array" ref="D61">IF(F61="","",F61-E61)</f>
       </c>
@@ -13876,7 +13897,7 @@
         <v>50</v>
       </c>
       <c r="B62" s="151"/>
-      <c r="C62" s="170"/>
+      <c r="C62" s="350"/>
       <c r="D62" t="str" s="157" cm="1">
         <f t="array" ref="D62">IF(F62="","",F62-E62)</f>
       </c>
@@ -13956,7 +13977,7 @@
         <v>51</v>
       </c>
       <c r="B63" s="151"/>
-      <c r="C63" s="170"/>
+      <c r="C63" s="350"/>
       <c r="D63" t="str" s="157" cm="1">
         <f t="array" ref="D63">IF(F63="","",F63-E63)</f>
       </c>
@@ -14036,7 +14057,7 @@
         <v>52</v>
       </c>
       <c r="B64" s="151"/>
-      <c r="C64" s="170"/>
+      <c r="C64" s="350"/>
       <c r="D64" t="str" s="157" cm="1">
         <f t="array" ref="D64">IF(F64="","",F64-E64)</f>
       </c>
@@ -14116,7 +14137,7 @@
         <v>53</v>
       </c>
       <c r="B65" s="151"/>
-      <c r="C65" s="170"/>
+      <c r="C65" s="350"/>
       <c r="D65" t="str" s="157" cm="1">
         <f t="array" ref="D65">IF(F65="","",F65-E65)</f>
       </c>
@@ -14196,7 +14217,7 @@
         <v>54</v>
       </c>
       <c r="B66" s="151"/>
-      <c r="C66" s="170"/>
+      <c r="C66" s="350"/>
       <c r="D66" t="str" s="157" cm="1">
         <f t="array" ref="D66">IF(F66="","",F66-E66)</f>
       </c>
@@ -14276,7 +14297,7 @@
         <v>55</v>
       </c>
       <c r="B67" s="151"/>
-      <c r="C67" s="170"/>
+      <c r="C67" s="350"/>
       <c r="D67" t="str" s="157" cm="1">
         <f t="array" ref="D67">IF(F67="","",F67-E67)</f>
       </c>
@@ -14356,7 +14377,7 @@
         <v>56</v>
       </c>
       <c r="B68" s="151"/>
-      <c r="C68" s="170"/>
+      <c r="C68" s="350"/>
       <c r="D68" t="str" s="157" cm="1">
         <f t="array" ref="D68">IF(F68="","",F68-E68)</f>
       </c>
@@ -14436,7 +14457,7 @@
         <v>57</v>
       </c>
       <c r="B69" s="151"/>
-      <c r="C69" s="170"/>
+      <c r="C69" s="350"/>
       <c r="D69" t="str" s="157" cm="1">
         <f t="array" ref="D69">IF(F69="","",F69-E69)</f>
       </c>
@@ -14516,7 +14537,7 @@
         <v>58</v>
       </c>
       <c r="B70" s="151"/>
-      <c r="C70" s="170"/>
+      <c r="C70" s="350"/>
       <c r="D70" t="str" s="157" cm="1">
         <f t="array" ref="D70">IF(F70="","",F70-E70)</f>
       </c>
@@ -14596,7 +14617,7 @@
         <v>59</v>
       </c>
       <c r="B71" s="151"/>
-      <c r="C71" s="170"/>
+      <c r="C71" s="350"/>
       <c r="D71" t="str" s="157" cm="1">
         <f t="array" ref="D71">IF(F71="","",F71-E71)</f>
       </c>
@@ -14676,7 +14697,7 @@
         <v>60</v>
       </c>
       <c r="B72" s="151"/>
-      <c r="C72" s="170"/>
+      <c r="C72" s="350"/>
       <c r="D72" t="str" s="157" cm="1">
         <f t="array" ref="D72">IF(F72="","",F72-E72)</f>
       </c>
@@ -14756,7 +14777,7 @@
         <v>61</v>
       </c>
       <c r="B73" s="151"/>
-      <c r="C73" s="170"/>
+      <c r="C73" s="350"/>
       <c r="D73" t="str" s="157" cm="1">
         <f t="array" ref="D73">IF(F73="","",F73-E73)</f>
       </c>
@@ -14836,7 +14857,7 @@
         <v>62</v>
       </c>
       <c r="B74" s="151"/>
-      <c r="C74" s="170"/>
+      <c r="C74" s="350"/>
       <c r="D74" t="str" s="157" cm="1">
         <f t="array" ref="D74">IF(F74="","",F74-E74)</f>
       </c>
@@ -14916,7 +14937,7 @@
         <v>63</v>
       </c>
       <c r="B75" s="151"/>
-      <c r="C75" s="170"/>
+      <c r="C75" s="350"/>
       <c r="D75" t="str" s="157" cm="1">
         <f t="array" ref="D75">IF(F75="","",F75-E75)</f>
       </c>
@@ -14996,7 +15017,7 @@
         <v>64</v>
       </c>
       <c r="B76" s="151"/>
-      <c r="C76" s="170"/>
+      <c r="C76" s="350"/>
       <c r="D76" t="str" s="157" cm="1">
         <f t="array" ref="D76">IF(F76="","",F76-E76)</f>
       </c>
@@ -15076,7 +15097,7 @@
         <v>65</v>
       </c>
       <c r="B77" s="151"/>
-      <c r="C77" s="170"/>
+      <c r="C77" s="350"/>
       <c r="D77" t="str" s="157" cm="1">
         <f t="array" ref="D77">IF(F77="","",F77-E77)</f>
       </c>
@@ -15156,7 +15177,7 @@
         <v>66</v>
       </c>
       <c r="B78" s="151"/>
-      <c r="C78" s="170"/>
+      <c r="C78" s="350"/>
       <c r="D78" t="str" s="157" cm="1">
         <f t="array" ref="D78">IF(F78="","",F78-E78)</f>
       </c>
@@ -15236,7 +15257,7 @@
         <v>67</v>
       </c>
       <c r="B79" s="151"/>
-      <c r="C79" s="170"/>
+      <c r="C79" s="350"/>
       <c r="D79" t="str" s="157" cm="1">
         <f t="array" ref="D79">IF(F79="","",F79-E79)</f>
       </c>
@@ -15316,7 +15337,7 @@
         <v>68</v>
       </c>
       <c r="B80" s="151"/>
-      <c r="C80" s="170"/>
+      <c r="C80" s="350"/>
       <c r="D80" t="str" s="157" cm="1">
         <f t="array" ref="D80">IF(F80="","",F80-E80)</f>
       </c>
@@ -15396,7 +15417,7 @@
         <v>69</v>
       </c>
       <c r="B81" s="151"/>
-      <c r="C81" s="170"/>
+      <c r="C81" s="350"/>
       <c r="D81" t="str" s="157" cm="1">
         <f t="array" ref="D81">IF(F81="","",F81-E81)</f>
       </c>
@@ -15476,7 +15497,7 @@
         <v>70</v>
       </c>
       <c r="B82" s="151"/>
-      <c r="C82" s="170"/>
+      <c r="C82" s="350"/>
       <c r="D82" t="str" s="157" cm="1">
         <f t="array" ref="D82">IF(F82="","",F82-E82)</f>
       </c>
@@ -15556,7 +15577,7 @@
         <v>71</v>
       </c>
       <c r="B83" s="151"/>
-      <c r="C83" s="170"/>
+      <c r="C83" s="350"/>
       <c r="D83" t="str" s="157" cm="1">
         <f t="array" ref="D83">IF(F83="","",F83-E83)</f>
       </c>
@@ -15636,7 +15657,7 @@
         <v>72</v>
       </c>
       <c r="B84" s="151"/>
-      <c r="C84" s="170"/>
+      <c r="C84" s="350"/>
       <c r="D84" t="str" s="157" cm="1">
         <f t="array" ref="D84">IF(F84="","",F84-E84)</f>
       </c>
@@ -15716,7 +15737,7 @@
         <v>73</v>
       </c>
       <c r="B85" s="151"/>
-      <c r="C85" s="170"/>
+      <c r="C85" s="350"/>
       <c r="D85" t="str" s="157" cm="1">
         <f t="array" ref="D85">IF(F85="","",F85-E85)</f>
       </c>
@@ -15796,7 +15817,7 @@
         <v>74</v>
       </c>
       <c r="B86" s="151"/>
-      <c r="C86" s="170"/>
+      <c r="C86" s="350"/>
       <c r="D86" t="str" s="157" cm="1">
         <f t="array" ref="D86">IF(F86="","",F86-E86)</f>
       </c>
@@ -15876,7 +15897,7 @@
         <v>75</v>
       </c>
       <c r="B87" s="151"/>
-      <c r="C87" s="170"/>
+      <c r="C87" s="350"/>
       <c r="D87" t="str" s="157" cm="1">
         <f t="array" ref="D87">IF(F87="","",F87-E87)</f>
       </c>
@@ -15956,7 +15977,7 @@
         <v>76</v>
       </c>
       <c r="B88" s="151"/>
-      <c r="C88" s="170"/>
+      <c r="C88" s="350"/>
       <c r="D88" t="str" s="157" cm="1">
         <f t="array" ref="D88">IF(F88="","",F88-E88)</f>
       </c>
@@ -16036,7 +16057,7 @@
         <v>77</v>
       </c>
       <c r="B89" s="151"/>
-      <c r="C89" s="170"/>
+      <c r="C89" s="350"/>
       <c r="D89" t="str" s="157" cm="1">
         <f t="array" ref="D89">IF(F89="","",F89-E89)</f>
       </c>
@@ -16116,7 +16137,7 @@
         <v>78</v>
       </c>
       <c r="B90" s="151"/>
-      <c r="C90" s="170"/>
+      <c r="C90" s="350"/>
       <c r="D90" t="str" s="157" cm="1">
         <f t="array" ref="D90">IF(F90="","",F90-E90)</f>
       </c>
@@ -16196,7 +16217,7 @@
         <v>79</v>
       </c>
       <c r="B91" s="151"/>
-      <c r="C91" s="170"/>
+      <c r="C91" s="350"/>
       <c r="D91" t="str" s="157" cm="1">
         <f t="array" ref="D91">IF(F91="","",F91-E91)</f>
       </c>
@@ -16276,7 +16297,7 @@
         <v>80</v>
       </c>
       <c r="B92" s="151"/>
-      <c r="C92" s="170"/>
+      <c r="C92" s="350"/>
       <c r="D92" t="str" s="157" cm="1">
         <f t="array" ref="D92">IF(F92="","",F92-E92)</f>
       </c>
@@ -16356,7 +16377,7 @@
         <v>81</v>
       </c>
       <c r="B93" s="151"/>
-      <c r="C93" s="170"/>
+      <c r="C93" s="350"/>
       <c r="D93" t="str" s="157" cm="1">
         <f t="array" ref="D93">IF(F93="","",F93-E93)</f>
       </c>
@@ -16436,7 +16457,7 @@
         <v>82</v>
       </c>
       <c r="B94" s="151"/>
-      <c r="C94" s="170"/>
+      <c r="C94" s="350"/>
       <c r="D94" t="str" s="157" cm="1">
         <f t="array" ref="D94">IF(F94="","",F94-E94)</f>
       </c>
@@ -16516,7 +16537,7 @@
         <v>83</v>
       </c>
       <c r="B95" s="151"/>
-      <c r="C95" s="170"/>
+      <c r="C95" s="350"/>
       <c r="D95" t="str" s="157" cm="1">
         <f t="array" ref="D95">IF(F95="","",F95-E95)</f>
       </c>
@@ -16596,7 +16617,7 @@
         <v>84</v>
       </c>
       <c r="B96" s="151"/>
-      <c r="C96" s="170"/>
+      <c r="C96" s="350"/>
       <c r="D96" t="str" s="157" cm="1">
         <f t="array" ref="D96">IF(F96="","",F96-E96)</f>
       </c>
@@ -16676,7 +16697,7 @@
         <v>85</v>
       </c>
       <c r="B97" s="151"/>
-      <c r="C97" s="170"/>
+      <c r="C97" s="350"/>
       <c r="D97" t="str" s="157" cm="1">
         <f t="array" ref="D97">IF(F97="","",F97-E97)</f>
       </c>
@@ -16756,7 +16777,7 @@
         <v>86</v>
       </c>
       <c r="B98" s="151"/>
-      <c r="C98" s="170"/>
+      <c r="C98" s="350"/>
       <c r="D98" t="str" s="157" cm="1">
         <f t="array" ref="D98">IF(F98="","",F98-E98)</f>
       </c>
@@ -16836,7 +16857,7 @@
         <v>87</v>
       </c>
       <c r="B99" s="151"/>
-      <c r="C99" s="170"/>
+      <c r="C99" s="350"/>
       <c r="D99" t="str" s="157" cm="1">
         <f t="array" ref="D99">IF(F99="","",F99-E99)</f>
       </c>
@@ -16916,7 +16937,7 @@
         <v>88</v>
       </c>
       <c r="B100" s="151"/>
-      <c r="C100" s="170"/>
+      <c r="C100" s="350"/>
       <c r="D100" t="str" s="157" cm="1">
         <f t="array" ref="D100">IF(F100="","",F100-E100)</f>
       </c>
@@ -16996,7 +17017,7 @@
         <v>89</v>
       </c>
       <c r="B101" s="151"/>
-      <c r="C101" s="170"/>
+      <c r="C101" s="350"/>
       <c r="D101" t="str" s="157" cm="1">
         <f t="array" ref="D101">IF(F101="","",F101-E101)</f>
       </c>
@@ -17076,7 +17097,7 @@
         <v>90</v>
       </c>
       <c r="B102" s="151"/>
-      <c r="C102" s="170"/>
+      <c r="C102" s="350"/>
       <c r="D102" t="str" s="157" cm="1">
         <f t="array" ref="D102">IF(F102="","",F102-E102)</f>
       </c>
@@ -17156,7 +17177,7 @@
         <v>91</v>
       </c>
       <c r="B103" s="151"/>
-      <c r="C103" s="170"/>
+      <c r="C103" s="350"/>
       <c r="D103" t="str" s="157" cm="1">
         <f t="array" ref="D103">IF(F103="","",F103-E103)</f>
       </c>
@@ -17236,7 +17257,7 @@
         <v>92</v>
       </c>
       <c r="B104" s="151"/>
-      <c r="C104" s="170"/>
+      <c r="C104" s="350"/>
       <c r="D104" t="str" s="157" cm="1">
         <f t="array" ref="D104">IF(F104="","",F104-E104)</f>
       </c>
@@ -17316,7 +17337,7 @@
         <v>93</v>
       </c>
       <c r="B105" s="151"/>
-      <c r="C105" s="170"/>
+      <c r="C105" s="350"/>
       <c r="D105" t="str" s="157" cm="1">
         <f t="array" ref="D105">IF(F105="","",F105-E105)</f>
       </c>
@@ -17396,7 +17417,7 @@
         <v>94</v>
       </c>
       <c r="B106" s="151"/>
-      <c r="C106" s="170"/>
+      <c r="C106" s="350"/>
       <c r="D106" t="str" s="157" cm="1">
         <f t="array" ref="D106">IF(F106="","",F106-E106)</f>
       </c>
@@ -17476,7 +17497,7 @@
         <v>95</v>
       </c>
       <c r="B107" s="151"/>
-      <c r="C107" s="170"/>
+      <c r="C107" s="350"/>
       <c r="D107" t="str" s="157" cm="1">
         <f t="array" ref="D107">IF(F107="","",F107-E107)</f>
       </c>
@@ -17556,7 +17577,7 @@
         <v>96</v>
       </c>
       <c r="B108" s="151"/>
-      <c r="C108" s="170"/>
+      <c r="C108" s="350"/>
       <c r="D108" t="str" s="157" cm="1">
         <f t="array" ref="D108">IF(F108="","",F108-E108)</f>
       </c>
@@ -17636,7 +17657,7 @@
         <v>97</v>
       </c>
       <c r="B109" s="151"/>
-      <c r="C109" s="170"/>
+      <c r="C109" s="350"/>
       <c r="D109" t="str" s="157" cm="1">
         <f t="array" ref="D109">IF(F109="","",F109-E109)</f>
       </c>
@@ -17716,7 +17737,7 @@
         <v>98</v>
       </c>
       <c r="B110" s="151"/>
-      <c r="C110" s="170"/>
+      <c r="C110" s="350"/>
       <c r="D110" t="str" s="157" cm="1">
         <f t="array" ref="D110">IF(F110="","",F110-E110)</f>
       </c>
@@ -17796,7 +17817,7 @@
         <v>99</v>
       </c>
       <c r="B111" s="151"/>
-      <c r="C111" s="170"/>
+      <c r="C111" s="350"/>
       <c r="D111" t="str" s="157" cm="1">
         <f t="array" ref="D111">IF(F111="","",F111-E111)</f>
       </c>
@@ -17876,7 +17897,7 @@
         <v>100</v>
       </c>
       <c r="B112" s="151"/>
-      <c r="C112" s="170"/>
+      <c r="C112" s="350"/>
       <c r="D112" t="str" s="157" cm="1">
         <f t="array" ref="D112">IF(F112="","",F112-E112)</f>
       </c>
@@ -17956,7 +17977,7 @@
         <v>101</v>
       </c>
       <c r="B113" s="151"/>
-      <c r="C113" s="170"/>
+      <c r="C113" s="350"/>
       <c r="D113" t="str" s="157" cm="1">
         <f t="array" ref="D113">IF(F113="","",F113-E113)</f>
       </c>
@@ -18036,7 +18057,7 @@
         <v>102</v>
       </c>
       <c r="B114" s="151"/>
-      <c r="C114" s="170"/>
+      <c r="C114" s="350"/>
       <c r="D114" t="str" s="157" cm="1">
         <f t="array" ref="D114">IF(F114="","",F114-E114)</f>
       </c>
@@ -18116,7 +18137,7 @@
         <v>103</v>
       </c>
       <c r="B115" s="151"/>
-      <c r="C115" s="170"/>
+      <c r="C115" s="350"/>
       <c r="D115" t="str" s="157" cm="1">
         <f t="array" ref="D115">IF(F115="","",F115-E115)</f>
       </c>
@@ -18196,7 +18217,7 @@
         <v>104</v>
       </c>
       <c r="B116" s="151"/>
-      <c r="C116" s="170"/>
+      <c r="C116" s="350"/>
       <c r="D116" t="str" s="157" cm="1">
         <f t="array" ref="D116">IF(F116="","",F116-E116)</f>
       </c>
@@ -18276,7 +18297,7 @@
         <v>105</v>
       </c>
       <c r="B117" s="151"/>
-      <c r="C117" s="170"/>
+      <c r="C117" s="350"/>
       <c r="D117" t="str" s="157" cm="1">
         <f t="array" ref="D117">IF(F117="","",F117-E117)</f>
       </c>
@@ -18356,7 +18377,7 @@
         <v>106</v>
       </c>
       <c r="B118" s="151"/>
-      <c r="C118" s="170"/>
+      <c r="C118" s="350"/>
       <c r="D118" t="str" s="157" cm="1">
         <f t="array" ref="D118">IF(F118="","",F118-E118)</f>
       </c>
@@ -18436,7 +18457,7 @@
         <v>107</v>
       </c>
       <c r="B119" s="151"/>
-      <c r="C119" s="170"/>
+      <c r="C119" s="350"/>
       <c r="D119" t="str" s="157" cm="1">
         <f t="array" ref="D119">IF(F119="","",F119-E119)</f>
       </c>
@@ -18516,7 +18537,7 @@
         <v>108</v>
       </c>
       <c r="B120" s="151"/>
-      <c r="C120" s="170"/>
+      <c r="C120" s="350"/>
       <c r="D120" t="str" s="157" cm="1">
         <f t="array" ref="D120">IF(F120="","",F120-E120)</f>
       </c>
@@ -18596,7 +18617,7 @@
         <v>109</v>
       </c>
       <c r="B121" s="151"/>
-      <c r="C121" s="170"/>
+      <c r="C121" s="350"/>
       <c r="D121" t="str" s="157" cm="1">
         <f t="array" ref="D121">IF(F121="","",F121-E121)</f>
       </c>
@@ -18676,7 +18697,7 @@
         <v>110</v>
       </c>
       <c r="B122" s="151"/>
-      <c r="C122" s="170"/>
+      <c r="C122" s="350"/>
       <c r="D122" t="str" s="157" cm="1">
         <f t="array" ref="D122">IF(F122="","",F122-E122)</f>
       </c>
@@ -18756,7 +18777,7 @@
         <v>111</v>
       </c>
       <c r="B123" s="151"/>
-      <c r="C123" s="170"/>
+      <c r="C123" s="350"/>
       <c r="D123" t="str" s="157" cm="1">
         <f t="array" ref="D123">IF(F123="","",F123-E123)</f>
       </c>
@@ -18836,7 +18857,7 @@
         <v>112</v>
       </c>
       <c r="B124" s="151"/>
-      <c r="C124" s="170"/>
+      <c r="C124" s="350"/>
       <c r="D124" t="str" s="157" cm="1">
         <f t="array" ref="D124">IF(F124="","",F124-E124)</f>
       </c>
@@ -18916,7 +18937,7 @@
         <v>113</v>
       </c>
       <c r="B125" s="151"/>
-      <c r="C125" s="170"/>
+      <c r="C125" s="350"/>
       <c r="D125" t="str" s="157" cm="1">
         <f t="array" ref="D125">IF(F125="","",F125-E125)</f>
       </c>
@@ -18996,7 +19017,7 @@
         <v>114</v>
       </c>
       <c r="B126" s="151"/>
-      <c r="C126" s="170"/>
+      <c r="C126" s="350"/>
       <c r="D126" t="str" s="157" cm="1">
         <f t="array" ref="D126">IF(F126="","",F126-E126)</f>
       </c>
@@ -19076,7 +19097,7 @@
         <v>115</v>
       </c>
       <c r="B127" s="151"/>
-      <c r="C127" s="170"/>
+      <c r="C127" s="350"/>
       <c r="D127" t="str" s="157" cm="1">
         <f t="array" ref="D127">IF(F127="","",F127-E127)</f>
       </c>
@@ -19156,7 +19177,7 @@
         <v>116</v>
       </c>
       <c r="B128" s="151"/>
-      <c r="C128" s="170"/>
+      <c r="C128" s="350"/>
       <c r="D128" t="str" s="157" cm="1">
         <f t="array" ref="D128">IF(F128="","",F128-E128)</f>
       </c>
@@ -19236,7 +19257,7 @@
         <v>117</v>
       </c>
       <c r="B129" s="151"/>
-      <c r="C129" s="170"/>
+      <c r="C129" s="350"/>
       <c r="D129" t="str" s="157" cm="1">
         <f t="array" ref="D129">IF(F129="","",F129-E129)</f>
       </c>
@@ -19316,7 +19337,7 @@
         <v>118</v>
       </c>
       <c r="B130" s="151"/>
-      <c r="C130" s="170"/>
+      <c r="C130" s="350"/>
       <c r="D130" t="str" s="157" cm="1">
         <f t="array" ref="D130">IF(F130="","",F130-E130)</f>
       </c>
@@ -19396,7 +19417,7 @@
         <v>119</v>
       </c>
       <c r="B131" s="151"/>
-      <c r="C131" s="170"/>
+      <c r="C131" s="350"/>
       <c r="D131" t="str" s="157" cm="1">
         <f t="array" ref="D131">IF(F131="","",F131-E131)</f>
       </c>
@@ -19476,7 +19497,7 @@
         <v>120</v>
       </c>
       <c r="B132" s="151"/>
-      <c r="C132" s="170"/>
+      <c r="C132" s="350"/>
       <c r="D132" t="str" s="157" cm="1">
         <f t="array" ref="D132">IF(F132="","",F132-E132)</f>
       </c>
@@ -19556,7 +19577,7 @@
         <v>121</v>
       </c>
       <c r="B133" s="151"/>
-      <c r="C133" s="170"/>
+      <c r="C133" s="350"/>
       <c r="D133" t="str" s="157" cm="1">
         <f t="array" ref="D133">IF(F133="","",F133-E133)</f>
       </c>
@@ -19636,7 +19657,7 @@
         <v>122</v>
       </c>
       <c r="B134" s="151"/>
-      <c r="C134" s="170"/>
+      <c r="C134" s="350"/>
       <c r="D134" t="str" s="157" cm="1">
         <f t="array" ref="D134">IF(F134="","",F134-E134)</f>
       </c>
@@ -19716,7 +19737,7 @@
         <v>123</v>
       </c>
       <c r="B135" s="151"/>
-      <c r="C135" s="170"/>
+      <c r="C135" s="350"/>
       <c r="D135" t="str" s="157" cm="1">
         <f t="array" ref="D135">IF(F135="","",F135-E135)</f>
       </c>
@@ -19796,7 +19817,7 @@
         <v>124</v>
       </c>
       <c r="B136" s="151"/>
-      <c r="C136" s="170"/>
+      <c r="C136" s="350"/>
       <c r="D136" t="str" s="157" cm="1">
         <f t="array" ref="D136">IF(F136="","",F136-E136)</f>
       </c>
@@ -19876,7 +19897,7 @@
         <v>125</v>
       </c>
       <c r="B137" s="151"/>
-      <c r="C137" s="170"/>
+      <c r="C137" s="350"/>
       <c r="D137" t="str" s="157" cm="1">
         <f t="array" ref="D137">IF(F137="","",F137-E137)</f>
       </c>
@@ -19956,7 +19977,7 @@
         <v>126</v>
       </c>
       <c r="B138" s="151"/>
-      <c r="C138" s="170"/>
+      <c r="C138" s="350"/>
       <c r="D138" t="str" s="157" cm="1">
         <f t="array" ref="D138">IF(F138="","",F138-E138)</f>
       </c>
@@ -20036,7 +20057,7 @@
         <v>127</v>
       </c>
       <c r="B139" s="151"/>
-      <c r="C139" s="170"/>
+      <c r="C139" s="350"/>
       <c r="D139" t="str" s="157" cm="1">
         <f t="array" ref="D139">IF(F139="","",F139-E139)</f>
       </c>
@@ -20116,7 +20137,7 @@
         <v>128</v>
       </c>
       <c r="B140" s="151"/>
-      <c r="C140" s="170"/>
+      <c r="C140" s="350"/>
       <c r="D140" t="str" s="157" cm="1">
         <f t="array" ref="D140">IF(F140="","",F140-E140)</f>
       </c>
@@ -20196,7 +20217,7 @@
         <v>129</v>
       </c>
       <c r="B141" s="151"/>
-      <c r="C141" s="170"/>
+      <c r="C141" s="350"/>
       <c r="D141" t="str" s="157" cm="1">
         <f t="array" ref="D141">IF(F141="","",F141-E141)</f>
       </c>
@@ -20276,7 +20297,7 @@
         <v>130</v>
       </c>
       <c r="B142" s="151"/>
-      <c r="C142" s="170"/>
+      <c r="C142" s="350"/>
       <c r="D142" t="str" s="157" cm="1">
         <f t="array" ref="D142">IF(F142="","",F142-E142)</f>
       </c>
@@ -20356,7 +20377,7 @@
         <v>131</v>
       </c>
       <c r="B143" s="151"/>
-      <c r="C143" s="170"/>
+      <c r="C143" s="350"/>
       <c r="D143" t="str" s="157" cm="1">
         <f t="array" ref="D143">IF(F143="","",F143-E143)</f>
       </c>
@@ -20436,7 +20457,7 @@
         <v>132</v>
       </c>
       <c r="B144" s="151"/>
-      <c r="C144" s="170"/>
+      <c r="C144" s="350"/>
       <c r="D144" t="str" s="157" cm="1">
         <f t="array" ref="D144">IF(F144="","",F144-E144)</f>
       </c>
@@ -20516,7 +20537,7 @@
         <v>133</v>
       </c>
       <c r="B145" s="151"/>
-      <c r="C145" s="170"/>
+      <c r="C145" s="350"/>
       <c r="D145" t="str" s="157" cm="1">
         <f t="array" ref="D145">IF(F145="","",F145-E145)</f>
       </c>
@@ -20596,7 +20617,7 @@
         <v>134</v>
       </c>
       <c r="B146" s="151"/>
-      <c r="C146" s="170"/>
+      <c r="C146" s="350"/>
       <c r="D146" t="str" s="157" cm="1">
         <f t="array" ref="D146">IF(F146="","",F146-E146)</f>
       </c>
@@ -20676,7 +20697,7 @@
         <v>135</v>
       </c>
       <c r="B147" s="151"/>
-      <c r="C147" s="170"/>
+      <c r="C147" s="350"/>
       <c r="D147" t="str" s="157" cm="1">
         <f t="array" ref="D147">IF(F147="","",F147-E147)</f>
       </c>
@@ -20756,7 +20777,7 @@
         <v>136</v>
       </c>
       <c r="B148" s="151"/>
-      <c r="C148" s="170"/>
+      <c r="C148" s="350"/>
       <c r="D148" t="str" s="157" cm="1">
         <f t="array" ref="D148">IF(F148="","",F148-E148)</f>
       </c>
@@ -20836,7 +20857,7 @@
         <v>137</v>
       </c>
       <c r="B149" s="151"/>
-      <c r="C149" s="170"/>
+      <c r="C149" s="350"/>
       <c r="D149" t="str" s="157" cm="1">
         <f t="array" ref="D149">IF(F149="","",F149-E149)</f>
       </c>
@@ -20916,7 +20937,7 @@
         <v>138</v>
       </c>
       <c r="B150" s="151"/>
-      <c r="C150" s="170"/>
+      <c r="C150" s="350"/>
       <c r="D150" t="str" s="157" cm="1">
         <f t="array" ref="D150">IF(F150="","",F150-E150)</f>
       </c>
@@ -20996,7 +21017,7 @@
         <v>139</v>
       </c>
       <c r="B151" s="151"/>
-      <c r="C151" s="170"/>
+      <c r="C151" s="350"/>
       <c r="D151" t="str" s="157" cm="1">
         <f t="array" ref="D151">IF(F151="","",F151-E151)</f>
       </c>
@@ -21076,7 +21097,7 @@
         <v>140</v>
       </c>
       <c r="B152" s="151"/>
-      <c r="C152" s="170"/>
+      <c r="C152" s="350"/>
       <c r="D152" t="str" s="157" cm="1">
         <f t="array" ref="D152">IF(F152="","",F152-E152)</f>
       </c>
@@ -21156,7 +21177,7 @@
         <v>141</v>
       </c>
       <c r="B153" s="151"/>
-      <c r="C153" s="170"/>
+      <c r="C153" s="350"/>
       <c r="D153" t="str" s="157" cm="1">
         <f t="array" ref="D153">IF(F153="","",F153-E153)</f>
       </c>
@@ -21236,7 +21257,7 @@
         <v>142</v>
       </c>
       <c r="B154" s="151"/>
-      <c r="C154" s="170"/>
+      <c r="C154" s="350"/>
       <c r="D154" t="str" s="157" cm="1">
         <f t="array" ref="D154">IF(F154="","",F154-E154)</f>
       </c>
@@ -21316,7 +21337,7 @@
         <v>143</v>
       </c>
       <c r="B155" s="151"/>
-      <c r="C155" s="170"/>
+      <c r="C155" s="350"/>
       <c r="D155" t="str" s="157" cm="1">
         <f t="array" ref="D155">IF(F155="","",F155-E155)</f>
       </c>
@@ -21396,7 +21417,7 @@
         <v>144</v>
       </c>
       <c r="B156" s="151"/>
-      <c r="C156" s="170"/>
+      <c r="C156" s="350"/>
       <c r="D156" t="str" s="157" cm="1">
         <f t="array" ref="D156">IF(F156="","",F156-E156)</f>
       </c>
@@ -21476,7 +21497,7 @@
         <v>145</v>
       </c>
       <c r="B157" s="151"/>
-      <c r="C157" s="170"/>
+      <c r="C157" s="350"/>
       <c r="D157" t="str" s="157" cm="1">
         <f t="array" ref="D157">IF(F157="","",F157-E157)</f>
       </c>
@@ -21556,7 +21577,7 @@
         <v>146</v>
       </c>
       <c r="B158" s="151"/>
-      <c r="C158" s="170"/>
+      <c r="C158" s="350"/>
       <c r="D158" t="str" s="157" cm="1">
         <f t="array" ref="D158">IF(F158="","",F158-E158)</f>
       </c>
@@ -21636,7 +21657,7 @@
         <v>147</v>
       </c>
       <c r="B159" s="151"/>
-      <c r="C159" s="170"/>
+      <c r="C159" s="350"/>
       <c r="D159" t="str" s="157" cm="1">
         <f t="array" ref="D159">IF(F159="","",F159-E159)</f>
       </c>
@@ -22750,7 +22771,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="151"/>
-      <c r="C11" t="s" s="156">
+      <c r="C11" t="s" s="349">
         <v>99</v>
       </c>
       <c r="D11" s="165"/>
@@ -22837,7 +22858,7 @@
           <t>三友-4</t>
         </is>
       </c>
-      <c r="C12" s="156" t="inlineStr">
+      <c r="C12" s="349" t="inlineStr">
         <is>
           <t>西側　1階食堂床見切り</t>
         </is>
@@ -22943,7 +22964,7 @@
           <t>三友-7</t>
         </is>
       </c>
-      <c r="C13" s="156" t="inlineStr">
+      <c r="C13" s="349" t="inlineStr">
         <is>
           <t>西側　ボックス席腰壁下地鉄骨</t>
         </is>
@@ -23051,7 +23072,7 @@
           <t>三友-8</t>
         </is>
       </c>
-      <c r="C14" s="156" t="inlineStr">
+      <c r="C14" s="349" t="inlineStr">
         <is>
           <t>東側　吹抜け部天井下地鉄骨</t>
         </is>
@@ -23155,7 +23176,7 @@
           <t>三友-9</t>
         </is>
       </c>
-      <c r="C15" s="156" t="inlineStr">
+      <c r="C15" s="349" t="inlineStr">
         <is>
           <t>東側　吸音ルーバー壁下地鉄骨</t>
         </is>
@@ -23265,7 +23286,7 @@
           <t>三友-10</t>
         </is>
       </c>
-      <c r="C16" s="156" t="inlineStr">
+      <c r="C16" s="349" t="inlineStr">
         <is>
           <t>東側　吸音ルーバー壁⑤通り部天端塞ぎ</t>
         </is>
@@ -23369,7 +23390,7 @@
           <t>三友-11</t>
         </is>
       </c>
-      <c r="C17" s="156" t="inlineStr">
+      <c r="C17" s="349" t="inlineStr">
         <is>
           <t>東側　腰壁下地鉄骨</t>
         </is>
@@ -23477,7 +23498,7 @@
           <t>三友-12</t>
         </is>
       </c>
-      <c r="C18" s="156" t="inlineStr">
+      <c r="C18" s="349" t="inlineStr">
         <is>
           <t>東側・西側　窓際カウンター下地</t>
         </is>
@@ -23581,7 +23602,7 @@
           <t>三友-13</t>
         </is>
       </c>
-      <c r="C19" s="156" t="inlineStr">
+      <c r="C19" s="349" t="inlineStr">
         <is>
           <t>東側　壁見切り</t>
         </is>
@@ -23685,7 +23706,7 @@
           <t>三友-14</t>
         </is>
       </c>
-      <c r="C20" s="156" t="inlineStr">
+      <c r="C20" s="349" t="inlineStr">
         <is>
           <t>東側　自動扉安全柵</t>
         </is>
@@ -23789,7 +23810,7 @@
           <t>三友-15</t>
         </is>
       </c>
-      <c r="C21" s="156" t="inlineStr">
+      <c r="C21" s="349" t="inlineStr">
         <is>
           <t>西側　壁アルミルーバー（天井裏下地込み）</t>
         </is>
@@ -23899,7 +23920,7 @@
           <t>三友-16</t>
         </is>
       </c>
-      <c r="C22" s="156" t="inlineStr">
+      <c r="C22" s="349" t="inlineStr">
         <is>
           <t>西側　ステンレスカウンター</t>
         </is>
@@ -24003,7 +24024,7 @@
           <t>三友-18</t>
         </is>
       </c>
-      <c r="C23" s="156" t="inlineStr">
+      <c r="C23" s="349" t="inlineStr">
         <is>
           <t>チャンバーボックス</t>
         </is>
@@ -24107,7 +24128,7 @@
           <t>三友-19</t>
         </is>
       </c>
-      <c r="C24" s="156" t="inlineStr">
+      <c r="C24" s="349" t="inlineStr">
         <is>
           <t>チャンバーボックス　グレーチング蓋</t>
         </is>
@@ -24211,7 +24232,7 @@
           <t>三友-20</t>
         </is>
       </c>
-      <c r="C25" s="156" t="inlineStr">
+      <c r="C25" s="349" t="inlineStr">
         <is>
           <t>東側　照明ボックススチールパネル</t>
         </is>
@@ -24315,7 +24336,7 @@
           <t>三友-21</t>
         </is>
       </c>
-      <c r="C26" s="156" t="inlineStr">
+      <c r="C26" s="349" t="inlineStr">
         <is>
           <t>西側　照明ボックススチールパネル</t>
         </is>
@@ -24415,7 +24436,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="151"/>
-      <c r="C27" s="170"/>
+      <c r="C27" s="350"/>
       <c r="D27" s="165"/>
       <c r="E27" s="164"/>
       <c r="F27" s="195" cm="1" t="str">
@@ -24496,7 +24517,7 @@
         <v>17</v>
       </c>
       <c r="B28" s="151"/>
-      <c r="C28" t="s" s="156">
+      <c r="C28" t="s" s="349">
         <v>115</v>
       </c>
       <c r="D28" s="165"/>
@@ -24581,7 +24602,7 @@
       <c r="B29" t="s" s="167">
         <v>116</v>
       </c>
-      <c r="C29" t="s" s="156">
+      <c r="C29" t="s" s="349">
         <v>117</v>
       </c>
       <c r="D29" s="165"/>
@@ -24688,7 +24709,7 @@
       <c r="B30" t="s" s="167">
         <v>119</v>
       </c>
-      <c r="C30" t="s" s="197">
+      <c r="C30" t="s" s="351">
         <v>120</v>
       </c>
       <c r="D30" s="165"/>
@@ -24775,7 +24796,7 @@
       <c r="B31" t="s" s="167">
         <v>122</v>
       </c>
-      <c r="C31" t="s" s="197">
+      <c r="C31" t="s" s="351">
         <v>123</v>
       </c>
       <c r="D31" s="165"/>
@@ -24884,7 +24905,7 @@
       <c r="B32" t="s" s="167">
         <v>125</v>
       </c>
-      <c r="C32" t="s" s="199">
+      <c r="C32" t="s" s="352">
         <v>126</v>
       </c>
       <c r="D32" s="165"/>
@@ -24969,7 +24990,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="151"/>
-      <c r="C33" s="170"/>
+      <c r="C33" s="350"/>
       <c r="D33" s="165"/>
       <c r="E33" s="164"/>
       <c r="F33" s="195" cm="1" t="str">
@@ -25050,7 +25071,7 @@
         <v>23</v>
       </c>
       <c r="B34" s="151"/>
-      <c r="C34" t="s" s="156">
+      <c r="C34" t="s" s="349">
         <v>128</v>
       </c>
       <c r="D34" s="165"/>
@@ -25135,7 +25156,7 @@
       <c r="B35" t="s" s="167">
         <v>129</v>
       </c>
-      <c r="C35" t="s" s="197">
+      <c r="C35" t="s" s="351">
         <v>130</v>
       </c>
       <c r="D35" s="165"/>
@@ -25242,7 +25263,7 @@
         <v>25</v>
       </c>
       <c r="B36" s="151"/>
-      <c r="C36" s="170"/>
+      <c r="C36" s="350"/>
       <c r="D36" s="165"/>
       <c r="E36" s="164"/>
       <c r="F36" s="195" cm="1" t="str">
@@ -25323,7 +25344,7 @@
         <v>26</v>
       </c>
       <c r="B37" s="151"/>
-      <c r="C37" t="s" s="156">
+      <c r="C37" t="s" s="349">
         <v>132</v>
       </c>
       <c r="D37" s="165"/>
@@ -25408,7 +25429,7 @@
       <c r="B38" t="s" s="167">
         <v>133</v>
       </c>
-      <c r="C38" t="s" s="197">
+      <c r="C38" t="s" s="351">
         <v>134</v>
       </c>
       <c r="D38" s="165"/>
@@ -25515,7 +25536,7 @@
       <c r="B39" t="s" s="167">
         <v>136</v>
       </c>
-      <c r="C39" t="s" s="156">
+      <c r="C39" t="s" s="349">
         <v>137</v>
       </c>
       <c r="D39" s="165"/>
@@ -25616,7 +25637,7 @@
       <c r="B40" t="s" s="167">
         <v>139</v>
       </c>
-      <c r="C40" t="s" s="156">
+      <c r="C40" t="s" s="349">
         <v>140</v>
       </c>
       <c r="D40" s="165"/>
@@ -25717,7 +25738,7 @@
       <c r="B41" t="s" s="167">
         <v>141</v>
       </c>
-      <c r="C41" t="s" s="156">
+      <c r="C41" t="s" s="349">
         <v>142</v>
       </c>
       <c r="D41" s="165"/>
@@ -25816,7 +25837,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="151"/>
-      <c r="C42" s="170"/>
+      <c r="C42" s="350"/>
       <c r="D42" s="165"/>
       <c r="E42" s="164"/>
       <c r="F42" s="195" cm="1" t="str">
@@ -25897,7 +25918,7 @@
         <v>32</v>
       </c>
       <c r="B43" s="151"/>
-      <c r="C43" t="s" s="156">
+      <c r="C43" t="s" s="349">
         <v>143</v>
       </c>
       <c r="D43" s="165"/>
@@ -25982,7 +26003,7 @@
       <c r="B44" t="s" s="167">
         <v>144</v>
       </c>
-      <c r="C44" t="s" s="156">
+      <c r="C44" t="s" s="349">
         <v>145</v>
       </c>
       <c r="D44" s="165"/>
@@ -26085,7 +26106,7 @@
         <v>34</v>
       </c>
       <c r="B45" s="151"/>
-      <c r="C45" s="170"/>
+      <c r="C45" s="350"/>
       <c r="D45" s="165"/>
       <c r="E45" s="164"/>
       <c r="F45" s="195" cm="1" t="str">
@@ -26166,7 +26187,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="151"/>
-      <c r="C46" t="s" s="156">
+      <c r="C46" t="s" s="349">
         <v>147</v>
       </c>
       <c r="D46" s="165"/>
@@ -26251,7 +26272,7 @@
       <c r="B47" t="s" s="167">
         <v>148</v>
       </c>
-      <c r="C47" t="s" s="156">
+      <c r="C47" t="s" s="349">
         <v>149</v>
       </c>
       <c r="D47" s="165"/>
@@ -26356,7 +26377,7 @@
         <v>37</v>
       </c>
       <c r="B48" s="151"/>
-      <c r="C48" s="170"/>
+      <c r="C48" s="350"/>
       <c r="D48" s="165"/>
       <c r="E48" s="164"/>
       <c r="F48" s="195" cm="1" t="str">
@@ -26437,7 +26458,7 @@
         <v>38</v>
       </c>
       <c r="B49" s="151"/>
-      <c r="C49" t="s" s="156">
+      <c r="C49" t="s" s="349">
         <v>150</v>
       </c>
       <c r="D49" s="165"/>
@@ -26522,7 +26543,7 @@
       <c r="B50" t="s" s="167">
         <v>151</v>
       </c>
-      <c r="C50" t="s" s="156">
+      <c r="C50" t="s" s="349">
         <v>152</v>
       </c>
       <c r="D50" s="165"/>
@@ -26621,7 +26642,7 @@
         <v>40</v>
       </c>
       <c r="B51" s="151"/>
-      <c r="C51" s="170"/>
+      <c r="C51" s="350"/>
       <c r="D51" s="165"/>
       <c r="E51" s="164"/>
       <c r="F51" s="195" cm="1" t="str">
@@ -26702,7 +26723,7 @@
         <v>41</v>
       </c>
       <c r="B52" s="151"/>
-      <c r="C52" s="156"/>
+      <c r="C52" s="349"/>
       <c r="D52" s="165"/>
       <c r="E52" s="164"/>
       <c r="F52" s="195" cm="1" t="str">
@@ -26783,7 +26804,7 @@
         <v>42</v>
       </c>
       <c r="B53" s="151"/>
-      <c r="C53" s="170"/>
+      <c r="C53" s="350"/>
       <c r="D53" s="165"/>
       <c r="E53" s="164"/>
       <c r="F53" s="195" cm="1" t="str">
@@ -26864,7 +26885,7 @@
         <v>43</v>
       </c>
       <c r="B54" s="151"/>
-      <c r="C54" s="170"/>
+      <c r="C54" s="350"/>
       <c r="D54" s="165"/>
       <c r="E54" s="164"/>
       <c r="F54" s="195" cm="1" t="str">
@@ -26945,7 +26966,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="151"/>
-      <c r="C55" s="170"/>
+      <c r="C55" s="350"/>
       <c r="D55" s="165"/>
       <c r="E55" s="164"/>
       <c r="F55" s="195" cm="1" t="str">
@@ -27026,7 +27047,7 @@
         <v>45</v>
       </c>
       <c r="B56" s="151"/>
-      <c r="C56" s="170"/>
+      <c r="C56" s="350"/>
       <c r="D56" s="165"/>
       <c r="E56" s="164"/>
       <c r="F56" s="195" cm="1" t="str">
@@ -27107,7 +27128,7 @@
         <v>46</v>
       </c>
       <c r="B57" s="151"/>
-      <c r="C57" s="170"/>
+      <c r="C57" s="350"/>
       <c r="D57" s="165"/>
       <c r="E57" s="164"/>
       <c r="F57" s="195" cm="1" t="str">
@@ -27188,7 +27209,7 @@
         <v>47</v>
       </c>
       <c r="B58" s="151"/>
-      <c r="C58" s="170"/>
+      <c r="C58" s="350"/>
       <c r="D58" s="165"/>
       <c r="E58" s="164"/>
       <c r="F58" s="195" cm="1" t="str">
@@ -27269,7 +27290,7 @@
         <v>48</v>
       </c>
       <c r="B59" s="151"/>
-      <c r="C59" s="170"/>
+      <c r="C59" s="350"/>
       <c r="D59" s="165"/>
       <c r="E59" s="164"/>
       <c r="F59" s="195" cm="1" t="str">
@@ -27350,7 +27371,7 @@
         <v>49</v>
       </c>
       <c r="B60" s="151"/>
-      <c r="C60" s="170"/>
+      <c r="C60" s="350"/>
       <c r="D60" s="165"/>
       <c r="E60" s="164"/>
       <c r="F60" s="195" cm="1" t="str">
@@ -27431,7 +27452,7 @@
         <v>50</v>
       </c>
       <c r="B61" s="151"/>
-      <c r="C61" s="156"/>
+      <c r="C61" s="349"/>
       <c r="D61" s="165"/>
       <c r="E61" s="164"/>
       <c r="F61" s="195" cm="1" t="str">
@@ -27512,7 +27533,7 @@
         <v>51</v>
       </c>
       <c r="B62" s="151"/>
-      <c r="C62" s="170"/>
+      <c r="C62" s="350"/>
       <c r="D62" s="165"/>
       <c r="E62" s="164"/>
       <c r="F62" s="195" cm="1" t="str">
@@ -27593,7 +27614,7 @@
         <v>52</v>
       </c>
       <c r="B63" s="151"/>
-      <c r="C63" s="170"/>
+      <c r="C63" s="350"/>
       <c r="D63" s="165"/>
       <c r="E63" s="164"/>
       <c r="F63" s="195" cm="1" t="str">
@@ -27674,7 +27695,7 @@
         <v>53</v>
       </c>
       <c r="B64" s="151"/>
-      <c r="C64" s="170"/>
+      <c r="C64" s="350"/>
       <c r="D64" s="165"/>
       <c r="E64" s="164"/>
       <c r="F64" s="195" cm="1" t="str">
@@ -27755,7 +27776,7 @@
         <v>54</v>
       </c>
       <c r="B65" s="151"/>
-      <c r="C65" s="170"/>
+      <c r="C65" s="350"/>
       <c r="D65" s="165"/>
       <c r="E65" s="164"/>
       <c r="F65" s="195" cm="1" t="str">
@@ -27836,7 +27857,7 @@
         <v>55</v>
       </c>
       <c r="B66" s="151"/>
-      <c r="C66" s="170"/>
+      <c r="C66" s="350"/>
       <c r="D66" s="165"/>
       <c r="E66" s="164"/>
       <c r="F66" s="195" cm="1" t="str">
@@ -27917,7 +27938,7 @@
         <v>56</v>
       </c>
       <c r="B67" s="151"/>
-      <c r="C67" s="170"/>
+      <c r="C67" s="350"/>
       <c r="D67" s="165"/>
       <c r="E67" s="164"/>
       <c r="F67" s="195" cm="1" t="str">
@@ -27998,7 +28019,7 @@
         <v>57</v>
       </c>
       <c r="B68" s="151"/>
-      <c r="C68" s="170"/>
+      <c r="C68" s="350"/>
       <c r="D68" s="165"/>
       <c r="E68" s="164"/>
       <c r="F68" s="195" cm="1" t="str">
@@ -28079,7 +28100,7 @@
         <v>58</v>
       </c>
       <c r="B69" s="151"/>
-      <c r="C69" s="156"/>
+      <c r="C69" s="349"/>
       <c r="D69" s="165"/>
       <c r="E69" s="164"/>
       <c r="F69" s="195" cm="1" t="str">
@@ -28160,7 +28181,7 @@
         <v>59</v>
       </c>
       <c r="B70" s="151"/>
-      <c r="C70" s="170"/>
+      <c r="C70" s="350"/>
       <c r="D70" s="165"/>
       <c r="E70" s="164"/>
       <c r="F70" s="195" cm="1" t="str">
@@ -28241,7 +28262,7 @@
         <v>60</v>
       </c>
       <c r="B71" s="151"/>
-      <c r="C71" s="170"/>
+      <c r="C71" s="350"/>
       <c r="D71" s="165"/>
       <c r="E71" s="164"/>
       <c r="F71" s="195" cm="1" t="str">
@@ -28322,7 +28343,7 @@
         <v>61</v>
       </c>
       <c r="B72" s="151"/>
-      <c r="C72" s="170"/>
+      <c r="C72" s="350"/>
       <c r="D72" s="165"/>
       <c r="E72" s="164"/>
       <c r="F72" s="195" cm="1" t="str">
@@ -28403,7 +28424,7 @@
         <v>62</v>
       </c>
       <c r="B73" s="151"/>
-      <c r="C73" s="170"/>
+      <c r="C73" s="350"/>
       <c r="D73" s="165"/>
       <c r="E73" s="164"/>
       <c r="F73" s="195" cm="1" t="str">
@@ -28484,7 +28505,7 @@
         <v>63</v>
       </c>
       <c r="B74" s="151"/>
-      <c r="C74" s="170"/>
+      <c r="C74" s="350"/>
       <c r="D74" s="165"/>
       <c r="E74" s="164"/>
       <c r="F74" s="195" cm="1" t="str">
@@ -28565,7 +28586,7 @@
         <v>64</v>
       </c>
       <c r="B75" s="151"/>
-      <c r="C75" s="170"/>
+      <c r="C75" s="350"/>
       <c r="D75" s="165"/>
       <c r="E75" s="164"/>
       <c r="F75" s="195" cm="1" t="str">
@@ -28646,7 +28667,7 @@
         <v>65</v>
       </c>
       <c r="B76" s="151"/>
-      <c r="C76" s="170"/>
+      <c r="C76" s="350"/>
       <c r="D76" s="165"/>
       <c r="E76" s="164"/>
       <c r="F76" s="195" cm="1" t="str">
@@ -28727,7 +28748,7 @@
         <v>66</v>
       </c>
       <c r="B77" s="151"/>
-      <c r="C77" s="170"/>
+      <c r="C77" s="350"/>
       <c r="D77" s="165"/>
       <c r="E77" s="164"/>
       <c r="F77" s="195" cm="1" t="str">
@@ -28808,7 +28829,7 @@
         <v>67</v>
       </c>
       <c r="B78" s="151"/>
-      <c r="C78" s="170"/>
+      <c r="C78" s="350"/>
       <c r="D78" s="165"/>
       <c r="E78" s="164"/>
       <c r="F78" s="195" cm="1" t="str">
@@ -28889,7 +28910,7 @@
         <v>68</v>
       </c>
       <c r="B79" s="151"/>
-      <c r="C79" s="170"/>
+      <c r="C79" s="350"/>
       <c r="D79" s="165"/>
       <c r="E79" s="164"/>
       <c r="F79" s="195" cm="1" t="str">
@@ -28970,7 +28991,7 @@
         <v>69</v>
       </c>
       <c r="B80" s="151"/>
-      <c r="C80" s="170"/>
+      <c r="C80" s="350"/>
       <c r="D80" s="165"/>
       <c r="E80" s="164"/>
       <c r="F80" s="195" cm="1" t="str">
@@ -29051,7 +29072,7 @@
         <v>70</v>
       </c>
       <c r="B81" s="151"/>
-      <c r="C81" s="170"/>
+      <c r="C81" s="350"/>
       <c r="D81" s="165"/>
       <c r="E81" s="164"/>
       <c r="F81" s="195" cm="1" t="str">
@@ -29132,7 +29153,7 @@
         <v>71</v>
       </c>
       <c r="B82" s="151"/>
-      <c r="C82" s="170"/>
+      <c r="C82" s="350"/>
       <c r="D82" s="165"/>
       <c r="E82" s="164"/>
       <c r="F82" s="195" cm="1" t="str">
@@ -29213,7 +29234,7 @@
         <v>72</v>
       </c>
       <c r="B83" s="151"/>
-      <c r="C83" s="170"/>
+      <c r="C83" s="350"/>
       <c r="D83" s="165"/>
       <c r="E83" s="164"/>
       <c r="F83" s="195" cm="1" t="str">
@@ -29294,7 +29315,7 @@
         <v>73</v>
       </c>
       <c r="B84" s="151"/>
-      <c r="C84" s="170"/>
+      <c r="C84" s="350"/>
       <c r="D84" s="165"/>
       <c r="E84" s="164"/>
       <c r="F84" s="195" cm="1" t="str">
@@ -29375,7 +29396,7 @@
         <v>74</v>
       </c>
       <c r="B85" s="151"/>
-      <c r="C85" s="170"/>
+      <c r="C85" s="350"/>
       <c r="D85" s="165"/>
       <c r="E85" s="164"/>
       <c r="F85" s="195" cm="1" t="str">
@@ -29456,7 +29477,7 @@
         <v>75</v>
       </c>
       <c r="B86" s="151"/>
-      <c r="C86" s="170"/>
+      <c r="C86" s="350"/>
       <c r="D86" s="165"/>
       <c r="E86" s="164"/>
       <c r="F86" s="195" cm="1" t="str">
@@ -29537,7 +29558,7 @@
         <v>76</v>
       </c>
       <c r="B87" s="151"/>
-      <c r="C87" s="170"/>
+      <c r="C87" s="350"/>
       <c r="D87" s="165"/>
       <c r="E87" s="164"/>
       <c r="F87" s="195" cm="1" t="str">
@@ -29618,7 +29639,7 @@
         <v>77</v>
       </c>
       <c r="B88" s="151"/>
-      <c r="C88" s="170"/>
+      <c r="C88" s="350"/>
       <c r="D88" s="165"/>
       <c r="E88" s="164"/>
       <c r="F88" s="195" cm="1" t="str">
@@ -29699,7 +29720,7 @@
         <v>78</v>
       </c>
       <c r="B89" s="151"/>
-      <c r="C89" s="170"/>
+      <c r="C89" s="350"/>
       <c r="D89" s="165"/>
       <c r="E89" s="164"/>
       <c r="F89" s="195" cm="1" t="str">
@@ -29780,7 +29801,7 @@
         <v>79</v>
       </c>
       <c r="B90" s="151"/>
-      <c r="C90" s="170"/>
+      <c r="C90" s="350"/>
       <c r="D90" s="165"/>
       <c r="E90" s="164"/>
       <c r="F90" s="195" cm="1" t="str">
@@ -29861,7 +29882,7 @@
         <v>80</v>
       </c>
       <c r="B91" s="151"/>
-      <c r="C91" s="170"/>
+      <c r="C91" s="350"/>
       <c r="D91" s="165"/>
       <c r="E91" s="164"/>
       <c r="F91" s="195" cm="1" t="str">
@@ -29942,7 +29963,7 @@
         <v>81</v>
       </c>
       <c r="B92" s="151"/>
-      <c r="C92" s="170"/>
+      <c r="C92" s="350"/>
       <c r="D92" s="165"/>
       <c r="E92" s="164"/>
       <c r="F92" s="195" cm="1" t="str">
@@ -30023,7 +30044,7 @@
         <v>82</v>
       </c>
       <c r="B93" s="151"/>
-      <c r="C93" s="170"/>
+      <c r="C93" s="350"/>
       <c r="D93" s="165"/>
       <c r="E93" s="164"/>
       <c r="F93" s="195" cm="1" t="str">
@@ -30104,7 +30125,7 @@
         <v>83</v>
       </c>
       <c r="B94" s="151"/>
-      <c r="C94" s="170"/>
+      <c r="C94" s="350"/>
       <c r="D94" s="165"/>
       <c r="E94" s="164"/>
       <c r="F94" s="195" cm="1" t="str">
@@ -30185,7 +30206,7 @@
         <v>84</v>
       </c>
       <c r="B95" s="151"/>
-      <c r="C95" s="170"/>
+      <c r="C95" s="350"/>
       <c r="D95" s="165"/>
       <c r="E95" s="164"/>
       <c r="F95" s="195" cm="1" t="str">
@@ -30266,7 +30287,7 @@
         <v>85</v>
       </c>
       <c r="B96" s="151"/>
-      <c r="C96" s="170"/>
+      <c r="C96" s="350"/>
       <c r="D96" s="165"/>
       <c r="E96" s="164"/>
       <c r="F96" s="195" cm="1" t="str">
@@ -30347,7 +30368,7 @@
         <v>86</v>
       </c>
       <c r="B97" s="151"/>
-      <c r="C97" s="170"/>
+      <c r="C97" s="350"/>
       <c r="D97" s="165"/>
       <c r="E97" s="164"/>
       <c r="F97" s="195" cm="1" t="str">
@@ -30428,7 +30449,7 @@
         <v>87</v>
       </c>
       <c r="B98" s="151"/>
-      <c r="C98" s="170"/>
+      <c r="C98" s="350"/>
       <c r="D98" s="165"/>
       <c r="E98" s="164"/>
       <c r="F98" s="195" cm="1" t="str">
@@ -30509,7 +30530,7 @@
         <v>88</v>
       </c>
       <c r="B99" s="151"/>
-      <c r="C99" s="170"/>
+      <c r="C99" s="350"/>
       <c r="D99" s="165"/>
       <c r="E99" s="164"/>
       <c r="F99" s="195" cm="1" t="str">
@@ -30590,7 +30611,7 @@
         <v>89</v>
       </c>
       <c r="B100" s="151"/>
-      <c r="C100" s="170"/>
+      <c r="C100" s="350"/>
       <c r="D100" s="165"/>
       <c r="E100" s="164"/>
       <c r="F100" s="195" cm="1" t="str">
@@ -30671,7 +30692,7 @@
         <v>90</v>
       </c>
       <c r="B101" s="151"/>
-      <c r="C101" s="170"/>
+      <c r="C101" s="350"/>
       <c r="D101" s="165"/>
       <c r="E101" s="164"/>
       <c r="F101" s="195" cm="1" t="str">
@@ -30752,7 +30773,7 @@
         <v>91</v>
       </c>
       <c r="B102" s="151"/>
-      <c r="C102" s="170"/>
+      <c r="C102" s="350"/>
       <c r="D102" s="165"/>
       <c r="E102" s="164"/>
       <c r="F102" s="195" cm="1" t="str">
@@ -30833,7 +30854,7 @@
         <v>92</v>
       </c>
       <c r="B103" s="151"/>
-      <c r="C103" s="170"/>
+      <c r="C103" s="350"/>
       <c r="D103" s="165"/>
       <c r="E103" s="164"/>
       <c r="F103" s="195" cm="1" t="str">
@@ -30914,7 +30935,7 @@
         <v>93</v>
       </c>
       <c r="B104" s="151"/>
-      <c r="C104" s="170"/>
+      <c r="C104" s="350"/>
       <c r="D104" s="165"/>
       <c r="E104" s="164"/>
       <c r="F104" s="195" cm="1" t="str">
@@ -30995,7 +31016,7 @@
         <v>94</v>
       </c>
       <c r="B105" s="151"/>
-      <c r="C105" s="170"/>
+      <c r="C105" s="350"/>
       <c r="D105" s="165"/>
       <c r="E105" s="164"/>
       <c r="F105" s="195" cm="1" t="str">
@@ -31076,7 +31097,7 @@
         <v>95</v>
       </c>
       <c r="B106" s="151"/>
-      <c r="C106" s="170"/>
+      <c r="C106" s="350"/>
       <c r="D106" s="165"/>
       <c r="E106" s="164"/>
       <c r="F106" s="195" cm="1" t="str">
@@ -31154,7 +31175,7 @@
         <v>96</v>
       </c>
       <c r="B107" s="151"/>
-      <c r="C107" s="170"/>
+      <c r="C107" s="350"/>
       <c r="D107" s="165"/>
       <c r="E107" s="164"/>
       <c r="F107" s="195" cm="1" t="str">
@@ -31232,7 +31253,7 @@
         <v>97</v>
       </c>
       <c r="B108" s="151"/>
-      <c r="C108" s="170"/>
+      <c r="C108" s="350"/>
       <c r="D108" s="165"/>
       <c r="E108" s="164"/>
       <c r="F108" s="195" cm="1" t="str">
@@ -31310,7 +31331,7 @@
         <v>98</v>
       </c>
       <c r="B109" s="151"/>
-      <c r="C109" s="170"/>
+      <c r="C109" s="350"/>
       <c r="D109" s="165"/>
       <c r="E109" s="164"/>
       <c r="F109" s="195" cm="1" t="str">
@@ -31388,7 +31409,7 @@
         <v>99</v>
       </c>
       <c r="B110" s="151"/>
-      <c r="C110" s="170"/>
+      <c r="C110" s="350"/>
       <c r="D110" s="165"/>
       <c r="E110" s="164"/>
       <c r="F110" s="195" cm="1" t="str">
@@ -31466,7 +31487,7 @@
         <v>100</v>
       </c>
       <c r="B111" s="151"/>
-      <c r="C111" s="170"/>
+      <c r="C111" s="350"/>
       <c r="D111" s="165"/>
       <c r="E111" s="164"/>
       <c r="F111" s="195" cm="1" t="str">
@@ -31544,7 +31565,7 @@
         <v>101</v>
       </c>
       <c r="B112" s="151"/>
-      <c r="C112" s="170"/>
+      <c r="C112" s="350"/>
       <c r="D112" s="165"/>
       <c r="E112" s="164"/>
       <c r="F112" s="195" cm="1" t="str">
@@ -31622,7 +31643,7 @@
         <v>102</v>
       </c>
       <c r="B113" s="151"/>
-      <c r="C113" s="170"/>
+      <c r="C113" s="350"/>
       <c r="D113" s="165"/>
       <c r="E113" s="164"/>
       <c r="F113" s="195" cm="1" t="str">
@@ -31700,7 +31721,7 @@
         <v>103</v>
       </c>
       <c r="B114" s="151"/>
-      <c r="C114" s="170"/>
+      <c r="C114" s="350"/>
       <c r="D114" s="165"/>
       <c r="E114" s="164"/>
       <c r="F114" s="195" cm="1" t="str">
@@ -31778,7 +31799,7 @@
         <v>104</v>
       </c>
       <c r="B115" s="151"/>
-      <c r="C115" s="170"/>
+      <c r="C115" s="350"/>
       <c r="D115" s="165"/>
       <c r="E115" s="164"/>
       <c r="F115" s="195" cm="1" t="str">
@@ -31856,7 +31877,7 @@
         <v>105</v>
       </c>
       <c r="B116" s="151"/>
-      <c r="C116" s="170"/>
+      <c r="C116" s="350"/>
       <c r="D116" s="165"/>
       <c r="E116" s="164"/>
       <c r="F116" s="195" cm="1" t="str">
@@ -31934,7 +31955,7 @@
         <v>106</v>
       </c>
       <c r="B117" s="151"/>
-      <c r="C117" s="170"/>
+      <c r="C117" s="350"/>
       <c r="D117" s="165"/>
       <c r="E117" s="164"/>
       <c r="F117" s="195" cm="1" t="str">
@@ -32012,7 +32033,7 @@
         <v>107</v>
       </c>
       <c r="B118" s="151"/>
-      <c r="C118" s="170"/>
+      <c r="C118" s="350"/>
       <c r="D118" s="165"/>
       <c r="E118" s="164"/>
       <c r="F118" s="195" cm="1" t="str">
@@ -32090,7 +32111,7 @@
         <v>108</v>
       </c>
       <c r="B119" s="151"/>
-      <c r="C119" s="170"/>
+      <c r="C119" s="350"/>
       <c r="D119" s="165"/>
       <c r="E119" s="164"/>
       <c r="F119" s="195" cm="1" t="str">
@@ -32168,7 +32189,7 @@
         <v>109</v>
       </c>
       <c r="B120" s="151"/>
-      <c r="C120" s="170"/>
+      <c r="C120" s="350"/>
       <c r="D120" s="165"/>
       <c r="E120" s="164"/>
       <c r="F120" s="195" cm="1" t="str">
@@ -32246,7 +32267,7 @@
         <v>110</v>
       </c>
       <c r="B121" s="151"/>
-      <c r="C121" s="170"/>
+      <c r="C121" s="350"/>
       <c r="D121" s="165"/>
       <c r="E121" s="164"/>
       <c r="F121" s="195" cm="1" t="str">
@@ -32324,7 +32345,7 @@
         <v>111</v>
       </c>
       <c r="B122" s="151"/>
-      <c r="C122" s="170"/>
+      <c r="C122" s="350"/>
       <c r="D122" s="165"/>
       <c r="E122" s="164"/>
       <c r="F122" s="195" cm="1" t="str">
@@ -32402,7 +32423,7 @@
         <v>112</v>
       </c>
       <c r="B123" s="151"/>
-      <c r="C123" s="170"/>
+      <c r="C123" s="350"/>
       <c r="D123" s="165"/>
       <c r="E123" s="164"/>
       <c r="F123" s="195" cm="1" t="str">
@@ -32480,7 +32501,7 @@
         <v>113</v>
       </c>
       <c r="B124" s="151"/>
-      <c r="C124" s="170"/>
+      <c r="C124" s="350"/>
       <c r="D124" s="165"/>
       <c r="E124" s="164"/>
       <c r="F124" s="195" cm="1" t="str">
@@ -32558,7 +32579,7 @@
         <v>114</v>
       </c>
       <c r="B125" s="151"/>
-      <c r="C125" s="170"/>
+      <c r="C125" s="350"/>
       <c r="D125" s="165"/>
       <c r="E125" s="164"/>
       <c r="F125" s="195" cm="1" t="str">
@@ -32636,7 +32657,7 @@
         <v>115</v>
       </c>
       <c r="B126" s="151"/>
-      <c r="C126" s="170"/>
+      <c r="C126" s="350"/>
       <c r="D126" s="165"/>
       <c r="E126" s="164"/>
       <c r="F126" s="195" cm="1" t="str">
@@ -32714,7 +32735,7 @@
         <v>116</v>
       </c>
       <c r="B127" s="151"/>
-      <c r="C127" s="170"/>
+      <c r="C127" s="350"/>
       <c r="D127" s="165"/>
       <c r="E127" s="164"/>
       <c r="F127" s="195" cm="1" t="str">
@@ -32792,7 +32813,7 @@
         <v>117</v>
       </c>
       <c r="B128" s="151"/>
-      <c r="C128" s="170"/>
+      <c r="C128" s="350"/>
       <c r="D128" s="165"/>
       <c r="E128" s="164"/>
       <c r="F128" s="195" cm="1" t="str">
@@ -32870,7 +32891,7 @@
         <v>118</v>
       </c>
       <c r="B129" s="151"/>
-      <c r="C129" s="170"/>
+      <c r="C129" s="350"/>
       <c r="D129" s="165"/>
       <c r="E129" s="164"/>
       <c r="F129" s="195" cm="1" t="str">
@@ -32948,7 +32969,7 @@
         <v>119</v>
       </c>
       <c r="B130" s="151"/>
-      <c r="C130" s="170"/>
+      <c r="C130" s="350"/>
       <c r="D130" s="165"/>
       <c r="E130" s="164"/>
       <c r="F130" s="195" cm="1" t="str">
@@ -33026,7 +33047,7 @@
         <v>120</v>
       </c>
       <c r="B131" s="151"/>
-      <c r="C131" s="170"/>
+      <c r="C131" s="350"/>
       <c r="D131" s="165"/>
       <c r="E131" s="164"/>
       <c r="F131" s="195" cm="1" t="str">
@@ -33104,7 +33125,7 @@
         <v>121</v>
       </c>
       <c r="B132" s="151"/>
-      <c r="C132" s="170"/>
+      <c r="C132" s="350"/>
       <c r="D132" s="165"/>
       <c r="E132" s="164"/>
       <c r="F132" s="195" cm="1" t="str">
@@ -33182,7 +33203,7 @@
         <v>122</v>
       </c>
       <c r="B133" s="151"/>
-      <c r="C133" s="170"/>
+      <c r="C133" s="350"/>
       <c r="D133" s="165"/>
       <c r="E133" s="164"/>
       <c r="F133" s="195" cm="1" t="str">
@@ -33260,7 +33281,7 @@
         <v>123</v>
       </c>
       <c r="B134" s="151"/>
-      <c r="C134" s="170"/>
+      <c r="C134" s="350"/>
       <c r="D134" s="165"/>
       <c r="E134" s="164"/>
       <c r="F134" s="195" cm="1" t="str">
@@ -33338,7 +33359,7 @@
         <v>124</v>
       </c>
       <c r="B135" s="151"/>
-      <c r="C135" s="170"/>
+      <c r="C135" s="350"/>
       <c r="D135" s="165"/>
       <c r="E135" s="164"/>
       <c r="F135" s="195" cm="1" t="str">
@@ -33416,7 +33437,7 @@
         <v>125</v>
       </c>
       <c r="B136" s="151"/>
-      <c r="C136" s="170"/>
+      <c r="C136" s="350"/>
       <c r="D136" s="165"/>
       <c r="E136" s="164"/>
       <c r="F136" s="195" cm="1" t="str">
@@ -33494,7 +33515,7 @@
         <v>126</v>
       </c>
       <c r="B137" s="151"/>
-      <c r="C137" s="170"/>
+      <c r="C137" s="350"/>
       <c r="D137" s="165"/>
       <c r="E137" s="164"/>
       <c r="F137" s="195" cm="1" t="str">
@@ -33572,7 +33593,7 @@
         <v>127</v>
       </c>
       <c r="B138" s="151"/>
-      <c r="C138" s="170"/>
+      <c r="C138" s="350"/>
       <c r="D138" s="165"/>
       <c r="E138" s="164"/>
       <c r="F138" s="195" cm="1" t="str">
@@ -33650,7 +33671,7 @@
         <v>128</v>
       </c>
       <c r="B139" s="151"/>
-      <c r="C139" s="170"/>
+      <c r="C139" s="350"/>
       <c r="D139" s="165"/>
       <c r="E139" s="164"/>
       <c r="F139" s="195" cm="1" t="str">
@@ -33728,7 +33749,7 @@
         <v>129</v>
       </c>
       <c r="B140" s="151"/>
-      <c r="C140" s="170"/>
+      <c r="C140" s="350"/>
       <c r="D140" s="165"/>
       <c r="E140" s="164"/>
       <c r="F140" s="195" cm="1" t="str">
@@ -33806,7 +33827,7 @@
         <v>130</v>
       </c>
       <c r="B141" s="151"/>
-      <c r="C141" s="170"/>
+      <c r="C141" s="350"/>
       <c r="D141" s="165"/>
       <c r="E141" s="164"/>
       <c r="F141" s="195" cm="1" t="str">
@@ -33884,7 +33905,7 @@
         <v>131</v>
       </c>
       <c r="B142" s="151"/>
-      <c r="C142" s="170"/>
+      <c r="C142" s="350"/>
       <c r="D142" s="165"/>
       <c r="E142" s="164"/>
       <c r="F142" s="195" cm="1" t="str">
@@ -33962,7 +33983,7 @@
         <v>132</v>
       </c>
       <c r="B143" s="151"/>
-      <c r="C143" s="170"/>
+      <c r="C143" s="350"/>
       <c r="D143" s="165"/>
       <c r="E143" s="164"/>
       <c r="F143" s="195" cm="1" t="str">
@@ -34040,7 +34061,7 @@
         <v>133</v>
       </c>
       <c r="B144" s="151"/>
-      <c r="C144" s="170"/>
+      <c r="C144" s="350"/>
       <c r="D144" s="165"/>
       <c r="E144" s="164"/>
       <c r="F144" s="195" cm="1" t="str">
@@ -34118,7 +34139,7 @@
         <v>134</v>
       </c>
       <c r="B145" s="151"/>
-      <c r="C145" s="170"/>
+      <c r="C145" s="350"/>
       <c r="D145" s="165"/>
       <c r="E145" s="164"/>
       <c r="F145" s="195" cm="1" t="str">
@@ -34196,7 +34217,7 @@
         <v>135</v>
       </c>
       <c r="B146" s="151"/>
-      <c r="C146" s="170"/>
+      <c r="C146" s="350"/>
       <c r="D146" s="165"/>
       <c r="E146" s="164"/>
       <c r="F146" s="195" cm="1" t="str">
@@ -34274,7 +34295,7 @@
         <v>136</v>
       </c>
       <c r="B147" s="151"/>
-      <c r="C147" s="170"/>
+      <c r="C147" s="350"/>
       <c r="D147" s="165"/>
       <c r="E147" s="164"/>
       <c r="F147" s="195" cm="1" t="str">
@@ -34352,7 +34373,7 @@
         <v>137</v>
       </c>
       <c r="B148" s="151"/>
-      <c r="C148" s="170"/>
+      <c r="C148" s="350"/>
       <c r="D148" s="165"/>
       <c r="E148" s="164"/>
       <c r="F148" s="195" cm="1" t="str">
@@ -34430,7 +34451,7 @@
         <v>138</v>
       </c>
       <c r="B149" s="151"/>
-      <c r="C149" s="170"/>
+      <c r="C149" s="350"/>
       <c r="D149" s="165"/>
       <c r="E149" s="164"/>
       <c r="F149" s="195" cm="1" t="str">
@@ -34508,7 +34529,7 @@
         <v>139</v>
       </c>
       <c r="B150" s="151"/>
-      <c r="C150" s="170"/>
+      <c r="C150" s="350"/>
       <c r="D150" s="165"/>
       <c r="E150" s="164"/>
       <c r="F150" s="195" cm="1" t="str">
@@ -34586,7 +34607,7 @@
         <v>140</v>
       </c>
       <c r="B151" s="151"/>
-      <c r="C151" s="170"/>
+      <c r="C151" s="350"/>
       <c r="D151" s="165"/>
       <c r="E151" s="164"/>
       <c r="F151" s="195" cm="1" t="str">
@@ -34664,7 +34685,7 @@
         <v>141</v>
       </c>
       <c r="B152" s="151"/>
-      <c r="C152" s="170"/>
+      <c r="C152" s="350"/>
       <c r="D152" s="165"/>
       <c r="E152" s="164"/>
       <c r="F152" s="195" cm="1" t="str">
@@ -34745,7 +34766,7 @@
         <v>142</v>
       </c>
       <c r="B153" s="151"/>
-      <c r="C153" s="170"/>
+      <c r="C153" s="350"/>
       <c r="D153" s="165"/>
       <c r="E153" s="164"/>
       <c r="F153" s="195" cm="1" t="str">
@@ -34826,7 +34847,7 @@
         <v>143</v>
       </c>
       <c r="B154" s="151"/>
-      <c r="C154" s="170"/>
+      <c r="C154" s="350"/>
       <c r="D154" s="165"/>
       <c r="E154" s="164"/>
       <c r="F154" s="195" cm="1" t="str">
@@ -34907,7 +34928,7 @@
         <v>144</v>
       </c>
       <c r="B155" s="151"/>
-      <c r="C155" s="170"/>
+      <c r="C155" s="350"/>
       <c r="D155" s="165"/>
       <c r="E155" s="164"/>
       <c r="F155" s="195" cm="1" t="str">
@@ -34988,7 +35009,7 @@
         <v>145</v>
       </c>
       <c r="B156" s="151"/>
-      <c r="C156" s="170"/>
+      <c r="C156" s="350"/>
       <c r="D156" s="165"/>
       <c r="E156" s="164"/>
       <c r="F156" s="195" cm="1" t="str">
@@ -35069,7 +35090,7 @@
         <v>146</v>
       </c>
       <c r="B157" s="151"/>
-      <c r="C157" s="170"/>
+      <c r="C157" s="350"/>
       <c r="D157" s="165"/>
       <c r="E157" s="164"/>
       <c r="F157" s="195" cm="1" t="str">
@@ -35150,7 +35171,7 @@
         <v>147</v>
       </c>
       <c r="B158" s="151"/>
-      <c r="C158" s="170"/>
+      <c r="C158" s="350"/>
       <c r="D158" s="165"/>
       <c r="E158" s="164"/>
       <c r="F158" s="195" cm="1" t="str">
@@ -35231,7 +35252,7 @@
         <v>148</v>
       </c>
       <c r="B159" s="151"/>
-      <c r="C159" s="170"/>
+      <c r="C159" s="350"/>
       <c r="D159" s="165"/>
       <c r="E159" s="164"/>
       <c r="F159" s="195" cm="1" t="str">
@@ -35312,7 +35333,7 @@
         <v>149</v>
       </c>
       <c r="B160" s="151"/>
-      <c r="C160" s="170"/>
+      <c r="C160" s="350"/>
       <c r="D160" s="165"/>
       <c r="E160" s="164"/>
       <c r="F160" s="195" cm="1" t="str">
@@ -35393,7 +35414,7 @@
         <v>150</v>
       </c>
       <c r="B161" s="151"/>
-      <c r="C161" s="170"/>
+      <c r="C161" s="350"/>
       <c r="D161" s="165"/>
       <c r="E161" s="164"/>
       <c r="F161" s="195" cm="1" t="str">
@@ -35474,7 +35495,7 @@
         <v>151</v>
       </c>
       <c r="B162" s="151"/>
-      <c r="C162" s="170"/>
+      <c r="C162" s="350"/>
       <c r="D162" s="165"/>
       <c r="E162" s="164"/>
       <c r="F162" s="195" cm="1" t="str">
@@ -35555,7 +35576,7 @@
         <v>152</v>
       </c>
       <c r="B163" s="151"/>
-      <c r="C163" s="170"/>
+      <c r="C163" s="350"/>
       <c r="D163" s="165"/>
       <c r="E163" s="164"/>
       <c r="F163" s="195" cm="1" t="str">
@@ -35636,7 +35657,7 @@
         <v>153</v>
       </c>
       <c r="B164" s="151"/>
-      <c r="C164" s="170"/>
+      <c r="C164" s="350"/>
       <c r="D164" s="165"/>
       <c r="E164" s="164"/>
       <c r="F164" s="195" cm="1" t="str">
@@ -35717,7 +35738,7 @@
         <v>154</v>
       </c>
       <c r="B165" s="151"/>
-      <c r="C165" s="170"/>
+      <c r="C165" s="350"/>
       <c r="D165" s="165"/>
       <c r="E165" s="164"/>
       <c r="F165" s="195" cm="1" t="str">
@@ -35798,7 +35819,7 @@
         <v>155</v>
       </c>
       <c r="B166" s="151"/>
-      <c r="C166" s="170"/>
+      <c r="C166" s="350"/>
       <c r="D166" s="165"/>
       <c r="E166" s="164"/>
       <c r="F166" s="195" cm="1" t="str">
@@ -35879,7 +35900,7 @@
         <v>156</v>
       </c>
       <c r="B167" s="151"/>
-      <c r="C167" s="170"/>
+      <c r="C167" s="350"/>
       <c r="D167" s="165"/>
       <c r="E167" s="164"/>
       <c r="F167" s="195" cm="1" t="str">
@@ -35960,7 +35981,7 @@
         <v>157</v>
       </c>
       <c r="B168" s="151"/>
-      <c r="C168" s="170"/>
+      <c r="C168" s="350"/>
       <c r="D168" s="165"/>
       <c r="E168" s="164"/>
       <c r="F168" s="195" cm="1" t="str">
@@ -36041,7 +36062,7 @@
         <v>158</v>
       </c>
       <c r="B169" s="151"/>
-      <c r="C169" s="170"/>
+      <c r="C169" s="350"/>
       <c r="D169" s="165"/>
       <c r="E169" s="164"/>
       <c r="F169" s="195" cm="1" t="str">
@@ -36122,7 +36143,7 @@
         <v>159</v>
       </c>
       <c r="B170" s="151"/>
-      <c r="C170" s="170"/>
+      <c r="C170" s="350"/>
       <c r="D170" s="165"/>
       <c r="E170" s="164"/>
       <c r="F170" s="195" cm="1" t="str">
@@ -36203,7 +36224,7 @@
         <v>160</v>
       </c>
       <c r="B171" s="151"/>
-      <c r="C171" s="170"/>
+      <c r="C171" s="350"/>
       <c r="D171" s="165"/>
       <c r="E171" s="164"/>
       <c r="F171" s="195" cm="1" t="str">
@@ -36284,7 +36305,7 @@
         <v>161</v>
       </c>
       <c r="B172" s="151"/>
-      <c r="C172" s="170"/>
+      <c r="C172" s="350"/>
       <c r="D172" s="165"/>
       <c r="E172" s="164"/>
       <c r="F172" s="195" cm="1" t="str">
@@ -36365,7 +36386,7 @@
         <v>162</v>
       </c>
       <c r="B173" s="151"/>
-      <c r="C173" s="170"/>
+      <c r="C173" s="350"/>
       <c r="D173" s="165"/>
       <c r="E173" s="164"/>
       <c r="F173" s="195" cm="1" t="str">
@@ -36446,7 +36467,7 @@
         <v>163</v>
       </c>
       <c r="B174" s="151"/>
-      <c r="C174" s="170"/>
+      <c r="C174" s="350"/>
       <c r="D174" s="165"/>
       <c r="E174" s="164"/>
       <c r="F174" s="195" cm="1" t="str">
@@ -36527,7 +36548,7 @@
         <v>164</v>
       </c>
       <c r="B175" s="151"/>
-      <c r="C175" s="170"/>
+      <c r="C175" s="350"/>
       <c r="D175" s="165"/>
       <c r="E175" s="164"/>
       <c r="F175" s="195" cm="1" t="str">
@@ -36608,7 +36629,7 @@
         <v>165</v>
       </c>
       <c r="B176" s="151"/>
-      <c r="C176" s="170"/>
+      <c r="C176" s="350"/>
       <c r="D176" s="165"/>
       <c r="E176" s="164"/>
       <c r="F176" s="195" cm="1" t="str">
@@ -36689,7 +36710,7 @@
         <v>166</v>
       </c>
       <c r="B177" s="151"/>
-      <c r="C177" s="170"/>
+      <c r="C177" s="350"/>
       <c r="D177" s="165"/>
       <c r="E177" s="164"/>
       <c r="F177" s="195" cm="1" t="str">
@@ -36770,7 +36791,7 @@
         <v>167</v>
       </c>
       <c r="B178" s="151"/>
-      <c r="C178" s="170"/>
+      <c r="C178" s="350"/>
       <c r="D178" s="165"/>
       <c r="E178" s="164"/>
       <c r="F178" s="195" cm="1" t="str">
@@ -36851,7 +36872,7 @@
         <v>168</v>
       </c>
       <c r="B179" s="151"/>
-      <c r="C179" s="170"/>
+      <c r="C179" s="350"/>
       <c r="D179" s="165"/>
       <c r="E179" s="164"/>
       <c r="F179" s="195" cm="1" t="str">
@@ -36932,7 +36953,7 @@
         <v>169</v>
       </c>
       <c r="B180" s="151"/>
-      <c r="C180" s="170"/>
+      <c r="C180" s="350"/>
       <c r="D180" s="165"/>
       <c r="E180" s="164"/>
       <c r="F180" s="195" cm="1" t="str">
@@ -37013,7 +37034,7 @@
         <v>170</v>
       </c>
       <c r="B181" s="151"/>
-      <c r="C181" s="170"/>
+      <c r="C181" s="350"/>
       <c r="D181" s="165"/>
       <c r="E181" s="164"/>
       <c r="F181" s="195" cm="1" t="str">
@@ -37094,7 +37115,7 @@
         <v>171</v>
       </c>
       <c r="B182" s="151"/>
-      <c r="C182" s="170"/>
+      <c r="C182" s="350"/>
       <c r="D182" s="165"/>
       <c r="E182" s="164"/>
       <c r="F182" s="195" cm="1" t="str">
@@ -37175,7 +37196,7 @@
         <v>172</v>
       </c>
       <c r="B183" s="151"/>
-      <c r="C183" s="170"/>
+      <c r="C183" s="350"/>
       <c r="D183" s="165"/>
       <c r="E183" s="164"/>
       <c r="F183" s="195" cm="1" t="str">
@@ -37256,7 +37277,7 @@
         <v>173</v>
       </c>
       <c r="B184" s="151"/>
-      <c r="C184" s="170"/>
+      <c r="C184" s="350"/>
       <c r="D184" s="165"/>
       <c r="E184" s="164"/>
       <c r="F184" s="195" cm="1" t="str">
@@ -37337,7 +37358,7 @@
         <v>174</v>
       </c>
       <c r="B185" s="151"/>
-      <c r="C185" s="170"/>
+      <c r="C185" s="350"/>
       <c r="D185" s="165"/>
       <c r="E185" s="164"/>
       <c r="F185" s="195" cm="1" t="str">
@@ -37418,7 +37439,7 @@
         <v>175</v>
       </c>
       <c r="B186" s="151"/>
-      <c r="C186" s="170"/>
+      <c r="C186" s="350"/>
       <c r="D186" s="165"/>
       <c r="E186" s="164"/>
       <c r="F186" s="195" cm="1" t="str">
@@ -37499,7 +37520,7 @@
         <v>176</v>
       </c>
       <c r="B187" s="151"/>
-      <c r="C187" s="170"/>
+      <c r="C187" s="350"/>
       <c r="D187" s="165"/>
       <c r="E187" s="164"/>
       <c r="F187" s="195" cm="1" t="str">
@@ -37580,7 +37601,7 @@
         <v>177</v>
       </c>
       <c r="B188" s="151"/>
-      <c r="C188" s="170"/>
+      <c r="C188" s="350"/>
       <c r="D188" s="165"/>
       <c r="E188" s="164"/>
       <c r="F188" s="195" cm="1" t="str">
@@ -37661,7 +37682,7 @@
         <v>178</v>
       </c>
       <c r="B189" s="151"/>
-      <c r="C189" s="170"/>
+      <c r="C189" s="350"/>
       <c r="D189" s="165"/>
       <c r="E189" s="164"/>
       <c r="F189" s="195" cm="1" t="str">
@@ -37742,7 +37763,7 @@
         <v>179</v>
       </c>
       <c r="B190" s="151"/>
-      <c r="C190" s="170"/>
+      <c r="C190" s="350"/>
       <c r="D190" s="165"/>
       <c r="E190" s="164"/>
       <c r="F190" s="195" cm="1" t="str">
@@ -37823,7 +37844,7 @@
         <v>180</v>
       </c>
       <c r="B191" s="151"/>
-      <c r="C191" s="170"/>
+      <c r="C191" s="350"/>
       <c r="D191" s="165"/>
       <c r="E191" s="164"/>
       <c r="F191" s="195" cm="1" t="str">
@@ -37904,7 +37925,7 @@
         <v>181</v>
       </c>
       <c r="B192" s="151"/>
-      <c r="C192" s="170"/>
+      <c r="C192" s="350"/>
       <c r="D192" s="165"/>
       <c r="E192" s="164"/>
       <c r="F192" s="195" cm="1" t="str">
@@ -37985,7 +38006,7 @@
         <v>182</v>
       </c>
       <c r="B193" s="151"/>
-      <c r="C193" s="170"/>
+      <c r="C193" s="350"/>
       <c r="D193" s="165"/>
       <c r="E193" s="164"/>
       <c r="F193" s="195" cm="1" t="str">
@@ -38066,7 +38087,7 @@
         <v>183</v>
       </c>
       <c r="B194" s="151"/>
-      <c r="C194" s="170"/>
+      <c r="C194" s="350"/>
       <c r="D194" s="165"/>
       <c r="E194" s="164"/>
       <c r="F194" s="195" cm="1" t="str">
@@ -38147,7 +38168,7 @@
         <v>184</v>
       </c>
       <c r="B195" s="151"/>
-      <c r="C195" s="170"/>
+      <c r="C195" s="350"/>
       <c r="D195" s="165"/>
       <c r="E195" s="164"/>
       <c r="F195" s="195" cm="1" t="str">
@@ -38228,7 +38249,7 @@
         <v>185</v>
       </c>
       <c r="B196" s="151"/>
-      <c r="C196" s="170"/>
+      <c r="C196" s="350"/>
       <c r="D196" s="165"/>
       <c r="E196" s="164"/>
       <c r="F196" s="195" cm="1" t="str">
@@ -38309,7 +38330,7 @@
         <v>186</v>
       </c>
       <c r="B197" s="151"/>
-      <c r="C197" s="170"/>
+      <c r="C197" s="350"/>
       <c r="D197" s="165"/>
       <c r="E197" s="164"/>
       <c r="F197" s="195" cm="1" t="str">
@@ -38390,7 +38411,7 @@
         <v>187</v>
       </c>
       <c r="B198" s="151"/>
-      <c r="C198" s="170"/>
+      <c r="C198" s="350"/>
       <c r="D198" s="165"/>
       <c r="E198" s="164"/>
       <c r="F198" s="195" cm="1" t="str">
@@ -38471,7 +38492,7 @@
         <v>188</v>
       </c>
       <c r="B199" s="151"/>
-      <c r="C199" s="170"/>
+      <c r="C199" s="350"/>
       <c r="D199" s="165"/>
       <c r="E199" s="164"/>
       <c r="F199" s="195" cm="1" t="str">
@@ -38552,7 +38573,7 @@
         <v>189</v>
       </c>
       <c r="B200" s="151"/>
-      <c r="C200" s="170"/>
+      <c r="C200" s="350"/>
       <c r="D200" s="165"/>
       <c r="E200" s="164"/>
       <c r="F200" s="195" cm="1" t="str">
@@ -38633,7 +38654,7 @@
         <v>190</v>
       </c>
       <c r="B201" s="151"/>
-      <c r="C201" s="170"/>
+      <c r="C201" s="350"/>
       <c r="D201" s="165"/>
       <c r="E201" s="164"/>
       <c r="F201" s="195" cm="1" t="str">
@@ -38714,7 +38735,7 @@
         <v>191</v>
       </c>
       <c r="B202" s="151"/>
-      <c r="C202" s="170"/>
+      <c r="C202" s="350"/>
       <c r="D202" s="165"/>
       <c r="E202" s="164"/>
       <c r="F202" s="195" cm="1" t="str">
@@ -38795,7 +38816,7 @@
         <v>192</v>
       </c>
       <c r="B203" s="151"/>
-      <c r="C203" s="170"/>
+      <c r="C203" s="350"/>
       <c r="D203" s="165"/>
       <c r="E203" s="164"/>
       <c r="F203" s="195" cm="1" t="str">
@@ -38876,7 +38897,7 @@
         <v>193</v>
       </c>
       <c r="B204" s="151"/>
-      <c r="C204" s="170"/>
+      <c r="C204" s="350"/>
       <c r="D204" s="165"/>
       <c r="E204" s="164"/>
       <c r="F204" s="195" cm="1" t="str">
@@ -38957,7 +38978,7 @@
         <v>194</v>
       </c>
       <c r="B205" s="151"/>
-      <c r="C205" s="170"/>
+      <c r="C205" s="350"/>
       <c r="D205" s="165"/>
       <c r="E205" s="164"/>
       <c r="F205" s="195" cm="1" t="str">
@@ -39038,7 +39059,7 @@
         <v>195</v>
       </c>
       <c r="B206" s="151"/>
-      <c r="C206" s="170"/>
+      <c r="C206" s="350"/>
       <c r="D206" s="165"/>
       <c r="E206" s="164"/>
       <c r="F206" s="195" cm="1" t="str">
@@ -39119,7 +39140,7 @@
         <v>196</v>
       </c>
       <c r="B207" s="151"/>
-      <c r="C207" s="170"/>
+      <c r="C207" s="350"/>
       <c r="D207" s="165"/>
       <c r="E207" s="164"/>
       <c r="F207" s="195" cm="1" t="str">
@@ -39200,7 +39221,7 @@
         <v>197</v>
       </c>
       <c r="B208" s="151"/>
-      <c r="C208" s="170"/>
+      <c r="C208" s="350"/>
       <c r="D208" s="165"/>
       <c r="E208" s="164"/>
       <c r="F208" s="195" cm="1" t="str">
@@ -39281,7 +39302,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="151"/>
-      <c r="C209" s="170"/>
+      <c r="C209" s="350"/>
       <c r="D209" s="165"/>
       <c r="E209" s="164"/>
       <c r="F209" s="195" cm="1" t="str">
@@ -39362,7 +39383,7 @@
         <v>199</v>
       </c>
       <c r="B210" s="151"/>
-      <c r="C210" s="170"/>
+      <c r="C210" s="350"/>
       <c r="D210" s="165"/>
       <c r="E210" s="164"/>
       <c r="F210" s="195" cm="1" t="str">
@@ -40040,8 +40061,8 @@
         <v>0</v>
       </c>
       <c r="B7" s="282"/>
-      <c r="C7" s="283"/>
-      <c r="D7" s="283"/>
+      <c r="C7" s="353"/>
+      <c r="D7" s="353"/>
       <c r="E7" s="284"/>
       <c r="F7" t="str" s="285" cm="1">
         <f t="array" ref="F7">IF(AD7="","",H7-G7)</f>
@@ -40097,10 +40118,10 @@
       <c r="B8" t="s" s="296">
         <v>178</v>
       </c>
-      <c r="C8" t="s" s="297">
+      <c r="C8" t="s" s="354">
         <v>179</v>
       </c>
-      <c r="D8" s="283"/>
+      <c r="D8" s="353"/>
       <c r="E8" s="284"/>
       <c r="F8" s="288" cm="1">
         <f t="array" ref="F8">IF($AD8="","",$H8-$G8)</f>
@@ -40173,10 +40194,10 @@
       <c r="B9" t="s" s="296">
         <v>181</v>
       </c>
-      <c r="C9" t="s" s="306">
+      <c r="C9" t="s" s="355">
         <v>182</v>
       </c>
-      <c r="D9" t="s" s="297">
+      <c r="D9" t="s" s="354">
         <v>183</v>
       </c>
       <c r="E9" s="284"/>
@@ -40251,10 +40272,10 @@
       <c r="B10" t="s" s="296">
         <v>185</v>
       </c>
-      <c r="C10" t="s" s="306">
+      <c r="C10" t="s" s="355">
         <v>186</v>
       </c>
-      <c r="D10" t="s" s="297">
+      <c r="D10" t="s" s="354">
         <v>187</v>
       </c>
       <c r="E10" s="284"/>
@@ -40329,10 +40350,10 @@
       <c r="B11" t="s" s="296">
         <v>189</v>
       </c>
-      <c r="C11" t="s" s="297">
+      <c r="C11" t="s" s="354">
         <v>190</v>
       </c>
-      <c r="D11" t="s" s="297">
+      <c r="D11" t="s" s="354">
         <v>187</v>
       </c>
       <c r="E11" s="284"/>
@@ -40407,10 +40428,10 @@
       <c r="B12" t="s" s="296">
         <v>192</v>
       </c>
-      <c r="C12" t="s" s="297">
+      <c r="C12" t="s" s="354">
         <v>193</v>
       </c>
-      <c r="D12" t="s" s="297">
+      <c r="D12" t="s" s="354">
         <v>194</v>
       </c>
       <c r="E12" s="284"/>
@@ -40483,10 +40504,10 @@
       <c r="B13" t="s" s="296">
         <v>195</v>
       </c>
-      <c r="C13" t="s" s="297">
+      <c r="C13" t="s" s="354">
         <v>196</v>
       </c>
-      <c r="D13" t="s" s="297">
+      <c r="D13" t="s" s="354">
         <v>197</v>
       </c>
       <c r="E13" s="284"/>
@@ -40561,10 +40582,10 @@
       <c r="B14" t="s" s="296">
         <v>199</v>
       </c>
-      <c r="C14" t="s" s="297">
+      <c r="C14" t="s" s="354">
         <v>200</v>
       </c>
-      <c r="D14" t="s" s="297">
+      <c r="D14" t="s" s="354">
         <v>201</v>
       </c>
       <c r="E14" s="284"/>
@@ -40637,10 +40658,10 @@
       <c r="B15" t="s" s="296">
         <v>202</v>
       </c>
-      <c r="C15" t="s" s="297">
+      <c r="C15" t="s" s="354">
         <v>203</v>
       </c>
-      <c r="D15" t="s" s="297">
+      <c r="D15" t="s" s="354">
         <v>204</v>
       </c>
       <c r="E15" s="284"/>
@@ -40713,10 +40734,10 @@
       <c r="B16" t="s" s="296">
         <v>205</v>
       </c>
-      <c r="C16" t="s" s="297">
+      <c r="C16" t="s" s="354">
         <v>206</v>
       </c>
-      <c r="D16" t="s" s="297">
+      <c r="D16" t="s" s="354">
         <v>207</v>
       </c>
       <c r="E16" s="284"/>
@@ -40789,10 +40810,10 @@
       <c r="B17" t="s" s="296">
         <v>208</v>
       </c>
-      <c r="C17" t="s" s="297">
+      <c r="C17" t="s" s="354">
         <v>209</v>
       </c>
-      <c r="D17" t="s" s="297">
+      <c r="D17" t="s" s="354">
         <v>210</v>
       </c>
       <c r="E17" s="284"/>
@@ -40865,10 +40886,10 @@
       <c r="B18" t="s" s="296">
         <v>211</v>
       </c>
-      <c r="C18" t="s" s="306">
+      <c r="C18" t="s" s="355">
         <v>212</v>
       </c>
-      <c r="D18" t="s" s="297">
+      <c r="D18" t="s" s="354">
         <v>213</v>
       </c>
       <c r="E18" s="284"/>
@@ -40943,10 +40964,10 @@
       <c r="B19" t="s" s="296">
         <v>214</v>
       </c>
-      <c r="C19" t="s" s="297">
+      <c r="C19" t="s" s="354">
         <v>215</v>
       </c>
-      <c r="D19" t="s" s="297">
+      <c r="D19" t="s" s="354">
         <v>216</v>
       </c>
       <c r="E19" s="284"/>
@@ -41021,10 +41042,10 @@
       <c r="B20" t="s" s="296">
         <v>218</v>
       </c>
-      <c r="C20" t="s" s="297">
+      <c r="C20" t="s" s="354">
         <v>219</v>
       </c>
-      <c r="D20" t="s" s="297">
+      <c r="D20" t="s" s="354">
         <v>220</v>
       </c>
       <c r="E20" s="284"/>
@@ -41097,10 +41118,10 @@
       <c r="B21" t="s" s="296">
         <v>221</v>
       </c>
-      <c r="C21" t="s" s="297">
+      <c r="C21" t="s" s="354">
         <v>222</v>
       </c>
-      <c r="D21" t="s" s="297">
+      <c r="D21" t="s" s="354">
         <v>223</v>
       </c>
       <c r="E21" s="284"/>
@@ -41173,10 +41194,10 @@
       <c r="B22" t="s" s="296">
         <v>224</v>
       </c>
-      <c r="C22" t="s" s="297">
+      <c r="C22" t="s" s="354">
         <v>225</v>
       </c>
-      <c r="D22" t="s" s="297">
+      <c r="D22" t="s" s="354">
         <v>226</v>
       </c>
       <c r="E22" s="284"/>
@@ -41247,8 +41268,8 @@
         <v>16</v>
       </c>
       <c r="B23" s="282"/>
-      <c r="C23" s="283"/>
-      <c r="D23" s="283"/>
+      <c r="C23" s="353"/>
+      <c r="D23" s="353"/>
       <c r="E23" s="284"/>
       <c r="F23" t="str" s="285" cm="1">
         <f t="array" ref="F23">IF($AD23="","",$H23-$G23)</f>
@@ -41302,10 +41323,10 @@
         <v>17</v>
       </c>
       <c r="B24" s="282"/>
-      <c r="C24" t="s" s="297">
+      <c r="C24" t="s" s="354">
         <v>227</v>
       </c>
-      <c r="D24" s="283"/>
+      <c r="D24" s="353"/>
       <c r="E24" s="284"/>
       <c r="F24" t="str" s="285" cm="1">
         <f t="array" ref="F24">IF($AD24="","",$H24-$G24)</f>
@@ -41361,10 +41382,10 @@
       <c r="B25" t="s" s="296">
         <v>228</v>
       </c>
-      <c r="C25" t="s" s="297">
+      <c r="C25" t="s" s="354">
         <v>229</v>
       </c>
-      <c r="D25" s="283"/>
+      <c r="D25" s="353"/>
       <c r="E25" s="284"/>
       <c r="F25" t="str" s="285" cm="1">
         <f t="array" ref="F25">IF($AD25="","",$H25-$G25)</f>
@@ -41422,10 +41443,10 @@
       <c r="B26" t="s" s="296">
         <v>231</v>
       </c>
-      <c r="C26" t="s" s="297">
+      <c r="C26" t="s" s="354">
         <v>232</v>
       </c>
-      <c r="D26" s="283"/>
+      <c r="D26" s="353"/>
       <c r="E26" s="284"/>
       <c r="F26" t="str" s="285" cm="1">
         <f t="array" ref="F26">IF($AD26="","",$H26-$G26)</f>
@@ -41481,8 +41502,8 @@
         <v>20</v>
       </c>
       <c r="B27" s="282"/>
-      <c r="C27" s="283"/>
-      <c r="D27" s="283"/>
+      <c r="C27" s="353"/>
+      <c r="D27" s="353"/>
       <c r="E27" s="284"/>
       <c r="F27" t="str" s="285" cm="1">
         <f t="array" ref="F27">IF($AD27="","",$H27-$G27)</f>
@@ -41536,8 +41557,8 @@
         <v>21</v>
       </c>
       <c r="B28" s="282"/>
-      <c r="C28" s="283"/>
-      <c r="D28" s="283"/>
+      <c r="C28" s="353"/>
+      <c r="D28" s="353"/>
       <c r="E28" s="284"/>
       <c r="F28" t="str" s="285" cm="1">
         <f t="array" ref="F28">IF($AD28="","",$H28-$G28)</f>
@@ -41591,8 +41612,8 @@
         <v>22</v>
       </c>
       <c r="B29" s="282"/>
-      <c r="C29" s="283"/>
-      <c r="D29" s="283"/>
+      <c r="C29" s="353"/>
+      <c r="D29" s="353"/>
       <c r="E29" s="284"/>
       <c r="F29" t="str" s="285" cm="1">
         <f t="array" ref="F29">IF($AD29="","",$H29-$G29)</f>
@@ -41646,8 +41667,8 @@
         <v>23</v>
       </c>
       <c r="B30" s="282"/>
-      <c r="C30" s="283"/>
-      <c r="D30" s="283"/>
+      <c r="C30" s="353"/>
+      <c r="D30" s="353"/>
       <c r="E30" s="284"/>
       <c r="F30" t="str" s="285" cm="1">
         <f t="array" ref="F30">IF($AD30="","",$H30-$G30)</f>
@@ -41701,8 +41722,8 @@
         <v>24</v>
       </c>
       <c r="B31" s="282"/>
-      <c r="C31" s="283"/>
-      <c r="D31" s="283"/>
+      <c r="C31" s="353"/>
+      <c r="D31" s="353"/>
       <c r="E31" s="284"/>
       <c r="F31" t="str" s="285" cm="1">
         <f t="array" ref="F31">IF($AD31="","",$H31-$G31)</f>
@@ -41756,8 +41777,8 @@
         <v>25</v>
       </c>
       <c r="B32" s="282"/>
-      <c r="C32" s="283"/>
-      <c r="D32" s="283"/>
+      <c r="C32" s="353"/>
+      <c r="D32" s="353"/>
       <c r="E32" s="284"/>
       <c r="F32" t="str" s="285" cm="1">
         <f t="array" ref="F32">IF($AD32="","",$H32-$G32)</f>
@@ -41811,8 +41832,8 @@
         <v>26</v>
       </c>
       <c r="B33" s="282"/>
-      <c r="C33" s="283"/>
-      <c r="D33" s="283"/>
+      <c r="C33" s="353"/>
+      <c r="D33" s="353"/>
       <c r="E33" s="284"/>
       <c r="F33" t="str" s="285" cm="1">
         <f t="array" ref="F33">IF($AD33="","",$H33-$G33)</f>
@@ -41866,8 +41887,8 @@
         <v>27</v>
       </c>
       <c r="B34" s="282"/>
-      <c r="C34" s="283"/>
-      <c r="D34" s="283"/>
+      <c r="C34" s="353"/>
+      <c r="D34" s="353"/>
       <c r="E34" s="284"/>
       <c r="F34" t="str" s="285" cm="1">
         <f t="array" ref="F34">IF($AD34="","",$H34-$G34)</f>
@@ -41921,8 +41942,8 @@
         <v>28</v>
       </c>
       <c r="B35" s="282"/>
-      <c r="C35" s="283"/>
-      <c r="D35" s="283"/>
+      <c r="C35" s="353"/>
+      <c r="D35" s="353"/>
       <c r="E35" s="284"/>
       <c r="F35" t="str" s="285" cm="1">
         <f t="array" ref="F35">IF($AD35="","",$H35-$G35)</f>
@@ -41976,8 +41997,8 @@
         <v>29</v>
       </c>
       <c r="B36" s="282"/>
-      <c r="C36" s="283"/>
-      <c r="D36" s="283"/>
+      <c r="C36" s="353"/>
+      <c r="D36" s="353"/>
       <c r="E36" s="284"/>
       <c r="F36" t="str" s="285" cm="1">
         <f t="array" ref="F36">IF($AD36="","",$H36-$G36)</f>
@@ -42031,10 +42052,10 @@
         <v>30</v>
       </c>
       <c r="B37" s="282"/>
-      <c r="C37" t="s" s="297">
+      <c r="C37" t="s" s="354">
         <v>234</v>
       </c>
-      <c r="D37" s="283"/>
+      <c r="D37" s="353"/>
       <c r="E37" s="284"/>
       <c r="F37" t="str" s="285" cm="1">
         <f t="array" ref="F37">IF($AD37="","",$H37-$G37)</f>
@@ -42088,10 +42109,10 @@
         <v>31</v>
       </c>
       <c r="B38" s="282"/>
-      <c r="C38" t="s" s="297">
+      <c r="C38" t="s" s="354">
         <v>235</v>
       </c>
-      <c r="D38" s="283"/>
+      <c r="D38" s="353"/>
       <c r="E38" s="284"/>
       <c r="F38" t="str" s="285" cm="1">
         <f t="array" ref="F38">IF($AD38="","",$H38-$G38)</f>
@@ -42145,10 +42166,10 @@
         <v>32</v>
       </c>
       <c r="B39" s="282"/>
-      <c r="C39" t="s" s="297">
+      <c r="C39" t="s" s="354">
         <v>236</v>
       </c>
-      <c r="D39" s="283"/>
+      <c r="D39" s="353"/>
       <c r="E39" s="284"/>
       <c r="F39" t="str" s="285" cm="1">
         <f t="array" ref="F39">IF($AD39="","",$H39-$G39)</f>
@@ -42202,10 +42223,10 @@
         <v>33</v>
       </c>
       <c r="B40" s="282"/>
-      <c r="C40" t="s" s="297">
+      <c r="C40" t="s" s="354">
         <v>237</v>
       </c>
-      <c r="D40" s="283"/>
+      <c r="D40" s="353"/>
       <c r="E40" s="284"/>
       <c r="F40" t="str" s="285" cm="1">
         <f t="array" ref="F40">IF($AD40="","",$H40-$G40)</f>
@@ -42259,10 +42280,10 @@
         <v>34</v>
       </c>
       <c r="B41" s="282"/>
-      <c r="C41" t="s" s="297">
+      <c r="C41" t="s" s="354">
         <v>193</v>
       </c>
-      <c r="D41" s="283"/>
+      <c r="D41" s="353"/>
       <c r="E41" s="284"/>
       <c r="F41" t="str" s="285" cm="1">
         <f t="array" ref="F41">IF($AD41="","",$H41-$G41)</f>
@@ -42316,10 +42337,10 @@
         <v>35</v>
       </c>
       <c r="B42" s="282"/>
-      <c r="C42" t="s" s="297">
+      <c r="C42" t="s" s="354">
         <v>238</v>
       </c>
-      <c r="D42" s="283"/>
+      <c r="D42" s="353"/>
       <c r="E42" s="284"/>
       <c r="F42" t="str" s="285" cm="1">
         <f t="array" ref="F42">IF($AD42="","",$H42-$G42)</f>
@@ -42373,10 +42394,10 @@
         <v>36</v>
       </c>
       <c r="B43" s="282"/>
-      <c r="C43" t="s" s="297">
+      <c r="C43" t="s" s="354">
         <v>222</v>
       </c>
-      <c r="D43" s="283"/>
+      <c r="D43" s="353"/>
       <c r="E43" s="284"/>
       <c r="F43" t="str" s="285" cm="1">
         <f t="array" ref="F43">IF($AD43="","",$H43-$G43)</f>
@@ -42430,10 +42451,10 @@
         <v>37</v>
       </c>
       <c r="B44" s="282"/>
-      <c r="C44" t="s" s="297">
+      <c r="C44" t="s" s="354">
         <v>239</v>
       </c>
-      <c r="D44" s="283"/>
+      <c r="D44" s="353"/>
       <c r="E44" s="284"/>
       <c r="F44" t="str" s="285" cm="1">
         <f t="array" ref="F44">IF($AD44="","",$H44-$G44)</f>
@@ -42487,10 +42508,10 @@
         <v>38</v>
       </c>
       <c r="B45" s="282"/>
-      <c r="C45" t="s" s="297">
+      <c r="C45" t="s" s="354">
         <v>219</v>
       </c>
-      <c r="D45" s="283"/>
+      <c r="D45" s="353"/>
       <c r="E45" s="284"/>
       <c r="F45" t="str" s="285" cm="1">
         <f t="array" ref="F45">IF($AD45="","",$H45-$G45)</f>
@@ -42544,8 +42565,8 @@
         <v>39</v>
       </c>
       <c r="B46" s="282"/>
-      <c r="C46" s="283"/>
-      <c r="D46" s="283"/>
+      <c r="C46" s="353"/>
+      <c r="D46" s="353"/>
       <c r="E46" s="284"/>
       <c r="F46" t="str" s="285" cm="1">
         <f t="array" ref="F46">IF($AD46="","",$H46-$G46)</f>
@@ -42599,8 +42620,8 @@
         <v>40</v>
       </c>
       <c r="B47" s="282"/>
-      <c r="C47" s="283"/>
-      <c r="D47" s="283"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
       <c r="E47" s="284"/>
       <c r="F47" t="str" s="285" cm="1">
         <f t="array" ref="F47">IF($AD47="","",$H47-$G47)</f>
@@ -42654,8 +42675,8 @@
         <v>41</v>
       </c>
       <c r="B48" s="282"/>
-      <c r="C48" s="283"/>
-      <c r="D48" s="283"/>
+      <c r="C48" s="353"/>
+      <c r="D48" s="353"/>
       <c r="E48" s="284"/>
       <c r="F48" t="str" s="285" cm="1">
         <f t="array" ref="F48">IF($AD48="","",$H48-$G48)</f>
@@ -42709,8 +42730,8 @@
         <v>42</v>
       </c>
       <c r="B49" s="282"/>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
+      <c r="C49" s="353"/>
+      <c r="D49" s="353"/>
       <c r="E49" s="284"/>
       <c r="F49" t="str" s="285" cm="1">
         <f t="array" ref="F49">IF($AD49="","",$H49-$G49)</f>
@@ -42764,8 +42785,8 @@
         <v>43</v>
       </c>
       <c r="B50" s="282"/>
-      <c r="C50" s="283"/>
-      <c r="D50" s="283"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
       <c r="E50" s="284"/>
       <c r="F50" t="str" s="285" cm="1">
         <f t="array" ref="F50">IF($AD50="","",$H50-$G50)</f>
@@ -42819,10 +42840,10 @@
         <v>44</v>
       </c>
       <c r="B51" s="282"/>
-      <c r="C51" t="s" s="297">
+      <c r="C51" t="s" s="354">
         <v>240</v>
       </c>
-      <c r="D51" s="283"/>
+      <c r="D51" s="353"/>
       <c r="E51" s="284"/>
       <c r="F51" t="str" s="285" cm="1">
         <f t="array" ref="F51">IF($AD51="","",$H51-$G51)</f>
@@ -42876,10 +42897,10 @@
         <v>45</v>
       </c>
       <c r="B52" s="282"/>
-      <c r="C52" t="s" s="297">
+      <c r="C52" t="s" s="354">
         <v>241</v>
       </c>
-      <c r="D52" s="283"/>
+      <c r="D52" s="353"/>
       <c r="E52" s="284"/>
       <c r="F52" t="str" s="285" cm="1">
         <f t="array" ref="F52">IF($AD52="","",$H52-$G52)</f>
@@ -42933,10 +42954,10 @@
         <v>46</v>
       </c>
       <c r="B53" s="282"/>
-      <c r="C53" t="s" s="297">
+      <c r="C53" t="s" s="354">
         <v>242</v>
       </c>
-      <c r="D53" s="283"/>
+      <c r="D53" s="353"/>
       <c r="E53" s="284"/>
       <c r="F53" t="str" s="285" cm="1">
         <f t="array" ref="F53">IF($AD53="","",$H53-$G53)</f>
@@ -42990,10 +43011,10 @@
         <v>47</v>
       </c>
       <c r="B54" s="282"/>
-      <c r="C54" t="s" s="297">
+      <c r="C54" t="s" s="354">
         <v>243</v>
       </c>
-      <c r="D54" s="283"/>
+      <c r="D54" s="353"/>
       <c r="E54" s="284"/>
       <c r="F54" t="str" s="285" cm="1">
         <f t="array" ref="F54">IF($AD54="","",$H54-$G54)</f>
@@ -43047,10 +43068,10 @@
         <v>48</v>
       </c>
       <c r="B55" s="282"/>
-      <c r="C55" t="s" s="297">
+      <c r="C55" t="s" s="354">
         <v>244</v>
       </c>
-      <c r="D55" s="283"/>
+      <c r="D55" s="353"/>
       <c r="E55" s="284"/>
       <c r="F55" t="str" s="285" cm="1">
         <f t="array" ref="F55">IF($AD55="","",$H55-$G55)</f>
@@ -43104,10 +43125,10 @@
         <v>49</v>
       </c>
       <c r="B56" s="282"/>
-      <c r="C56" t="s" s="297">
+      <c r="C56" t="s" s="354">
         <v>245</v>
       </c>
-      <c r="D56" s="283"/>
+      <c r="D56" s="353"/>
       <c r="E56" s="284"/>
       <c r="F56" t="str" s="285" cm="1">
         <f t="array" ref="F56">IF($AD56="","",$H56-$G56)</f>
@@ -43161,10 +43182,10 @@
         <v>50</v>
       </c>
       <c r="B57" s="282"/>
-      <c r="C57" t="s" s="297">
+      <c r="C57" t="s" s="354">
         <v>246</v>
       </c>
-      <c r="D57" s="283"/>
+      <c r="D57" s="353"/>
       <c r="E57" s="284"/>
       <c r="F57" t="str" s="285" cm="1">
         <f t="array" ref="F57">IF($AD57="","",$H57-$G57)</f>
@@ -43218,10 +43239,10 @@
         <v>51</v>
       </c>
       <c r="B58" s="282"/>
-      <c r="C58" t="s" s="297">
+      <c r="C58" t="s" s="354">
         <v>247</v>
       </c>
-      <c r="D58" s="283"/>
+      <c r="D58" s="353"/>
       <c r="E58" s="284"/>
       <c r="F58" t="str" s="285" cm="1">
         <f t="array" ref="F58">IF($AD58="","",$H58-$G58)</f>
@@ -43275,10 +43296,10 @@
         <v>52</v>
       </c>
       <c r="B59" s="282"/>
-      <c r="C59" t="s" s="297">
+      <c r="C59" t="s" s="354">
         <v>248</v>
       </c>
-      <c r="D59" s="283"/>
+      <c r="D59" s="353"/>
       <c r="E59" s="284"/>
       <c r="F59" t="str" s="285" cm="1">
         <f t="array" ref="F59">IF($AD59="","",$H59-$G59)</f>
@@ -43332,10 +43353,10 @@
         <v>53</v>
       </c>
       <c r="B60" s="282"/>
-      <c r="C60" t="s" s="297">
+      <c r="C60" t="s" s="354">
         <v>249</v>
       </c>
-      <c r="D60" s="283"/>
+      <c r="D60" s="353"/>
       <c r="E60" s="284"/>
       <c r="F60" t="str" s="285" cm="1">
         <f t="array" ref="F60">IF($AD60="","",$H60-$G60)</f>
@@ -43389,10 +43410,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="282"/>
-      <c r="C61" t="s" s="297">
+      <c r="C61" t="s" s="354">
         <v>250</v>
       </c>
-      <c r="D61" s="283"/>
+      <c r="D61" s="353"/>
       <c r="E61" s="284"/>
       <c r="F61" t="str" s="285" cm="1">
         <f t="array" ref="F61">IF($AD61="","",$H61-$G61)</f>
@@ -43446,10 +43467,10 @@
         <v>55</v>
       </c>
       <c r="B62" s="282"/>
-      <c r="C62" t="s" s="297">
+      <c r="C62" t="s" s="354">
         <v>251</v>
       </c>
-      <c r="D62" s="283"/>
+      <c r="D62" s="353"/>
       <c r="E62" s="284"/>
       <c r="F62" t="str" s="285" cm="1">
         <f t="array" ref="F62">IF($AD62="","",$H62-$G62)</f>
@@ -43503,10 +43524,10 @@
         <v>56</v>
       </c>
       <c r="B63" s="282"/>
-      <c r="C63" t="s" s="297">
+      <c r="C63" t="s" s="354">
         <v>252</v>
       </c>
-      <c r="D63" s="283"/>
+      <c r="D63" s="353"/>
       <c r="E63" s="284"/>
       <c r="F63" t="str" s="285" cm="1">
         <f t="array" ref="F63">IF($AD63="","",$H63-$G63)</f>
@@ -43560,10 +43581,10 @@
         <v>57</v>
       </c>
       <c r="B64" s="282"/>
-      <c r="C64" t="s" s="297">
+      <c r="C64" t="s" s="354">
         <v>253</v>
       </c>
-      <c r="D64" s="283"/>
+      <c r="D64" s="353"/>
       <c r="E64" s="284"/>
       <c r="F64" t="str" s="285" cm="1">
         <f t="array" ref="F64">IF($AD64="","",$H64-$G64)</f>
@@ -43617,8 +43638,8 @@
         <v>58</v>
       </c>
       <c r="B65" s="282"/>
-      <c r="C65" s="283"/>
-      <c r="D65" s="283"/>
+      <c r="C65" s="353"/>
+      <c r="D65" s="353"/>
       <c r="E65" s="284"/>
       <c r="F65" t="str" s="285" cm="1">
         <f t="array" ref="F65">IF($AD65="","",$H65-$G65)</f>
@@ -43672,8 +43693,8 @@
         <v>59</v>
       </c>
       <c r="B66" s="282"/>
-      <c r="C66" s="283"/>
-      <c r="D66" s="283"/>
+      <c r="C66" s="353"/>
+      <c r="D66" s="353"/>
       <c r="E66" s="284"/>
       <c r="F66" t="str" s="285" cm="1">
         <f t="array" ref="F66">IF($AD66="","",$H66-$G66)</f>
@@ -43727,8 +43748,8 @@
         <v>60</v>
       </c>
       <c r="B67" s="282"/>
-      <c r="C67" s="283"/>
-      <c r="D67" s="283"/>
+      <c r="C67" s="353"/>
+      <c r="D67" s="353"/>
       <c r="E67" s="284"/>
       <c r="F67" t="str" s="285" cm="1">
         <f t="array" ref="F67">IF($AD67="","",$H67-$G67)</f>
@@ -43782,8 +43803,8 @@
         <v>61</v>
       </c>
       <c r="B68" s="282"/>
-      <c r="C68" s="283"/>
-      <c r="D68" s="283"/>
+      <c r="C68" s="353"/>
+      <c r="D68" s="353"/>
       <c r="E68" s="284"/>
       <c r="F68" t="str" s="285" cm="1">
         <f t="array" ref="F68">IF($AD68="","",$H68-$G68)</f>
@@ -43837,8 +43858,8 @@
         <v>62</v>
       </c>
       <c r="B69" s="282"/>
-      <c r="C69" s="283"/>
-      <c r="D69" s="283"/>
+      <c r="C69" s="353"/>
+      <c r="D69" s="353"/>
       <c r="E69" s="284"/>
       <c r="F69" t="str" s="285" cm="1">
         <f t="array" ref="F69">IF($AD69="","",$H69-$G69)</f>
@@ -43892,8 +43913,8 @@
         <v>63</v>
       </c>
       <c r="B70" s="282"/>
-      <c r="C70" s="283"/>
-      <c r="D70" s="283"/>
+      <c r="C70" s="353"/>
+      <c r="D70" s="353"/>
       <c r="E70" s="284"/>
       <c r="F70" t="str" s="285" cm="1">
         <f t="array" ref="F70">IF($AD70="","",$H70-$G70)</f>
@@ -43947,10 +43968,10 @@
         <v>64</v>
       </c>
       <c r="B71" s="282"/>
-      <c r="C71" t="s" s="297">
+      <c r="C71" t="s" s="354">
         <v>254</v>
       </c>
-      <c r="D71" s="283"/>
+      <c r="D71" s="353"/>
       <c r="E71" s="284"/>
       <c r="F71" t="str" s="285" cm="1">
         <f t="array" ref="F71">IF($AD71="","",$H71-$G71)</f>
@@ -44004,10 +44025,10 @@
         <v>65</v>
       </c>
       <c r="B72" s="282"/>
-      <c r="C72" t="s" s="297">
+      <c r="C72" t="s" s="354">
         <v>255</v>
       </c>
-      <c r="D72" s="283"/>
+      <c r="D72" s="353"/>
       <c r="E72" s="284"/>
       <c r="F72" t="str" s="285" cm="1">
         <f t="array" ref="F72">IF($AD72="","",$H72-$G72)</f>
@@ -44061,10 +44082,10 @@
         <v>66</v>
       </c>
       <c r="B73" s="282"/>
-      <c r="C73" t="s" s="297">
+      <c r="C73" t="s" s="354">
         <v>256</v>
       </c>
-      <c r="D73" s="283"/>
+      <c r="D73" s="353"/>
       <c r="E73" s="284"/>
       <c r="F73" t="str" s="285" cm="1">
         <f t="array" ref="F73">IF($AD73="","",$H73-$G73)</f>
@@ -44118,8 +44139,8 @@
         <v>67</v>
       </c>
       <c r="B74" s="282"/>
-      <c r="C74" s="283"/>
-      <c r="D74" s="283"/>
+      <c r="C74" s="353"/>
+      <c r="D74" s="353"/>
       <c r="E74" s="284"/>
       <c r="F74" t="str" s="285" cm="1">
         <f t="array" ref="F74">IF($AD74="","",$H74-$G74)</f>
@@ -44173,8 +44194,8 @@
         <v>68</v>
       </c>
       <c r="B75" s="282"/>
-      <c r="C75" s="283"/>
-      <c r="D75" s="283"/>
+      <c r="C75" s="353"/>
+      <c r="D75" s="353"/>
       <c r="E75" s="284"/>
       <c r="F75" t="str" s="285" cm="1">
         <f t="array" ref="F75">IF($AD75="","",$H75-$G75)</f>
@@ -44228,8 +44249,8 @@
         <v>69</v>
       </c>
       <c r="B76" s="282"/>
-      <c r="C76" s="283"/>
-      <c r="D76" s="283"/>
+      <c r="C76" s="353"/>
+      <c r="D76" s="353"/>
       <c r="E76" s="284"/>
       <c r="F76" t="str" s="285" cm="1">
         <f t="array" ref="F76">IF($AD76="","",$H76-$G76)</f>
@@ -44283,8 +44304,8 @@
         <v>70</v>
       </c>
       <c r="B77" s="282"/>
-      <c r="C77" s="283"/>
-      <c r="D77" s="283"/>
+      <c r="C77" s="353"/>
+      <c r="D77" s="353"/>
       <c r="E77" s="284"/>
       <c r="F77" t="str" s="285" cm="1">
         <f t="array" ref="F77">IF($AD77="","",$H77-$G77)</f>
@@ -44338,8 +44359,8 @@
         <v>71</v>
       </c>
       <c r="B78" s="282"/>
-      <c r="C78" s="283"/>
-      <c r="D78" s="283"/>
+      <c r="C78" s="353"/>
+      <c r="D78" s="353"/>
       <c r="E78" s="284"/>
       <c r="F78" t="str" s="285" cm="1">
         <f t="array" ref="F78">IF($AD78="","",$H78-$G78)</f>
@@ -44393,8 +44414,8 @@
         <v>72</v>
       </c>
       <c r="B79" s="282"/>
-      <c r="C79" s="283"/>
-      <c r="D79" s="283"/>
+      <c r="C79" s="353"/>
+      <c r="D79" s="353"/>
       <c r="E79" s="284"/>
       <c r="F79" t="str" s="285" cm="1">
         <f t="array" ref="F79">IF($AD79="","",$H79-$G79)</f>
@@ -44448,8 +44469,8 @@
         <v>73</v>
       </c>
       <c r="B80" s="282"/>
-      <c r="C80" s="283"/>
-      <c r="D80" s="283"/>
+      <c r="C80" s="353"/>
+      <c r="D80" s="353"/>
       <c r="E80" s="284"/>
       <c r="F80" t="str" s="285" cm="1">
         <f t="array" ref="F80">IF($AD80="","",$H80-$G80)</f>
@@ -44503,10 +44524,10 @@
         <v>74</v>
       </c>
       <c r="B81" s="282"/>
-      <c r="C81" t="s" s="297">
+      <c r="C81" t="s" s="354">
         <v>257</v>
       </c>
-      <c r="D81" s="283"/>
+      <c r="D81" s="353"/>
       <c r="E81" s="284"/>
       <c r="F81" t="str" s="285" cm="1">
         <f t="array" ref="F81">IF($AD81="","",$H81-$G81)</f>
@@ -44560,10 +44581,10 @@
         <v>75</v>
       </c>
       <c r="B82" s="282"/>
-      <c r="C82" t="s" s="297">
+      <c r="C82" t="s" s="354">
         <v>258</v>
       </c>
-      <c r="D82" s="283"/>
+      <c r="D82" s="353"/>
       <c r="E82" s="284"/>
       <c r="F82" t="str" s="285" cm="1">
         <f t="array" ref="F82">IF($AD82="","",$H82-$G82)</f>
@@ -44617,10 +44638,10 @@
         <v>76</v>
       </c>
       <c r="B83" s="282"/>
-      <c r="C83" t="s" s="297">
+      <c r="C83" t="s" s="354">
         <v>259</v>
       </c>
-      <c r="D83" s="283"/>
+      <c r="D83" s="353"/>
       <c r="E83" s="284"/>
       <c r="F83" t="str" s="285" cm="1">
         <f t="array" ref="F83">IF($AD83="","",$H83-$G83)</f>
@@ -44674,10 +44695,10 @@
         <v>77</v>
       </c>
       <c r="B84" s="282"/>
-      <c r="C84" t="s" s="297">
+      <c r="C84" t="s" s="354">
         <v>260</v>
       </c>
-      <c r="D84" s="283"/>
+      <c r="D84" s="353"/>
       <c r="E84" s="284"/>
       <c r="F84" t="str" s="285" cm="1">
         <f t="array" ref="F84">IF($AD84="","",$H84-$G84)</f>
@@ -44731,10 +44752,10 @@
         <v>78</v>
       </c>
       <c r="B85" s="282"/>
-      <c r="C85" t="s" s="297">
+      <c r="C85" t="s" s="354">
         <v>261</v>
       </c>
-      <c r="D85" s="283"/>
+      <c r="D85" s="353"/>
       <c r="E85" s="284"/>
       <c r="F85" t="str" s="285" cm="1">
         <f t="array" ref="F85">IF($AD85="","",$H85-$G85)</f>
@@ -44788,10 +44809,10 @@
         <v>79</v>
       </c>
       <c r="B86" s="282"/>
-      <c r="C86" t="s" s="297">
+      <c r="C86" t="s" s="354">
         <v>262</v>
       </c>
-      <c r="D86" s="283"/>
+      <c r="D86" s="353"/>
       <c r="E86" s="284"/>
       <c r="F86" t="str" s="285" cm="1">
         <f t="array" ref="F86">IF($AD86="","",$H86-$G86)</f>
@@ -44845,10 +44866,10 @@
         <v>80</v>
       </c>
       <c r="B87" s="282"/>
-      <c r="C87" t="s" s="297">
+      <c r="C87" t="s" s="354">
         <v>263</v>
       </c>
-      <c r="D87" s="283"/>
+      <c r="D87" s="353"/>
       <c r="E87" s="284"/>
       <c r="F87" t="str" s="285" cm="1">
         <f t="array" ref="F87">IF($AD87="","",$H87-$G87)</f>
@@ -44902,10 +44923,10 @@
         <v>81</v>
       </c>
       <c r="B88" s="282"/>
-      <c r="C88" t="s" s="297">
+      <c r="C88" t="s" s="354">
         <v>264</v>
       </c>
-      <c r="D88" s="283"/>
+      <c r="D88" s="353"/>
       <c r="E88" s="284"/>
       <c r="F88" t="str" s="285" cm="1">
         <f t="array" ref="F88">IF($AD88="","",$H88-$G88)</f>
@@ -44959,10 +44980,10 @@
         <v>82</v>
       </c>
       <c r="B89" s="282"/>
-      <c r="C89" t="s" s="297">
+      <c r="C89" t="s" s="354">
         <v>265</v>
       </c>
-      <c r="D89" s="283"/>
+      <c r="D89" s="353"/>
       <c r="E89" s="284"/>
       <c r="F89" t="str" s="285" cm="1">
         <f t="array" ref="F89">IF($AD89="","",$H89-$G89)</f>
@@ -45016,10 +45037,10 @@
         <v>83</v>
       </c>
       <c r="B90" s="282"/>
-      <c r="C90" t="s" s="297">
+      <c r="C90" t="s" s="354">
         <v>266</v>
       </c>
-      <c r="D90" s="283"/>
+      <c r="D90" s="353"/>
       <c r="E90" s="284"/>
       <c r="F90" t="str" s="285" cm="1">
         <f t="array" ref="F90">IF($AD90="","",$H90-$G90)</f>
@@ -45073,10 +45094,10 @@
         <v>84</v>
       </c>
       <c r="B91" s="282"/>
-      <c r="C91" t="s" s="297">
+      <c r="C91" t="s" s="354">
         <v>234</v>
       </c>
-      <c r="D91" s="283"/>
+      <c r="D91" s="353"/>
       <c r="E91" s="284"/>
       <c r="F91" t="str" s="285" cm="1">
         <f t="array" ref="F91">IF($AD91="","",$H91-$G91)</f>
@@ -45130,10 +45151,10 @@
         <v>85</v>
       </c>
       <c r="B92" s="282"/>
-      <c r="C92" t="s" s="297">
+      <c r="C92" t="s" s="354">
         <v>267</v>
       </c>
-      <c r="D92" s="283"/>
+      <c r="D92" s="353"/>
       <c r="E92" s="284"/>
       <c r="F92" t="str" s="285" cm="1">
         <f t="array" ref="F92">IF($AD92="","",$H92-$G92)</f>
@@ -45187,10 +45208,10 @@
         <v>86</v>
       </c>
       <c r="B93" s="282"/>
-      <c r="C93" t="s" s="297">
+      <c r="C93" t="s" s="354">
         <v>268</v>
       </c>
-      <c r="D93" s="283"/>
+      <c r="D93" s="353"/>
       <c r="E93" s="284"/>
       <c r="F93" t="str" s="285" cm="1">
         <f t="array" ref="F93">IF($AD93="","",$H93-$G93)</f>
@@ -45244,10 +45265,10 @@
         <v>87</v>
       </c>
       <c r="B94" s="282"/>
-      <c r="C94" t="s" s="297">
+      <c r="C94" t="s" s="354">
         <v>269</v>
       </c>
-      <c r="D94" s="283"/>
+      <c r="D94" s="353"/>
       <c r="E94" s="284"/>
       <c r="F94" t="str" s="285" cm="1">
         <f t="array" ref="F94">IF($AD94="","",$H94-$G94)</f>
@@ -45301,10 +45322,10 @@
         <v>88</v>
       </c>
       <c r="B95" s="282"/>
-      <c r="C95" t="s" s="297">
+      <c r="C95" t="s" s="354">
         <v>270</v>
       </c>
-      <c r="D95" s="283"/>
+      <c r="D95" s="353"/>
       <c r="E95" s="284"/>
       <c r="F95" t="str" s="285" cm="1">
         <f t="array" ref="F95">IF($AD95="","",$H95-$G95)</f>
@@ -45360,10 +45381,10 @@
         <v>89</v>
       </c>
       <c r="B96" s="282"/>
-      <c r="C96" t="s" s="297">
+      <c r="C96" t="s" s="354">
         <v>212</v>
       </c>
-      <c r="D96" s="283"/>
+      <c r="D96" s="353"/>
       <c r="E96" s="284"/>
       <c r="F96" t="str" s="285" cm="1">
         <f t="array" ref="F96">IF($AD96="","",$H96-$G96)</f>
@@ -45417,10 +45438,10 @@
         <v>90</v>
       </c>
       <c r="B97" s="282"/>
-      <c r="C97" t="s" s="297">
+      <c r="C97" t="s" s="354">
         <v>215</v>
       </c>
-      <c r="D97" s="283"/>
+      <c r="D97" s="353"/>
       <c r="E97" s="284"/>
       <c r="F97" t="str" s="285" cm="1">
         <f t="array" ref="F97">IF($AD97="","",$H97-$G97)</f>
@@ -45474,10 +45495,10 @@
         <v>91</v>
       </c>
       <c r="B98" s="282"/>
-      <c r="C98" t="s" s="297">
+      <c r="C98" t="s" s="354">
         <v>272</v>
       </c>
-      <c r="D98" s="283"/>
+      <c r="D98" s="353"/>
       <c r="E98" s="284"/>
       <c r="F98" t="str" s="285" cm="1">
         <f t="array" ref="F98">IF($AD98="","",$H98-$G98)</f>
@@ -45531,10 +45552,10 @@
         <v>92</v>
       </c>
       <c r="B99" s="282"/>
-      <c r="C99" t="s" s="297">
+      <c r="C99" t="s" s="354">
         <v>273</v>
       </c>
-      <c r="D99" s="283"/>
+      <c r="D99" s="353"/>
       <c r="E99" s="284"/>
       <c r="F99" t="str" s="285" cm="1">
         <f t="array" ref="F99">IF($AD99="","",$H99-$G99)</f>
@@ -45588,10 +45609,10 @@
         <v>93</v>
       </c>
       <c r="B100" s="282"/>
-      <c r="C100" t="s" s="297">
+      <c r="C100" t="s" s="354">
         <v>179</v>
       </c>
-      <c r="D100" s="283"/>
+      <c r="D100" s="353"/>
       <c r="E100" s="284"/>
       <c r="F100" t="str" s="285" cm="1">
         <f t="array" ref="F100">IF($AD100="","",$H100-$G100)</f>
@@ -45642,8 +45663,8 @@
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="282"/>
       <c r="B101" s="282"/>
-      <c r="C101" s="283"/>
-      <c r="D101" s="283"/>
+      <c r="C101" s="353"/>
+      <c r="D101" s="353"/>
       <c r="E101" s="284"/>
       <c r="F101" t="str" s="285" cm="1">
         <f t="array" ref="F101">IF($AD101="","",$H101-$G101)</f>
@@ -45694,8 +45715,8 @@
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="282"/>
       <c r="B102" s="282"/>
-      <c r="C102" s="283"/>
-      <c r="D102" s="283"/>
+      <c r="C102" s="353"/>
+      <c r="D102" s="353"/>
       <c r="E102" s="284"/>
       <c r="F102" t="str" s="285" cm="1">
         <f t="array" ref="F102">IF($AD102="","",$H102-$G102)</f>
@@ -45746,8 +45767,8 @@
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="282"/>
       <c r="B103" s="282"/>
-      <c r="C103" s="283"/>
-      <c r="D103" s="283"/>
+      <c r="C103" s="353"/>
+      <c r="D103" s="353"/>
       <c r="E103" s="284"/>
       <c r="F103" t="str" s="285" cm="1">
         <f t="array" ref="F103">IF($AD103="","",$H103-$G103)</f>
@@ -45798,8 +45819,8 @@
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="282"/>
       <c r="B104" s="282"/>
-      <c r="C104" s="283"/>
-      <c r="D104" s="283"/>
+      <c r="C104" s="353"/>
+      <c r="D104" s="353"/>
       <c r="E104" s="284"/>
       <c r="F104" t="str" s="285" cm="1">
         <f t="array" ref="F104">IF($AD104="","",$H104-$G104)</f>
@@ -45850,8 +45871,8 @@
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="282"/>
       <c r="B105" s="282"/>
-      <c r="C105" s="283"/>
-      <c r="D105" s="283"/>
+      <c r="C105" s="353"/>
+      <c r="D105" s="353"/>
       <c r="E105" s="284"/>
       <c r="F105" t="str" s="285" cm="1">
         <f t="array" ref="F105">IF($AD105="","",$H105-$G105)</f>
@@ -45902,8 +45923,8 @@
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="282"/>
       <c r="B106" s="282"/>
-      <c r="C106" s="283"/>
-      <c r="D106" s="283"/>
+      <c r="C106" s="353"/>
+      <c r="D106" s="353"/>
       <c r="E106" s="284"/>
       <c r="F106" t="str" s="285" cm="1">
         <f t="array" ref="F106">IF($AD106="","",$H106-$G106)</f>
@@ -45954,8 +45975,8 @@
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="282"/>
       <c r="B107" s="282"/>
-      <c r="C107" s="283"/>
-      <c r="D107" s="283"/>
+      <c r="C107" s="353"/>
+      <c r="D107" s="353"/>
       <c r="E107" s="284"/>
       <c r="F107" t="str" s="285" cm="1">
         <f t="array" ref="F107">IF($AD107="","",$H107-$G107)</f>
@@ -46006,8 +46027,8 @@
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="282"/>
       <c r="B108" s="282"/>
-      <c r="C108" s="283"/>
-      <c r="D108" s="283"/>
+      <c r="C108" s="353"/>
+      <c r="D108" s="353"/>
       <c r="E108" s="284"/>
       <c r="F108" t="str" s="285" cm="1">
         <f t="array" ref="F108">IF($AD108="","",$H108-$G108)</f>
@@ -46058,8 +46079,8 @@
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="282"/>
       <c r="B109" s="282"/>
-      <c r="C109" s="283"/>
-      <c r="D109" s="283"/>
+      <c r="C109" s="353"/>
+      <c r="D109" s="353"/>
       <c r="E109" s="284"/>
       <c r="F109" t="str" s="285" cm="1">
         <f t="array" ref="F109">IF($AD109="","",$H109-$G109)</f>
@@ -46110,8 +46131,8 @@
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="282"/>
       <c r="B110" s="282"/>
-      <c r="C110" s="283"/>
-      <c r="D110" s="283"/>
+      <c r="C110" s="353"/>
+      <c r="D110" s="353"/>
       <c r="E110" s="284"/>
       <c r="F110" t="str" s="285" cm="1">
         <f t="array" ref="F110">IF($AD110="","",$H110-$G110)</f>
@@ -46162,8 +46183,8 @@
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="282"/>
       <c r="B111" s="282"/>
-      <c r="C111" s="283"/>
-      <c r="D111" s="283"/>
+      <c r="C111" s="353"/>
+      <c r="D111" s="353"/>
       <c r="E111" s="284"/>
       <c r="F111" t="str" s="285" cm="1">
         <f t="array" ref="F111">IF($AD111="","",$H111-$G111)</f>
@@ -46214,8 +46235,8 @@
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="282"/>
       <c r="B112" s="282"/>
-      <c r="C112" s="283"/>
-      <c r="D112" s="283"/>
+      <c r="C112" s="353"/>
+      <c r="D112" s="353"/>
       <c r="E112" s="284"/>
       <c r="F112" t="str" s="285" cm="1">
         <f t="array" ref="F112">IF($AD112="","",$H112-$G112)</f>
@@ -46266,8 +46287,8 @@
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="282"/>
       <c r="B113" s="282"/>
-      <c r="C113" s="283"/>
-      <c r="D113" s="283"/>
+      <c r="C113" s="353"/>
+      <c r="D113" s="353"/>
       <c r="E113" s="284"/>
       <c r="F113" t="str" s="285" cm="1">
         <f t="array" ref="F113">IF($AD113="","",$H113-$G113)</f>
@@ -46318,8 +46339,8 @@
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="282"/>
       <c r="B114" s="282"/>
-      <c r="C114" s="283"/>
-      <c r="D114" s="283"/>
+      <c r="C114" s="353"/>
+      <c r="D114" s="353"/>
       <c r="E114" s="284"/>
       <c r="F114" t="str" s="285" cm="1">
         <f t="array" ref="F114">IF($AD114="","",$H114-$G114)</f>
@@ -46370,8 +46391,8 @@
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="282"/>
       <c r="B115" s="282"/>
-      <c r="C115" s="283"/>
-      <c r="D115" s="283"/>
+      <c r="C115" s="353"/>
+      <c r="D115" s="353"/>
       <c r="E115" s="284"/>
       <c r="F115" t="str" s="285" cm="1">
         <f t="array" ref="F115">IF($AD115="","",$H115-$G115)</f>
@@ -46422,8 +46443,8 @@
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="282"/>
       <c r="B116" s="282"/>
-      <c r="C116" s="283"/>
-      <c r="D116" s="283"/>
+      <c r="C116" s="353"/>
+      <c r="D116" s="353"/>
       <c r="E116" s="284"/>
       <c r="F116" t="str" s="285" cm="1">
         <f t="array" ref="F116">IF($AD116="","",$H116-$G116)</f>
@@ -46474,8 +46495,8 @@
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="282"/>
       <c r="B117" s="282"/>
-      <c r="C117" s="283"/>
-      <c r="D117" s="283"/>
+      <c r="C117" s="353"/>
+      <c r="D117" s="353"/>
       <c r="E117" s="284"/>
       <c r="F117" t="str" s="285" cm="1">
         <f t="array" ref="F117">IF($AD117="","",$H117-$G117)</f>
@@ -46526,8 +46547,8 @@
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="282"/>
       <c r="B118" s="282"/>
-      <c r="C118" s="283"/>
-      <c r="D118" s="283"/>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
       <c r="E118" s="284"/>
       <c r="F118" t="str" s="285" cm="1">
         <f t="array" ref="F118">IF($AD118="","",$H118-$G118)</f>
@@ -46578,8 +46599,8 @@
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="282"/>
       <c r="B119" s="282"/>
-      <c r="C119" s="283"/>
-      <c r="D119" s="283"/>
+      <c r="C119" s="353"/>
+      <c r="D119" s="353"/>
       <c r="E119" s="284"/>
       <c r="F119" t="str" s="285" cm="1">
         <f t="array" ref="F119">IF($AD119="","",$H119-$G119)</f>
@@ -46630,8 +46651,8 @@
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="282"/>
       <c r="B120" s="282"/>
-      <c r="C120" s="283"/>
-      <c r="D120" s="283"/>
+      <c r="C120" s="353"/>
+      <c r="D120" s="353"/>
       <c r="E120" s="284"/>
       <c r="F120" t="str" s="285" cm="1">
         <f t="array" ref="F120">IF($AD120="","",$H120-$G120)</f>
@@ -46682,8 +46703,8 @@
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="282"/>
       <c r="B121" s="282"/>
-      <c r="C121" s="283"/>
-      <c r="D121" s="283"/>
+      <c r="C121" s="353"/>
+      <c r="D121" s="353"/>
       <c r="E121" s="284"/>
       <c r="F121" t="str" s="285" cm="1">
         <f t="array" ref="F121">IF($AD121="","",$H121-$G121)</f>
@@ -46734,8 +46755,8 @@
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="282"/>
       <c r="B122" s="282"/>
-      <c r="C122" s="283"/>
-      <c r="D122" s="283"/>
+      <c r="C122" s="353"/>
+      <c r="D122" s="353"/>
       <c r="E122" s="284"/>
       <c r="F122" t="str" s="285" cm="1">
         <f t="array" ref="F122">IF($AD122="","",$H122-$G122)</f>
@@ -46786,8 +46807,8 @@
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="282"/>
       <c r="B123" s="282"/>
-      <c r="C123" s="283"/>
-      <c r="D123" s="283"/>
+      <c r="C123" s="353"/>
+      <c r="D123" s="353"/>
       <c r="E123" s="284"/>
       <c r="F123" t="str" s="285" cm="1">
         <f t="array" ref="F123">IF($AD123="","",$H123-$G123)</f>
@@ -46838,8 +46859,8 @@
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="282"/>
       <c r="B124" s="282"/>
-      <c r="C124" s="283"/>
-      <c r="D124" s="283"/>
+      <c r="C124" s="353"/>
+      <c r="D124" s="353"/>
       <c r="E124" s="284"/>
       <c r="F124" t="str" s="285" cm="1">
         <f t="array" ref="F124">IF($AD124="","",$H124-$G124)</f>
@@ -46890,8 +46911,8 @@
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="282"/>
       <c r="B125" s="282"/>
-      <c r="C125" s="283"/>
-      <c r="D125" s="283"/>
+      <c r="C125" s="353"/>
+      <c r="D125" s="353"/>
       <c r="E125" s="284"/>
       <c r="F125" t="str" s="285" cm="1">
         <f t="array" ref="F125">IF($AD125="","",$H125-$G125)</f>
@@ -46942,8 +46963,8 @@
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="282"/>
       <c r="B126" s="282"/>
-      <c r="C126" s="283"/>
-      <c r="D126" s="283"/>
+      <c r="C126" s="353"/>
+      <c r="D126" s="353"/>
       <c r="E126" s="284"/>
       <c r="F126" t="str" s="285" cm="1">
         <f t="array" ref="F126">IF($AD126="","",$H126-$G126)</f>
@@ -46994,8 +47015,8 @@
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="282"/>
       <c r="B127" s="282"/>
-      <c r="C127" s="283"/>
-      <c r="D127" s="283"/>
+      <c r="C127" s="353"/>
+      <c r="D127" s="353"/>
       <c r="E127" s="284"/>
       <c r="F127" t="str" s="285" cm="1">
         <f t="array" ref="F127">IF($AD127="","",$H127-$G127)</f>
@@ -47046,8 +47067,8 @@
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="282"/>
       <c r="B128" s="282"/>
-      <c r="C128" s="283"/>
-      <c r="D128" s="283"/>
+      <c r="C128" s="353"/>
+      <c r="D128" s="353"/>
       <c r="E128" s="284"/>
       <c r="F128" t="str" s="285" cm="1">
         <f t="array" ref="F128">IF($AD128="","",$H128-$G128)</f>
@@ -47098,8 +47119,8 @@
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="282"/>
       <c r="B129" s="282"/>
-      <c r="C129" s="283"/>
-      <c r="D129" s="283"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
       <c r="E129" s="284"/>
       <c r="F129" t="str" s="285" cm="1">
         <f t="array" ref="F129">IF($AD129="","",$H129-$G129)</f>
@@ -47150,8 +47171,8 @@
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="282"/>
       <c r="B130" s="282"/>
-      <c r="C130" s="283"/>
-      <c r="D130" s="283"/>
+      <c r="C130" s="353"/>
+      <c r="D130" s="353"/>
       <c r="E130" s="284"/>
       <c r="F130" t="str" s="285" cm="1">
         <f t="array" ref="F130">IF($AD130="","",$H130-$G130)</f>
@@ -47202,8 +47223,8 @@
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="282"/>
       <c r="B131" s="282"/>
-      <c r="C131" s="283"/>
-      <c r="D131" s="283"/>
+      <c r="C131" s="353"/>
+      <c r="D131" s="353"/>
       <c r="E131" s="284"/>
       <c r="F131" t="str" s="285" cm="1">
         <f t="array" ref="F131">IF($AD131="","",$H131-$G131)</f>
@@ -47254,8 +47275,8 @@
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="282"/>
       <c r="B132" s="282"/>
-      <c r="C132" s="283"/>
-      <c r="D132" s="283"/>
+      <c r="C132" s="353"/>
+      <c r="D132" s="353"/>
       <c r="E132" s="284"/>
       <c r="F132" t="str" s="285" cm="1">
         <f t="array" ref="F132">IF($AD132="","",$H132-$G132)</f>
@@ -47306,8 +47327,8 @@
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="282"/>
       <c r="B133" s="282"/>
-      <c r="C133" s="283"/>
-      <c r="D133" s="283"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
       <c r="E133" s="284"/>
       <c r="F133" t="str" s="285" cm="1">
         <f t="array" ref="F133">IF($AD133="","",$H133-$G133)</f>
@@ -47358,8 +47379,8 @@
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="282"/>
       <c r="B134" s="282"/>
-      <c r="C134" s="283"/>
-      <c r="D134" s="283"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
       <c r="E134" s="284"/>
       <c r="F134" t="str" s="285" cm="1">
         <f t="array" ref="F134">IF($AD134="","",$H134-$G134)</f>
@@ -47410,8 +47431,8 @@
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="282"/>
       <c r="B135" s="282"/>
-      <c r="C135" s="283"/>
-      <c r="D135" s="283"/>
+      <c r="C135" s="353"/>
+      <c r="D135" s="353"/>
       <c r="E135" s="284"/>
       <c r="F135" t="str" s="285" cm="1">
         <f t="array" ref="F135">IF($AD135="","",$H135-$G135)</f>
@@ -47462,8 +47483,8 @@
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="282"/>
       <c r="B136" s="282"/>
-      <c r="C136" s="283"/>
-      <c r="D136" s="283"/>
+      <c r="C136" s="353"/>
+      <c r="D136" s="353"/>
       <c r="E136" s="284"/>
       <c r="F136" t="str" s="285" cm="1">
         <f t="array" ref="F136">IF($AD136="","",$H136-$G136)</f>
@@ -47514,8 +47535,8 @@
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="282"/>
       <c r="B137" s="282"/>
-      <c r="C137" s="283"/>
-      <c r="D137" s="283"/>
+      <c r="C137" s="353"/>
+      <c r="D137" s="353"/>
       <c r="E137" s="284"/>
       <c r="F137" t="str" s="285" cm="1">
         <f t="array" ref="F137">IF($AD137="","",$H137-$G137)</f>
@@ -47566,8 +47587,8 @@
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="282"/>
       <c r="B138" s="282"/>
-      <c r="C138" s="283"/>
-      <c r="D138" s="283"/>
+      <c r="C138" s="353"/>
+      <c r="D138" s="353"/>
       <c r="E138" s="284"/>
       <c r="F138" t="str" s="285" cm="1">
         <f t="array" ref="F138">IF($AD138="","",$H138-$G138)</f>
@@ -47618,8 +47639,8 @@
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="282"/>
       <c r="B139" s="282"/>
-      <c r="C139" s="283"/>
-      <c r="D139" s="283"/>
+      <c r="C139" s="353"/>
+      <c r="D139" s="353"/>
       <c r="E139" s="284"/>
       <c r="F139" t="str" s="285" cm="1">
         <f t="array" ref="F139">IF($AD139="","",$H139-$G139)</f>
@@ -47670,8 +47691,8 @@
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="282"/>
       <c r="B140" s="282"/>
-      <c r="C140" s="283"/>
-      <c r="D140" s="283"/>
+      <c r="C140" s="353"/>
+      <c r="D140" s="353"/>
       <c r="E140" s="284"/>
       <c r="F140" t="str" s="285" cm="1">
         <f t="array" ref="F140">IF($AD140="","",$H140-$G140)</f>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -2764,7 +2764,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="274">
   <si>
-    <t>現場／統括：、現場責任者：新地工事長、主任：、担当：</t>
+    <t>現場／統括：、現場責任者：金子主任、主任：、担当：</t>
   </si>
   <si>
     <t>統責者</t>
@@ -3017,7 +3017,7 @@
         <color indexed="8"/>
         <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
       </rPr>
-      <t>現場／統括：、現場責任者：新地工事長、主任：、担当：</t>
+      <t>現場／統括：、現場責任者：金子主任、主任：、担当：</t>
     </r>
   </si>
   <si>
@@ -4994,7 +4994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="356">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -6062,6 +6062,12 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment shrinkToFit="1" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21904,7 +21910,7 @@
     <row r="1" ht="24.75" customHeight="1">
       <c r="A1" s="172" cm="1" t="str">
         <f t="array" ref="A1">'①施工図リスト'!A1</f>
-        <v>現場／統括：、現場責任者：新地工事長、主任：、担当：</v>
+        <v>現場／統括：、現場責任者：金子主任、主任：、担当：</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -39639,17 +39645,15 @@
     <col min="45" max="16384" width="9" style="201" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.6" customHeight="1">
-      <c r="A1" t="s" s="167">
-        <v>3</v>
-      </c>
-      <c r="B1" s="202"/>
-      <c r="C1" t="str" s="203" cm="1">
-        <f t="array" ref="C1">'①施工図リスト'!C2</f>
-        <v>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事</v>
-      </c>
-      <c r="D1" s="203"/>
-      <c r="E1" s="204"/>
+    <row r="1" ht="24.75" customHeight="1">
+      <c r="A1" s="172" t="str">
+        <f>'①施工図リスト'!A1</f>
+        <v>現場／統括：、現場責任者：金子主任、主任：、担当：</v>
+      </c>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
       <c r="F1" s="205" cm="1">
         <f t="array" ref="F1">'①施工図リスト'!AG7</f>
         <v>7</v>
@@ -39700,10 +39704,15 @@
       <c r="AQ1" s="12"/>
       <c r="AR1" s="12"/>
     </row>
-    <row r="2" ht="18.6" customHeight="1">
-      <c r="A2" s="151"/>
+    <row r="2" ht="56.65" customHeight="1">
+      <c r="A2" s="357" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="211"/>
-      <c r="C2" s="212"/>
+      <c r="C2" s="356" t="str">
+        <f>'①施工図リスト'!C2</f>
+        <v>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事</v>
+      </c>
       <c r="D2" s="212"/>
       <c r="E2" s="213"/>
       <c r="F2" s="214" cm="1">
@@ -48034,7 +48043,8 @@
     <mergeCell ref="P4:P6"/>
     <mergeCell ref="W4:X4"/>
     <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="G2:I2"/>
@@ -48044,7 +48054,7 @@
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="H4:H6"/>
-    <mergeCell ref="C1:E3"/>
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="G4:G6"/>
     <mergeCell ref="B4:B6"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -6073,7 +6073,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="26">
     <dxf>
       <font>
         <color rgb="ffff0000"/>
@@ -6224,6 +6224,51 @@
           <bgColor rgb="FFFFFF66"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF66FF66"/>
+          <bgColor rgb="FF66FF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB2A1C7"/>
+          <bgColor rgb="FFB2A1C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF9999"/>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFCC66"/>
+          <bgColor rgb="FFFFCC66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0"/>
@@ -21829,36 +21874,141 @@
       <formula>NOT(ISBLANK(S11))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G11:G159">
+    <cfRule type="expression" dxfId="23" priority="41" stopIfTrue="1">
+      <formula>AND(G11="",ISNUMBER(F11),F11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="42" stopIfTrue="1">
+      <formula>AND(G11="",ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11:J159">
+    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
+      <formula>AND(J11="",ISNUMBER(I11),I11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="44" stopIfTrue="1">
+      <formula>AND(J11="",ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11:L159">
+    <cfRule type="expression" dxfId="23" priority="45" stopIfTrue="1">
+      <formula>AND(L11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="46" stopIfTrue="1">
+      <formula>AND(L11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M159">
+    <cfRule type="expression" dxfId="23" priority="47" stopIfTrue="1">
+      <formula>AND(M11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="48" stopIfTrue="1">
+      <formula>AND(M11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S11:S159">
+    <cfRule type="expression" dxfId="23" priority="49" stopIfTrue="1">
+      <formula>AND(S11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="50" stopIfTrue="1">
+      <formula>AND(S11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T11:T159">
+    <cfRule type="expression" dxfId="23" priority="51" stopIfTrue="1">
+      <formula>AND(T11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="52" stopIfTrue="1">
+      <formula>AND(T11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:D159">
+    <cfRule type="expression" dxfId="20" priority="53">
+      <formula>AND(ISNUMBER(D11),YEAR(D11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="54">
+      <formula>AND(ISNUMBER(D11),YEAR(D11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="55">
+      <formula>AND(ISNUMBER(D11),YEAR(D11)=$AH$9)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F11:F159">
-    <cfRule type="expression" dxfId="18" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="56">
       <formula>AND(ISNUMBER(F11),F11&lt;=TODAY(),G11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="51" stopIfTrue="1">
-      <formula>AND(ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7,G11="")</formula>
+    <cfRule type="expression" dxfId="20" priority="57">
+      <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="58">
+      <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="59">
+      <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I159">
-    <cfRule type="expression" dxfId="18" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="60">
       <formula>AND(ISNUMBER(I11),I11&lt;=TODAY(),J11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="53" stopIfTrue="1">
-      <formula>AND(ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7,J11="")</formula>
+    <cfRule type="expression" dxfId="20" priority="61">
+      <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="62">
+      <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="63">
+      <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P159">
-    <cfRule type="expression" dxfId="18" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="64">
       <formula>AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="55" stopIfTrue="1">
-      <formula>AND(ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7,OR(L11="",M11=""))</formula>
+    <cfRule type="expression" dxfId="20" priority="65">
+      <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="66">
+      <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="67">
+      <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC159">
-    <cfRule type="expression" dxfId="18" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="68">
       <formula>AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="57" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7,OR(S11="",T11=""))</formula>
+    <cfRule type="expression" dxfId="20" priority="69">
+      <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="70">
+      <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="71">
+      <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD11:AD159">
+    <cfRule type="expression" dxfId="20" priority="72">
+      <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="73">
+      <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="74">
+      <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG11:AG159">
+    <cfRule type="expression" dxfId="20" priority="75">
+      <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="76">
+      <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="77">
+      <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.472441" right="0.19685" top="0.787402" bottom="0.19685" header="0.511811" footer="0.511811"/>
@@ -39583,36 +39733,141 @@
       <formula>NOT(ISBLANK(S12))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G11:G210">
+    <cfRule type="expression" dxfId="23" priority="41" stopIfTrue="1">
+      <formula>AND(G11="",ISNUMBER(F11),F11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="42" stopIfTrue="1">
+      <formula>AND(G11="",ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11:J210">
+    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
+      <formula>AND(J11="",ISNUMBER(I11),I11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="44" stopIfTrue="1">
+      <formula>AND(J11="",ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L11:L210">
+    <cfRule type="expression" dxfId="23" priority="45" stopIfTrue="1">
+      <formula>AND(L11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="46" stopIfTrue="1">
+      <formula>AND(L11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M210">
+    <cfRule type="expression" dxfId="23" priority="47" stopIfTrue="1">
+      <formula>AND(M11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="48" stopIfTrue="1">
+      <formula>AND(M11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S11:S210">
+    <cfRule type="expression" dxfId="23" priority="49" stopIfTrue="1">
+      <formula>AND(S11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="50" stopIfTrue="1">
+      <formula>AND(S11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T11:T210">
+    <cfRule type="expression" dxfId="23" priority="51" stopIfTrue="1">
+      <formula>AND(T11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="52" stopIfTrue="1">
+      <formula>AND(T11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E210">
+    <cfRule type="expression" dxfId="20" priority="53">
+      <formula>AND(ISNUMBER(E11),YEAR(E11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="54">
+      <formula>AND(ISNUMBER(E11),YEAR(E11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="55">
+      <formula>AND(ISNUMBER(E11),YEAR(E11)=$AH$9)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F11:F210">
-    <cfRule type="expression" dxfId="18" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="56">
       <formula>AND(ISNUMBER(F11),F11&lt;=TODAY(),G11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="51" stopIfTrue="1">
-      <formula>AND(ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7,G11="")</formula>
+    <cfRule type="expression" dxfId="20" priority="57">
+      <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="58">
+      <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="59">
+      <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I210">
-    <cfRule type="expression" dxfId="18" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="60">
       <formula>AND(ISNUMBER(I11),I11&lt;=TODAY(),J11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="53" stopIfTrue="1">
-      <formula>AND(ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7,J11="")</formula>
+    <cfRule type="expression" dxfId="20" priority="61">
+      <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="62">
+      <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="63">
+      <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P210">
-    <cfRule type="expression" dxfId="18" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="64">
       <formula>AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="55" stopIfTrue="1">
-      <formula>AND(ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7,OR(L11="",M11=""))</formula>
+    <cfRule type="expression" dxfId="20" priority="65">
+      <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="66">
+      <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="67">
+      <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC210">
-    <cfRule type="expression" dxfId="18" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="68">
       <formula>AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="57" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7,OR(S11="",T11=""))</formula>
+    <cfRule type="expression" dxfId="20" priority="69">
+      <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="70">
+      <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="71">
+      <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD11:AD210">
+    <cfRule type="expression" dxfId="20" priority="72">
+      <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="73">
+      <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="74">
+      <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG11:AG210">
+    <cfRule type="expression" dxfId="20" priority="75">
+      <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="76">
+      <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="77">
+      <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.472441" right="0.19685" top="0.787402" bottom="0.19685" header="0.511811" footer="0.511811"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -6073,7 +6073,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="35">
     <dxf>
       <font>
         <color rgb="ffff0000"/>
@@ -6269,6 +6269,84 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF66FF66"/>
+          <bgColor rgb="FF66FF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB2A1C7"/>
+          <bgColor rgb="FFB2A1C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF9999"/>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFABF8F"/>
+          <bgColor rgb="FFFABF8F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF66FF66"/>
+          <bgColor rgb="FF66FF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB2A1C7"/>
+          <bgColor rgb="FFB2A1C7"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0"/>
@@ -21865,149 +21943,185 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:O11 AI11:AL11 J12 L12:O12 AE12 AI12:AL12 J13 L13:O13 AE13 AI13:AL13 J14 L14:O14 AE14 AI14:AL14 J15 L15:O15 AE15 AI15:AL15 J16 L16:O16 AE16 AI16:AL16 J17 L17:O17 AE17 AI17:AL17 J18 L18:O18 AE18 AI18:AL18 J19 L19:O19 AE19 AI19:AL19 J20 L20:O20 AE20 AI20:AL20 J21 L21:O21 AE21 AI21:AL21 J22 L22:O22 AE22 AI22:AL22 J23 L23:O23 AE23 AI23:AL23 J24 L24:O24 AE24 AI24:AL24 J25 L25:O25 AE25 AI25:AL25 J26 L26:O26 AE26 AI26:AL26 J27 L27:O27 AE27 AI27:AL27 J28 L28:O28 AE28 AI28:AL28 J29 L29:O29 AE29 AI29:AL29 J30 L30:O30 AE30 AI30:AL30 J31 L31:O31 AE31 AI31:AL31 J32 L32:O32 AE32 AI32:AL32 J33 L33:O33 AE33 AI33:AL33 J34 L34:O34 AE34 AI34:AL34 J35 L35:O35 AE35 AI35:AL35 J36 L36:O36 AE36 AI36:AL36 J37 L37:O37 AE37 AI37:AL37 J38 L38:O38 AE38 AI38:AL38 J39 L39:O39 AE39 AI39:AL39 J40 L40:O40 AE40 AI40:AL40 J41 L41:O41 AE41 AI41:AL41 J42 L42:O42 AE42 AI42:AL42 J43 L43:O43 AE43 AI43:AL43 J44 L44:O44 AE44 AI44:AL44 J45 L45:O45 AE45 AI45:AL45 J46 L46:O46 AE46 AI46:AL46 J47 L47:O47 AE47 AI47:AL47 J48 L48:O48 AE48 AI48:AL48 J49 L49:O49 AE49 AI49:AL49 J50 L50:O50 AE50 AI50:AL50 J51 L51:O51 AE51 AI51:AL51 J52 L52:O52 AE52 AI52:AL52 J53 L53:O53 AE53 AI53:AL53 J54 L54:O54 AE54 AI54:AL54 J55 L55:O55 AE55 AI55:AL55 J56 L56:O56 AE56 AI56:AL56 J57 L57:O57 AE57 AI57:AL57 J58 L58:O58 AE58 AI58:AL58 J59 L59:O59 AE59 AI59:AL59 J60 L60:O60 AE60 AI60:AL60 J61 L61:O61 AE61 AI61:AL61 J62 L62:O62 AE62 AI62:AL62 J63 L63:O63 AE63 AI63:AL63 J64 L64:O64 AE64 AI64:AL64 J65 L65:O65 AE65 AI65:AL65 J66 L66:O66 AE66 AI66:AL66 J67 L67:O67 AE67 AI67:AL67 J68 L68:O68 AE68 AI68:AL68 J69 L69:O69 AE69 AI69:AL69 J70 L70:O70 AE70 AI70:AL70 J71 L71:O71 AE71 AI71:AL71 J72 L72:O72 AE72 AI72:AL72 J73 L73:O73 AE73 AI73:AL73 J74 L74:O74 AE74 AI74:AL74 J75 L75:O75 AE75 AI75:AL75 J76 L76:O76 AE76 AI76:AL76 J77 L77:O77 AE77 AI77:AL77 J78 L78:O78 AE78 AI78:AL78 J79 L79:O79 AE79 AI79:AL79 J80 L80:O80 AE80 AI80:AL80 J81 L81:O81 AE81 AI81:AL81 J82 L82:O82 AE82 AI82:AL82 J83 L83:O83 AE83 AI83:AL83 J84 L84:O84 AE84 AI84:AL84 J85 L85:O85 AE85 AI85:AL85 J86 L86:O86 AE86 AI86:AL86 J87 L87:O87 AE87 AI87:AL87 J88 L88:O88 AE88 AI88:AL88 J89 L89:O89 AE89 AI89:AL89 J90 L90:O90 AE90 AI90:AL90 J91 L91:O91 AE91 AI91:AL91 J92 L92:O92 AE92 AI92:AL92 J93 L93:O93 AE93 AI93:AL93 J94 L94:O94 AE94 AI94:AL94 J95 L95:O95 AE95 AI95:AL95 J96 L96:O96 AE96 AI96:AL96 J97 L97:O97 AE97 AI97:AL97 J98 L98:O98 AE98 AI98:AL98 J99 L99:O99 AE99 AI99:AL99 J100 L100:O100 AE100 AI100:AL100 J101 L101:O101 AE101 AI101:AL101 J102 L102:O102 AE102 AI102:AL102 J103 L103:O103 AE103 AI103:AL103 J104 L104:O104 AE104 AI104:AL104 J105 L105:O105 AE105 AI105:AL105 J106 L106:O106 AE106 AI106:AL106 J107 L107:O107 AE107 AI107:AL107 J108 L108:O108 AE108 AI108:AL108 J109 L109:O109 AE109 AI109:AL109 J110 L110:O110 AE110 AI110:AL110 J111 L111:O111 AE111 AI111:AL111 J112 L112:O112 AE112 AI112:AL112 J113 L113:O113 AE113 AI113:AL113 J114 L114:O114 AE114 AI114:AL114 J115 L115:O115 AE115 AI115:AL115 J116 L116:O116 AE116 AI116:AL116 J117 L117:O117 AE117 AI117:AL117 J118 L118:O118 AE118 AI118:AL118 J119 L119:O119 AE119 AI119:AL119 J120 L120:O120 AE120 AI120:AL120 J121 L121:O121 AE121 AI121:AL121 J122 L122:O122 AE122 AI122:AL122 J123 L123:O123 AE123 AI123:AL123 J124 L124:O124 AE124 AI124:AL124 J125 L125:O125 AE125 AI125:AL125 J126 L126:O126 AE126 AI126:AL126 J127 L127:O127 AE127 AI127:AL127 J128 L128:O128 AE128 AI128:AL128 J129 L129:O129 AE129 AI129:AL129 J130 L130:O130 AE130 AI130:AL130 J131 L131:O131 AE131 AI131:AL131 J132 L132:O132 AE132 AI132:AL132 J133 L133:O133 AE133 AI133:AL133 J134 L134:O134 AE134 AI134:AL134 J135 L135:O135 AE135 AI135:AL135 J136 L136:O136 AE136 AI136:AL136 J137 L137:O137 AE137 AI137:AL137 J138 L138:O138 AE138 AI138:AL138 J139 L139:O139 AE139 AI139:AL139 J140 L140:O140 AE140 AI140:AL140 J141 L141:O141 AE141 AI141:AL141 J142 L142:O142 AE142 AI142:AL142 J143 L143:O143 AE143 AI143:AL143 J144 L144:O144 AE144 AI144:AL144 J145 L145:O145 AE145 AI145:AL145 J146 L146:O146 AE146 AI146:AL146 J147 L147:O147 AE147 AI147:AL147 J148 L148:O148 AE148 AI148:AL148 J149 L149:O149 AE149 AI149:AL149 J150 L150:O150 AE150 AI150:AL150 J151 L151:O151 AE151 AI151:AL151 J152 L152:O152 AE152 AI152:AL152 J153 L153:O153 AE153 AI153:AL153 J154 L154:O154 AE154 AI154:AL154 J155 L155:O155 AE155 AI155:AL155 J156 L156:O156 AE156 AI156:AL156 J157 L157:O157 AE157 AI157:AL157 J158 L158:O158 AE158 AI158:AL158 J159 L159:O159 AE159 AI159:AL159">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="3" stopIfTrue="1">
       <formula>NOT(ISBLANK(M11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:AB159">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="4" stopIfTrue="1">
       <formula>NOT(ISBLANK(S11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G159">
-    <cfRule type="expression" dxfId="23" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
       <formula>AND(G11="",ISNUMBER(F11),F11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="6" stopIfTrue="1">
       <formula>AND(G11="",ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J159">
-    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="7" stopIfTrue="1">
       <formula>AND(J11="",ISNUMBER(I11),I11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="8" stopIfTrue="1">
       <formula>AND(J11="",ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L159">
-    <cfRule type="expression" dxfId="23" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="9" stopIfTrue="1">
       <formula>AND(L11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="10" stopIfTrue="1">
       <formula>AND(L11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M159">
-    <cfRule type="expression" dxfId="23" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="11" stopIfTrue="1">
       <formula>AND(M11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
       <formula>AND(M11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S159">
-    <cfRule type="expression" dxfId="23" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="13" stopIfTrue="1">
       <formula>AND(S11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="14" stopIfTrue="1">
       <formula>AND(S11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T159">
-    <cfRule type="expression" dxfId="23" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="15" stopIfTrue="1">
       <formula>AND(T11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="16" stopIfTrue="1">
       <formula>AND(T11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D159">
-    <cfRule type="expression" dxfId="20" priority="53">
+    <cfRule type="expression" dxfId="20" priority="17">
       <formula>AND(ISNUMBER(D11),YEAR(D11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="54">
+    <cfRule type="expression" dxfId="21" priority="18">
       <formula>AND(ISNUMBER(D11),YEAR(D11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="55">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>AND(ISNUMBER(D11),YEAR(D11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F159">
-    <cfRule type="expression" dxfId="25" priority="56">
+    <cfRule type="expression" dxfId="32" priority="20" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F11),F11&lt;=TODAY(),G11=""),YEAR(F11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="21" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F11),F11&lt;=TODAY(),G11=""),YEAR(F11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="22" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F11),F11&lt;=TODAY(),G11=""),YEAR(F11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="23">
       <formula>AND(ISNUMBER(F11),F11&lt;=TODAY(),G11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="57">
+    <cfRule type="expression" dxfId="20" priority="24">
       <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="58">
+    <cfRule type="expression" dxfId="21" priority="25">
       <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="59">
+    <cfRule type="expression" dxfId="22" priority="26">
       <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I159">
-    <cfRule type="expression" dxfId="25" priority="60">
+    <cfRule type="expression" dxfId="32" priority="27" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(I11),I11&lt;=TODAY(),J11=""),YEAR(I11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="28" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(I11),I11&lt;=TODAY(),J11=""),YEAR(I11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="29" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(I11),I11&lt;=TODAY(),J11=""),YEAR(I11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="30">
       <formula>AND(ISNUMBER(I11),I11&lt;=TODAY(),J11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="61">
+    <cfRule type="expression" dxfId="20" priority="31">
       <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="62">
+    <cfRule type="expression" dxfId="21" priority="32">
       <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="63">
+    <cfRule type="expression" dxfId="22" priority="33">
       <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P159">
-    <cfRule type="expression" dxfId="25" priority="64">
+    <cfRule type="expression" dxfId="32" priority="34" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11="")),YEAR(P11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11="")),YEAR(P11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="36" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11="")),YEAR(P11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="37">
       <formula>AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="65">
+    <cfRule type="expression" dxfId="20" priority="38">
       <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="66">
+    <cfRule type="expression" dxfId="21" priority="39">
       <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="67">
+    <cfRule type="expression" dxfId="22" priority="40">
       <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC159">
-    <cfRule type="expression" dxfId="25" priority="68">
+    <cfRule type="expression" dxfId="32" priority="41" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11="")),YEAR(AC11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="42" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11="")),YEAR(AC11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="43" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11="")),YEAR(AC11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="44">
       <formula>AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="69">
+    <cfRule type="expression" dxfId="20" priority="45">
       <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="70">
+    <cfRule type="expression" dxfId="21" priority="46">
       <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="71">
+    <cfRule type="expression" dxfId="22" priority="47">
       <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD159">
-    <cfRule type="expression" dxfId="20" priority="72">
+    <cfRule type="expression" dxfId="20" priority="48">
       <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="73">
+    <cfRule type="expression" dxfId="21" priority="49">
       <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="74">
+    <cfRule type="expression" dxfId="22" priority="50">
       <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG11:AG159">
-    <cfRule type="expression" dxfId="20" priority="75">
+    <cfRule type="expression" dxfId="20" priority="51">
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="76">
+    <cfRule type="expression" dxfId="21" priority="52">
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="77">
+    <cfRule type="expression" dxfId="22" priority="53">
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39694,179 +39808,215 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11 K11 Q11:R11">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan" stopIfTrue="1">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan" stopIfTrue="1">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="6" priority="2" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="6" priority="3" stopIfTrue="1">
       <formula>NOT(ISBLANK(H11))</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="7" priority="3" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="7" priority="4" stopIfTrue="1">
       <formula>NOT(ISBLANK(H11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:O11">
-    <cfRule type="notContainsBlanks" dxfId="8" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="8" priority="5" stopIfTrue="1">
       <formula>NOT(ISBLANK(M11))</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="9" priority="2" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="9" priority="6" stopIfTrue="1">
       <formula>NOT(ISBLANK(M11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:AB11">
-    <cfRule type="notContainsBlanks" dxfId="10" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="10" priority="7" stopIfTrue="1">
       <formula>NOT(ISBLANK(S11))</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="11" priority="2" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="11" priority="8" stopIfTrue="1">
       <formula>NOT(ISBLANK(S11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF11 H12 K12 Q12:R12 AF12 H13 K13 Q13:R13 AF13 H14 K14 Q14:R14 AF14 H15 K15 Q15:R15 AF15 H16 K16 Q16:R16 AF16 H17 K17 Q17:R17 AF17 H18 K18 Q18:R18 AF18 H19 K19 Q19:R19 AF19 H20 K20 Q20:R20 AF20 H21 K21 Q21:R21 AF21 H22 K22 Q22:R22 AF22 H23 K23 Q23:R23 AF23 H24 K24 Q24:R24 AF24 H25 K25 Q25:R25 AF25 H26 K26 Q26:R26 AF26 H27 K27 Q27:R27 AF27 H28 K28 Q28:R28 AF28 H29 K29 Q29:R29 AF29 H30 K30 Q30:R30 AF30 H31 K31 Q31:R31 AF31 H32 K32 Q32:R32 AF32 H33 K33 Q33:R33 AF33 H34 K34 Q34:R34 AF34 H35 K35 Q35:R35 AF35 H36 K36 Q36:R36 AF36 H37 K37 Q37:R37 AF37 H38 K38 Q38:R38 AF38 H39 K39 Q39:R39 AF39 H40 K40 Q40:R40 AF40 H41 K41 Q41:R41 AF41 H42 K42 Q42:R42 AF42 H43 K43 Q43:R43 AF43 H44 K44 Q44:R44 AF44 H45 K45 Q45:R45 AF45 H46 K46 Q46:R46 AF46 H47 K47 Q47:R47 AF47 H48 K48 Q48:R48 AF48 H49 K49 Q49:R49 AF49 H50 K50 Q50:R50 AF50 H51 K51 Q51:R51 AF51 H52 K52 Q52:R52 AF52 H53 K53 Q53:R53 AF53 H54 K54 Q54:R54 AF54 H55 K55 Q55:R55 AF55 H56 K56 Q56:R56 AF56 H57 K57 Q57:R57 AF57 H58 K58 Q58:R58 AF58 H59 K59 Q59:R59 AF59 H60 K60 Q60:R60 AF60 H61 K61 Q61:R61 AF61 H62 K62 Q62:R62 AF62 H63 K63 Q63:R63 AF63 H64 K64 Q64:R64 AF64 H65 K65 Q65:R65 AF65 H66 K66 Q66:R66 AF66 H67 K67 Q67:R67 AF67 H68 K68 Q68:R68 AF68 H69 K69 Q69:R69 AF69 H70 K70 Q70:R70 AF70 H71 K71 Q71:R71 AF71 H72 K72 Q72:R72 AF72 H73 K73 Q73:R73 AF73 H74 K74 Q74:R74 AF74 H75 K75 Q75:R75 AF75 H76 K76 Q76:R76 AF76 H77 K77 Q77:R77 AF77 H78 K78 Q78:R78 AF78 H79 K79 Q79:R79 AF79 H80 K80 Q80:R80 AF80 H81 K81 Q81:R81 AF81 H82 K82 Q82:R82 AF82 H83 K83 Q83:R83 AF83 H84 K84 Q84:R84 AF84 H85 K85 Q85:R85 AF85 H86 K86 Q86:R86 AF86 H87 K87 Q87:R87 AF87 H88 K88 Q88:R88 AF88 H89 K89 Q89:R89 AF89 H90 K90 Q90:R90 AF90 H91 K91 Q91:R91 AF91 H92 K92 Q92:R92 AF92 H93 K93 Q93:R93 AF93 H94 K94 Q94:R94 AF94 H95 K95 Q95:R95 AF95 H96 K96 Q96:R96 AF96 H97 K97 Q97:R97 AF97 H98 K98 Q98:R98 AF98 H99 K99 Q99:R99 AF99 H100 K100 Q100:R100 AF100 H101 K101 Q101:R101 AF101 H102 K102 Q102:R102 AF102 H103 K103 Q103:R103 AF103 H104 K104 Q104:R104 AF104 H105 K105 Q105:R105 AF105 H106 K106 Q106:R106 AF106 H107 K107 Q107:R107 AF107 H108 K108 Q108:R108 AF108 H109 K109 Q109:R109 AF109 H110 K110 Q110:R110 AF110 H111 K111 Q111:R111 AF111 H112 K112 Q112:R112 AF112 H113 K113 Q113:R113 AF113 H114 K114 Q114:R114 AF114 H115 K115 Q115:R115 AF115 H116 K116 Q116:R116 AF116 H117 K117 Q117:R117 AF117 H118 K118 Q118:R118 AF118 H119 K119 Q119:R119 AF119 H120 K120 Q120:R120 AF120 H121 K121 Q121:R121 AF121 H122 K122 Q122:R122 AF122 H123 K123 Q123:R123 AF123 H124 K124 Q124:R124 AF124 H125 K125 Q125:R125 AF125 H126 K126 Q126:R126 AF126 H127 K127 Q127:R127 AF127 H128 K128 Q128:R128 AF128 H129 K129 Q129:R129 AF129 H130 K130 Q130:R130 AF130 H131 K131 Q131:R131 AF131 H132 K132 Q132:R132 AF132 H133 K133 Q133:R133 AF133 H134 K134 Q134:R134 AF134 H135 K135 Q135:R135 AF135 H136 K136 Q136:R136 AF136 H137 K137 Q137:R137 AF137 H138 K138 Q138:R138 AF138 H139 K139 Q139:R139 AF139 H140 K140 Q140:R140 AF140 H141 K141 Q141:R141 AF141 H142 K142 Q142:R142 AF142 H143 K143 Q143:R143 AF143 H144 K144 Q144:R144 AF144 H145 K145 Q145:R145 AF145 H146 K146 Q146:R146 AF146 H147 K147 Q147:R147 AF147 H148 K148 Q148:R148 AF148 H149 K149 Q149:R149 AF149 H150 K150 Q150:R150 AF150 H151 K151 Q151:R151 AF151 H152 K152 Q152:R152 AF152 H153 K153 Q153:R153 AF153 H154 K154 Q154:R154 AF154 H155 K155 Q155:R155 AF155 H156 K156 Q156:R156 AF156 H157 K157 Q157:R157 AF157 H158 K158 Q158:R158 AF158 H159 K159 Q159:R159 AF159 H160 K160 Q160:R160 AF160 H161 K161 Q161:R161 AF161 H162 K162 Q162:R162 AF162 H163 K163 Q163:R163 AF163 H164 K164 Q164:R164 AF164 H165 K165 Q165:R165 AF165 H166 K166 Q166:R166 AF166 H167 K167 Q167:R167 AF167 H168 K168 Q168:R168 AF168 H169 K169 Q169:R169 AF169 H170 K170 Q170:R170 AF170 H171 K171 Q171:R171 AF171 H172 K172 Q172:R172 AF172 H173 K173 Q173:R173 AF173 H174 K174 Q174:R174 AF174 H175 K175 Q175:R175 AF175 H176 K176 Q176:R176 AF176 H177 K177 Q177:R177 AF177 H178 K178 Q178:R178 AF178 H179 K179 Q179:R179 AF179 H180 K180 Q180:R180 AF180 H181 K181 Q181:R181 AF181 H182 K182 Q182:R182 AF182 H183 K183 Q183:R183 AF183 H184 K184 Q184:R184 AF184 H185 K185 Q185:R185 AF185 H186 K186 Q186:R186 AF186 H187 K187 Q187:R187 AF187 H188 K188 Q188:R188 AF188 H189 K189 Q189:R189 AF189 H190 K190 Q190:R190 AF190 H191 K191 Q191:R191 AF191 H192 K192 Q192:R192 AF192 H193 K193 Q193:R193 AF193 H194 K194 Q194:R194 AF194 H195 K195 Q195:R195 AF195 H196 K196 Q196:R196 AF196 H197 K197 Q197:R197 AF197 H198 K198 Q198:R198 AF198 H199 K199 Q199:R199 AF199 H200 K200 Q200:R200 AF200 H201 K201 Q201:R201 AF201 H202 K202 Q202:R202 AF202 H203 K203 Q203:R203 AF203 H204 K204 Q204:R204 AF204 H205 K205 Q205:R205 AF205 H206 K206 Q206:R206 AF206 H207 K207 Q207:R207 AF207 H208 K208 Q208:R208 AF208 H209 K209 Q209:R209 AF209 H210 K210 Q210:R210 AF210">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan" stopIfTrue="1">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThan" stopIfTrue="1">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="13" priority="2" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="13" priority="10" stopIfTrue="1">
       <formula>NOT(ISBLANK(AF11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:AB210">
-    <cfRule type="notContainsBlanks" dxfId="14" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="14" priority="11" stopIfTrue="1">
       <formula>NOT(ISBLANK(S12))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G210">
-    <cfRule type="expression" dxfId="23" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="12" stopIfTrue="1">
       <formula>AND(G11="",ISNUMBER(F11),F11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="13" stopIfTrue="1">
       <formula>AND(G11="",ISNUMBER(F11),F11&gt;TODAY(),F11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J210">
-    <cfRule type="expression" dxfId="23" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="14" stopIfTrue="1">
       <formula>AND(J11="",ISNUMBER(I11),I11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="15" stopIfTrue="1">
       <formula>AND(J11="",ISNUMBER(I11),I11&gt;TODAY(),I11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L210">
-    <cfRule type="expression" dxfId="23" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="16" stopIfTrue="1">
       <formula>AND(L11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="17" stopIfTrue="1">
       <formula>AND(L11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M210">
-    <cfRule type="expression" dxfId="23" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="18" stopIfTrue="1">
       <formula>AND(M11="",ISNUMBER(P11),P11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="19" stopIfTrue="1">
       <formula>AND(M11="",ISNUMBER(P11),P11&gt;TODAY(),P11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S210">
-    <cfRule type="expression" dxfId="23" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="20" stopIfTrue="1">
       <formula>AND(S11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="21" stopIfTrue="1">
       <formula>AND(S11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T210">
-    <cfRule type="expression" dxfId="23" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="22" stopIfTrue="1">
       <formula>AND(T11="",ISNUMBER(AC11),AC11&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="23" stopIfTrue="1">
       <formula>AND(T11="",ISNUMBER(AC11),AC11&gt;TODAY(),AC11&lt;=TODAY()+7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E210">
-    <cfRule type="expression" dxfId="20" priority="53">
+    <cfRule type="expression" dxfId="20" priority="24">
       <formula>AND(ISNUMBER(E11),YEAR(E11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="54">
+    <cfRule type="expression" dxfId="21" priority="25">
       <formula>AND(ISNUMBER(E11),YEAR(E11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="55">
+    <cfRule type="expression" dxfId="22" priority="26">
       <formula>AND(ISNUMBER(E11),YEAR(E11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F210">
-    <cfRule type="expression" dxfId="25" priority="56">
+    <cfRule type="expression" dxfId="32" priority="27" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F11),F11&lt;=TODAY(),G11=""),YEAR(F11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="28" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F11),F11&lt;=TODAY(),G11=""),YEAR(F11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="29" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F11),F11&lt;=TODAY(),G11=""),YEAR(F11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="30">
       <formula>AND(ISNUMBER(F11),F11&lt;=TODAY(),G11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="57">
+    <cfRule type="expression" dxfId="20" priority="31">
       <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="58">
+    <cfRule type="expression" dxfId="21" priority="32">
       <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="59">
+    <cfRule type="expression" dxfId="22" priority="33">
       <formula>AND(ISNUMBER(F11),YEAR(F11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I210">
-    <cfRule type="expression" dxfId="25" priority="60">
+    <cfRule type="expression" dxfId="32" priority="34" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(I11),I11&lt;=TODAY(),J11=""),YEAR(I11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(I11),I11&lt;=TODAY(),J11=""),YEAR(I11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="36" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(I11),I11&lt;=TODAY(),J11=""),YEAR(I11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="37">
       <formula>AND(ISNUMBER(I11),I11&lt;=TODAY(),J11="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="61">
+    <cfRule type="expression" dxfId="20" priority="38">
       <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="62">
+    <cfRule type="expression" dxfId="21" priority="39">
       <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="63">
+    <cfRule type="expression" dxfId="22" priority="40">
       <formula>AND(ISNUMBER(I11),YEAR(I11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P210">
-    <cfRule type="expression" dxfId="25" priority="64">
+    <cfRule type="expression" dxfId="32" priority="41" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11="")),YEAR(P11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="42" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11="")),YEAR(P11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="43" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11="")),YEAR(P11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="44">
       <formula>AND(ISNUMBER(P11),P11&lt;=TODAY(),OR(L11="",M11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="65">
+    <cfRule type="expression" dxfId="20" priority="45">
       <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="66">
+    <cfRule type="expression" dxfId="21" priority="46">
       <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="67">
+    <cfRule type="expression" dxfId="22" priority="47">
       <formula>AND(ISNUMBER(P11),YEAR(P11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC210">
-    <cfRule type="expression" dxfId="25" priority="68">
+    <cfRule type="expression" dxfId="32" priority="48" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11="")),YEAR(AC11)=$AH$7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="49" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11="")),YEAR(AC11)=$AH$8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="50" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11="")),YEAR(AC11)=$AH$9)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="51">
       <formula>AND(ISNUMBER(AC11),AC11&lt;=TODAY(),OR(S11="",T11=""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="69">
+    <cfRule type="expression" dxfId="20" priority="52">
       <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="70">
+    <cfRule type="expression" dxfId="21" priority="53">
       <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="71">
+    <cfRule type="expression" dxfId="22" priority="54">
       <formula>AND(ISNUMBER(AC11),YEAR(AC11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD210">
-    <cfRule type="expression" dxfId="20" priority="72">
+    <cfRule type="expression" dxfId="20" priority="55">
       <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="73">
+    <cfRule type="expression" dxfId="21" priority="56">
       <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="74">
+    <cfRule type="expression" dxfId="22" priority="57">
       <formula>AND(ISNUMBER(AD11),YEAR(AD11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG11:AG210">
-    <cfRule type="expression" dxfId="20" priority="75">
+    <cfRule type="expression" dxfId="20" priority="58">
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="76">
+    <cfRule type="expression" dxfId="21" priority="59">
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="77">
+    <cfRule type="expression" dxfId="22" priority="60">
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48343,13 +48493,114 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7 J7 O7:P7 AC7 G8 J8 O8:P8 AC8 G9 J9 O9:P9 AC9 G10 J10 O10:P10 AC10 G11 J11 O11:P11 AC11 G12 J12 O12:P12 AC12 G13 J13 O13:P13 AC13 G14 J14 O14:P14 AC14 G15 J15 O15:P15 AC15 G16 J16 O16:P16 AC16 G17 J17 O17:P17 AC17 G18 J18 O18:P18 AC18 G19 J19 O19:P19 AC19 G20 J20 O20:P20 AC20 G21 J21 O21:P21 AC21 G22 J22 O22:P22 AC22 G23 J23 O23:P23 AC23 G24 J24 O24:P24 AC24 G25 J25 O25:P25 AC25 G26 J26 O26:P26 AC26 G27 J27 O27:P27 AC27 G28 J28 O28:P28 AC28 G29 J29 O29:P29 AC29 G30 J30 O30:P30 AC30 G31 J31 O31:P31 AC31 G32 J32 O32:P32 AC32 G33 J33 O33:P33 AC33 G34 J34 O34:P34 AC34 G35 J35 O35:P35 AC35 G36 J36 O36:P36 AC36 G37 J37 O37:P37 AC37 G38 J38 O38:P38 AC38 G39 J39 O39:P39 AC39 G40 J40 O40:P40 AC40 G41 J41 O41:P41 AC41 G42 J42 O42:P42 AC42 G43 J43 O43:P43 AC43 G44 J44 O44:P44 AC44 G45 J45 O45:P45 AC45 G46 J46 O46:P46 AC46 G47 J47 O47:P47 AC47 G48 J48 O48:P48 AC48 G49 J49 O49:P49 AC49 G50 J50 O50:P50 AC50 G51 J51 O51:P51 AC51 G52 J52 O52:P52 AC52 G53 J53 O53:P53 AC53 G54 J54 O54:P54 AC54 G55 J55 O55:P55 AC55 G56 J56 O56:P56 AC56 G57 J57 O57:P57 AC57 G58 J58 O58:P58 AC58 G59 J59 O59:P59 AC59 G60 J60 O60:P60 AC60 G61 J61 O61:P61 AC61 G62 J62 O62:P62 AC62 G63 J63 O63:P63 AC63 G64 J64 O64:P64 AC64 G65 J65 O65:P65 AC65 G66 J66 O66:P66 AC66 G67 J67 O67:P67 AC67 G68 J68 O68:P68 AC68 G69 J69 O69:P69 AC69 G70 J70 O70:P70 AC70 G71 J71 O71:P71 AC71 G72 J72 O72:P72 AC72 G73 J73 O73:P73 AC73 G74 J74 O74:P74 AC74 G75 J75 O75:P75 AC75 G76 J76 O76:P76 AC76 G77 J77 O77:P77 AC77 G78 J78 O78:P78 AC78 G79 J79 O79:P79 AC79 G80 J80 O80:P80 AC80 G81 J81 O81:P81 AC81 G82 J82 O82:P82 AC82 G83 J83 O83:P83 AC83 G84 J84 O84:P84 AC84 G85 J85 O85:P85 AC85 G86 J86 O86:P86 AC86 G87 J87 O87:P87 AC87 G88 J88 O88:P88 AC88 G89 J89 O89:P89 AC89 G90 J90 O90:P90 AC90 G91 J91 O91:P91 AC91 G92 J92 O92:P92 AC92 G93 J93 O93:P93 AC93 G94 J94 O94:P94 AC94 G95 J95 O95:P95 AC95 G96 J96 O96:P96 AC96 G97 J97 O97:P97 AC97 G98 J98 O98:P98 AC98 G99 J99 O99:P99 AC99 G100 J100 O100:P100 AC100 G101 J101 O101:P101 AC101 G102 J102 O102:P102 AC102 G103 J103 O103:P103 AC103 G104 J104 O104:P104 AC104 G105 J105 O105:P105 AC105 G106 J106 O106:P106 AC106 G107 J107 O107:P107 AC107 G108 J108 O108:P108 AC108 G109 J109 O109:P109 AC109 G110 J110 O110:P110 AC110 G111 J111 O111:P111 AC111 G112 J112 O112:P112 AC112 G113 J113 O113:P113 AC113 G114 J114 O114:P114 AC114 G115 J115 O115:P115 AC115 G116 J116 O116:P116 AC116 G117 J117 O117:P117 AC117 G118 J118 O118:P118 AC118 G119 J119 O119:P119 AC119 G120 J120 O120:P120 AC120 G121 J121 O121:P121 AC121 G122 J122 O122:P122 AC122 G123 J123 O123:P123 AC123 G124 J124 O124:P124 AC124 G125 J125 O125:P125 AC125 G126 J126 O126:P126 AC126 G127 J127 O127:P127 AC127 G128 J128 O128:P128 AC128 G129 J129 O129:P129 AC129 G130 J130 O130:P130 AC130 G131 J131 O131:P131 AC131 G132 J132 O132:P132 AC132 G133 J133 O133:P133 AC133 G134 J134 O134:P134 AC134 G135 J135 O135:P135 AC135 G136 J136 O136:P136 AC136 G137 J137 O137:P137 AC137 G138 J138 O138:P138 AC138 G139 J139 O139:P139 AC139 G140 J140 O140:P140 AC140">
-    <cfRule type="notContainsBlanks" dxfId="16" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="16" priority="2" stopIfTrue="1">
       <formula>NOT(ISBLANK(G7))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7:Z140">
-    <cfRule type="notContainsBlanks" dxfId="17" priority="1" stopIfTrue="1">
+    <cfRule type="notContainsBlanks" dxfId="17" priority="3" stopIfTrue="1">
       <formula>NOT(ISBLANK(Q7))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I140">
+    <cfRule type="expression" dxfId="29" priority="4" stopIfTrue="1">
+      <formula>AND(I7="",ISNUMBER($H7),$H7&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="5" stopIfTrue="1">
+      <formula>AND(I7="",ISNUMBER($H7),$H7&gt;TODAY(),$H7&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K140">
+    <cfRule type="expression" dxfId="29" priority="6" stopIfTrue="1">
+      <formula>AND(K7="",ISNUMBER($H7),($H7+$J7)&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="7" stopIfTrue="1">
+      <formula>AND(K7="",ISNUMBER($H7),($H7+$J7)&gt;TODAY(),($H7+$J7)&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L140">
+    <cfRule type="expression" dxfId="29" priority="8" stopIfTrue="1">
+      <formula>AND(L7="",ISNUMBER($H7),($H7+$J7)&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="9" stopIfTrue="1">
+      <formula>AND(L7="",ISNUMBER($H7),($H7+$J7)&gt;TODAY(),($H7+$J7)&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB7:AB140">
+    <cfRule type="expression" dxfId="29" priority="10" stopIfTrue="1">
+      <formula>AND(AB7="",ISNUMBER($AA7),$AA7&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="11" stopIfTrue="1">
+      <formula>AND(AB7="",ISNUMBER($AA7),$AA7&gt;TODAY(),$AA7&lt;=TODAY()+7)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F140">
+    <cfRule type="expression" dxfId="32" priority="12" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F7),F7&lt;=TODAY(),E7=""),YEAR(F7)=$G$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="13" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F7),F7&lt;=TODAY(),E7=""),YEAR(F7)=$G$2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="14" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(F7),F7&lt;=TODAY(),E7=""),YEAR(F7)=$G$3)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="15">
+      <formula>AND(ISNUMBER(F7),F7&lt;=TODAY(),E7="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="16">
+      <formula>AND(ISNUMBER(F7),YEAR(F7)=$G$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="17">
+      <formula>AND(ISNUMBER(F7),YEAR(F7)=$G$2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="18">
+      <formula>AND(ISNUMBER(F7),YEAR(F7)=$G$3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H140">
+    <cfRule type="expression" dxfId="32" priority="19" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(H7),H7&lt;=TODAY(),I7=""),YEAR(H7)=$G$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="20" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(H7),H7&lt;=TODAY(),I7=""),YEAR(H7)=$G$2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="21" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(H7),H7&lt;=TODAY(),I7=""),YEAR(H7)=$G$3)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="22">
+      <formula>AND(ISNUMBER(H7),H7&lt;=TODAY(),I7="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="23">
+      <formula>AND(ISNUMBER(H7),YEAR(H7)=$G$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="24">
+      <formula>AND(ISNUMBER(H7),YEAR(H7)=$G$2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="25">
+      <formula>AND(ISNUMBER(H7),YEAR(H7)=$G$3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA140">
+    <cfRule type="expression" dxfId="32" priority="26" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AA7),AA7&lt;=TODAY(),AB7=""),YEAR(AA7)=$G$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="27" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AA7),AA7&lt;=TODAY(),AB7=""),YEAR(AA7)=$G$2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="28" stopIfTrue="1">
+      <formula>AND(AND(ISNUMBER(AA7),AA7&lt;=TODAY(),AB7=""),YEAR(AA7)=$G$3)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="29">
+      <formula>AND(ISNUMBER(AA7),AA7&lt;=TODAY(),AB7="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="30">
+      <formula>AND(ISNUMBER(AA7),YEAR(AA7)=$G$1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="31">
+      <formula>AND(ISNUMBER(AA7),YEAR(AA7)=$G$2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="32">
+      <formula>AND(ISNUMBER(AA7),YEAR(AA7)=$G$3)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.393701" right="0.19685" top="0.787402" bottom="0.393701" header="0.511811" footer="0.511811"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -3629,7 +3629,7 @@
     <numFmt numFmtId="61" formatCode="?.#&quot;年&quot;"/>
     <numFmt numFmtId="62" formatCode="0&quot; &quot;;(0)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3757,6 +3757,12 @@
       <sz val="40"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="HG丸ｺﾞｼｯｸM-PRO"/>
     </font>
   </fonts>
   <fills count="11">
@@ -4994,7 +5000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="359">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -6068,6 +6074,9 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment shrinkToFit="1" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -24979,7 +24988,7 @@
       <c r="B30" t="s" s="167">
         <v>119</v>
       </c>
-      <c r="C30" t="s" s="351">
+      <c r="C30" t="s" s="358">
         <v>120</v>
       </c>
       <c r="D30" s="165"/>
@@ -25066,7 +25075,7 @@
       <c r="B31" t="s" s="167">
         <v>122</v>
       </c>
-      <c r="C31" t="s" s="351">
+      <c r="C31" t="s" s="358">
         <v>123</v>
       </c>
       <c r="D31" s="165"/>
@@ -25426,7 +25435,7 @@
       <c r="B35" t="s" s="167">
         <v>129</v>
       </c>
-      <c r="C35" t="s" s="351">
+      <c r="C35" t="s" s="358">
         <v>130</v>
       </c>
       <c r="D35" s="165"/>
@@ -25699,7 +25708,7 @@
       <c r="B38" t="s" s="167">
         <v>133</v>
       </c>
-      <c r="C38" t="s" s="351">
+      <c r="C38" t="s" s="358">
         <v>134</v>
       </c>
       <c r="D38" s="165"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22134,6 +22134,11 @@
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C159">
+    <cfRule type="expression" dxfId="25" priority="54">
+      <formula>OR(AND($G11="",ISNUMBER($F11),$F11&lt;=TODAY()+7),AND($J11="",ISNUMBER($I11),$I11&lt;=TODAY()+7),AND(OR($L11="",$M11=""),ISNUMBER($P11),$P11&lt;=TODAY()+7),AND(OR($S11="",$T11=""),ISNUMBER($AC11),$AC11&lt;=TODAY()+7))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.472441" right="0.19685" top="0.787402" bottom="0.19685" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>
@@ -40029,6 +40034,11 @@
       <formula>AND(ISNUMBER(AG11),YEAR(AG11)=$AH$9)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C210">
+    <cfRule type="expression" dxfId="25" priority="61">
+      <formula>OR(AND($G11="",ISNUMBER($F11),$F11&lt;=TODAY()+7),AND($J11="",ISNUMBER($I11),$I11&lt;=TODAY()+7),AND(OR($L11="",$M11=""),ISNUMBER($P11),$P11&lt;=TODAY()+7),AND(OR($S11="",$T11=""),ISNUMBER($AC11),$AC11&lt;=TODAY()+7))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.472441" right="0.19685" top="0.787402" bottom="0.19685" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>
@@ -48612,6 +48622,11 @@
       <formula>AND(ISNUMBER(AA7),YEAR(AA7)=$G$3)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C140">
+    <cfRule type="expression" dxfId="25" priority="33">
+      <formula>OR(AND($E7="",ISNUMBER($F7),$F7&lt;=TODAY()),AND($I7="",ISNUMBER($H7),$H7&lt;=TODAY()+7),AND(OR($K7="",$L7=""),ISNUMBER($H7),($H7+$J7)&lt;=TODAY()+7),AND($AB7="",ISNUMBER($AA7),$AA7&lt;=TODAY()+7))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.393701" right="0.19685" top="0.787402" bottom="0.393701" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
   <headerFooter>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -23452,8 +23452,9 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="24"/>
       <c r="B3" s="26"/>
-      <c r="C3" t="s" s="34">
-        <v>83</v>
+      <c r="C3" s="34" t="str">
+        <f>'①施工図リスト'!C3</f>
+        <v>工期：2026/11/9～2027/03/31</v>
       </c>
       <c r="D3" t="s" s="515">
         <v>84</v>
@@ -23569,8 +23570,9 @@
       <c r="B4" t="s" s="314">
         <v>25</v>
       </c>
-      <c r="C4" t="s" s="62">
-        <v>26</v>
+      <c r="C4" s="62" t="str">
+        <f>'①施工図リスト'!C4</f>
+        <v>敷地：m2</v>
       </c>
       <c r="D4" t="s" s="522">
         <v>88</v>
@@ -23691,8 +23693,9 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="85"/>
       <c r="B5" s="93"/>
-      <c r="C5" t="s" s="62">
-        <v>48</v>
+      <c r="C5" s="62" t="str">
+        <f>'①施工図リスト'!C5</f>
+        <v>建面：m2</v>
       </c>
       <c r="D5" s="528"/>
       <c r="E5" s="529"/>
@@ -23811,8 +23814,9 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="85"/>
       <c r="B6" s="93"/>
-      <c r="C6" t="s" s="62">
-        <v>96</v>
+      <c r="C6" s="62" t="str">
+        <f>'①施工図リスト'!C6</f>
+        <v>改修面積：675m2</v>
       </c>
       <c r="D6" s="528"/>
       <c r="E6" s="529"/>
@@ -23879,8 +23883,9 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="85"/>
       <c r="B7" s="93"/>
-      <c r="C7" t="s" s="62">
-        <v>97</v>
+      <c r="C7" s="62" t="str">
+        <f>'①施工図リスト'!C7</f>
+        <v>構造：RC造</v>
       </c>
       <c r="D7" s="528"/>
       <c r="E7" s="529"/>
@@ -23952,8 +23957,9 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="85"/>
       <c r="B8" s="93"/>
-      <c r="C8" t="s" s="117">
-        <v>98</v>
+      <c r="C8" s="117" t="str">
+        <f>'①施工図リスト'!C8</f>
+        <v>設計者：日建設計</v>
       </c>
       <c r="D8" s="528"/>
       <c r="E8" s="529"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -5000,7 +5000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="637">
+  <cellXfs count="647">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -7189,6 +7189,36 @@
     <xf applyProtection="1" numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="255" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -41181,7 +41211,7 @@
   <cols>
     <col min="1" max="2" width="5.73438" style="201" customWidth="1"/>
     <col min="3" max="3" width="29.1562" style="201" customWidth="1"/>
-    <col min="4" max="4" width="12.2891" style="636" customWidth="1"/>
+    <col min="4" max="4" width="12.2891" style="646" customWidth="1"/>
     <col min="5" max="30" width="5.15625" style="636" customWidth="1"/>
     <col min="31" max="31" width="23.7344" style="636" customWidth="1"/>
     <col min="32" max="41" width="9.28906" style="636" customWidth="1"/>
@@ -41196,7 +41226,7 @@
       </c>
       <c r="B1" s="172"/>
       <c r="C1" s="172"/>
-      <c r="D1" s="542"/>
+      <c r="D1" s="637"/>
       <c r="E1" s="542"/>
       <c r="F1" s="543" cm="1">
         <f t="array" ref="F1">'①施工図リスト'!AG7</f>
@@ -41257,7 +41287,7 @@
         <f>'①施工図リスト'!C2</f>
         <v>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事</v>
       </c>
-      <c r="D2" s="549"/>
+      <c r="D2" s="638"/>
       <c r="E2" s="550"/>
       <c r="F2" s="551" cm="1">
         <f t="array" ref="F2">'①施工図リスト'!AG8</f>
@@ -41311,7 +41341,7 @@
       <c r="A3" s="151"/>
       <c r="B3" s="222"/>
       <c r="C3" s="223"/>
-      <c r="D3" s="559"/>
+      <c r="D3" s="639"/>
       <c r="E3" s="560"/>
       <c r="F3" s="561" cm="1">
         <f t="array" ref="F3">'①施工図リスト'!AG9</f>
@@ -41374,7 +41404,7 @@
       <c r="C4" t="s" s="234">
         <v>160</v>
       </c>
-      <c r="D4" t="s" s="569">
+      <c r="D4" t="s" s="640">
         <v>161</v>
       </c>
       <c r="E4" t="s" s="570">
@@ -41481,7 +41511,7 @@
       <c r="A5" s="255"/>
       <c r="B5" s="256"/>
       <c r="C5" s="149"/>
-      <c r="D5" s="496"/>
+      <c r="D5" s="641"/>
       <c r="E5" s="590"/>
       <c r="F5" s="591"/>
       <c r="G5" s="592"/>
@@ -41559,7 +41589,7 @@
       <c r="A6" s="272"/>
       <c r="B6" s="273"/>
       <c r="C6" s="274"/>
-      <c r="D6" s="496"/>
+      <c r="D6" s="641"/>
       <c r="E6" s="605"/>
       <c r="F6" s="591"/>
       <c r="G6" s="592"/>
@@ -41615,7 +41645,7 @@
       </c>
       <c r="B7" s="282"/>
       <c r="C7" s="353"/>
-      <c r="D7" s="611"/>
+      <c r="D7" s="642"/>
       <c r="E7" s="612"/>
       <c r="F7" t="str" s="613" cm="1">
         <f t="array" ref="F7">IF(AD7="","",H7-G7)</f>
@@ -41674,7 +41704,11 @@
       <c r="C8" t="s" s="354">
         <v>179</v>
       </c>
-      <c r="D8" s="611"/>
+      <c r="D8" s="642" t="inlineStr">
+        <is>
+          <t>現場</t>
+        </is>
+      </c>
       <c r="E8" s="612"/>
       <c r="F8" s="616" cm="1">
         <f t="array" ref="F8">IF($AD8="","",$H8-$G8)</f>
@@ -41750,7 +41784,7 @@
       <c r="C9" t="s" s="355">
         <v>182</v>
       </c>
-      <c r="D9" t="s" s="632">
+      <c r="D9" t="s" s="643">
         <v>183</v>
       </c>
       <c r="E9" s="612"/>
@@ -41828,7 +41862,7 @@
       <c r="C10" t="s" s="355">
         <v>186</v>
       </c>
-      <c r="D10" t="s" s="632">
+      <c r="D10" t="s" s="643">
         <v>187</v>
       </c>
       <c r="E10" s="612"/>
@@ -41906,7 +41940,7 @@
       <c r="C11" t="s" s="354">
         <v>190</v>
       </c>
-      <c r="D11" t="s" s="632">
+      <c r="D11" t="s" s="643">
         <v>187</v>
       </c>
       <c r="E11" s="612"/>
@@ -41984,7 +42018,7 @@
       <c r="C12" t="s" s="354">
         <v>193</v>
       </c>
-      <c r="D12" t="s" s="632">
+      <c r="D12" t="s" s="643">
         <v>194</v>
       </c>
       <c r="E12" s="612"/>
@@ -42060,7 +42094,7 @@
       <c r="C13" t="s" s="354">
         <v>196</v>
       </c>
-      <c r="D13" t="s" s="632">
+      <c r="D13" t="s" s="643">
         <v>197</v>
       </c>
       <c r="E13" s="612"/>
@@ -42138,7 +42172,7 @@
       <c r="C14" t="s" s="354">
         <v>200</v>
       </c>
-      <c r="D14" t="s" s="632">
+      <c r="D14" t="s" s="643">
         <v>201</v>
       </c>
       <c r="E14" s="612"/>
@@ -42214,7 +42248,7 @@
       <c r="C15" t="s" s="354">
         <v>203</v>
       </c>
-      <c r="D15" t="s" s="632">
+      <c r="D15" t="s" s="643">
         <v>204</v>
       </c>
       <c r="E15" s="612"/>
@@ -42290,7 +42324,7 @@
       <c r="C16" t="s" s="354">
         <v>206</v>
       </c>
-      <c r="D16" t="s" s="632">
+      <c r="D16" t="s" s="643">
         <v>207</v>
       </c>
       <c r="E16" s="612"/>
@@ -42366,7 +42400,7 @@
       <c r="C17" t="s" s="354">
         <v>209</v>
       </c>
-      <c r="D17" t="s" s="632">
+      <c r="D17" t="s" s="643">
         <v>210</v>
       </c>
       <c r="E17" s="612"/>
@@ -42442,7 +42476,7 @@
       <c r="C18" t="s" s="355">
         <v>212</v>
       </c>
-      <c r="D18" t="s" s="632">
+      <c r="D18" t="s" s="643">
         <v>213</v>
       </c>
       <c r="E18" s="612"/>
@@ -42520,7 +42554,7 @@
       <c r="C19" t="s" s="354">
         <v>215</v>
       </c>
-      <c r="D19" t="s" s="632">
+      <c r="D19" t="s" s="643">
         <v>216</v>
       </c>
       <c r="E19" s="612"/>
@@ -42598,7 +42632,7 @@
       <c r="C20" t="s" s="354">
         <v>219</v>
       </c>
-      <c r="D20" t="s" s="632">
+      <c r="D20" t="s" s="643">
         <v>220</v>
       </c>
       <c r="E20" s="612"/>
@@ -42674,7 +42708,7 @@
       <c r="C21" t="s" s="354">
         <v>222</v>
       </c>
-      <c r="D21" t="s" s="632">
+      <c r="D21" t="s" s="643">
         <v>223</v>
       </c>
       <c r="E21" s="612"/>
@@ -42750,7 +42784,7 @@
       <c r="C22" t="s" s="354">
         <v>225</v>
       </c>
-      <c r="D22" t="s" s="632">
+      <c r="D22" t="s" s="643">
         <v>226</v>
       </c>
       <c r="E22" s="612"/>
@@ -42822,7 +42856,7 @@
       </c>
       <c r="B23" s="282"/>
       <c r="C23" s="353"/>
-      <c r="D23" s="611"/>
+      <c r="D23" s="642"/>
       <c r="E23" s="612"/>
       <c r="F23" t="str" s="613" cm="1">
         <f t="array" ref="F23">IF($AD23="","",$H23-$G23)</f>
@@ -42879,7 +42913,7 @@
       <c r="C24" t="s" s="354">
         <v>227</v>
       </c>
-      <c r="D24" s="611"/>
+      <c r="D24" s="642"/>
       <c r="E24" s="612"/>
       <c r="F24" t="str" s="613" cm="1">
         <f t="array" ref="F24">IF($AD24="","",$H24-$G24)</f>
@@ -42938,7 +42972,7 @@
       <c r="C25" t="s" s="354">
         <v>229</v>
       </c>
-      <c r="D25" s="611"/>
+      <c r="D25" s="642"/>
       <c r="E25" s="612"/>
       <c r="F25" t="str" s="613" cm="1">
         <f t="array" ref="F25">IF($AD25="","",$H25-$G25)</f>
@@ -42999,7 +43033,7 @@
       <c r="C26" t="s" s="354">
         <v>232</v>
       </c>
-      <c r="D26" s="611"/>
+      <c r="D26" s="642"/>
       <c r="E26" s="612"/>
       <c r="F26" t="str" s="613" cm="1">
         <f t="array" ref="F26">IF($AD26="","",$H26-$G26)</f>
@@ -43056,7 +43090,7 @@
       </c>
       <c r="B27" s="282"/>
       <c r="C27" s="353"/>
-      <c r="D27" s="611"/>
+      <c r="D27" s="642"/>
       <c r="E27" s="612"/>
       <c r="F27" t="str" s="613" cm="1">
         <f t="array" ref="F27">IF($AD27="","",$H27-$G27)</f>
@@ -43111,7 +43145,7 @@
       </c>
       <c r="B28" s="282"/>
       <c r="C28" s="353"/>
-      <c r="D28" s="611"/>
+      <c r="D28" s="642"/>
       <c r="E28" s="612"/>
       <c r="F28" t="str" s="613" cm="1">
         <f t="array" ref="F28">IF($AD28="","",$H28-$G28)</f>
@@ -43166,7 +43200,7 @@
       </c>
       <c r="B29" s="282"/>
       <c r="C29" s="353"/>
-      <c r="D29" s="611"/>
+      <c r="D29" s="642"/>
       <c r="E29" s="612"/>
       <c r="F29" t="str" s="613" cm="1">
         <f t="array" ref="F29">IF($AD29="","",$H29-$G29)</f>
@@ -43221,7 +43255,7 @@
       </c>
       <c r="B30" s="282"/>
       <c r="C30" s="353"/>
-      <c r="D30" s="611"/>
+      <c r="D30" s="642"/>
       <c r="E30" s="612"/>
       <c r="F30" t="str" s="613" cm="1">
         <f t="array" ref="F30">IF($AD30="","",$H30-$G30)</f>
@@ -43276,7 +43310,7 @@
       </c>
       <c r="B31" s="282"/>
       <c r="C31" s="353"/>
-      <c r="D31" s="611"/>
+      <c r="D31" s="642"/>
       <c r="E31" s="612"/>
       <c r="F31" t="str" s="613" cm="1">
         <f t="array" ref="F31">IF($AD31="","",$H31-$G31)</f>
@@ -43331,7 +43365,7 @@
       </c>
       <c r="B32" s="282"/>
       <c r="C32" s="353"/>
-      <c r="D32" s="611"/>
+      <c r="D32" s="642"/>
       <c r="E32" s="612"/>
       <c r="F32" t="str" s="613" cm="1">
         <f t="array" ref="F32">IF($AD32="","",$H32-$G32)</f>
@@ -43386,7 +43420,7 @@
       </c>
       <c r="B33" s="282"/>
       <c r="C33" s="353"/>
-      <c r="D33" s="611"/>
+      <c r="D33" s="642"/>
       <c r="E33" s="612"/>
       <c r="F33" t="str" s="613" cm="1">
         <f t="array" ref="F33">IF($AD33="","",$H33-$G33)</f>
@@ -43441,7 +43475,7 @@
       </c>
       <c r="B34" s="282"/>
       <c r="C34" s="353"/>
-      <c r="D34" s="611"/>
+      <c r="D34" s="642"/>
       <c r="E34" s="612"/>
       <c r="F34" t="str" s="613" cm="1">
         <f t="array" ref="F34">IF($AD34="","",$H34-$G34)</f>
@@ -43496,7 +43530,7 @@
       </c>
       <c r="B35" s="282"/>
       <c r="C35" s="353"/>
-      <c r="D35" s="611"/>
+      <c r="D35" s="642"/>
       <c r="E35" s="612"/>
       <c r="F35" t="str" s="613" cm="1">
         <f t="array" ref="F35">IF($AD35="","",$H35-$G35)</f>
@@ -43551,7 +43585,7 @@
       </c>
       <c r="B36" s="282"/>
       <c r="C36" s="353"/>
-      <c r="D36" s="611"/>
+      <c r="D36" s="642"/>
       <c r="E36" s="612"/>
       <c r="F36" t="str" s="613" cm="1">
         <f t="array" ref="F36">IF($AD36="","",$H36-$G36)</f>
@@ -43608,7 +43642,7 @@
       <c r="C37" t="s" s="354">
         <v>234</v>
       </c>
-      <c r="D37" s="611"/>
+      <c r="D37" s="642"/>
       <c r="E37" s="612"/>
       <c r="F37" t="str" s="613" cm="1">
         <f t="array" ref="F37">IF($AD37="","",$H37-$G37)</f>
@@ -43665,7 +43699,7 @@
       <c r="C38" t="s" s="354">
         <v>235</v>
       </c>
-      <c r="D38" s="611"/>
+      <c r="D38" s="642"/>
       <c r="E38" s="612"/>
       <c r="F38" t="str" s="613" cm="1">
         <f t="array" ref="F38">IF($AD38="","",$H38-$G38)</f>
@@ -43722,7 +43756,7 @@
       <c r="C39" t="s" s="354">
         <v>236</v>
       </c>
-      <c r="D39" s="611"/>
+      <c r="D39" s="642"/>
       <c r="E39" s="612"/>
       <c r="F39" t="str" s="613" cm="1">
         <f t="array" ref="F39">IF($AD39="","",$H39-$G39)</f>
@@ -43779,7 +43813,7 @@
       <c r="C40" t="s" s="354">
         <v>237</v>
       </c>
-      <c r="D40" s="611"/>
+      <c r="D40" s="642"/>
       <c r="E40" s="612"/>
       <c r="F40" t="str" s="613" cm="1">
         <f t="array" ref="F40">IF($AD40="","",$H40-$G40)</f>
@@ -43836,7 +43870,7 @@
       <c r="C41" t="s" s="354">
         <v>193</v>
       </c>
-      <c r="D41" s="611"/>
+      <c r="D41" s="642"/>
       <c r="E41" s="612"/>
       <c r="F41" t="str" s="613" cm="1">
         <f t="array" ref="F41">IF($AD41="","",$H41-$G41)</f>
@@ -43893,7 +43927,7 @@
       <c r="C42" t="s" s="354">
         <v>238</v>
       </c>
-      <c r="D42" s="611"/>
+      <c r="D42" s="642"/>
       <c r="E42" s="612"/>
       <c r="F42" t="str" s="613" cm="1">
         <f t="array" ref="F42">IF($AD42="","",$H42-$G42)</f>
@@ -43950,7 +43984,7 @@
       <c r="C43" t="s" s="354">
         <v>222</v>
       </c>
-      <c r="D43" s="611"/>
+      <c r="D43" s="642"/>
       <c r="E43" s="612"/>
       <c r="F43" t="str" s="613" cm="1">
         <f t="array" ref="F43">IF($AD43="","",$H43-$G43)</f>
@@ -44007,7 +44041,7 @@
       <c r="C44" t="s" s="354">
         <v>239</v>
       </c>
-      <c r="D44" s="611"/>
+      <c r="D44" s="642"/>
       <c r="E44" s="612"/>
       <c r="F44" t="str" s="613" cm="1">
         <f t="array" ref="F44">IF($AD44="","",$H44-$G44)</f>
@@ -44064,7 +44098,7 @@
       <c r="C45" t="s" s="354">
         <v>219</v>
       </c>
-      <c r="D45" s="611"/>
+      <c r="D45" s="642"/>
       <c r="E45" s="612"/>
       <c r="F45" t="str" s="613" cm="1">
         <f t="array" ref="F45">IF($AD45="","",$H45-$G45)</f>
@@ -44119,7 +44153,7 @@
       </c>
       <c r="B46" s="282"/>
       <c r="C46" s="353"/>
-      <c r="D46" s="611"/>
+      <c r="D46" s="642"/>
       <c r="E46" s="612"/>
       <c r="F46" t="str" s="613" cm="1">
         <f t="array" ref="F46">IF($AD46="","",$H46-$G46)</f>
@@ -44174,7 +44208,7 @@
       </c>
       <c r="B47" s="282"/>
       <c r="C47" s="353"/>
-      <c r="D47" s="611"/>
+      <c r="D47" s="642"/>
       <c r="E47" s="612"/>
       <c r="F47" t="str" s="613" cm="1">
         <f t="array" ref="F47">IF($AD47="","",$H47-$G47)</f>
@@ -44229,7 +44263,7 @@
       </c>
       <c r="B48" s="282"/>
       <c r="C48" s="353"/>
-      <c r="D48" s="611"/>
+      <c r="D48" s="642"/>
       <c r="E48" s="612"/>
       <c r="F48" t="str" s="613" cm="1">
         <f t="array" ref="F48">IF($AD48="","",$H48-$G48)</f>
@@ -44284,7 +44318,7 @@
       </c>
       <c r="B49" s="282"/>
       <c r="C49" s="353"/>
-      <c r="D49" s="611"/>
+      <c r="D49" s="642"/>
       <c r="E49" s="612"/>
       <c r="F49" t="str" s="613" cm="1">
         <f t="array" ref="F49">IF($AD49="","",$H49-$G49)</f>
@@ -44339,7 +44373,7 @@
       </c>
       <c r="B50" s="282"/>
       <c r="C50" s="353"/>
-      <c r="D50" s="611"/>
+      <c r="D50" s="642"/>
       <c r="E50" s="612"/>
       <c r="F50" t="str" s="613" cm="1">
         <f t="array" ref="F50">IF($AD50="","",$H50-$G50)</f>
@@ -44396,7 +44430,7 @@
       <c r="C51" t="s" s="354">
         <v>240</v>
       </c>
-      <c r="D51" s="611"/>
+      <c r="D51" s="642"/>
       <c r="E51" s="612"/>
       <c r="F51" t="str" s="613" cm="1">
         <f t="array" ref="F51">IF($AD51="","",$H51-$G51)</f>
@@ -44453,7 +44487,7 @@
       <c r="C52" t="s" s="354">
         <v>241</v>
       </c>
-      <c r="D52" s="611"/>
+      <c r="D52" s="642"/>
       <c r="E52" s="612"/>
       <c r="F52" t="str" s="613" cm="1">
         <f t="array" ref="F52">IF($AD52="","",$H52-$G52)</f>
@@ -44510,7 +44544,7 @@
       <c r="C53" t="s" s="354">
         <v>242</v>
       </c>
-      <c r="D53" s="611"/>
+      <c r="D53" s="642"/>
       <c r="E53" s="612"/>
       <c r="F53" t="str" s="613" cm="1">
         <f t="array" ref="F53">IF($AD53="","",$H53-$G53)</f>
@@ -44567,7 +44601,7 @@
       <c r="C54" t="s" s="354">
         <v>243</v>
       </c>
-      <c r="D54" s="611"/>
+      <c r="D54" s="642"/>
       <c r="E54" s="612"/>
       <c r="F54" t="str" s="613" cm="1">
         <f t="array" ref="F54">IF($AD54="","",$H54-$G54)</f>
@@ -44624,7 +44658,7 @@
       <c r="C55" t="s" s="354">
         <v>244</v>
       </c>
-      <c r="D55" s="611"/>
+      <c r="D55" s="642"/>
       <c r="E55" s="612"/>
       <c r="F55" t="str" s="613" cm="1">
         <f t="array" ref="F55">IF($AD55="","",$H55-$G55)</f>
@@ -44681,7 +44715,7 @@
       <c r="C56" t="s" s="354">
         <v>245</v>
       </c>
-      <c r="D56" s="611"/>
+      <c r="D56" s="642"/>
       <c r="E56" s="612"/>
       <c r="F56" t="str" s="613" cm="1">
         <f t="array" ref="F56">IF($AD56="","",$H56-$G56)</f>
@@ -44738,7 +44772,7 @@
       <c r="C57" t="s" s="354">
         <v>246</v>
       </c>
-      <c r="D57" s="611"/>
+      <c r="D57" s="642"/>
       <c r="E57" s="612"/>
       <c r="F57" t="str" s="613" cm="1">
         <f t="array" ref="F57">IF($AD57="","",$H57-$G57)</f>
@@ -44795,7 +44829,7 @@
       <c r="C58" t="s" s="354">
         <v>247</v>
       </c>
-      <c r="D58" s="611"/>
+      <c r="D58" s="642"/>
       <c r="E58" s="612"/>
       <c r="F58" t="str" s="613" cm="1">
         <f t="array" ref="F58">IF($AD58="","",$H58-$G58)</f>
@@ -44852,7 +44886,7 @@
       <c r="C59" t="s" s="354">
         <v>248</v>
       </c>
-      <c r="D59" s="611"/>
+      <c r="D59" s="642"/>
       <c r="E59" s="612"/>
       <c r="F59" t="str" s="613" cm="1">
         <f t="array" ref="F59">IF($AD59="","",$H59-$G59)</f>
@@ -44909,7 +44943,7 @@
       <c r="C60" t="s" s="354">
         <v>249</v>
       </c>
-      <c r="D60" s="611"/>
+      <c r="D60" s="642"/>
       <c r="E60" s="612"/>
       <c r="F60" t="str" s="613" cm="1">
         <f t="array" ref="F60">IF($AD60="","",$H60-$G60)</f>
@@ -44966,7 +45000,7 @@
       <c r="C61" t="s" s="354">
         <v>250</v>
       </c>
-      <c r="D61" s="611"/>
+      <c r="D61" s="642"/>
       <c r="E61" s="612"/>
       <c r="F61" t="str" s="613" cm="1">
         <f t="array" ref="F61">IF($AD61="","",$H61-$G61)</f>
@@ -45023,7 +45057,7 @@
       <c r="C62" t="s" s="354">
         <v>251</v>
       </c>
-      <c r="D62" s="611"/>
+      <c r="D62" s="642"/>
       <c r="E62" s="612"/>
       <c r="F62" t="str" s="613" cm="1">
         <f t="array" ref="F62">IF($AD62="","",$H62-$G62)</f>
@@ -45080,7 +45114,7 @@
       <c r="C63" t="s" s="354">
         <v>252</v>
       </c>
-      <c r="D63" s="611"/>
+      <c r="D63" s="642"/>
       <c r="E63" s="612"/>
       <c r="F63" t="str" s="613" cm="1">
         <f t="array" ref="F63">IF($AD63="","",$H63-$G63)</f>
@@ -45137,7 +45171,7 @@
       <c r="C64" t="s" s="354">
         <v>253</v>
       </c>
-      <c r="D64" s="611"/>
+      <c r="D64" s="642"/>
       <c r="E64" s="612"/>
       <c r="F64" t="str" s="613" cm="1">
         <f t="array" ref="F64">IF($AD64="","",$H64-$G64)</f>
@@ -45192,7 +45226,7 @@
       </c>
       <c r="B65" s="282"/>
       <c r="C65" s="353"/>
-      <c r="D65" s="611"/>
+      <c r="D65" s="642"/>
       <c r="E65" s="612"/>
       <c r="F65" t="str" s="613" cm="1">
         <f t="array" ref="F65">IF($AD65="","",$H65-$G65)</f>
@@ -45247,7 +45281,7 @@
       </c>
       <c r="B66" s="282"/>
       <c r="C66" s="353"/>
-      <c r="D66" s="611"/>
+      <c r="D66" s="642"/>
       <c r="E66" s="612"/>
       <c r="F66" t="str" s="613" cm="1">
         <f t="array" ref="F66">IF($AD66="","",$H66-$G66)</f>
@@ -45302,7 +45336,7 @@
       </c>
       <c r="B67" s="282"/>
       <c r="C67" s="353"/>
-      <c r="D67" s="611"/>
+      <c r="D67" s="642"/>
       <c r="E67" s="612"/>
       <c r="F67" t="str" s="613" cm="1">
         <f t="array" ref="F67">IF($AD67="","",$H67-$G67)</f>
@@ -45357,7 +45391,7 @@
       </c>
       <c r="B68" s="282"/>
       <c r="C68" s="353"/>
-      <c r="D68" s="611"/>
+      <c r="D68" s="642"/>
       <c r="E68" s="612"/>
       <c r="F68" t="str" s="613" cm="1">
         <f t="array" ref="F68">IF($AD68="","",$H68-$G68)</f>
@@ -45412,7 +45446,7 @@
       </c>
       <c r="B69" s="282"/>
       <c r="C69" s="353"/>
-      <c r="D69" s="611"/>
+      <c r="D69" s="642"/>
       <c r="E69" s="612"/>
       <c r="F69" t="str" s="613" cm="1">
         <f t="array" ref="F69">IF($AD69="","",$H69-$G69)</f>
@@ -45467,7 +45501,7 @@
       </c>
       <c r="B70" s="282"/>
       <c r="C70" s="353"/>
-      <c r="D70" s="611"/>
+      <c r="D70" s="642"/>
       <c r="E70" s="612"/>
       <c r="F70" t="str" s="613" cm="1">
         <f t="array" ref="F70">IF($AD70="","",$H70-$G70)</f>
@@ -45524,7 +45558,7 @@
       <c r="C71" t="s" s="354">
         <v>254</v>
       </c>
-      <c r="D71" s="611"/>
+      <c r="D71" s="642"/>
       <c r="E71" s="612"/>
       <c r="F71" t="str" s="613" cm="1">
         <f t="array" ref="F71">IF($AD71="","",$H71-$G71)</f>
@@ -45581,7 +45615,7 @@
       <c r="C72" t="s" s="354">
         <v>255</v>
       </c>
-      <c r="D72" s="611"/>
+      <c r="D72" s="642"/>
       <c r="E72" s="612"/>
       <c r="F72" t="str" s="613" cm="1">
         <f t="array" ref="F72">IF($AD72="","",$H72-$G72)</f>
@@ -45638,7 +45672,7 @@
       <c r="C73" t="s" s="354">
         <v>256</v>
       </c>
-      <c r="D73" s="611"/>
+      <c r="D73" s="642"/>
       <c r="E73" s="612"/>
       <c r="F73" t="str" s="613" cm="1">
         <f t="array" ref="F73">IF($AD73="","",$H73-$G73)</f>
@@ -45693,7 +45727,7 @@
       </c>
       <c r="B74" s="282"/>
       <c r="C74" s="353"/>
-      <c r="D74" s="611"/>
+      <c r="D74" s="642"/>
       <c r="E74" s="612"/>
       <c r="F74" t="str" s="613" cm="1">
         <f t="array" ref="F74">IF($AD74="","",$H74-$G74)</f>
@@ -45748,7 +45782,7 @@
       </c>
       <c r="B75" s="282"/>
       <c r="C75" s="353"/>
-      <c r="D75" s="611"/>
+      <c r="D75" s="642"/>
       <c r="E75" s="612"/>
       <c r="F75" t="str" s="613" cm="1">
         <f t="array" ref="F75">IF($AD75="","",$H75-$G75)</f>
@@ -45803,7 +45837,7 @@
       </c>
       <c r="B76" s="282"/>
       <c r="C76" s="353"/>
-      <c r="D76" s="611"/>
+      <c r="D76" s="642"/>
       <c r="E76" s="612"/>
       <c r="F76" t="str" s="613" cm="1">
         <f t="array" ref="F76">IF($AD76="","",$H76-$G76)</f>
@@ -45858,7 +45892,7 @@
       </c>
       <c r="B77" s="282"/>
       <c r="C77" s="353"/>
-      <c r="D77" s="611"/>
+      <c r="D77" s="642"/>
       <c r="E77" s="612"/>
       <c r="F77" t="str" s="613" cm="1">
         <f t="array" ref="F77">IF($AD77="","",$H77-$G77)</f>
@@ -45913,7 +45947,7 @@
       </c>
       <c r="B78" s="282"/>
       <c r="C78" s="353"/>
-      <c r="D78" s="611"/>
+      <c r="D78" s="642"/>
       <c r="E78" s="612"/>
       <c r="F78" t="str" s="613" cm="1">
         <f t="array" ref="F78">IF($AD78="","",$H78-$G78)</f>
@@ -45968,7 +46002,7 @@
       </c>
       <c r="B79" s="282"/>
       <c r="C79" s="353"/>
-      <c r="D79" s="611"/>
+      <c r="D79" s="642"/>
       <c r="E79" s="612"/>
       <c r="F79" t="str" s="613" cm="1">
         <f t="array" ref="F79">IF($AD79="","",$H79-$G79)</f>
@@ -46023,7 +46057,7 @@
       </c>
       <c r="B80" s="282"/>
       <c r="C80" s="353"/>
-      <c r="D80" s="611"/>
+      <c r="D80" s="642"/>
       <c r="E80" s="612"/>
       <c r="F80" t="str" s="613" cm="1">
         <f t="array" ref="F80">IF($AD80="","",$H80-$G80)</f>
@@ -46080,7 +46114,7 @@
       <c r="C81" t="s" s="354">
         <v>257</v>
       </c>
-      <c r="D81" s="611"/>
+      <c r="D81" s="642"/>
       <c r="E81" s="612"/>
       <c r="F81" t="str" s="613" cm="1">
         <f t="array" ref="F81">IF($AD81="","",$H81-$G81)</f>
@@ -46137,7 +46171,7 @@
       <c r="C82" t="s" s="354">
         <v>258</v>
       </c>
-      <c r="D82" s="611"/>
+      <c r="D82" s="642"/>
       <c r="E82" s="612"/>
       <c r="F82" t="str" s="613" cm="1">
         <f t="array" ref="F82">IF($AD82="","",$H82-$G82)</f>
@@ -46194,7 +46228,7 @@
       <c r="C83" t="s" s="354">
         <v>259</v>
       </c>
-      <c r="D83" s="611"/>
+      <c r="D83" s="642"/>
       <c r="E83" s="612"/>
       <c r="F83" t="str" s="613" cm="1">
         <f t="array" ref="F83">IF($AD83="","",$H83-$G83)</f>
@@ -46251,7 +46285,7 @@
       <c r="C84" t="s" s="354">
         <v>260</v>
       </c>
-      <c r="D84" s="611"/>
+      <c r="D84" s="642"/>
       <c r="E84" s="612"/>
       <c r="F84" t="str" s="613" cm="1">
         <f t="array" ref="F84">IF($AD84="","",$H84-$G84)</f>
@@ -46308,7 +46342,7 @@
       <c r="C85" t="s" s="354">
         <v>261</v>
       </c>
-      <c r="D85" s="611"/>
+      <c r="D85" s="642"/>
       <c r="E85" s="612"/>
       <c r="F85" t="str" s="613" cm="1">
         <f t="array" ref="F85">IF($AD85="","",$H85-$G85)</f>
@@ -46365,7 +46399,7 @@
       <c r="C86" t="s" s="354">
         <v>262</v>
       </c>
-      <c r="D86" s="611"/>
+      <c r="D86" s="642"/>
       <c r="E86" s="612"/>
       <c r="F86" t="str" s="613" cm="1">
         <f t="array" ref="F86">IF($AD86="","",$H86-$G86)</f>
@@ -46422,7 +46456,7 @@
       <c r="C87" t="s" s="354">
         <v>263</v>
       </c>
-      <c r="D87" s="611"/>
+      <c r="D87" s="642"/>
       <c r="E87" s="612"/>
       <c r="F87" t="str" s="613" cm="1">
         <f t="array" ref="F87">IF($AD87="","",$H87-$G87)</f>
@@ -46479,7 +46513,7 @@
       <c r="C88" t="s" s="354">
         <v>264</v>
       </c>
-      <c r="D88" s="611"/>
+      <c r="D88" s="642"/>
       <c r="E88" s="612"/>
       <c r="F88" t="str" s="613" cm="1">
         <f t="array" ref="F88">IF($AD88="","",$H88-$G88)</f>
@@ -46536,7 +46570,7 @@
       <c r="C89" t="s" s="354">
         <v>265</v>
       </c>
-      <c r="D89" s="611"/>
+      <c r="D89" s="642"/>
       <c r="E89" s="612"/>
       <c r="F89" t="str" s="613" cm="1">
         <f t="array" ref="F89">IF($AD89="","",$H89-$G89)</f>
@@ -46593,7 +46627,7 @@
       <c r="C90" t="s" s="354">
         <v>266</v>
       </c>
-      <c r="D90" s="611"/>
+      <c r="D90" s="642"/>
       <c r="E90" s="612"/>
       <c r="F90" t="str" s="613" cm="1">
         <f t="array" ref="F90">IF($AD90="","",$H90-$G90)</f>
@@ -46650,7 +46684,7 @@
       <c r="C91" t="s" s="354">
         <v>234</v>
       </c>
-      <c r="D91" s="611"/>
+      <c r="D91" s="642"/>
       <c r="E91" s="612"/>
       <c r="F91" t="str" s="613" cm="1">
         <f t="array" ref="F91">IF($AD91="","",$H91-$G91)</f>
@@ -46707,7 +46741,7 @@
       <c r="C92" t="s" s="354">
         <v>267</v>
       </c>
-      <c r="D92" s="611"/>
+      <c r="D92" s="642"/>
       <c r="E92" s="612"/>
       <c r="F92" t="str" s="613" cm="1">
         <f t="array" ref="F92">IF($AD92="","",$H92-$G92)</f>
@@ -46764,7 +46798,7 @@
       <c r="C93" t="s" s="354">
         <v>268</v>
       </c>
-      <c r="D93" s="611"/>
+      <c r="D93" s="642"/>
       <c r="E93" s="612"/>
       <c r="F93" t="str" s="613" cm="1">
         <f t="array" ref="F93">IF($AD93="","",$H93-$G93)</f>
@@ -46821,7 +46855,7 @@
       <c r="C94" t="s" s="354">
         <v>269</v>
       </c>
-      <c r="D94" s="611"/>
+      <c r="D94" s="642"/>
       <c r="E94" s="612"/>
       <c r="F94" t="str" s="613" cm="1">
         <f t="array" ref="F94">IF($AD94="","",$H94-$G94)</f>
@@ -46878,7 +46912,7 @@
       <c r="C95" t="s" s="354">
         <v>270</v>
       </c>
-      <c r="D95" s="611"/>
+      <c r="D95" s="642"/>
       <c r="E95" s="612"/>
       <c r="F95" t="str" s="613" cm="1">
         <f t="array" ref="F95">IF($AD95="","",$H95-$G95)</f>
@@ -46937,7 +46971,7 @@
       <c r="C96" t="s" s="354">
         <v>212</v>
       </c>
-      <c r="D96" s="611"/>
+      <c r="D96" s="642"/>
       <c r="E96" s="612"/>
       <c r="F96" t="str" s="613" cm="1">
         <f t="array" ref="F96">IF($AD96="","",$H96-$G96)</f>
@@ -46994,7 +47028,7 @@
       <c r="C97" t="s" s="354">
         <v>215</v>
       </c>
-      <c r="D97" s="611"/>
+      <c r="D97" s="642"/>
       <c r="E97" s="612"/>
       <c r="F97" t="str" s="613" cm="1">
         <f t="array" ref="F97">IF($AD97="","",$H97-$G97)</f>
@@ -47051,7 +47085,7 @@
       <c r="C98" t="s" s="354">
         <v>272</v>
       </c>
-      <c r="D98" s="611"/>
+      <c r="D98" s="642"/>
       <c r="E98" s="612"/>
       <c r="F98" t="str" s="613" cm="1">
         <f t="array" ref="F98">IF($AD98="","",$H98-$G98)</f>
@@ -47108,7 +47142,7 @@
       <c r="C99" t="s" s="354">
         <v>273</v>
       </c>
-      <c r="D99" s="611"/>
+      <c r="D99" s="642"/>
       <c r="E99" s="612"/>
       <c r="F99" t="str" s="613" cm="1">
         <f t="array" ref="F99">IF($AD99="","",$H99-$G99)</f>
@@ -47165,7 +47199,7 @@
       <c r="C100" t="s" s="354">
         <v>179</v>
       </c>
-      <c r="D100" s="611"/>
+      <c r="D100" s="642"/>
       <c r="E100" s="612"/>
       <c r="F100" t="str" s="613" cm="1">
         <f t="array" ref="F100">IF($AD100="","",$H100-$G100)</f>
@@ -47217,7 +47251,7 @@
       <c r="A101" s="282"/>
       <c r="B101" s="282"/>
       <c r="C101" s="353"/>
-      <c r="D101" s="611"/>
+      <c r="D101" s="642"/>
       <c r="E101" s="612"/>
       <c r="F101" t="str" s="613" cm="1">
         <f t="array" ref="F101">IF($AD101="","",$H101-$G101)</f>
@@ -47269,7 +47303,7 @@
       <c r="A102" s="282"/>
       <c r="B102" s="282"/>
       <c r="C102" s="353"/>
-      <c r="D102" s="611"/>
+      <c r="D102" s="642"/>
       <c r="E102" s="612"/>
       <c r="F102" t="str" s="613" cm="1">
         <f t="array" ref="F102">IF($AD102="","",$H102-$G102)</f>
@@ -47321,7 +47355,7 @@
       <c r="A103" s="282"/>
       <c r="B103" s="282"/>
       <c r="C103" s="353"/>
-      <c r="D103" s="611"/>
+      <c r="D103" s="642"/>
       <c r="E103" s="612"/>
       <c r="F103" t="str" s="613" cm="1">
         <f t="array" ref="F103">IF($AD103="","",$H103-$G103)</f>
@@ -47373,7 +47407,7 @@
       <c r="A104" s="282"/>
       <c r="B104" s="282"/>
       <c r="C104" s="353"/>
-      <c r="D104" s="611"/>
+      <c r="D104" s="642"/>
       <c r="E104" s="612"/>
       <c r="F104" t="str" s="613" cm="1">
         <f t="array" ref="F104">IF($AD104="","",$H104-$G104)</f>
@@ -47425,7 +47459,7 @@
       <c r="A105" s="282"/>
       <c r="B105" s="282"/>
       <c r="C105" s="353"/>
-      <c r="D105" s="611"/>
+      <c r="D105" s="642"/>
       <c r="E105" s="612"/>
       <c r="F105" t="str" s="613" cm="1">
         <f t="array" ref="F105">IF($AD105="","",$H105-$G105)</f>
@@ -47477,7 +47511,7 @@
       <c r="A106" s="282"/>
       <c r="B106" s="282"/>
       <c r="C106" s="353"/>
-      <c r="D106" s="611"/>
+      <c r="D106" s="642"/>
       <c r="E106" s="612"/>
       <c r="F106" t="str" s="613" cm="1">
         <f t="array" ref="F106">IF($AD106="","",$H106-$G106)</f>
@@ -47529,7 +47563,7 @@
       <c r="A107" s="282"/>
       <c r="B107" s="282"/>
       <c r="C107" s="353"/>
-      <c r="D107" s="611"/>
+      <c r="D107" s="642"/>
       <c r="E107" s="612"/>
       <c r="F107" t="str" s="613" cm="1">
         <f t="array" ref="F107">IF($AD107="","",$H107-$G107)</f>
@@ -47581,7 +47615,7 @@
       <c r="A108" s="282"/>
       <c r="B108" s="282"/>
       <c r="C108" s="353"/>
-      <c r="D108" s="611"/>
+      <c r="D108" s="642"/>
       <c r="E108" s="612"/>
       <c r="F108" t="str" s="613" cm="1">
         <f t="array" ref="F108">IF($AD108="","",$H108-$G108)</f>
@@ -47633,7 +47667,7 @@
       <c r="A109" s="282"/>
       <c r="B109" s="282"/>
       <c r="C109" s="353"/>
-      <c r="D109" s="611"/>
+      <c r="D109" s="642"/>
       <c r="E109" s="612"/>
       <c r="F109" t="str" s="613" cm="1">
         <f t="array" ref="F109">IF($AD109="","",$H109-$G109)</f>
@@ -47685,7 +47719,7 @@
       <c r="A110" s="282"/>
       <c r="B110" s="282"/>
       <c r="C110" s="353"/>
-      <c r="D110" s="611"/>
+      <c r="D110" s="642"/>
       <c r="E110" s="612"/>
       <c r="F110" t="str" s="613" cm="1">
         <f t="array" ref="F110">IF($AD110="","",$H110-$G110)</f>
@@ -47737,7 +47771,7 @@
       <c r="A111" s="282"/>
       <c r="B111" s="282"/>
       <c r="C111" s="353"/>
-      <c r="D111" s="611"/>
+      <c r="D111" s="642"/>
       <c r="E111" s="612"/>
       <c r="F111" t="str" s="613" cm="1">
         <f t="array" ref="F111">IF($AD111="","",$H111-$G111)</f>
@@ -47789,7 +47823,7 @@
       <c r="A112" s="282"/>
       <c r="B112" s="282"/>
       <c r="C112" s="353"/>
-      <c r="D112" s="611"/>
+      <c r="D112" s="642"/>
       <c r="E112" s="612"/>
       <c r="F112" t="str" s="613" cm="1">
         <f t="array" ref="F112">IF($AD112="","",$H112-$G112)</f>
@@ -47841,7 +47875,7 @@
       <c r="A113" s="282"/>
       <c r="B113" s="282"/>
       <c r="C113" s="353"/>
-      <c r="D113" s="611"/>
+      <c r="D113" s="642"/>
       <c r="E113" s="612"/>
       <c r="F113" t="str" s="613" cm="1">
         <f t="array" ref="F113">IF($AD113="","",$H113-$G113)</f>
@@ -47893,7 +47927,7 @@
       <c r="A114" s="282"/>
       <c r="B114" s="282"/>
       <c r="C114" s="353"/>
-      <c r="D114" s="611"/>
+      <c r="D114" s="642"/>
       <c r="E114" s="612"/>
       <c r="F114" t="str" s="613" cm="1">
         <f t="array" ref="F114">IF($AD114="","",$H114-$G114)</f>
@@ -47945,7 +47979,7 @@
       <c r="A115" s="282"/>
       <c r="B115" s="282"/>
       <c r="C115" s="353"/>
-      <c r="D115" s="611"/>
+      <c r="D115" s="642"/>
       <c r="E115" s="612"/>
       <c r="F115" t="str" s="613" cm="1">
         <f t="array" ref="F115">IF($AD115="","",$H115-$G115)</f>
@@ -47997,7 +48031,7 @@
       <c r="A116" s="282"/>
       <c r="B116" s="282"/>
       <c r="C116" s="353"/>
-      <c r="D116" s="611"/>
+      <c r="D116" s="642"/>
       <c r="E116" s="612"/>
       <c r="F116" t="str" s="613" cm="1">
         <f t="array" ref="F116">IF($AD116="","",$H116-$G116)</f>
@@ -48049,7 +48083,7 @@
       <c r="A117" s="282"/>
       <c r="B117" s="282"/>
       <c r="C117" s="353"/>
-      <c r="D117" s="611"/>
+      <c r="D117" s="642"/>
       <c r="E117" s="612"/>
       <c r="F117" t="str" s="613" cm="1">
         <f t="array" ref="F117">IF($AD117="","",$H117-$G117)</f>
@@ -48101,7 +48135,7 @@
       <c r="A118" s="282"/>
       <c r="B118" s="282"/>
       <c r="C118" s="353"/>
-      <c r="D118" s="611"/>
+      <c r="D118" s="642"/>
       <c r="E118" s="612"/>
       <c r="F118" t="str" s="613" cm="1">
         <f t="array" ref="F118">IF($AD118="","",$H118-$G118)</f>
@@ -48153,7 +48187,7 @@
       <c r="A119" s="282"/>
       <c r="B119" s="282"/>
       <c r="C119" s="353"/>
-      <c r="D119" s="611"/>
+      <c r="D119" s="642"/>
       <c r="E119" s="612"/>
       <c r="F119" t="str" s="613" cm="1">
         <f t="array" ref="F119">IF($AD119="","",$H119-$G119)</f>
@@ -48205,7 +48239,7 @@
       <c r="A120" s="282"/>
       <c r="B120" s="282"/>
       <c r="C120" s="353"/>
-      <c r="D120" s="611"/>
+      <c r="D120" s="642"/>
       <c r="E120" s="612"/>
       <c r="F120" t="str" s="613" cm="1">
         <f t="array" ref="F120">IF($AD120="","",$H120-$G120)</f>
@@ -48257,7 +48291,7 @@
       <c r="A121" s="282"/>
       <c r="B121" s="282"/>
       <c r="C121" s="353"/>
-      <c r="D121" s="611"/>
+      <c r="D121" s="642"/>
       <c r="E121" s="612"/>
       <c r="F121" t="str" s="613" cm="1">
         <f t="array" ref="F121">IF($AD121="","",$H121-$G121)</f>
@@ -48309,7 +48343,7 @@
       <c r="A122" s="282"/>
       <c r="B122" s="282"/>
       <c r="C122" s="353"/>
-      <c r="D122" s="611"/>
+      <c r="D122" s="642"/>
       <c r="E122" s="612"/>
       <c r="F122" t="str" s="613" cm="1">
         <f t="array" ref="F122">IF($AD122="","",$H122-$G122)</f>
@@ -48361,7 +48395,7 @@
       <c r="A123" s="282"/>
       <c r="B123" s="282"/>
       <c r="C123" s="353"/>
-      <c r="D123" s="611"/>
+      <c r="D123" s="642"/>
       <c r="E123" s="612"/>
       <c r="F123" t="str" s="613" cm="1">
         <f t="array" ref="F123">IF($AD123="","",$H123-$G123)</f>
@@ -48413,7 +48447,7 @@
       <c r="A124" s="282"/>
       <c r="B124" s="282"/>
       <c r="C124" s="353"/>
-      <c r="D124" s="611"/>
+      <c r="D124" s="642"/>
       <c r="E124" s="612"/>
       <c r="F124" t="str" s="613" cm="1">
         <f t="array" ref="F124">IF($AD124="","",$H124-$G124)</f>
@@ -48465,7 +48499,7 @@
       <c r="A125" s="282"/>
       <c r="B125" s="282"/>
       <c r="C125" s="353"/>
-      <c r="D125" s="611"/>
+      <c r="D125" s="642"/>
       <c r="E125" s="612"/>
       <c r="F125" t="str" s="613" cm="1">
         <f t="array" ref="F125">IF($AD125="","",$H125-$G125)</f>
@@ -48517,7 +48551,7 @@
       <c r="A126" s="282"/>
       <c r="B126" s="282"/>
       <c r="C126" s="353"/>
-      <c r="D126" s="611"/>
+      <c r="D126" s="642"/>
       <c r="E126" s="612"/>
       <c r="F126" t="str" s="613" cm="1">
         <f t="array" ref="F126">IF($AD126="","",$H126-$G126)</f>
@@ -48569,7 +48603,7 @@
       <c r="A127" s="282"/>
       <c r="B127" s="282"/>
       <c r="C127" s="353"/>
-      <c r="D127" s="611"/>
+      <c r="D127" s="642"/>
       <c r="E127" s="612"/>
       <c r="F127" t="str" s="613" cm="1">
         <f t="array" ref="F127">IF($AD127="","",$H127-$G127)</f>
@@ -48621,7 +48655,7 @@
       <c r="A128" s="282"/>
       <c r="B128" s="282"/>
       <c r="C128" s="353"/>
-      <c r="D128" s="611"/>
+      <c r="D128" s="642"/>
       <c r="E128" s="612"/>
       <c r="F128" t="str" s="613" cm="1">
         <f t="array" ref="F128">IF($AD128="","",$H128-$G128)</f>
@@ -48673,7 +48707,7 @@
       <c r="A129" s="282"/>
       <c r="B129" s="282"/>
       <c r="C129" s="353"/>
-      <c r="D129" s="611"/>
+      <c r="D129" s="642"/>
       <c r="E129" s="612"/>
       <c r="F129" t="str" s="613" cm="1">
         <f t="array" ref="F129">IF($AD129="","",$H129-$G129)</f>
@@ -48725,7 +48759,7 @@
       <c r="A130" s="282"/>
       <c r="B130" s="282"/>
       <c r="C130" s="353"/>
-      <c r="D130" s="611"/>
+      <c r="D130" s="642"/>
       <c r="E130" s="612"/>
       <c r="F130" t="str" s="613" cm="1">
         <f t="array" ref="F130">IF($AD130="","",$H130-$G130)</f>
@@ -48777,7 +48811,7 @@
       <c r="A131" s="282"/>
       <c r="B131" s="282"/>
       <c r="C131" s="353"/>
-      <c r="D131" s="611"/>
+      <c r="D131" s="642"/>
       <c r="E131" s="612"/>
       <c r="F131" t="str" s="613" cm="1">
         <f t="array" ref="F131">IF($AD131="","",$H131-$G131)</f>
@@ -48829,7 +48863,7 @@
       <c r="A132" s="282"/>
       <c r="B132" s="282"/>
       <c r="C132" s="353"/>
-      <c r="D132" s="611"/>
+      <c r="D132" s="642"/>
       <c r="E132" s="612"/>
       <c r="F132" t="str" s="613" cm="1">
         <f t="array" ref="F132">IF($AD132="","",$H132-$G132)</f>
@@ -48881,7 +48915,7 @@
       <c r="A133" s="282"/>
       <c r="B133" s="282"/>
       <c r="C133" s="353"/>
-      <c r="D133" s="611"/>
+      <c r="D133" s="642"/>
       <c r="E133" s="612"/>
       <c r="F133" t="str" s="613" cm="1">
         <f t="array" ref="F133">IF($AD133="","",$H133-$G133)</f>
@@ -48933,7 +48967,7 @@
       <c r="A134" s="282"/>
       <c r="B134" s="282"/>
       <c r="C134" s="353"/>
-      <c r="D134" s="611"/>
+      <c r="D134" s="642"/>
       <c r="E134" s="612"/>
       <c r="F134" t="str" s="613" cm="1">
         <f t="array" ref="F134">IF($AD134="","",$H134-$G134)</f>
@@ -48985,7 +49019,7 @@
       <c r="A135" s="282"/>
       <c r="B135" s="282"/>
       <c r="C135" s="353"/>
-      <c r="D135" s="611"/>
+      <c r="D135" s="642"/>
       <c r="E135" s="612"/>
       <c r="F135" t="str" s="613" cm="1">
         <f t="array" ref="F135">IF($AD135="","",$H135-$G135)</f>
@@ -49037,7 +49071,7 @@
       <c r="A136" s="282"/>
       <c r="B136" s="282"/>
       <c r="C136" s="353"/>
-      <c r="D136" s="611"/>
+      <c r="D136" s="642"/>
       <c r="E136" s="612"/>
       <c r="F136" t="str" s="613" cm="1">
         <f t="array" ref="F136">IF($AD136="","",$H136-$G136)</f>
@@ -49089,7 +49123,7 @@
       <c r="A137" s="282"/>
       <c r="B137" s="282"/>
       <c r="C137" s="353"/>
-      <c r="D137" s="611"/>
+      <c r="D137" s="642"/>
       <c r="E137" s="612"/>
       <c r="F137" t="str" s="613" cm="1">
         <f t="array" ref="F137">IF($AD137="","",$H137-$G137)</f>
@@ -49141,7 +49175,7 @@
       <c r="A138" s="282"/>
       <c r="B138" s="282"/>
       <c r="C138" s="353"/>
-      <c r="D138" s="611"/>
+      <c r="D138" s="642"/>
       <c r="E138" s="612"/>
       <c r="F138" t="str" s="613" cm="1">
         <f t="array" ref="F138">IF($AD138="","",$H138-$G138)</f>
@@ -49193,7 +49227,7 @@
       <c r="A139" s="282"/>
       <c r="B139" s="282"/>
       <c r="C139" s="353"/>
-      <c r="D139" s="611"/>
+      <c r="D139" s="642"/>
       <c r="E139" s="612"/>
       <c r="F139" t="str" s="613" cm="1">
         <f t="array" ref="F139">IF($AD139="","",$H139-$G139)</f>
@@ -49245,7 +49279,7 @@
       <c r="A140" s="282"/>
       <c r="B140" s="282"/>
       <c r="C140" s="353"/>
-      <c r="D140" s="611"/>
+      <c r="D140" s="642"/>
       <c r="E140" s="612"/>
       <c r="F140" t="str" s="613" cm="1">
         <f t="array" ref="F140">IF($AD140="","",$H140-$G140)</f>
@@ -49297,7 +49331,7 @@
       <c r="A141" s="309"/>
       <c r="B141" s="309"/>
       <c r="C141" s="309"/>
-      <c r="D141" s="635"/>
+      <c r="D141" s="644"/>
       <c r="E141" s="635"/>
       <c r="F141" s="635"/>
       <c r="G141" s="635"/>
@@ -49343,7 +49377,7 @@
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
-      <c r="D142" s="368"/>
+      <c r="D142" s="645"/>
       <c r="E142" s="368"/>
       <c r="F142" s="368"/>
       <c r="G142" s="368"/>
@@ -49389,7 +49423,7 @@
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
-      <c r="D143" s="368"/>
+      <c r="D143" s="645"/>
       <c r="E143" s="368"/>
       <c r="F143" s="368"/>
       <c r="G143" s="368"/>
@@ -49435,7 +49469,7 @@
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
-      <c r="D144" s="368"/>
+      <c r="D144" s="645"/>
       <c r="E144" s="368"/>
       <c r="F144" s="368"/>
       <c r="G144" s="368"/>
@@ -49481,7 +49515,7 @@
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
-      <c r="D145" s="368"/>
+      <c r="D145" s="645"/>
       <c r="E145" s="368"/>
       <c r="F145" s="368"/>
       <c r="G145" s="368"/>
@@ -49527,7 +49561,7 @@
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
-      <c r="D146" s="368"/>
+      <c r="D146" s="645"/>
       <c r="E146" s="368"/>
       <c r="F146" s="368"/>
       <c r="G146" s="368"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -11695,7 +11695,9 @@
         <f t="array" ref="F19">IF(I19="","",I19-H19)</f>
         <v>46300</v>
       </c>
-      <c r="G19" s="505"/>
+      <c r="G19" s="505">
+        <v>46304</v>
+      </c>
       <c r="H19" s="503">
         <v>7</v>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -10998,14 +10998,13 @@
       </c>
       <c r="D12" s="510" cm="1">
         <f t="array" ref="D12">IF(F12="","",F12-E12)</f>
-        <v>46304</v>
+        <v>46293</v>
       </c>
       <c r="E12" s="503">
         <v>7</v>
       </c>
-      <c r="F12" s="506" cm="1">
-        <f t="array" ref="F12">IF(I12="","",I12-H12)</f>
-        <v>46311</v>
+      <c r="F12" s="506">
+        <v>46300</v>
       </c>
       <c r="G12" s="505">
         <v>46301</v>
@@ -11477,8 +11476,7 @@
       <c r="E17" s="503">
         <v>7</v>
       </c>
-      <c r="F17" s="506" cm="1">
-        <f t="array" ref="F17">IF(I17="","",I17-H17)</f>
+      <c r="F17" s="506">
         <v>46308</v>
       </c>
       <c r="G17" s="505"/>
@@ -11579,14 +11577,13 @@
       </c>
       <c r="D18" s="510" cm="1">
         <f t="array" ref="D18">IF(F18="","",F18-E18)</f>
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="E18" s="503">
         <v>7</v>
       </c>
-      <c r="F18" s="506" cm="1">
-        <f t="array" ref="F18">IF(I18="","",I18-H18)</f>
-        <v>46321</v>
+      <c r="F18" s="506">
+        <v>46324</v>
       </c>
       <c r="G18" s="505"/>
       <c r="H18" s="503">
@@ -11686,14 +11683,13 @@
       </c>
       <c r="D19" s="510" cm="1">
         <f t="array" ref="D19">IF(F19="","",F19-E19)</f>
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="E19" s="503">
         <v>7</v>
       </c>
-      <c r="F19" s="506" cm="1">
-        <f t="array" ref="F19">IF(I19="","",I19-H19)</f>
-        <v>46300</v>
+      <c r="F19" s="506">
+        <v>46304</v>
       </c>
       <c r="G19" s="505">
         <v>46304</v>
@@ -11797,14 +11793,13 @@
       </c>
       <c r="D20" s="510" cm="1">
         <f t="array" ref="D20">IF(F20="","",F20-E20)</f>
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="E20" s="503">
         <v>7</v>
       </c>
-      <c r="F20" s="506" cm="1">
-        <f t="array" ref="F20">IF(I20="","",I20-H20)</f>
-        <v>46325</v>
+      <c r="F20" s="506">
+        <v>46318</v>
       </c>
       <c r="G20" s="505"/>
       <c r="H20" s="503">

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -23091,11 +23091,6 @@
       <formula>NOT(ISBLANK(E11))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11:O11 AI11:AL11 J12 L12:O12 AE12 AI12:AL12 J13 L13:O13 AE13 AI13:AL13 J14 L14:O14 AE14 AI14:AL14 J15 L15:O15 AE15 AI15:AL15 J16 L16:O16 AE16 AI16:AL16 J17 L17:O17 AE17 AI17:AL17 J18 L18:O18 AE18 AI18:AL18 J19 L19:O19 AE19 AI19:AL19 J20 L20:O20 AE20 AI20:AL20 J21 L21:O21 AE21 AI21:AL21 J22 L22:O22 AE22 AI22:AL22 J23 L23:O23 AE23 AI23:AL23 J24 L24:O24 AE24 AI24:AL24 J25 L25:O25 AE25 AI25:AL25 J26 L26:O26 AE26 AI26:AL26 J27 L27:O27 AE27 AI27:AL27 J28 L28:O28 AE28 AI28:AL28 J29 L29:O29 AE29 AI29:AL29 J30 L30:O30 AE30 AI30:AL30 J31 L31:O31 AE31 AI31:AL31 J32 L32:O32 AE32 AI32:AL32 J33 L33:O33 AE33 AI33:AL33 J34 L34:O34 AE34 AI34:AL34 J35 L35:O35 AE35 AI35:AL35 J36 L36:O36 AE36 AI36:AL36 J37 L37:O37 AE37 AI37:AL37 J38 L38:O38 AE38 AI38:AL38 J39 L39:O39 AE39 AI39:AL39 J40 L40:O40 AE40 AI40:AL40 J41 L41:O41 AE41 AI41:AL41 J42 L42:O42 AE42 AI42:AL42 J43 L43:O43 AE43 AI43:AL43 J44 L44:O44 AE44 AI44:AL44 J45 L45:O45 AE45 AI45:AL45 J46 L46:O46 AE46 AI46:AL46 J47 L47:O47 AE47 AI47:AL47 J48 L48:O48 AE48 AI48:AL48 J49 L49:O49 AE49 AI49:AL49 J50 L50:O50 AE50 AI50:AL50 J51 L51:O51 AE51 AI51:AL51 J52 L52:O52 AE52 AI52:AL52 J53 L53:O53 AE53 AI53:AL53 J54 L54:O54 AE54 AI54:AL54 J55 L55:O55 AE55 AI55:AL55 J56 L56:O56 AE56 AI56:AL56 J57 L57:O57 AE57 AI57:AL57 J58 L58:O58 AE58 AI58:AL58 J59 L59:O59 AE59 AI59:AL59 J60 L60:O60 AE60 AI60:AL60 J61 L61:O61 AE61 AI61:AL61 J62 L62:O62 AE62 AI62:AL62 J63 L63:O63 AE63 AI63:AL63 J64 L64:O64 AE64 AI64:AL64 J65 L65:O65 AE65 AI65:AL65 J66 L66:O66 AE66 AI66:AL66 J67 L67:O67 AE67 AI67:AL67 J68 L68:O68 AE68 AI68:AL68 J69 L69:O69 AE69 AI69:AL69 J70 L70:O70 AE70 AI70:AL70 J71 L71:O71 AE71 AI71:AL71 J72 L72:O72 AE72 AI72:AL72 J73 L73:O73 AE73 AI73:AL73 J74 L74:O74 AE74 AI74:AL74 J75 L75:O75 AE75 AI75:AL75 J76 L76:O76 AE76 AI76:AL76 J77 L77:O77 AE77 AI77:AL77 J78 L78:O78 AE78 AI78:AL78 J79 L79:O79 AE79 AI79:AL79 J80 L80:O80 AE80 AI80:AL80 J81 L81:O81 AE81 AI81:AL81 J82 L82:O82 AE82 AI82:AL82 J83 L83:O83 AE83 AI83:AL83 J84 L84:O84 AE84 AI84:AL84 J85 L85:O85 AE85 AI85:AL85 J86 L86:O86 AE86 AI86:AL86 J87 L87:O87 AE87 AI87:AL87 J88 L88:O88 AE88 AI88:AL88 J89 L89:O89 AE89 AI89:AL89 J90 L90:O90 AE90 AI90:AL90 J91 L91:O91 AE91 AI91:AL91 J92 L92:O92 AE92 AI92:AL92 J93 L93:O93 AE93 AI93:AL93 J94 L94:O94 AE94 AI94:AL94 J95 L95:O95 AE95 AI95:AL95 J96 L96:O96 AE96 AI96:AL96 J97 L97:O97 AE97 AI97:AL97 J98 L98:O98 AE98 AI98:AL98 J99 L99:O99 AE99 AI99:AL99 J100 L100:O100 AE100 AI100:AL100 J101 L101:O101 AE101 AI101:AL101 J102 L102:O102 AE102 AI102:AL102 J103 L103:O103 AE103 AI103:AL103 J104 L104:O104 AE104 AI104:AL104 J105 L105:O105 AE105 AI105:AL105 J106 L106:O106 AE106 AI106:AL106 J107 L107:O107 AE107 AI107:AL107 J108 L108:O108 AE108 AI108:AL108 J109 L109:O109 AE109 AI109:AL109 J110 L110:O110 AE110 AI110:AL110 J111 L111:O111 AE111 AI111:AL111 J112 L112:O112 AE112 AI112:AL112 J113 L113:O113 AE113 AI113:AL113 J114 L114:O114 AE114 AI114:AL114 J115 L115:O115 AE115 AI115:AL115 J116 L116:O116 AE116 AI116:AL116 J117 L117:O117 AE117 AI117:AL117 J118 L118:O118 AE118 AI118:AL118 J119 L119:O119 AE119 AI119:AL119 J120 L120:O120 AE120 AI120:AL120 J121 L121:O121 AE121 AI121:AL121 J122 L122:O122 AE122 AI122:AL122 J123 L123:O123 AE123 AI123:AL123 J124 L124:O124 AE124 AI124:AL124 J125 L125:O125 AE125 AI125:AL125 J126 L126:O126 AE126 AI126:AL126 J127 L127:O127 AE127 AI127:AL127 J128 L128:O128 AE128 AI128:AL128 J129 L129:O129 AE129 AI129:AL129 J130 L130:O130 AE130 AI130:AL130 J131 L131:O131 AE131 AI131:AL131 J132 L132:O132 AE132 AI132:AL132 J133 L133:O133 AE133 AI133:AL133 J134 L134:O134 AE134 AI134:AL134 J135 L135:O135 AE135 AI135:AL135 J136 L136:O136 AE136 AI136:AL136 J137 L137:O137 AE137 AI137:AL137 J138 L138:O138 AE138 AI138:AL138 J139 L139:O139 AE139 AI139:AL139 J140 L140:O140 AE140 AI140:AL140 J141 L141:O141 AE141 AI141:AL141 J142 L142:O142 AE142 AI142:AL142 J143 L143:O143 AE143 AI143:AL143 J144 L144:O144 AE144 AI144:AL144 J145 L145:O145 AE145 AI145:AL145 J146 L146:O146 AE146 AI146:AL146 J147 L147:O147 AE147 AI147:AL147 J148 L148:O148 AE148 AI148:AL148 J149 L149:O149 AE149 AI149:AL149 J150 L150:O150 AE150 AI150:AL150 J151 L151:O151 AE151 AI151:AL151 J152 L152:O152 AE152 AI152:AL152 J153 L153:O153 AE153 AI153:AL153 J154 L154:O154 AE154 AI154:AL154 J155 L155:O155 AE155 AI155:AL155 J156 L156:O156 AE156 AI156:AL156 J157 L157:O157 AE157 AI157:AL157 J158 L158:O158 AE158 AI158:AL158 J159 L159:O159 AE159 AI159:AL159">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>NOT(ISBLANK(M11))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="S11:AB159">
     <cfRule type="notContainsBlanks" dxfId="3" priority="4" stopIfTrue="1">
       <formula>NOT(ISBLANK(S11))</formula>
@@ -40963,11 +40958,6 @@
     <mergeCell ref="AB5:AB9"/>
     <mergeCell ref="AP2:BD2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D11 G11 J11 L11 AE11 AI11:AL11 D12 G12 J12 L12:O12 AE12 AI12:AL12 D13 G13 J13 L13:O13 AE13 AI13:AL13 D14 G14 J14 L14:O14 AE14 AI14:AL14 D15 G15 J15 L15:O15 AE15 AI15:AL15 D16 G16 J16 L16:O16 AE16 AI16:AL16 D17 G17 J17 L17:O17 AE17 AI17:AL17 D18 G18 J18 L18:O18 AE18 AI18:AL18 D19 G19 J19 L19:O19 AE19 AI19:AL19 D20 G20 J20 L20:O20 AE20 AI20:AL20 D21 G21 J21 L21:O21 AE21 AI21:AL21 D22 G22 J22 L22:O22 AE22 AI22:AL22 D23 G23 J23 L23:O23 AE23 AI23:AL23 D24 G24 J24 L24:O24 AE24 AI24:AL24 D25 G25 J25 L25:O25 AE25 AI25:AL25 D26 G26 J26 L26:O26 AE26 AI26:AL26 D27 G27 J27 L27:O27 AE27 AI27:AL27 D28 G28 J28 L28:O28 AE28 AI28:AL28 D29 G29 J29 L29:O29 AE29 AI29:AL29 D30 G30 J30 L30:O30 AE30 AI30:AL30 D31 G31 J31 L31:O31 AE31 AI31:AL31 D32 G32 J32 L32:O32 AE32 AI32:AL32 D33 G33 J33 L33:O33 AE33 AI33:AL33 D34 G34 J34 L34:O34 AE34 AI34:AL34 D35 G35 J35 L35:O35 AE35 AI35:AL35 D36 G36 J36 L36:O36 AE36 AI36:AL36 D37 G37 J37 L37:O37 AE37 AI37:AL37 D38 G38 J38 L38:O38 AE38 AI38:AL38 D39 G39 J39 L39:O39 AE39 AI39:AL39 D40 G40 J40 L40:O40 AE40 AI40:AL40 D41 G41 J41 L41:O41 AE41 AI41:AL41 D42 G42 J42 L42:O42 AE42 AI42:AL42 D43 G43 J43 L43:O43 AE43 AI43:AL43 D44 G44 J44 L44:O44 AE44 AI44:AL44 D45 G45 J45 L45:O45 AE45 AI45:AL45 D46 G46 J46 L46:O46 AE46 AI46:AL46 D47 G47 J47 L47:O47 AE47 AI47:AL47 D48 G48 J48 L48:O48 AE48 AI48:AL48 D49 G49 J49 L49:O49 AE49 AI49:AL49 D50 G50 J50 L50:O50 AE50 AI50:AL50 D51 G51 J51 L51:O51 AE51 AI51:AL51 D52 G52 J52 L52:O52 AE52 AI52:AL52 D53 G53 J53 L53:O53 AE53 AI53:AL53 D54 G54 J54 L54:O54 AE54 AI54:AL54 D55 G55 J55 L55:O55 AE55 AI55:AL55 D56 G56 J56 L56:O56 AE56 AI56:AL56 D57 G57 J57 L57:O57 AE57 AI57:AL57 D58 G58 J58 L58:O58 AE58 AI58:AL58 D59 G59 J59 L59:O59 AE59 AI59:AL59 D60 G60 J60 L60:O60 AE60 AI60:AL60 D61 G61 J61 L61:O61 AE61 AI61:AL61 D62 G62 J62 L62:O62 AE62 AI62:AL62 D63 G63 J63 L63:O63 AE63 AI63:AL63 D64 G64 J64 L64:O64 AE64 AI64:AL64 D65 G65 J65 L65:O65 AE65 AI65:AL65 D66 G66 J66 L66:O66 AE66 AI66:AL66 D67 G67 J67 L67:O67 AE67 AI67:AL67 D68 G68 J68 L68:O68 AE68 AI68:AL68 D69 G69 J69 L69:O69 AE69 AI69:AL69 D70 G70 J70 L70:O70 AE70 AI70:AL70 D71 G71 J71 L71:O71 AE71 AI71:AL71 D72 G72 J72 L72:O72 AE72 AI72:AL72 D73 G73 J73 L73:O73 AE73 AI73:AL73 D74 G74 J74 L74:O74 AE74 AI74:AL74 D75 G75 J75 L75:O75 AE75 AI75:AL75 D76 G76 J76 L76:O76 AE76 AI76:AL76 D77 G77 J77 L77:O77 AE77 AI77:AL77 D78 G78 J78 L78:O78 AE78 AI78:AL78 D79 G79 J79 L79:O79 AE79 AI79:AL79 D80 G80 J80 L80:O80 AE80 AI80:AL80 D81 G81 J81 L81:O81 AE81 AI81:AL81 D82 G82 J82 L82:O82 AE82 AI82:AL82 D83 G83 J83 L83:O83 AE83 AI83:AL83 D84 G84 J84 L84:O84 AE84 AI84:AL84 D85 G85 J85 L85:O85 AE85 AI85:AL85 D86 G86 J86 L86:O86 AE86 AI86:AL86 D87 G87 J87 L87:O87 AE87 AI87:AL87 D88 G88 J88 L88:O88 AE88 AI88:AL88 D89 G89 J89 L89:O89 AE89 AI89:AL89 D90 G90 J90 L90:O90 AE90 AI90:AL90 D91 G91 J91 L91:O91 AE91 AI91:AL91 D92 G92 J92 L92:O92 AE92 AI92:AL92 D93 G93 J93 L93:O93 AE93 AI93:AL93 D94 G94 J94 L94:O94 AE94 AI94:AL94 D95 G95 J95 L95:O95 AE95 AI95:AL95 D96 G96 J96 L96:O96 AE96 AI96:AL96 D97 G97 J97 L97:O97 AE97 AI97:AL97 D98 G98 J98 L98:O98 AE98 AI98:AL98 D99 G99 J99 L99:O99 AE99 AI99:AL99 D100 G100 J100 L100:O100 AE100 AI100:AL100 D101 G101 J101 L101:O101 AE101 AI101:AL101 D102 G102 J102 L102:O102 AE102 AI102:AL102 D103 G103 J103 L103:O103 AE103 AI103:AL103 D104 G104 J104 L104:O104 AE104 AI104:AL104 D105 G105 J105 L105:O105 AE105 AI105:AL105 D106 G106 J106 L106:O106 AE106 AI106:AL106 D107 G107 J107 L107:O107 AE107 AI107:AL107 D108 G108 J108 L108:O108 AE108 AI108:AL108 D109 G109 J109 L109:O109 AE109 AI109:AL109 D110 G110 J110 L110:O110 AE110 AI110:AL110 D111 G111 J111 L111:O111 AE111 AI111:AL111 D112 G112 J112 L112:O112 AE112 AI112:AL112 D113 G113 J113 L113:O113 AE113 AI113:AL113 D114 G114 J114 L114:O114 AE114 AI114:AL114 D115 G115 J115 L115:O115 AE115 AI115:AL115 D116 G116 J116 L116:O116 AE116 AI116:AL116 D117 G117 J117 L117:O117 AE117 AI117:AL117 D118 G118 J118 L118:O118 AE118 AI118:AL118 D119 G119 J119 L119:O119 AE119 AI119:AL119 D120 G120 J120 L120:O120 AE120 AI120:AL120 D121 G121 J121 L121:O121 AE121 AI121:AL121 D122 G122 J122 L122:O122 AE122 AI122:AL122 D123 G123 J123 L123:O123 AE123 AI123:AL123 D124 G124 J124 L124:O124 AE124 AI124:AL124 D125 G125 J125 L125:O125 AE125 AI125:AL125 D126 G126 J126 L126:O126 AE126 AI126:AL126 D127 G127 J127 L127:O127 AE127 AI127:AL127 D128 G128 J128 L128:O128 AE128 AI128:AL128 D129 G129 J129 L129:O129 AE129 AI129:AL129 D130 G130 J130 L130:O130 AE130 AI130:AL130 D131 G131 J131 L131:O131 AE131 AI131:AL131 D132 G132 J132 L132:O132 AE132 AI132:AL132 D133 G133 J133 L133:O133 AE133 AI133:AL133 D134 G134 J134 L134:O134 AE134 AI134:AL134 D135 G135 J135 L135:O135 AE135 AI135:AL135 D136 G136 J136 L136:O136 AE136 AI136:AL136 D137 G137 J137 L137:O137 AE137 AI137:AL137 D138 G138 J138 L138:O138 AE138 AI138:AL138 D139 G139 J139 L139:O139 AE139 AI139:AL139 D140 G140 J140 L140:O140 AE140 AI140:AL140 D141 G141 J141 L141:O141 AE141 AI141:AL141 D142 G142 J142 L142:O142 AE142 AI142:AL142 D143 G143 J143 L143:O143 AE143 AI143:AL143 D144 G144 J144 L144:O144 AE144 AI144:AL144 D145 G145 J145 L145:O145 AE145 AI145:AL145 D146 G146 J146 L146:O146 AE146 AI146:AL146 D147 G147 J147 L147:O147 AE147 AI147:AL147 D148 G148 J148 L148:O148 AE148 AI148:AL148 D149 G149 J149 L149:O149 AE149 AI149:AL149 D150 G150 J150 L150:O150 AE150 AI150:AL150 D151 G151 J151 L151:O151 AE151 AI151:AL151 D152 G152 J152 L152:O152 AE152 AI152:AL152 D153 G153 J153 L153:O153 AE153 AI153:AL153 D154 G154 J154 L154:O154 AE154 AI154:AL154 D155 G155 J155 L155:O155 AE155 AI155:AL155 D156 G156 J156 L156:O156 AE156 AI156:AL156 D157 G157 J157 L157:O157 AE157 AI157:AL157 D158 G158 J158 L158:O158 AE158 AI158:AL158 D159 G159 J159 L159:O159 AE159 AI159:AL159 D160 G160 J160 L160:O160 AE160 AI160:AL160 D161 G161 J161 L161:O161 AE161 AI161:AL161 D162 G162 J162 L162:O162 AE162 AI162:AL162 D163 G163 J163 L163:O163 AE163 AI163:AL163 D164 G164 J164 L164:O164 AE164 AI164:AL164 D165 G165 J165 L165:O165 AE165 AI165:AL165 D166 G166 J166 L166:O166 AE166 AI166:AL166 D167 G167 J167 L167:O167 AE167 AI167:AL167 D168 G168 J168 L168:O168 AE168 AI168:AL168 D169 G169 J169 L169:O169 AE169 AI169:AL169 D170 G170 J170 L170:O170 AE170 AI170:AL170 D171 G171 J171 L171:O171 AE171 AI171:AL171 D172 G172 J172 L172:O172 AE172 AI172:AL172 D173 G173 J173 L173:O173 AE173 AI173:AL173 D174 G174 J174 L174:O174 AE174 AI174:AL174 D175 G175 J175 L175:O175 AE175 AI175:AL175 D176 G176 J176 L176:O176 AE176 AI176:AL176 D177 G177 J177 L177:O177 AE177 AI177:AL177 D178 G178 J178 L178:O178 AE178 AI178:AL178 D179 G179 J179 L179:O179 AE179 AI179:AL179 D180 G180 J180 L180:O180 AE180 AI180:AL180 D181 G181 J181 L181:O181 AE181 AI181:AL181 D182 G182 J182 L182:O182 AE182 AI182:AL182 D183 G183 J183 L183:O183 AE183 AI183:AL183 D184 G184 J184 L184:O184 AE184 AI184:AL184 D185 G185 J185 L185:O185 AE185 AI185:AL185 D186 G186 J186 L186:O186 AE186 AI186:AL186 D187 G187 J187 L187:O187 AE187 AI187:AL187 D188 G188 J188 L188:O188 AE188 AI188:AL188 D189 G189 J189 L189:O189 AE189 AI189:AL189 D190 G190 J190 L190:O190 AE190 AI190:AL190 D191 G191 J191 L191:O191 AE191 AI191:AL191 D192 G192 J192 L192:O192 AE192 AI192:AL192 D193 G193 J193 L193:O193 AE193 AI193:AL193 D194 G194 J194 L194:O194 AE194 AI194:AL194 D195 G195 J195 L195:O195 AE195 AI195:AL195 D196 G196 J196 L196:O196 AE196 AI196:AL196 D197 G197 J197 L197:O197 AE197 AI197:AL197 D198 G198 J198 L198:O198 AE198 AI198:AL198 D199 G199 J199 L199:O199 AE199 AI199:AL199 D200 G200 J200 L200:O200 AE200 AI200:AL200 D201 G201 J201 L201:O201 AE201 AI201:AL201 D202 G202 J202 L202:O202 AE202 AI202:AL202 D203 G203 J203 L203:O203 AE203 AI203:AL203 D204 G204 J204 L204:O204 AE204 AI204:AL204 D205 G205 J205 L205:O205 AE205 AI205:AL205 D206 G206 J206 L206:O206 AE206 AI206:AL206 D207 G207 J207 L207:O207 AE207 AI207:AL207 D208 G208 J208 L208:O208 AE208 AI208:AL208 D209 G209 J209 L209:O209 AE209 AI209:AL209 D210 G210 J210 L210:O210 AE210 AI210:AL210">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="1" stopIfTrue="1">
-      <formula>NOT(ISBLANK(D11))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H11 K11 Q11:R11">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan" stopIfTrue="1">
       <formula>0</formula>
@@ -40977,14 +40967,6 @@
     </cfRule>
     <cfRule type="notContainsBlanks" dxfId="7" priority="4" stopIfTrue="1">
       <formula>NOT(ISBLANK(H11))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M11:O11">
-    <cfRule type="notContainsBlanks" dxfId="8" priority="5" stopIfTrue="1">
-      <formula>NOT(ISBLANK(M11))</formula>
-    </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="9" priority="6" stopIfTrue="1">
-      <formula>NOT(ISBLANK(M11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:AB11">
@@ -49658,11 +49640,6 @@
     <mergeCell ref="U5:U6"/>
     <mergeCell ref="V5:V6"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7 I7 K7:N7 AB7 E8 I8 K8:N8 AB8 E9 I9 K9:N9 AB9 E10 I10 K10:N10 AB10 E11 I11 K11:N11 AB11 E12 I12 K12:N12 AB12 E13 I13 K13:N13 AB13 E14 I14 K14:N14 AB14 E15 I15 K15:N15 AB15 E16 I16 K16:N16 AB16 E17 I17 K17:N17 AB17 E18 I18 K18:N18 AB18 E19 I19 K19:N19 AB19 E20 I20 K20:N20 AB20 E21 I21 K21:N21 AB21 E22 I22 K22:N22 AB22 E23 I23 K23:N23 AB23 E24 I24 K24:N24 AB24 E25 I25 K25:N25 AB25 E26 I26 K26:N26 AB26 E27 I27 K27:N27 AB27 E28 I28 K28:N28 AB28 E29 I29 K29:N29 AB29 E30 I30 K30:N30 AB30 E31 I31 K31:N31 AB31 E32 I32 K32:N32 AB32 E33 I33 K33:N33 AB33 E34 I34 K34:N34 AB34 E35 I35 K35:N35 AB35 E36 I36 K36:N36 AB36 E37 I37 K37:N37 AB37 E38 I38 K38:N38 AB38 E39 I39 K39:N39 AB39 E40 I40 K40:N40 AB40 E41 I41 K41:N41 AB41 E42 I42 K42:N42 AB42 E43 I43 K43:N43 AB43 E44 I44 K44:N44 AB44 E45 I45 K45:N45 AB45 E46 I46 K46:N46 AB46 E47 I47 K47:N47 AB47 E48 I48 K48:N48 AB48 E49 I49 K49:N49 AB49 E50 I50 K50:N50 AB50 E51 I51 K51:N51 AB51 E52 I52 K52:N52 AB52 E53 I53 K53:N53 AB53 E54 I54 K54:N54 AB54 E55 I55 K55:N55 AB55 E56 I56 K56:N56 AB56 E57 I57 K57:N57 AB57 E58 I58 K58:N58 AB58 E59 I59 K59:N59 AB59 E60 I60 K60:N60 AB60 E61 I61 K61:N61 AB61 E62 I62 K62:N62 AB62 E63 I63 K63:N63 AB63 E64 I64 K64:N64 AB64 E65 I65 K65:N65 AB65 E66 I66 K66:N66 AB66 E67 I67 K67:N67 AB67 E68 I68 K68:N68 AB68 E69 I69 K69:N69 AB69 E70 I70 K70:N70 AB70 E71 I71 K71:N71 AB71 E72 I72 K72:N72 AB72 E73 I73 K73:N73 AB73 E74 I74 K74:N74 AB74 E75 I75 K75:N75 AB75 E76 I76 K76:N76 AB76 E77 I77 K77:N77 AB77 E78 I78 K78:N78 AB78 E79 I79 K79:N79 AB79 E80 I80 K80:N80 AB80 E81 I81 K81:N81 AB81 E82 I82 K82:N82 AB82 E83 I83 K83:N83 AB83 E84 I84 K84:N84 AB84 E85 I85 K85:N85 AB85 E86 I86 K86:N86 AB86 E87 I87 K87:N87 AB87 E88 I88 K88:N88 AB88 E89 I89 K89:N89 AB89 E90 I90 K90:N90 AB90 E91 I91 K91:N91 AB91 E92 I92 K92:N92 AB92 E93 I93 K93:N93 AB93 E94 I94 K94:N94 AB94 E95 I95 K95:N95 AB95 E96 I96 K96:N96 AB96 E97 I97 K97:N97 AB97 E98 I98 K98:N98 AB98 E99 I99 K99:N99 AB99 E100 I100 K100:N100 AB100 E101 I101 K101:N101 AB101 E102 I102 K102:N102 AB102 E103 I103 K103:N103 AB103 E104 I104 K104:N104 AB104 E105 I105 K105:N105 AB105 E106 I106 K106:N106 AB106 E107 I107 K107:N107 AB107 E108 I108 K108:N108 AB108 E109 I109 K109:N109 AB109 E110 I110 K110:N110 AB110 E111 I111 K111:N111 AB111 E112 I112 K112:N112 AB112 E113 I113 K113:N113 AB113 E114 I114 K114:N114 AB114 E115 I115 K115:N115 AB115 E116 I116 K116:N116 AB116 E117 I117 K117:N117 AB117 E118 I118 K118:N118 AB118 E119 I119 K119:N119 AB119 E120 I120 K120:N120 AB120 E121 I121 K121:N121 AB121 E122 I122 K122:N122 AB122 E123 I123 K123:N123 AB123 E124 I124 K124:N124 AB124 E125 I125 K125:N125 AB125 E126 I126 K126:N126 AB126 E127 I127 K127:N127 AB127 E128 I128 K128:N128 AB128 E129 I129 K129:N129 AB129 E130 I130 K130:N130 AB130 E131 I131 K131:N131 AB131 E132 I132 K132:N132 AB132 E133 I133 K133:N133 AB133 E134 I134 K134:N134 AB134 E135 I135 K135:N135 AB135 E136 I136 K136:N136 AB136 E137 I137 K137:N137 AB137 E138 I138 K138:N138 AB138 E139 I139 K139:N139 AB139 E140 I140 K140:N140 AB140">
-    <cfRule type="notContainsBlanks" dxfId="15" priority="1" stopIfTrue="1">
-      <formula>NOT(ISBLANK(E7))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G7 J7 O7:P7 AC7 G8 J8 O8:P8 AC8 G9 J9 O9:P9 AC9 G10 J10 O10:P10 AC10 G11 J11 O11:P11 AC11 G12 J12 O12:P12 AC12 G13 J13 O13:P13 AC13 G14 J14 O14:P14 AC14 G15 J15 O15:P15 AC15 G16 J16 O16:P16 AC16 G17 J17 O17:P17 AC17 G18 J18 O18:P18 AC18 G19 J19 O19:P19 AC19 G20 J20 O20:P20 AC20 G21 J21 O21:P21 AC21 G22 J22 O22:P22 AC22 G23 J23 O23:P23 AC23 G24 J24 O24:P24 AC24 G25 J25 O25:P25 AC25 G26 J26 O26:P26 AC26 G27 J27 O27:P27 AC27 G28 J28 O28:P28 AC28 G29 J29 O29:P29 AC29 G30 J30 O30:P30 AC30 G31 J31 O31:P31 AC31 G32 J32 O32:P32 AC32 G33 J33 O33:P33 AC33 G34 J34 O34:P34 AC34 G35 J35 O35:P35 AC35 G36 J36 O36:P36 AC36 G37 J37 O37:P37 AC37 G38 J38 O38:P38 AC38 G39 J39 O39:P39 AC39 G40 J40 O40:P40 AC40 G41 J41 O41:P41 AC41 G42 J42 O42:P42 AC42 G43 J43 O43:P43 AC43 G44 J44 O44:P44 AC44 G45 J45 O45:P45 AC45 G46 J46 O46:P46 AC46 G47 J47 O47:P47 AC47 G48 J48 O48:P48 AC48 G49 J49 O49:P49 AC49 G50 J50 O50:P50 AC50 G51 J51 O51:P51 AC51 G52 J52 O52:P52 AC52 G53 J53 O53:P53 AC53 G54 J54 O54:P54 AC54 G55 J55 O55:P55 AC55 G56 J56 O56:P56 AC56 G57 J57 O57:P57 AC57 G58 J58 O58:P58 AC58 G59 J59 O59:P59 AC59 G60 J60 O60:P60 AC60 G61 J61 O61:P61 AC61 G62 J62 O62:P62 AC62 G63 J63 O63:P63 AC63 G64 J64 O64:P64 AC64 G65 J65 O65:P65 AC65 G66 J66 O66:P66 AC66 G67 J67 O67:P67 AC67 G68 J68 O68:P68 AC68 G69 J69 O69:P69 AC69 G70 J70 O70:P70 AC70 G71 J71 O71:P71 AC71 G72 J72 O72:P72 AC72 G73 J73 O73:P73 AC73 G74 J74 O74:P74 AC74 G75 J75 O75:P75 AC75 G76 J76 O76:P76 AC76 G77 J77 O77:P77 AC77 G78 J78 O78:P78 AC78 G79 J79 O79:P79 AC79 G80 J80 O80:P80 AC80 G81 J81 O81:P81 AC81 G82 J82 O82:P82 AC82 G83 J83 O83:P83 AC83 G84 J84 O84:P84 AC84 G85 J85 O85:P85 AC85 G86 J86 O86:P86 AC86 G87 J87 O87:P87 AC87 G88 J88 O88:P88 AC88 G89 J89 O89:P89 AC89 G90 J90 O90:P90 AC90 G91 J91 O91:P91 AC91 G92 J92 O92:P92 AC92 G93 J93 O93:P93 AC93 G94 J94 O94:P94 AC94 G95 J95 O95:P95 AC95 G96 J96 O96:P96 AC96 G97 J97 O97:P97 AC97 G98 J98 O98:P98 AC98 G99 J99 O99:P99 AC99 G100 J100 O100:P100 AC100 G101 J101 O101:P101 AC101 G102 J102 O102:P102 AC102 G103 J103 O103:P103 AC103 G104 J104 O104:P104 AC104 G105 J105 O105:P105 AC105 G106 J106 O106:P106 AC106 G107 J107 O107:P107 AC107 G108 J108 O108:P108 AC108 G109 J109 O109:P109 AC109 G110 J110 O110:P110 AC110 G111 J111 O111:P111 AC111 G112 J112 O112:P112 AC112 G113 J113 O113:P113 AC113 G114 J114 O114:P114 AC114 G115 J115 O115:P115 AC115 G116 J116 O116:P116 AC116 G117 J117 O117:P117 AC117 G118 J118 O118:P118 AC118 G119 J119 O119:P119 AC119 G120 J120 O120:P120 AC120 G121 J121 O121:P121 AC121 G122 J122 O122:P122 AC122 G123 J123 O123:P123 AC123 G124 J124 O124:P124 AC124 G125 J125 O125:P125 AC125 G126 J126 O126:P126 AC126 G127 J127 O127:P127 AC127 G128 J128 O128:P128 AC128 G129 J129 O129:P129 AC129 G130 J130 O130:P130 AC130 G131 J131 O131:P131 AC131 G132 J132 O132:P132 AC132 G133 J133 O133:P133 AC133 G134 J134 O134:P134 AC134 G135 J135 O135:P135 AC135 G136 J136 O136:P136 AC136 G137 J137 O137:P137 AC137 G138 J138 O138:P138 AC138 G139 J139 O139:P139 AC139 G140 J140 O140:P140 AC140">
     <cfRule type="notContainsBlanks" dxfId="16" priority="2" stopIfTrue="1">
       <formula>NOT(ISBLANK(G7))</formula>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -3622,7 +3622,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode=";;;"/>
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="m/d"/>
     <numFmt numFmtId="60" formatCode="&quot;R&quot;?.#"/>
@@ -5000,7 +5001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="647">
+  <cellXfs count="653">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -7219,12 +7220,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" applyProtection="1" numFmtId="164" fontId="13" fillId="2" borderId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" applyProtection="1" numFmtId="164" fontId="13" fillId="2" borderId="62" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" applyProtection="1" numFmtId="164" fontId="13" fillId="2" borderId="63" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" applyProtection="1" numFmtId="164" fontId="23" fillId="2" borderId="62" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" applyProtection="1" numFmtId="164" fontId="23" fillId="2" borderId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" applyProtection="1" numFmtId="164" fontId="13" fillId="2" borderId="64" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="36">
     <dxf>
       <font>
         <color rgb="ffff0000"/>
@@ -7499,6 +7524,7 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf/>
   </dxfs>
   <tableStyles count="0"/>
   <colors>
@@ -41766,47 +41792,47 @@
       <c r="D9" t="s" s="643">
         <v>183</v>
       </c>
-      <c r="E9" s="612"/>
-      <c r="F9" s="616" cm="1">
+      <c r="E9" s="647"/>
+      <c r="F9" s="648" cm="1">
         <f t="array" ref="F9">IF($AD9="","",$H9-$G9)</f>
         <v>46321</v>
       </c>
       <c r="G9" s="624">
         <v>7</v>
       </c>
-      <c r="H9" s="616" cm="1">
+      <c r="H9" s="648" cm="1">
         <f t="array" ref="H9">IF($AD9="","",$AA9-$J9-$P9-$O9)</f>
         <v>46328</v>
       </c>
-      <c r="I9" s="615"/>
+      <c r="I9" s="649"/>
       <c r="J9" s="624">
         <v>7</v>
       </c>
-      <c r="K9" s="625"/>
-      <c r="L9" s="626"/>
-      <c r="M9" s="616"/>
-      <c r="N9" s="615"/>
+      <c r="K9" s="650"/>
+      <c r="L9" s="651"/>
+      <c r="M9" s="648"/>
+      <c r="N9" s="649"/>
       <c r="O9" s="627">
         <v>7</v>
       </c>
       <c r="P9" s="624">
         <v>14</v>
       </c>
-      <c r="Q9" s="616"/>
-      <c r="R9" s="615"/>
-      <c r="S9" s="615"/>
-      <c r="T9" s="615"/>
-      <c r="U9" s="615"/>
-      <c r="V9" s="615"/>
-      <c r="W9" s="615"/>
-      <c r="X9" s="615"/>
-      <c r="Y9" s="615"/>
-      <c r="Z9" s="617"/>
-      <c r="AA9" s="616" cm="1">
+      <c r="Q9" s="648"/>
+      <c r="R9" s="649"/>
+      <c r="S9" s="649"/>
+      <c r="T9" s="649"/>
+      <c r="U9" s="649"/>
+      <c r="V9" s="649"/>
+      <c r="W9" s="649"/>
+      <c r="X9" s="649"/>
+      <c r="Y9" s="649"/>
+      <c r="Z9" s="652"/>
+      <c r="AA9" s="648" cm="1">
         <f t="array" ref="AA9">IF(AD9="","",AD9-AC9)</f>
         <v>46356</v>
       </c>
-      <c r="AB9" s="617"/>
+      <c r="AB9" s="652"/>
       <c r="AC9" s="628">
         <v>14</v>
       </c>
@@ -41844,47 +41870,47 @@
       <c r="D10" t="s" s="643">
         <v>187</v>
       </c>
-      <c r="E10" s="612"/>
-      <c r="F10" s="616" cm="1">
+      <c r="E10" s="647"/>
+      <c r="F10" s="648" cm="1">
         <f t="array" ref="F10">IF($AD10="","",$H10-$G10)</f>
         <v>46321</v>
       </c>
       <c r="G10" s="624">
         <v>7</v>
       </c>
-      <c r="H10" s="616" cm="1">
+      <c r="H10" s="648" cm="1">
         <f t="array" ref="H10">IF($AD10="","",$AA10-$J10-$P10-$O10)</f>
         <v>46328</v>
       </c>
-      <c r="I10" s="615"/>
+      <c r="I10" s="649"/>
       <c r="J10" s="624">
         <v>7</v>
       </c>
-      <c r="K10" s="625"/>
-      <c r="L10" s="626"/>
-      <c r="M10" s="616"/>
-      <c r="N10" s="615"/>
+      <c r="K10" s="650"/>
+      <c r="L10" s="651"/>
+      <c r="M10" s="648"/>
+      <c r="N10" s="649"/>
       <c r="O10" s="627">
         <v>7</v>
       </c>
       <c r="P10" s="624">
         <v>14</v>
       </c>
-      <c r="Q10" s="616"/>
-      <c r="R10" s="615"/>
-      <c r="S10" s="615"/>
-      <c r="T10" s="615"/>
-      <c r="U10" s="615"/>
-      <c r="V10" s="615"/>
-      <c r="W10" s="615"/>
-      <c r="X10" s="615"/>
-      <c r="Y10" s="615"/>
-      <c r="Z10" s="617"/>
-      <c r="AA10" s="616" cm="1">
+      <c r="Q10" s="648"/>
+      <c r="R10" s="649"/>
+      <c r="S10" s="649"/>
+      <c r="T10" s="649"/>
+      <c r="U10" s="649"/>
+      <c r="V10" s="649"/>
+      <c r="W10" s="649"/>
+      <c r="X10" s="649"/>
+      <c r="Y10" s="649"/>
+      <c r="Z10" s="652"/>
+      <c r="AA10" s="648" cm="1">
         <f t="array" ref="AA10">IF(AD10="","",AD10-AC10)</f>
         <v>46356</v>
       </c>
-      <c r="AB10" s="617"/>
+      <c r="AB10" s="652"/>
       <c r="AC10" t="s" s="584">
         <v>188</v>
       </c>
@@ -42455,50 +42481,52 @@
       <c r="C18" t="s" s="355">
         <v>212</v>
       </c>
-      <c r="D18" t="s" s="643">
-        <v>213</v>
-      </c>
-      <c r="E18" s="612"/>
-      <c r="F18" s="616" cm="1">
+      <c r="D18" s="643" t="inlineStr">
+        <is>
+          <t>竹甚板硝子</t>
+        </is>
+      </c>
+      <c r="E18" s="647"/>
+      <c r="F18" s="648" cm="1">
         <f t="array" ref="F18">IF($AD18="","",$H18-$G18)</f>
         <v>46325</v>
       </c>
       <c r="G18" s="624">
         <v>7</v>
       </c>
-      <c r="H18" s="616" cm="1">
+      <c r="H18" s="648" cm="1">
         <f t="array" ref="H18">IF($AD18="","",$AA18-$J18-$P18-$O18)</f>
         <v>46332</v>
       </c>
-      <c r="I18" s="615"/>
+      <c r="I18" s="649"/>
       <c r="J18" s="624">
         <v>7</v>
       </c>
-      <c r="K18" s="625"/>
-      <c r="L18" s="626"/>
-      <c r="M18" s="616"/>
-      <c r="N18" s="615"/>
+      <c r="K18" s="650"/>
+      <c r="L18" s="651"/>
+      <c r="M18" s="648"/>
+      <c r="N18" s="649"/>
       <c r="O18" s="627">
         <v>7</v>
       </c>
       <c r="P18" s="624">
         <v>14</v>
       </c>
-      <c r="Q18" s="616"/>
-      <c r="R18" s="615"/>
-      <c r="S18" s="615"/>
-      <c r="T18" s="615"/>
-      <c r="U18" s="615"/>
-      <c r="V18" s="615"/>
-      <c r="W18" s="615"/>
-      <c r="X18" s="615"/>
-      <c r="Y18" s="615"/>
-      <c r="Z18" s="617"/>
-      <c r="AA18" s="616" cm="1">
+      <c r="Q18" s="648"/>
+      <c r="R18" s="649"/>
+      <c r="S18" s="649"/>
+      <c r="T18" s="649"/>
+      <c r="U18" s="649"/>
+      <c r="V18" s="649"/>
+      <c r="W18" s="649"/>
+      <c r="X18" s="649"/>
+      <c r="Y18" s="649"/>
+      <c r="Z18" s="652"/>
+      <c r="AA18" s="648" cm="1">
         <f t="array" ref="AA18">IF(AD18="","",AD18-AC18)</f>
         <v>46360</v>
       </c>
-      <c r="AB18" s="617"/>
+      <c r="AB18" s="652"/>
       <c r="AC18" s="628">
         <v>14</v>
       </c>
@@ -49640,6 +49668,11 @@
     <mergeCell ref="U5:U6"/>
     <mergeCell ref="V5:V6"/>
   </mergeCells>
+  <conditionalFormatting sqref="C9:AB9 C10:AB10 C18:AB18">
+    <cfRule type="expression" dxfId="35" priority="1" stopIfTrue="1">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G7 J7 O7:P7 AC7 G8 J8 O8:P8 AC8 G9 J9 O9:P9 AC9 G10 J10 O10:P10 AC10 G11 J11 O11:P11 AC11 G12 J12 O12:P12 AC12 G13 J13 O13:P13 AC13 G14 J14 O14:P14 AC14 G15 J15 O15:P15 AC15 G16 J16 O16:P16 AC16 G17 J17 O17:P17 AC17 G18 J18 O18:P18 AC18 G19 J19 O19:P19 AC19 G20 J20 O20:P20 AC20 G21 J21 O21:P21 AC21 G22 J22 O22:P22 AC22 G23 J23 O23:P23 AC23 G24 J24 O24:P24 AC24 G25 J25 O25:P25 AC25 G26 J26 O26:P26 AC26 G27 J27 O27:P27 AC27 G28 J28 O28:P28 AC28 G29 J29 O29:P29 AC29 G30 J30 O30:P30 AC30 G31 J31 O31:P31 AC31 G32 J32 O32:P32 AC32 G33 J33 O33:P33 AC33 G34 J34 O34:P34 AC34 G35 J35 O35:P35 AC35 G36 J36 O36:P36 AC36 G37 J37 O37:P37 AC37 G38 J38 O38:P38 AC38 G39 J39 O39:P39 AC39 G40 J40 O40:P40 AC40 G41 J41 O41:P41 AC41 G42 J42 O42:P42 AC42 G43 J43 O43:P43 AC43 G44 J44 O44:P44 AC44 G45 J45 O45:P45 AC45 G46 J46 O46:P46 AC46 G47 J47 O47:P47 AC47 G48 J48 O48:P48 AC48 G49 J49 O49:P49 AC49 G50 J50 O50:P50 AC50 G51 J51 O51:P51 AC51 G52 J52 O52:P52 AC52 G53 J53 O53:P53 AC53 G54 J54 O54:P54 AC54 G55 J55 O55:P55 AC55 G56 J56 O56:P56 AC56 G57 J57 O57:P57 AC57 G58 J58 O58:P58 AC58 G59 J59 O59:P59 AC59 G60 J60 O60:P60 AC60 G61 J61 O61:P61 AC61 G62 J62 O62:P62 AC62 G63 J63 O63:P63 AC63 G64 J64 O64:P64 AC64 G65 J65 O65:P65 AC65 G66 J66 O66:P66 AC66 G67 J67 O67:P67 AC67 G68 J68 O68:P68 AC68 G69 J69 O69:P69 AC69 G70 J70 O70:P70 AC70 G71 J71 O71:P71 AC71 G72 J72 O72:P72 AC72 G73 J73 O73:P73 AC73 G74 J74 O74:P74 AC74 G75 J75 O75:P75 AC75 G76 J76 O76:P76 AC76 G77 J77 O77:P77 AC77 G78 J78 O78:P78 AC78 G79 J79 O79:P79 AC79 G80 J80 O80:P80 AC80 G81 J81 O81:P81 AC81 G82 J82 O82:P82 AC82 G83 J83 O83:P83 AC83 G84 J84 O84:P84 AC84 G85 J85 O85:P85 AC85 G86 J86 O86:P86 AC86 G87 J87 O87:P87 AC87 G88 J88 O88:P88 AC88 G89 J89 O89:P89 AC89 G90 J90 O90:P90 AC90 G91 J91 O91:P91 AC91 G92 J92 O92:P92 AC92 G93 J93 O93:P93 AC93 G94 J94 O94:P94 AC94 G95 J95 O95:P95 AC95 G96 J96 O96:P96 AC96 G97 J97 O97:P97 AC97 G98 J98 O98:P98 AC98 G99 J99 O99:P99 AC99 G100 J100 O100:P100 AC100 G101 J101 O101:P101 AC101 G102 J102 O102:P102 AC102 G103 J103 O103:P103 AC103 G104 J104 O104:P104 AC104 G105 J105 O105:P105 AC105 G106 J106 O106:P106 AC106 G107 J107 O107:P107 AC107 G108 J108 O108:P108 AC108 G109 J109 O109:P109 AC109 G110 J110 O110:P110 AC110 G111 J111 O111:P111 AC111 G112 J112 O112:P112 AC112 G113 J113 O113:P113 AC113 G114 J114 O114:P114 AC114 G115 J115 O115:P115 AC115 G116 J116 O116:P116 AC116 G117 J117 O117:P117 AC117 G118 J118 O118:P118 AC118 G119 J119 O119:P119 AC119 G120 J120 O120:P120 AC120 G121 J121 O121:P121 AC121 G122 J122 O122:P122 AC122 G123 J123 O123:P123 AC123 G124 J124 O124:P124 AC124 G125 J125 O125:P125 AC125 G126 J126 O126:P126 AC126 G127 J127 O127:P127 AC127 G128 J128 O128:P128 AC128 G129 J129 O129:P129 AC129 G130 J130 O130:P130 AC130 G131 J131 O131:P131 AC131 G132 J132 O132:P132 AC132 G133 J133 O133:P133 AC133 G134 J134 O134:P134 AC134 G135 J135 O135:P135 AC135 G136 J136 O136:P136 AC136 G137 J137 O137:P137 AC137 G138 J138 O138:P138 AC138 G139 J139 O139:P139 AC139 G140 J140 O140:P140 AC140">
     <cfRule type="notContainsBlanks" dxfId="16" priority="2" stopIfTrue="1">
       <formula>NOT(ISBLANK(G7))</formula>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -41797,27 +41797,19 @@
         <f t="array" ref="F9">IF($AD9="","",$H9-$G9)</f>
         <v>46321</v>
       </c>
-      <c r="G9" s="624">
-        <v>7</v>
-      </c>
+      <c r="G9" s="624"/>
       <c r="H9" s="648" cm="1">
         <f t="array" ref="H9">IF($AD9="","",$AA9-$J9-$P9-$O9)</f>
         <v>46328</v>
       </c>
       <c r="I9" s="649"/>
-      <c r="J9" s="624">
-        <v>7</v>
-      </c>
+      <c r="J9" s="624"/>
       <c r="K9" s="650"/>
       <c r="L9" s="651"/>
       <c r="M9" s="648"/>
       <c r="N9" s="649"/>
-      <c r="O9" s="627">
-        <v>7</v>
-      </c>
-      <c r="P9" s="624">
-        <v>14</v>
-      </c>
+      <c r="O9" s="627"/>
+      <c r="P9" s="624"/>
       <c r="Q9" s="648"/>
       <c r="R9" s="649"/>
       <c r="S9" s="649"/>
@@ -41833,9 +41825,7 @@
         <v>46356</v>
       </c>
       <c r="AB9" s="652"/>
-      <c r="AC9" s="628">
-        <v>14</v>
-      </c>
+      <c r="AC9" s="628"/>
       <c r="AD9" s="612">
         <v>46370</v>
       </c>
@@ -41875,27 +41865,19 @@
         <f t="array" ref="F10">IF($AD10="","",$H10-$G10)</f>
         <v>46321</v>
       </c>
-      <c r="G10" s="624">
-        <v>7</v>
-      </c>
+      <c r="G10" s="624"/>
       <c r="H10" s="648" cm="1">
         <f t="array" ref="H10">IF($AD10="","",$AA10-$J10-$P10-$O10)</f>
         <v>46328</v>
       </c>
       <c r="I10" s="649"/>
-      <c r="J10" s="624">
-        <v>7</v>
-      </c>
+      <c r="J10" s="624"/>
       <c r="K10" s="650"/>
       <c r="L10" s="651"/>
       <c r="M10" s="648"/>
       <c r="N10" s="649"/>
-      <c r="O10" s="627">
-        <v>7</v>
-      </c>
-      <c r="P10" s="624">
-        <v>14</v>
-      </c>
+      <c r="O10" s="627"/>
+      <c r="P10" s="624"/>
       <c r="Q10" s="648"/>
       <c r="R10" s="649"/>
       <c r="S10" s="649"/>
@@ -41911,9 +41893,7 @@
         <v>46356</v>
       </c>
       <c r="AB10" s="652"/>
-      <c r="AC10" t="s" s="584">
-        <v>188</v>
-      </c>
+      <c r="AC10" s="584"/>
       <c r="AD10" s="612">
         <v>46370</v>
       </c>
@@ -42491,27 +42471,19 @@
         <f t="array" ref="F18">IF($AD18="","",$H18-$G18)</f>
         <v>46325</v>
       </c>
-      <c r="G18" s="624">
-        <v>7</v>
-      </c>
+      <c r="G18" s="624"/>
       <c r="H18" s="648" cm="1">
         <f t="array" ref="H18">IF($AD18="","",$AA18-$J18-$P18-$O18)</f>
         <v>46332</v>
       </c>
       <c r="I18" s="649"/>
-      <c r="J18" s="624">
-        <v>7</v>
-      </c>
+      <c r="J18" s="624"/>
       <c r="K18" s="650"/>
       <c r="L18" s="651"/>
       <c r="M18" s="648"/>
       <c r="N18" s="649"/>
-      <c r="O18" s="627">
-        <v>7</v>
-      </c>
-      <c r="P18" s="624">
-        <v>14</v>
-      </c>
+      <c r="O18" s="627"/>
+      <c r="P18" s="624"/>
       <c r="Q18" s="648"/>
       <c r="R18" s="649"/>
       <c r="S18" s="649"/>
@@ -42527,9 +42499,7 @@
         <v>46360</v>
       </c>
       <c r="AB18" s="652"/>
-      <c r="AC18" s="628">
-        <v>14</v>
-      </c>
+      <c r="AC18" s="628"/>
       <c r="AD18" s="612">
         <v>46374</v>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22832,7 +22832,7 @@
       <c r="AB11" s="67"/>
       <c r="AC11" s="70"/>
       <c r="AD11" s="66" cm="1" t="str">
-        <f t="array" ref="AD11">IF(AG11="","",$AG11-$AF11)</f>
+        <f t="array" ref="AD11">IF(AG11="","",WORKDAY($AG11-$AF11+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE11" s="67"/>
@@ -22930,8 +22930,8 @@
         <v>46374</v>
       </c>
       <c r="AD12" s="68">
-        <f t="shared" ref="AD12:AD26" si="4">IF(AG12="","",$AG12-$AF12)</f>
-        <v>46376</v>
+        <f t="shared" ref="AD12:AD26" si="4">IF(AG12="","",WORKDAY($AG12-$AF12+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46374</v>
       </c>
       <c r="AE12" s="67"/>
       <c r="AF12" s="83">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AD18" s="68">
         <f t="shared" si="4"/>
-        <v>46375</v>
+        <v>46374</v>
       </c>
       <c r="AE18" s="67"/>
       <c r="AF18" s="83">
@@ -23639,7 +23639,7 @@
       </c>
       <c r="AD19" s="68">
         <f t="shared" si="4"/>
-        <v>46362</v>
+        <v>46360</v>
       </c>
       <c r="AE19" s="67"/>
       <c r="AF19" s="83">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="AD20" s="68">
         <f t="shared" si="4"/>
-        <v>46386</v>
+        <v>46381</v>
       </c>
       <c r="AE20" s="67"/>
       <c r="AF20" s="83">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="AD22" s="68">
         <f t="shared" si="4"/>
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="AE22" s="67"/>
       <c r="AF22" s="83">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="AD24" s="68">
         <f t="shared" si="4"/>
-        <v>46386</v>
+        <v>46381</v>
       </c>
       <c r="AE24" s="67"/>
       <c r="AF24" s="83">
@@ -24452,8 +24452,8 @@
         <v>46346</v>
       </c>
       <c r="AD27" s="68">
-        <f>IF(AG27="","",$AG27-$AF27)</f>
-        <v>46347</v>
+        <f>IF(AG27="","",WORKDAY($AG27-$AF27+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46346</v>
       </c>
       <c r="AE27" s="67"/>
       <c r="AF27" s="83">
@@ -24537,7 +24537,7 @@
       <c r="AB28" s="67"/>
       <c r="AC28" s="70"/>
       <c r="AD28" s="66" cm="1" t="str">
-        <f t="array" ref="AD28">IF(AG28="","",$AG28-$AF28)</f>
+        <f t="array" ref="AD28">IF(AG28="","",WORKDAY($AG28-$AF28+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE28" s="67"/>
@@ -24620,7 +24620,7 @@
       <c r="AB29" s="67"/>
       <c r="AC29" s="70"/>
       <c r="AD29" s="66" cm="1" t="str">
-        <f t="array" ref="AD29">IF(AG29="","",$AG29-$AF29)</f>
+        <f t="array" ref="AD29">IF(AG29="","",WORKDAY($AG29-$AF29+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE29" s="67"/>
@@ -24721,7 +24721,7 @@
         <v>46310</v>
       </c>
       <c r="AD30" s="68" cm="1">
-        <f t="array" ref="AD30">IF(AG30="","",$AG30-$AF30)</f>
+        <f t="array" ref="AD30">IF(AG30="","",WORKDAY($AG30-$AF30+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46332</v>
       </c>
       <c r="AE30" s="67"/>
@@ -24812,7 +24812,7 @@
       <c r="AB31" s="67"/>
       <c r="AC31" s="70"/>
       <c r="AD31" s="66" cm="1" t="str">
-        <f t="array" ref="AD31">IF(AG31="","",$AG31-$AF31)</f>
+        <f t="array" ref="AD31">IF(AG31="","",WORKDAY($AG31-$AF31+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE31" s="67"/>
@@ -24917,8 +24917,8 @@
         <v>46310</v>
       </c>
       <c r="AD32" s="68" cm="1">
-        <f t="array" ref="AD32">IF(AG32="","",$AG32-$AF32)</f>
-        <v>46334</v>
+        <f t="array" ref="AD32">IF(AG32="","",WORKDAY($AG32-$AF32+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46332</v>
       </c>
       <c r="AE32" s="67"/>
       <c r="AF32" s="83">
@@ -25008,7 +25008,7 @@
       <c r="AB33" s="67"/>
       <c r="AC33" s="70"/>
       <c r="AD33" s="66" cm="1" t="str">
-        <f t="array" ref="AD33">IF(AG33="","",$AG33-$AF33)</f>
+        <f t="array" ref="AD33">IF(AG33="","",WORKDAY($AG33-$AF33+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE33" s="67"/>
@@ -25091,7 +25091,7 @@
       <c r="AB34" s="67"/>
       <c r="AC34" s="70"/>
       <c r="AD34" s="66" cm="1" t="str">
-        <f t="array" ref="AD34">IF(AG34="","",$AG34-$AF34)</f>
+        <f t="array" ref="AD34">IF(AG34="","",WORKDAY($AG34-$AF34+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE34" s="67"/>
@@ -25174,7 +25174,7 @@
       <c r="AB35" s="67"/>
       <c r="AC35" s="70"/>
       <c r="AD35" s="66" cm="1" t="str">
-        <f t="array" ref="AD35">IF(AG35="","",$AG35-$AF35)</f>
+        <f t="array" ref="AD35">IF(AG35="","",WORKDAY($AG35-$AF35+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE35" s="67"/>
@@ -25277,7 +25277,7 @@
         <v>46297</v>
       </c>
       <c r="AD36" s="68" cm="1">
-        <f t="array" ref="AD36">IF(AG36="","",$AG36-$AF36)</f>
+        <f t="array" ref="AD36">IF(AG36="","",WORKDAY($AG36-$AF36+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46314</v>
       </c>
       <c r="AE36" s="67"/>
@@ -25364,7 +25364,7 @@
       <c r="AB37" s="67"/>
       <c r="AC37" s="70"/>
       <c r="AD37" s="66" cm="1" t="str">
-        <f t="array" ref="AD37">IF(AG37="","",$AG37-$AF37)</f>
+        <f t="array" ref="AD37">IF(AG37="","",WORKDAY($AG37-$AF37+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE37" s="67"/>
@@ -25447,7 +25447,7 @@
       <c r="AB38" s="67"/>
       <c r="AC38" s="70"/>
       <c r="AD38" s="66" cm="1" t="str">
-        <f t="array" ref="AD38">IF(AG38="","",$AG38-$AF38)</f>
+        <f t="array" ref="AD38">IF(AG38="","",WORKDAY($AG38-$AF38+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE38" s="67"/>
@@ -25548,7 +25548,7 @@
         <v>46328</v>
       </c>
       <c r="AD39" s="68" cm="1">
-        <f t="array" ref="AD39">IF(AG39="","",$AG39-$AF39)</f>
+        <f t="array" ref="AD39">IF(AG39="","",WORKDAY($AG39-$AF39+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46315</v>
       </c>
       <c r="AE39" s="67"/>
@@ -25649,8 +25649,8 @@
         <v>46381</v>
       </c>
       <c r="AD40" s="68" cm="1">
-        <f t="array" ref="AD40">IF(AG40="","",$AG40-$AF40)</f>
-        <v>46362</v>
+        <f t="array" ref="AD40">IF(AG40="","",WORKDAY($AG40-$AF40+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46360</v>
       </c>
       <c r="AE40" s="67"/>
       <c r="AF40" s="83">
@@ -25750,7 +25750,7 @@
         <v>46381</v>
       </c>
       <c r="AD41" s="68" cm="1">
-        <f t="array" ref="AD41">IF(AG41="","",$AG41-$AF41)</f>
+        <f t="array" ref="AD41">IF(AG41="","",WORKDAY($AG41-$AF41+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46393</v>
       </c>
       <c r="AE41" s="67"/>
@@ -25851,8 +25851,8 @@
         <v>46381</v>
       </c>
       <c r="AD42" s="68" cm="1">
-        <f t="array" ref="AD42">IF(AG42="","",$AG42-$AF42)</f>
-        <v>46389</v>
+        <f t="array" ref="AD42">IF(AG42="","",WORKDAY($AG42-$AF42+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46381</v>
       </c>
       <c r="AE42" s="67"/>
       <c r="AF42" s="83">
@@ -25938,7 +25938,7 @@
       <c r="AB43" s="67"/>
       <c r="AC43" s="70"/>
       <c r="AD43" s="66" cm="1" t="str">
-        <f t="array" ref="AD43">IF(AG43="","",$AG43-$AF43)</f>
+        <f t="array" ref="AD43">IF(AG43="","",WORKDAY($AG43-$AF43+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE43" s="67"/>
@@ -26021,7 +26021,7 @@
       <c r="AB44" s="67"/>
       <c r="AC44" s="70"/>
       <c r="AD44" s="66" cm="1" t="str">
-        <f t="array" ref="AD44">IF(AG44="","",$AG44-$AF44)</f>
+        <f t="array" ref="AD44">IF(AG44="","",WORKDAY($AG44-$AF44+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE44" s="67"/>
@@ -26120,7 +26120,7 @@
         <v>46380</v>
       </c>
       <c r="AD45" s="68" cm="1">
-        <f t="array" ref="AD45">IF(AG45="","",$AG45-$AF45)</f>
+        <f t="array" ref="AD45">IF(AG45="","",WORKDAY($AG45-$AF45+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46380</v>
       </c>
       <c r="AE45" s="67"/>
@@ -26207,7 +26207,7 @@
       <c r="AB46" s="67"/>
       <c r="AC46" s="70"/>
       <c r="AD46" s="66" cm="1" t="str">
-        <f t="array" ref="AD46">IF(AG46="","",$AG46-$AF46)</f>
+        <f t="array" ref="AD46">IF(AG46="","",WORKDAY($AG46-$AF46+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE46" s="67"/>
@@ -26290,7 +26290,7 @@
       <c r="AB47" s="67"/>
       <c r="AC47" s="70"/>
       <c r="AD47" s="66" cm="1" t="str">
-        <f t="array" ref="AD47">IF(AG47="","",$AG47-$AF47)</f>
+        <f t="array" ref="AD47">IF(AG47="","",WORKDAY($AG47-$AF47+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE47" s="67"/>
@@ -26391,8 +26391,8 @@
         <v>46416</v>
       </c>
       <c r="AD48" s="68" cm="1">
-        <f t="array" ref="AD48">IF(AG48="","",$AG48-$AF48)</f>
-        <v>46417</v>
+        <f t="array" ref="AD48">IF(AG48="","",WORKDAY($AG48-$AF48+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46416</v>
       </c>
       <c r="AE48" s="67"/>
       <c r="AF48" s="83">
@@ -26478,7 +26478,7 @@
       <c r="AB49" s="67"/>
       <c r="AC49" s="70"/>
       <c r="AD49" s="66" cm="1" t="str">
-        <f t="array" ref="AD49">IF(AG49="","",$AG49-$AF49)</f>
+        <f t="array" ref="AD49">IF(AG49="","",WORKDAY($AG49-$AF49+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE49" s="67"/>
@@ -26561,7 +26561,7 @@
       <c r="AB50" s="67"/>
       <c r="AC50" s="70"/>
       <c r="AD50" s="66" cm="1" t="str">
-        <f t="array" ref="AD50">IF(AG50="","",$AG50-$AF50)</f>
+        <f t="array" ref="AD50">IF(AG50="","",WORKDAY($AG50-$AF50+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE50" s="67"/>
@@ -26656,8 +26656,8 @@
         <v>46430</v>
       </c>
       <c r="AD51" s="68" cm="1">
-        <f t="array" ref="AD51">IF(AG51="","",$AG51-$AF51)</f>
-        <v>46432</v>
+        <f t="array" ref="AD51">IF(AG51="","",WORKDAY($AG51-$AF51+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46430</v>
       </c>
       <c r="AE51" s="67"/>
       <c r="AF51" s="83">
@@ -26743,7 +26743,7 @@
       <c r="AB52" s="67"/>
       <c r="AC52" s="70"/>
       <c r="AD52" s="66" cm="1" t="str">
-        <f t="array" ref="AD52">IF(AG52="","",$AG52-$AF52)</f>
+        <f t="array" ref="AD52">IF(AG52="","",WORKDAY($AG52-$AF52+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE52" s="67"/>
@@ -26824,7 +26824,7 @@
       <c r="AB53" s="67"/>
       <c r="AC53" s="70"/>
       <c r="AD53" s="66" cm="1" t="str">
-        <f t="array" ref="AD53">IF(AG53="","",$AG53-$AF53)</f>
+        <f t="array" ref="AD53">IF(AG53="","",WORKDAY($AG53-$AF53+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE53" s="67"/>
@@ -26905,7 +26905,7 @@
       <c r="AB54" s="67"/>
       <c r="AC54" s="70"/>
       <c r="AD54" s="66" cm="1" t="str">
-        <f t="array" ref="AD54">IF(AG54="","",$AG54-$AF54)</f>
+        <f t="array" ref="AD54">IF(AG54="","",WORKDAY($AG54-$AF54+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE54" s="67"/>
@@ -26986,7 +26986,7 @@
       <c r="AB55" s="67"/>
       <c r="AC55" s="70"/>
       <c r="AD55" s="66" cm="1" t="str">
-        <f t="array" ref="AD55">IF(AG55="","",$AG55-$AF55)</f>
+        <f t="array" ref="AD55">IF(AG55="","",WORKDAY($AG55-$AF55+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE55" s="67"/>
@@ -27067,7 +27067,7 @@
       <c r="AB56" s="67"/>
       <c r="AC56" s="70"/>
       <c r="AD56" s="66" cm="1" t="str">
-        <f t="array" ref="AD56">IF(AG56="","",$AG56-$AF56)</f>
+        <f t="array" ref="AD56">IF(AG56="","",WORKDAY($AG56-$AF56+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE56" s="67"/>
@@ -27148,7 +27148,7 @@
       <c r="AB57" s="67"/>
       <c r="AC57" s="70"/>
       <c r="AD57" s="66" cm="1" t="str">
-        <f t="array" ref="AD57">IF(AG57="","",$AG57-$AF57)</f>
+        <f t="array" ref="AD57">IF(AG57="","",WORKDAY($AG57-$AF57+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE57" s="67"/>
@@ -27229,7 +27229,7 @@
       <c r="AB58" s="67"/>
       <c r="AC58" s="70"/>
       <c r="AD58" s="66" cm="1" t="str">
-        <f t="array" ref="AD58">IF(AG58="","",$AG58-$AF58)</f>
+        <f t="array" ref="AD58">IF(AG58="","",WORKDAY($AG58-$AF58+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE58" s="67"/>
@@ -27310,7 +27310,7 @@
       <c r="AB59" s="67"/>
       <c r="AC59" s="70"/>
       <c r="AD59" s="66" cm="1" t="str">
-        <f t="array" ref="AD59">IF(AG59="","",$AG59-$AF59)</f>
+        <f t="array" ref="AD59">IF(AG59="","",WORKDAY($AG59-$AF59+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE59" s="67"/>
@@ -27391,7 +27391,7 @@
       <c r="AB60" s="67"/>
       <c r="AC60" s="70"/>
       <c r="AD60" s="66" cm="1" t="str">
-        <f t="array" ref="AD60">IF(AG60="","",$AG60-$AF60)</f>
+        <f t="array" ref="AD60">IF(AG60="","",WORKDAY($AG60-$AF60+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE60" s="67"/>
@@ -27472,7 +27472,7 @@
       <c r="AB61" s="67"/>
       <c r="AC61" s="70"/>
       <c r="AD61" s="66" cm="1" t="str">
-        <f t="array" ref="AD61">IF(AG61="","",$AG61-$AF61)</f>
+        <f t="array" ref="AD61">IF(AG61="","",WORKDAY($AG61-$AF61+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE61" s="67"/>
@@ -27553,7 +27553,7 @@
       <c r="AB62" s="67"/>
       <c r="AC62" s="70"/>
       <c r="AD62" s="66" cm="1" t="str">
-        <f t="array" ref="AD62">IF(AG62="","",$AG62-$AF62)</f>
+        <f t="array" ref="AD62">IF(AG62="","",WORKDAY($AG62-$AF62+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE62" s="67"/>
@@ -27634,7 +27634,7 @@
       <c r="AB63" s="67"/>
       <c r="AC63" s="70"/>
       <c r="AD63" s="66" cm="1" t="str">
-        <f t="array" ref="AD63">IF(AG63="","",$AG63-$AF63)</f>
+        <f t="array" ref="AD63">IF(AG63="","",WORKDAY($AG63-$AF63+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE63" s="67"/>
@@ -27715,7 +27715,7 @@
       <c r="AB64" s="67"/>
       <c r="AC64" s="70"/>
       <c r="AD64" s="66" cm="1" t="str">
-        <f t="array" ref="AD64">IF(AG64="","",$AG64-$AF64)</f>
+        <f t="array" ref="AD64">IF(AG64="","",WORKDAY($AG64-$AF64+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE64" s="67"/>
@@ -27796,7 +27796,7 @@
       <c r="AB65" s="67"/>
       <c r="AC65" s="70"/>
       <c r="AD65" s="66" cm="1" t="str">
-        <f t="array" ref="AD65">IF(AG65="","",$AG65-$AF65)</f>
+        <f t="array" ref="AD65">IF(AG65="","",WORKDAY($AG65-$AF65+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE65" s="67"/>
@@ -27877,7 +27877,7 @@
       <c r="AB66" s="67"/>
       <c r="AC66" s="70"/>
       <c r="AD66" s="66" cm="1" t="str">
-        <f t="array" ref="AD66">IF(AG66="","",$AG66-$AF66)</f>
+        <f t="array" ref="AD66">IF(AG66="","",WORKDAY($AG66-$AF66+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE66" s="67"/>
@@ -27958,7 +27958,7 @@
       <c r="AB67" s="67"/>
       <c r="AC67" s="70"/>
       <c r="AD67" s="66" cm="1" t="str">
-        <f t="array" ref="AD67">IF(AG67="","",$AG67-$AF67)</f>
+        <f t="array" ref="AD67">IF(AG67="","",WORKDAY($AG67-$AF67+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE67" s="67"/>
@@ -28039,7 +28039,7 @@
       <c r="AB68" s="67"/>
       <c r="AC68" s="70"/>
       <c r="AD68" s="66" cm="1" t="str">
-        <f t="array" ref="AD68">IF(AG68="","",$AG68-$AF68)</f>
+        <f t="array" ref="AD68">IF(AG68="","",WORKDAY($AG68-$AF68+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE68" s="67"/>
@@ -28120,7 +28120,7 @@
       <c r="AB69" s="67"/>
       <c r="AC69" s="70"/>
       <c r="AD69" s="66" cm="1" t="str">
-        <f t="array" ref="AD69">IF(AG69="","",$AG69-$AF69)</f>
+        <f t="array" ref="AD69">IF(AG69="","",WORKDAY($AG69-$AF69+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE69" s="67"/>
@@ -28201,7 +28201,7 @@
       <c r="AB70" s="67"/>
       <c r="AC70" s="70"/>
       <c r="AD70" s="66" cm="1" t="str">
-        <f t="array" ref="AD70">IF(AG70="","",$AG70-$AF70)</f>
+        <f t="array" ref="AD70">IF(AG70="","",WORKDAY($AG70-$AF70+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE70" s="67"/>
@@ -28282,7 +28282,7 @@
       <c r="AB71" s="67"/>
       <c r="AC71" s="70"/>
       <c r="AD71" s="66" cm="1" t="str">
-        <f t="array" ref="AD71">IF(AG71="","",$AG71-$AF71)</f>
+        <f t="array" ref="AD71">IF(AG71="","",WORKDAY($AG71-$AF71+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE71" s="67"/>
@@ -28363,7 +28363,7 @@
       <c r="AB72" s="67"/>
       <c r="AC72" s="70"/>
       <c r="AD72" s="66" cm="1" t="str">
-        <f t="array" ref="AD72">IF(AG72="","",$AG72-$AF72)</f>
+        <f t="array" ref="AD72">IF(AG72="","",WORKDAY($AG72-$AF72+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE72" s="67"/>
@@ -28444,7 +28444,7 @@
       <c r="AB73" s="67"/>
       <c r="AC73" s="70"/>
       <c r="AD73" s="66" cm="1" t="str">
-        <f t="array" ref="AD73">IF(AG73="","",$AG73-$AF73)</f>
+        <f t="array" ref="AD73">IF(AG73="","",WORKDAY($AG73-$AF73+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE73" s="67"/>
@@ -28525,7 +28525,7 @@
       <c r="AB74" s="67"/>
       <c r="AC74" s="70"/>
       <c r="AD74" s="66" cm="1" t="str">
-        <f t="array" ref="AD74">IF(AG74="","",$AG74-$AF74)</f>
+        <f t="array" ref="AD74">IF(AG74="","",WORKDAY($AG74-$AF74+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE74" s="67"/>
@@ -28606,7 +28606,7 @@
       <c r="AB75" s="67"/>
       <c r="AC75" s="70"/>
       <c r="AD75" s="66" cm="1" t="str">
-        <f t="array" ref="AD75">IF(AG75="","",$AG75-$AF75)</f>
+        <f t="array" ref="AD75">IF(AG75="","",WORKDAY($AG75-$AF75+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE75" s="67"/>
@@ -28687,7 +28687,7 @@
       <c r="AB76" s="67"/>
       <c r="AC76" s="70"/>
       <c r="AD76" s="66" cm="1" t="str">
-        <f t="array" ref="AD76">IF(AG76="","",$AG76-$AF76)</f>
+        <f t="array" ref="AD76">IF(AG76="","",WORKDAY($AG76-$AF76+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE76" s="67"/>
@@ -28768,7 +28768,7 @@
       <c r="AB77" s="67"/>
       <c r="AC77" s="70"/>
       <c r="AD77" s="66" cm="1" t="str">
-        <f t="array" ref="AD77">IF(AG77="","",$AG77-$AF77)</f>
+        <f t="array" ref="AD77">IF(AG77="","",WORKDAY($AG77-$AF77+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE77" s="67"/>
@@ -28849,7 +28849,7 @@
       <c r="AB78" s="67"/>
       <c r="AC78" s="70"/>
       <c r="AD78" s="66" cm="1" t="str">
-        <f t="array" ref="AD78">IF(AG78="","",$AG78-$AF78)</f>
+        <f t="array" ref="AD78">IF(AG78="","",WORKDAY($AG78-$AF78+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE78" s="67"/>
@@ -28930,7 +28930,7 @@
       <c r="AB79" s="67"/>
       <c r="AC79" s="70"/>
       <c r="AD79" s="66" cm="1" t="str">
-        <f t="array" ref="AD79">IF(AG79="","",$AG79-$AF79)</f>
+        <f t="array" ref="AD79">IF(AG79="","",WORKDAY($AG79-$AF79+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE79" s="67"/>
@@ -29011,7 +29011,7 @@
       <c r="AB80" s="67"/>
       <c r="AC80" s="70"/>
       <c r="AD80" s="66" cm="1" t="str">
-        <f t="array" ref="AD80">IF(AG80="","",$AG80-$AF80)</f>
+        <f t="array" ref="AD80">IF(AG80="","",WORKDAY($AG80-$AF80+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE80" s="67"/>
@@ -29092,7 +29092,7 @@
       <c r="AB81" s="67"/>
       <c r="AC81" s="70"/>
       <c r="AD81" s="66" cm="1" t="str">
-        <f t="array" ref="AD81">IF(AG81="","",$AG81-$AF81)</f>
+        <f t="array" ref="AD81">IF(AG81="","",WORKDAY($AG81-$AF81+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE81" s="67"/>
@@ -29173,7 +29173,7 @@
       <c r="AB82" s="67"/>
       <c r="AC82" s="70"/>
       <c r="AD82" s="66" cm="1" t="str">
-        <f t="array" ref="AD82">IF(AG82="","",$AG82-$AF82)</f>
+        <f t="array" ref="AD82">IF(AG82="","",WORKDAY($AG82-$AF82+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE82" s="67"/>
@@ -29254,7 +29254,7 @@
       <c r="AB83" s="67"/>
       <c r="AC83" s="70"/>
       <c r="AD83" s="66" cm="1" t="str">
-        <f t="array" ref="AD83">IF(AG83="","",$AG83-$AF83)</f>
+        <f t="array" ref="AD83">IF(AG83="","",WORKDAY($AG83-$AF83+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE83" s="67"/>
@@ -29335,7 +29335,7 @@
       <c r="AB84" s="67"/>
       <c r="AC84" s="70"/>
       <c r="AD84" s="66" cm="1" t="str">
-        <f t="array" ref="AD84">IF(AG84="","",$AG84-$AF84)</f>
+        <f t="array" ref="AD84">IF(AG84="","",WORKDAY($AG84-$AF84+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE84" s="67"/>
@@ -29416,7 +29416,7 @@
       <c r="AB85" s="67"/>
       <c r="AC85" s="70"/>
       <c r="AD85" s="66" cm="1" t="str">
-        <f t="array" ref="AD85">IF(AG85="","",$AG85-$AF85)</f>
+        <f t="array" ref="AD85">IF(AG85="","",WORKDAY($AG85-$AF85+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE85" s="67"/>
@@ -29497,7 +29497,7 @@
       <c r="AB86" s="67"/>
       <c r="AC86" s="70"/>
       <c r="AD86" s="66" cm="1" t="str">
-        <f t="array" ref="AD86">IF(AG86="","",$AG86-$AF86)</f>
+        <f t="array" ref="AD86">IF(AG86="","",WORKDAY($AG86-$AF86+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE86" s="67"/>
@@ -29578,7 +29578,7 @@
       <c r="AB87" s="67"/>
       <c r="AC87" s="70"/>
       <c r="AD87" s="66" cm="1" t="str">
-        <f t="array" ref="AD87">IF(AG87="","",$AG87-$AF87)</f>
+        <f t="array" ref="AD87">IF(AG87="","",WORKDAY($AG87-$AF87+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE87" s="67"/>
@@ -29659,7 +29659,7 @@
       <c r="AB88" s="67"/>
       <c r="AC88" s="70"/>
       <c r="AD88" s="66" cm="1" t="str">
-        <f t="array" ref="AD88">IF(AG88="","",$AG88-$AF88)</f>
+        <f t="array" ref="AD88">IF(AG88="","",WORKDAY($AG88-$AF88+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE88" s="67"/>
@@ -29740,7 +29740,7 @@
       <c r="AB89" s="67"/>
       <c r="AC89" s="70"/>
       <c r="AD89" s="66" cm="1" t="str">
-        <f t="array" ref="AD89">IF(AG89="","",$AG89-$AF89)</f>
+        <f t="array" ref="AD89">IF(AG89="","",WORKDAY($AG89-$AF89+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE89" s="67"/>
@@ -29821,7 +29821,7 @@
       <c r="AB90" s="67"/>
       <c r="AC90" s="70"/>
       <c r="AD90" s="66" cm="1" t="str">
-        <f t="array" ref="AD90">IF(AG90="","",$AG90-$AF90)</f>
+        <f t="array" ref="AD90">IF(AG90="","",WORKDAY($AG90-$AF90+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE90" s="67"/>
@@ -29902,7 +29902,7 @@
       <c r="AB91" s="67"/>
       <c r="AC91" s="70"/>
       <c r="AD91" s="66" cm="1" t="str">
-        <f t="array" ref="AD91">IF(AG91="","",$AG91-$AF91)</f>
+        <f t="array" ref="AD91">IF(AG91="","",WORKDAY($AG91-$AF91+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE91" s="67"/>
@@ -29983,7 +29983,7 @@
       <c r="AB92" s="67"/>
       <c r="AC92" s="70"/>
       <c r="AD92" s="66" cm="1" t="str">
-        <f t="array" ref="AD92">IF(AG92="","",$AG92-$AF92)</f>
+        <f t="array" ref="AD92">IF(AG92="","",WORKDAY($AG92-$AF92+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE92" s="67"/>
@@ -30064,7 +30064,7 @@
       <c r="AB93" s="67"/>
       <c r="AC93" s="70"/>
       <c r="AD93" s="66" cm="1" t="str">
-        <f t="array" ref="AD93">IF(AG93="","",$AG93-$AF93)</f>
+        <f t="array" ref="AD93">IF(AG93="","",WORKDAY($AG93-$AF93+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE93" s="67"/>
@@ -30145,7 +30145,7 @@
       <c r="AB94" s="67"/>
       <c r="AC94" s="70"/>
       <c r="AD94" s="66" cm="1" t="str">
-        <f t="array" ref="AD94">IF(AG94="","",$AG94-$AF94)</f>
+        <f t="array" ref="AD94">IF(AG94="","",WORKDAY($AG94-$AF94+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE94" s="67"/>
@@ -30226,7 +30226,7 @@
       <c r="AB95" s="67"/>
       <c r="AC95" s="70"/>
       <c r="AD95" s="66" cm="1" t="str">
-        <f t="array" ref="AD95">IF(AG95="","",$AG95-$AF95)</f>
+        <f t="array" ref="AD95">IF(AG95="","",WORKDAY($AG95-$AF95+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE95" s="67"/>
@@ -30307,7 +30307,7 @@
       <c r="AB96" s="67"/>
       <c r="AC96" s="70"/>
       <c r="AD96" s="66" cm="1" t="str">
-        <f t="array" ref="AD96">IF(AG96="","",$AG96-$AF96)</f>
+        <f t="array" ref="AD96">IF(AG96="","",WORKDAY($AG96-$AF96+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE96" s="67"/>
@@ -30388,7 +30388,7 @@
       <c r="AB97" s="67"/>
       <c r="AC97" s="70"/>
       <c r="AD97" s="66" cm="1" t="str">
-        <f t="array" ref="AD97">IF(AG97="","",$AG97-$AF97)</f>
+        <f t="array" ref="AD97">IF(AG97="","",WORKDAY($AG97-$AF97+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE97" s="67"/>
@@ -30469,7 +30469,7 @@
       <c r="AB98" s="67"/>
       <c r="AC98" s="70"/>
       <c r="AD98" s="66" cm="1" t="str">
-        <f t="array" ref="AD98">IF(AG98="","",$AG98-$AF98)</f>
+        <f t="array" ref="AD98">IF(AG98="","",WORKDAY($AG98-$AF98+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE98" s="67"/>
@@ -30550,7 +30550,7 @@
       <c r="AB99" s="67"/>
       <c r="AC99" s="70"/>
       <c r="AD99" s="66" cm="1" t="str">
-        <f t="array" ref="AD99">IF(AG99="","",$AG99-$AF99)</f>
+        <f t="array" ref="AD99">IF(AG99="","",WORKDAY($AG99-$AF99+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE99" s="67"/>
@@ -30631,7 +30631,7 @@
       <c r="AB100" s="67"/>
       <c r="AC100" s="70"/>
       <c r="AD100" s="66" cm="1" t="str">
-        <f t="array" ref="AD100">IF(AG100="","",$AG100-$AF100)</f>
+        <f t="array" ref="AD100">IF(AG100="","",WORKDAY($AG100-$AF100+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE100" s="67"/>
@@ -30712,7 +30712,7 @@
       <c r="AB101" s="67"/>
       <c r="AC101" s="70"/>
       <c r="AD101" s="66" cm="1" t="str">
-        <f t="array" ref="AD101">IF(AG101="","",$AG101-$AF101)</f>
+        <f t="array" ref="AD101">IF(AG101="","",WORKDAY($AG101-$AF101+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE101" s="67"/>
@@ -30793,7 +30793,7 @@
       <c r="AB102" s="67"/>
       <c r="AC102" s="70"/>
       <c r="AD102" s="66" cm="1" t="str">
-        <f t="array" ref="AD102">IF(AG102="","",$AG102-$AF102)</f>
+        <f t="array" ref="AD102">IF(AG102="","",WORKDAY($AG102-$AF102+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE102" s="67"/>
@@ -30874,7 +30874,7 @@
       <c r="AB103" s="67"/>
       <c r="AC103" s="70"/>
       <c r="AD103" s="66" cm="1" t="str">
-        <f t="array" ref="AD103">IF(AG103="","",$AG103-$AF103)</f>
+        <f t="array" ref="AD103">IF(AG103="","",WORKDAY($AG103-$AF103+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE103" s="67"/>
@@ -30955,7 +30955,7 @@
       <c r="AB104" s="67"/>
       <c r="AC104" s="70"/>
       <c r="AD104" s="66" cm="1" t="str">
-        <f t="array" ref="AD104">IF(AG104="","",$AG104-$AF104)</f>
+        <f t="array" ref="AD104">IF(AG104="","",WORKDAY($AG104-$AF104+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE104" s="67"/>
@@ -31036,7 +31036,7 @@
       <c r="AB105" s="67"/>
       <c r="AC105" s="70"/>
       <c r="AD105" s="66" cm="1" t="str">
-        <f t="array" ref="AD105">IF(AG105="","",$AG105-$AF105)</f>
+        <f t="array" ref="AD105">IF(AG105="","",WORKDAY($AG105-$AF105+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AE105" s="67"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22302,11 +22302,11 @@
       </c>
       <c r="BK4" s="40" cm="1">
         <f t="array" aca="1" ref="BK4" ca="1">COUNTIFS($F$10:$F$116,"&lt;="&amp;TODAY(),$F$10:$F$116,"&gt;"&amp;0,$G$10:$G$116,"="&amp;"")+COUNTIFS($I$10:$I$116,"&lt;="&amp;TODAY(),$I$10:$I$116,"&gt;"&amp;0,$J$10:$J$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY(),$P$10:$P$116,"&gt;"&amp;0,$L$10:$L$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY(),$P$10:$P$116,"&gt;"&amp;0,$M$10:$M$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY(),$AC$10:$AC$116,"&gt;"&amp;0,$S$10:$S$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY(),$AC$10:$AC$116,"&gt;"&amp;0,$T$10:$T$116,"="&amp;"")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BL4" s="28" cm="1" t="str">
         <f t="array" aca="1" ref="BL4" ca="1">BJ4&amp;": "&amp;BK4&amp;"個"</f>
-        <v>赤色: 8個</v>
+        <v>赤色: 5個</v>
       </c>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
@@ -22423,11 +22423,11 @@
       </c>
       <c r="BK5" s="40" cm="1">
         <f t="array" aca="1" ref="BK5" ca="1">COUNTIFS($F$10:$F$116,"&lt;="&amp;TODAY()+7,$F$10:$F$116,"&gt;"&amp;0,$G$10:$G$116,"="&amp;"")+COUNTIFS($I$10:$I$116,"&lt;="&amp;TODAY()+7,$I$10:$I$116,"&gt;"&amp;0,$J$10:$J$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY()+7,$P$10:$P$116,"&gt;"&amp;0,$L$10:$L$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY()+7,$P$10:$P$116,"&gt;"&amp;0,$M$10:$M$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY()+7,$AC$10:$AC$116,"&gt;"&amp;0,$S$10:$S$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY()+7,$AC$10:$AC$116,"&gt;"&amp;0,$T$10:$T$116,"="&amp;"")-BK4</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BL5" s="28" cm="1" t="str">
         <f t="array" aca="1" ref="BL5" ca="1">BJ5&amp;": "&amp;BK5&amp;"個"</f>
-        <v>黄色: 11個</v>
+        <v>黄色: 8個</v>
       </c>
     </row>
     <row r="6" spans="1:64" ht="15" customHeight="1">
@@ -22830,9 +22830,12 @@
       <c r="Z11" s="68"/>
       <c r="AA11" s="68"/>
       <c r="AB11" s="67"/>
-      <c r="AC11" s="70"/>
+      <c r="AC11" s="70" t="str">
+        <f>IF(AG11="","",WORKDAY(AG11-AF11+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD11" s="66" cm="1" t="str">
-        <f t="array" ref="AD11">IF(AG11="","",WORKDAY($AG11-$AF11+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD11">IF(AG11="","",$AG11-$AF11)</f>
         <v/>
       </c>
       <c r="AE11" s="67"/>
@@ -22930,8 +22933,8 @@
         <v>46374</v>
       </c>
       <c r="AD12" s="68">
-        <f t="shared" ref="AD12:AD26" si="4">IF(AG12="","",WORKDAY($AG12-$AF12+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46374</v>
+        <f t="shared" ref="AD12:AD26" si="4">IF(AG12="","",$AG12-$AF12)</f>
+        <v>46376</v>
       </c>
       <c r="AE12" s="67"/>
       <c r="AF12" s="83">
@@ -23539,7 +23542,7 @@
       </c>
       <c r="AD18" s="68">
         <f t="shared" si="4"/>
-        <v>46374</v>
+        <v>46375</v>
       </c>
       <c r="AE18" s="67"/>
       <c r="AF18" s="83">
@@ -23639,7 +23642,7 @@
       </c>
       <c r="AD19" s="68">
         <f t="shared" si="4"/>
-        <v>46360</v>
+        <v>46362</v>
       </c>
       <c r="AE19" s="67"/>
       <c r="AF19" s="83">
@@ -23739,7 +23742,7 @@
       </c>
       <c r="AD20" s="68">
         <f t="shared" si="4"/>
-        <v>46381</v>
+        <v>46386</v>
       </c>
       <c r="AE20" s="67"/>
       <c r="AF20" s="83">
@@ -23943,7 +23946,7 @@
       </c>
       <c r="AD22" s="68">
         <f t="shared" si="4"/>
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="AE22" s="67"/>
       <c r="AF22" s="83">
@@ -24145,7 +24148,7 @@
       </c>
       <c r="AD24" s="68">
         <f t="shared" si="4"/>
-        <v>46381</v>
+        <v>46386</v>
       </c>
       <c r="AE24" s="67"/>
       <c r="AF24" s="83">
@@ -24452,8 +24455,8 @@
         <v>46346</v>
       </c>
       <c r="AD27" s="68">
-        <f>IF(AG27="","",WORKDAY($AG27-$AF27+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46346</v>
+        <f>IF(AG27="","",$AG27-$AF27)</f>
+        <v>46347</v>
       </c>
       <c r="AE27" s="67"/>
       <c r="AF27" s="83">
@@ -24535,9 +24538,12 @@
       <c r="Z28" s="68"/>
       <c r="AA28" s="68"/>
       <c r="AB28" s="67"/>
-      <c r="AC28" s="70"/>
+      <c r="AC28" s="70" t="str">
+        <f>IF(AG28="","",WORKDAY(AG28-AF28+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD28" s="66" cm="1" t="str">
-        <f t="array" ref="AD28">IF(AG28="","",WORKDAY($AG28-$AF28+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD28">IF(AG28="","",$AG28-$AF28)</f>
         <v/>
       </c>
       <c r="AE28" s="67"/>
@@ -24618,9 +24624,12 @@
       <c r="Z29" s="68"/>
       <c r="AA29" s="68"/>
       <c r="AB29" s="67"/>
-      <c r="AC29" s="70"/>
+      <c r="AC29" s="70" t="str">
+        <f>IF(AG29="","",WORKDAY(AG29-AF29+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD29" s="66" cm="1" t="str">
-        <f t="array" ref="AD29">IF(AG29="","",WORKDAY($AG29-$AF29+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD29">IF(AG29="","",$AG29-$AF29)</f>
         <v/>
       </c>
       <c r="AE29" s="67"/>
@@ -24673,7 +24682,7 @@
       <c r="E30" s="71"/>
       <c r="F30" s="70" cm="1">
         <f t="array" ref="F30">IF(AG30="","",I30-H30)</f>
-        <v>46275</v>
+        <v>46297</v>
       </c>
       <c r="G30" s="67">
         <v>46301</v>
@@ -24683,7 +24692,7 @@
       </c>
       <c r="I30" s="68" cm="1">
         <f t="array" ref="I30">IF(AG30="","",P30-K30)</f>
-        <v>46282</v>
+        <v>46304</v>
       </c>
       <c r="J30" s="67">
         <v>46302</v>
@@ -24699,7 +24708,7 @@
       <c r="O30" s="68"/>
       <c r="P30" s="68" cm="1">
         <f t="array" ref="P30">IF(AG30="","",AC30-R30-Q30)</f>
-        <v>46289</v>
+        <v>46311</v>
       </c>
       <c r="Q30" s="69">
         <v>7</v>
@@ -24718,10 +24727,11 @@
       <c r="AA30" s="68"/>
       <c r="AB30" s="67"/>
       <c r="AC30" s="70">
-        <v>46310</v>
+        <f>IF(AG30="","",WORKDAY(AG30-AF30+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46332</v>
       </c>
       <c r="AD30" s="68" cm="1">
-        <f t="array" ref="AD30">IF(AG30="","",WORKDAY($AG30-$AF30+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD30">IF(AG30="","",$AG30-$AF30)</f>
         <v>46332</v>
       </c>
       <c r="AE30" s="67"/>
@@ -24810,9 +24820,12 @@
       <c r="Z31" s="68"/>
       <c r="AA31" s="68"/>
       <c r="AB31" s="67"/>
-      <c r="AC31" s="70"/>
+      <c r="AC31" s="70" t="str">
+        <f>IF(AG31="","",WORKDAY(AG31-AF31+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD31" s="66" cm="1" t="str">
-        <f t="array" ref="AD31">IF(AG31="","",WORKDAY($AG31-$AF31+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD31">IF(AG31="","",$AG31-$AF31)</f>
         <v/>
       </c>
       <c r="AE31" s="67"/>
@@ -24867,7 +24880,7 @@
       <c r="E32" s="71"/>
       <c r="F32" s="70" cm="1">
         <f t="array" ref="F32">IF(AG32="","",I32-H32)</f>
-        <v>46275</v>
+        <v>46297</v>
       </c>
       <c r="G32" s="67">
         <v>46290</v>
@@ -24877,7 +24890,7 @@
       </c>
       <c r="I32" s="68" cm="1">
         <f t="array" ref="I32">IF(AG32="","",P32-K32)</f>
-        <v>46282</v>
+        <v>46304</v>
       </c>
       <c r="J32" s="67">
         <v>46290</v>
@@ -24895,7 +24908,7 @@
       <c r="O32" s="68"/>
       <c r="P32" s="68" cm="1">
         <f t="array" ref="P32">IF(AG32="","",AC32-R32-Q32)</f>
-        <v>46289</v>
+        <v>46311</v>
       </c>
       <c r="Q32" s="69">
         <v>7</v>
@@ -24914,11 +24927,12 @@
       <c r="AA32" s="68"/>
       <c r="AB32" s="67"/>
       <c r="AC32" s="70">
-        <v>46310</v>
+        <f>IF(AG32="","",WORKDAY(AG32-AF32+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46332</v>
       </c>
       <c r="AD32" s="68" cm="1">
-        <f t="array" ref="AD32">IF(AG32="","",WORKDAY($AG32-$AF32+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46332</v>
+        <f t="array" ref="AD32">IF(AG32="","",$AG32-$AF32)</f>
+        <v>46334</v>
       </c>
       <c r="AE32" s="67"/>
       <c r="AF32" s="83">
@@ -25006,9 +25020,12 @@
       <c r="Z33" s="68"/>
       <c r="AA33" s="68"/>
       <c r="AB33" s="67"/>
-      <c r="AC33" s="70"/>
+      <c r="AC33" s="70" t="str">
+        <f>IF(AG33="","",WORKDAY(AG33-AF33+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD33" s="66" cm="1" t="str">
-        <f t="array" ref="AD33">IF(AG33="","",WORKDAY($AG33-$AF33+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD33">IF(AG33="","",$AG33-$AF33)</f>
         <v/>
       </c>
       <c r="AE33" s="67"/>
@@ -25089,9 +25106,12 @@
       <c r="Z34" s="68"/>
       <c r="AA34" s="68"/>
       <c r="AB34" s="67"/>
-      <c r="AC34" s="70"/>
+      <c r="AC34" s="70" t="str">
+        <f>IF(AG34="","",WORKDAY(AG34-AF34+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD34" s="66" cm="1" t="str">
-        <f t="array" ref="AD34">IF(AG34="","",WORKDAY($AG34-$AF34+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD34">IF(AG34="","",$AG34-$AF34)</f>
         <v/>
       </c>
       <c r="AE34" s="67"/>
@@ -25172,9 +25192,12 @@
       <c r="Z35" s="68"/>
       <c r="AA35" s="68"/>
       <c r="AB35" s="67"/>
-      <c r="AC35" s="70"/>
+      <c r="AC35" s="70" t="str">
+        <f>IF(AG35="","",WORKDAY(AG35-AF35+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD35" s="66" cm="1" t="str">
-        <f t="array" ref="AD35">IF(AG35="","",WORKDAY($AG35-$AF35+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD35">IF(AG35="","",$AG35-$AF35)</f>
         <v/>
       </c>
       <c r="AE35" s="67"/>
@@ -25227,7 +25250,7 @@
       <c r="E36" s="71"/>
       <c r="F36" s="70" cm="1">
         <f t="array" ref="F36">IF(AG36="","",I36-H36)</f>
-        <v>46269</v>
+        <v>46286</v>
       </c>
       <c r="G36" s="67">
         <v>46282</v>
@@ -25237,7 +25260,7 @@
       </c>
       <c r="I36" s="68" cm="1">
         <f t="array" ref="I36">IF(AG36="","",P36-K36)</f>
-        <v>46276</v>
+        <v>46293</v>
       </c>
       <c r="J36" s="67">
         <v>46289</v>
@@ -25255,7 +25278,7 @@
       <c r="O36" s="68"/>
       <c r="P36" s="68" cm="1">
         <f t="array" ref="P36">IF(AG36="","",AC36-R36-Q36)</f>
-        <v>46283</v>
+        <v>46300</v>
       </c>
       <c r="Q36" s="69">
         <v>7</v>
@@ -25274,10 +25297,11 @@
       <c r="AA36" s="68"/>
       <c r="AB36" s="67"/>
       <c r="AC36" s="70">
-        <v>46297</v>
+        <f>IF(AG36="","",WORKDAY(AG36-AF36+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46314</v>
       </c>
       <c r="AD36" s="68" cm="1">
-        <f t="array" ref="AD36">IF(AG36="","",WORKDAY($AG36-$AF36+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD36">IF(AG36="","",$AG36-$AF36)</f>
         <v>46314</v>
       </c>
       <c r="AE36" s="67"/>
@@ -25362,9 +25386,12 @@
       <c r="Z37" s="68"/>
       <c r="AA37" s="68"/>
       <c r="AB37" s="67"/>
-      <c r="AC37" s="70"/>
+      <c r="AC37" s="70" t="str">
+        <f>IF(AG37="","",WORKDAY(AG37-AF37+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD37" s="66" cm="1" t="str">
-        <f t="array" ref="AD37">IF(AG37="","",WORKDAY($AG37-$AF37+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD37">IF(AG37="","",$AG37-$AF37)</f>
         <v/>
       </c>
       <c r="AE37" s="67"/>
@@ -25445,9 +25472,12 @@
       <c r="Z38" s="68"/>
       <c r="AA38" s="68"/>
       <c r="AB38" s="67"/>
-      <c r="AC38" s="70"/>
+      <c r="AC38" s="70" t="str">
+        <f>IF(AG38="","",WORKDAY(AG38-AF38+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD38" s="66" cm="1" t="str">
-        <f t="array" ref="AD38">IF(AG38="","",WORKDAY($AG38-$AF38+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD38">IF(AG38="","",$AG38-$AF38)</f>
         <v/>
       </c>
       <c r="AE38" s="67"/>
@@ -25500,7 +25530,7 @@
       <c r="E39" s="71"/>
       <c r="F39" s="70" cm="1">
         <f t="array" ref="F39">IF(AG39="","",I39-H39)</f>
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="G39" s="67">
         <v>46300</v>
@@ -25510,7 +25540,7 @@
       </c>
       <c r="I39" s="68" cm="1">
         <f t="array" ref="I39">IF(AG39="","",P39-K39)</f>
-        <v>46300</v>
+        <v>46287</v>
       </c>
       <c r="J39" s="67">
         <v>46302</v>
@@ -25526,7 +25556,7 @@
       <c r="O39" s="68"/>
       <c r="P39" s="68" cm="1">
         <f t="array" ref="P39">IF(AG39="","",AC39-R39-Q39)</f>
-        <v>46307</v>
+        <v>46294</v>
       </c>
       <c r="Q39" s="69">
         <v>7</v>
@@ -25545,10 +25575,11 @@
       <c r="AA39" s="68"/>
       <c r="AB39" s="67"/>
       <c r="AC39" s="70">
-        <v>46328</v>
+        <f>IF(AG39="","",WORKDAY(AG39-AF39+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46315</v>
       </c>
       <c r="AD39" s="68" cm="1">
-        <f t="array" ref="AD39">IF(AG39="","",WORKDAY($AG39-$AF39+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD39">IF(AG39="","",$AG39-$AF39)</f>
         <v>46315</v>
       </c>
       <c r="AE39" s="67"/>
@@ -25607,7 +25638,7 @@
       <c r="E40" s="71"/>
       <c r="F40" s="70" cm="1">
         <f t="array" ref="F40">IF(AG40="","",I40-H40)</f>
-        <v>46346</v>
+        <v>46325</v>
       </c>
       <c r="G40" s="67"/>
       <c r="H40" s="65">
@@ -25615,7 +25646,7 @@
       </c>
       <c r="I40" s="68" cm="1">
         <f t="array" ref="I40">IF(AG40="","",P40-K40)</f>
-        <v>46353</v>
+        <v>46332</v>
       </c>
       <c r="J40" s="67"/>
       <c r="K40" s="65">
@@ -25627,7 +25658,7 @@
       <c r="O40" s="68"/>
       <c r="P40" s="68" cm="1">
         <f t="array" ref="P40">IF(AG40="","",AC40-R40-Q40)</f>
-        <v>46360</v>
+        <v>46339</v>
       </c>
       <c r="Q40" s="69">
         <v>7</v>
@@ -25646,11 +25677,12 @@
       <c r="AA40" s="68"/>
       <c r="AB40" s="67"/>
       <c r="AC40" s="70">
-        <v>46381</v>
+        <f>IF(AG40="","",WORKDAY(AG40-AF40+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46360</v>
       </c>
       <c r="AD40" s="68" cm="1">
-        <f t="array" ref="AD40">IF(AG40="","",WORKDAY($AG40-$AF40+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46360</v>
+        <f t="array" ref="AD40">IF(AG40="","",$AG40-$AF40)</f>
+        <v>46362</v>
       </c>
       <c r="AE40" s="67"/>
       <c r="AF40" s="83">
@@ -25708,7 +25740,7 @@
       <c r="E41" s="71"/>
       <c r="F41" s="70" cm="1">
         <f t="array" ref="F41">IF(AG41="","",I41-H41)</f>
-        <v>46346</v>
+        <v>46358</v>
       </c>
       <c r="G41" s="67"/>
       <c r="H41" s="65">
@@ -25716,7 +25748,7 @@
       </c>
       <c r="I41" s="68" cm="1">
         <f t="array" ref="I41">IF(AG41="","",P41-K41)</f>
-        <v>46353</v>
+        <v>46365</v>
       </c>
       <c r="J41" s="67"/>
       <c r="K41" s="65">
@@ -25728,7 +25760,7 @@
       <c r="O41" s="68"/>
       <c r="P41" s="68" cm="1">
         <f t="array" ref="P41">IF(AG41="","",AC41-R41-Q41)</f>
-        <v>46360</v>
+        <v>46372</v>
       </c>
       <c r="Q41" s="69">
         <v>7</v>
@@ -25747,10 +25779,11 @@
       <c r="AA41" s="68"/>
       <c r="AB41" s="67"/>
       <c r="AC41" s="70">
-        <v>46381</v>
+        <f>IF(AG41="","",WORKDAY(AG41-AF41+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v>46393</v>
       </c>
       <c r="AD41" s="68" cm="1">
-        <f t="array" ref="AD41">IF(AG41="","",WORKDAY($AG41-$AF41+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD41">IF(AG41="","",$AG41-$AF41)</f>
         <v>46393</v>
       </c>
       <c r="AE41" s="67"/>
@@ -25848,11 +25881,12 @@
       <c r="AA42" s="68"/>
       <c r="AB42" s="67"/>
       <c r="AC42" s="70">
+        <f>IF(AG42="","",WORKDAY(AG42-AF42+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46381</v>
       </c>
       <c r="AD42" s="68" cm="1">
-        <f t="array" ref="AD42">IF(AG42="","",WORKDAY($AG42-$AF42+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46381</v>
+        <f t="array" ref="AD42">IF(AG42="","",$AG42-$AF42)</f>
+        <v>46389</v>
       </c>
       <c r="AE42" s="67"/>
       <c r="AF42" s="83">
@@ -25936,9 +25970,12 @@
       <c r="Z43" s="68"/>
       <c r="AA43" s="68"/>
       <c r="AB43" s="67"/>
-      <c r="AC43" s="70"/>
+      <c r="AC43" s="70" t="str">
+        <f>IF(AG43="","",WORKDAY(AG43-AF43+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD43" s="66" cm="1" t="str">
-        <f t="array" ref="AD43">IF(AG43="","",WORKDAY($AG43-$AF43+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD43">IF(AG43="","",$AG43-$AF43)</f>
         <v/>
       </c>
       <c r="AE43" s="67"/>
@@ -26019,9 +26056,12 @@
       <c r="Z44" s="68"/>
       <c r="AA44" s="68"/>
       <c r="AB44" s="67"/>
-      <c r="AC44" s="70"/>
+      <c r="AC44" s="70" t="str">
+        <f>IF(AG44="","",WORKDAY(AG44-AF44+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD44" s="66" cm="1" t="str">
-        <f t="array" ref="AD44">IF(AG44="","",WORKDAY($AG44-$AF44+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD44">IF(AG44="","",$AG44-$AF44)</f>
         <v/>
       </c>
       <c r="AE44" s="67"/>
@@ -26117,10 +26157,11 @@
       <c r="AA45" s="68"/>
       <c r="AB45" s="67"/>
       <c r="AC45" s="70">
+        <f>IF(AG45="","",WORKDAY(AG45-AF45+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46380</v>
       </c>
       <c r="AD45" s="68" cm="1">
-        <f t="array" ref="AD45">IF(AG45="","",WORKDAY($AG45-$AF45+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD45">IF(AG45="","",$AG45-$AF45)</f>
         <v>46380</v>
       </c>
       <c r="AE45" s="67"/>
@@ -26205,9 +26246,12 @@
       <c r="Z46" s="68"/>
       <c r="AA46" s="68"/>
       <c r="AB46" s="67"/>
-      <c r="AC46" s="70"/>
+      <c r="AC46" s="70" t="str">
+        <f>IF(AG46="","",WORKDAY(AG46-AF46+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD46" s="66" cm="1" t="str">
-        <f t="array" ref="AD46">IF(AG46="","",WORKDAY($AG46-$AF46+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD46">IF(AG46="","",$AG46-$AF46)</f>
         <v/>
       </c>
       <c r="AE46" s="67"/>
@@ -26288,9 +26332,12 @@
       <c r="Z47" s="68"/>
       <c r="AA47" s="68"/>
       <c r="AB47" s="67"/>
-      <c r="AC47" s="70"/>
+      <c r="AC47" s="70" t="str">
+        <f>IF(AG47="","",WORKDAY(AG47-AF47+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD47" s="66" cm="1" t="str">
-        <f t="array" ref="AD47">IF(AG47="","",WORKDAY($AG47-$AF47+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD47">IF(AG47="","",$AG47-$AF47)</f>
         <v/>
       </c>
       <c r="AE47" s="67"/>
@@ -26388,11 +26435,12 @@
       <c r="AA48" s="68"/>
       <c r="AB48" s="67"/>
       <c r="AC48" s="70">
+        <f>IF(AG48="","",WORKDAY(AG48-AF48+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46416</v>
       </c>
       <c r="AD48" s="68" cm="1">
-        <f t="array" ref="AD48">IF(AG48="","",WORKDAY($AG48-$AF48+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46416</v>
+        <f t="array" ref="AD48">IF(AG48="","",$AG48-$AF48)</f>
+        <v>46417</v>
       </c>
       <c r="AE48" s="67"/>
       <c r="AF48" s="83">
@@ -26476,9 +26524,12 @@
       <c r="Z49" s="68"/>
       <c r="AA49" s="68"/>
       <c r="AB49" s="67"/>
-      <c r="AC49" s="70"/>
+      <c r="AC49" s="70" t="str">
+        <f>IF(AG49="","",WORKDAY(AG49-AF49+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD49" s="66" cm="1" t="str">
-        <f t="array" ref="AD49">IF(AG49="","",WORKDAY($AG49-$AF49+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD49">IF(AG49="","",$AG49-$AF49)</f>
         <v/>
       </c>
       <c r="AE49" s="67"/>
@@ -26559,9 +26610,12 @@
       <c r="Z50" s="68"/>
       <c r="AA50" s="68"/>
       <c r="AB50" s="67"/>
-      <c r="AC50" s="70"/>
+      <c r="AC50" s="70" t="str">
+        <f>IF(AG50="","",WORKDAY(AG50-AF50+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD50" s="66" cm="1" t="str">
-        <f t="array" ref="AD50">IF(AG50="","",WORKDAY($AG50-$AF50+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD50">IF(AG50="","",$AG50-$AF50)</f>
         <v/>
       </c>
       <c r="AE50" s="67"/>
@@ -26653,11 +26707,12 @@
       <c r="AA51" s="68"/>
       <c r="AB51" s="67"/>
       <c r="AC51" s="70">
+        <f>IF(AG51="","",WORKDAY(AG51-AF51+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v>46430</v>
       </c>
       <c r="AD51" s="68" cm="1">
-        <f t="array" ref="AD51">IF(AG51="","",WORKDAY($AG51-$AF51+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46430</v>
+        <f t="array" ref="AD51">IF(AG51="","",$AG51-$AF51)</f>
+        <v>46432</v>
       </c>
       <c r="AE51" s="67"/>
       <c r="AF51" s="83">
@@ -26741,9 +26796,12 @@
       <c r="Z52" s="68"/>
       <c r="AA52" s="68"/>
       <c r="AB52" s="67"/>
-      <c r="AC52" s="70"/>
+      <c r="AC52" s="70" t="str">
+        <f>IF(AG52="","",WORKDAY(AG52-AF52+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD52" s="66" cm="1" t="str">
-        <f t="array" ref="AD52">IF(AG52="","",WORKDAY($AG52-$AF52+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD52">IF(AG52="","",$AG52-$AF52)</f>
         <v/>
       </c>
       <c r="AE52" s="67"/>
@@ -26822,9 +26880,12 @@
       <c r="Z53" s="68"/>
       <c r="AA53" s="68"/>
       <c r="AB53" s="67"/>
-      <c r="AC53" s="70"/>
+      <c r="AC53" s="70" t="str">
+        <f>IF(AG53="","",WORKDAY(AG53-AF53+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD53" s="66" cm="1" t="str">
-        <f t="array" ref="AD53">IF(AG53="","",WORKDAY($AG53-$AF53+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD53">IF(AG53="","",$AG53-$AF53)</f>
         <v/>
       </c>
       <c r="AE53" s="67"/>
@@ -26903,9 +26964,12 @@
       <c r="Z54" s="68"/>
       <c r="AA54" s="68"/>
       <c r="AB54" s="67"/>
-      <c r="AC54" s="70"/>
+      <c r="AC54" s="70" t="str">
+        <f>IF(AG54="","",WORKDAY(AG54-AF54+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD54" s="66" cm="1" t="str">
-        <f t="array" ref="AD54">IF(AG54="","",WORKDAY($AG54-$AF54+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD54">IF(AG54="","",$AG54-$AF54)</f>
         <v/>
       </c>
       <c r="AE54" s="67"/>
@@ -26984,9 +27048,12 @@
       <c r="Z55" s="68"/>
       <c r="AA55" s="68"/>
       <c r="AB55" s="67"/>
-      <c r="AC55" s="70"/>
+      <c r="AC55" s="70" t="str">
+        <f>IF(AG55="","",WORKDAY(AG55-AF55+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD55" s="66" cm="1" t="str">
-        <f t="array" ref="AD55">IF(AG55="","",WORKDAY($AG55-$AF55+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD55">IF(AG55="","",$AG55-$AF55)</f>
         <v/>
       </c>
       <c r="AE55" s="67"/>
@@ -27065,9 +27132,12 @@
       <c r="Z56" s="68"/>
       <c r="AA56" s="68"/>
       <c r="AB56" s="67"/>
-      <c r="AC56" s="70"/>
+      <c r="AC56" s="70" t="str">
+        <f>IF(AG56="","",WORKDAY(AG56-AF56+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD56" s="66" cm="1" t="str">
-        <f t="array" ref="AD56">IF(AG56="","",WORKDAY($AG56-$AF56+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD56">IF(AG56="","",$AG56-$AF56)</f>
         <v/>
       </c>
       <c r="AE56" s="67"/>
@@ -27146,9 +27216,12 @@
       <c r="Z57" s="68"/>
       <c r="AA57" s="68"/>
       <c r="AB57" s="67"/>
-      <c r="AC57" s="70"/>
+      <c r="AC57" s="70" t="str">
+        <f>IF(AG57="","",WORKDAY(AG57-AF57+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD57" s="66" cm="1" t="str">
-        <f t="array" ref="AD57">IF(AG57="","",WORKDAY($AG57-$AF57+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD57">IF(AG57="","",$AG57-$AF57)</f>
         <v/>
       </c>
       <c r="AE57" s="67"/>
@@ -27227,9 +27300,12 @@
       <c r="Z58" s="68"/>
       <c r="AA58" s="68"/>
       <c r="AB58" s="67"/>
-      <c r="AC58" s="70"/>
+      <c r="AC58" s="70" t="str">
+        <f>IF(AG58="","",WORKDAY(AG58-AF58+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD58" s="66" cm="1" t="str">
-        <f t="array" ref="AD58">IF(AG58="","",WORKDAY($AG58-$AF58+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD58">IF(AG58="","",$AG58-$AF58)</f>
         <v/>
       </c>
       <c r="AE58" s="67"/>
@@ -27308,9 +27384,12 @@
       <c r="Z59" s="68"/>
       <c r="AA59" s="68"/>
       <c r="AB59" s="67"/>
-      <c r="AC59" s="70"/>
+      <c r="AC59" s="70" t="str">
+        <f>IF(AG59="","",WORKDAY(AG59-AF59+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD59" s="66" cm="1" t="str">
-        <f t="array" ref="AD59">IF(AG59="","",WORKDAY($AG59-$AF59+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD59">IF(AG59="","",$AG59-$AF59)</f>
         <v/>
       </c>
       <c r="AE59" s="67"/>
@@ -27389,9 +27468,12 @@
       <c r="Z60" s="68"/>
       <c r="AA60" s="68"/>
       <c r="AB60" s="67"/>
-      <c r="AC60" s="70"/>
+      <c r="AC60" s="70" t="str">
+        <f>IF(AG60="","",WORKDAY(AG60-AF60+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD60" s="66" cm="1" t="str">
-        <f t="array" ref="AD60">IF(AG60="","",WORKDAY($AG60-$AF60+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD60">IF(AG60="","",$AG60-$AF60)</f>
         <v/>
       </c>
       <c r="AE60" s="67"/>
@@ -27470,9 +27552,12 @@
       <c r="Z61" s="68"/>
       <c r="AA61" s="68"/>
       <c r="AB61" s="67"/>
-      <c r="AC61" s="70"/>
+      <c r="AC61" s="70" t="str">
+        <f>IF(AG61="","",WORKDAY(AG61-AF61+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD61" s="66" cm="1" t="str">
-        <f t="array" ref="AD61">IF(AG61="","",WORKDAY($AG61-$AF61+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD61">IF(AG61="","",$AG61-$AF61)</f>
         <v/>
       </c>
       <c r="AE61" s="67"/>
@@ -27551,9 +27636,12 @@
       <c r="Z62" s="68"/>
       <c r="AA62" s="68"/>
       <c r="AB62" s="67"/>
-      <c r="AC62" s="70"/>
+      <c r="AC62" s="70" t="str">
+        <f>IF(AG62="","",WORKDAY(AG62-AF62+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD62" s="66" cm="1" t="str">
-        <f t="array" ref="AD62">IF(AG62="","",WORKDAY($AG62-$AF62+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD62">IF(AG62="","",$AG62-$AF62)</f>
         <v/>
       </c>
       <c r="AE62" s="67"/>
@@ -27632,9 +27720,12 @@
       <c r="Z63" s="68"/>
       <c r="AA63" s="68"/>
       <c r="AB63" s="67"/>
-      <c r="AC63" s="70"/>
+      <c r="AC63" s="70" t="str">
+        <f>IF(AG63="","",WORKDAY(AG63-AF63+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD63" s="66" cm="1" t="str">
-        <f t="array" ref="AD63">IF(AG63="","",WORKDAY($AG63-$AF63+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD63">IF(AG63="","",$AG63-$AF63)</f>
         <v/>
       </c>
       <c r="AE63" s="67"/>
@@ -27713,9 +27804,12 @@
       <c r="Z64" s="68"/>
       <c r="AA64" s="68"/>
       <c r="AB64" s="67"/>
-      <c r="AC64" s="70"/>
+      <c r="AC64" s="70" t="str">
+        <f>IF(AG64="","",WORKDAY(AG64-AF64+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD64" s="66" cm="1" t="str">
-        <f t="array" ref="AD64">IF(AG64="","",WORKDAY($AG64-$AF64+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD64">IF(AG64="","",$AG64-$AF64)</f>
         <v/>
       </c>
       <c r="AE64" s="67"/>
@@ -27794,9 +27888,12 @@
       <c r="Z65" s="68"/>
       <c r="AA65" s="68"/>
       <c r="AB65" s="67"/>
-      <c r="AC65" s="70"/>
+      <c r="AC65" s="70" t="str">
+        <f>IF(AG65="","",WORKDAY(AG65-AF65+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD65" s="66" cm="1" t="str">
-        <f t="array" ref="AD65">IF(AG65="","",WORKDAY($AG65-$AF65+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD65">IF(AG65="","",$AG65-$AF65)</f>
         <v/>
       </c>
       <c r="AE65" s="67"/>
@@ -27875,9 +27972,12 @@
       <c r="Z66" s="68"/>
       <c r="AA66" s="68"/>
       <c r="AB66" s="67"/>
-      <c r="AC66" s="70"/>
+      <c r="AC66" s="70" t="str">
+        <f>IF(AG66="","",WORKDAY(AG66-AF66+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD66" s="66" cm="1" t="str">
-        <f t="array" ref="AD66">IF(AG66="","",WORKDAY($AG66-$AF66+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD66">IF(AG66="","",$AG66-$AF66)</f>
         <v/>
       </c>
       <c r="AE66" s="67"/>
@@ -27956,9 +28056,12 @@
       <c r="Z67" s="68"/>
       <c r="AA67" s="68"/>
       <c r="AB67" s="67"/>
-      <c r="AC67" s="70"/>
+      <c r="AC67" s="70" t="str">
+        <f>IF(AG67="","",WORKDAY(AG67-AF67+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD67" s="66" cm="1" t="str">
-        <f t="array" ref="AD67">IF(AG67="","",WORKDAY($AG67-$AF67+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD67">IF(AG67="","",$AG67-$AF67)</f>
         <v/>
       </c>
       <c r="AE67" s="67"/>
@@ -28037,9 +28140,12 @@
       <c r="Z68" s="68"/>
       <c r="AA68" s="68"/>
       <c r="AB68" s="67"/>
-      <c r="AC68" s="70"/>
+      <c r="AC68" s="70" t="str">
+        <f>IF(AG68="","",WORKDAY(AG68-AF68+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD68" s="66" cm="1" t="str">
-        <f t="array" ref="AD68">IF(AG68="","",WORKDAY($AG68-$AF68+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD68">IF(AG68="","",$AG68-$AF68)</f>
         <v/>
       </c>
       <c r="AE68" s="67"/>
@@ -28118,9 +28224,12 @@
       <c r="Z69" s="68"/>
       <c r="AA69" s="68"/>
       <c r="AB69" s="67"/>
-      <c r="AC69" s="70"/>
+      <c r="AC69" s="70" t="str">
+        <f>IF(AG69="","",WORKDAY(AG69-AF69+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD69" s="66" cm="1" t="str">
-        <f t="array" ref="AD69">IF(AG69="","",WORKDAY($AG69-$AF69+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD69">IF(AG69="","",$AG69-$AF69)</f>
         <v/>
       </c>
       <c r="AE69" s="67"/>
@@ -28199,9 +28308,12 @@
       <c r="Z70" s="68"/>
       <c r="AA70" s="68"/>
       <c r="AB70" s="67"/>
-      <c r="AC70" s="70"/>
+      <c r="AC70" s="70" t="str">
+        <f>IF(AG70="","",WORKDAY(AG70-AF70+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD70" s="66" cm="1" t="str">
-        <f t="array" ref="AD70">IF(AG70="","",WORKDAY($AG70-$AF70+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD70">IF(AG70="","",$AG70-$AF70)</f>
         <v/>
       </c>
       <c r="AE70" s="67"/>
@@ -28280,9 +28392,12 @@
       <c r="Z71" s="68"/>
       <c r="AA71" s="68"/>
       <c r="AB71" s="67"/>
-      <c r="AC71" s="70"/>
+      <c r="AC71" s="70" t="str">
+        <f>IF(AG71="","",WORKDAY(AG71-AF71+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD71" s="66" cm="1" t="str">
-        <f t="array" ref="AD71">IF(AG71="","",WORKDAY($AG71-$AF71+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD71">IF(AG71="","",$AG71-$AF71)</f>
         <v/>
       </c>
       <c r="AE71" s="67"/>
@@ -28361,9 +28476,12 @@
       <c r="Z72" s="68"/>
       <c r="AA72" s="68"/>
       <c r="AB72" s="67"/>
-      <c r="AC72" s="70"/>
+      <c r="AC72" s="70" t="str">
+        <f>IF(AG72="","",WORKDAY(AG72-AF72+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD72" s="66" cm="1" t="str">
-        <f t="array" ref="AD72">IF(AG72="","",WORKDAY($AG72-$AF72+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD72">IF(AG72="","",$AG72-$AF72)</f>
         <v/>
       </c>
       <c r="AE72" s="67"/>
@@ -28442,9 +28560,12 @@
       <c r="Z73" s="68"/>
       <c r="AA73" s="68"/>
       <c r="AB73" s="67"/>
-      <c r="AC73" s="70"/>
+      <c r="AC73" s="70" t="str">
+        <f>IF(AG73="","",WORKDAY(AG73-AF73+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD73" s="66" cm="1" t="str">
-        <f t="array" ref="AD73">IF(AG73="","",WORKDAY($AG73-$AF73+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD73">IF(AG73="","",$AG73-$AF73)</f>
         <v/>
       </c>
       <c r="AE73" s="67"/>
@@ -28523,9 +28644,12 @@
       <c r="Z74" s="68"/>
       <c r="AA74" s="68"/>
       <c r="AB74" s="67"/>
-      <c r="AC74" s="70"/>
+      <c r="AC74" s="70" t="str">
+        <f>IF(AG74="","",WORKDAY(AG74-AF74+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD74" s="66" cm="1" t="str">
-        <f t="array" ref="AD74">IF(AG74="","",WORKDAY($AG74-$AF74+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD74">IF(AG74="","",$AG74-$AF74)</f>
         <v/>
       </c>
       <c r="AE74" s="67"/>
@@ -28604,9 +28728,12 @@
       <c r="Z75" s="68"/>
       <c r="AA75" s="68"/>
       <c r="AB75" s="67"/>
-      <c r="AC75" s="70"/>
+      <c r="AC75" s="70" t="str">
+        <f>IF(AG75="","",WORKDAY(AG75-AF75+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD75" s="66" cm="1" t="str">
-        <f t="array" ref="AD75">IF(AG75="","",WORKDAY($AG75-$AF75+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD75">IF(AG75="","",$AG75-$AF75)</f>
         <v/>
       </c>
       <c r="AE75" s="67"/>
@@ -28685,9 +28812,12 @@
       <c r="Z76" s="68"/>
       <c r="AA76" s="68"/>
       <c r="AB76" s="67"/>
-      <c r="AC76" s="70"/>
+      <c r="AC76" s="70" t="str">
+        <f>IF(AG76="","",WORKDAY(AG76-AF76+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD76" s="66" cm="1" t="str">
-        <f t="array" ref="AD76">IF(AG76="","",WORKDAY($AG76-$AF76+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD76">IF(AG76="","",$AG76-$AF76)</f>
         <v/>
       </c>
       <c r="AE76" s="67"/>
@@ -28766,9 +28896,12 @@
       <c r="Z77" s="68"/>
       <c r="AA77" s="68"/>
       <c r="AB77" s="67"/>
-      <c r="AC77" s="70"/>
+      <c r="AC77" s="70" t="str">
+        <f>IF(AG77="","",WORKDAY(AG77-AF77+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD77" s="66" cm="1" t="str">
-        <f t="array" ref="AD77">IF(AG77="","",WORKDAY($AG77-$AF77+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD77">IF(AG77="","",$AG77-$AF77)</f>
         <v/>
       </c>
       <c r="AE77" s="67"/>
@@ -28847,9 +28980,12 @@
       <c r="Z78" s="68"/>
       <c r="AA78" s="68"/>
       <c r="AB78" s="67"/>
-      <c r="AC78" s="70"/>
+      <c r="AC78" s="70" t="str">
+        <f>IF(AG78="","",WORKDAY(AG78-AF78+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD78" s="66" cm="1" t="str">
-        <f t="array" ref="AD78">IF(AG78="","",WORKDAY($AG78-$AF78+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD78">IF(AG78="","",$AG78-$AF78)</f>
         <v/>
       </c>
       <c r="AE78" s="67"/>
@@ -28928,9 +29064,12 @@
       <c r="Z79" s="68"/>
       <c r="AA79" s="68"/>
       <c r="AB79" s="67"/>
-      <c r="AC79" s="70"/>
+      <c r="AC79" s="70" t="str">
+        <f>IF(AG79="","",WORKDAY(AG79-AF79+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD79" s="66" cm="1" t="str">
-        <f t="array" ref="AD79">IF(AG79="","",WORKDAY($AG79-$AF79+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD79">IF(AG79="","",$AG79-$AF79)</f>
         <v/>
       </c>
       <c r="AE79" s="67"/>
@@ -29009,9 +29148,12 @@
       <c r="Z80" s="68"/>
       <c r="AA80" s="68"/>
       <c r="AB80" s="67"/>
-      <c r="AC80" s="70"/>
+      <c r="AC80" s="70" t="str">
+        <f>IF(AG80="","",WORKDAY(AG80-AF80+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD80" s="66" cm="1" t="str">
-        <f t="array" ref="AD80">IF(AG80="","",WORKDAY($AG80-$AF80+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD80">IF(AG80="","",$AG80-$AF80)</f>
         <v/>
       </c>
       <c r="AE80" s="67"/>
@@ -29090,9 +29232,12 @@
       <c r="Z81" s="68"/>
       <c r="AA81" s="68"/>
       <c r="AB81" s="67"/>
-      <c r="AC81" s="70"/>
+      <c r="AC81" s="70" t="str">
+        <f>IF(AG81="","",WORKDAY(AG81-AF81+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD81" s="66" cm="1" t="str">
-        <f t="array" ref="AD81">IF(AG81="","",WORKDAY($AG81-$AF81+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD81">IF(AG81="","",$AG81-$AF81)</f>
         <v/>
       </c>
       <c r="AE81" s="67"/>
@@ -29171,9 +29316,12 @@
       <c r="Z82" s="68"/>
       <c r="AA82" s="68"/>
       <c r="AB82" s="67"/>
-      <c r="AC82" s="70"/>
+      <c r="AC82" s="70" t="str">
+        <f>IF(AG82="","",WORKDAY(AG82-AF82+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD82" s="66" cm="1" t="str">
-        <f t="array" ref="AD82">IF(AG82="","",WORKDAY($AG82-$AF82+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD82">IF(AG82="","",$AG82-$AF82)</f>
         <v/>
       </c>
       <c r="AE82" s="67"/>
@@ -29252,9 +29400,12 @@
       <c r="Z83" s="68"/>
       <c r="AA83" s="68"/>
       <c r="AB83" s="67"/>
-      <c r="AC83" s="70"/>
+      <c r="AC83" s="70" t="str">
+        <f>IF(AG83="","",WORKDAY(AG83-AF83+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD83" s="66" cm="1" t="str">
-        <f t="array" ref="AD83">IF(AG83="","",WORKDAY($AG83-$AF83+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD83">IF(AG83="","",$AG83-$AF83)</f>
         <v/>
       </c>
       <c r="AE83" s="67"/>
@@ -29333,9 +29484,12 @@
       <c r="Z84" s="68"/>
       <c r="AA84" s="68"/>
       <c r="AB84" s="67"/>
-      <c r="AC84" s="70"/>
+      <c r="AC84" s="70" t="str">
+        <f>IF(AG84="","",WORKDAY(AG84-AF84+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD84" s="66" cm="1" t="str">
-        <f t="array" ref="AD84">IF(AG84="","",WORKDAY($AG84-$AF84+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD84">IF(AG84="","",$AG84-$AF84)</f>
         <v/>
       </c>
       <c r="AE84" s="67"/>
@@ -29414,9 +29568,12 @@
       <c r="Z85" s="68"/>
       <c r="AA85" s="68"/>
       <c r="AB85" s="67"/>
-      <c r="AC85" s="70"/>
+      <c r="AC85" s="70" t="str">
+        <f>IF(AG85="","",WORKDAY(AG85-AF85+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD85" s="66" cm="1" t="str">
-        <f t="array" ref="AD85">IF(AG85="","",WORKDAY($AG85-$AF85+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD85">IF(AG85="","",$AG85-$AF85)</f>
         <v/>
       </c>
       <c r="AE85" s="67"/>
@@ -29495,9 +29652,12 @@
       <c r="Z86" s="68"/>
       <c r="AA86" s="68"/>
       <c r="AB86" s="67"/>
-      <c r="AC86" s="70"/>
+      <c r="AC86" s="70" t="str">
+        <f>IF(AG86="","",WORKDAY(AG86-AF86+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD86" s="66" cm="1" t="str">
-        <f t="array" ref="AD86">IF(AG86="","",WORKDAY($AG86-$AF86+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD86">IF(AG86="","",$AG86-$AF86)</f>
         <v/>
       </c>
       <c r="AE86" s="67"/>
@@ -29576,9 +29736,12 @@
       <c r="Z87" s="68"/>
       <c r="AA87" s="68"/>
       <c r="AB87" s="67"/>
-      <c r="AC87" s="70"/>
+      <c r="AC87" s="70" t="str">
+        <f>IF(AG87="","",WORKDAY(AG87-AF87+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD87" s="66" cm="1" t="str">
-        <f t="array" ref="AD87">IF(AG87="","",WORKDAY($AG87-$AF87+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD87">IF(AG87="","",$AG87-$AF87)</f>
         <v/>
       </c>
       <c r="AE87" s="67"/>
@@ -29657,9 +29820,12 @@
       <c r="Z88" s="68"/>
       <c r="AA88" s="68"/>
       <c r="AB88" s="67"/>
-      <c r="AC88" s="70"/>
+      <c r="AC88" s="70" t="str">
+        <f>IF(AG88="","",WORKDAY(AG88-AF88+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD88" s="66" cm="1" t="str">
-        <f t="array" ref="AD88">IF(AG88="","",WORKDAY($AG88-$AF88+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD88">IF(AG88="","",$AG88-$AF88)</f>
         <v/>
       </c>
       <c r="AE88" s="67"/>
@@ -29738,9 +29904,12 @@
       <c r="Z89" s="68"/>
       <c r="AA89" s="68"/>
       <c r="AB89" s="67"/>
-      <c r="AC89" s="70"/>
+      <c r="AC89" s="70" t="str">
+        <f>IF(AG89="","",WORKDAY(AG89-AF89+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD89" s="66" cm="1" t="str">
-        <f t="array" ref="AD89">IF(AG89="","",WORKDAY($AG89-$AF89+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD89">IF(AG89="","",$AG89-$AF89)</f>
         <v/>
       </c>
       <c r="AE89" s="67"/>
@@ -29819,9 +29988,12 @@
       <c r="Z90" s="68"/>
       <c r="AA90" s="68"/>
       <c r="AB90" s="67"/>
-      <c r="AC90" s="70"/>
+      <c r="AC90" s="70" t="str">
+        <f>IF(AG90="","",WORKDAY(AG90-AF90+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD90" s="66" cm="1" t="str">
-        <f t="array" ref="AD90">IF(AG90="","",WORKDAY($AG90-$AF90+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD90">IF(AG90="","",$AG90-$AF90)</f>
         <v/>
       </c>
       <c r="AE90" s="67"/>
@@ -29900,9 +30072,12 @@
       <c r="Z91" s="68"/>
       <c r="AA91" s="68"/>
       <c r="AB91" s="67"/>
-      <c r="AC91" s="70"/>
+      <c r="AC91" s="70" t="str">
+        <f>IF(AG91="","",WORKDAY(AG91-AF91+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD91" s="66" cm="1" t="str">
-        <f t="array" ref="AD91">IF(AG91="","",WORKDAY($AG91-$AF91+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD91">IF(AG91="","",$AG91-$AF91)</f>
         <v/>
       </c>
       <c r="AE91" s="67"/>
@@ -29981,9 +30156,12 @@
       <c r="Z92" s="68"/>
       <c r="AA92" s="68"/>
       <c r="AB92" s="67"/>
-      <c r="AC92" s="70"/>
+      <c r="AC92" s="70" t="str">
+        <f>IF(AG92="","",WORKDAY(AG92-AF92+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD92" s="66" cm="1" t="str">
-        <f t="array" ref="AD92">IF(AG92="","",WORKDAY($AG92-$AF92+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD92">IF(AG92="","",$AG92-$AF92)</f>
         <v/>
       </c>
       <c r="AE92" s="67"/>
@@ -30062,9 +30240,12 @@
       <c r="Z93" s="68"/>
       <c r="AA93" s="68"/>
       <c r="AB93" s="67"/>
-      <c r="AC93" s="70"/>
+      <c r="AC93" s="70" t="str">
+        <f>IF(AG93="","",WORKDAY(AG93-AF93+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD93" s="66" cm="1" t="str">
-        <f t="array" ref="AD93">IF(AG93="","",WORKDAY($AG93-$AF93+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD93">IF(AG93="","",$AG93-$AF93)</f>
         <v/>
       </c>
       <c r="AE93" s="67"/>
@@ -30143,9 +30324,12 @@
       <c r="Z94" s="68"/>
       <c r="AA94" s="68"/>
       <c r="AB94" s="67"/>
-      <c r="AC94" s="70"/>
+      <c r="AC94" s="70" t="str">
+        <f>IF(AG94="","",WORKDAY(AG94-AF94+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD94" s="66" cm="1" t="str">
-        <f t="array" ref="AD94">IF(AG94="","",WORKDAY($AG94-$AF94+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD94">IF(AG94="","",$AG94-$AF94)</f>
         <v/>
       </c>
       <c r="AE94" s="67"/>
@@ -30224,9 +30408,12 @@
       <c r="Z95" s="68"/>
       <c r="AA95" s="68"/>
       <c r="AB95" s="67"/>
-      <c r="AC95" s="70"/>
+      <c r="AC95" s="70" t="str">
+        <f>IF(AG95="","",WORKDAY(AG95-AF95+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD95" s="66" cm="1" t="str">
-        <f t="array" ref="AD95">IF(AG95="","",WORKDAY($AG95-$AF95+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD95">IF(AG95="","",$AG95-$AF95)</f>
         <v/>
       </c>
       <c r="AE95" s="67"/>
@@ -30305,9 +30492,12 @@
       <c r="Z96" s="68"/>
       <c r="AA96" s="68"/>
       <c r="AB96" s="67"/>
-      <c r="AC96" s="70"/>
+      <c r="AC96" s="70" t="str">
+        <f>IF(AG96="","",WORKDAY(AG96-AF96+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD96" s="66" cm="1" t="str">
-        <f t="array" ref="AD96">IF(AG96="","",WORKDAY($AG96-$AF96+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD96">IF(AG96="","",$AG96-$AF96)</f>
         <v/>
       </c>
       <c r="AE96" s="67"/>
@@ -30386,9 +30576,12 @@
       <c r="Z97" s="68"/>
       <c r="AA97" s="68"/>
       <c r="AB97" s="67"/>
-      <c r="AC97" s="70"/>
+      <c r="AC97" s="70" t="str">
+        <f>IF(AG97="","",WORKDAY(AG97-AF97+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD97" s="66" cm="1" t="str">
-        <f t="array" ref="AD97">IF(AG97="","",WORKDAY($AG97-$AF97+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD97">IF(AG97="","",$AG97-$AF97)</f>
         <v/>
       </c>
       <c r="AE97" s="67"/>
@@ -30467,9 +30660,12 @@
       <c r="Z98" s="68"/>
       <c r="AA98" s="68"/>
       <c r="AB98" s="67"/>
-      <c r="AC98" s="70"/>
+      <c r="AC98" s="70" t="str">
+        <f>IF(AG98="","",WORKDAY(AG98-AF98+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD98" s="66" cm="1" t="str">
-        <f t="array" ref="AD98">IF(AG98="","",WORKDAY($AG98-$AF98+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD98">IF(AG98="","",$AG98-$AF98)</f>
         <v/>
       </c>
       <c r="AE98" s="67"/>
@@ -30548,9 +30744,12 @@
       <c r="Z99" s="68"/>
       <c r="AA99" s="68"/>
       <c r="AB99" s="67"/>
-      <c r="AC99" s="70"/>
+      <c r="AC99" s="70" t="str">
+        <f>IF(AG99="","",WORKDAY(AG99-AF99+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD99" s="66" cm="1" t="str">
-        <f t="array" ref="AD99">IF(AG99="","",WORKDAY($AG99-$AF99+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD99">IF(AG99="","",$AG99-$AF99)</f>
         <v/>
       </c>
       <c r="AE99" s="67"/>
@@ -30629,9 +30828,12 @@
       <c r="Z100" s="68"/>
       <c r="AA100" s="68"/>
       <c r="AB100" s="67"/>
-      <c r="AC100" s="70"/>
+      <c r="AC100" s="70" t="str">
+        <f>IF(AG100="","",WORKDAY(AG100-AF100+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD100" s="66" cm="1" t="str">
-        <f t="array" ref="AD100">IF(AG100="","",WORKDAY($AG100-$AF100+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD100">IF(AG100="","",$AG100-$AF100)</f>
         <v/>
       </c>
       <c r="AE100" s="67"/>
@@ -30710,9 +30912,12 @@
       <c r="Z101" s="68"/>
       <c r="AA101" s="68"/>
       <c r="AB101" s="67"/>
-      <c r="AC101" s="70"/>
+      <c r="AC101" s="70" t="str">
+        <f>IF(AG101="","",WORKDAY(AG101-AF101+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD101" s="66" cm="1" t="str">
-        <f t="array" ref="AD101">IF(AG101="","",WORKDAY($AG101-$AF101+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD101">IF(AG101="","",$AG101-$AF101)</f>
         <v/>
       </c>
       <c r="AE101" s="67"/>
@@ -30791,9 +30996,12 @@
       <c r="Z102" s="68"/>
       <c r="AA102" s="68"/>
       <c r="AB102" s="67"/>
-      <c r="AC102" s="70"/>
+      <c r="AC102" s="70" t="str">
+        <f>IF(AG102="","",WORKDAY(AG102-AF102+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD102" s="66" cm="1" t="str">
-        <f t="array" ref="AD102">IF(AG102="","",WORKDAY($AG102-$AF102+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD102">IF(AG102="","",$AG102-$AF102)</f>
         <v/>
       </c>
       <c r="AE102" s="67"/>
@@ -30872,9 +31080,12 @@
       <c r="Z103" s="68"/>
       <c r="AA103" s="68"/>
       <c r="AB103" s="67"/>
-      <c r="AC103" s="70"/>
+      <c r="AC103" s="70" t="str">
+        <f>IF(AG103="","",WORKDAY(AG103-AF103+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD103" s="66" cm="1" t="str">
-        <f t="array" ref="AD103">IF(AG103="","",WORKDAY($AG103-$AF103+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD103">IF(AG103="","",$AG103-$AF103)</f>
         <v/>
       </c>
       <c r="AE103" s="67"/>
@@ -30953,9 +31164,12 @@
       <c r="Z104" s="68"/>
       <c r="AA104" s="68"/>
       <c r="AB104" s="67"/>
-      <c r="AC104" s="70"/>
+      <c r="AC104" s="70" t="str">
+        <f>IF(AG104="","",WORKDAY(AG104-AF104+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD104" s="66" cm="1" t="str">
-        <f t="array" ref="AD104">IF(AG104="","",WORKDAY($AG104-$AF104+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD104">IF(AG104="","",$AG104-$AF104)</f>
         <v/>
       </c>
       <c r="AE104" s="67"/>
@@ -31034,9 +31248,12 @@
       <c r="Z105" s="68"/>
       <c r="AA105" s="68"/>
       <c r="AB105" s="67"/>
-      <c r="AC105" s="70"/>
+      <c r="AC105" s="70" t="str">
+        <f>IF(AG105="","",WORKDAY(AG105-AF105+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD105" s="66" cm="1" t="str">
-        <f t="array" ref="AD105">IF(AG105="","",WORKDAY($AG105-$AF105+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <f t="array" ref="AD105">IF(AG105="","",$AG105-$AF105)</f>
         <v/>
       </c>
       <c r="AE105" s="67"/>
@@ -31115,7 +31332,10 @@
       <c r="Z106" s="68"/>
       <c r="AA106" s="68"/>
       <c r="AB106" s="67"/>
-      <c r="AC106" s="70"/>
+      <c r="AC106" s="70" t="str">
+        <f>IF(AG106="","",WORKDAY(AG106-AF106+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD106" s="68"/>
       <c r="AE106" s="67"/>
       <c r="AF106" s="83"/>
@@ -31193,7 +31413,10 @@
       <c r="Z107" s="68"/>
       <c r="AA107" s="68"/>
       <c r="AB107" s="67"/>
-      <c r="AC107" s="70"/>
+      <c r="AC107" s="70" t="str">
+        <f>IF(AG107="","",WORKDAY(AG107-AF107+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD107" s="68"/>
       <c r="AE107" s="67"/>
       <c r="AF107" s="83"/>
@@ -31271,7 +31494,10 @@
       <c r="Z108" s="68"/>
       <c r="AA108" s="68"/>
       <c r="AB108" s="67"/>
-      <c r="AC108" s="70"/>
+      <c r="AC108" s="70" t="str">
+        <f>IF(AG108="","",WORKDAY(AG108-AF108+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD108" s="68"/>
       <c r="AE108" s="67"/>
       <c r="AF108" s="83"/>
@@ -31349,7 +31575,10 @@
       <c r="Z109" s="68"/>
       <c r="AA109" s="68"/>
       <c r="AB109" s="67"/>
-      <c r="AC109" s="70"/>
+      <c r="AC109" s="70" t="str">
+        <f>IF(AG109="","",WORKDAY(AG109-AF109+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD109" s="68"/>
       <c r="AE109" s="67"/>
       <c r="AF109" s="83"/>
@@ -31427,7 +31656,10 @@
       <c r="Z110" s="68"/>
       <c r="AA110" s="68"/>
       <c r="AB110" s="67"/>
-      <c r="AC110" s="70"/>
+      <c r="AC110" s="70" t="str">
+        <f>IF(AG110="","",WORKDAY(AG110-AF110+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD110" s="68"/>
       <c r="AE110" s="67"/>
       <c r="AF110" s="83"/>
@@ -31505,7 +31737,10 @@
       <c r="Z111" s="68"/>
       <c r="AA111" s="68"/>
       <c r="AB111" s="67"/>
-      <c r="AC111" s="70"/>
+      <c r="AC111" s="70" t="str">
+        <f>IF(AG111="","",WORKDAY(AG111-AF111+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD111" s="68"/>
       <c r="AE111" s="67"/>
       <c r="AF111" s="83"/>
@@ -31583,7 +31818,10 @@
       <c r="Z112" s="68"/>
       <c r="AA112" s="68"/>
       <c r="AB112" s="67"/>
-      <c r="AC112" s="70"/>
+      <c r="AC112" s="70" t="str">
+        <f>IF(AG112="","",WORKDAY(AG112-AF112+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD112" s="68"/>
       <c r="AE112" s="67"/>
       <c r="AF112" s="83"/>
@@ -31661,7 +31899,10 @@
       <c r="Z113" s="68"/>
       <c r="AA113" s="68"/>
       <c r="AB113" s="67"/>
-      <c r="AC113" s="70"/>
+      <c r="AC113" s="70" t="str">
+        <f>IF(AG113="","",WORKDAY(AG113-AF113+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD113" s="68"/>
       <c r="AE113" s="67"/>
       <c r="AF113" s="83"/>
@@ -31739,7 +31980,10 @@
       <c r="Z114" s="68"/>
       <c r="AA114" s="68"/>
       <c r="AB114" s="67"/>
-      <c r="AC114" s="70"/>
+      <c r="AC114" s="70" t="str">
+        <f>IF(AG114="","",WORKDAY(AG114-AF114+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD114" s="68"/>
       <c r="AE114" s="67"/>
       <c r="AF114" s="83"/>
@@ -31817,7 +32061,10 @@
       <c r="Z115" s="68"/>
       <c r="AA115" s="68"/>
       <c r="AB115" s="67"/>
-      <c r="AC115" s="70"/>
+      <c r="AC115" s="70" t="str">
+        <f>IF(AG115="","",WORKDAY(AG115-AF115+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD115" s="68"/>
       <c r="AE115" s="67"/>
       <c r="AF115" s="83"/>
@@ -31895,7 +32142,10 @@
       <c r="Z116" s="68"/>
       <c r="AA116" s="68"/>
       <c r="AB116" s="67"/>
-      <c r="AC116" s="70"/>
+      <c r="AC116" s="70" t="str">
+        <f>IF(AG116="","",WORKDAY(AG116-AF116+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD116" s="68"/>
       <c r="AE116" s="67"/>
       <c r="AF116" s="83"/>
@@ -31973,7 +32223,10 @@
       <c r="Z117" s="68"/>
       <c r="AA117" s="68"/>
       <c r="AB117" s="67"/>
-      <c r="AC117" s="70"/>
+      <c r="AC117" s="70" t="str">
+        <f>IF(AG117="","",WORKDAY(AG117-AF117+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD117" s="68"/>
       <c r="AE117" s="67"/>
       <c r="AF117" s="83"/>
@@ -32051,7 +32304,10 @@
       <c r="Z118" s="68"/>
       <c r="AA118" s="68"/>
       <c r="AB118" s="67"/>
-      <c r="AC118" s="70"/>
+      <c r="AC118" s="70" t="str">
+        <f>IF(AG118="","",WORKDAY(AG118-AF118+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD118" s="68"/>
       <c r="AE118" s="67"/>
       <c r="AF118" s="83"/>
@@ -32129,7 +32385,10 @@
       <c r="Z119" s="68"/>
       <c r="AA119" s="68"/>
       <c r="AB119" s="67"/>
-      <c r="AC119" s="70"/>
+      <c r="AC119" s="70" t="str">
+        <f>IF(AG119="","",WORKDAY(AG119-AF119+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD119" s="68"/>
       <c r="AE119" s="67"/>
       <c r="AF119" s="83"/>
@@ -32207,7 +32466,10 @@
       <c r="Z120" s="68"/>
       <c r="AA120" s="68"/>
       <c r="AB120" s="67"/>
-      <c r="AC120" s="70"/>
+      <c r="AC120" s="70" t="str">
+        <f>IF(AG120="","",WORKDAY(AG120-AF120+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD120" s="68"/>
       <c r="AE120" s="67"/>
       <c r="AF120" s="83"/>
@@ -32285,7 +32547,10 @@
       <c r="Z121" s="68"/>
       <c r="AA121" s="68"/>
       <c r="AB121" s="67"/>
-      <c r="AC121" s="70"/>
+      <c r="AC121" s="70" t="str">
+        <f>IF(AG121="","",WORKDAY(AG121-AF121+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD121" s="68"/>
       <c r="AE121" s="67"/>
       <c r="AF121" s="83"/>
@@ -32363,7 +32628,10 @@
       <c r="Z122" s="68"/>
       <c r="AA122" s="68"/>
       <c r="AB122" s="67"/>
-      <c r="AC122" s="70"/>
+      <c r="AC122" s="70" t="str">
+        <f>IF(AG122="","",WORKDAY(AG122-AF122+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD122" s="68"/>
       <c r="AE122" s="67"/>
       <c r="AF122" s="83"/>
@@ -32441,7 +32709,10 @@
       <c r="Z123" s="68"/>
       <c r="AA123" s="68"/>
       <c r="AB123" s="67"/>
-      <c r="AC123" s="70"/>
+      <c r="AC123" s="70" t="str">
+        <f>IF(AG123="","",WORKDAY(AG123-AF123+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD123" s="68"/>
       <c r="AE123" s="67"/>
       <c r="AF123" s="83"/>
@@ -32519,7 +32790,10 @@
       <c r="Z124" s="68"/>
       <c r="AA124" s="68"/>
       <c r="AB124" s="67"/>
-      <c r="AC124" s="70"/>
+      <c r="AC124" s="70" t="str">
+        <f>IF(AG124="","",WORKDAY(AG124-AF124+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD124" s="68"/>
       <c r="AE124" s="67"/>
       <c r="AF124" s="83"/>
@@ -32597,7 +32871,10 @@
       <c r="Z125" s="68"/>
       <c r="AA125" s="68"/>
       <c r="AB125" s="67"/>
-      <c r="AC125" s="70"/>
+      <c r="AC125" s="70" t="str">
+        <f>IF(AG125="","",WORKDAY(AG125-AF125+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD125" s="68"/>
       <c r="AE125" s="67"/>
       <c r="AF125" s="83"/>
@@ -32675,7 +32952,10 @@
       <c r="Z126" s="68"/>
       <c r="AA126" s="68"/>
       <c r="AB126" s="67"/>
-      <c r="AC126" s="70"/>
+      <c r="AC126" s="70" t="str">
+        <f>IF(AG126="","",WORKDAY(AG126-AF126+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD126" s="68"/>
       <c r="AE126" s="67"/>
       <c r="AF126" s="83"/>
@@ -32753,7 +33033,10 @@
       <c r="Z127" s="68"/>
       <c r="AA127" s="68"/>
       <c r="AB127" s="67"/>
-      <c r="AC127" s="70"/>
+      <c r="AC127" s="70" t="str">
+        <f>IF(AG127="","",WORKDAY(AG127-AF127+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD127" s="68"/>
       <c r="AE127" s="67"/>
       <c r="AF127" s="83"/>
@@ -32831,7 +33114,10 @@
       <c r="Z128" s="68"/>
       <c r="AA128" s="68"/>
       <c r="AB128" s="67"/>
-      <c r="AC128" s="70"/>
+      <c r="AC128" s="70" t="str">
+        <f>IF(AG128="","",WORKDAY(AG128-AF128+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD128" s="68"/>
       <c r="AE128" s="67"/>
       <c r="AF128" s="83"/>
@@ -32909,7 +33195,10 @@
       <c r="Z129" s="68"/>
       <c r="AA129" s="68"/>
       <c r="AB129" s="67"/>
-      <c r="AC129" s="70"/>
+      <c r="AC129" s="70" t="str">
+        <f>IF(AG129="","",WORKDAY(AG129-AF129+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD129" s="68"/>
       <c r="AE129" s="67"/>
       <c r="AF129" s="83"/>
@@ -32987,7 +33276,10 @@
       <c r="Z130" s="68"/>
       <c r="AA130" s="68"/>
       <c r="AB130" s="67"/>
-      <c r="AC130" s="70"/>
+      <c r="AC130" s="70" t="str">
+        <f>IF(AG130="","",WORKDAY(AG130-AF130+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD130" s="68"/>
       <c r="AE130" s="67"/>
       <c r="AF130" s="83"/>
@@ -33065,7 +33357,10 @@
       <c r="Z131" s="68"/>
       <c r="AA131" s="68"/>
       <c r="AB131" s="67"/>
-      <c r="AC131" s="70"/>
+      <c r="AC131" s="70" t="str">
+        <f>IF(AG131="","",WORKDAY(AG131-AF131+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD131" s="68"/>
       <c r="AE131" s="67"/>
       <c r="AF131" s="83"/>
@@ -33143,7 +33438,10 @@
       <c r="Z132" s="68"/>
       <c r="AA132" s="68"/>
       <c r="AB132" s="67"/>
-      <c r="AC132" s="70"/>
+      <c r="AC132" s="70" t="str">
+        <f>IF(AG132="","",WORKDAY(AG132-AF132+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD132" s="68"/>
       <c r="AE132" s="67"/>
       <c r="AF132" s="83"/>
@@ -33221,7 +33519,10 @@
       <c r="Z133" s="68"/>
       <c r="AA133" s="68"/>
       <c r="AB133" s="67"/>
-      <c r="AC133" s="70"/>
+      <c r="AC133" s="70" t="str">
+        <f>IF(AG133="","",WORKDAY(AG133-AF133+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD133" s="68"/>
       <c r="AE133" s="67"/>
       <c r="AF133" s="83"/>
@@ -33299,7 +33600,10 @@
       <c r="Z134" s="68"/>
       <c r="AA134" s="68"/>
       <c r="AB134" s="67"/>
-      <c r="AC134" s="70"/>
+      <c r="AC134" s="70" t="str">
+        <f>IF(AG134="","",WORKDAY(AG134-AF134+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD134" s="68"/>
       <c r="AE134" s="67"/>
       <c r="AF134" s="83"/>
@@ -33377,7 +33681,10 @@
       <c r="Z135" s="68"/>
       <c r="AA135" s="68"/>
       <c r="AB135" s="67"/>
-      <c r="AC135" s="70"/>
+      <c r="AC135" s="70" t="str">
+        <f>IF(AG135="","",WORKDAY(AG135-AF135+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD135" s="68"/>
       <c r="AE135" s="67"/>
       <c r="AF135" s="83"/>
@@ -33455,7 +33762,10 @@
       <c r="Z136" s="68"/>
       <c r="AA136" s="68"/>
       <c r="AB136" s="67"/>
-      <c r="AC136" s="70"/>
+      <c r="AC136" s="70" t="str">
+        <f>IF(AG136="","",WORKDAY(AG136-AF136+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD136" s="68"/>
       <c r="AE136" s="67"/>
       <c r="AF136" s="83"/>
@@ -33533,7 +33843,10 @@
       <c r="Z137" s="68"/>
       <c r="AA137" s="68"/>
       <c r="AB137" s="67"/>
-      <c r="AC137" s="70"/>
+      <c r="AC137" s="70" t="str">
+        <f>IF(AG137="","",WORKDAY(AG137-AF137+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD137" s="68"/>
       <c r="AE137" s="67"/>
       <c r="AF137" s="83"/>
@@ -33611,7 +33924,10 @@
       <c r="Z138" s="68"/>
       <c r="AA138" s="68"/>
       <c r="AB138" s="67"/>
-      <c r="AC138" s="70"/>
+      <c r="AC138" s="70" t="str">
+        <f>IF(AG138="","",WORKDAY(AG138-AF138+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD138" s="68"/>
       <c r="AE138" s="67"/>
       <c r="AF138" s="83"/>
@@ -33689,7 +34005,10 @@
       <c r="Z139" s="68"/>
       <c r="AA139" s="68"/>
       <c r="AB139" s="67"/>
-      <c r="AC139" s="70"/>
+      <c r="AC139" s="70" t="str">
+        <f>IF(AG139="","",WORKDAY(AG139-AF139+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD139" s="68"/>
       <c r="AE139" s="67"/>
       <c r="AF139" s="83"/>
@@ -33767,7 +34086,10 @@
       <c r="Z140" s="68"/>
       <c r="AA140" s="68"/>
       <c r="AB140" s="67"/>
-      <c r="AC140" s="70"/>
+      <c r="AC140" s="70" t="str">
+        <f>IF(AG140="","",WORKDAY(AG140-AF140+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD140" s="68"/>
       <c r="AE140" s="67"/>
       <c r="AF140" s="83"/>
@@ -33845,7 +34167,10 @@
       <c r="Z141" s="68"/>
       <c r="AA141" s="68"/>
       <c r="AB141" s="67"/>
-      <c r="AC141" s="70"/>
+      <c r="AC141" s="70" t="str">
+        <f>IF(AG141="","",WORKDAY(AG141-AF141+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD141" s="68"/>
       <c r="AE141" s="67"/>
       <c r="AF141" s="83"/>
@@ -33923,7 +34248,10 @@
       <c r="Z142" s="68"/>
       <c r="AA142" s="68"/>
       <c r="AB142" s="67"/>
-      <c r="AC142" s="70"/>
+      <c r="AC142" s="70" t="str">
+        <f>IF(AG142="","",WORKDAY(AG142-AF142+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD142" s="68"/>
       <c r="AE142" s="67"/>
       <c r="AF142" s="83"/>
@@ -34001,7 +34329,10 @@
       <c r="Z143" s="68"/>
       <c r="AA143" s="68"/>
       <c r="AB143" s="67"/>
-      <c r="AC143" s="70"/>
+      <c r="AC143" s="70" t="str">
+        <f>IF(AG143="","",WORKDAY(AG143-AF143+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD143" s="68"/>
       <c r="AE143" s="67"/>
       <c r="AF143" s="83"/>
@@ -34079,7 +34410,10 @@
       <c r="Z144" s="68"/>
       <c r="AA144" s="68"/>
       <c r="AB144" s="67"/>
-      <c r="AC144" s="70"/>
+      <c r="AC144" s="70" t="str">
+        <f>IF(AG144="","",WORKDAY(AG144-AF144+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD144" s="68"/>
       <c r="AE144" s="67"/>
       <c r="AF144" s="83"/>
@@ -34157,7 +34491,10 @@
       <c r="Z145" s="68"/>
       <c r="AA145" s="68"/>
       <c r="AB145" s="67"/>
-      <c r="AC145" s="70"/>
+      <c r="AC145" s="70" t="str">
+        <f>IF(AG145="","",WORKDAY(AG145-AF145+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD145" s="68"/>
       <c r="AE145" s="67"/>
       <c r="AF145" s="83"/>
@@ -34235,7 +34572,10 @@
       <c r="Z146" s="68"/>
       <c r="AA146" s="68"/>
       <c r="AB146" s="67"/>
-      <c r="AC146" s="70"/>
+      <c r="AC146" s="70" t="str">
+        <f>IF(AG146="","",WORKDAY(AG146-AF146+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD146" s="68"/>
       <c r="AE146" s="67"/>
       <c r="AF146" s="83"/>
@@ -34313,7 +34653,10 @@
       <c r="Z147" s="68"/>
       <c r="AA147" s="68"/>
       <c r="AB147" s="67"/>
-      <c r="AC147" s="70"/>
+      <c r="AC147" s="70" t="str">
+        <f>IF(AG147="","",WORKDAY(AG147-AF147+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD147" s="68"/>
       <c r="AE147" s="67"/>
       <c r="AF147" s="83"/>
@@ -34391,7 +34734,10 @@
       <c r="Z148" s="68"/>
       <c r="AA148" s="68"/>
       <c r="AB148" s="67"/>
-      <c r="AC148" s="70"/>
+      <c r="AC148" s="70" t="str">
+        <f>IF(AG148="","",WORKDAY(AG148-AF148+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD148" s="68"/>
       <c r="AE148" s="67"/>
       <c r="AF148" s="83"/>
@@ -34469,7 +34815,10 @@
       <c r="Z149" s="68"/>
       <c r="AA149" s="68"/>
       <c r="AB149" s="67"/>
-      <c r="AC149" s="70"/>
+      <c r="AC149" s="70" t="str">
+        <f>IF(AG149="","",WORKDAY(AG149-AF149+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD149" s="68"/>
       <c r="AE149" s="67"/>
       <c r="AF149" s="83"/>
@@ -34547,7 +34896,10 @@
       <c r="Z150" s="68"/>
       <c r="AA150" s="68"/>
       <c r="AB150" s="67"/>
-      <c r="AC150" s="70"/>
+      <c r="AC150" s="70" t="str">
+        <f>IF(AG150="","",WORKDAY(AG150-AF150+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD150" s="68"/>
       <c r="AE150" s="67"/>
       <c r="AF150" s="83"/>
@@ -34625,7 +34977,10 @@
       <c r="Z151" s="68"/>
       <c r="AA151" s="68"/>
       <c r="AB151" s="67"/>
-      <c r="AC151" s="70"/>
+      <c r="AC151" s="70" t="str">
+        <f>IF(AG151="","",WORKDAY(AG151-AF151+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
+        <v/>
+      </c>
       <c r="AD151" s="68"/>
       <c r="AE151" s="67"/>
       <c r="AF151" s="83"/>
@@ -34703,8 +35058,8 @@
       <c r="Z152" s="68"/>
       <c r="AA152" s="68"/>
       <c r="AB152" s="67"/>
-      <c r="AC152" s="82" cm="1" t="str">
-        <f t="array" ref="AC152">IF(AG152="","",AG152-AF152)</f>
+      <c r="AC152" s="82" t="str">
+        <f>IF(AG152="","",WORKDAY(AG152-AF152+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD152" s="68"/>
@@ -34784,8 +35139,8 @@
       <c r="Z153" s="68"/>
       <c r="AA153" s="68"/>
       <c r="AB153" s="67"/>
-      <c r="AC153" s="82" cm="1" t="str">
-        <f t="array" ref="AC153">IF(AG153="","",AG153-AF153)</f>
+      <c r="AC153" s="82" t="str">
+        <f>IF(AG153="","",WORKDAY(AG153-AF153+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD153" s="68"/>
@@ -34865,8 +35220,8 @@
       <c r="Z154" s="68"/>
       <c r="AA154" s="68"/>
       <c r="AB154" s="67"/>
-      <c r="AC154" s="82" cm="1" t="str">
-        <f t="array" ref="AC154">IF(AG154="","",AG154-AF154)</f>
+      <c r="AC154" s="82" t="str">
+        <f>IF(AG154="","",WORKDAY(AG154-AF154+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD154" s="68"/>
@@ -34946,8 +35301,8 @@
       <c r="Z155" s="68"/>
       <c r="AA155" s="68"/>
       <c r="AB155" s="67"/>
-      <c r="AC155" s="82" cm="1" t="str">
-        <f t="array" ref="AC155">IF(AG155="","",AG155-AF155)</f>
+      <c r="AC155" s="82" t="str">
+        <f>IF(AG155="","",WORKDAY(AG155-AF155+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD155" s="68"/>
@@ -35027,8 +35382,8 @@
       <c r="Z156" s="68"/>
       <c r="AA156" s="68"/>
       <c r="AB156" s="67"/>
-      <c r="AC156" s="82" cm="1" t="str">
-        <f t="array" ref="AC156">IF(AG156="","",AG156-AF156)</f>
+      <c r="AC156" s="82" t="str">
+        <f>IF(AG156="","",WORKDAY(AG156-AF156+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD156" s="68"/>
@@ -35108,8 +35463,8 @@
       <c r="Z157" s="68"/>
       <c r="AA157" s="68"/>
       <c r="AB157" s="67"/>
-      <c r="AC157" s="82" cm="1" t="str">
-        <f t="array" ref="AC157">IF(AG157="","",AG157-AF157)</f>
+      <c r="AC157" s="82" t="str">
+        <f>IF(AG157="","",WORKDAY(AG157-AF157+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD157" s="68"/>
@@ -35189,8 +35544,8 @@
       <c r="Z158" s="68"/>
       <c r="AA158" s="68"/>
       <c r="AB158" s="67"/>
-      <c r="AC158" s="82" cm="1" t="str">
-        <f t="array" ref="AC158">IF(AG158="","",AG158-AF158)</f>
+      <c r="AC158" s="82" t="str">
+        <f>IF(AG158="","",WORKDAY(AG158-AF158+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD158" s="68"/>
@@ -35270,8 +35625,8 @@
       <c r="Z159" s="68"/>
       <c r="AA159" s="68"/>
       <c r="AB159" s="67"/>
-      <c r="AC159" s="82" cm="1" t="str">
-        <f t="array" ref="AC159">IF(AG159="","",AG159-AF159)</f>
+      <c r="AC159" s="82" t="str">
+        <f>IF(AG159="","",WORKDAY(AG159-AF159+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD159" s="68"/>
@@ -35351,8 +35706,8 @@
       <c r="Z160" s="68"/>
       <c r="AA160" s="68"/>
       <c r="AB160" s="67"/>
-      <c r="AC160" s="82" cm="1" t="str">
-        <f t="array" ref="AC160">IF(AG160="","",AG160-AF160)</f>
+      <c r="AC160" s="82" t="str">
+        <f>IF(AG160="","",WORKDAY(AG160-AF160+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD160" s="68"/>
@@ -35432,8 +35787,8 @@
       <c r="Z161" s="68"/>
       <c r="AA161" s="68"/>
       <c r="AB161" s="67"/>
-      <c r="AC161" s="82" cm="1" t="str">
-        <f t="array" ref="AC161">IF(AG161="","",AG161-AF161)</f>
+      <c r="AC161" s="82" t="str">
+        <f>IF(AG161="","",WORKDAY(AG161-AF161+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD161" s="68"/>
@@ -35513,8 +35868,8 @@
       <c r="Z162" s="68"/>
       <c r="AA162" s="68"/>
       <c r="AB162" s="67"/>
-      <c r="AC162" s="82" cm="1" t="str">
-        <f t="array" ref="AC162">IF(AG162="","",AG162-AF162)</f>
+      <c r="AC162" s="82" t="str">
+        <f>IF(AG162="","",WORKDAY(AG162-AF162+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD162" s="68"/>
@@ -35594,8 +35949,8 @@
       <c r="Z163" s="68"/>
       <c r="AA163" s="68"/>
       <c r="AB163" s="67"/>
-      <c r="AC163" s="82" cm="1" t="str">
-        <f t="array" ref="AC163">IF(AG163="","",AG163-AF163)</f>
+      <c r="AC163" s="82" t="str">
+        <f>IF(AG163="","",WORKDAY(AG163-AF163+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD163" s="68"/>
@@ -35675,8 +36030,8 @@
       <c r="Z164" s="68"/>
       <c r="AA164" s="68"/>
       <c r="AB164" s="67"/>
-      <c r="AC164" s="82" cm="1" t="str">
-        <f t="array" ref="AC164">IF(AG164="","",AG164-AF164)</f>
+      <c r="AC164" s="82" t="str">
+        <f>IF(AG164="","",WORKDAY(AG164-AF164+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD164" s="68"/>
@@ -35756,8 +36111,8 @@
       <c r="Z165" s="68"/>
       <c r="AA165" s="68"/>
       <c r="AB165" s="67"/>
-      <c r="AC165" s="82" cm="1" t="str">
-        <f t="array" ref="AC165">IF(AG165="","",AG165-AF165)</f>
+      <c r="AC165" s="82" t="str">
+        <f>IF(AG165="","",WORKDAY(AG165-AF165+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD165" s="68"/>
@@ -35837,8 +36192,8 @@
       <c r="Z166" s="68"/>
       <c r="AA166" s="68"/>
       <c r="AB166" s="67"/>
-      <c r="AC166" s="82" cm="1" t="str">
-        <f t="array" ref="AC166">IF(AG166="","",AG166-AF166)</f>
+      <c r="AC166" s="82" t="str">
+        <f>IF(AG166="","",WORKDAY(AG166-AF166+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD166" s="68"/>
@@ -35918,8 +36273,8 @@
       <c r="Z167" s="68"/>
       <c r="AA167" s="68"/>
       <c r="AB167" s="67"/>
-      <c r="AC167" s="82" cm="1" t="str">
-        <f t="array" ref="AC167">IF(AG167="","",AG167-AF167)</f>
+      <c r="AC167" s="82" t="str">
+        <f>IF(AG167="","",WORKDAY(AG167-AF167+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD167" s="68"/>
@@ -35999,8 +36354,8 @@
       <c r="Z168" s="68"/>
       <c r="AA168" s="68"/>
       <c r="AB168" s="67"/>
-      <c r="AC168" s="82" cm="1" t="str">
-        <f t="array" ref="AC168">IF(AG168="","",AG168-AF168)</f>
+      <c r="AC168" s="82" t="str">
+        <f>IF(AG168="","",WORKDAY(AG168-AF168+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD168" s="68"/>
@@ -36080,8 +36435,8 @@
       <c r="Z169" s="68"/>
       <c r="AA169" s="68"/>
       <c r="AB169" s="67"/>
-      <c r="AC169" s="82" cm="1" t="str">
-        <f t="array" ref="AC169">IF(AG169="","",AG169-AF169)</f>
+      <c r="AC169" s="82" t="str">
+        <f>IF(AG169="","",WORKDAY(AG169-AF169+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD169" s="68"/>
@@ -36161,8 +36516,8 @@
       <c r="Z170" s="68"/>
       <c r="AA170" s="68"/>
       <c r="AB170" s="67"/>
-      <c r="AC170" s="82" cm="1" t="str">
-        <f t="array" ref="AC170">IF(AG170="","",AG170-AF170)</f>
+      <c r="AC170" s="82" t="str">
+        <f>IF(AG170="","",WORKDAY(AG170-AF170+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD170" s="68"/>
@@ -36242,8 +36597,8 @@
       <c r="Z171" s="68"/>
       <c r="AA171" s="68"/>
       <c r="AB171" s="67"/>
-      <c r="AC171" s="82" cm="1" t="str">
-        <f t="array" ref="AC171">IF(AG171="","",AG171-AF171)</f>
+      <c r="AC171" s="82" t="str">
+        <f>IF(AG171="","",WORKDAY(AG171-AF171+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD171" s="68"/>
@@ -36323,8 +36678,8 @@
       <c r="Z172" s="68"/>
       <c r="AA172" s="68"/>
       <c r="AB172" s="67"/>
-      <c r="AC172" s="82" cm="1" t="str">
-        <f t="array" ref="AC172">IF(AG172="","",AG172-AF172)</f>
+      <c r="AC172" s="82" t="str">
+        <f>IF(AG172="","",WORKDAY(AG172-AF172+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD172" s="68"/>
@@ -36404,8 +36759,8 @@
       <c r="Z173" s="68"/>
       <c r="AA173" s="68"/>
       <c r="AB173" s="67"/>
-      <c r="AC173" s="82" cm="1" t="str">
-        <f t="array" ref="AC173">IF(AG173="","",AG173-AF173)</f>
+      <c r="AC173" s="82" t="str">
+        <f>IF(AG173="","",WORKDAY(AG173-AF173+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD173" s="68"/>
@@ -36485,8 +36840,8 @@
       <c r="Z174" s="68"/>
       <c r="AA174" s="68"/>
       <c r="AB174" s="67"/>
-      <c r="AC174" s="82" cm="1" t="str">
-        <f t="array" ref="AC174">IF(AG174="","",AG174-AF174)</f>
+      <c r="AC174" s="82" t="str">
+        <f>IF(AG174="","",WORKDAY(AG174-AF174+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD174" s="68"/>
@@ -36566,8 +36921,8 @@
       <c r="Z175" s="68"/>
       <c r="AA175" s="68"/>
       <c r="AB175" s="67"/>
-      <c r="AC175" s="82" cm="1" t="str">
-        <f t="array" ref="AC175">IF(AG175="","",AG175-AF175)</f>
+      <c r="AC175" s="82" t="str">
+        <f>IF(AG175="","",WORKDAY(AG175-AF175+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD175" s="68"/>
@@ -36647,8 +37002,8 @@
       <c r="Z176" s="68"/>
       <c r="AA176" s="68"/>
       <c r="AB176" s="67"/>
-      <c r="AC176" s="82" cm="1" t="str">
-        <f t="array" ref="AC176">IF(AG176="","",AG176-AF176)</f>
+      <c r="AC176" s="82" t="str">
+        <f>IF(AG176="","",WORKDAY(AG176-AF176+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD176" s="68"/>
@@ -36728,8 +37083,8 @@
       <c r="Z177" s="68"/>
       <c r="AA177" s="68"/>
       <c r="AB177" s="67"/>
-      <c r="AC177" s="82" cm="1" t="str">
-        <f t="array" ref="AC177">IF(AG177="","",AG177-AF177)</f>
+      <c r="AC177" s="82" t="str">
+        <f>IF(AG177="","",WORKDAY(AG177-AF177+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD177" s="68"/>
@@ -36809,8 +37164,8 @@
       <c r="Z178" s="68"/>
       <c r="AA178" s="68"/>
       <c r="AB178" s="67"/>
-      <c r="AC178" s="82" cm="1" t="str">
-        <f t="array" ref="AC178">IF(AG178="","",AG178-AF178)</f>
+      <c r="AC178" s="82" t="str">
+        <f>IF(AG178="","",WORKDAY(AG178-AF178+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD178" s="68"/>
@@ -36890,8 +37245,8 @@
       <c r="Z179" s="68"/>
       <c r="AA179" s="68"/>
       <c r="AB179" s="67"/>
-      <c r="AC179" s="82" cm="1" t="str">
-        <f t="array" ref="AC179">IF(AG179="","",AG179-AF179)</f>
+      <c r="AC179" s="82" t="str">
+        <f>IF(AG179="","",WORKDAY(AG179-AF179+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD179" s="68"/>
@@ -36971,8 +37326,8 @@
       <c r="Z180" s="68"/>
       <c r="AA180" s="68"/>
       <c r="AB180" s="67"/>
-      <c r="AC180" s="82" cm="1" t="str">
-        <f t="array" ref="AC180">IF(AG180="","",AG180-AF180)</f>
+      <c r="AC180" s="82" t="str">
+        <f>IF(AG180="","",WORKDAY(AG180-AF180+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD180" s="68"/>
@@ -37052,8 +37407,8 @@
       <c r="Z181" s="68"/>
       <c r="AA181" s="68"/>
       <c r="AB181" s="67"/>
-      <c r="AC181" s="82" cm="1" t="str">
-        <f t="array" ref="AC181">IF(AG181="","",AG181-AF181)</f>
+      <c r="AC181" s="82" t="str">
+        <f>IF(AG181="","",WORKDAY(AG181-AF181+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD181" s="68"/>
@@ -37133,8 +37488,8 @@
       <c r="Z182" s="68"/>
       <c r="AA182" s="68"/>
       <c r="AB182" s="67"/>
-      <c r="AC182" s="82" cm="1" t="str">
-        <f t="array" ref="AC182">IF(AG182="","",AG182-AF182)</f>
+      <c r="AC182" s="82" t="str">
+        <f>IF(AG182="","",WORKDAY(AG182-AF182+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD182" s="68"/>
@@ -37214,8 +37569,8 @@
       <c r="Z183" s="68"/>
       <c r="AA183" s="68"/>
       <c r="AB183" s="67"/>
-      <c r="AC183" s="82" cm="1" t="str">
-        <f t="array" ref="AC183">IF(AG183="","",AG183-AF183)</f>
+      <c r="AC183" s="82" t="str">
+        <f>IF(AG183="","",WORKDAY(AG183-AF183+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD183" s="68"/>
@@ -37295,8 +37650,8 @@
       <c r="Z184" s="68"/>
       <c r="AA184" s="68"/>
       <c r="AB184" s="67"/>
-      <c r="AC184" s="82" cm="1" t="str">
-        <f t="array" ref="AC184">IF(AG184="","",AG184-AF184)</f>
+      <c r="AC184" s="82" t="str">
+        <f>IF(AG184="","",WORKDAY(AG184-AF184+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD184" s="68"/>
@@ -37376,8 +37731,8 @@
       <c r="Z185" s="68"/>
       <c r="AA185" s="68"/>
       <c r="AB185" s="67"/>
-      <c r="AC185" s="82" cm="1" t="str">
-        <f t="array" ref="AC185">IF(AG185="","",AG185-AF185)</f>
+      <c r="AC185" s="82" t="str">
+        <f>IF(AG185="","",WORKDAY(AG185-AF185+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD185" s="68"/>
@@ -37457,8 +37812,8 @@
       <c r="Z186" s="68"/>
       <c r="AA186" s="68"/>
       <c r="AB186" s="67"/>
-      <c r="AC186" s="82" cm="1" t="str">
-        <f t="array" ref="AC186">IF(AG186="","",AG186-AF186)</f>
+      <c r="AC186" s="82" t="str">
+        <f>IF(AG186="","",WORKDAY(AG186-AF186+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD186" s="68"/>
@@ -37538,8 +37893,8 @@
       <c r="Z187" s="68"/>
       <c r="AA187" s="68"/>
       <c r="AB187" s="67"/>
-      <c r="AC187" s="82" cm="1" t="str">
-        <f t="array" ref="AC187">IF(AG187="","",AG187-AF187)</f>
+      <c r="AC187" s="82" t="str">
+        <f>IF(AG187="","",WORKDAY(AG187-AF187+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD187" s="68"/>
@@ -37619,8 +37974,8 @@
       <c r="Z188" s="68"/>
       <c r="AA188" s="68"/>
       <c r="AB188" s="67"/>
-      <c r="AC188" s="82" cm="1" t="str">
-        <f t="array" ref="AC188">IF(AG188="","",AG188-AF188)</f>
+      <c r="AC188" s="82" t="str">
+        <f>IF(AG188="","",WORKDAY(AG188-AF188+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD188" s="68"/>
@@ -37700,8 +38055,8 @@
       <c r="Z189" s="68"/>
       <c r="AA189" s="68"/>
       <c r="AB189" s="67"/>
-      <c r="AC189" s="82" cm="1" t="str">
-        <f t="array" ref="AC189">IF(AG189="","",AG189-AF189)</f>
+      <c r="AC189" s="82" t="str">
+        <f>IF(AG189="","",WORKDAY(AG189-AF189+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD189" s="68"/>
@@ -37781,8 +38136,8 @@
       <c r="Z190" s="68"/>
       <c r="AA190" s="68"/>
       <c r="AB190" s="67"/>
-      <c r="AC190" s="82" cm="1" t="str">
-        <f t="array" ref="AC190">IF(AG190="","",AG190-AF190)</f>
+      <c r="AC190" s="82" t="str">
+        <f>IF(AG190="","",WORKDAY(AG190-AF190+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD190" s="68"/>
@@ -37862,8 +38217,8 @@
       <c r="Z191" s="68"/>
       <c r="AA191" s="68"/>
       <c r="AB191" s="67"/>
-      <c r="AC191" s="82" cm="1" t="str">
-        <f t="array" ref="AC191">IF(AG191="","",AG191-AF191)</f>
+      <c r="AC191" s="82" t="str">
+        <f>IF(AG191="","",WORKDAY(AG191-AF191+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD191" s="68"/>
@@ -37943,8 +38298,8 @@
       <c r="Z192" s="68"/>
       <c r="AA192" s="68"/>
       <c r="AB192" s="67"/>
-      <c r="AC192" s="82" cm="1" t="str">
-        <f t="array" ref="AC192">IF(AG192="","",AG192-AF192)</f>
+      <c r="AC192" s="82" t="str">
+        <f>IF(AG192="","",WORKDAY(AG192-AF192+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD192" s="68"/>
@@ -38024,8 +38379,8 @@
       <c r="Z193" s="68"/>
       <c r="AA193" s="68"/>
       <c r="AB193" s="67"/>
-      <c r="AC193" s="82" cm="1" t="str">
-        <f t="array" ref="AC193">IF(AG193="","",AG193-AF193)</f>
+      <c r="AC193" s="82" t="str">
+        <f>IF(AG193="","",WORKDAY(AG193-AF193+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD193" s="68"/>
@@ -38105,8 +38460,8 @@
       <c r="Z194" s="68"/>
       <c r="AA194" s="68"/>
       <c r="AB194" s="67"/>
-      <c r="AC194" s="82" cm="1" t="str">
-        <f t="array" ref="AC194">IF(AG194="","",AG194-AF194)</f>
+      <c r="AC194" s="82" t="str">
+        <f>IF(AG194="","",WORKDAY(AG194-AF194+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD194" s="68"/>
@@ -38186,8 +38541,8 @@
       <c r="Z195" s="68"/>
       <c r="AA195" s="68"/>
       <c r="AB195" s="67"/>
-      <c r="AC195" s="82" cm="1" t="str">
-        <f t="array" ref="AC195">IF(AG195="","",AG195-AF195)</f>
+      <c r="AC195" s="82" t="str">
+        <f>IF(AG195="","",WORKDAY(AG195-AF195+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD195" s="68"/>
@@ -38267,8 +38622,8 @@
       <c r="Z196" s="68"/>
       <c r="AA196" s="68"/>
       <c r="AB196" s="67"/>
-      <c r="AC196" s="82" cm="1" t="str">
-        <f t="array" ref="AC196">IF(AG196="","",AG196-AF196)</f>
+      <c r="AC196" s="82" t="str">
+        <f>IF(AG196="","",WORKDAY(AG196-AF196+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD196" s="68"/>
@@ -38348,8 +38703,8 @@
       <c r="Z197" s="68"/>
       <c r="AA197" s="68"/>
       <c r="AB197" s="67"/>
-      <c r="AC197" s="82" cm="1" t="str">
-        <f t="array" ref="AC197">IF(AG197="","",AG197-AF197)</f>
+      <c r="AC197" s="82" t="str">
+        <f>IF(AG197="","",WORKDAY(AG197-AF197+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD197" s="68"/>
@@ -38429,8 +38784,8 @@
       <c r="Z198" s="68"/>
       <c r="AA198" s="68"/>
       <c r="AB198" s="67"/>
-      <c r="AC198" s="82" cm="1" t="str">
-        <f t="array" ref="AC198">IF(AG198="","",AG198-AF198)</f>
+      <c r="AC198" s="82" t="str">
+        <f>IF(AG198="","",WORKDAY(AG198-AF198+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD198" s="68"/>
@@ -38510,8 +38865,8 @@
       <c r="Z199" s="68"/>
       <c r="AA199" s="68"/>
       <c r="AB199" s="67"/>
-      <c r="AC199" s="82" cm="1" t="str">
-        <f t="array" ref="AC199">IF(AG199="","",AG199-AF199)</f>
+      <c r="AC199" s="82" t="str">
+        <f>IF(AG199="","",WORKDAY(AG199-AF199+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD199" s="68"/>
@@ -38591,8 +38946,8 @@
       <c r="Z200" s="68"/>
       <c r="AA200" s="68"/>
       <c r="AB200" s="67"/>
-      <c r="AC200" s="82" cm="1" t="str">
-        <f t="array" ref="AC200">IF(AG200="","",AG200-AF200)</f>
+      <c r="AC200" s="82" t="str">
+        <f>IF(AG200="","",WORKDAY(AG200-AF200+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD200" s="68"/>
@@ -38672,8 +39027,8 @@
       <c r="Z201" s="68"/>
       <c r="AA201" s="68"/>
       <c r="AB201" s="67"/>
-      <c r="AC201" s="82" cm="1" t="str">
-        <f t="array" ref="AC201">IF(AG201="","",AG201-AF201)</f>
+      <c r="AC201" s="82" t="str">
+        <f>IF(AG201="","",WORKDAY(AG201-AF201+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD201" s="68"/>
@@ -38753,8 +39108,8 @@
       <c r="Z202" s="68"/>
       <c r="AA202" s="68"/>
       <c r="AB202" s="67"/>
-      <c r="AC202" s="82" cm="1" t="str">
-        <f t="array" ref="AC202">IF(AG202="","",AG202-AF202)</f>
+      <c r="AC202" s="82" t="str">
+        <f>IF(AG202="","",WORKDAY(AG202-AF202+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD202" s="68"/>
@@ -38834,8 +39189,8 @@
       <c r="Z203" s="68"/>
       <c r="AA203" s="68"/>
       <c r="AB203" s="67"/>
-      <c r="AC203" s="82" cm="1" t="str">
-        <f t="array" ref="AC203">IF(AG203="","",AG203-AF203)</f>
+      <c r="AC203" s="82" t="str">
+        <f>IF(AG203="","",WORKDAY(AG203-AF203+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD203" s="68"/>
@@ -38915,8 +39270,8 @@
       <c r="Z204" s="68"/>
       <c r="AA204" s="68"/>
       <c r="AB204" s="67"/>
-      <c r="AC204" s="82" cm="1" t="str">
-        <f t="array" ref="AC204">IF(AG204="","",AG204-AF204)</f>
+      <c r="AC204" s="82" t="str">
+        <f>IF(AG204="","",WORKDAY(AG204-AF204+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD204" s="68"/>
@@ -38996,8 +39351,8 @@
       <c r="Z205" s="68"/>
       <c r="AA205" s="68"/>
       <c r="AB205" s="67"/>
-      <c r="AC205" s="82" cm="1" t="str">
-        <f t="array" ref="AC205">IF(AG205="","",AG205-AF205)</f>
+      <c r="AC205" s="82" t="str">
+        <f>IF(AG205="","",WORKDAY(AG205-AF205+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD205" s="68"/>
@@ -39077,8 +39432,8 @@
       <c r="Z206" s="68"/>
       <c r="AA206" s="68"/>
       <c r="AB206" s="67"/>
-      <c r="AC206" s="82" cm="1" t="str">
-        <f t="array" ref="AC206">IF(AG206="","",AG206-AF206)</f>
+      <c r="AC206" s="82" t="str">
+        <f>IF(AG206="","",WORKDAY(AG206-AF206+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD206" s="68"/>
@@ -39158,8 +39513,8 @@
       <c r="Z207" s="68"/>
       <c r="AA207" s="68"/>
       <c r="AB207" s="67"/>
-      <c r="AC207" s="82" cm="1" t="str">
-        <f t="array" ref="AC207">IF(AG207="","",AG207-AF207)</f>
+      <c r="AC207" s="82" t="str">
+        <f>IF(AG207="","",WORKDAY(AG207-AF207+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD207" s="68"/>
@@ -39239,8 +39594,8 @@
       <c r="Z208" s="68"/>
       <c r="AA208" s="68"/>
       <c r="AB208" s="67"/>
-      <c r="AC208" s="82" cm="1" t="str">
-        <f t="array" ref="AC208">IF(AG208="","",AG208-AF208)</f>
+      <c r="AC208" s="82" t="str">
+        <f>IF(AG208="","",WORKDAY(AG208-AF208+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD208" s="68"/>
@@ -39320,8 +39675,8 @@
       <c r="Z209" s="68"/>
       <c r="AA209" s="68"/>
       <c r="AB209" s="67"/>
-      <c r="AC209" s="82" cm="1" t="str">
-        <f t="array" ref="AC209">IF(AG209="","",AG209-AF209)</f>
+      <c r="AC209" s="82" t="str">
+        <f>IF(AG209="","",WORKDAY(AG209-AF209+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD209" s="68"/>
@@ -39401,8 +39756,8 @@
       <c r="Z210" s="68"/>
       <c r="AA210" s="68"/>
       <c r="AB210" s="67"/>
-      <c r="AC210" s="82" cm="1" t="str">
-        <f t="array" ref="AC210">IF(AG210="","",AG210-AF210)</f>
+      <c r="AC210" s="82" t="str">
+        <f>IF(AG210="","",WORKDAY(AG210-AF210+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
       <c r="AD210" s="68"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -8942,14 +8942,14 @@
       </c>
       <c r="AD12" s="68" cm="1">
         <f t="array" ref="AD12">IF(AG12="","",AG12-AF12)</f>
-        <v>46014</v>
+        <v>46379</v>
       </c>
       <c r="AE12" s="67"/>
       <c r="AF12" s="65">
         <v>14</v>
       </c>
       <c r="AG12" s="67">
-        <v>46028</v>
+        <v>46393</v>
       </c>
       <c r="AH12" s="74" t="s">
         <v>60</v>
@@ -22423,11 +22423,11 @@
       </c>
       <c r="BK5" s="40" cm="1">
         <f t="array" aca="1" ref="BK5" ca="1">COUNTIFS($F$10:$F$116,"&lt;="&amp;TODAY()+7,$F$10:$F$116,"&gt;"&amp;0,$G$10:$G$116,"="&amp;"")+COUNTIFS($I$10:$I$116,"&lt;="&amp;TODAY()+7,$I$10:$I$116,"&gt;"&amp;0,$J$10:$J$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY()+7,$P$10:$P$116,"&gt;"&amp;0,$L$10:$L$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY()+7,$P$10:$P$116,"&gt;"&amp;0,$M$10:$M$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY()+7,$AC$10:$AC$116,"&gt;"&amp;0,$S$10:$S$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY()+7,$AC$10:$AC$116,"&gt;"&amp;0,$T$10:$T$116,"="&amp;"")-BK4</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BL5" s="28" cm="1" t="str">
         <f t="array" aca="1" ref="BL5" ca="1">BJ5&amp;": "&amp;BK5&amp;"個"</f>
-        <v>黄色: 8個</v>
+        <v>黄色: 9個</v>
       </c>
     </row>
     <row r="6" spans="1:64" ht="15" customHeight="1">
@@ -24306,7 +24306,7 @@
       <c r="E26" s="71"/>
       <c r="F26" s="70">
         <f t="shared" si="1"/>
-        <v>46679</v>
+        <v>46311</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="65">
@@ -24314,7 +24314,7 @@
       </c>
       <c r="I26" s="68">
         <f t="shared" si="2"/>
-        <v>46686</v>
+        <v>46318</v>
       </c>
       <c r="J26" s="67"/>
       <c r="K26" s="65">
@@ -24326,7 +24326,7 @@
       <c r="O26" s="68"/>
       <c r="P26" s="68">
         <f t="shared" si="3"/>
-        <v>46693</v>
+        <v>46325</v>
       </c>
       <c r="Q26" s="69">
         <v>7</v>
@@ -24346,18 +24346,18 @@
       <c r="AB26" s="67"/>
       <c r="AC26" s="70">
         <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46714</v>
+        <v>46346</v>
       </c>
       <c r="AD26" s="68">
         <f t="shared" si="4"/>
-        <v>46714</v>
+        <v>46349</v>
       </c>
       <c r="AE26" s="67"/>
       <c r="AF26" s="83">
         <v>30</v>
       </c>
       <c r="AG26" s="72">
-        <v>46744</v>
+        <v>46379</v>
       </c>
       <c r="AH26" s="71"/>
       <c r="AI26" s="70"/>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -40047,7 +40047,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="AF11:AF210 H12:H210 K12:K210 Q12:R210">
     <cfRule type="notContainsBlanks" dxfId="34" priority="10" stopIfTrue="1">
-      <formula>NOT(ISBLANK(AF11))</formula>
+      <formula>NOT(ISBLANK(H11))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF11:AF210">

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -21964,7 +21964,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="24.75" customHeight="1">
-      <c r="A1" s="197" t="str" cm="1">
+      <c r="A1" s="197" cm="1" t="str">
         <f t="array" ref="A1">①施工図リスト!A1</f>
         <v>現場／統括：、現場責任者：金子主任、主任：、担当：</v>
       </c>
@@ -22041,7 +22041,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="190"/>
-      <c r="C2" s="204" t="str" cm="1">
+      <c r="C2" s="204" cm="1" t="str">
         <f t="array" ref="C2">①施工図リスト!C2</f>
         <v>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事</v>
       </c>
@@ -22110,7 +22110,7 @@
       </c>
       <c r="BK2" s="31" cm="1">
         <f t="array" ref="BK2">BI3/BH3</f>
-        <v>0.12820512820512819</v>
+        <v>0.128205128205128</v>
       </c>
       <c r="BL2" s="32"/>
     </row>
@@ -22224,7 +22224,7 @@
       </c>
       <c r="BK3" s="32" cm="1">
         <f t="array" ref="BK3">1-BK2</f>
-        <v>0.87179487179487181</v>
+        <v>0.871794871794872</v>
       </c>
       <c r="BL3" s="32"/>
     </row>
@@ -22350,7 +22350,7 @@
         <f t="array" aca="1" ref="BK4" ca="1">COUNTIFS($F$10:$F$116,"&lt;="&amp;TODAY(),$F$10:$F$116,"&gt;"&amp;0,$G$10:$G$116,"="&amp;"")+COUNTIFS($I$10:$I$116,"&lt;="&amp;TODAY(),$I$10:$I$116,"&gt;"&amp;0,$J$10:$J$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY(),$P$10:$P$116,"&gt;"&amp;0,$L$10:$L$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY(),$P$10:$P$116,"&gt;"&amp;0,$M$10:$M$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY(),$AC$10:$AC$116,"&gt;"&amp;0,$S$10:$S$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY(),$AC$10:$AC$116,"&gt;"&amp;0,$T$10:$T$116,"="&amp;"")</f>
         <v>5</v>
       </c>
-      <c r="BL4" s="28" t="str" cm="1">
+      <c r="BL4" s="28" cm="1" t="str">
         <f t="array" aca="1" ref="BL4" ca="1">BJ4&amp;": "&amp;BK4&amp;"個"</f>
         <v>赤色: 5個</v>
       </c>
@@ -22469,11 +22469,11 @@
       </c>
       <c r="BK5" s="40" cm="1">
         <f t="array" aca="1" ref="BK5" ca="1">COUNTIFS($F$10:$F$116,"&lt;="&amp;TODAY()+7,$F$10:$F$116,"&gt;"&amp;0,$G$10:$G$116,"="&amp;"")+COUNTIFS($I$10:$I$116,"&lt;="&amp;TODAY()+7,$I$10:$I$116,"&gt;"&amp;0,$J$10:$J$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY()+7,$P$10:$P$116,"&gt;"&amp;0,$L$10:$L$116,"="&amp;"")+COUNTIFS($P$10:$P$116,"&lt;="&amp;TODAY()+7,$P$10:$P$116,"&gt;"&amp;0,$M$10:$M$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY()+7,$AC$10:$AC$116,"&gt;"&amp;0,$S$10:$S$116,"="&amp;"")+COUNTIFS($AC$10:$AC$116,"&lt;="&amp;TODAY()+7,$AC$10:$AC$116,"&gt;"&amp;0,$T$10:$T$116,"="&amp;"")-BK4</f>
-        <v>9</v>
-      </c>
-      <c r="BL5" s="28" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="BL5" s="28" cm="1" t="str">
         <f t="array" aca="1" ref="BL5" ca="1">BJ5&amp;": "&amp;BK5&amp;"個"</f>
-        <v>黄色: 9個</v>
+        <v>黄色: 4個</v>
       </c>
     </row>
     <row r="6" spans="1:64" ht="15" customHeight="1">
@@ -22844,13 +22844,13 @@
       </c>
       <c r="D11" s="72"/>
       <c r="E11" s="71"/>
-      <c r="F11" s="82" t="str" cm="1">
+      <c r="F11" s="82" cm="1" t="str">
         <f t="array" ref="F11">IF(AG11="","",I11-H11)</f>
         <v/>
       </c>
       <c r="G11" s="67"/>
       <c r="H11" s="65"/>
-      <c r="I11" s="66" t="str" cm="1">
+      <c r="I11" s="66" cm="1" t="str">
         <f t="array" ref="I11">IF(AG11="","",P11-K11)</f>
         <v/>
       </c>
@@ -22860,7 +22860,7 @@
       <c r="M11" s="68"/>
       <c r="N11" s="68"/>
       <c r="O11" s="68"/>
-      <c r="P11" s="66" t="str" cm="1">
+      <c r="P11" s="66" cm="1" t="str">
         <f t="array" ref="P11">IF(AG11="","",AC11-R11-Q11)</f>
         <v/>
       </c>
@@ -22880,7 +22880,7 @@
         <f>IF(AG11="","",WORKDAY(AG11-AF11+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD11" s="66" t="str" cm="1">
+      <c r="AD11" s="66" cm="1" t="str">
         <f t="array" ref="AD11">IF(AG11="","",$AG11-$AF11)</f>
         <v/>
       </c>
@@ -22934,7 +22934,7 @@
       <c r="E12" s="71"/>
       <c r="F12" s="70">
         <f t="shared" ref="F12:F26" si="1">IF(AG12="","",I12-H12)</f>
-        <v>46339</v>
+        <v>46357</v>
       </c>
       <c r="G12" s="67"/>
       <c r="H12" s="65">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="I12" s="68">
         <f t="shared" ref="I12:I26" si="2">IF(AG12="","",P12-K12)</f>
-        <v>46346</v>
+        <v>46364</v>
       </c>
       <c r="J12" s="67"/>
       <c r="K12" s="65">
@@ -22956,7 +22956,7 @@
       <c r="O12" s="68"/>
       <c r="P12" s="68">
         <f t="shared" ref="P12:P26" si="3">IF(AG12="","",AC12-R12-Q12)</f>
-        <v>46353</v>
+        <v>46371</v>
       </c>
       <c r="Q12" s="69">
         <v>7</v>
@@ -22976,15 +22976,15 @@
       <c r="AB12" s="67"/>
       <c r="AC12" s="70">
         <f>IF(AG12="","",WORKDAY(AG12-AF12+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46374</v>
+        <v>46392</v>
       </c>
       <c r="AD12" s="68">
         <f t="shared" ref="AD12:AD26" si="4">IF(AG12="","",$AG12-$AF12)</f>
-        <v>46376</v>
+        <v>46392</v>
       </c>
       <c r="AE12" s="67"/>
       <c r="AF12" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG12" s="72">
         <v>46406</v>
@@ -23342,7 +23342,7 @@
       <c r="E16" s="71"/>
       <c r="F16" s="70">
         <f t="shared" si="1"/>
-        <v>46309</v>
+        <v>46325</v>
       </c>
       <c r="G16" s="67"/>
       <c r="H16" s="65">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="I16" s="68">
         <f t="shared" si="2"/>
-        <v>46316</v>
+        <v>46332</v>
       </c>
       <c r="J16" s="67"/>
       <c r="K16" s="65">
@@ -23362,7 +23362,7 @@
       <c r="O16" s="68"/>
       <c r="P16" s="68">
         <f t="shared" si="3"/>
-        <v>46323</v>
+        <v>46339</v>
       </c>
       <c r="Q16" s="69">
         <v>7</v>
@@ -23382,15 +23382,15 @@
       <c r="AB16" s="67"/>
       <c r="AC16" s="70">
         <f>IF(AG16="","",WORKDAY(AG16-AF16+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46344</v>
+        <v>46360</v>
       </c>
       <c r="AD16" s="68">
         <f t="shared" si="4"/>
-        <v>46344</v>
+        <v>46360</v>
       </c>
       <c r="AE16" s="67"/>
       <c r="AF16" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG16" s="72">
         <v>46374</v>
@@ -23544,7 +23544,7 @@
       <c r="E18" s="71"/>
       <c r="F18" s="70">
         <f t="shared" si="1"/>
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="G18" s="67"/>
       <c r="H18" s="65">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="I18" s="68">
         <f t="shared" si="2"/>
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="J18" s="67"/>
       <c r="K18" s="65">
@@ -23564,7 +23564,7 @@
       <c r="O18" s="68"/>
       <c r="P18" s="68">
         <f t="shared" si="3"/>
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="Q18" s="69">
         <v>7</v>
@@ -23584,15 +23584,15 @@
       <c r="AB18" s="67"/>
       <c r="AC18" s="70">
         <f>IF(AG18="","",WORKDAY(AG18-AF18+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46374</v>
+        <v>46381</v>
       </c>
       <c r="AD18" s="68">
         <f t="shared" si="4"/>
-        <v>46375</v>
+        <v>46391</v>
       </c>
       <c r="AE18" s="67"/>
       <c r="AF18" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG18" s="72">
         <v>46405</v>
@@ -23644,7 +23644,7 @@
       <c r="E19" s="71"/>
       <c r="F19" s="70">
         <f t="shared" si="1"/>
-        <v>46325</v>
+        <v>46343</v>
       </c>
       <c r="G19" s="67"/>
       <c r="H19" s="65">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="I19" s="68">
         <f t="shared" si="2"/>
-        <v>46332</v>
+        <v>46350</v>
       </c>
       <c r="J19" s="67"/>
       <c r="K19" s="65">
@@ -23664,7 +23664,7 @@
       <c r="O19" s="68"/>
       <c r="P19" s="68">
         <f t="shared" si="3"/>
-        <v>46339</v>
+        <v>46357</v>
       </c>
       <c r="Q19" s="69">
         <v>7</v>
@@ -23684,15 +23684,15 @@
       <c r="AB19" s="67"/>
       <c r="AC19" s="70">
         <f>IF(AG19="","",WORKDAY(AG19-AF19+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46360</v>
+        <v>46378</v>
       </c>
       <c r="AD19" s="68">
         <f t="shared" si="4"/>
-        <v>46362</v>
+        <v>46378</v>
       </c>
       <c r="AE19" s="67"/>
       <c r="AF19" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG19" s="72">
         <v>46392</v>
@@ -23744,7 +23744,7 @@
       <c r="E20" s="71"/>
       <c r="F20" s="70">
         <f t="shared" si="1"/>
-        <v>46346</v>
+        <v>46367</v>
       </c>
       <c r="G20" s="67"/>
       <c r="H20" s="65">
@@ -23752,7 +23752,7 @@
       </c>
       <c r="I20" s="68">
         <f t="shared" si="2"/>
-        <v>46353</v>
+        <v>46374</v>
       </c>
       <c r="J20" s="67"/>
       <c r="K20" s="65">
@@ -23764,7 +23764,7 @@
       <c r="O20" s="68"/>
       <c r="P20" s="68">
         <f t="shared" si="3"/>
-        <v>46360</v>
+        <v>46381</v>
       </c>
       <c r="Q20" s="69">
         <v>7</v>
@@ -23784,15 +23784,15 @@
       <c r="AB20" s="67"/>
       <c r="AC20" s="70">
         <f>IF(AG20="","",WORKDAY(AG20-AF20+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46381</v>
+        <v>46402</v>
       </c>
       <c r="AD20" s="68">
         <f t="shared" si="4"/>
-        <v>46386</v>
+        <v>46402</v>
       </c>
       <c r="AE20" s="67"/>
       <c r="AF20" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG20" s="72">
         <v>46416</v>
@@ -23948,7 +23948,7 @@
       <c r="E22" s="71"/>
       <c r="F22" s="70">
         <f t="shared" si="1"/>
-        <v>46311</v>
+        <v>46328</v>
       </c>
       <c r="G22" s="67"/>
       <c r="H22" s="65">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="I22" s="68">
         <f t="shared" si="2"/>
-        <v>46318</v>
+        <v>46335</v>
       </c>
       <c r="J22" s="67"/>
       <c r="K22" s="65">
@@ -23968,7 +23968,7 @@
       <c r="O22" s="68"/>
       <c r="P22" s="68">
         <f t="shared" si="3"/>
-        <v>46325</v>
+        <v>46342</v>
       </c>
       <c r="Q22" s="69">
         <v>7</v>
@@ -23988,15 +23988,15 @@
       <c r="AB22" s="67"/>
       <c r="AC22" s="70">
         <f>IF(AG22="","",WORKDAY(AG22-AF22+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46346</v>
+        <v>46363</v>
       </c>
       <c r="AD22" s="68">
         <f t="shared" si="4"/>
-        <v>46347</v>
+        <v>46363</v>
       </c>
       <c r="AE22" s="67"/>
       <c r="AF22" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG22" s="72">
         <v>46377</v>
@@ -24050,7 +24050,7 @@
       <c r="E23" s="71"/>
       <c r="F23" s="70">
         <f t="shared" si="1"/>
-        <v>46337</v>
+        <v>46346</v>
       </c>
       <c r="G23" s="67"/>
       <c r="H23" s="65">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="I23" s="68">
         <f t="shared" si="2"/>
-        <v>46344</v>
+        <v>46353</v>
       </c>
       <c r="J23" s="67"/>
       <c r="K23" s="65">
@@ -24070,7 +24070,7 @@
       <c r="O23" s="68"/>
       <c r="P23" s="68">
         <f t="shared" si="3"/>
-        <v>46351</v>
+        <v>46360</v>
       </c>
       <c r="Q23" s="69">
         <v>7</v>
@@ -24090,15 +24090,15 @@
       <c r="AB23" s="67"/>
       <c r="AC23" s="70">
         <f>IF(AG23="","",WORKDAY(AG23-AF23+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46372</v>
+        <v>46381</v>
       </c>
       <c r="AD23" s="68">
         <f t="shared" si="4"/>
-        <v>46372</v>
+        <v>46388</v>
       </c>
       <c r="AE23" s="67"/>
       <c r="AF23" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG23" s="72">
         <v>46402</v>
@@ -24150,7 +24150,7 @@
       <c r="E24" s="71"/>
       <c r="F24" s="70">
         <f t="shared" si="1"/>
-        <v>46346</v>
+        <v>46367</v>
       </c>
       <c r="G24" s="67"/>
       <c r="H24" s="65">
@@ -24158,7 +24158,7 @@
       </c>
       <c r="I24" s="68">
         <f t="shared" si="2"/>
-        <v>46353</v>
+        <v>46374</v>
       </c>
       <c r="J24" s="67"/>
       <c r="K24" s="65">
@@ -24170,7 +24170,7 @@
       <c r="O24" s="68"/>
       <c r="P24" s="68">
         <f t="shared" si="3"/>
-        <v>46360</v>
+        <v>46381</v>
       </c>
       <c r="Q24" s="69">
         <v>7</v>
@@ -24190,15 +24190,15 @@
       <c r="AB24" s="67"/>
       <c r="AC24" s="70">
         <f>IF(AG24="","",WORKDAY(AG24-AF24+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46381</v>
+        <v>46402</v>
       </c>
       <c r="AD24" s="68">
         <f t="shared" si="4"/>
-        <v>46386</v>
+        <v>46402</v>
       </c>
       <c r="AE24" s="67"/>
       <c r="AF24" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG24" s="72">
         <v>46416</v>
@@ -24250,7 +24250,7 @@
       <c r="E25" s="71"/>
       <c r="F25" s="70">
         <f t="shared" si="1"/>
-        <v>46307</v>
+        <v>46323</v>
       </c>
       <c r="G25" s="67"/>
       <c r="H25" s="65">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="I25" s="68">
         <f t="shared" si="2"/>
-        <v>46314</v>
+        <v>46330</v>
       </c>
       <c r="J25" s="67"/>
       <c r="K25" s="65">
@@ -24270,7 +24270,7 @@
       <c r="O25" s="68"/>
       <c r="P25" s="68">
         <f t="shared" si="3"/>
-        <v>46321</v>
+        <v>46337</v>
       </c>
       <c r="Q25" s="69">
         <v>7</v>
@@ -24290,15 +24290,15 @@
       <c r="AB25" s="67"/>
       <c r="AC25" s="70">
         <f>IF(AG25="","",WORKDAY(AG25-AF25+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46342</v>
+        <v>46358</v>
       </c>
       <c r="AD25" s="68">
         <f t="shared" si="4"/>
-        <v>46342</v>
+        <v>46358</v>
       </c>
       <c r="AE25" s="67"/>
       <c r="AF25" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG25" s="72">
         <v>46372</v>
@@ -24352,7 +24352,7 @@
       <c r="E26" s="71"/>
       <c r="F26" s="70">
         <f t="shared" si="1"/>
-        <v>46311</v>
+        <v>46330</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="65">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="I26" s="68">
         <f t="shared" si="2"/>
-        <v>46318</v>
+        <v>46337</v>
       </c>
       <c r="J26" s="67"/>
       <c r="K26" s="65">
@@ -24372,7 +24372,7 @@
       <c r="O26" s="68"/>
       <c r="P26" s="68">
         <f t="shared" si="3"/>
-        <v>46325</v>
+        <v>46344</v>
       </c>
       <c r="Q26" s="69">
         <v>7</v>
@@ -24392,15 +24392,15 @@
       <c r="AB26" s="67"/>
       <c r="AC26" s="70">
         <f>IF(AG26="","",WORKDAY(AG26-AF26+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46346</v>
+        <v>46365</v>
       </c>
       <c r="AD26" s="68">
         <f t="shared" si="4"/>
-        <v>46349</v>
+        <v>46365</v>
       </c>
       <c r="AE26" s="67"/>
       <c r="AF26" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG26" s="72">
         <v>46379</v>
@@ -24454,7 +24454,7 @@
       <c r="E27" s="71"/>
       <c r="F27" s="70">
         <f>IF(AG27="","",I27-H27)</f>
-        <v>46311</v>
+        <v>46328</v>
       </c>
       <c r="G27" s="67"/>
       <c r="H27" s="65">
@@ -24462,7 +24462,7 @@
       </c>
       <c r="I27" s="68">
         <f>IF(AG27="","",P27-K27)</f>
-        <v>46318</v>
+        <v>46335</v>
       </c>
       <c r="J27" s="67"/>
       <c r="K27" s="65">
@@ -24474,7 +24474,7 @@
       <c r="O27" s="68"/>
       <c r="P27" s="68">
         <f>IF(AG27="","",AC27-R27-Q27)</f>
-        <v>46325</v>
+        <v>46342</v>
       </c>
       <c r="Q27" s="69">
         <v>7</v>
@@ -24494,15 +24494,15 @@
       <c r="AB27" s="67"/>
       <c r="AC27" s="70">
         <f>IF(AG27="","",WORKDAY(AG27-AF27+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
-        <v>46346</v>
+        <v>46363</v>
       </c>
       <c r="AD27" s="68">
         <f>IF(AG27="","",$AG27-$AF27)</f>
-        <v>46347</v>
+        <v>46363</v>
       </c>
       <c r="AE27" s="67"/>
       <c r="AF27" s="83">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG27" s="72">
         <v>46377</v>
@@ -24548,13 +24548,13 @@
       <c r="C28" s="19"/>
       <c r="D28" s="72"/>
       <c r="E28" s="71"/>
-      <c r="F28" s="82" t="str" cm="1">
+      <c r="F28" s="82" cm="1" t="str">
         <f t="array" ref="F28">IF(AG28="","",I28-H28)</f>
         <v/>
       </c>
       <c r="G28" s="67"/>
       <c r="H28" s="65"/>
-      <c r="I28" s="66" t="str" cm="1">
+      <c r="I28" s="66" cm="1" t="str">
         <f t="array" ref="I28">IF(AG28="","",P28-K28)</f>
         <v/>
       </c>
@@ -24564,7 +24564,7 @@
       <c r="M28" s="68"/>
       <c r="N28" s="68"/>
       <c r="O28" s="68"/>
-      <c r="P28" s="66" t="str" cm="1">
+      <c r="P28" s="66" cm="1" t="str">
         <f t="array" ref="P28">IF(AG28="","",AC28-R28-Q28)</f>
         <v/>
       </c>
@@ -24584,7 +24584,7 @@
         <f>IF(AG28="","",WORKDAY(AG28-AF28+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD28" s="66" t="str" cm="1">
+      <c r="AD28" s="66" cm="1" t="str">
         <f t="array" ref="AD28">IF(AG28="","",$AG28-$AF28)</f>
         <v/>
       </c>
@@ -24634,13 +24634,13 @@
       </c>
       <c r="D29" s="72"/>
       <c r="E29" s="71"/>
-      <c r="F29" s="82" t="str" cm="1">
+      <c r="F29" s="82" cm="1" t="str">
         <f t="array" ref="F29">IF(AG29="","",I29-H29)</f>
         <v/>
       </c>
       <c r="G29" s="67"/>
       <c r="H29" s="65"/>
-      <c r="I29" s="66" t="str" cm="1">
+      <c r="I29" s="66" cm="1" t="str">
         <f t="array" ref="I29">IF(AG29="","",P29-K29)</f>
         <v/>
       </c>
@@ -24650,7 +24650,7 @@
       <c r="M29" s="68"/>
       <c r="N29" s="68"/>
       <c r="O29" s="68"/>
-      <c r="P29" s="66" t="str" cm="1">
+      <c r="P29" s="66" cm="1" t="str">
         <f t="array" ref="P29">IF(AG29="","",AC29-R29-Q29)</f>
         <v/>
       </c>
@@ -24670,7 +24670,7 @@
         <f>IF(AG29="","",WORKDAY(AG29-AF29+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD29" s="66" t="str" cm="1">
+      <c r="AD29" s="66" cm="1" t="str">
         <f t="array" ref="AD29">IF(AG29="","",$AG29-$AF29)</f>
         <v/>
       </c>
@@ -24830,13 +24830,13 @@
       </c>
       <c r="D31" s="72"/>
       <c r="E31" s="71"/>
-      <c r="F31" s="82" t="str" cm="1">
+      <c r="F31" s="82" cm="1" t="str">
         <f t="array" ref="F31">IF(AG31="","",I31-H31)</f>
         <v/>
       </c>
       <c r="G31" s="67"/>
       <c r="H31" s="65"/>
-      <c r="I31" s="66" t="str" cm="1">
+      <c r="I31" s="66" cm="1" t="str">
         <f t="array" ref="I31">IF(AG31="","",P31-K31)</f>
         <v/>
       </c>
@@ -24846,7 +24846,7 @@
       <c r="M31" s="68"/>
       <c r="N31" s="68"/>
       <c r="O31" s="68"/>
-      <c r="P31" s="66" t="str" cm="1">
+      <c r="P31" s="66" cm="1" t="str">
         <f t="array" ref="P31">IF(AG31="","",AC31-R31-Q31)</f>
         <v/>
       </c>
@@ -24866,7 +24866,7 @@
         <f>IF(AG31="","",WORKDAY(AG31-AF31+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD31" s="66" t="str" cm="1">
+      <c r="AD31" s="66" cm="1" t="str">
         <f t="array" ref="AD31">IF(AG31="","",$AG31-$AF31)</f>
         <v/>
       </c>
@@ -25030,13 +25030,13 @@
       </c>
       <c r="D33" s="72"/>
       <c r="E33" s="71"/>
-      <c r="F33" s="82" t="str" cm="1">
+      <c r="F33" s="82" cm="1" t="str">
         <f t="array" ref="F33">IF(AG33="","",I33-H33)</f>
         <v/>
       </c>
       <c r="G33" s="67"/>
       <c r="H33" s="65"/>
-      <c r="I33" s="66" t="str" cm="1">
+      <c r="I33" s="66" cm="1" t="str">
         <f t="array" ref="I33">IF(AG33="","",P33-K33)</f>
         <v/>
       </c>
@@ -25046,7 +25046,7 @@
       <c r="M33" s="68"/>
       <c r="N33" s="68"/>
       <c r="O33" s="68"/>
-      <c r="P33" s="66" t="str" cm="1">
+      <c r="P33" s="66" cm="1" t="str">
         <f t="array" ref="P33">IF(AG33="","",AC33-R33-Q33)</f>
         <v/>
       </c>
@@ -25066,7 +25066,7 @@
         <f>IF(AG33="","",WORKDAY(AG33-AF33+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD33" s="66" t="str" cm="1">
+      <c r="AD33" s="66" cm="1" t="str">
         <f t="array" ref="AD33">IF(AG33="","",$AG33-$AF33)</f>
         <v/>
       </c>
@@ -25116,13 +25116,13 @@
       <c r="C34" s="19"/>
       <c r="D34" s="72"/>
       <c r="E34" s="71"/>
-      <c r="F34" s="82" t="str" cm="1">
+      <c r="F34" s="82" cm="1" t="str">
         <f t="array" ref="F34">IF(AG34="","",I34-H34)</f>
         <v/>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="65"/>
-      <c r="I34" s="66" t="str" cm="1">
+      <c r="I34" s="66" cm="1" t="str">
         <f t="array" ref="I34">IF(AG34="","",P34-K34)</f>
         <v/>
       </c>
@@ -25132,7 +25132,7 @@
       <c r="M34" s="68"/>
       <c r="N34" s="68"/>
       <c r="O34" s="68"/>
-      <c r="P34" s="66" t="str" cm="1">
+      <c r="P34" s="66" cm="1" t="str">
         <f t="array" ref="P34">IF(AG34="","",AC34-R34-Q34)</f>
         <v/>
       </c>
@@ -25152,7 +25152,7 @@
         <f>IF(AG34="","",WORKDAY(AG34-AF34+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD34" s="66" t="str" cm="1">
+      <c r="AD34" s="66" cm="1" t="str">
         <f t="array" ref="AD34">IF(AG34="","",$AG34-$AF34)</f>
         <v/>
       </c>
@@ -25202,13 +25202,13 @@
       </c>
       <c r="D35" s="72"/>
       <c r="E35" s="71"/>
-      <c r="F35" s="82" t="str" cm="1">
+      <c r="F35" s="82" cm="1" t="str">
         <f t="array" ref="F35">IF(AG35="","",I35-H35)</f>
         <v/>
       </c>
       <c r="G35" s="67"/>
       <c r="H35" s="65"/>
-      <c r="I35" s="66" t="str" cm="1">
+      <c r="I35" s="66" cm="1" t="str">
         <f t="array" ref="I35">IF(AG35="","",P35-K35)</f>
         <v/>
       </c>
@@ -25218,7 +25218,7 @@
       <c r="M35" s="68"/>
       <c r="N35" s="68"/>
       <c r="O35" s="68"/>
-      <c r="P35" s="66" t="str" cm="1">
+      <c r="P35" s="66" cm="1" t="str">
         <f t="array" ref="P35">IF(AG35="","",AC35-R35-Q35)</f>
         <v/>
       </c>
@@ -25238,7 +25238,7 @@
         <f>IF(AG35="","",WORKDAY(AG35-AF35+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD35" s="66" t="str" cm="1">
+      <c r="AD35" s="66" cm="1" t="str">
         <f t="array" ref="AD35">IF(AG35="","",$AG35-$AF35)</f>
         <v/>
       </c>
@@ -25396,13 +25396,13 @@
       <c r="C37" s="19"/>
       <c r="D37" s="72"/>
       <c r="E37" s="71"/>
-      <c r="F37" s="82" t="str" cm="1">
+      <c r="F37" s="82" cm="1" t="str">
         <f t="array" ref="F37">IF(AG37="","",I37-H37)</f>
         <v/>
       </c>
       <c r="G37" s="67"/>
       <c r="H37" s="65"/>
-      <c r="I37" s="66" t="str" cm="1">
+      <c r="I37" s="66" cm="1" t="str">
         <f t="array" ref="I37">IF(AG37="","",P37-K37)</f>
         <v/>
       </c>
@@ -25412,7 +25412,7 @@
       <c r="M37" s="68"/>
       <c r="N37" s="68"/>
       <c r="O37" s="68"/>
-      <c r="P37" s="66" t="str" cm="1">
+      <c r="P37" s="66" cm="1" t="str">
         <f t="array" ref="P37">IF(AG37="","",AC37-R37-Q37)</f>
         <v/>
       </c>
@@ -25432,7 +25432,7 @@
         <f>IF(AG37="","",WORKDAY(AG37-AF37+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD37" s="66" t="str" cm="1">
+      <c r="AD37" s="66" cm="1" t="str">
         <f t="array" ref="AD37">IF(AG37="","",$AG37-$AF37)</f>
         <v/>
       </c>
@@ -25482,13 +25482,13 @@
       </c>
       <c r="D38" s="72"/>
       <c r="E38" s="71"/>
-      <c r="F38" s="82" t="str" cm="1">
+      <c r="F38" s="82" cm="1" t="str">
         <f t="array" ref="F38">IF(AG38="","",I38-H38)</f>
         <v/>
       </c>
       <c r="G38" s="67"/>
       <c r="H38" s="65"/>
-      <c r="I38" s="66" t="str" cm="1">
+      <c r="I38" s="66" cm="1" t="str">
         <f t="array" ref="I38">IF(AG38="","",P38-K38)</f>
         <v/>
       </c>
@@ -25498,7 +25498,7 @@
       <c r="M38" s="68"/>
       <c r="N38" s="68"/>
       <c r="O38" s="68"/>
-      <c r="P38" s="66" t="str" cm="1">
+      <c r="P38" s="66" cm="1" t="str">
         <f t="array" ref="P38">IF(AG38="","",AC38-R38-Q38)</f>
         <v/>
       </c>
@@ -25518,7 +25518,7 @@
         <f>IF(AG38="","",WORKDAY(AG38-AF38+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD38" s="66" t="str" cm="1">
+      <c r="AD38" s="66" cm="1" t="str">
         <f t="array" ref="AD38">IF(AG38="","",$AG38-$AF38)</f>
         <v/>
       </c>
@@ -25980,13 +25980,13 @@
       <c r="C43" s="19"/>
       <c r="D43" s="72"/>
       <c r="E43" s="71"/>
-      <c r="F43" s="82" t="str" cm="1">
+      <c r="F43" s="82" cm="1" t="str">
         <f t="array" ref="F43">IF(AG43="","",I43-H43)</f>
         <v/>
       </c>
       <c r="G43" s="67"/>
       <c r="H43" s="65"/>
-      <c r="I43" s="66" t="str" cm="1">
+      <c r="I43" s="66" cm="1" t="str">
         <f t="array" ref="I43">IF(AG43="","",P43-K43)</f>
         <v/>
       </c>
@@ -25996,7 +25996,7 @@
       <c r="M43" s="68"/>
       <c r="N43" s="68"/>
       <c r="O43" s="68"/>
-      <c r="P43" s="66" t="str" cm="1">
+      <c r="P43" s="66" cm="1" t="str">
         <f t="array" ref="P43">IF(AG43="","",AC43-R43-Q43)</f>
         <v/>
       </c>
@@ -26016,7 +26016,7 @@
         <f>IF(AG43="","",WORKDAY(AG43-AF43+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD43" s="66" t="str" cm="1">
+      <c r="AD43" s="66" cm="1" t="str">
         <f t="array" ref="AD43">IF(AG43="","",$AG43-$AF43)</f>
         <v/>
       </c>
@@ -26066,13 +26066,13 @@
       </c>
       <c r="D44" s="72"/>
       <c r="E44" s="71"/>
-      <c r="F44" s="82" t="str" cm="1">
+      <c r="F44" s="82" cm="1" t="str">
         <f t="array" ref="F44">IF(AG44="","",I44-H44)</f>
         <v/>
       </c>
       <c r="G44" s="67"/>
       <c r="H44" s="65"/>
-      <c r="I44" s="66" t="str" cm="1">
+      <c r="I44" s="66" cm="1" t="str">
         <f t="array" ref="I44">IF(AG44="","",P44-K44)</f>
         <v/>
       </c>
@@ -26082,7 +26082,7 @@
       <c r="M44" s="68"/>
       <c r="N44" s="68"/>
       <c r="O44" s="68"/>
-      <c r="P44" s="66" t="str" cm="1">
+      <c r="P44" s="66" cm="1" t="str">
         <f t="array" ref="P44">IF(AG44="","",AC44-R44-Q44)</f>
         <v/>
       </c>
@@ -26102,7 +26102,7 @@
         <f>IF(AG44="","",WORKDAY(AG44-AF44+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD44" s="66" t="str" cm="1">
+      <c r="AD44" s="66" cm="1" t="str">
         <f t="array" ref="AD44">IF(AG44="","",$AG44-$AF44)</f>
         <v/>
       </c>
@@ -26256,13 +26256,13 @@
       <c r="C46" s="19"/>
       <c r="D46" s="72"/>
       <c r="E46" s="71"/>
-      <c r="F46" s="82" t="str" cm="1">
+      <c r="F46" s="82" cm="1" t="str">
         <f t="array" ref="F46">IF(AG46="","",I46-H46)</f>
         <v/>
       </c>
       <c r="G46" s="67"/>
       <c r="H46" s="65"/>
-      <c r="I46" s="66" t="str" cm="1">
+      <c r="I46" s="66" cm="1" t="str">
         <f t="array" ref="I46">IF(AG46="","",P46-K46)</f>
         <v/>
       </c>
@@ -26272,7 +26272,7 @@
       <c r="M46" s="68"/>
       <c r="N46" s="68"/>
       <c r="O46" s="68"/>
-      <c r="P46" s="66" t="str" cm="1">
+      <c r="P46" s="66" cm="1" t="str">
         <f t="array" ref="P46">IF(AG46="","",AC46-R46-Q46)</f>
         <v/>
       </c>
@@ -26292,7 +26292,7 @@
         <f>IF(AG46="","",WORKDAY(AG46-AF46+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD46" s="66" t="str" cm="1">
+      <c r="AD46" s="66" cm="1" t="str">
         <f t="array" ref="AD46">IF(AG46="","",$AG46-$AF46)</f>
         <v/>
       </c>
@@ -26342,13 +26342,13 @@
       </c>
       <c r="D47" s="72"/>
       <c r="E47" s="71"/>
-      <c r="F47" s="82" t="str" cm="1">
+      <c r="F47" s="82" cm="1" t="str">
         <f t="array" ref="F47">IF(AG47="","",I47-H47)</f>
         <v/>
       </c>
       <c r="G47" s="67"/>
       <c r="H47" s="65"/>
-      <c r="I47" s="66" t="str" cm="1">
+      <c r="I47" s="66" cm="1" t="str">
         <f t="array" ref="I47">IF(AG47="","",P47-K47)</f>
         <v/>
       </c>
@@ -26358,7 +26358,7 @@
       <c r="M47" s="68"/>
       <c r="N47" s="68"/>
       <c r="O47" s="68"/>
-      <c r="P47" s="66" t="str" cm="1">
+      <c r="P47" s="66" cm="1" t="str">
         <f t="array" ref="P47">IF(AG47="","",AC47-R47-Q47)</f>
         <v/>
       </c>
@@ -26378,7 +26378,7 @@
         <f>IF(AG47="","",WORKDAY(AG47-AF47+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD47" s="66" t="str" cm="1">
+      <c r="AD47" s="66" cm="1" t="str">
         <f t="array" ref="AD47">IF(AG47="","",$AG47-$AF47)</f>
         <v/>
       </c>
@@ -26534,13 +26534,13 @@
       <c r="C49" s="19"/>
       <c r="D49" s="72"/>
       <c r="E49" s="71"/>
-      <c r="F49" s="82" t="str" cm="1">
+      <c r="F49" s="82" cm="1" t="str">
         <f t="array" ref="F49">IF(AG49="","",I49-H49)</f>
         <v/>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="65"/>
-      <c r="I49" s="66" t="str" cm="1">
+      <c r="I49" s="66" cm="1" t="str">
         <f t="array" ref="I49">IF(AG49="","",P49-K49)</f>
         <v/>
       </c>
@@ -26550,7 +26550,7 @@
       <c r="M49" s="68"/>
       <c r="N49" s="68"/>
       <c r="O49" s="68"/>
-      <c r="P49" s="66" t="str" cm="1">
+      <c r="P49" s="66" cm="1" t="str">
         <f t="array" ref="P49">IF(AG49="","",AC49-R49-Q49)</f>
         <v/>
       </c>
@@ -26570,7 +26570,7 @@
         <f>IF(AG49="","",WORKDAY(AG49-AF49+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD49" s="66" t="str" cm="1">
+      <c r="AD49" s="66" cm="1" t="str">
         <f t="array" ref="AD49">IF(AG49="","",$AG49-$AF49)</f>
         <v/>
       </c>
@@ -26620,13 +26620,13 @@
       </c>
       <c r="D50" s="72"/>
       <c r="E50" s="71"/>
-      <c r="F50" s="82" t="str" cm="1">
+      <c r="F50" s="82" cm="1" t="str">
         <f t="array" ref="F50">IF(AG50="","",I50-H50)</f>
         <v/>
       </c>
       <c r="G50" s="67"/>
       <c r="H50" s="65"/>
-      <c r="I50" s="66" t="str" cm="1">
+      <c r="I50" s="66" cm="1" t="str">
         <f t="array" ref="I50">IF(AG50="","",P50-K50)</f>
         <v/>
       </c>
@@ -26636,7 +26636,7 @@
       <c r="M50" s="68"/>
       <c r="N50" s="68"/>
       <c r="O50" s="68"/>
-      <c r="P50" s="66" t="str" cm="1">
+      <c r="P50" s="66" cm="1" t="str">
         <f t="array" ref="P50">IF(AG50="","",AC50-R50-Q50)</f>
         <v/>
       </c>
@@ -26656,7 +26656,7 @@
         <f>IF(AG50="","",WORKDAY(AG50-AF50+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD50" s="66" t="str" cm="1">
+      <c r="AD50" s="66" cm="1" t="str">
         <f t="array" ref="AD50">IF(AG50="","",$AG50-$AF50)</f>
         <v/>
       </c>
@@ -26806,13 +26806,13 @@
       <c r="C52" s="19"/>
       <c r="D52" s="72"/>
       <c r="E52" s="71"/>
-      <c r="F52" s="82" t="str" cm="1">
+      <c r="F52" s="82" cm="1" t="str">
         <f t="array" ref="F52">IF(AG52="","",I52-H52)</f>
         <v/>
       </c>
       <c r="G52" s="67"/>
       <c r="H52" s="65"/>
-      <c r="I52" s="66" t="str" cm="1">
+      <c r="I52" s="66" cm="1" t="str">
         <f t="array" ref="I52">IF(AG52="","",P52-K52)</f>
         <v/>
       </c>
@@ -26822,7 +26822,7 @@
       <c r="M52" s="68"/>
       <c r="N52" s="68"/>
       <c r="O52" s="68"/>
-      <c r="P52" s="66" t="str" cm="1">
+      <c r="P52" s="66" cm="1" t="str">
         <f t="array" ref="P52">IF(AG52="","",AC52-R52-Q52)</f>
         <v/>
       </c>
@@ -26842,7 +26842,7 @@
         <f>IF(AG52="","",WORKDAY(AG52-AF52+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD52" s="66" t="str" cm="1">
+      <c r="AD52" s="66" cm="1" t="str">
         <f t="array" ref="AD52">IF(AG52="","",$AG52-$AF52)</f>
         <v/>
       </c>
@@ -26890,13 +26890,13 @@
       <c r="C53" s="19"/>
       <c r="D53" s="72"/>
       <c r="E53" s="71"/>
-      <c r="F53" s="82" t="str" cm="1">
+      <c r="F53" s="82" cm="1" t="str">
         <f t="array" ref="F53">IF(AG53="","",I53-H53)</f>
         <v/>
       </c>
       <c r="G53" s="67"/>
       <c r="H53" s="65"/>
-      <c r="I53" s="66" t="str" cm="1">
+      <c r="I53" s="66" cm="1" t="str">
         <f t="array" ref="I53">IF(AG53="","",P53-K53)</f>
         <v/>
       </c>
@@ -26906,7 +26906,7 @@
       <c r="M53" s="68"/>
       <c r="N53" s="68"/>
       <c r="O53" s="68"/>
-      <c r="P53" s="66" t="str" cm="1">
+      <c r="P53" s="66" cm="1" t="str">
         <f t="array" ref="P53">IF(AG53="","",AC53-R53-Q53)</f>
         <v/>
       </c>
@@ -26926,7 +26926,7 @@
         <f>IF(AG53="","",WORKDAY(AG53-AF53+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD53" s="66" t="str" cm="1">
+      <c r="AD53" s="66" cm="1" t="str">
         <f t="array" ref="AD53">IF(AG53="","",$AG53-$AF53)</f>
         <v/>
       </c>
@@ -26974,13 +26974,13 @@
       <c r="C54" s="19"/>
       <c r="D54" s="72"/>
       <c r="E54" s="71"/>
-      <c r="F54" s="82" t="str" cm="1">
+      <c r="F54" s="82" cm="1" t="str">
         <f t="array" ref="F54">IF(AG54="","",I54-H54)</f>
         <v/>
       </c>
       <c r="G54" s="67"/>
       <c r="H54" s="65"/>
-      <c r="I54" s="66" t="str" cm="1">
+      <c r="I54" s="66" cm="1" t="str">
         <f t="array" ref="I54">IF(AG54="","",P54-K54)</f>
         <v/>
       </c>
@@ -26990,7 +26990,7 @@
       <c r="M54" s="68"/>
       <c r="N54" s="68"/>
       <c r="O54" s="68"/>
-      <c r="P54" s="66" t="str" cm="1">
+      <c r="P54" s="66" cm="1" t="str">
         <f t="array" ref="P54">IF(AG54="","",AC54-R54-Q54)</f>
         <v/>
       </c>
@@ -27010,7 +27010,7 @@
         <f>IF(AG54="","",WORKDAY(AG54-AF54+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD54" s="66" t="str" cm="1">
+      <c r="AD54" s="66" cm="1" t="str">
         <f t="array" ref="AD54">IF(AG54="","",$AG54-$AF54)</f>
         <v/>
       </c>
@@ -27058,13 +27058,13 @@
       <c r="C55" s="19"/>
       <c r="D55" s="72"/>
       <c r="E55" s="71"/>
-      <c r="F55" s="82" t="str" cm="1">
+      <c r="F55" s="82" cm="1" t="str">
         <f t="array" ref="F55">IF(AG55="","",I55-H55)</f>
         <v/>
       </c>
       <c r="G55" s="67"/>
       <c r="H55" s="65"/>
-      <c r="I55" s="66" t="str" cm="1">
+      <c r="I55" s="66" cm="1" t="str">
         <f t="array" ref="I55">IF(AG55="","",P55-K55)</f>
         <v/>
       </c>
@@ -27074,7 +27074,7 @@
       <c r="M55" s="68"/>
       <c r="N55" s="68"/>
       <c r="O55" s="68"/>
-      <c r="P55" s="66" t="str" cm="1">
+      <c r="P55" s="66" cm="1" t="str">
         <f t="array" ref="P55">IF(AG55="","",AC55-R55-Q55)</f>
         <v/>
       </c>
@@ -27094,7 +27094,7 @@
         <f>IF(AG55="","",WORKDAY(AG55-AF55+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD55" s="66" t="str" cm="1">
+      <c r="AD55" s="66" cm="1" t="str">
         <f t="array" ref="AD55">IF(AG55="","",$AG55-$AF55)</f>
         <v/>
       </c>
@@ -27142,13 +27142,13 @@
       <c r="C56" s="19"/>
       <c r="D56" s="72"/>
       <c r="E56" s="71"/>
-      <c r="F56" s="82" t="str" cm="1">
+      <c r="F56" s="82" cm="1" t="str">
         <f t="array" ref="F56">IF(AG56="","",I56-H56)</f>
         <v/>
       </c>
       <c r="G56" s="67"/>
       <c r="H56" s="65"/>
-      <c r="I56" s="66" t="str" cm="1">
+      <c r="I56" s="66" cm="1" t="str">
         <f t="array" ref="I56">IF(AG56="","",P56-K56)</f>
         <v/>
       </c>
@@ -27158,7 +27158,7 @@
       <c r="M56" s="68"/>
       <c r="N56" s="68"/>
       <c r="O56" s="68"/>
-      <c r="P56" s="66" t="str" cm="1">
+      <c r="P56" s="66" cm="1" t="str">
         <f t="array" ref="P56">IF(AG56="","",AC56-R56-Q56)</f>
         <v/>
       </c>
@@ -27178,7 +27178,7 @@
         <f>IF(AG56="","",WORKDAY(AG56-AF56+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD56" s="66" t="str" cm="1">
+      <c r="AD56" s="66" cm="1" t="str">
         <f t="array" ref="AD56">IF(AG56="","",$AG56-$AF56)</f>
         <v/>
       </c>
@@ -27226,13 +27226,13 @@
       <c r="C57" s="19"/>
       <c r="D57" s="72"/>
       <c r="E57" s="71"/>
-      <c r="F57" s="82" t="str" cm="1">
+      <c r="F57" s="82" cm="1" t="str">
         <f t="array" ref="F57">IF(AG57="","",I57-H57)</f>
         <v/>
       </c>
       <c r="G57" s="67"/>
       <c r="H57" s="65"/>
-      <c r="I57" s="66" t="str" cm="1">
+      <c r="I57" s="66" cm="1" t="str">
         <f t="array" ref="I57">IF(AG57="","",P57-K57)</f>
         <v/>
       </c>
@@ -27242,7 +27242,7 @@
       <c r="M57" s="68"/>
       <c r="N57" s="68"/>
       <c r="O57" s="68"/>
-      <c r="P57" s="66" t="str" cm="1">
+      <c r="P57" s="66" cm="1" t="str">
         <f t="array" ref="P57">IF(AG57="","",AC57-R57-Q57)</f>
         <v/>
       </c>
@@ -27262,7 +27262,7 @@
         <f>IF(AG57="","",WORKDAY(AG57-AF57+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD57" s="66" t="str" cm="1">
+      <c r="AD57" s="66" cm="1" t="str">
         <f t="array" ref="AD57">IF(AG57="","",$AG57-$AF57)</f>
         <v/>
       </c>
@@ -27310,13 +27310,13 @@
       <c r="C58" s="19"/>
       <c r="D58" s="72"/>
       <c r="E58" s="71"/>
-      <c r="F58" s="82" t="str" cm="1">
+      <c r="F58" s="82" cm="1" t="str">
         <f t="array" ref="F58">IF(AG58="","",I58-H58)</f>
         <v/>
       </c>
       <c r="G58" s="67"/>
       <c r="H58" s="65"/>
-      <c r="I58" s="66" t="str" cm="1">
+      <c r="I58" s="66" cm="1" t="str">
         <f t="array" ref="I58">IF(AG58="","",P58-K58)</f>
         <v/>
       </c>
@@ -27326,7 +27326,7 @@
       <c r="M58" s="68"/>
       <c r="N58" s="68"/>
       <c r="O58" s="68"/>
-      <c r="P58" s="66" t="str" cm="1">
+      <c r="P58" s="66" cm="1" t="str">
         <f t="array" ref="P58">IF(AG58="","",AC58-R58-Q58)</f>
         <v/>
       </c>
@@ -27346,7 +27346,7 @@
         <f>IF(AG58="","",WORKDAY(AG58-AF58+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD58" s="66" t="str" cm="1">
+      <c r="AD58" s="66" cm="1" t="str">
         <f t="array" ref="AD58">IF(AG58="","",$AG58-$AF58)</f>
         <v/>
       </c>
@@ -27394,13 +27394,13 @@
       <c r="C59" s="19"/>
       <c r="D59" s="72"/>
       <c r="E59" s="71"/>
-      <c r="F59" s="82" t="str" cm="1">
+      <c r="F59" s="82" cm="1" t="str">
         <f t="array" ref="F59">IF(AG59="","",I59-H59)</f>
         <v/>
       </c>
       <c r="G59" s="67"/>
       <c r="H59" s="65"/>
-      <c r="I59" s="66" t="str" cm="1">
+      <c r="I59" s="66" cm="1" t="str">
         <f t="array" ref="I59">IF(AG59="","",P59-K59)</f>
         <v/>
       </c>
@@ -27410,7 +27410,7 @@
       <c r="M59" s="68"/>
       <c r="N59" s="68"/>
       <c r="O59" s="68"/>
-      <c r="P59" s="66" t="str" cm="1">
+      <c r="P59" s="66" cm="1" t="str">
         <f t="array" ref="P59">IF(AG59="","",AC59-R59-Q59)</f>
         <v/>
       </c>
@@ -27430,7 +27430,7 @@
         <f>IF(AG59="","",WORKDAY(AG59-AF59+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD59" s="66" t="str" cm="1">
+      <c r="AD59" s="66" cm="1" t="str">
         <f t="array" ref="AD59">IF(AG59="","",$AG59-$AF59)</f>
         <v/>
       </c>
@@ -27478,13 +27478,13 @@
       <c r="C60" s="19"/>
       <c r="D60" s="72"/>
       <c r="E60" s="71"/>
-      <c r="F60" s="82" t="str" cm="1">
+      <c r="F60" s="82" cm="1" t="str">
         <f t="array" ref="F60">IF(AG60="","",I60-H60)</f>
         <v/>
       </c>
       <c r="G60" s="67"/>
       <c r="H60" s="65"/>
-      <c r="I60" s="66" t="str" cm="1">
+      <c r="I60" s="66" cm="1" t="str">
         <f t="array" ref="I60">IF(AG60="","",P60-K60)</f>
         <v/>
       </c>
@@ -27494,7 +27494,7 @@
       <c r="M60" s="68"/>
       <c r="N60" s="68"/>
       <c r="O60" s="68"/>
-      <c r="P60" s="66" t="str" cm="1">
+      <c r="P60" s="66" cm="1" t="str">
         <f t="array" ref="P60">IF(AG60="","",AC60-R60-Q60)</f>
         <v/>
       </c>
@@ -27514,7 +27514,7 @@
         <f>IF(AG60="","",WORKDAY(AG60-AF60+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD60" s="66" t="str" cm="1">
+      <c r="AD60" s="66" cm="1" t="str">
         <f t="array" ref="AD60">IF(AG60="","",$AG60-$AF60)</f>
         <v/>
       </c>
@@ -27562,13 +27562,13 @@
       <c r="C61" s="18"/>
       <c r="D61" s="72"/>
       <c r="E61" s="71"/>
-      <c r="F61" s="82" t="str" cm="1">
+      <c r="F61" s="82" cm="1" t="str">
         <f t="array" ref="F61">IF(AG61="","",I61-H61)</f>
         <v/>
       </c>
       <c r="G61" s="67"/>
       <c r="H61" s="65"/>
-      <c r="I61" s="66" t="str" cm="1">
+      <c r="I61" s="66" cm="1" t="str">
         <f t="array" ref="I61">IF(AG61="","",P61-K61)</f>
         <v/>
       </c>
@@ -27578,7 +27578,7 @@
       <c r="M61" s="68"/>
       <c r="N61" s="68"/>
       <c r="O61" s="68"/>
-      <c r="P61" s="66" t="str" cm="1">
+      <c r="P61" s="66" cm="1" t="str">
         <f t="array" ref="P61">IF(AG61="","",AC61-R61-Q61)</f>
         <v/>
       </c>
@@ -27598,7 +27598,7 @@
         <f>IF(AG61="","",WORKDAY(AG61-AF61+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD61" s="66" t="str" cm="1">
+      <c r="AD61" s="66" cm="1" t="str">
         <f t="array" ref="AD61">IF(AG61="","",$AG61-$AF61)</f>
         <v/>
       </c>
@@ -27646,13 +27646,13 @@
       <c r="C62" s="19"/>
       <c r="D62" s="72"/>
       <c r="E62" s="71"/>
-      <c r="F62" s="82" t="str" cm="1">
+      <c r="F62" s="82" cm="1" t="str">
         <f t="array" ref="F62">IF(AG62="","",I62-H62)</f>
         <v/>
       </c>
       <c r="G62" s="67"/>
       <c r="H62" s="65"/>
-      <c r="I62" s="66" t="str" cm="1">
+      <c r="I62" s="66" cm="1" t="str">
         <f t="array" ref="I62">IF(AG62="","",P62-K62)</f>
         <v/>
       </c>
@@ -27662,7 +27662,7 @@
       <c r="M62" s="68"/>
       <c r="N62" s="68"/>
       <c r="O62" s="68"/>
-      <c r="P62" s="66" t="str" cm="1">
+      <c r="P62" s="66" cm="1" t="str">
         <f t="array" ref="P62">IF(AG62="","",AC62-R62-Q62)</f>
         <v/>
       </c>
@@ -27682,7 +27682,7 @@
         <f>IF(AG62="","",WORKDAY(AG62-AF62+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD62" s="66" t="str" cm="1">
+      <c r="AD62" s="66" cm="1" t="str">
         <f t="array" ref="AD62">IF(AG62="","",$AG62-$AF62)</f>
         <v/>
       </c>
@@ -27730,13 +27730,13 @@
       <c r="C63" s="19"/>
       <c r="D63" s="72"/>
       <c r="E63" s="71"/>
-      <c r="F63" s="82" t="str" cm="1">
+      <c r="F63" s="82" cm="1" t="str">
         <f t="array" ref="F63">IF(AG63="","",I63-H63)</f>
         <v/>
       </c>
       <c r="G63" s="67"/>
       <c r="H63" s="65"/>
-      <c r="I63" s="66" t="str" cm="1">
+      <c r="I63" s="66" cm="1" t="str">
         <f t="array" ref="I63">IF(AG63="","",P63-K63)</f>
         <v/>
       </c>
@@ -27746,7 +27746,7 @@
       <c r="M63" s="68"/>
       <c r="N63" s="68"/>
       <c r="O63" s="68"/>
-      <c r="P63" s="66" t="str" cm="1">
+      <c r="P63" s="66" cm="1" t="str">
         <f t="array" ref="P63">IF(AG63="","",AC63-R63-Q63)</f>
         <v/>
       </c>
@@ -27766,7 +27766,7 @@
         <f>IF(AG63="","",WORKDAY(AG63-AF63+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD63" s="66" t="str" cm="1">
+      <c r="AD63" s="66" cm="1" t="str">
         <f t="array" ref="AD63">IF(AG63="","",$AG63-$AF63)</f>
         <v/>
       </c>
@@ -27814,13 +27814,13 @@
       <c r="C64" s="19"/>
       <c r="D64" s="72"/>
       <c r="E64" s="71"/>
-      <c r="F64" s="82" t="str" cm="1">
+      <c r="F64" s="82" cm="1" t="str">
         <f t="array" ref="F64">IF(AG64="","",I64-H64)</f>
         <v/>
       </c>
       <c r="G64" s="67"/>
       <c r="H64" s="65"/>
-      <c r="I64" s="66" t="str" cm="1">
+      <c r="I64" s="66" cm="1" t="str">
         <f t="array" ref="I64">IF(AG64="","",P64-K64)</f>
         <v/>
       </c>
@@ -27830,7 +27830,7 @@
       <c r="M64" s="68"/>
       <c r="N64" s="68"/>
       <c r="O64" s="68"/>
-      <c r="P64" s="66" t="str" cm="1">
+      <c r="P64" s="66" cm="1" t="str">
         <f t="array" ref="P64">IF(AG64="","",AC64-R64-Q64)</f>
         <v/>
       </c>
@@ -27850,7 +27850,7 @@
         <f>IF(AG64="","",WORKDAY(AG64-AF64+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD64" s="66" t="str" cm="1">
+      <c r="AD64" s="66" cm="1" t="str">
         <f t="array" ref="AD64">IF(AG64="","",$AG64-$AF64)</f>
         <v/>
       </c>
@@ -27898,13 +27898,13 @@
       <c r="C65" s="19"/>
       <c r="D65" s="72"/>
       <c r="E65" s="71"/>
-      <c r="F65" s="82" t="str" cm="1">
+      <c r="F65" s="82" cm="1" t="str">
         <f t="array" ref="F65">IF(AG65="","",I65-H65)</f>
         <v/>
       </c>
       <c r="G65" s="67"/>
       <c r="H65" s="65"/>
-      <c r="I65" s="66" t="str" cm="1">
+      <c r="I65" s="66" cm="1" t="str">
         <f t="array" ref="I65">IF(AG65="","",P65-K65)</f>
         <v/>
       </c>
@@ -27914,7 +27914,7 @@
       <c r="M65" s="68"/>
       <c r="N65" s="68"/>
       <c r="O65" s="68"/>
-      <c r="P65" s="66" t="str" cm="1">
+      <c r="P65" s="66" cm="1" t="str">
         <f t="array" ref="P65">IF(AG65="","",AC65-R65-Q65)</f>
         <v/>
       </c>
@@ -27934,7 +27934,7 @@
         <f>IF(AG65="","",WORKDAY(AG65-AF65+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD65" s="66" t="str" cm="1">
+      <c r="AD65" s="66" cm="1" t="str">
         <f t="array" ref="AD65">IF(AG65="","",$AG65-$AF65)</f>
         <v/>
       </c>
@@ -27982,13 +27982,13 @@
       <c r="C66" s="19"/>
       <c r="D66" s="72"/>
       <c r="E66" s="71"/>
-      <c r="F66" s="82" t="str" cm="1">
+      <c r="F66" s="82" cm="1" t="str">
         <f t="array" ref="F66">IF(AG66="","",I66-H66)</f>
         <v/>
       </c>
       <c r="G66" s="67"/>
       <c r="H66" s="65"/>
-      <c r="I66" s="66" t="str" cm="1">
+      <c r="I66" s="66" cm="1" t="str">
         <f t="array" ref="I66">IF(AG66="","",P66-K66)</f>
         <v/>
       </c>
@@ -27998,7 +27998,7 @@
       <c r="M66" s="68"/>
       <c r="N66" s="68"/>
       <c r="O66" s="68"/>
-      <c r="P66" s="66" t="str" cm="1">
+      <c r="P66" s="66" cm="1" t="str">
         <f t="array" ref="P66">IF(AG66="","",AC66-R66-Q66)</f>
         <v/>
       </c>
@@ -28018,7 +28018,7 @@
         <f>IF(AG66="","",WORKDAY(AG66-AF66+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD66" s="66" t="str" cm="1">
+      <c r="AD66" s="66" cm="1" t="str">
         <f t="array" ref="AD66">IF(AG66="","",$AG66-$AF66)</f>
         <v/>
       </c>
@@ -28066,13 +28066,13 @@
       <c r="C67" s="19"/>
       <c r="D67" s="72"/>
       <c r="E67" s="71"/>
-      <c r="F67" s="82" t="str" cm="1">
+      <c r="F67" s="82" cm="1" t="str">
         <f t="array" ref="F67">IF(AG67="","",I67-H67)</f>
         <v/>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="65"/>
-      <c r="I67" s="66" t="str" cm="1">
+      <c r="I67" s="66" cm="1" t="str">
         <f t="array" ref="I67">IF(AG67="","",P67-K67)</f>
         <v/>
       </c>
@@ -28082,7 +28082,7 @@
       <c r="M67" s="68"/>
       <c r="N67" s="68"/>
       <c r="O67" s="68"/>
-      <c r="P67" s="66" t="str" cm="1">
+      <c r="P67" s="66" cm="1" t="str">
         <f t="array" ref="P67">IF(AG67="","",AC67-R67-Q67)</f>
         <v/>
       </c>
@@ -28102,7 +28102,7 @@
         <f>IF(AG67="","",WORKDAY(AG67-AF67+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD67" s="66" t="str" cm="1">
+      <c r="AD67" s="66" cm="1" t="str">
         <f t="array" ref="AD67">IF(AG67="","",$AG67-$AF67)</f>
         <v/>
       </c>
@@ -28150,13 +28150,13 @@
       <c r="C68" s="19"/>
       <c r="D68" s="72"/>
       <c r="E68" s="71"/>
-      <c r="F68" s="82" t="str" cm="1">
+      <c r="F68" s="82" cm="1" t="str">
         <f t="array" ref="F68">IF(AG68="","",I68-H68)</f>
         <v/>
       </c>
       <c r="G68" s="67"/>
       <c r="H68" s="65"/>
-      <c r="I68" s="66" t="str" cm="1">
+      <c r="I68" s="66" cm="1" t="str">
         <f t="array" ref="I68">IF(AG68="","",P68-K68)</f>
         <v/>
       </c>
@@ -28166,7 +28166,7 @@
       <c r="M68" s="68"/>
       <c r="N68" s="68"/>
       <c r="O68" s="68"/>
-      <c r="P68" s="66" t="str" cm="1">
+      <c r="P68" s="66" cm="1" t="str">
         <f t="array" ref="P68">IF(AG68="","",AC68-R68-Q68)</f>
         <v/>
       </c>
@@ -28186,7 +28186,7 @@
         <f>IF(AG68="","",WORKDAY(AG68-AF68+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD68" s="66" t="str" cm="1">
+      <c r="AD68" s="66" cm="1" t="str">
         <f t="array" ref="AD68">IF(AG68="","",$AG68-$AF68)</f>
         <v/>
       </c>
@@ -28234,13 +28234,13 @@
       <c r="C69" s="18"/>
       <c r="D69" s="72"/>
       <c r="E69" s="71"/>
-      <c r="F69" s="82" t="str" cm="1">
+      <c r="F69" s="82" cm="1" t="str">
         <f t="array" ref="F69">IF(AG69="","",I69-H69)</f>
         <v/>
       </c>
       <c r="G69" s="67"/>
       <c r="H69" s="65"/>
-      <c r="I69" s="66" t="str" cm="1">
+      <c r="I69" s="66" cm="1" t="str">
         <f t="array" ref="I69">IF(AG69="","",P69-K69)</f>
         <v/>
       </c>
@@ -28250,7 +28250,7 @@
       <c r="M69" s="68"/>
       <c r="N69" s="68"/>
       <c r="O69" s="68"/>
-      <c r="P69" s="66" t="str" cm="1">
+      <c r="P69" s="66" cm="1" t="str">
         <f t="array" ref="P69">IF(AG69="","",AC69-R69-Q69)</f>
         <v/>
       </c>
@@ -28270,7 +28270,7 @@
         <f>IF(AG69="","",WORKDAY(AG69-AF69+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD69" s="66" t="str" cm="1">
+      <c r="AD69" s="66" cm="1" t="str">
         <f t="array" ref="AD69">IF(AG69="","",$AG69-$AF69)</f>
         <v/>
       </c>
@@ -28318,13 +28318,13 @@
       <c r="C70" s="19"/>
       <c r="D70" s="72"/>
       <c r="E70" s="71"/>
-      <c r="F70" s="82" t="str" cm="1">
+      <c r="F70" s="82" cm="1" t="str">
         <f t="array" ref="F70">IF(AG70="","",I70-H70)</f>
         <v/>
       </c>
       <c r="G70" s="67"/>
       <c r="H70" s="65"/>
-      <c r="I70" s="66" t="str" cm="1">
+      <c r="I70" s="66" cm="1" t="str">
         <f t="array" ref="I70">IF(AG70="","",P70-K70)</f>
         <v/>
       </c>
@@ -28334,7 +28334,7 @@
       <c r="M70" s="68"/>
       <c r="N70" s="68"/>
       <c r="O70" s="68"/>
-      <c r="P70" s="66" t="str" cm="1">
+      <c r="P70" s="66" cm="1" t="str">
         <f t="array" ref="P70">IF(AG70="","",AC70-R70-Q70)</f>
         <v/>
       </c>
@@ -28354,7 +28354,7 @@
         <f>IF(AG70="","",WORKDAY(AG70-AF70+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD70" s="66" t="str" cm="1">
+      <c r="AD70" s="66" cm="1" t="str">
         <f t="array" ref="AD70">IF(AG70="","",$AG70-$AF70)</f>
         <v/>
       </c>
@@ -28402,13 +28402,13 @@
       <c r="C71" s="19"/>
       <c r="D71" s="72"/>
       <c r="E71" s="71"/>
-      <c r="F71" s="82" t="str" cm="1">
+      <c r="F71" s="82" cm="1" t="str">
         <f t="array" ref="F71">IF(AG71="","",I71-H71)</f>
         <v/>
       </c>
       <c r="G71" s="67"/>
       <c r="H71" s="65"/>
-      <c r="I71" s="66" t="str" cm="1">
+      <c r="I71" s="66" cm="1" t="str">
         <f t="array" ref="I71">IF(AG71="","",P71-K71)</f>
         <v/>
       </c>
@@ -28418,7 +28418,7 @@
       <c r="M71" s="68"/>
       <c r="N71" s="68"/>
       <c r="O71" s="68"/>
-      <c r="P71" s="66" t="str" cm="1">
+      <c r="P71" s="66" cm="1" t="str">
         <f t="array" ref="P71">IF(AG71="","",AC71-R71-Q71)</f>
         <v/>
       </c>
@@ -28438,7 +28438,7 @@
         <f>IF(AG71="","",WORKDAY(AG71-AF71+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD71" s="66" t="str" cm="1">
+      <c r="AD71" s="66" cm="1" t="str">
         <f t="array" ref="AD71">IF(AG71="","",$AG71-$AF71)</f>
         <v/>
       </c>
@@ -28486,13 +28486,13 @@
       <c r="C72" s="19"/>
       <c r="D72" s="72"/>
       <c r="E72" s="71"/>
-      <c r="F72" s="82" t="str" cm="1">
+      <c r="F72" s="82" cm="1" t="str">
         <f t="array" ref="F72">IF(AG72="","",I72-H72)</f>
         <v/>
       </c>
       <c r="G72" s="67"/>
       <c r="H72" s="65"/>
-      <c r="I72" s="66" t="str" cm="1">
+      <c r="I72" s="66" cm="1" t="str">
         <f t="array" ref="I72">IF(AG72="","",P72-K72)</f>
         <v/>
       </c>
@@ -28502,7 +28502,7 @@
       <c r="M72" s="68"/>
       <c r="N72" s="68"/>
       <c r="O72" s="68"/>
-      <c r="P72" s="66" t="str" cm="1">
+      <c r="P72" s="66" cm="1" t="str">
         <f t="array" ref="P72">IF(AG72="","",AC72-R72-Q72)</f>
         <v/>
       </c>
@@ -28522,7 +28522,7 @@
         <f>IF(AG72="","",WORKDAY(AG72-AF72+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD72" s="66" t="str" cm="1">
+      <c r="AD72" s="66" cm="1" t="str">
         <f t="array" ref="AD72">IF(AG72="","",$AG72-$AF72)</f>
         <v/>
       </c>
@@ -28570,13 +28570,13 @@
       <c r="C73" s="19"/>
       <c r="D73" s="72"/>
       <c r="E73" s="71"/>
-      <c r="F73" s="82" t="str" cm="1">
+      <c r="F73" s="82" cm="1" t="str">
         <f t="array" ref="F73">IF(AG73="","",I73-H73)</f>
         <v/>
       </c>
       <c r="G73" s="67"/>
       <c r="H73" s="65"/>
-      <c r="I73" s="66" t="str" cm="1">
+      <c r="I73" s="66" cm="1" t="str">
         <f t="array" ref="I73">IF(AG73="","",P73-K73)</f>
         <v/>
       </c>
@@ -28586,7 +28586,7 @@
       <c r="M73" s="68"/>
       <c r="N73" s="68"/>
       <c r="O73" s="68"/>
-      <c r="P73" s="66" t="str" cm="1">
+      <c r="P73" s="66" cm="1" t="str">
         <f t="array" ref="P73">IF(AG73="","",AC73-R73-Q73)</f>
         <v/>
       </c>
@@ -28606,7 +28606,7 @@
         <f>IF(AG73="","",WORKDAY(AG73-AF73+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD73" s="66" t="str" cm="1">
+      <c r="AD73" s="66" cm="1" t="str">
         <f t="array" ref="AD73">IF(AG73="","",$AG73-$AF73)</f>
         <v/>
       </c>
@@ -28654,13 +28654,13 @@
       <c r="C74" s="19"/>
       <c r="D74" s="72"/>
       <c r="E74" s="71"/>
-      <c r="F74" s="82" t="str" cm="1">
+      <c r="F74" s="82" cm="1" t="str">
         <f t="array" ref="F74">IF(AG74="","",I74-H74)</f>
         <v/>
       </c>
       <c r="G74" s="67"/>
       <c r="H74" s="65"/>
-      <c r="I74" s="66" t="str" cm="1">
+      <c r="I74" s="66" cm="1" t="str">
         <f t="array" ref="I74">IF(AG74="","",P74-K74)</f>
         <v/>
       </c>
@@ -28670,7 +28670,7 @@
       <c r="M74" s="68"/>
       <c r="N74" s="68"/>
       <c r="O74" s="68"/>
-      <c r="P74" s="66" t="str" cm="1">
+      <c r="P74" s="66" cm="1" t="str">
         <f t="array" ref="P74">IF(AG74="","",AC74-R74-Q74)</f>
         <v/>
       </c>
@@ -28690,7 +28690,7 @@
         <f>IF(AG74="","",WORKDAY(AG74-AF74+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD74" s="66" t="str" cm="1">
+      <c r="AD74" s="66" cm="1" t="str">
         <f t="array" ref="AD74">IF(AG74="","",$AG74-$AF74)</f>
         <v/>
       </c>
@@ -28738,13 +28738,13 @@
       <c r="C75" s="19"/>
       <c r="D75" s="72"/>
       <c r="E75" s="71"/>
-      <c r="F75" s="82" t="str" cm="1">
+      <c r="F75" s="82" cm="1" t="str">
         <f t="array" ref="F75">IF(AG75="","",I75-H75)</f>
         <v/>
       </c>
       <c r="G75" s="67"/>
       <c r="H75" s="65"/>
-      <c r="I75" s="66" t="str" cm="1">
+      <c r="I75" s="66" cm="1" t="str">
         <f t="array" ref="I75">IF(AG75="","",P75-K75)</f>
         <v/>
       </c>
@@ -28754,7 +28754,7 @@
       <c r="M75" s="68"/>
       <c r="N75" s="68"/>
       <c r="O75" s="68"/>
-      <c r="P75" s="66" t="str" cm="1">
+      <c r="P75" s="66" cm="1" t="str">
         <f t="array" ref="P75">IF(AG75="","",AC75-R75-Q75)</f>
         <v/>
       </c>
@@ -28774,7 +28774,7 @@
         <f>IF(AG75="","",WORKDAY(AG75-AF75+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD75" s="66" t="str" cm="1">
+      <c r="AD75" s="66" cm="1" t="str">
         <f t="array" ref="AD75">IF(AG75="","",$AG75-$AF75)</f>
         <v/>
       </c>
@@ -28822,13 +28822,13 @@
       <c r="C76" s="19"/>
       <c r="D76" s="72"/>
       <c r="E76" s="71"/>
-      <c r="F76" s="82" t="str" cm="1">
+      <c r="F76" s="82" cm="1" t="str">
         <f t="array" ref="F76">IF(AG76="","",I76-H76)</f>
         <v/>
       </c>
       <c r="G76" s="67"/>
       <c r="H76" s="65"/>
-      <c r="I76" s="66" t="str" cm="1">
+      <c r="I76" s="66" cm="1" t="str">
         <f t="array" ref="I76">IF(AG76="","",P76-K76)</f>
         <v/>
       </c>
@@ -28838,7 +28838,7 @@
       <c r="M76" s="68"/>
       <c r="N76" s="68"/>
       <c r="O76" s="68"/>
-      <c r="P76" s="66" t="str" cm="1">
+      <c r="P76" s="66" cm="1" t="str">
         <f t="array" ref="P76">IF(AG76="","",AC76-R76-Q76)</f>
         <v/>
       </c>
@@ -28858,7 +28858,7 @@
         <f>IF(AG76="","",WORKDAY(AG76-AF76+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD76" s="66" t="str" cm="1">
+      <c r="AD76" s="66" cm="1" t="str">
         <f t="array" ref="AD76">IF(AG76="","",$AG76-$AF76)</f>
         <v/>
       </c>
@@ -28906,13 +28906,13 @@
       <c r="C77" s="19"/>
       <c r="D77" s="72"/>
       <c r="E77" s="71"/>
-      <c r="F77" s="82" t="str" cm="1">
+      <c r="F77" s="82" cm="1" t="str">
         <f t="array" ref="F77">IF(AG77="","",I77-H77)</f>
         <v/>
       </c>
       <c r="G77" s="67"/>
       <c r="H77" s="65"/>
-      <c r="I77" s="66" t="str" cm="1">
+      <c r="I77" s="66" cm="1" t="str">
         <f t="array" ref="I77">IF(AG77="","",P77-K77)</f>
         <v/>
       </c>
@@ -28922,7 +28922,7 @@
       <c r="M77" s="68"/>
       <c r="N77" s="68"/>
       <c r="O77" s="68"/>
-      <c r="P77" s="66" t="str" cm="1">
+      <c r="P77" s="66" cm="1" t="str">
         <f t="array" ref="P77">IF(AG77="","",AC77-R77-Q77)</f>
         <v/>
       </c>
@@ -28942,7 +28942,7 @@
         <f>IF(AG77="","",WORKDAY(AG77-AF77+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD77" s="66" t="str" cm="1">
+      <c r="AD77" s="66" cm="1" t="str">
         <f t="array" ref="AD77">IF(AG77="","",$AG77-$AF77)</f>
         <v/>
       </c>
@@ -28990,13 +28990,13 @@
       <c r="C78" s="19"/>
       <c r="D78" s="72"/>
       <c r="E78" s="71"/>
-      <c r="F78" s="82" t="str" cm="1">
+      <c r="F78" s="82" cm="1" t="str">
         <f t="array" ref="F78">IF(AG78="","",I78-H78)</f>
         <v/>
       </c>
       <c r="G78" s="67"/>
       <c r="H78" s="65"/>
-      <c r="I78" s="66" t="str" cm="1">
+      <c r="I78" s="66" cm="1" t="str">
         <f t="array" ref="I78">IF(AG78="","",P78-K78)</f>
         <v/>
       </c>
@@ -29006,7 +29006,7 @@
       <c r="M78" s="68"/>
       <c r="N78" s="68"/>
       <c r="O78" s="68"/>
-      <c r="P78" s="66" t="str" cm="1">
+      <c r="P78" s="66" cm="1" t="str">
         <f t="array" ref="P78">IF(AG78="","",AC78-R78-Q78)</f>
         <v/>
       </c>
@@ -29026,7 +29026,7 @@
         <f>IF(AG78="","",WORKDAY(AG78-AF78+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD78" s="66" t="str" cm="1">
+      <c r="AD78" s="66" cm="1" t="str">
         <f t="array" ref="AD78">IF(AG78="","",$AG78-$AF78)</f>
         <v/>
       </c>
@@ -29074,13 +29074,13 @@
       <c r="C79" s="19"/>
       <c r="D79" s="72"/>
       <c r="E79" s="71"/>
-      <c r="F79" s="82" t="str" cm="1">
+      <c r="F79" s="82" cm="1" t="str">
         <f t="array" ref="F79">IF(AG79="","",I79-H79)</f>
         <v/>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="65"/>
-      <c r="I79" s="66" t="str" cm="1">
+      <c r="I79" s="66" cm="1" t="str">
         <f t="array" ref="I79">IF(AG79="","",P79-K79)</f>
         <v/>
       </c>
@@ -29090,7 +29090,7 @@
       <c r="M79" s="68"/>
       <c r="N79" s="68"/>
       <c r="O79" s="68"/>
-      <c r="P79" s="66" t="str" cm="1">
+      <c r="P79" s="66" cm="1" t="str">
         <f t="array" ref="P79">IF(AG79="","",AC79-R79-Q79)</f>
         <v/>
       </c>
@@ -29110,7 +29110,7 @@
         <f>IF(AG79="","",WORKDAY(AG79-AF79+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD79" s="66" t="str" cm="1">
+      <c r="AD79" s="66" cm="1" t="str">
         <f t="array" ref="AD79">IF(AG79="","",$AG79-$AF79)</f>
         <v/>
       </c>
@@ -29158,13 +29158,13 @@
       <c r="C80" s="19"/>
       <c r="D80" s="72"/>
       <c r="E80" s="71"/>
-      <c r="F80" s="82" t="str" cm="1">
+      <c r="F80" s="82" cm="1" t="str">
         <f t="array" ref="F80">IF(AG80="","",I80-H80)</f>
         <v/>
       </c>
       <c r="G80" s="67"/>
       <c r="H80" s="65"/>
-      <c r="I80" s="66" t="str" cm="1">
+      <c r="I80" s="66" cm="1" t="str">
         <f t="array" ref="I80">IF(AG80="","",P80-K80)</f>
         <v/>
       </c>
@@ -29174,7 +29174,7 @@
       <c r="M80" s="68"/>
       <c r="N80" s="68"/>
       <c r="O80" s="68"/>
-      <c r="P80" s="66" t="str" cm="1">
+      <c r="P80" s="66" cm="1" t="str">
         <f t="array" ref="P80">IF(AG80="","",AC80-R80-Q80)</f>
         <v/>
       </c>
@@ -29194,7 +29194,7 @@
         <f>IF(AG80="","",WORKDAY(AG80-AF80+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD80" s="66" t="str" cm="1">
+      <c r="AD80" s="66" cm="1" t="str">
         <f t="array" ref="AD80">IF(AG80="","",$AG80-$AF80)</f>
         <v/>
       </c>
@@ -29242,13 +29242,13 @@
       <c r="C81" s="19"/>
       <c r="D81" s="72"/>
       <c r="E81" s="71"/>
-      <c r="F81" s="82" t="str" cm="1">
+      <c r="F81" s="82" cm="1" t="str">
         <f t="array" ref="F81">IF(AG81="","",I81-H81)</f>
         <v/>
       </c>
       <c r="G81" s="67"/>
       <c r="H81" s="65"/>
-      <c r="I81" s="66" t="str" cm="1">
+      <c r="I81" s="66" cm="1" t="str">
         <f t="array" ref="I81">IF(AG81="","",P81-K81)</f>
         <v/>
       </c>
@@ -29258,7 +29258,7 @@
       <c r="M81" s="68"/>
       <c r="N81" s="68"/>
       <c r="O81" s="68"/>
-      <c r="P81" s="66" t="str" cm="1">
+      <c r="P81" s="66" cm="1" t="str">
         <f t="array" ref="P81">IF(AG81="","",AC81-R81-Q81)</f>
         <v/>
       </c>
@@ -29278,7 +29278,7 @@
         <f>IF(AG81="","",WORKDAY(AG81-AF81+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD81" s="66" t="str" cm="1">
+      <c r="AD81" s="66" cm="1" t="str">
         <f t="array" ref="AD81">IF(AG81="","",$AG81-$AF81)</f>
         <v/>
       </c>
@@ -29326,13 +29326,13 @@
       <c r="C82" s="19"/>
       <c r="D82" s="72"/>
       <c r="E82" s="71"/>
-      <c r="F82" s="82" t="str" cm="1">
+      <c r="F82" s="82" cm="1" t="str">
         <f t="array" ref="F82">IF(AG82="","",I82-H82)</f>
         <v/>
       </c>
       <c r="G82" s="67"/>
       <c r="H82" s="65"/>
-      <c r="I82" s="66" t="str" cm="1">
+      <c r="I82" s="66" cm="1" t="str">
         <f t="array" ref="I82">IF(AG82="","",P82-K82)</f>
         <v/>
       </c>
@@ -29342,7 +29342,7 @@
       <c r="M82" s="68"/>
       <c r="N82" s="68"/>
       <c r="O82" s="68"/>
-      <c r="P82" s="66" t="str" cm="1">
+      <c r="P82" s="66" cm="1" t="str">
         <f t="array" ref="P82">IF(AG82="","",AC82-R82-Q82)</f>
         <v/>
       </c>
@@ -29362,7 +29362,7 @@
         <f>IF(AG82="","",WORKDAY(AG82-AF82+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD82" s="66" t="str" cm="1">
+      <c r="AD82" s="66" cm="1" t="str">
         <f t="array" ref="AD82">IF(AG82="","",$AG82-$AF82)</f>
         <v/>
       </c>
@@ -29410,13 +29410,13 @@
       <c r="C83" s="19"/>
       <c r="D83" s="72"/>
       <c r="E83" s="71"/>
-      <c r="F83" s="82" t="str" cm="1">
+      <c r="F83" s="82" cm="1" t="str">
         <f t="array" ref="F83">IF(AG83="","",I83-H83)</f>
         <v/>
       </c>
       <c r="G83" s="67"/>
       <c r="H83" s="65"/>
-      <c r="I83" s="66" t="str" cm="1">
+      <c r="I83" s="66" cm="1" t="str">
         <f t="array" ref="I83">IF(AG83="","",P83-K83)</f>
         <v/>
       </c>
@@ -29426,7 +29426,7 @@
       <c r="M83" s="68"/>
       <c r="N83" s="68"/>
       <c r="O83" s="68"/>
-      <c r="P83" s="66" t="str" cm="1">
+      <c r="P83" s="66" cm="1" t="str">
         <f t="array" ref="P83">IF(AG83="","",AC83-R83-Q83)</f>
         <v/>
       </c>
@@ -29446,7 +29446,7 @@
         <f>IF(AG83="","",WORKDAY(AG83-AF83+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD83" s="66" t="str" cm="1">
+      <c r="AD83" s="66" cm="1" t="str">
         <f t="array" ref="AD83">IF(AG83="","",$AG83-$AF83)</f>
         <v/>
       </c>
@@ -29494,13 +29494,13 @@
       <c r="C84" s="19"/>
       <c r="D84" s="72"/>
       <c r="E84" s="71"/>
-      <c r="F84" s="82" t="str" cm="1">
+      <c r="F84" s="82" cm="1" t="str">
         <f t="array" ref="F84">IF(AG84="","",I84-H84)</f>
         <v/>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="65"/>
-      <c r="I84" s="66" t="str" cm="1">
+      <c r="I84" s="66" cm="1" t="str">
         <f t="array" ref="I84">IF(AG84="","",P84-K84)</f>
         <v/>
       </c>
@@ -29510,7 +29510,7 @@
       <c r="M84" s="68"/>
       <c r="N84" s="68"/>
       <c r="O84" s="68"/>
-      <c r="P84" s="66" t="str" cm="1">
+      <c r="P84" s="66" cm="1" t="str">
         <f t="array" ref="P84">IF(AG84="","",AC84-R84-Q84)</f>
         <v/>
       </c>
@@ -29530,7 +29530,7 @@
         <f>IF(AG84="","",WORKDAY(AG84-AF84+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD84" s="66" t="str" cm="1">
+      <c r="AD84" s="66" cm="1" t="str">
         <f t="array" ref="AD84">IF(AG84="","",$AG84-$AF84)</f>
         <v/>
       </c>
@@ -29578,13 +29578,13 @@
       <c r="C85" s="19"/>
       <c r="D85" s="72"/>
       <c r="E85" s="71"/>
-      <c r="F85" s="82" t="str" cm="1">
+      <c r="F85" s="82" cm="1" t="str">
         <f t="array" ref="F85">IF(AG85="","",I85-H85)</f>
         <v/>
       </c>
       <c r="G85" s="67"/>
       <c r="H85" s="65"/>
-      <c r="I85" s="66" t="str" cm="1">
+      <c r="I85" s="66" cm="1" t="str">
         <f t="array" ref="I85">IF(AG85="","",P85-K85)</f>
         <v/>
       </c>
@@ -29594,7 +29594,7 @@
       <c r="M85" s="68"/>
       <c r="N85" s="68"/>
       <c r="O85" s="68"/>
-      <c r="P85" s="66" t="str" cm="1">
+      <c r="P85" s="66" cm="1" t="str">
         <f t="array" ref="P85">IF(AG85="","",AC85-R85-Q85)</f>
         <v/>
       </c>
@@ -29614,7 +29614,7 @@
         <f>IF(AG85="","",WORKDAY(AG85-AF85+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD85" s="66" t="str" cm="1">
+      <c r="AD85" s="66" cm="1" t="str">
         <f t="array" ref="AD85">IF(AG85="","",$AG85-$AF85)</f>
         <v/>
       </c>
@@ -29662,13 +29662,13 @@
       <c r="C86" s="19"/>
       <c r="D86" s="72"/>
       <c r="E86" s="71"/>
-      <c r="F86" s="82" t="str" cm="1">
+      <c r="F86" s="82" cm="1" t="str">
         <f t="array" ref="F86">IF(AG86="","",I86-H86)</f>
         <v/>
       </c>
       <c r="G86" s="67"/>
       <c r="H86" s="65"/>
-      <c r="I86" s="66" t="str" cm="1">
+      <c r="I86" s="66" cm="1" t="str">
         <f t="array" ref="I86">IF(AG86="","",P86-K86)</f>
         <v/>
       </c>
@@ -29678,7 +29678,7 @@
       <c r="M86" s="68"/>
       <c r="N86" s="68"/>
       <c r="O86" s="68"/>
-      <c r="P86" s="66" t="str" cm="1">
+      <c r="P86" s="66" cm="1" t="str">
         <f t="array" ref="P86">IF(AG86="","",AC86-R86-Q86)</f>
         <v/>
       </c>
@@ -29698,7 +29698,7 @@
         <f>IF(AG86="","",WORKDAY(AG86-AF86+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD86" s="66" t="str" cm="1">
+      <c r="AD86" s="66" cm="1" t="str">
         <f t="array" ref="AD86">IF(AG86="","",$AG86-$AF86)</f>
         <v/>
       </c>
@@ -29746,13 +29746,13 @@
       <c r="C87" s="19"/>
       <c r="D87" s="72"/>
       <c r="E87" s="71"/>
-      <c r="F87" s="82" t="str" cm="1">
+      <c r="F87" s="82" cm="1" t="str">
         <f t="array" ref="F87">IF(AG87="","",I87-H87)</f>
         <v/>
       </c>
       <c r="G87" s="67"/>
       <c r="H87" s="65"/>
-      <c r="I87" s="66" t="str" cm="1">
+      <c r="I87" s="66" cm="1" t="str">
         <f t="array" ref="I87">IF(AG87="","",P87-K87)</f>
         <v/>
       </c>
@@ -29762,7 +29762,7 @@
       <c r="M87" s="68"/>
       <c r="N87" s="68"/>
       <c r="O87" s="68"/>
-      <c r="P87" s="66" t="str" cm="1">
+      <c r="P87" s="66" cm="1" t="str">
         <f t="array" ref="P87">IF(AG87="","",AC87-R87-Q87)</f>
         <v/>
       </c>
@@ -29782,7 +29782,7 @@
         <f>IF(AG87="","",WORKDAY(AG87-AF87+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD87" s="66" t="str" cm="1">
+      <c r="AD87" s="66" cm="1" t="str">
         <f t="array" ref="AD87">IF(AG87="","",$AG87-$AF87)</f>
         <v/>
       </c>
@@ -29830,13 +29830,13 @@
       <c r="C88" s="19"/>
       <c r="D88" s="72"/>
       <c r="E88" s="71"/>
-      <c r="F88" s="82" t="str" cm="1">
+      <c r="F88" s="82" cm="1" t="str">
         <f t="array" ref="F88">IF(AG88="","",I88-H88)</f>
         <v/>
       </c>
       <c r="G88" s="67"/>
       <c r="H88" s="65"/>
-      <c r="I88" s="66" t="str" cm="1">
+      <c r="I88" s="66" cm="1" t="str">
         <f t="array" ref="I88">IF(AG88="","",P88-K88)</f>
         <v/>
       </c>
@@ -29846,7 +29846,7 @@
       <c r="M88" s="68"/>
       <c r="N88" s="68"/>
       <c r="O88" s="68"/>
-      <c r="P88" s="66" t="str" cm="1">
+      <c r="P88" s="66" cm="1" t="str">
         <f t="array" ref="P88">IF(AG88="","",AC88-R88-Q88)</f>
         <v/>
       </c>
@@ -29866,7 +29866,7 @@
         <f>IF(AG88="","",WORKDAY(AG88-AF88+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD88" s="66" t="str" cm="1">
+      <c r="AD88" s="66" cm="1" t="str">
         <f t="array" ref="AD88">IF(AG88="","",$AG88-$AF88)</f>
         <v/>
       </c>
@@ -29914,13 +29914,13 @@
       <c r="C89" s="19"/>
       <c r="D89" s="72"/>
       <c r="E89" s="71"/>
-      <c r="F89" s="82" t="str" cm="1">
+      <c r="F89" s="82" cm="1" t="str">
         <f t="array" ref="F89">IF(AG89="","",I89-H89)</f>
         <v/>
       </c>
       <c r="G89" s="67"/>
       <c r="H89" s="65"/>
-      <c r="I89" s="66" t="str" cm="1">
+      <c r="I89" s="66" cm="1" t="str">
         <f t="array" ref="I89">IF(AG89="","",P89-K89)</f>
         <v/>
       </c>
@@ -29930,7 +29930,7 @@
       <c r="M89" s="68"/>
       <c r="N89" s="68"/>
       <c r="O89" s="68"/>
-      <c r="P89" s="66" t="str" cm="1">
+      <c r="P89" s="66" cm="1" t="str">
         <f t="array" ref="P89">IF(AG89="","",AC89-R89-Q89)</f>
         <v/>
       </c>
@@ -29950,7 +29950,7 @@
         <f>IF(AG89="","",WORKDAY(AG89-AF89+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD89" s="66" t="str" cm="1">
+      <c r="AD89" s="66" cm="1" t="str">
         <f t="array" ref="AD89">IF(AG89="","",$AG89-$AF89)</f>
         <v/>
       </c>
@@ -29998,13 +29998,13 @@
       <c r="C90" s="19"/>
       <c r="D90" s="72"/>
       <c r="E90" s="71"/>
-      <c r="F90" s="82" t="str" cm="1">
+      <c r="F90" s="82" cm="1" t="str">
         <f t="array" ref="F90">IF(AG90="","",I90-H90)</f>
         <v/>
       </c>
       <c r="G90" s="67"/>
       <c r="H90" s="65"/>
-      <c r="I90" s="66" t="str" cm="1">
+      <c r="I90" s="66" cm="1" t="str">
         <f t="array" ref="I90">IF(AG90="","",P90-K90)</f>
         <v/>
       </c>
@@ -30014,7 +30014,7 @@
       <c r="M90" s="68"/>
       <c r="N90" s="68"/>
       <c r="O90" s="68"/>
-      <c r="P90" s="66" t="str" cm="1">
+      <c r="P90" s="66" cm="1" t="str">
         <f t="array" ref="P90">IF(AG90="","",AC90-R90-Q90)</f>
         <v/>
       </c>
@@ -30034,7 +30034,7 @@
         <f>IF(AG90="","",WORKDAY(AG90-AF90+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD90" s="66" t="str" cm="1">
+      <c r="AD90" s="66" cm="1" t="str">
         <f t="array" ref="AD90">IF(AG90="","",$AG90-$AF90)</f>
         <v/>
       </c>
@@ -30082,13 +30082,13 @@
       <c r="C91" s="19"/>
       <c r="D91" s="72"/>
       <c r="E91" s="71"/>
-      <c r="F91" s="82" t="str" cm="1">
+      <c r="F91" s="82" cm="1" t="str">
         <f t="array" ref="F91">IF(AG91="","",I91-H91)</f>
         <v/>
       </c>
       <c r="G91" s="67"/>
       <c r="H91" s="65"/>
-      <c r="I91" s="66" t="str" cm="1">
+      <c r="I91" s="66" cm="1" t="str">
         <f t="array" ref="I91">IF(AG91="","",P91-K91)</f>
         <v/>
       </c>
@@ -30098,7 +30098,7 @@
       <c r="M91" s="68"/>
       <c r="N91" s="68"/>
       <c r="O91" s="68"/>
-      <c r="P91" s="66" t="str" cm="1">
+      <c r="P91" s="66" cm="1" t="str">
         <f t="array" ref="P91">IF(AG91="","",AC91-R91-Q91)</f>
         <v/>
       </c>
@@ -30118,7 +30118,7 @@
         <f>IF(AG91="","",WORKDAY(AG91-AF91+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD91" s="66" t="str" cm="1">
+      <c r="AD91" s="66" cm="1" t="str">
         <f t="array" ref="AD91">IF(AG91="","",$AG91-$AF91)</f>
         <v/>
       </c>
@@ -30166,13 +30166,13 @@
       <c r="C92" s="19"/>
       <c r="D92" s="72"/>
       <c r="E92" s="71"/>
-      <c r="F92" s="82" t="str" cm="1">
+      <c r="F92" s="82" cm="1" t="str">
         <f t="array" ref="F92">IF(AG92="","",I92-H92)</f>
         <v/>
       </c>
       <c r="G92" s="67"/>
       <c r="H92" s="65"/>
-      <c r="I92" s="66" t="str" cm="1">
+      <c r="I92" s="66" cm="1" t="str">
         <f t="array" ref="I92">IF(AG92="","",P92-K92)</f>
         <v/>
       </c>
@@ -30182,7 +30182,7 @@
       <c r="M92" s="68"/>
       <c r="N92" s="68"/>
       <c r="O92" s="68"/>
-      <c r="P92" s="66" t="str" cm="1">
+      <c r="P92" s="66" cm="1" t="str">
         <f t="array" ref="P92">IF(AG92="","",AC92-R92-Q92)</f>
         <v/>
       </c>
@@ -30202,7 +30202,7 @@
         <f>IF(AG92="","",WORKDAY(AG92-AF92+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD92" s="66" t="str" cm="1">
+      <c r="AD92" s="66" cm="1" t="str">
         <f t="array" ref="AD92">IF(AG92="","",$AG92-$AF92)</f>
         <v/>
       </c>
@@ -30250,13 +30250,13 @@
       <c r="C93" s="19"/>
       <c r="D93" s="72"/>
       <c r="E93" s="71"/>
-      <c r="F93" s="82" t="str" cm="1">
+      <c r="F93" s="82" cm="1" t="str">
         <f t="array" ref="F93">IF(AG93="","",I93-H93)</f>
         <v/>
       </c>
       <c r="G93" s="67"/>
       <c r="H93" s="65"/>
-      <c r="I93" s="66" t="str" cm="1">
+      <c r="I93" s="66" cm="1" t="str">
         <f t="array" ref="I93">IF(AG93="","",P93-K93)</f>
         <v/>
       </c>
@@ -30266,7 +30266,7 @@
       <c r="M93" s="68"/>
       <c r="N93" s="68"/>
       <c r="O93" s="68"/>
-      <c r="P93" s="66" t="str" cm="1">
+      <c r="P93" s="66" cm="1" t="str">
         <f t="array" ref="P93">IF(AG93="","",AC93-R93-Q93)</f>
         <v/>
       </c>
@@ -30286,7 +30286,7 @@
         <f>IF(AG93="","",WORKDAY(AG93-AF93+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD93" s="66" t="str" cm="1">
+      <c r="AD93" s="66" cm="1" t="str">
         <f t="array" ref="AD93">IF(AG93="","",$AG93-$AF93)</f>
         <v/>
       </c>
@@ -30334,13 +30334,13 @@
       <c r="C94" s="19"/>
       <c r="D94" s="72"/>
       <c r="E94" s="71"/>
-      <c r="F94" s="82" t="str" cm="1">
+      <c r="F94" s="82" cm="1" t="str">
         <f t="array" ref="F94">IF(AG94="","",I94-H94)</f>
         <v/>
       </c>
       <c r="G94" s="67"/>
       <c r="H94" s="65"/>
-      <c r="I94" s="66" t="str" cm="1">
+      <c r="I94" s="66" cm="1" t="str">
         <f t="array" ref="I94">IF(AG94="","",P94-K94)</f>
         <v/>
       </c>
@@ -30350,7 +30350,7 @@
       <c r="M94" s="68"/>
       <c r="N94" s="68"/>
       <c r="O94" s="68"/>
-      <c r="P94" s="66" t="str" cm="1">
+      <c r="P94" s="66" cm="1" t="str">
         <f t="array" ref="P94">IF(AG94="","",AC94-R94-Q94)</f>
         <v/>
       </c>
@@ -30370,7 +30370,7 @@
         <f>IF(AG94="","",WORKDAY(AG94-AF94+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD94" s="66" t="str" cm="1">
+      <c r="AD94" s="66" cm="1" t="str">
         <f t="array" ref="AD94">IF(AG94="","",$AG94-$AF94)</f>
         <v/>
       </c>
@@ -30418,13 +30418,13 @@
       <c r="C95" s="19"/>
       <c r="D95" s="72"/>
       <c r="E95" s="71"/>
-      <c r="F95" s="82" t="str" cm="1">
+      <c r="F95" s="82" cm="1" t="str">
         <f t="array" ref="F95">IF(AG95="","",I95-H95)</f>
         <v/>
       </c>
       <c r="G95" s="67"/>
       <c r="H95" s="65"/>
-      <c r="I95" s="66" t="str" cm="1">
+      <c r="I95" s="66" cm="1" t="str">
         <f t="array" ref="I95">IF(AG95="","",P95-K95)</f>
         <v/>
       </c>
@@ -30434,7 +30434,7 @@
       <c r="M95" s="68"/>
       <c r="N95" s="68"/>
       <c r="O95" s="68"/>
-      <c r="P95" s="66" t="str" cm="1">
+      <c r="P95" s="66" cm="1" t="str">
         <f t="array" ref="P95">IF(AG95="","",AC95-R95-Q95)</f>
         <v/>
       </c>
@@ -30454,7 +30454,7 @@
         <f>IF(AG95="","",WORKDAY(AG95-AF95+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD95" s="66" t="str" cm="1">
+      <c r="AD95" s="66" cm="1" t="str">
         <f t="array" ref="AD95">IF(AG95="","",$AG95-$AF95)</f>
         <v/>
       </c>
@@ -30502,13 +30502,13 @@
       <c r="C96" s="19"/>
       <c r="D96" s="72"/>
       <c r="E96" s="71"/>
-      <c r="F96" s="82" t="str" cm="1">
+      <c r="F96" s="82" cm="1" t="str">
         <f t="array" ref="F96">IF(AG96="","",I96-H96)</f>
         <v/>
       </c>
       <c r="G96" s="67"/>
       <c r="H96" s="65"/>
-      <c r="I96" s="66" t="str" cm="1">
+      <c r="I96" s="66" cm="1" t="str">
         <f t="array" ref="I96">IF(AG96="","",P96-K96)</f>
         <v/>
       </c>
@@ -30518,7 +30518,7 @@
       <c r="M96" s="68"/>
       <c r="N96" s="68"/>
       <c r="O96" s="68"/>
-      <c r="P96" s="66" t="str" cm="1">
+      <c r="P96" s="66" cm="1" t="str">
         <f t="array" ref="P96">IF(AG96="","",AC96-R96-Q96)</f>
         <v/>
       </c>
@@ -30538,7 +30538,7 @@
         <f>IF(AG96="","",WORKDAY(AG96-AF96+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD96" s="66" t="str" cm="1">
+      <c r="AD96" s="66" cm="1" t="str">
         <f t="array" ref="AD96">IF(AG96="","",$AG96-$AF96)</f>
         <v/>
       </c>
@@ -30586,13 +30586,13 @@
       <c r="C97" s="19"/>
       <c r="D97" s="72"/>
       <c r="E97" s="71"/>
-      <c r="F97" s="82" t="str" cm="1">
+      <c r="F97" s="82" cm="1" t="str">
         <f t="array" ref="F97">IF(AG97="","",I97-H97)</f>
         <v/>
       </c>
       <c r="G97" s="67"/>
       <c r="H97" s="65"/>
-      <c r="I97" s="66" t="str" cm="1">
+      <c r="I97" s="66" cm="1" t="str">
         <f t="array" ref="I97">IF(AG97="","",P97-K97)</f>
         <v/>
       </c>
@@ -30602,7 +30602,7 @@
       <c r="M97" s="68"/>
       <c r="N97" s="68"/>
       <c r="O97" s="68"/>
-      <c r="P97" s="66" t="str" cm="1">
+      <c r="P97" s="66" cm="1" t="str">
         <f t="array" ref="P97">IF(AG97="","",AC97-R97-Q97)</f>
         <v/>
       </c>
@@ -30622,7 +30622,7 @@
         <f>IF(AG97="","",WORKDAY(AG97-AF97+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD97" s="66" t="str" cm="1">
+      <c r="AD97" s="66" cm="1" t="str">
         <f t="array" ref="AD97">IF(AG97="","",$AG97-$AF97)</f>
         <v/>
       </c>
@@ -30670,13 +30670,13 @@
       <c r="C98" s="19"/>
       <c r="D98" s="72"/>
       <c r="E98" s="71"/>
-      <c r="F98" s="82" t="str" cm="1">
+      <c r="F98" s="82" cm="1" t="str">
         <f t="array" ref="F98">IF(AG98="","",I98-H98)</f>
         <v/>
       </c>
       <c r="G98" s="67"/>
       <c r="H98" s="65"/>
-      <c r="I98" s="66" t="str" cm="1">
+      <c r="I98" s="66" cm="1" t="str">
         <f t="array" ref="I98">IF(AG98="","",P98-K98)</f>
         <v/>
       </c>
@@ -30686,7 +30686,7 @@
       <c r="M98" s="68"/>
       <c r="N98" s="68"/>
       <c r="O98" s="68"/>
-      <c r="P98" s="66" t="str" cm="1">
+      <c r="P98" s="66" cm="1" t="str">
         <f t="array" ref="P98">IF(AG98="","",AC98-R98-Q98)</f>
         <v/>
       </c>
@@ -30706,7 +30706,7 @@
         <f>IF(AG98="","",WORKDAY(AG98-AF98+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD98" s="66" t="str" cm="1">
+      <c r="AD98" s="66" cm="1" t="str">
         <f t="array" ref="AD98">IF(AG98="","",$AG98-$AF98)</f>
         <v/>
       </c>
@@ -30754,13 +30754,13 @@
       <c r="C99" s="19"/>
       <c r="D99" s="72"/>
       <c r="E99" s="71"/>
-      <c r="F99" s="82" t="str" cm="1">
+      <c r="F99" s="82" cm="1" t="str">
         <f t="array" ref="F99">IF(AG99="","",I99-H99)</f>
         <v/>
       </c>
       <c r="G99" s="67"/>
       <c r="H99" s="65"/>
-      <c r="I99" s="66" t="str" cm="1">
+      <c r="I99" s="66" cm="1" t="str">
         <f t="array" ref="I99">IF(AG99="","",P99-K99)</f>
         <v/>
       </c>
@@ -30770,7 +30770,7 @@
       <c r="M99" s="68"/>
       <c r="N99" s="68"/>
       <c r="O99" s="68"/>
-      <c r="P99" s="66" t="str" cm="1">
+      <c r="P99" s="66" cm="1" t="str">
         <f t="array" ref="P99">IF(AG99="","",AC99-R99-Q99)</f>
         <v/>
       </c>
@@ -30790,7 +30790,7 @@
         <f>IF(AG99="","",WORKDAY(AG99-AF99+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD99" s="66" t="str" cm="1">
+      <c r="AD99" s="66" cm="1" t="str">
         <f t="array" ref="AD99">IF(AG99="","",$AG99-$AF99)</f>
         <v/>
       </c>
@@ -30838,13 +30838,13 @@
       <c r="C100" s="19"/>
       <c r="D100" s="72"/>
       <c r="E100" s="71"/>
-      <c r="F100" s="82" t="str" cm="1">
+      <c r="F100" s="82" cm="1" t="str">
         <f t="array" ref="F100">IF(AG100="","",I100-H100)</f>
         <v/>
       </c>
       <c r="G100" s="67"/>
       <c r="H100" s="65"/>
-      <c r="I100" s="66" t="str" cm="1">
+      <c r="I100" s="66" cm="1" t="str">
         <f t="array" ref="I100">IF(AG100="","",P100-K100)</f>
         <v/>
       </c>
@@ -30854,7 +30854,7 @@
       <c r="M100" s="68"/>
       <c r="N100" s="68"/>
       <c r="O100" s="68"/>
-      <c r="P100" s="66" t="str" cm="1">
+      <c r="P100" s="66" cm="1" t="str">
         <f t="array" ref="P100">IF(AG100="","",AC100-R100-Q100)</f>
         <v/>
       </c>
@@ -30874,7 +30874,7 @@
         <f>IF(AG100="","",WORKDAY(AG100-AF100+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD100" s="66" t="str" cm="1">
+      <c r="AD100" s="66" cm="1" t="str">
         <f t="array" ref="AD100">IF(AG100="","",$AG100-$AF100)</f>
         <v/>
       </c>
@@ -30922,13 +30922,13 @@
       <c r="C101" s="19"/>
       <c r="D101" s="72"/>
       <c r="E101" s="71"/>
-      <c r="F101" s="82" t="str" cm="1">
+      <c r="F101" s="82" cm="1" t="str">
         <f t="array" ref="F101">IF(AG101="","",I101-H101)</f>
         <v/>
       </c>
       <c r="G101" s="67"/>
       <c r="H101" s="65"/>
-      <c r="I101" s="66" t="str" cm="1">
+      <c r="I101" s="66" cm="1" t="str">
         <f t="array" ref="I101">IF(AG101="","",P101-K101)</f>
         <v/>
       </c>
@@ -30938,7 +30938,7 @@
       <c r="M101" s="68"/>
       <c r="N101" s="68"/>
       <c r="O101" s="68"/>
-      <c r="P101" s="66" t="str" cm="1">
+      <c r="P101" s="66" cm="1" t="str">
         <f t="array" ref="P101">IF(AG101="","",AC101-R101-Q101)</f>
         <v/>
       </c>
@@ -30958,7 +30958,7 @@
         <f>IF(AG101="","",WORKDAY(AG101-AF101+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD101" s="66" t="str" cm="1">
+      <c r="AD101" s="66" cm="1" t="str">
         <f t="array" ref="AD101">IF(AG101="","",$AG101-$AF101)</f>
         <v/>
       </c>
@@ -31006,13 +31006,13 @@
       <c r="C102" s="19"/>
       <c r="D102" s="72"/>
       <c r="E102" s="71"/>
-      <c r="F102" s="82" t="str" cm="1">
+      <c r="F102" s="82" cm="1" t="str">
         <f t="array" ref="F102">IF(AG102="","",I102-H102)</f>
         <v/>
       </c>
       <c r="G102" s="67"/>
       <c r="H102" s="65"/>
-      <c r="I102" s="66" t="str" cm="1">
+      <c r="I102" s="66" cm="1" t="str">
         <f t="array" ref="I102">IF(AG102="","",P102-K102)</f>
         <v/>
       </c>
@@ -31022,7 +31022,7 @@
       <c r="M102" s="68"/>
       <c r="N102" s="68"/>
       <c r="O102" s="68"/>
-      <c r="P102" s="66" t="str" cm="1">
+      <c r="P102" s="66" cm="1" t="str">
         <f t="array" ref="P102">IF(AG102="","",AC102-R102-Q102)</f>
         <v/>
       </c>
@@ -31042,7 +31042,7 @@
         <f>IF(AG102="","",WORKDAY(AG102-AF102+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD102" s="66" t="str" cm="1">
+      <c r="AD102" s="66" cm="1" t="str">
         <f t="array" ref="AD102">IF(AG102="","",$AG102-$AF102)</f>
         <v/>
       </c>
@@ -31090,13 +31090,13 @@
       <c r="C103" s="19"/>
       <c r="D103" s="72"/>
       <c r="E103" s="71"/>
-      <c r="F103" s="82" t="str" cm="1">
+      <c r="F103" s="82" cm="1" t="str">
         <f t="array" ref="F103">IF(AG103="","",I103-H103)</f>
         <v/>
       </c>
       <c r="G103" s="67"/>
       <c r="H103" s="65"/>
-      <c r="I103" s="66" t="str" cm="1">
+      <c r="I103" s="66" cm="1" t="str">
         <f t="array" ref="I103">IF(AG103="","",P103-K103)</f>
         <v/>
       </c>
@@ -31106,7 +31106,7 @@
       <c r="M103" s="68"/>
       <c r="N103" s="68"/>
       <c r="O103" s="68"/>
-      <c r="P103" s="66" t="str" cm="1">
+      <c r="P103" s="66" cm="1" t="str">
         <f t="array" ref="P103">IF(AG103="","",AC103-R103-Q103)</f>
         <v/>
       </c>
@@ -31126,7 +31126,7 @@
         <f>IF(AG103="","",WORKDAY(AG103-AF103+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD103" s="66" t="str" cm="1">
+      <c r="AD103" s="66" cm="1" t="str">
         <f t="array" ref="AD103">IF(AG103="","",$AG103-$AF103)</f>
         <v/>
       </c>
@@ -31174,13 +31174,13 @@
       <c r="C104" s="19"/>
       <c r="D104" s="72"/>
       <c r="E104" s="71"/>
-      <c r="F104" s="82" t="str" cm="1">
+      <c r="F104" s="82" cm="1" t="str">
         <f t="array" ref="F104">IF(AG104="","",I104-H104)</f>
         <v/>
       </c>
       <c r="G104" s="67"/>
       <c r="H104" s="65"/>
-      <c r="I104" s="66" t="str" cm="1">
+      <c r="I104" s="66" cm="1" t="str">
         <f t="array" ref="I104">IF(AG104="","",P104-K104)</f>
         <v/>
       </c>
@@ -31190,7 +31190,7 @@
       <c r="M104" s="68"/>
       <c r="N104" s="68"/>
       <c r="O104" s="68"/>
-      <c r="P104" s="66" t="str" cm="1">
+      <c r="P104" s="66" cm="1" t="str">
         <f t="array" ref="P104">IF(AG104="","",AC104-R104-Q104)</f>
         <v/>
       </c>
@@ -31210,7 +31210,7 @@
         <f>IF(AG104="","",WORKDAY(AG104-AF104+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD104" s="66" t="str" cm="1">
+      <c r="AD104" s="66" cm="1" t="str">
         <f t="array" ref="AD104">IF(AG104="","",$AG104-$AF104)</f>
         <v/>
       </c>
@@ -31258,13 +31258,13 @@
       <c r="C105" s="19"/>
       <c r="D105" s="72"/>
       <c r="E105" s="71"/>
-      <c r="F105" s="82" t="str" cm="1">
+      <c r="F105" s="82" cm="1" t="str">
         <f t="array" ref="F105">IF(AG105="","",I105-H105)</f>
         <v/>
       </c>
       <c r="G105" s="67"/>
       <c r="H105" s="65"/>
-      <c r="I105" s="66" t="str" cm="1">
+      <c r="I105" s="66" cm="1" t="str">
         <f t="array" ref="I105">IF(AG105="","",P105-K105)</f>
         <v/>
       </c>
@@ -31274,7 +31274,7 @@
       <c r="M105" s="68"/>
       <c r="N105" s="68"/>
       <c r="O105" s="68"/>
-      <c r="P105" s="66" t="str" cm="1">
+      <c r="P105" s="66" cm="1" t="str">
         <f t="array" ref="P105">IF(AG105="","",AC105-R105-Q105)</f>
         <v/>
       </c>
@@ -31294,7 +31294,7 @@
         <f>IF(AG105="","",WORKDAY(AG105-AF105+1,-1,{46329,46349,46384,46385,46386,46387,46388,46391,46398,46429,46441,46468}))</f>
         <v/>
       </c>
-      <c r="AD105" s="66" t="str" cm="1">
+      <c r="AD105" s="66" cm="1" t="str">
         <f t="array" ref="AD105">IF(AG105="","",$AG105-$AF105)</f>
         <v/>
       </c>
@@ -31342,13 +31342,13 @@
       <c r="C106" s="19"/>
       <c r="D106" s="72"/>
       <c r="E106" s="71"/>
-      <c r="F106" s="82" t="str" cm="1">
+      <c r="F106" s="82" cm="1" t="str">
         <f t="array" ref="F106">IF(AG106="","",I106-H106)</f>
         <v/>
       </c>
       <c r="G106" s="67"/>
       <c r="H106" s="65"/>
-      <c r="I106" s="66" t="str" cm="1">
+      <c r="I106" s="66" cm="1" t="str">
         <f t="array" ref="I106">IF(AG106="","",P106-K106)</f>
         <v/>
       </c>
@@ -31358,7 +31358,7 @@
       <c r="M106" s="68"/>
       <c r="N106" s="68"/>
       <c r="O106" s="68"/>
-      <c r="P106" s="66" t="str" cm="1">
+      <c r="P106" s="66" cm="1" t="str">
         <f t="array" ref="P106">IF(AG106="","",AC106-R106-Q106)</f>
         <v/>
       </c>
@@ -31423,13 +31423,13 @@
       <c r="C107" s="19"/>
       <c r="D107" s="72"/>
       <c r="E107" s="71"/>
-      <c r="F107" s="82" t="str" cm="1">
+      <c r="F107" s="82" cm="1" t="str">
         <f t="array" ref="F107">IF(AG107="","",I107-H107)</f>
         <v/>
       </c>
       <c r="G107" s="67"/>
       <c r="H107" s="65"/>
-      <c r="I107" s="66" t="str" cm="1">
+      <c r="I107" s="66" cm="1" t="str">
         <f t="array" ref="I107">IF(AG107="","",P107-K107)</f>
         <v/>
       </c>
@@ -31439,7 +31439,7 @@
       <c r="M107" s="68"/>
       <c r="N107" s="68"/>
       <c r="O107" s="68"/>
-      <c r="P107" s="66" t="str" cm="1">
+      <c r="P107" s="66" cm="1" t="str">
         <f t="array" ref="P107">IF(AG107="","",AC107-R107-Q107)</f>
         <v/>
       </c>
@@ -31504,13 +31504,13 @@
       <c r="C108" s="19"/>
       <c r="D108" s="72"/>
       <c r="E108" s="71"/>
-      <c r="F108" s="82" t="str" cm="1">
+      <c r="F108" s="82" cm="1" t="str">
         <f t="array" ref="F108">IF(AG108="","",I108-H108)</f>
         <v/>
       </c>
       <c r="G108" s="67"/>
       <c r="H108" s="65"/>
-      <c r="I108" s="66" t="str" cm="1">
+      <c r="I108" s="66" cm="1" t="str">
         <f t="array" ref="I108">IF(AG108="","",P108-K108)</f>
         <v/>
       </c>
@@ -31520,7 +31520,7 @@
       <c r="M108" s="68"/>
       <c r="N108" s="68"/>
       <c r="O108" s="68"/>
-      <c r="P108" s="66" t="str" cm="1">
+      <c r="P108" s="66" cm="1" t="str">
         <f t="array" ref="P108">IF(AG108="","",AC108-R108-Q108)</f>
         <v/>
       </c>
@@ -31585,13 +31585,13 @@
       <c r="C109" s="19"/>
       <c r="D109" s="72"/>
       <c r="E109" s="71"/>
-      <c r="F109" s="82" t="str" cm="1">
+      <c r="F109" s="82" cm="1" t="str">
         <f t="array" ref="F109">IF(AG109="","",I109-H109)</f>
         <v/>
       </c>
       <c r="G109" s="67"/>
       <c r="H109" s="65"/>
-      <c r="I109" s="66" t="str" cm="1">
+      <c r="I109" s="66" cm="1" t="str">
         <f t="array" ref="I109">IF(AG109="","",P109-K109)</f>
         <v/>
       </c>
@@ -31601,7 +31601,7 @@
       <c r="M109" s="68"/>
       <c r="N109" s="68"/>
       <c r="O109" s="68"/>
-      <c r="P109" s="66" t="str" cm="1">
+      <c r="P109" s="66" cm="1" t="str">
         <f t="array" ref="P109">IF(AG109="","",AC109-R109-Q109)</f>
         <v/>
       </c>
@@ -31666,13 +31666,13 @@
       <c r="C110" s="19"/>
       <c r="D110" s="72"/>
       <c r="E110" s="71"/>
-      <c r="F110" s="82" t="str" cm="1">
+      <c r="F110" s="82" cm="1" t="str">
         <f t="array" ref="F110">IF(AG110="","",I110-H110)</f>
         <v/>
       </c>
       <c r="G110" s="67"/>
       <c r="H110" s="65"/>
-      <c r="I110" s="66" t="str" cm="1">
+      <c r="I110" s="66" cm="1" t="str">
         <f t="array" ref="I110">IF(AG110="","",P110-K110)</f>
         <v/>
       </c>
@@ -31682,7 +31682,7 @@
       <c r="M110" s="68"/>
       <c r="N110" s="68"/>
       <c r="O110" s="68"/>
-      <c r="P110" s="66" t="str" cm="1">
+      <c r="P110" s="66" cm="1" t="str">
         <f t="array" ref="P110">IF(AG110="","",AC110-R110-Q110)</f>
         <v/>
       </c>
@@ -31747,13 +31747,13 @@
       <c r="C111" s="19"/>
       <c r="D111" s="72"/>
       <c r="E111" s="71"/>
-      <c r="F111" s="82" t="str" cm="1">
+      <c r="F111" s="82" cm="1" t="str">
         <f t="array" ref="F111">IF(AG111="","",I111-H111)</f>
         <v/>
       </c>
       <c r="G111" s="67"/>
       <c r="H111" s="65"/>
-      <c r="I111" s="66" t="str" cm="1">
+      <c r="I111" s="66" cm="1" t="str">
         <f t="array" ref="I111">IF(AG111="","",P111-K111)</f>
         <v/>
       </c>
@@ -31763,7 +31763,7 @@
       <c r="M111" s="68"/>
       <c r="N111" s="68"/>
       <c r="O111" s="68"/>
-      <c r="P111" s="66" t="str" cm="1">
+      <c r="P111" s="66" cm="1" t="str">
         <f t="array" ref="P111">IF(AG111="","",AC111-R111-Q111)</f>
         <v/>
       </c>
@@ -31828,13 +31828,13 @@
       <c r="C112" s="19"/>
       <c r="D112" s="72"/>
       <c r="E112" s="71"/>
-      <c r="F112" s="82" t="str" cm="1">
+      <c r="F112" s="82" cm="1" t="str">
         <f t="array" ref="F112">IF(AG112="","",I112-H112)</f>
         <v/>
       </c>
       <c r="G112" s="67"/>
       <c r="H112" s="65"/>
-      <c r="I112" s="66" t="str" cm="1">
+      <c r="I112" s="66" cm="1" t="str">
         <f t="array" ref="I112">IF(AG112="","",P112-K112)</f>
         <v/>
       </c>
@@ -31844,7 +31844,7 @@
       <c r="M112" s="68"/>
       <c r="N112" s="68"/>
       <c r="O112" s="68"/>
-      <c r="P112" s="66" t="str" cm="1">
+      <c r="P112" s="66" cm="1" t="str">
         <f t="array" ref="P112">IF(AG112="","",AC112-R112-Q112)</f>
         <v/>
       </c>
@@ -31909,13 +31909,13 @@
       <c r="C113" s="19"/>
       <c r="D113" s="72"/>
       <c r="E113" s="71"/>
-      <c r="F113" s="82" t="str" cm="1">
+      <c r="F113" s="82" cm="1" t="str">
         <f t="array" ref="F113">IF(AG113="","",I113-H113)</f>
         <v/>
       </c>
       <c r="G113" s="67"/>
       <c r="H113" s="65"/>
-      <c r="I113" s="66" t="str" cm="1">
+      <c r="I113" s="66" cm="1" t="str">
         <f t="array" ref="I113">IF(AG113="","",P113-K113)</f>
         <v/>
       </c>
@@ -31925,7 +31925,7 @@
       <c r="M113" s="68"/>
       <c r="N113" s="68"/>
       <c r="O113" s="68"/>
-      <c r="P113" s="66" t="str" cm="1">
+      <c r="P113" s="66" cm="1" t="str">
         <f t="array" ref="P113">IF(AG113="","",AC113-R113-Q113)</f>
         <v/>
       </c>
@@ -31990,13 +31990,13 @@
       <c r="C114" s="19"/>
       <c r="D114" s="72"/>
       <c r="E114" s="71"/>
-      <c r="F114" s="82" t="str" cm="1">
+      <c r="F114" s="82" cm="1" t="str">
         <f t="array" ref="F114">IF(AG114="","",I114-H114)</f>
         <v/>
       </c>
       <c r="G114" s="67"/>
       <c r="H114" s="65"/>
-      <c r="I114" s="66" t="str" cm="1">
+      <c r="I114" s="66" cm="1" t="str">
         <f t="array" ref="I114">IF(AG114="","",P114-K114)</f>
         <v/>
       </c>
@@ -32006,7 +32006,7 @@
       <c r="M114" s="68"/>
       <c r="N114" s="68"/>
       <c r="O114" s="68"/>
-      <c r="P114" s="66" t="str" cm="1">
+      <c r="P114" s="66" cm="1" t="str">
         <f t="array" ref="P114">IF(AG114="","",AC114-R114-Q114)</f>
         <v/>
       </c>
@@ -32071,13 +32071,13 @@
       <c r="C115" s="19"/>
       <c r="D115" s="72"/>
       <c r="E115" s="71"/>
-      <c r="F115" s="82" t="str" cm="1">
+      <c r="F115" s="82" cm="1" t="str">
         <f t="array" ref="F115">IF(AG115="","",I115-H115)</f>
         <v/>
       </c>
       <c r="G115" s="67"/>
       <c r="H115" s="65"/>
-      <c r="I115" s="66" t="str" cm="1">
+      <c r="I115" s="66" cm="1" t="str">
         <f t="array" ref="I115">IF(AG115="","",P115-K115)</f>
         <v/>
       </c>
@@ -32087,7 +32087,7 @@
       <c r="M115" s="68"/>
       <c r="N115" s="68"/>
       <c r="O115" s="68"/>
-      <c r="P115" s="66" t="str" cm="1">
+      <c r="P115" s="66" cm="1" t="str">
         <f t="array" ref="P115">IF(AG115="","",AC115-R115-Q115)</f>
         <v/>
       </c>
@@ -32152,13 +32152,13 @@
       <c r="C116" s="19"/>
       <c r="D116" s="72"/>
       <c r="E116" s="71"/>
-      <c r="F116" s="82" t="str" cm="1">
+      <c r="F116" s="82" cm="1" t="str">
         <f t="array" ref="F116">IF(AG116="","",I116-H116)</f>
         <v/>
       </c>
       <c r="G116" s="67"/>
       <c r="H116" s="65"/>
-      <c r="I116" s="66" t="str" cm="1">
+      <c r="I116" s="66" cm="1" t="str">
         <f t="array" ref="I116">IF(AG116="","",P116-K116)</f>
         <v/>
       </c>
@@ -32168,7 +32168,7 @@
       <c r="M116" s="68"/>
       <c r="N116" s="68"/>
       <c r="O116" s="68"/>
-      <c r="P116" s="66" t="str" cm="1">
+      <c r="P116" s="66" cm="1" t="str">
         <f t="array" ref="P116">IF(AG116="","",AC116-R116-Q116)</f>
         <v/>
       </c>
@@ -32233,13 +32233,13 @@
       <c r="C117" s="19"/>
       <c r="D117" s="72"/>
       <c r="E117" s="71"/>
-      <c r="F117" s="82" t="str" cm="1">
+      <c r="F117" s="82" cm="1" t="str">
         <f t="array" ref="F117">IF(AG117="","",I117-H117)</f>
         <v/>
       </c>
       <c r="G117" s="67"/>
       <c r="H117" s="65"/>
-      <c r="I117" s="66" t="str" cm="1">
+      <c r="I117" s="66" cm="1" t="str">
         <f t="array" ref="I117">IF(AG117="","",P117-K117)</f>
         <v/>
       </c>
@@ -32249,7 +32249,7 @@
       <c r="M117" s="68"/>
       <c r="N117" s="68"/>
       <c r="O117" s="68"/>
-      <c r="P117" s="66" t="str" cm="1">
+      <c r="P117" s="66" cm="1" t="str">
         <f t="array" ref="P117">IF(AG117="","",AC117-R117-Q117)</f>
         <v/>
       </c>
@@ -32314,13 +32314,13 @@
       <c r="C118" s="19"/>
       <c r="D118" s="72"/>
       <c r="E118" s="71"/>
-      <c r="F118" s="82" t="str" cm="1">
+      <c r="F118" s="82" cm="1" t="str">
         <f t="array" ref="F118">IF(AG118="","",I118-H118)</f>
         <v/>
       </c>
       <c r="G118" s="67"/>
       <c r="H118" s="65"/>
-      <c r="I118" s="66" t="str" cm="1">
+      <c r="I118" s="66" cm="1" t="str">
         <f t="array" ref="I118">IF(AG118="","",P118-K118)</f>
         <v/>
       </c>
@@ -32330,7 +32330,7 @@
       <c r="M118" s="68"/>
       <c r="N118" s="68"/>
       <c r="O118" s="68"/>
-      <c r="P118" s="66" t="str" cm="1">
+      <c r="P118" s="66" cm="1" t="str">
         <f t="array" ref="P118">IF(AG118="","",AC118-R118-Q118)</f>
         <v/>
       </c>
@@ -32395,13 +32395,13 @@
       <c r="C119" s="19"/>
       <c r="D119" s="72"/>
       <c r="E119" s="71"/>
-      <c r="F119" s="82" t="str" cm="1">
+      <c r="F119" s="82" cm="1" t="str">
         <f t="array" ref="F119">IF(AG119="","",I119-H119)</f>
         <v/>
       </c>
       <c r="G119" s="67"/>
       <c r="H119" s="65"/>
-      <c r="I119" s="66" t="str" cm="1">
+      <c r="I119" s="66" cm="1" t="str">
         <f t="array" ref="I119">IF(AG119="","",P119-K119)</f>
         <v/>
       </c>
@@ -32411,7 +32411,7 @@
       <c r="M119" s="68"/>
       <c r="N119" s="68"/>
       <c r="O119" s="68"/>
-      <c r="P119" s="66" t="str" cm="1">
+      <c r="P119" s="66" cm="1" t="str">
         <f t="array" ref="P119">IF(AG119="","",AC119-R119-Q119)</f>
         <v/>
       </c>
@@ -32476,13 +32476,13 @@
       <c r="C120" s="19"/>
       <c r="D120" s="72"/>
       <c r="E120" s="71"/>
-      <c r="F120" s="82" t="str" cm="1">
+      <c r="F120" s="82" cm="1" t="str">
         <f t="array" ref="F120">IF(AG120="","",I120-H120)</f>
         <v/>
       </c>
       <c r="G120" s="67"/>
       <c r="H120" s="65"/>
-      <c r="I120" s="66" t="str" cm="1">
+      <c r="I120" s="66" cm="1" t="str">
         <f t="array" ref="I120">IF(AG120="","",P120-K120)</f>
         <v/>
       </c>
@@ -32492,7 +32492,7 @@
       <c r="M120" s="68"/>
       <c r="N120" s="68"/>
       <c r="O120" s="68"/>
-      <c r="P120" s="66" t="str" cm="1">
+      <c r="P120" s="66" cm="1" t="str">
         <f t="array" ref="P120">IF(AG120="","",AC120-R120-Q120)</f>
         <v/>
       </c>
@@ -32557,13 +32557,13 @@
       <c r="C121" s="19"/>
       <c r="D121" s="72"/>
       <c r="E121" s="71"/>
-      <c r="F121" s="82" t="str" cm="1">
+      <c r="F121" s="82" cm="1" t="str">
         <f t="array" ref="F121">IF(AG121="","",I121-H121)</f>
         <v/>
       </c>
       <c r="G121" s="67"/>
       <c r="H121" s="65"/>
-      <c r="I121" s="66" t="str" cm="1">
+      <c r="I121" s="66" cm="1" t="str">
         <f t="array" ref="I121">IF(AG121="","",P121-K121)</f>
         <v/>
       </c>
@@ -32573,7 +32573,7 @@
       <c r="M121" s="68"/>
       <c r="N121" s="68"/>
       <c r="O121" s="68"/>
-      <c r="P121" s="66" t="str" cm="1">
+      <c r="P121" s="66" cm="1" t="str">
         <f t="array" ref="P121">IF(AG121="","",AC121-R121-Q121)</f>
         <v/>
       </c>
@@ -32638,13 +32638,13 @@
       <c r="C122" s="19"/>
       <c r="D122" s="72"/>
       <c r="E122" s="71"/>
-      <c r="F122" s="82" t="str" cm="1">
+      <c r="F122" s="82" cm="1" t="str">
         <f t="array" ref="F122">IF(AG122="","",I122-H122)</f>
         <v/>
       </c>
       <c r="G122" s="67"/>
       <c r="H122" s="65"/>
-      <c r="I122" s="66" t="str" cm="1">
+      <c r="I122" s="66" cm="1" t="str">
         <f t="array" ref="I122">IF(AG122="","",P122-K122)</f>
         <v/>
       </c>
@@ -32654,7 +32654,7 @@
       <c r="M122" s="68"/>
       <c r="N122" s="68"/>
       <c r="O122" s="68"/>
-      <c r="P122" s="66" t="str" cm="1">
+      <c r="P122" s="66" cm="1" t="str">
         <f t="array" ref="P122">IF(AG122="","",AC122-R122-Q122)</f>
         <v/>
       </c>
@@ -32719,13 +32719,13 @@
       <c r="C123" s="19"/>
       <c r="D123" s="72"/>
       <c r="E123" s="71"/>
-      <c r="F123" s="82" t="str" cm="1">
+      <c r="F123" s="82" cm="1" t="str">
         <f t="array" ref="F123">IF(AG123="","",I123-H123)</f>
         <v/>
       </c>
       <c r="G123" s="67"/>
       <c r="H123" s="65"/>
-      <c r="I123" s="66" t="str" cm="1">
+      <c r="I123" s="66" cm="1" t="str">
         <f t="array" ref="I123">IF(AG123="","",P123-K123)</f>
         <v/>
       </c>
@@ -32735,7 +32735,7 @@
       <c r="M123" s="68"/>
       <c r="N123" s="68"/>
       <c r="O123" s="68"/>
-      <c r="P123" s="66" t="str" cm="1">
+      <c r="P123" s="66" cm="1" t="str">
         <f t="array" ref="P123">IF(AG123="","",AC123-R123-Q123)</f>
         <v/>
       </c>
@@ -32800,13 +32800,13 @@
       <c r="C124" s="19"/>
       <c r="D124" s="72"/>
       <c r="E124" s="71"/>
-      <c r="F124" s="82" t="str" cm="1">
+      <c r="F124" s="82" cm="1" t="str">
         <f t="array" ref="F124">IF(AG124="","",I124-H124)</f>
         <v/>
       </c>
       <c r="G124" s="67"/>
       <c r="H124" s="65"/>
-      <c r="I124" s="66" t="str" cm="1">
+      <c r="I124" s="66" cm="1" t="str">
         <f t="array" ref="I124">IF(AG124="","",P124-K124)</f>
         <v/>
       </c>
@@ -32816,7 +32816,7 @@
       <c r="M124" s="68"/>
       <c r="N124" s="68"/>
       <c r="O124" s="68"/>
-      <c r="P124" s="66" t="str" cm="1">
+      <c r="P124" s="66" cm="1" t="str">
         <f t="array" ref="P124">IF(AG124="","",AC124-R124-Q124)</f>
         <v/>
       </c>
@@ -32881,13 +32881,13 @@
       <c r="C125" s="19"/>
       <c r="D125" s="72"/>
       <c r="E125" s="71"/>
-      <c r="F125" s="82" t="str" cm="1">
+      <c r="F125" s="82" cm="1" t="str">
         <f t="array" ref="F125">IF(AG125="","",I125-H125)</f>
         <v/>
       </c>
       <c r="G125" s="67"/>
       <c r="H125" s="65"/>
-      <c r="I125" s="66" t="str" cm="1">
+      <c r="I125" s="66" cm="1" t="str">
         <f t="array" ref="I125">IF(AG125="","",P125-K125)</f>
         <v/>
       </c>
@@ -32897,7 +32897,7 @@
       <c r="M125" s="68"/>
       <c r="N125" s="68"/>
       <c r="O125" s="68"/>
-      <c r="P125" s="66" t="str" cm="1">
+      <c r="P125" s="66" cm="1" t="str">
         <f t="array" ref="P125">IF(AG125="","",AC125-R125-Q125)</f>
         <v/>
       </c>
@@ -32962,13 +32962,13 @@
       <c r="C126" s="19"/>
       <c r="D126" s="72"/>
       <c r="E126" s="71"/>
-      <c r="F126" s="82" t="str" cm="1">
+      <c r="F126" s="82" cm="1" t="str">
         <f t="array" ref="F126">IF(AG126="","",I126-H126)</f>
         <v/>
       </c>
       <c r="G126" s="67"/>
       <c r="H126" s="65"/>
-      <c r="I126" s="66" t="str" cm="1">
+      <c r="I126" s="66" cm="1" t="str">
         <f t="array" ref="I126">IF(AG126="","",P126-K126)</f>
         <v/>
       </c>
@@ -32978,7 +32978,7 @@
       <c r="M126" s="68"/>
       <c r="N126" s="68"/>
       <c r="O126" s="68"/>
-      <c r="P126" s="66" t="str" cm="1">
+      <c r="P126" s="66" cm="1" t="str">
         <f t="array" ref="P126">IF(AG126="","",AC126-R126-Q126)</f>
         <v/>
       </c>
@@ -33043,13 +33043,13 @@
       <c r="C127" s="19"/>
       <c r="D127" s="72"/>
       <c r="E127" s="71"/>
-      <c r="F127" s="82" t="str" cm="1">
+      <c r="F127" s="82" cm="1" t="str">
         <f t="array" ref="F127">IF(AG127="","",I127-H127)</f>
         <v/>
       </c>
       <c r="G127" s="67"/>
       <c r="H127" s="65"/>
-      <c r="I127" s="66" t="str" cm="1">
+      <c r="I127" s="66" cm="1" t="str">
         <f t="array" ref="I127">IF(AG127="","",P127-K127)</f>
         <v/>
       </c>
@@ -33059,7 +33059,7 @@
       <c r="M127" s="68"/>
       <c r="N127" s="68"/>
       <c r="O127" s="68"/>
-      <c r="P127" s="66" t="str" cm="1">
+      <c r="P127" s="66" cm="1" t="str">
         <f t="array" ref="P127">IF(AG127="","",AC127-R127-Q127)</f>
         <v/>
       </c>
@@ -33124,13 +33124,13 @@
       <c r="C128" s="19"/>
       <c r="D128" s="72"/>
       <c r="E128" s="71"/>
-      <c r="F128" s="82" t="str" cm="1">
+      <c r="F128" s="82" cm="1" t="str">
         <f t="array" ref="F128">IF(AG128="","",I128-H128)</f>
         <v/>
       </c>
       <c r="G128" s="67"/>
       <c r="H128" s="65"/>
-      <c r="I128" s="66" t="str" cm="1">
+      <c r="I128" s="66" cm="1" t="str">
         <f t="array" ref="I128">IF(AG128="","",P128-K128)</f>
         <v/>
       </c>
@@ -33140,7 +33140,7 @@
       <c r="M128" s="68"/>
       <c r="N128" s="68"/>
       <c r="O128" s="68"/>
-      <c r="P128" s="66" t="str" cm="1">
+      <c r="P128" s="66" cm="1" t="str">
         <f t="array" ref="P128">IF(AG128="","",AC128-R128-Q128)</f>
         <v/>
       </c>
@@ -33205,13 +33205,13 @@
       <c r="C129" s="19"/>
       <c r="D129" s="72"/>
       <c r="E129" s="71"/>
-      <c r="F129" s="82" t="str" cm="1">
+      <c r="F129" s="82" cm="1" t="str">
         <f t="array" ref="F129">IF(AG129="","",I129-H129)</f>
         <v/>
       </c>
       <c r="G129" s="67"/>
       <c r="H129" s="65"/>
-      <c r="I129" s="66" t="str" cm="1">
+      <c r="I129" s="66" cm="1" t="str">
         <f t="array" ref="I129">IF(AG129="","",P129-K129)</f>
         <v/>
       </c>
@@ -33221,7 +33221,7 @@
       <c r="M129" s="68"/>
       <c r="N129" s="68"/>
       <c r="O129" s="68"/>
-      <c r="P129" s="66" t="str" cm="1">
+      <c r="P129" s="66" cm="1" t="str">
         <f t="array" ref="P129">IF(AG129="","",AC129-R129-Q129)</f>
         <v/>
       </c>
@@ -33286,13 +33286,13 @@
       <c r="C130" s="19"/>
       <c r="D130" s="72"/>
       <c r="E130" s="71"/>
-      <c r="F130" s="82" t="str" cm="1">
+      <c r="F130" s="82" cm="1" t="str">
         <f t="array" ref="F130">IF(AG130="","",I130-H130)</f>
         <v/>
       </c>
       <c r="G130" s="67"/>
       <c r="H130" s="65"/>
-      <c r="I130" s="66" t="str" cm="1">
+      <c r="I130" s="66" cm="1" t="str">
         <f t="array" ref="I130">IF(AG130="","",P130-K130)</f>
         <v/>
       </c>
@@ -33302,7 +33302,7 @@
       <c r="M130" s="68"/>
       <c r="N130" s="68"/>
       <c r="O130" s="68"/>
-      <c r="P130" s="66" t="str" cm="1">
+      <c r="P130" s="66" cm="1" t="str">
         <f t="array" ref="P130">IF(AG130="","",AC130-R130-Q130)</f>
         <v/>
       </c>
@@ -33367,13 +33367,13 @@
       <c r="C131" s="19"/>
       <c r="D131" s="72"/>
       <c r="E131" s="71"/>
-      <c r="F131" s="82" t="str" cm="1">
+      <c r="F131" s="82" cm="1" t="str">
         <f t="array" ref="F131">IF(AG131="","",I131-H131)</f>
         <v/>
       </c>
       <c r="G131" s="67"/>
       <c r="H131" s="65"/>
-      <c r="I131" s="66" t="str" cm="1">
+      <c r="I131" s="66" cm="1" t="str">
         <f t="array" ref="I131">IF(AG131="","",P131-K131)</f>
         <v/>
       </c>
@@ -33383,7 +33383,7 @@
       <c r="M131" s="68"/>
       <c r="N131" s="68"/>
       <c r="O131" s="68"/>
-      <c r="P131" s="66" t="str" cm="1">
+      <c r="P131" s="66" cm="1" t="str">
         <f t="array" ref="P131">IF(AG131="","",AC131-R131-Q131)</f>
         <v/>
       </c>
@@ -33448,13 +33448,13 @@
       <c r="C132" s="19"/>
       <c r="D132" s="72"/>
       <c r="E132" s="71"/>
-      <c r="F132" s="82" t="str" cm="1">
+      <c r="F132" s="82" cm="1" t="str">
         <f t="array" ref="F132">IF(AG132="","",I132-H132)</f>
         <v/>
       </c>
       <c r="G132" s="67"/>
       <c r="H132" s="65"/>
-      <c r="I132" s="66" t="str" cm="1">
+      <c r="I132" s="66" cm="1" t="str">
         <f t="array" ref="I132">IF(AG132="","",P132-K132)</f>
         <v/>
       </c>
@@ -33464,7 +33464,7 @@
       <c r="M132" s="68"/>
       <c r="N132" s="68"/>
       <c r="O132" s="68"/>
-      <c r="P132" s="66" t="str" cm="1">
+      <c r="P132" s="66" cm="1" t="str">
         <f t="array" ref="P132">IF(AG132="","",AC132-R132-Q132)</f>
         <v/>
       </c>
@@ -33529,13 +33529,13 @@
       <c r="C133" s="19"/>
       <c r="D133" s="72"/>
       <c r="E133" s="71"/>
-      <c r="F133" s="82" t="str" cm="1">
+      <c r="F133" s="82" cm="1" t="str">
         <f t="array" ref="F133">IF(AG133="","",I133-H133)</f>
         <v/>
       </c>
       <c r="G133" s="67"/>
       <c r="H133" s="65"/>
-      <c r="I133" s="66" t="str" cm="1">
+      <c r="I133" s="66" cm="1" t="str">
         <f t="array" ref="I133">IF(AG133="","",P133-K133)</f>
         <v/>
       </c>
@@ -33545,7 +33545,7 @@
       <c r="M133" s="68"/>
       <c r="N133" s="68"/>
       <c r="O133" s="68"/>
-      <c r="P133" s="66" t="str" cm="1">
+      <c r="P133" s="66" cm="1" t="str">
         <f t="array" ref="P133">IF(AG133="","",AC133-R133-Q133)</f>
         <v/>
       </c>
@@ -33610,13 +33610,13 @@
       <c r="C134" s="19"/>
       <c r="D134" s="72"/>
       <c r="E134" s="71"/>
-      <c r="F134" s="82" t="str" cm="1">
+      <c r="F134" s="82" cm="1" t="str">
         <f t="array" ref="F134">IF(AG134="","",I134-H134)</f>
         <v/>
       </c>
       <c r="G134" s="67"/>
       <c r="H134" s="65"/>
-      <c r="I134" s="66" t="str" cm="1">
+      <c r="I134" s="66" cm="1" t="str">
         <f t="array" ref="I134">IF(AG134="","",P134-K134)</f>
         <v/>
       </c>
@@ -33626,7 +33626,7 @@
       <c r="M134" s="68"/>
       <c r="N134" s="68"/>
       <c r="O134" s="68"/>
-      <c r="P134" s="66" t="str" cm="1">
+      <c r="P134" s="66" cm="1" t="str">
         <f t="array" ref="P134">IF(AG134="","",AC134-R134-Q134)</f>
         <v/>
       </c>
@@ -33691,13 +33691,13 @@
       <c r="C135" s="19"/>
       <c r="D135" s="72"/>
       <c r="E135" s="71"/>
-      <c r="F135" s="82" t="str" cm="1">
+      <c r="F135" s="82" cm="1" t="str">
         <f t="array" ref="F135">IF(AG135="","",I135-H135)</f>
         <v/>
       </c>
       <c r="G135" s="67"/>
       <c r="H135" s="65"/>
-      <c r="I135" s="66" t="str" cm="1">
+      <c r="I135" s="66" cm="1" t="str">
         <f t="array" ref="I135">IF(AG135="","",P135-K135)</f>
         <v/>
       </c>
@@ -33707,7 +33707,7 @@
       <c r="M135" s="68"/>
       <c r="N135" s="68"/>
       <c r="O135" s="68"/>
-      <c r="P135" s="66" t="str" cm="1">
+      <c r="P135" s="66" cm="1" t="str">
         <f t="array" ref="P135">IF(AG135="","",AC135-R135-Q135)</f>
         <v/>
       </c>
@@ -33772,13 +33772,13 @@
       <c r="C136" s="19"/>
       <c r="D136" s="72"/>
       <c r="E136" s="71"/>
-      <c r="F136" s="82" t="str" cm="1">
+      <c r="F136" s="82" cm="1" t="str">
         <f t="array" ref="F136">IF(AG136="","",I136-H136)</f>
         <v/>
       </c>
       <c r="G136" s="67"/>
       <c r="H136" s="65"/>
-      <c r="I136" s="66" t="str" cm="1">
+      <c r="I136" s="66" cm="1" t="str">
         <f t="array" ref="I136">IF(AG136="","",P136-K136)</f>
         <v/>
       </c>
@@ -33788,7 +33788,7 @@
       <c r="M136" s="68"/>
       <c r="N136" s="68"/>
       <c r="O136" s="68"/>
-      <c r="P136" s="66" t="str" cm="1">
+      <c r="P136" s="66" cm="1" t="str">
         <f t="array" ref="P136">IF(AG136="","",AC136-R136-Q136)</f>
         <v/>
       </c>
@@ -33853,13 +33853,13 @@
       <c r="C137" s="19"/>
       <c r="D137" s="72"/>
       <c r="E137" s="71"/>
-      <c r="F137" s="82" t="str" cm="1">
+      <c r="F137" s="82" cm="1" t="str">
         <f t="array" ref="F137">IF(AG137="","",I137-H137)</f>
         <v/>
       </c>
       <c r="G137" s="67"/>
       <c r="H137" s="65"/>
-      <c r="I137" s="66" t="str" cm="1">
+      <c r="I137" s="66" cm="1" t="str">
         <f t="array" ref="I137">IF(AG137="","",P137-K137)</f>
         <v/>
       </c>
@@ -33869,7 +33869,7 @@
       <c r="M137" s="68"/>
       <c r="N137" s="68"/>
       <c r="O137" s="68"/>
-      <c r="P137" s="66" t="str" cm="1">
+      <c r="P137" s="66" cm="1" t="str">
         <f t="array" ref="P137">IF(AG137="","",AC137-R137-Q137)</f>
         <v/>
       </c>
@@ -33934,13 +33934,13 @@
       <c r="C138" s="19"/>
       <c r="D138" s="72"/>
       <c r="E138" s="71"/>
-      <c r="F138" s="82" t="str" cm="1">
+      <c r="F138" s="82" cm="1" t="str">
         <f t="array" ref="F138">IF(AG138="","",I138-H138)</f>
         <v/>
       </c>
       <c r="G138" s="67"/>
       <c r="H138" s="65"/>
-      <c r="I138" s="66" t="str" cm="1">
+      <c r="I138" s="66" cm="1" t="str">
         <f t="array" ref="I138">IF(AG138="","",P138-K138)</f>
         <v/>
       </c>
@@ -33950,7 +33950,7 @@
       <c r="M138" s="68"/>
       <c r="N138" s="68"/>
       <c r="O138" s="68"/>
-      <c r="P138" s="66" t="str" cm="1">
+      <c r="P138" s="66" cm="1" t="str">
         <f t="array" ref="P138">IF(AG138="","",AC138-R138-Q138)</f>
         <v/>
       </c>
@@ -34015,13 +34015,13 @@
       <c r="C139" s="19"/>
       <c r="D139" s="72"/>
       <c r="E139" s="71"/>
-      <c r="F139" s="82" t="str" cm="1">
+      <c r="F139" s="82" cm="1" t="str">
         <f t="array" ref="F139">IF(AG139="","",I139-H139)</f>
         <v/>
       </c>
       <c r="G139" s="67"/>
       <c r="H139" s="65"/>
-      <c r="I139" s="66" t="str" cm="1">
+      <c r="I139" s="66" cm="1" t="str">
         <f t="array" ref="I139">IF(AG139="","",P139-K139)</f>
         <v/>
       </c>
@@ -34031,7 +34031,7 @@
       <c r="M139" s="68"/>
       <c r="N139" s="68"/>
       <c r="O139" s="68"/>
-      <c r="P139" s="66" t="str" cm="1">
+      <c r="P139" s="66" cm="1" t="str">
         <f t="array" ref="P139">IF(AG139="","",AC139-R139-Q139)</f>
         <v/>
       </c>
@@ -34096,13 +34096,13 @@
       <c r="C140" s="19"/>
       <c r="D140" s="72"/>
       <c r="E140" s="71"/>
-      <c r="F140" s="82" t="str" cm="1">
+      <c r="F140" s="82" cm="1" t="str">
         <f t="array" ref="F140">IF(AG140="","",I140-H140)</f>
         <v/>
       </c>
       <c r="G140" s="67"/>
       <c r="H140" s="65"/>
-      <c r="I140" s="66" t="str" cm="1">
+      <c r="I140" s="66" cm="1" t="str">
         <f t="array" ref="I140">IF(AG140="","",P140-K140)</f>
         <v/>
       </c>
@@ -34112,7 +34112,7 @@
       <c r="M140" s="68"/>
       <c r="N140" s="68"/>
       <c r="O140" s="68"/>
-      <c r="P140" s="66" t="str" cm="1">
+      <c r="P140" s="66" cm="1" t="str">
         <f t="array" ref="P140">IF(AG140="","",AC140-R140-Q140)</f>
         <v/>
       </c>
@@ -34177,13 +34177,13 @@
       <c r="C141" s="19"/>
       <c r="D141" s="72"/>
       <c r="E141" s="71"/>
-      <c r="F141" s="82" t="str" cm="1">
+      <c r="F141" s="82" cm="1" t="str">
         <f t="array" ref="F141">IF(AG141="","",I141-H141)</f>
         <v/>
       </c>
       <c r="G141" s="67"/>
       <c r="H141" s="65"/>
-      <c r="I141" s="66" t="str" cm="1">
+      <c r="I141" s="66" cm="1" t="str">
         <f t="array" ref="I141">IF(AG141="","",P141-K141)</f>
         <v/>
       </c>
@@ -34193,7 +34193,7 @@
       <c r="M141" s="68"/>
       <c r="N141" s="68"/>
       <c r="O141" s="68"/>
-      <c r="P141" s="66" t="str" cm="1">
+      <c r="P141" s="66" cm="1" t="str">
         <f t="array" ref="P141">IF(AG141="","",AC141-R141-Q141)</f>
         <v/>
       </c>
@@ -34258,13 +34258,13 @@
       <c r="C142" s="19"/>
       <c r="D142" s="72"/>
       <c r="E142" s="71"/>
-      <c r="F142" s="82" t="str" cm="1">
+      <c r="F142" s="82" cm="1" t="str">
         <f t="array" ref="F142">IF(AG142="","",I142-H142)</f>
         <v/>
       </c>
       <c r="G142" s="67"/>
       <c r="H142" s="65"/>
-      <c r="I142" s="66" t="str" cm="1">
+      <c r="I142" s="66" cm="1" t="str">
         <f t="array" ref="I142">IF(AG142="","",P142-K142)</f>
         <v/>
       </c>
@@ -34274,7 +34274,7 @@
       <c r="M142" s="68"/>
       <c r="N142" s="68"/>
       <c r="O142" s="68"/>
-      <c r="P142" s="66" t="str" cm="1">
+      <c r="P142" s="66" cm="1" t="str">
         <f t="array" ref="P142">IF(AG142="","",AC142-R142-Q142)</f>
         <v/>
       </c>
@@ -34339,13 +34339,13 @@
       <c r="C143" s="19"/>
       <c r="D143" s="72"/>
       <c r="E143" s="71"/>
-      <c r="F143" s="82" t="str" cm="1">
+      <c r="F143" s="82" cm="1" t="str">
         <f t="array" ref="F143">IF(AG143="","",I143-H143)</f>
         <v/>
       </c>
       <c r="G143" s="67"/>
       <c r="H143" s="65"/>
-      <c r="I143" s="66" t="str" cm="1">
+      <c r="I143" s="66" cm="1" t="str">
         <f t="array" ref="I143">IF(AG143="","",P143-K143)</f>
         <v/>
       </c>
@@ -34355,7 +34355,7 @@
       <c r="M143" s="68"/>
       <c r="N143" s="68"/>
       <c r="O143" s="68"/>
-      <c r="P143" s="66" t="str" cm="1">
+      <c r="P143" s="66" cm="1" t="str">
         <f t="array" ref="P143">IF(AG143="","",AC143-R143-Q143)</f>
         <v/>
       </c>
@@ -34420,13 +34420,13 @@
       <c r="C144" s="19"/>
       <c r="D144" s="72"/>
       <c r="E144" s="71"/>
-      <c r="F144" s="82" t="str" cm="1">
+      <c r="F144" s="82" cm="1" t="str">
         <f t="array" ref="F144">IF(AG144="","",I144-H144)</f>
         <v/>
       </c>
       <c r="G144" s="67"/>
       <c r="H144" s="65"/>
-      <c r="I144" s="66" t="str" cm="1">
+      <c r="I144" s="66" cm="1" t="str">
         <f t="array" ref="I144">IF(AG144="","",P144-K144)</f>
         <v/>
       </c>
@@ -34436,7 +34436,7 @@
       <c r="M144" s="68"/>
       <c r="N144" s="68"/>
       <c r="O144" s="68"/>
-      <c r="P144" s="66" t="str" cm="1">
+      <c r="P144" s="66" cm="1" t="str">
         <f t="array" ref="P144">IF(AG144="","",AC144-R144-Q144)</f>
         <v/>
       </c>
@@ -34501,13 +34501,13 @@
       <c r="C145" s="19"/>
       <c r="D145" s="72"/>
       <c r="E145" s="71"/>
-      <c r="F145" s="82" t="str" cm="1">
+      <c r="F145" s="82" cm="1" t="str">
         <f t="array" ref="F145">IF(AG145="","",I145-H145)</f>
         <v/>
       </c>
       <c r="G145" s="67"/>
       <c r="H145" s="65"/>
-      <c r="I145" s="66" t="str" cm="1">
+      <c r="I145" s="66" cm="1" t="str">
         <f t="array" ref="I145">IF(AG145="","",P145-K145)</f>
         <v/>
       </c>
@@ -34517,7 +34517,7 @@
       <c r="M145" s="68"/>
       <c r="N145" s="68"/>
       <c r="O145" s="68"/>
-      <c r="P145" s="66" t="str" cm="1">
+      <c r="P145" s="66" cm="1" t="str">
         <f t="array" ref="P145">IF(AG145="","",AC145-R145-Q145)</f>
         <v/>
       </c>
@@ -34582,13 +34582,13 @@
       <c r="C146" s="19"/>
       <c r="D146" s="72"/>
       <c r="E146" s="71"/>
-      <c r="F146" s="82" t="str" cm="1">
+      <c r="F146" s="82" cm="1" t="str">
         <f t="array" ref="F146">IF(AG146="","",I146-H146)</f>
         <v/>
       </c>
       <c r="G146" s="67"/>
       <c r="H146" s="65"/>
-      <c r="I146" s="66" t="str" cm="1">
+      <c r="I146" s="66" cm="1" t="str">
         <f t="array" ref="I146">IF(AG146="","",P146-K146)</f>
         <v/>
       </c>
@@ -34598,7 +34598,7 @@
       <c r="M146" s="68"/>
       <c r="N146" s="68"/>
       <c r="O146" s="68"/>
-      <c r="P146" s="66" t="str" cm="1">
+      <c r="P146" s="66" cm="1" t="str">
         <f t="array" ref="P146">IF(AG146="","",AC146-R146-Q146)</f>
         <v/>
       </c>
@@ -34663,13 +34663,13 @@
       <c r="C147" s="19"/>
       <c r="D147" s="72"/>
       <c r="E147" s="71"/>
-      <c r="F147" s="82" t="str" cm="1">
+      <c r="F147" s="82" cm="1" t="str">
         <f t="array" ref="F147">IF(AG147="","",I147-H147)</f>
         <v/>
       </c>
       <c r="G147" s="67"/>
       <c r="H147" s="65"/>
-      <c r="I147" s="66" t="str" cm="1">
+      <c r="I147" s="66" cm="1" t="str">
         <f t="array" ref="I147">IF(AG147="","",P147-K147)</f>
         <v/>
       </c>
@@ -34679,7 +34679,7 @@
       <c r="M147" s="68"/>
       <c r="N147" s="68"/>
       <c r="O147" s="68"/>
-      <c r="P147" s="66" t="str" cm="1">
+      <c r="P147" s="66" cm="1" t="str">
         <f t="array" ref="P147">IF(AG147="","",AC147-R147-Q147)</f>
         <v/>
       </c>
@@ -34744,13 +34744,13 @@
       <c r="C148" s="19"/>
       <c r="D148" s="72"/>
       <c r="E148" s="71"/>
-      <c r="F148" s="82" t="str" cm="1">
+      <c r="F148" s="82" cm="1" t="str">
         <f t="array" ref="F148">IF(AG148="","",I148-H148)</f>
         <v/>
       </c>
       <c r="G148" s="67"/>
       <c r="H148" s="65"/>
-      <c r="I148" s="66" t="str" cm="1">
+      <c r="I148" s="66" cm="1" t="str">
         <f t="array" ref="I148">IF(AG148="","",P148-K148)</f>
         <v/>
       </c>
@@ -34760,7 +34760,7 @@
       <c r="M148" s="68"/>
       <c r="N148" s="68"/>
       <c r="O148" s="68"/>
-      <c r="P148" s="66" t="str" cm="1">
+      <c r="P148" s="66" cm="1" t="str">
         <f t="array" ref="P148">IF(AG148="","",AC148-R148-Q148)</f>
         <v/>
       </c>
@@ -34825,13 +34825,13 @@
       <c r="C149" s="19"/>
       <c r="D149" s="72"/>
       <c r="E149" s="71"/>
-      <c r="F149" s="82" t="str" cm="1">
+      <c r="F149" s="82" cm="1" t="str">
         <f t="array" ref="F149">IF(AG149="","",I149-H149)</f>
         <v/>
       </c>
       <c r="G149" s="67"/>
       <c r="H149" s="65"/>
-      <c r="I149" s="66" t="str" cm="1">
+      <c r="I149" s="66" cm="1" t="str">
         <f t="array" ref="I149">IF(AG149="","",P149-K149)</f>
         <v/>
       </c>
@@ -34841,7 +34841,7 @@
       <c r="M149" s="68"/>
       <c r="N149" s="68"/>
       <c r="O149" s="68"/>
-      <c r="P149" s="66" t="str" cm="1">
+      <c r="P149" s="66" cm="1" t="str">
         <f t="array" ref="P149">IF(AG149="","",AC149-R149-Q149)</f>
         <v/>
       </c>
@@ -34906,13 +34906,13 @@
       <c r="C150" s="19"/>
       <c r="D150" s="72"/>
       <c r="E150" s="71"/>
-      <c r="F150" s="82" t="str" cm="1">
+      <c r="F150" s="82" cm="1" t="str">
         <f t="array" ref="F150">IF(AG150="","",I150-H150)</f>
         <v/>
       </c>
       <c r="G150" s="67"/>
       <c r="H150" s="65"/>
-      <c r="I150" s="66" t="str" cm="1">
+      <c r="I150" s="66" cm="1" t="str">
         <f t="array" ref="I150">IF(AG150="","",P150-K150)</f>
         <v/>
       </c>
@@ -34922,7 +34922,7 @@
       <c r="M150" s="68"/>
       <c r="N150" s="68"/>
       <c r="O150" s="68"/>
-      <c r="P150" s="66" t="str" cm="1">
+      <c r="P150" s="66" cm="1" t="str">
         <f t="array" ref="P150">IF(AG150="","",AC150-R150-Q150)</f>
         <v/>
       </c>
@@ -34987,13 +34987,13 @@
       <c r="C151" s="19"/>
       <c r="D151" s="72"/>
       <c r="E151" s="71"/>
-      <c r="F151" s="82" t="str" cm="1">
+      <c r="F151" s="82" cm="1" t="str">
         <f t="array" ref="F151">IF(AG151="","",I151-H151)</f>
         <v/>
       </c>
       <c r="G151" s="67"/>
       <c r="H151" s="65"/>
-      <c r="I151" s="66" t="str" cm="1">
+      <c r="I151" s="66" cm="1" t="str">
         <f t="array" ref="I151">IF(AG151="","",P151-K151)</f>
         <v/>
       </c>
@@ -35003,7 +35003,7 @@
       <c r="M151" s="68"/>
       <c r="N151" s="68"/>
       <c r="O151" s="68"/>
-      <c r="P151" s="66" t="str" cm="1">
+      <c r="P151" s="66" cm="1" t="str">
         <f t="array" ref="P151">IF(AG151="","",AC151-R151-Q151)</f>
         <v/>
       </c>
@@ -35068,13 +35068,13 @@
       <c r="C152" s="19"/>
       <c r="D152" s="72"/>
       <c r="E152" s="71"/>
-      <c r="F152" s="82" t="str" cm="1">
+      <c r="F152" s="82" cm="1" t="str">
         <f t="array" ref="F152">IF(AG152="","",I152-H152)</f>
         <v/>
       </c>
       <c r="G152" s="67"/>
       <c r="H152" s="65"/>
-      <c r="I152" s="66" t="str" cm="1">
+      <c r="I152" s="66" cm="1" t="str">
         <f t="array" ref="I152">IF(AG152="","",P152-K152)</f>
         <v/>
       </c>
@@ -35084,7 +35084,7 @@
       <c r="M152" s="68"/>
       <c r="N152" s="68"/>
       <c r="O152" s="68"/>
-      <c r="P152" s="66" t="str" cm="1">
+      <c r="P152" s="66" cm="1" t="str">
         <f t="array" ref="P152">IF(AG152="","",AC152-R152-Q152)</f>
         <v/>
       </c>
@@ -35149,13 +35149,13 @@
       <c r="C153" s="19"/>
       <c r="D153" s="72"/>
       <c r="E153" s="71"/>
-      <c r="F153" s="82" t="str" cm="1">
+      <c r="F153" s="82" cm="1" t="str">
         <f t="array" ref="F153">IF(AG153="","",I153-H153)</f>
         <v/>
       </c>
       <c r="G153" s="67"/>
       <c r="H153" s="65"/>
-      <c r="I153" s="66" t="str" cm="1">
+      <c r="I153" s="66" cm="1" t="str">
         <f t="array" ref="I153">IF(AG153="","",P153-K153)</f>
         <v/>
       </c>
@@ -35165,7 +35165,7 @@
       <c r="M153" s="68"/>
       <c r="N153" s="68"/>
       <c r="O153" s="68"/>
-      <c r="P153" s="66" t="str" cm="1">
+      <c r="P153" s="66" cm="1" t="str">
         <f t="array" ref="P153">IF(AG153="","",AC153-R153-Q153)</f>
         <v/>
       </c>
@@ -35230,13 +35230,13 @@
       <c r="C154" s="19"/>
       <c r="D154" s="72"/>
       <c r="E154" s="71"/>
-      <c r="F154" s="82" t="str" cm="1">
+      <c r="F154" s="82" cm="1" t="str">
         <f t="array" ref="F154">IF(AG154="","",I154-H154)</f>
         <v/>
       </c>
       <c r="G154" s="67"/>
       <c r="H154" s="65"/>
-      <c r="I154" s="66" t="str" cm="1">
+      <c r="I154" s="66" cm="1" t="str">
         <f t="array" ref="I154">IF(AG154="","",P154-K154)</f>
         <v/>
       </c>
@@ -35246,7 +35246,7 @@
       <c r="M154" s="68"/>
       <c r="N154" s="68"/>
       <c r="O154" s="68"/>
-      <c r="P154" s="66" t="str" cm="1">
+      <c r="P154" s="66" cm="1" t="str">
         <f t="array" ref="P154">IF(AG154="","",AC154-R154-Q154)</f>
         <v/>
       </c>
@@ -35311,13 +35311,13 @@
       <c r="C155" s="19"/>
       <c r="D155" s="72"/>
       <c r="E155" s="71"/>
-      <c r="F155" s="82" t="str" cm="1">
+      <c r="F155" s="82" cm="1" t="str">
         <f t="array" ref="F155">IF(AG155="","",I155-H155)</f>
         <v/>
       </c>
       <c r="G155" s="67"/>
       <c r="H155" s="65"/>
-      <c r="I155" s="66" t="str" cm="1">
+      <c r="I155" s="66" cm="1" t="str">
         <f t="array" ref="I155">IF(AG155="","",P155-K155)</f>
         <v/>
       </c>
@@ -35327,7 +35327,7 @@
       <c r="M155" s="68"/>
       <c r="N155" s="68"/>
       <c r="O155" s="68"/>
-      <c r="P155" s="66" t="str" cm="1">
+      <c r="P155" s="66" cm="1" t="str">
         <f t="array" ref="P155">IF(AG155="","",AC155-R155-Q155)</f>
         <v/>
       </c>
@@ -35392,13 +35392,13 @@
       <c r="C156" s="19"/>
       <c r="D156" s="72"/>
       <c r="E156" s="71"/>
-      <c r="F156" s="82" t="str" cm="1">
+      <c r="F156" s="82" cm="1" t="str">
         <f t="array" ref="F156">IF(AG156="","",I156-H156)</f>
         <v/>
       </c>
       <c r="G156" s="67"/>
       <c r="H156" s="65"/>
-      <c r="I156" s="66" t="str" cm="1">
+      <c r="I156" s="66" cm="1" t="str">
         <f t="array" ref="I156">IF(AG156="","",P156-K156)</f>
         <v/>
       </c>
@@ -35408,7 +35408,7 @@
       <c r="M156" s="68"/>
       <c r="N156" s="68"/>
       <c r="O156" s="68"/>
-      <c r="P156" s="66" t="str" cm="1">
+      <c r="P156" s="66" cm="1" t="str">
         <f t="array" ref="P156">IF(AG156="","",AC156-R156-Q156)</f>
         <v/>
       </c>
@@ -35473,13 +35473,13 @@
       <c r="C157" s="19"/>
       <c r="D157" s="72"/>
       <c r="E157" s="71"/>
-      <c r="F157" s="82" t="str" cm="1">
+      <c r="F157" s="82" cm="1" t="str">
         <f t="array" ref="F157">IF(AG157="","",I157-H157)</f>
         <v/>
       </c>
       <c r="G157" s="67"/>
       <c r="H157" s="65"/>
-      <c r="I157" s="66" t="str" cm="1">
+      <c r="I157" s="66" cm="1" t="str">
         <f t="array" ref="I157">IF(AG157="","",P157-K157)</f>
         <v/>
       </c>
@@ -35489,7 +35489,7 @@
       <c r="M157" s="68"/>
       <c r="N157" s="68"/>
       <c r="O157" s="68"/>
-      <c r="P157" s="66" t="str" cm="1">
+      <c r="P157" s="66" cm="1" t="str">
         <f t="array" ref="P157">IF(AG157="","",AC157-R157-Q157)</f>
         <v/>
       </c>
@@ -35554,13 +35554,13 @@
       <c r="C158" s="19"/>
       <c r="D158" s="72"/>
       <c r="E158" s="71"/>
-      <c r="F158" s="82" t="str" cm="1">
+      <c r="F158" s="82" cm="1" t="str">
         <f t="array" ref="F158">IF(AG158="","",I158-H158)</f>
         <v/>
       </c>
       <c r="G158" s="67"/>
       <c r="H158" s="65"/>
-      <c r="I158" s="66" t="str" cm="1">
+      <c r="I158" s="66" cm="1" t="str">
         <f t="array" ref="I158">IF(AG158="","",P158-K158)</f>
         <v/>
       </c>
@@ -35570,7 +35570,7 @@
       <c r="M158" s="68"/>
       <c r="N158" s="68"/>
       <c r="O158" s="68"/>
-      <c r="P158" s="66" t="str" cm="1">
+      <c r="P158" s="66" cm="1" t="str">
         <f t="array" ref="P158">IF(AG158="","",AC158-R158-Q158)</f>
         <v/>
       </c>
@@ -35635,13 +35635,13 @@
       <c r="C159" s="19"/>
       <c r="D159" s="72"/>
       <c r="E159" s="71"/>
-      <c r="F159" s="82" t="str" cm="1">
+      <c r="F159" s="82" cm="1" t="str">
         <f t="array" ref="F159">IF(AG159="","",I159-H159)</f>
         <v/>
       </c>
       <c r="G159" s="67"/>
       <c r="H159" s="65"/>
-      <c r="I159" s="66" t="str" cm="1">
+      <c r="I159" s="66" cm="1" t="str">
         <f t="array" ref="I159">IF(AG159="","",P159-K159)</f>
         <v/>
       </c>
@@ -35651,7 +35651,7 @@
       <c r="M159" s="68"/>
       <c r="N159" s="68"/>
       <c r="O159" s="68"/>
-      <c r="P159" s="66" t="str" cm="1">
+      <c r="P159" s="66" cm="1" t="str">
         <f t="array" ref="P159">IF(AG159="","",AC159-R159-Q159)</f>
         <v/>
       </c>
@@ -35716,13 +35716,13 @@
       <c r="C160" s="19"/>
       <c r="D160" s="72"/>
       <c r="E160" s="71"/>
-      <c r="F160" s="82" t="str" cm="1">
+      <c r="F160" s="82" cm="1" t="str">
         <f t="array" ref="F160">IF(AG160="","",I160-H160)</f>
         <v/>
       </c>
       <c r="G160" s="67"/>
       <c r="H160" s="65"/>
-      <c r="I160" s="66" t="str" cm="1">
+      <c r="I160" s="66" cm="1" t="str">
         <f t="array" ref="I160">IF(AG160="","",P160-K160)</f>
         <v/>
       </c>
@@ -35732,7 +35732,7 @@
       <c r="M160" s="68"/>
       <c r="N160" s="68"/>
       <c r="O160" s="68"/>
-      <c r="P160" s="66" t="str" cm="1">
+      <c r="P160" s="66" cm="1" t="str">
         <f t="array" ref="P160">IF(AG160="","",AC160-R160-Q160)</f>
         <v/>
       </c>
@@ -35797,13 +35797,13 @@
       <c r="C161" s="19"/>
       <c r="D161" s="72"/>
       <c r="E161" s="71"/>
-      <c r="F161" s="82" t="str" cm="1">
+      <c r="F161" s="82" cm="1" t="str">
         <f t="array" ref="F161">IF(AG161="","",I161-H161)</f>
         <v/>
       </c>
       <c r="G161" s="67"/>
       <c r="H161" s="65"/>
-      <c r="I161" s="66" t="str" cm="1">
+      <c r="I161" s="66" cm="1" t="str">
         <f t="array" ref="I161">IF(AG161="","",P161-K161)</f>
         <v/>
       </c>
@@ -35813,7 +35813,7 @@
       <c r="M161" s="68"/>
       <c r="N161" s="68"/>
       <c r="O161" s="68"/>
-      <c r="P161" s="66" t="str" cm="1">
+      <c r="P161" s="66" cm="1" t="str">
         <f t="array" ref="P161">IF(AG161="","",AC161-R161-Q161)</f>
         <v/>
       </c>
@@ -35878,13 +35878,13 @@
       <c r="C162" s="19"/>
       <c r="D162" s="72"/>
       <c r="E162" s="71"/>
-      <c r="F162" s="82" t="str" cm="1">
+      <c r="F162" s="82" cm="1" t="str">
         <f t="array" ref="F162">IF(AG162="","",I162-H162)</f>
         <v/>
       </c>
       <c r="G162" s="67"/>
       <c r="H162" s="65"/>
-      <c r="I162" s="66" t="str" cm="1">
+      <c r="I162" s="66" cm="1" t="str">
         <f t="array" ref="I162">IF(AG162="","",P162-K162)</f>
         <v/>
       </c>
@@ -35894,7 +35894,7 @@
       <c r="M162" s="68"/>
       <c r="N162" s="68"/>
       <c r="O162" s="68"/>
-      <c r="P162" s="66" t="str" cm="1">
+      <c r="P162" s="66" cm="1" t="str">
         <f t="array" ref="P162">IF(AG162="","",AC162-R162-Q162)</f>
         <v/>
       </c>
@@ -35959,13 +35959,13 @@
       <c r="C163" s="19"/>
       <c r="D163" s="72"/>
       <c r="E163" s="71"/>
-      <c r="F163" s="82" t="str" cm="1">
+      <c r="F163" s="82" cm="1" t="str">
         <f t="array" ref="F163">IF(AG163="","",I163-H163)</f>
         <v/>
       </c>
       <c r="G163" s="67"/>
       <c r="H163" s="65"/>
-      <c r="I163" s="66" t="str" cm="1">
+      <c r="I163" s="66" cm="1" t="str">
         <f t="array" ref="I163">IF(AG163="","",P163-K163)</f>
         <v/>
       </c>
@@ -35975,7 +35975,7 @@
       <c r="M163" s="68"/>
       <c r="N163" s="68"/>
       <c r="O163" s="68"/>
-      <c r="P163" s="66" t="str" cm="1">
+      <c r="P163" s="66" cm="1" t="str">
         <f t="array" ref="P163">IF(AG163="","",AC163-R163-Q163)</f>
         <v/>
       </c>
@@ -36040,13 +36040,13 @@
       <c r="C164" s="19"/>
       <c r="D164" s="72"/>
       <c r="E164" s="71"/>
-      <c r="F164" s="82" t="str" cm="1">
+      <c r="F164" s="82" cm="1" t="str">
         <f t="array" ref="F164">IF(AG164="","",I164-H164)</f>
         <v/>
       </c>
       <c r="G164" s="67"/>
       <c r="H164" s="65"/>
-      <c r="I164" s="66" t="str" cm="1">
+      <c r="I164" s="66" cm="1" t="str">
         <f t="array" ref="I164">IF(AG164="","",P164-K164)</f>
         <v/>
       </c>
@@ -36056,7 +36056,7 @@
       <c r="M164" s="68"/>
       <c r="N164" s="68"/>
       <c r="O164" s="68"/>
-      <c r="P164" s="66" t="str" cm="1">
+      <c r="P164" s="66" cm="1" t="str">
         <f t="array" ref="P164">IF(AG164="","",AC164-R164-Q164)</f>
         <v/>
       </c>
@@ -36121,13 +36121,13 @@
       <c r="C165" s="19"/>
       <c r="D165" s="72"/>
       <c r="E165" s="71"/>
-      <c r="F165" s="82" t="str" cm="1">
+      <c r="F165" s="82" cm="1" t="str">
         <f t="array" ref="F165">IF(AG165="","",I165-H165)</f>
         <v/>
       </c>
       <c r="G165" s="67"/>
       <c r="H165" s="65"/>
-      <c r="I165" s="66" t="str" cm="1">
+      <c r="I165" s="66" cm="1" t="str">
         <f t="array" ref="I165">IF(AG165="","",P165-K165)</f>
         <v/>
       </c>
@@ -36137,7 +36137,7 @@
       <c r="M165" s="68"/>
       <c r="N165" s="68"/>
       <c r="O165" s="68"/>
-      <c r="P165" s="66" t="str" cm="1">
+      <c r="P165" s="66" cm="1" t="str">
         <f t="array" ref="P165">IF(AG165="","",AC165-R165-Q165)</f>
         <v/>
       </c>
@@ -36202,13 +36202,13 @@
       <c r="C166" s="19"/>
       <c r="D166" s="72"/>
       <c r="E166" s="71"/>
-      <c r="F166" s="82" t="str" cm="1">
+      <c r="F166" s="82" cm="1" t="str">
         <f t="array" ref="F166">IF(AG166="","",I166-H166)</f>
         <v/>
       </c>
       <c r="G166" s="67"/>
       <c r="H166" s="65"/>
-      <c r="I166" s="66" t="str" cm="1">
+      <c r="I166" s="66" cm="1" t="str">
         <f t="array" ref="I166">IF(AG166="","",P166-K166)</f>
         <v/>
       </c>
@@ -36218,7 +36218,7 @@
       <c r="M166" s="68"/>
       <c r="N166" s="68"/>
       <c r="O166" s="68"/>
-      <c r="P166" s="66" t="str" cm="1">
+      <c r="P166" s="66" cm="1" t="str">
         <f t="array" ref="P166">IF(AG166="","",AC166-R166-Q166)</f>
         <v/>
       </c>
@@ -36283,13 +36283,13 @@
       <c r="C167" s="19"/>
       <c r="D167" s="72"/>
       <c r="E167" s="71"/>
-      <c r="F167" s="82" t="str" cm="1">
+      <c r="F167" s="82" cm="1" t="str">
         <f t="array" ref="F167">IF(AG167="","",I167-H167)</f>
         <v/>
       </c>
       <c r="G167" s="67"/>
       <c r="H167" s="65"/>
-      <c r="I167" s="66" t="str" cm="1">
+      <c r="I167" s="66" cm="1" t="str">
         <f t="array" ref="I167">IF(AG167="","",P167-K167)</f>
         <v/>
       </c>
@@ -36299,7 +36299,7 @@
       <c r="M167" s="68"/>
       <c r="N167" s="68"/>
       <c r="O167" s="68"/>
-      <c r="P167" s="66" t="str" cm="1">
+      <c r="P167" s="66" cm="1" t="str">
         <f t="array" ref="P167">IF(AG167="","",AC167-R167-Q167)</f>
         <v/>
       </c>
@@ -36364,13 +36364,13 @@
       <c r="C168" s="19"/>
       <c r="D168" s="72"/>
       <c r="E168" s="71"/>
-      <c r="F168" s="82" t="str" cm="1">
+      <c r="F168" s="82" cm="1" t="str">
         <f t="array" ref="F168">IF(AG168="","",I168-H168)</f>
         <v/>
       </c>
       <c r="G168" s="67"/>
       <c r="H168" s="65"/>
-      <c r="I168" s="66" t="str" cm="1">
+      <c r="I168" s="66" cm="1" t="str">
         <f t="array" ref="I168">IF(AG168="","",P168-K168)</f>
         <v/>
       </c>
@@ -36380,7 +36380,7 @@
       <c r="M168" s="68"/>
       <c r="N168" s="68"/>
       <c r="O168" s="68"/>
-      <c r="P168" s="66" t="str" cm="1">
+      <c r="P168" s="66" cm="1" t="str">
         <f t="array" ref="P168">IF(AG168="","",AC168-R168-Q168)</f>
         <v/>
       </c>
@@ -36445,13 +36445,13 @@
       <c r="C169" s="19"/>
       <c r="D169" s="72"/>
       <c r="E169" s="71"/>
-      <c r="F169" s="82" t="str" cm="1">
+      <c r="F169" s="82" cm="1" t="str">
         <f t="array" ref="F169">IF(AG169="","",I169-H169)</f>
         <v/>
       </c>
       <c r="G169" s="67"/>
       <c r="H169" s="65"/>
-      <c r="I169" s="66" t="str" cm="1">
+      <c r="I169" s="66" cm="1" t="str">
         <f t="array" ref="I169">IF(AG169="","",P169-K169)</f>
         <v/>
       </c>
@@ -36461,7 +36461,7 @@
       <c r="M169" s="68"/>
       <c r="N169" s="68"/>
       <c r="O169" s="68"/>
-      <c r="P169" s="66" t="str" cm="1">
+      <c r="P169" s="66" cm="1" t="str">
         <f t="array" ref="P169">IF(AG169="","",AC169-R169-Q169)</f>
         <v/>
       </c>
@@ -36526,13 +36526,13 @@
       <c r="C170" s="19"/>
       <c r="D170" s="72"/>
       <c r="E170" s="71"/>
-      <c r="F170" s="82" t="str" cm="1">
+      <c r="F170" s="82" cm="1" t="str">
         <f t="array" ref="F170">IF(AG170="","",I170-H170)</f>
         <v/>
       </c>
       <c r="G170" s="67"/>
       <c r="H170" s="65"/>
-      <c r="I170" s="66" t="str" cm="1">
+      <c r="I170" s="66" cm="1" t="str">
         <f t="array" ref="I170">IF(AG170="","",P170-K170)</f>
         <v/>
       </c>
@@ -36542,7 +36542,7 @@
       <c r="M170" s="68"/>
       <c r="N170" s="68"/>
       <c r="O170" s="68"/>
-      <c r="P170" s="66" t="str" cm="1">
+      <c r="P170" s="66" cm="1" t="str">
         <f t="array" ref="P170">IF(AG170="","",AC170-R170-Q170)</f>
         <v/>
       </c>
@@ -36607,13 +36607,13 @@
       <c r="C171" s="19"/>
       <c r="D171" s="72"/>
       <c r="E171" s="71"/>
-      <c r="F171" s="82" t="str" cm="1">
+      <c r="F171" s="82" cm="1" t="str">
         <f t="array" ref="F171">IF(AG171="","",I171-H171)</f>
         <v/>
       </c>
       <c r="G171" s="67"/>
       <c r="H171" s="65"/>
-      <c r="I171" s="66" t="str" cm="1">
+      <c r="I171" s="66" cm="1" t="str">
         <f t="array" ref="I171">IF(AG171="","",P171-K171)</f>
         <v/>
       </c>
@@ -36623,7 +36623,7 @@
       <c r="M171" s="68"/>
       <c r="N171" s="68"/>
       <c r="O171" s="68"/>
-      <c r="P171" s="66" t="str" cm="1">
+      <c r="P171" s="66" cm="1" t="str">
         <f t="array" ref="P171">IF(AG171="","",AC171-R171-Q171)</f>
         <v/>
       </c>
@@ -36688,13 +36688,13 @@
       <c r="C172" s="19"/>
       <c r="D172" s="72"/>
       <c r="E172" s="71"/>
-      <c r="F172" s="82" t="str" cm="1">
+      <c r="F172" s="82" cm="1" t="str">
         <f t="array" ref="F172">IF(AG172="","",I172-H172)</f>
         <v/>
       </c>
       <c r="G172" s="67"/>
       <c r="H172" s="65"/>
-      <c r="I172" s="66" t="str" cm="1">
+      <c r="I172" s="66" cm="1" t="str">
         <f t="array" ref="I172">IF(AG172="","",P172-K172)</f>
         <v/>
       </c>
@@ -36704,7 +36704,7 @@
       <c r="M172" s="68"/>
       <c r="N172" s="68"/>
       <c r="O172" s="68"/>
-      <c r="P172" s="66" t="str" cm="1">
+      <c r="P172" s="66" cm="1" t="str">
         <f t="array" ref="P172">IF(AG172="","",AC172-R172-Q172)</f>
         <v/>
       </c>
@@ -36769,13 +36769,13 @@
       <c r="C173" s="19"/>
       <c r="D173" s="72"/>
       <c r="E173" s="71"/>
-      <c r="F173" s="82" t="str" cm="1">
+      <c r="F173" s="82" cm="1" t="str">
         <f t="array" ref="F173">IF(AG173="","",I173-H173)</f>
         <v/>
       </c>
       <c r="G173" s="67"/>
       <c r="H173" s="65"/>
-      <c r="I173" s="66" t="str" cm="1">
+      <c r="I173" s="66" cm="1" t="str">
         <f t="array" ref="I173">IF(AG173="","",P173-K173)</f>
         <v/>
       </c>
@@ -36785,7 +36785,7 @@
       <c r="M173" s="68"/>
       <c r="N173" s="68"/>
       <c r="O173" s="68"/>
-      <c r="P173" s="66" t="str" cm="1">
+      <c r="P173" s="66" cm="1" t="str">
         <f t="array" ref="P173">IF(AG173="","",AC173-R173-Q173)</f>
         <v/>
       </c>
@@ -36850,13 +36850,13 @@
       <c r="C174" s="19"/>
       <c r="D174" s="72"/>
       <c r="E174" s="71"/>
-      <c r="F174" s="82" t="str" cm="1">
+      <c r="F174" s="82" cm="1" t="str">
         <f t="array" ref="F174">IF(AG174="","",I174-H174)</f>
         <v/>
       </c>
       <c r="G174" s="67"/>
       <c r="H174" s="65"/>
-      <c r="I174" s="66" t="str" cm="1">
+      <c r="I174" s="66" cm="1" t="str">
         <f t="array" ref="I174">IF(AG174="","",P174-K174)</f>
         <v/>
       </c>
@@ -36866,7 +36866,7 @@
       <c r="M174" s="68"/>
       <c r="N174" s="68"/>
       <c r="O174" s="68"/>
-      <c r="P174" s="66" t="str" cm="1">
+      <c r="P174" s="66" cm="1" t="str">
         <f t="array" ref="P174">IF(AG174="","",AC174-R174-Q174)</f>
         <v/>
       </c>
@@ -36931,13 +36931,13 @@
       <c r="C175" s="19"/>
       <c r="D175" s="72"/>
       <c r="E175" s="71"/>
-      <c r="F175" s="82" t="str" cm="1">
+      <c r="F175" s="82" cm="1" t="str">
         <f t="array" ref="F175">IF(AG175="","",I175-H175)</f>
         <v/>
       </c>
       <c r="G175" s="67"/>
       <c r="H175" s="65"/>
-      <c r="I175" s="66" t="str" cm="1">
+      <c r="I175" s="66" cm="1" t="str">
         <f t="array" ref="I175">IF(AG175="","",P175-K175)</f>
         <v/>
       </c>
@@ -36947,7 +36947,7 @@
       <c r="M175" s="68"/>
       <c r="N175" s="68"/>
       <c r="O175" s="68"/>
-      <c r="P175" s="66" t="str" cm="1">
+      <c r="P175" s="66" cm="1" t="str">
         <f t="array" ref="P175">IF(AG175="","",AC175-R175-Q175)</f>
         <v/>
       </c>
@@ -37012,13 +37012,13 @@
       <c r="C176" s="19"/>
       <c r="D176" s="72"/>
       <c r="E176" s="71"/>
-      <c r="F176" s="82" t="str" cm="1">
+      <c r="F176" s="82" cm="1" t="str">
         <f t="array" ref="F176">IF(AG176="","",I176-H176)</f>
         <v/>
       </c>
       <c r="G176" s="67"/>
       <c r="H176" s="65"/>
-      <c r="I176" s="66" t="str" cm="1">
+      <c r="I176" s="66" cm="1" t="str">
         <f t="array" ref="I176">IF(AG176="","",P176-K176)</f>
         <v/>
       </c>
@@ -37028,7 +37028,7 @@
       <c r="M176" s="68"/>
       <c r="N176" s="68"/>
       <c r="O176" s="68"/>
-      <c r="P176" s="66" t="str" cm="1">
+      <c r="P176" s="66" cm="1" t="str">
         <f t="array" ref="P176">IF(AG176="","",AC176-R176-Q176)</f>
         <v/>
       </c>
@@ -37093,13 +37093,13 @@
       <c r="C177" s="19"/>
       <c r="D177" s="72"/>
       <c r="E177" s="71"/>
-      <c r="F177" s="82" t="str" cm="1">
+      <c r="F177" s="82" cm="1" t="str">
         <f t="array" ref="F177">IF(AG177="","",I177-H177)</f>
         <v/>
       </c>
       <c r="G177" s="67"/>
       <c r="H177" s="65"/>
-      <c r="I177" s="66" t="str" cm="1">
+      <c r="I177" s="66" cm="1" t="str">
         <f t="array" ref="I177">IF(AG177="","",P177-K177)</f>
         <v/>
       </c>
@@ -37109,7 +37109,7 @@
       <c r="M177" s="68"/>
       <c r="N177" s="68"/>
       <c r="O177" s="68"/>
-      <c r="P177" s="66" t="str" cm="1">
+      <c r="P177" s="66" cm="1" t="str">
         <f t="array" ref="P177">IF(AG177="","",AC177-R177-Q177)</f>
         <v/>
       </c>
@@ -37174,13 +37174,13 @@
       <c r="C178" s="19"/>
       <c r="D178" s="72"/>
       <c r="E178" s="71"/>
-      <c r="F178" s="82" t="str" cm="1">
+      <c r="F178" s="82" cm="1" t="str">
         <f t="array" ref="F178">IF(AG178="","",I178-H178)</f>
         <v/>
       </c>
       <c r="G178" s="67"/>
       <c r="H178" s="65"/>
-      <c r="I178" s="66" t="str" cm="1">
+      <c r="I178" s="66" cm="1" t="str">
         <f t="array" ref="I178">IF(AG178="","",P178-K178)</f>
         <v/>
       </c>
@@ -37190,7 +37190,7 @@
       <c r="M178" s="68"/>
       <c r="N178" s="68"/>
       <c r="O178" s="68"/>
-      <c r="P178" s="66" t="str" cm="1">
+      <c r="P178" s="66" cm="1" t="str">
         <f t="array" ref="P178">IF(AG178="","",AC178-R178-Q178)</f>
         <v/>
       </c>
@@ -37255,13 +37255,13 @@
       <c r="C179" s="19"/>
       <c r="D179" s="72"/>
       <c r="E179" s="71"/>
-      <c r="F179" s="82" t="str" cm="1">
+      <c r="F179" s="82" cm="1" t="str">
         <f t="array" ref="F179">IF(AG179="","",I179-H179)</f>
         <v/>
       </c>
       <c r="G179" s="67"/>
       <c r="H179" s="65"/>
-      <c r="I179" s="66" t="str" cm="1">
+      <c r="I179" s="66" cm="1" t="str">
         <f t="array" ref="I179">IF(AG179="","",P179-K179)</f>
         <v/>
       </c>
@@ -37271,7 +37271,7 @@
       <c r="M179" s="68"/>
       <c r="N179" s="68"/>
       <c r="O179" s="68"/>
-      <c r="P179" s="66" t="str" cm="1">
+      <c r="P179" s="66" cm="1" t="str">
         <f t="array" ref="P179">IF(AG179="","",AC179-R179-Q179)</f>
         <v/>
       </c>
@@ -37336,13 +37336,13 @@
       <c r="C180" s="19"/>
       <c r="D180" s="72"/>
       <c r="E180" s="71"/>
-      <c r="F180" s="82" t="str" cm="1">
+      <c r="F180" s="82" cm="1" t="str">
         <f t="array" ref="F180">IF(AG180="","",I180-H180)</f>
         <v/>
       </c>
       <c r="G180" s="67"/>
       <c r="H180" s="65"/>
-      <c r="I180" s="66" t="str" cm="1">
+      <c r="I180" s="66" cm="1" t="str">
         <f t="array" ref="I180">IF(AG180="","",P180-K180)</f>
         <v/>
       </c>
@@ -37352,7 +37352,7 @@
       <c r="M180" s="68"/>
       <c r="N180" s="68"/>
       <c r="O180" s="68"/>
-      <c r="P180" s="66" t="str" cm="1">
+      <c r="P180" s="66" cm="1" t="str">
         <f t="array" ref="P180">IF(AG180="","",AC180-R180-Q180)</f>
         <v/>
       </c>
@@ -37417,13 +37417,13 @@
       <c r="C181" s="19"/>
       <c r="D181" s="72"/>
       <c r="E181" s="71"/>
-      <c r="F181" s="82" t="str" cm="1">
+      <c r="F181" s="82" cm="1" t="str">
         <f t="array" ref="F181">IF(AG181="","",I181-H181)</f>
         <v/>
       </c>
       <c r="G181" s="67"/>
       <c r="H181" s="65"/>
-      <c r="I181" s="66" t="str" cm="1">
+      <c r="I181" s="66" cm="1" t="str">
         <f t="array" ref="I181">IF(AG181="","",P181-K181)</f>
         <v/>
       </c>
@@ -37433,7 +37433,7 @@
       <c r="M181" s="68"/>
       <c r="N181" s="68"/>
       <c r="O181" s="68"/>
-      <c r="P181" s="66" t="str" cm="1">
+      <c r="P181" s="66" cm="1" t="str">
         <f t="array" ref="P181">IF(AG181="","",AC181-R181-Q181)</f>
         <v/>
       </c>
@@ -37498,13 +37498,13 @@
       <c r="C182" s="19"/>
       <c r="D182" s="72"/>
       <c r="E182" s="71"/>
-      <c r="F182" s="82" t="str" cm="1">
+      <c r="F182" s="82" cm="1" t="str">
         <f t="array" ref="F182">IF(AG182="","",I182-H182)</f>
         <v/>
       </c>
       <c r="G182" s="67"/>
       <c r="H182" s="65"/>
-      <c r="I182" s="66" t="str" cm="1">
+      <c r="I182" s="66" cm="1" t="str">
         <f t="array" ref="I182">IF(AG182="","",P182-K182)</f>
         <v/>
       </c>
@@ -37514,7 +37514,7 @@
       <c r="M182" s="68"/>
       <c r="N182" s="68"/>
       <c r="O182" s="68"/>
-      <c r="P182" s="66" t="str" cm="1">
+      <c r="P182" s="66" cm="1" t="str">
         <f t="array" ref="P182">IF(AG182="","",AC182-R182-Q182)</f>
         <v/>
       </c>
@@ -37579,13 +37579,13 @@
       <c r="C183" s="19"/>
       <c r="D183" s="72"/>
       <c r="E183" s="71"/>
-      <c r="F183" s="82" t="str" cm="1">
+      <c r="F183" s="82" cm="1" t="str">
         <f t="array" ref="F183">IF(AG183="","",I183-H183)</f>
         <v/>
       </c>
       <c r="G183" s="67"/>
       <c r="H183" s="65"/>
-      <c r="I183" s="66" t="str" cm="1">
+      <c r="I183" s="66" cm="1" t="str">
         <f t="array" ref="I183">IF(AG183="","",P183-K183)</f>
         <v/>
       </c>
@@ -37595,7 +37595,7 @@
       <c r="M183" s="68"/>
       <c r="N183" s="68"/>
       <c r="O183" s="68"/>
-      <c r="P183" s="66" t="str" cm="1">
+      <c r="P183" s="66" cm="1" t="str">
         <f t="array" ref="P183">IF(AG183="","",AC183-R183-Q183)</f>
         <v/>
       </c>
@@ -37660,13 +37660,13 @@
       <c r="C184" s="19"/>
       <c r="D184" s="72"/>
       <c r="E184" s="71"/>
-      <c r="F184" s="82" t="str" cm="1">
+      <c r="F184" s="82" cm="1" t="str">
         <f t="array" ref="F184">IF(AG184="","",I184-H184)</f>
         <v/>
       </c>
       <c r="G184" s="67"/>
       <c r="H184" s="65"/>
-      <c r="I184" s="66" t="str" cm="1">
+      <c r="I184" s="66" cm="1" t="str">
         <f t="array" ref="I184">IF(AG184="","",P184-K184)</f>
         <v/>
       </c>
@@ -37676,7 +37676,7 @@
       <c r="M184" s="68"/>
       <c r="N184" s="68"/>
       <c r="O184" s="68"/>
-      <c r="P184" s="66" t="str" cm="1">
+      <c r="P184" s="66" cm="1" t="str">
         <f t="array" ref="P184">IF(AG184="","",AC184-R184-Q184)</f>
         <v/>
       </c>
@@ -37741,13 +37741,13 @@
       <c r="C185" s="19"/>
       <c r="D185" s="72"/>
       <c r="E185" s="71"/>
-      <c r="F185" s="82" t="str" cm="1">
+      <c r="F185" s="82" cm="1" t="str">
         <f t="array" ref="F185">IF(AG185="","",I185-H185)</f>
         <v/>
       </c>
       <c r="G185" s="67"/>
       <c r="H185" s="65"/>
-      <c r="I185" s="66" t="str" cm="1">
+      <c r="I185" s="66" cm="1" t="str">
         <f t="array" ref="I185">IF(AG185="","",P185-K185)</f>
         <v/>
       </c>
@@ -37757,7 +37757,7 @@
       <c r="M185" s="68"/>
       <c r="N185" s="68"/>
       <c r="O185" s="68"/>
-      <c r="P185" s="66" t="str" cm="1">
+      <c r="P185" s="66" cm="1" t="str">
         <f t="array" ref="P185">IF(AG185="","",AC185-R185-Q185)</f>
         <v/>
       </c>
@@ -37822,13 +37822,13 @@
       <c r="C186" s="19"/>
       <c r="D186" s="72"/>
       <c r="E186" s="71"/>
-      <c r="F186" s="82" t="str" cm="1">
+      <c r="F186" s="82" cm="1" t="str">
         <f t="array" ref="F186">IF(AG186="","",I186-H186)</f>
         <v/>
       </c>
       <c r="G186" s="67"/>
       <c r="H186" s="65"/>
-      <c r="I186" s="66" t="str" cm="1">
+      <c r="I186" s="66" cm="1" t="str">
         <f t="array" ref="I186">IF(AG186="","",P186-K186)</f>
         <v/>
       </c>
@@ -37838,7 +37838,7 @@
       <c r="M186" s="68"/>
       <c r="N186" s="68"/>
       <c r="O186" s="68"/>
-      <c r="P186" s="66" t="str" cm="1">
+      <c r="P186" s="66" cm="1" t="str">
         <f t="array" ref="P186">IF(AG186="","",AC186-R186-Q186)</f>
         <v/>
       </c>
@@ -37903,13 +37903,13 @@
       <c r="C187" s="19"/>
       <c r="D187" s="72"/>
       <c r="E187" s="71"/>
-      <c r="F187" s="82" t="str" cm="1">
+      <c r="F187" s="82" cm="1" t="str">
         <f t="array" ref="F187">IF(AG187="","",I187-H187)</f>
         <v/>
       </c>
       <c r="G187" s="67"/>
       <c r="H187" s="65"/>
-      <c r="I187" s="66" t="str" cm="1">
+      <c r="I187" s="66" cm="1" t="str">
         <f t="array" ref="I187">IF(AG187="","",P187-K187)</f>
         <v/>
       </c>
@@ -37919,7 +37919,7 @@
       <c r="M187" s="68"/>
       <c r="N187" s="68"/>
       <c r="O187" s="68"/>
-      <c r="P187" s="66" t="str" cm="1">
+      <c r="P187" s="66" cm="1" t="str">
         <f t="array" ref="P187">IF(AG187="","",AC187-R187-Q187)</f>
         <v/>
       </c>
@@ -37984,13 +37984,13 @@
       <c r="C188" s="19"/>
       <c r="D188" s="72"/>
       <c r="E188" s="71"/>
-      <c r="F188" s="82" t="str" cm="1">
+      <c r="F188" s="82" cm="1" t="str">
         <f t="array" ref="F188">IF(AG188="","",I188-H188)</f>
         <v/>
       </c>
       <c r="G188" s="67"/>
       <c r="H188" s="65"/>
-      <c r="I188" s="66" t="str" cm="1">
+      <c r="I188" s="66" cm="1" t="str">
         <f t="array" ref="I188">IF(AG188="","",P188-K188)</f>
         <v/>
       </c>
@@ -38000,7 +38000,7 @@
       <c r="M188" s="68"/>
       <c r="N188" s="68"/>
       <c r="O188" s="68"/>
-      <c r="P188" s="66" t="str" cm="1">
+      <c r="P188" s="66" cm="1" t="str">
         <f t="array" ref="P188">IF(AG188="","",AC188-R188-Q188)</f>
         <v/>
       </c>
@@ -38065,13 +38065,13 @@
       <c r="C189" s="19"/>
       <c r="D189" s="72"/>
       <c r="E189" s="71"/>
-      <c r="F189" s="82" t="str" cm="1">
+      <c r="F189" s="82" cm="1" t="str">
         <f t="array" ref="F189">IF(AG189="","",I189-H189)</f>
         <v/>
       </c>
       <c r="G189" s="67"/>
       <c r="H189" s="65"/>
-      <c r="I189" s="66" t="str" cm="1">
+      <c r="I189" s="66" cm="1" t="str">
         <f t="array" ref="I189">IF(AG189="","",P189-K189)</f>
         <v/>
       </c>
@@ -38081,7 +38081,7 @@
       <c r="M189" s="68"/>
       <c r="N189" s="68"/>
       <c r="O189" s="68"/>
-      <c r="P189" s="66" t="str" cm="1">
+      <c r="P189" s="66" cm="1" t="str">
         <f t="array" ref="P189">IF(AG189="","",AC189-R189-Q189)</f>
         <v/>
       </c>
@@ -38146,13 +38146,13 @@
       <c r="C190" s="19"/>
       <c r="D190" s="72"/>
       <c r="E190" s="71"/>
-      <c r="F190" s="82" t="str" cm="1">
+      <c r="F190" s="82" cm="1" t="str">
         <f t="array" ref="F190">IF(AG190="","",I190-H190)</f>
         <v/>
       </c>
       <c r="G190" s="67"/>
       <c r="H190" s="65"/>
-      <c r="I190" s="66" t="str" cm="1">
+      <c r="I190" s="66" cm="1" t="str">
         <f t="array" ref="I190">IF(AG190="","",P190-K190)</f>
         <v/>
       </c>
@@ -38162,7 +38162,7 @@
       <c r="M190" s="68"/>
       <c r="N190" s="68"/>
       <c r="O190" s="68"/>
-      <c r="P190" s="66" t="str" cm="1">
+      <c r="P190" s="66" cm="1" t="str">
         <f t="array" ref="P190">IF(AG190="","",AC190-R190-Q190)</f>
         <v/>
       </c>
@@ -38227,13 +38227,13 @@
       <c r="C191" s="19"/>
       <c r="D191" s="72"/>
       <c r="E191" s="71"/>
-      <c r="F191" s="82" t="str" cm="1">
+      <c r="F191" s="82" cm="1" t="str">
         <f t="array" ref="F191">IF(AG191="","",I191-H191)</f>
         <v/>
       </c>
       <c r="G191" s="67"/>
       <c r="H191" s="65"/>
-      <c r="I191" s="66" t="str" cm="1">
+      <c r="I191" s="66" cm="1" t="str">
         <f t="array" ref="I191">IF(AG191="","",P191-K191)</f>
         <v/>
       </c>
@@ -38243,7 +38243,7 @@
       <c r="M191" s="68"/>
       <c r="N191" s="68"/>
       <c r="O191" s="68"/>
-      <c r="P191" s="66" t="str" cm="1">
+      <c r="P191" s="66" cm="1" t="str">
         <f t="array" ref="P191">IF(AG191="","",AC191-R191-Q191)</f>
         <v/>
       </c>
@@ -38308,13 +38308,13 @@
       <c r="C192" s="19"/>
       <c r="D192" s="72"/>
       <c r="E192" s="71"/>
-      <c r="F192" s="82" t="str" cm="1">
+      <c r="F192" s="82" cm="1" t="str">
         <f t="array" ref="F192">IF(AG192="","",I192-H192)</f>
         <v/>
       </c>
       <c r="G192" s="67"/>
       <c r="H192" s="65"/>
-      <c r="I192" s="66" t="str" cm="1">
+      <c r="I192" s="66" cm="1" t="str">
         <f t="array" ref="I192">IF(AG192="","",P192-K192)</f>
         <v/>
       </c>
@@ -38324,7 +38324,7 @@
       <c r="M192" s="68"/>
       <c r="N192" s="68"/>
       <c r="O192" s="68"/>
-      <c r="P192" s="66" t="str" cm="1">
+      <c r="P192" s="66" cm="1" t="str">
         <f t="array" ref="P192">IF(AG192="","",AC192-R192-Q192)</f>
         <v/>
       </c>
@@ -38389,13 +38389,13 @@
       <c r="C193" s="19"/>
       <c r="D193" s="72"/>
       <c r="E193" s="71"/>
-      <c r="F193" s="82" t="str" cm="1">
+      <c r="F193" s="82" cm="1" t="str">
         <f t="array" ref="F193">IF(AG193="","",I193-H193)</f>
         <v/>
       </c>
       <c r="G193" s="67"/>
       <c r="H193" s="65"/>
-      <c r="I193" s="66" t="str" cm="1">
+      <c r="I193" s="66" cm="1" t="str">
         <f t="array" ref="I193">IF(AG193="","",P193-K193)</f>
         <v/>
       </c>
@@ -38405,7 +38405,7 @@
       <c r="M193" s="68"/>
       <c r="N193" s="68"/>
       <c r="O193" s="68"/>
-      <c r="P193" s="66" t="str" cm="1">
+      <c r="P193" s="66" cm="1" t="str">
         <f t="array" ref="P193">IF(AG193="","",AC193-R193-Q193)</f>
         <v/>
       </c>
@@ -38470,13 +38470,13 @@
       <c r="C194" s="19"/>
       <c r="D194" s="72"/>
       <c r="E194" s="71"/>
-      <c r="F194" s="82" t="str" cm="1">
+      <c r="F194" s="82" cm="1" t="str">
         <f t="array" ref="F194">IF(AG194="","",I194-H194)</f>
         <v/>
       </c>
       <c r="G194" s="67"/>
       <c r="H194" s="65"/>
-      <c r="I194" s="66" t="str" cm="1">
+      <c r="I194" s="66" cm="1" t="str">
         <f t="array" ref="I194">IF(AG194="","",P194-K194)</f>
         <v/>
       </c>
@@ -38486,7 +38486,7 @@
       <c r="M194" s="68"/>
       <c r="N194" s="68"/>
       <c r="O194" s="68"/>
-      <c r="P194" s="66" t="str" cm="1">
+      <c r="P194" s="66" cm="1" t="str">
         <f t="array" ref="P194">IF(AG194="","",AC194-R194-Q194)</f>
         <v/>
       </c>
@@ -38551,13 +38551,13 @@
       <c r="C195" s="19"/>
       <c r="D195" s="72"/>
       <c r="E195" s="71"/>
-      <c r="F195" s="82" t="str" cm="1">
+      <c r="F195" s="82" cm="1" t="str">
         <f t="array" ref="F195">IF(AG195="","",I195-H195)</f>
         <v/>
       </c>
       <c r="G195" s="67"/>
       <c r="H195" s="65"/>
-      <c r="I195" s="66" t="str" cm="1">
+      <c r="I195" s="66" cm="1" t="str">
         <f t="array" ref="I195">IF(AG195="","",P195-K195)</f>
         <v/>
       </c>
@@ -38567,7 +38567,7 @@
       <c r="M195" s="68"/>
       <c r="N195" s="68"/>
       <c r="O195" s="68"/>
-      <c r="P195" s="66" t="str" cm="1">
+      <c r="P195" s="66" cm="1" t="str">
         <f t="array" ref="P195">IF(AG195="","",AC195-R195-Q195)</f>
         <v/>
       </c>
@@ -38632,13 +38632,13 @@
       <c r="C196" s="19"/>
       <c r="D196" s="72"/>
       <c r="E196" s="71"/>
-      <c r="F196" s="82" t="str" cm="1">
+      <c r="F196" s="82" cm="1" t="str">
         <f t="array" ref="F196">IF(AG196="","",I196-H196)</f>
         <v/>
       </c>
       <c r="G196" s="67"/>
       <c r="H196" s="65"/>
-      <c r="I196" s="66" t="str" cm="1">
+      <c r="I196" s="66" cm="1" t="str">
         <f t="array" ref="I196">IF(AG196="","",P196-K196)</f>
         <v/>
       </c>
@@ -38648,7 +38648,7 @@
       <c r="M196" s="68"/>
       <c r="N196" s="68"/>
       <c r="O196" s="68"/>
-      <c r="P196" s="66" t="str" cm="1">
+      <c r="P196" s="66" cm="1" t="str">
         <f t="array" ref="P196">IF(AG196="","",AC196-R196-Q196)</f>
         <v/>
       </c>
@@ -38713,13 +38713,13 @@
       <c r="C197" s="19"/>
       <c r="D197" s="72"/>
       <c r="E197" s="71"/>
-      <c r="F197" s="82" t="str" cm="1">
+      <c r="F197" s="82" cm="1" t="str">
         <f t="array" ref="F197">IF(AG197="","",I197-H197)</f>
         <v/>
       </c>
       <c r="G197" s="67"/>
       <c r="H197" s="65"/>
-      <c r="I197" s="66" t="str" cm="1">
+      <c r="I197" s="66" cm="1" t="str">
         <f t="array" ref="I197">IF(AG197="","",P197-K197)</f>
         <v/>
       </c>
@@ -38729,7 +38729,7 @@
       <c r="M197" s="68"/>
       <c r="N197" s="68"/>
       <c r="O197" s="68"/>
-      <c r="P197" s="66" t="str" cm="1">
+      <c r="P197" s="66" cm="1" t="str">
         <f t="array" ref="P197">IF(AG197="","",AC197-R197-Q197)</f>
         <v/>
       </c>
@@ -38794,13 +38794,13 @@
       <c r="C198" s="19"/>
       <c r="D198" s="72"/>
       <c r="E198" s="71"/>
-      <c r="F198" s="82" t="str" cm="1">
+      <c r="F198" s="82" cm="1" t="str">
         <f t="array" ref="F198">IF(AG198="","",I198-H198)</f>
         <v/>
       </c>
       <c r="G198" s="67"/>
       <c r="H198" s="65"/>
-      <c r="I198" s="66" t="str" cm="1">
+      <c r="I198" s="66" cm="1" t="str">
         <f t="array" ref="I198">IF(AG198="","",P198-K198)</f>
         <v/>
       </c>
@@ -38810,7 +38810,7 @@
       <c r="M198" s="68"/>
       <c r="N198" s="68"/>
       <c r="O198" s="68"/>
-      <c r="P198" s="66" t="str" cm="1">
+      <c r="P198" s="66" cm="1" t="str">
         <f t="array" ref="P198">IF(AG198="","",AC198-R198-Q198)</f>
         <v/>
       </c>
@@ -38875,13 +38875,13 @@
       <c r="C199" s="19"/>
       <c r="D199" s="72"/>
       <c r="E199" s="71"/>
-      <c r="F199" s="82" t="str" cm="1">
+      <c r="F199" s="82" cm="1" t="str">
         <f t="array" ref="F199">IF(AG199="","",I199-H199)</f>
         <v/>
       </c>
       <c r="G199" s="67"/>
       <c r="H199" s="65"/>
-      <c r="I199" s="66" t="str" cm="1">
+      <c r="I199" s="66" cm="1" t="str">
         <f t="array" ref="I199">IF(AG199="","",P199-K199)</f>
         <v/>
       </c>
@@ -38891,7 +38891,7 @@
       <c r="M199" s="68"/>
       <c r="N199" s="68"/>
       <c r="O199" s="68"/>
-      <c r="P199" s="66" t="str" cm="1">
+      <c r="P199" s="66" cm="1" t="str">
         <f t="array" ref="P199">IF(AG199="","",AC199-R199-Q199)</f>
         <v/>
       </c>
@@ -38956,13 +38956,13 @@
       <c r="C200" s="19"/>
       <c r="D200" s="72"/>
       <c r="E200" s="71"/>
-      <c r="F200" s="82" t="str" cm="1">
+      <c r="F200" s="82" cm="1" t="str">
         <f t="array" ref="F200">IF(AG200="","",I200-H200)</f>
         <v/>
       </c>
       <c r="G200" s="67"/>
       <c r="H200" s="65"/>
-      <c r="I200" s="66" t="str" cm="1">
+      <c r="I200" s="66" cm="1" t="str">
         <f t="array" ref="I200">IF(AG200="","",P200-K200)</f>
         <v/>
       </c>
@@ -38972,7 +38972,7 @@
       <c r="M200" s="68"/>
       <c r="N200" s="68"/>
       <c r="O200" s="68"/>
-      <c r="P200" s="66" t="str" cm="1">
+      <c r="P200" s="66" cm="1" t="str">
         <f t="array" ref="P200">IF(AG200="","",AC200-R200-Q200)</f>
         <v/>
       </c>
@@ -39037,13 +39037,13 @@
       <c r="C201" s="19"/>
       <c r="D201" s="72"/>
       <c r="E201" s="71"/>
-      <c r="F201" s="82" t="str" cm="1">
+      <c r="F201" s="82" cm="1" t="str">
         <f t="array" ref="F201">IF(AG201="","",I201-H201)</f>
         <v/>
       </c>
       <c r="G201" s="67"/>
       <c r="H201" s="65"/>
-      <c r="I201" s="66" t="str" cm="1">
+      <c r="I201" s="66" cm="1" t="str">
         <f t="array" ref="I201">IF(AG201="","",P201-K201)</f>
         <v/>
       </c>
@@ -39053,7 +39053,7 @@
       <c r="M201" s="68"/>
       <c r="N201" s="68"/>
       <c r="O201" s="68"/>
-      <c r="P201" s="66" t="str" cm="1">
+      <c r="P201" s="66" cm="1" t="str">
         <f t="array" ref="P201">IF(AG201="","",AC201-R201-Q201)</f>
         <v/>
       </c>
@@ -39118,13 +39118,13 @@
       <c r="C202" s="19"/>
       <c r="D202" s="72"/>
       <c r="E202" s="71"/>
-      <c r="F202" s="82" t="str" cm="1">
+      <c r="F202" s="82" cm="1" t="str">
         <f t="array" ref="F202">IF(AG202="","",I202-H202)</f>
         <v/>
       </c>
       <c r="G202" s="67"/>
       <c r="H202" s="65"/>
-      <c r="I202" s="66" t="str" cm="1">
+      <c r="I202" s="66" cm="1" t="str">
         <f t="array" ref="I202">IF(AG202="","",P202-K202)</f>
         <v/>
       </c>
@@ -39134,7 +39134,7 @@
       <c r="M202" s="68"/>
       <c r="N202" s="68"/>
       <c r="O202" s="68"/>
-      <c r="P202" s="66" t="str" cm="1">
+      <c r="P202" s="66" cm="1" t="str">
         <f t="array" ref="P202">IF(AG202="","",AC202-R202-Q202)</f>
         <v/>
       </c>
@@ -39199,13 +39199,13 @@
       <c r="C203" s="19"/>
       <c r="D203" s="72"/>
       <c r="E203" s="71"/>
-      <c r="F203" s="82" t="str" cm="1">
+      <c r="F203" s="82" cm="1" t="str">
         <f t="array" ref="F203">IF(AG203="","",I203-H203)</f>
         <v/>
       </c>
       <c r="G203" s="67"/>
       <c r="H203" s="65"/>
-      <c r="I203" s="66" t="str" cm="1">
+      <c r="I203" s="66" cm="1" t="str">
         <f t="array" ref="I203">IF(AG203="","",P203-K203)</f>
         <v/>
       </c>
@@ -39215,7 +39215,7 @@
       <c r="M203" s="68"/>
       <c r="N203" s="68"/>
       <c r="O203" s="68"/>
-      <c r="P203" s="66" t="str" cm="1">
+      <c r="P203" s="66" cm="1" t="str">
         <f t="array" ref="P203">IF(AG203="","",AC203-R203-Q203)</f>
         <v/>
       </c>
@@ -39280,13 +39280,13 @@
       <c r="C204" s="19"/>
       <c r="D204" s="72"/>
       <c r="E204" s="71"/>
-      <c r="F204" s="82" t="str" cm="1">
+      <c r="F204" s="82" cm="1" t="str">
         <f t="array" ref="F204">IF(AG204="","",I204-H204)</f>
         <v/>
       </c>
       <c r="G204" s="67"/>
       <c r="H204" s="65"/>
-      <c r="I204" s="66" t="str" cm="1">
+      <c r="I204" s="66" cm="1" t="str">
         <f t="array" ref="I204">IF(AG204="","",P204-K204)</f>
         <v/>
       </c>
@@ -39296,7 +39296,7 @@
       <c r="M204" s="68"/>
       <c r="N204" s="68"/>
       <c r="O204" s="68"/>
-      <c r="P204" s="66" t="str" cm="1">
+      <c r="P204" s="66" cm="1" t="str">
         <f t="array" ref="P204">IF(AG204="","",AC204-R204-Q204)</f>
         <v/>
       </c>
@@ -39361,13 +39361,13 @@
       <c r="C205" s="19"/>
       <c r="D205" s="72"/>
       <c r="E205" s="71"/>
-      <c r="F205" s="82" t="str" cm="1">
+      <c r="F205" s="82" cm="1" t="str">
         <f t="array" ref="F205">IF(AG205="","",I205-H205)</f>
         <v/>
       </c>
       <c r="G205" s="67"/>
       <c r="H205" s="65"/>
-      <c r="I205" s="66" t="str" cm="1">
+      <c r="I205" s="66" cm="1" t="str">
         <f t="array" ref="I205">IF(AG205="","",P205-K205)</f>
         <v/>
       </c>
@@ -39377,7 +39377,7 @@
       <c r="M205" s="68"/>
       <c r="N205" s="68"/>
       <c r="O205" s="68"/>
-      <c r="P205" s="66" t="str" cm="1">
+      <c r="P205" s="66" cm="1" t="str">
         <f t="array" ref="P205">IF(AG205="","",AC205-R205-Q205)</f>
         <v/>
       </c>
@@ -39442,13 +39442,13 @@
       <c r="C206" s="19"/>
       <c r="D206" s="72"/>
       <c r="E206" s="71"/>
-      <c r="F206" s="82" t="str" cm="1">
+      <c r="F206" s="82" cm="1" t="str">
         <f t="array" ref="F206">IF(AG206="","",I206-H206)</f>
         <v/>
       </c>
       <c r="G206" s="67"/>
       <c r="H206" s="65"/>
-      <c r="I206" s="66" t="str" cm="1">
+      <c r="I206" s="66" cm="1" t="str">
         <f t="array" ref="I206">IF(AG206="","",P206-K206)</f>
         <v/>
       </c>
@@ -39458,7 +39458,7 @@
       <c r="M206" s="68"/>
       <c r="N206" s="68"/>
       <c r="O206" s="68"/>
-      <c r="P206" s="66" t="str" cm="1">
+      <c r="P206" s="66" cm="1" t="str">
         <f t="array" ref="P206">IF(AG206="","",AC206-R206-Q206)</f>
         <v/>
       </c>
@@ -39523,13 +39523,13 @@
       <c r="C207" s="19"/>
       <c r="D207" s="72"/>
       <c r="E207" s="71"/>
-      <c r="F207" s="82" t="str" cm="1">
+      <c r="F207" s="82" cm="1" t="str">
         <f t="array" ref="F207">IF(AG207="","",I207-H207)</f>
         <v/>
       </c>
       <c r="G207" s="67"/>
       <c r="H207" s="65"/>
-      <c r="I207" s="66" t="str" cm="1">
+      <c r="I207" s="66" cm="1" t="str">
         <f t="array" ref="I207">IF(AG207="","",P207-K207)</f>
         <v/>
       </c>
@@ -39539,7 +39539,7 @@
       <c r="M207" s="68"/>
       <c r="N207" s="68"/>
       <c r="O207" s="68"/>
-      <c r="P207" s="66" t="str" cm="1">
+      <c r="P207" s="66" cm="1" t="str">
         <f t="array" ref="P207">IF(AG207="","",AC207-R207-Q207)</f>
         <v/>
       </c>
@@ -39604,13 +39604,13 @@
       <c r="C208" s="19"/>
       <c r="D208" s="72"/>
       <c r="E208" s="71"/>
-      <c r="F208" s="82" t="str" cm="1">
+      <c r="F208" s="82" cm="1" t="str">
         <f t="array" ref="F208">IF(AG208="","",I208-H208)</f>
         <v/>
       </c>
       <c r="G208" s="67"/>
       <c r="H208" s="65"/>
-      <c r="I208" s="66" t="str" cm="1">
+      <c r="I208" s="66" cm="1" t="str">
         <f t="array" ref="I208">IF(AG208="","",P208-K208)</f>
         <v/>
       </c>
@@ -39620,7 +39620,7 @@
       <c r="M208" s="68"/>
       <c r="N208" s="68"/>
       <c r="O208" s="68"/>
-      <c r="P208" s="66" t="str" cm="1">
+      <c r="P208" s="66" cm="1" t="str">
         <f t="array" ref="P208">IF(AG208="","",AC208-R208-Q208)</f>
         <v/>
       </c>
@@ -39685,13 +39685,13 @@
       <c r="C209" s="19"/>
       <c r="D209" s="72"/>
       <c r="E209" s="71"/>
-      <c r="F209" s="82" t="str" cm="1">
+      <c r="F209" s="82" cm="1" t="str">
         <f t="array" ref="F209">IF(AG209="","",I209-H209)</f>
         <v/>
       </c>
       <c r="G209" s="67"/>
       <c r="H209" s="65"/>
-      <c r="I209" s="66" t="str" cm="1">
+      <c r="I209" s="66" cm="1" t="str">
         <f t="array" ref="I209">IF(AG209="","",P209-K209)</f>
         <v/>
       </c>
@@ -39701,7 +39701,7 @@
       <c r="M209" s="68"/>
       <c r="N209" s="68"/>
       <c r="O209" s="68"/>
-      <c r="P209" s="66" t="str" cm="1">
+      <c r="P209" s="66" cm="1" t="str">
         <f t="array" ref="P209">IF(AG209="","",AC209-R209-Q209)</f>
         <v/>
       </c>
@@ -39766,13 +39766,13 @@
       <c r="C210" s="19"/>
       <c r="D210" s="72"/>
       <c r="E210" s="71"/>
-      <c r="F210" s="82" t="str" cm="1">
+      <c r="F210" s="82" cm="1" t="str">
         <f t="array" ref="F210">IF(AG210="","",I210-H210)</f>
         <v/>
       </c>
       <c r="G210" s="67"/>
       <c r="H210" s="65"/>
-      <c r="I210" s="66" t="str" cm="1">
+      <c r="I210" s="66" cm="1" t="str">
         <f t="array" ref="I210">IF(AG210="","",P210-K210)</f>
         <v/>
       </c>
@@ -39782,7 +39782,7 @@
       <c r="M210" s="68"/>
       <c r="N210" s="68"/>
       <c r="O210" s="68"/>
-      <c r="P210" s="66" t="str" cm="1">
+      <c r="P210" s="66" cm="1" t="str">
         <f t="array" ref="P210">IF(AG210="","",AC210-R210-Q210)</f>
         <v/>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -22936,7 +22936,9 @@
         <f t="shared" ref="F12:F26" si="1">IF(AG12="","",I12-H12)</f>
         <v>46357</v>
       </c>
-      <c r="G12" s="67"/>
+      <c r="G12" s="67">
+        <v>46301</v>
+      </c>
       <c r="H12" s="65">
         <v>7</v>
       </c>
@@ -22944,7 +22946,9 @@
         <f t="shared" ref="I12:I26" si="2">IF(AG12="","",P12-K12)</f>
         <v>46364</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="67">
+        <v>46302</v>
+      </c>
       <c r="K12" s="65">
         <v>7</v>
       </c>
@@ -23240,7 +23244,9 @@
         <f t="shared" si="1"/>
         <v>46325</v>
       </c>
-      <c r="G15" s="67"/>
+      <c r="G15" s="67">
+        <v>46301</v>
+      </c>
       <c r="H15" s="65">
         <v>7</v>
       </c>
@@ -23248,7 +23254,9 @@
         <f t="shared" si="2"/>
         <v>46332</v>
       </c>
-      <c r="J15" s="67"/>
+      <c r="J15" s="67">
+        <v>46302</v>
+      </c>
       <c r="K15" s="65">
         <v>7</v>
       </c>
@@ -23444,7 +23452,9 @@
         <f t="shared" si="1"/>
         <v>46336</v>
       </c>
-      <c r="G17" s="67"/>
+      <c r="G17" s="67">
+        <v>46304</v>
+      </c>
       <c r="H17" s="65">
         <v>7</v>
       </c>
@@ -23846,7 +23856,9 @@
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G21" s="67"/>
+      <c r="G21" s="67">
+        <v>46301</v>
+      </c>
       <c r="H21" s="65">
         <v>7</v>
       </c>
@@ -23854,7 +23866,9 @@
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="J21" s="67"/>
+      <c r="J21" s="67">
+        <v>46302</v>
+      </c>
       <c r="K21" s="65">
         <v>7</v>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -24957,7 +24957,9 @@
       <c r="L32" s="68">
         <v>46293</v>
       </c>
-      <c r="M32" s="68"/>
+      <c r="M32" s="68">
+        <v>46297</v>
+      </c>
       <c r="N32" s="68">
         <v>46302</v>
       </c>
@@ -25327,7 +25329,9 @@
       <c r="L36" s="68">
         <v>46293</v>
       </c>
-      <c r="M36" s="68"/>
+      <c r="M36" s="68">
+        <v>46297</v>
+      </c>
       <c r="N36" s="68">
         <v>46302</v>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -9634,8 +9634,10 @@
       <c r="B19" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>71</v>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>解体範囲図（床・壁・天井）</t>
+        </is>
       </c>
       <c r="D19" s="72" cm="1">
         <f t="array" ref="D19">IF(F19="","",F19-E19)</f>
@@ -9657,7 +9659,9 @@
         <f t="array" ref="I19">IF(P19="","",P19-K19)</f>
         <v>46307</v>
       </c>
-      <c r="J19" s="67"/>
+      <c r="J19" s="67">
+        <v>46305</v>
+      </c>
       <c r="K19" s="65">
         <v>7</v>
       </c>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -40943,7 +40943,9 @@
       <c r="D12" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="102"/>
+      <c r="E12" s="102">
+        <v>46298</v>
+      </c>
       <c r="F12" s="106" cm="1">
         <f t="array" ref="F12">IF($AD12="","",$H12-$G12)</f>
         <v>46351</v>
@@ -41251,7 +41253,9 @@
       <c r="D16" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="E16" s="102"/>
+      <c r="E16" s="102">
+        <v>46294</v>
+      </c>
       <c r="F16" s="106" cm="1">
         <f t="array" ref="F16">IF($AD16="","",$H16-$G16)</f>
         <v>46330</v>
@@ -41547,7 +41551,9 @@
       <c r="D20" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="E20" s="102"/>
+      <c r="E20" s="102">
+        <v>46295</v>
+      </c>
       <c r="F20" s="106" cm="1">
         <f t="array" ref="F20">IF($AD20="","",$H20-$G20)</f>
         <v>46329</v>

--- a/図面・計画書リスト.xlsx
+++ b/図面・計画書リスト.xlsx
@@ -21664,7 +21664,6 @@
       <c r="BM159" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="CC6F" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="71">
     <mergeCell ref="A1:AH1"/>
     <mergeCell ref="C2:AH2"/>
@@ -39861,7 +39860,6 @@
       <c r="BL210" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="CC6F" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="71">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
@@ -48876,7 +48874,6 @@
       <c r="AR146" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="CC6F" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="54">
     <mergeCell ref="J1:N1"/>
     <mergeCell ref="J2:N3"/>
